--- a/data.xlsx
+++ b/data.xlsx
@@ -5742,15 +5742,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -6011,6 +6002,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19085706-475A-47B8-AC19-64F084D28E59}">
   <ds:schemaRefs>
@@ -6023,13 +6023,28 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A02432C2-097A-4B88-A372-7C95D690C5C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{952F739C-0654-4468-9DC3-FF416434CCBC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A02432C2-097A-4B88-A372-7C95D690C5C7}"/>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes.sharepoint.com/sites/DeLunaOperaes/Documentos Partilhados/GESTÃO DE FROTA/Controle de Frota - BID 2026/painel-frota-deluna-pronto-para-publicar/site_deploy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_40453C32AA65790B7DE51D384C84BAC981E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69233357-7B46-455D-93B5-95A9597A04CF}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_40453C32AA65790B7DE51D384C84BAC981E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A65D703-186D-41F9-B9DA-ED5AB1F58E41}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="219">
   <si>
     <t>Placa</t>
   </si>
@@ -61,9 +61,6 @@
     <t>RJ/ES</t>
   </si>
   <si>
-    <t>Vuc Dedicado</t>
-  </si>
-  <si>
     <t>SPRINTER 317</t>
   </si>
   <si>
@@ -677,6 +674,12 @@
   </si>
   <si>
     <t>Deluna</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Vuc Deluna</t>
   </si>
 </sst>
 </file>
@@ -1081,16 +1084,16 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2">
@@ -1099,7 +1102,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -1108,16 +1111,16 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2">
@@ -1126,7 +1129,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1135,16 +1138,16 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2">
@@ -1153,25 +1156,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
-        <v>217</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2">
@@ -1180,25 +1183,25 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
       <c r="D6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
-        <v>217</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2">
@@ -1207,25 +1210,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" t="s">
+        <v>216</v>
+      </c>
+      <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" t="s">
-        <v>217</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>13</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2">
@@ -1234,25 +1237,25 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
       </c>
       <c r="D8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F8" t="s">
         <v>12</v>
       </c>
-      <c r="E8" t="s">
-        <v>217</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>13</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2">
@@ -1261,25 +1264,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E9" t="s">
+        <v>216</v>
+      </c>
+      <c r="F9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" t="s">
-        <v>217</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2">
@@ -1288,25 +1291,25 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
         <v>26</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>27</v>
-      </c>
-      <c r="G10" t="s">
-        <v>28</v>
       </c>
       <c r="H10" s="2">
         <v>46171</v>
@@ -1317,25 +1320,25 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
         <v>26</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>27</v>
-      </c>
-      <c r="G11" t="s">
-        <v>28</v>
       </c>
       <c r="H11" s="2">
         <v>46171</v>
@@ -1346,25 +1349,25 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
         <v>31</v>
       </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
         <v>32</v>
       </c>
-      <c r="E12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>33</v>
-      </c>
-      <c r="G12" t="s">
-        <v>34</v>
       </c>
       <c r="H12" s="2">
         <v>46207</v>
@@ -1375,187 +1378,199 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>36</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
         <v>37</v>
       </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>38</v>
       </c>
-      <c r="F13" t="s">
-        <v>39</v>
-      </c>
       <c r="G13" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="I13" s="2">
         <v>46202</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
         <v>36</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
         <v>37</v>
       </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>38</v>
       </c>
-      <c r="F14" t="s">
-        <v>39</v>
-      </c>
       <c r="G14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="I14" s="2">
         <v>46202</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
         <v>36</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
         <v>37</v>
       </c>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>38</v>
       </c>
-      <c r="F15" t="s">
-        <v>39</v>
-      </c>
       <c r="G15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="I15" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
         <v>36</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" t="s">
         <v>37</v>
       </c>
-      <c r="D16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>38</v>
       </c>
-      <c r="F16" t="s">
-        <v>39</v>
-      </c>
       <c r="G16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="I16" s="2">
         <v>46202</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="I17" s="2">
         <v>46202</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
         <v>36</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
         <v>37</v>
       </c>
-      <c r="D18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>38</v>
       </c>
-      <c r="F18" t="s">
-        <v>39</v>
-      </c>
       <c r="G18" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="I18" s="2">
         <v>46202</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
         <v>36</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" t="s">
         <v>37</v>
       </c>
-      <c r="D19" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>38</v>
       </c>
-      <c r="F19" t="s">
-        <v>39</v>
-      </c>
       <c r="G19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H19" s="2">
         <v>46211</v>
@@ -1566,79 +1581,83 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
         <v>36</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
         <v>37</v>
       </c>
-      <c r="D20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>38</v>
       </c>
-      <c r="F20" t="s">
-        <v>39</v>
-      </c>
       <c r="G20" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="I20" s="2">
         <v>46202</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
         <v>36</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" t="s">
         <v>37</v>
       </c>
-      <c r="D21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>38</v>
       </c>
-      <c r="F21" t="s">
-        <v>39</v>
-      </c>
       <c r="G21" t="s">
-        <v>44</v>
-      </c>
-      <c r="H21" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="I21" s="2">
         <v>46202</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
         <v>49</v>
       </c>
-      <c r="B22" t="s">
-        <v>50</v>
-      </c>
       <c r="C22" t="s">
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" t="s">
         <v>38</v>
       </c>
-      <c r="F22" t="s">
-        <v>39</v>
-      </c>
       <c r="G22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H22" s="2">
         <v>46190</v>
@@ -1649,25 +1668,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" t="s">
         <v>38</v>
       </c>
-      <c r="F23" t="s">
-        <v>39</v>
-      </c>
       <c r="G23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H23" s="2">
         <v>46190</v>
@@ -1678,25 +1697,25 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" t="s">
         <v>38</v>
       </c>
-      <c r="F24" t="s">
-        <v>39</v>
-      </c>
       <c r="G24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H24" s="2">
         <v>46189</v>
@@ -1707,25 +1726,25 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" t="s">
         <v>38</v>
       </c>
-      <c r="F25" t="s">
-        <v>39</v>
-      </c>
       <c r="G25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H25" s="2">
         <v>46189</v>
@@ -1736,25 +1755,25 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" t="s">
         <v>38</v>
       </c>
-      <c r="F26" t="s">
-        <v>39</v>
-      </c>
       <c r="G26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H26" s="2">
         <v>46189</v>
@@ -1765,25 +1784,25 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" t="s">
         <v>38</v>
       </c>
-      <c r="F27" t="s">
-        <v>39</v>
-      </c>
       <c r="G27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H27" s="2">
         <v>46189</v>
@@ -1794,25 +1813,25 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" t="s">
         <v>38</v>
       </c>
-      <c r="F28" t="s">
-        <v>39</v>
-      </c>
       <c r="G28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H28" s="2">
         <v>46190</v>
@@ -1823,25 +1842,25 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E29" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" t="s">
         <v>38</v>
       </c>
-      <c r="F29" t="s">
-        <v>39</v>
-      </c>
       <c r="G29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H29" s="2">
         <v>46190</v>
@@ -1852,25 +1871,25 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" t="s">
         <v>38</v>
       </c>
-      <c r="F30" t="s">
-        <v>39</v>
-      </c>
       <c r="G30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H30" s="2">
         <v>46189</v>
@@ -1881,25 +1900,25 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" t="s">
         <v>38</v>
       </c>
-      <c r="F31" t="s">
-        <v>39</v>
-      </c>
       <c r="G31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H31" s="2">
         <v>46189</v>
@@ -1910,25 +1929,25 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" t="s">
         <v>38</v>
       </c>
-      <c r="F32" t="s">
-        <v>39</v>
-      </c>
       <c r="G32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H32" s="2">
         <v>46190</v>
@@ -1939,25 +1958,25 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
         <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" t="s">
         <v>38</v>
       </c>
-      <c r="F33" t="s">
-        <v>39</v>
-      </c>
       <c r="G33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H33" s="2">
         <v>46190</v>
@@ -1968,25 +1987,25 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E34" t="s">
+        <v>37</v>
+      </c>
+      <c r="F34" t="s">
         <v>38</v>
       </c>
-      <c r="F34" t="s">
-        <v>39</v>
-      </c>
       <c r="G34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H34" s="2">
         <v>46190</v>
@@ -1997,25 +2016,25 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E35" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" t="s">
         <v>38</v>
       </c>
-      <c r="F35" t="s">
-        <v>39</v>
-      </c>
       <c r="G35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H35" s="2">
         <v>46190</v>
@@ -2026,25 +2045,25 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E36" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" t="s">
         <v>38</v>
       </c>
-      <c r="F36" t="s">
-        <v>39</v>
-      </c>
       <c r="G36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H36" s="2">
         <v>46190</v>
@@ -2055,25 +2074,25 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" t="s">
         <v>65</v>
       </c>
-      <c r="B37" t="s">
-        <v>66</v>
-      </c>
       <c r="C37" t="s">
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E37" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" t="s">
         <v>38</v>
       </c>
-      <c r="F37" t="s">
-        <v>39</v>
-      </c>
       <c r="G37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H37" s="2">
         <v>46209</v>
@@ -2084,25 +2103,25 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C38" t="s">
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E38" t="s">
+        <v>37</v>
+      </c>
+      <c r="F38" t="s">
         <v>38</v>
       </c>
-      <c r="F38" t="s">
-        <v>39</v>
-      </c>
       <c r="G38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H38" s="2">
         <v>46211</v>
@@ -2113,25 +2132,25 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E39" t="s">
+        <v>37</v>
+      </c>
+      <c r="F39" t="s">
         <v>38</v>
       </c>
-      <c r="F39" t="s">
-        <v>39</v>
-      </c>
       <c r="G39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H39" s="2">
         <v>46209</v>
@@ -2142,25 +2161,25 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E40" t="s">
+        <v>37</v>
+      </c>
+      <c r="F40" t="s">
         <v>38</v>
       </c>
-      <c r="F40" t="s">
-        <v>39</v>
-      </c>
       <c r="G40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H40" s="2">
         <v>46210</v>
@@ -2171,52 +2190,54 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C41" t="s">
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E41" t="s">
+        <v>37</v>
+      </c>
+      <c r="F41" t="s">
         <v>38</v>
       </c>
-      <c r="F41" t="s">
-        <v>39</v>
-      </c>
       <c r="G41" t="s">
-        <v>28</v>
-      </c>
-      <c r="H41" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="I41" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E42" t="s">
+        <v>37</v>
+      </c>
+      <c r="F42" t="s">
         <v>38</v>
       </c>
-      <c r="F42" t="s">
-        <v>39</v>
-      </c>
       <c r="G42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H42" s="2">
         <v>46209</v>
@@ -2227,25 +2248,25 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E43" t="s">
+        <v>37</v>
+      </c>
+      <c r="F43" t="s">
         <v>38</v>
       </c>
-      <c r="F43" t="s">
-        <v>39</v>
-      </c>
       <c r="G43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H43" s="2">
         <v>46209</v>
@@ -2256,52 +2277,54 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E44" t="s">
+        <v>37</v>
+      </c>
+      <c r="F44" t="s">
         <v>38</v>
       </c>
-      <c r="F44" t="s">
-        <v>39</v>
-      </c>
       <c r="G44" t="s">
-        <v>28</v>
-      </c>
-      <c r="H44" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="I44" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C45" t="s">
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E45" t="s">
+        <v>37</v>
+      </c>
+      <c r="F45" t="s">
         <v>38</v>
       </c>
-      <c r="F45" t="s">
-        <v>39</v>
-      </c>
       <c r="G45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H45" s="2">
         <v>46211</v>
@@ -2312,25 +2335,25 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E46" t="s">
+        <v>37</v>
+      </c>
+      <c r="F46" t="s">
         <v>38</v>
       </c>
-      <c r="F46" t="s">
-        <v>39</v>
-      </c>
       <c r="G46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H46" s="2">
         <v>46211</v>
@@ -2341,25 +2364,25 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C47" t="s">
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E47" t="s">
+        <v>37</v>
+      </c>
+      <c r="F47" t="s">
         <v>38</v>
       </c>
-      <c r="F47" t="s">
-        <v>39</v>
-      </c>
       <c r="G47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H47" s="2">
         <v>46211</v>
@@ -2370,52 +2393,54 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C48" t="s">
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E48" t="s">
+        <v>37</v>
+      </c>
+      <c r="F48" t="s">
         <v>38</v>
       </c>
-      <c r="F48" t="s">
-        <v>39</v>
-      </c>
       <c r="G48" t="s">
-        <v>34</v>
-      </c>
-      <c r="H48" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="I48" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C49" t="s">
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E49" t="s">
+        <v>37</v>
+      </c>
+      <c r="F49" t="s">
         <v>38</v>
       </c>
-      <c r="F49" t="s">
-        <v>39</v>
-      </c>
       <c r="G49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H49" s="2">
         <v>46217</v>
@@ -2426,7 +2451,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
@@ -2435,16 +2460,16 @@
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E50" t="s">
+        <v>37</v>
+      </c>
+      <c r="F50" t="s">
         <v>38</v>
       </c>
-      <c r="F50" t="s">
-        <v>39</v>
-      </c>
       <c r="G50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H50" s="2">
         <v>46190</v>
@@ -2455,7 +2480,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
@@ -2464,16 +2489,16 @@
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E51" t="s">
+        <v>37</v>
+      </c>
+      <c r="F51" t="s">
         <v>38</v>
       </c>
-      <c r="F51" t="s">
-        <v>39</v>
-      </c>
       <c r="G51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H51" s="2">
         <v>46190</v>
@@ -2484,7 +2509,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
@@ -2493,16 +2518,16 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E52" t="s">
+        <v>37</v>
+      </c>
+      <c r="F52" t="s">
         <v>38</v>
       </c>
-      <c r="F52" t="s">
-        <v>39</v>
-      </c>
       <c r="G52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H52" s="2">
         <v>46190</v>
@@ -2513,7 +2538,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
@@ -2522,16 +2547,16 @@
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F53" t="s">
         <v>38</v>
       </c>
-      <c r="F53" t="s">
-        <v>39</v>
-      </c>
       <c r="G53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H53" s="2">
         <v>46191</v>
@@ -2542,7 +2567,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
@@ -2551,16 +2576,16 @@
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F54" t="s">
         <v>38</v>
       </c>
-      <c r="F54" t="s">
-        <v>39</v>
-      </c>
       <c r="G54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H54" s="2">
         <v>46191</v>
@@ -2571,7 +2596,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
@@ -2580,16 +2605,16 @@
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E55" t="s">
+        <v>37</v>
+      </c>
+      <c r="F55" t="s">
         <v>38</v>
       </c>
-      <c r="F55" t="s">
-        <v>39</v>
-      </c>
       <c r="G55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H55" s="2">
         <v>46190</v>
@@ -2600,7 +2625,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
@@ -2609,16 +2634,16 @@
         <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E56" t="s">
+        <v>37</v>
+      </c>
+      <c r="F56" t="s">
         <v>38</v>
       </c>
-      <c r="F56" t="s">
-        <v>39</v>
-      </c>
       <c r="G56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H56" s="2">
         <v>46191</v>
@@ -2629,7 +2654,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
@@ -2638,16 +2663,16 @@
         <v>11</v>
       </c>
       <c r="D57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E57" t="s">
+        <v>37</v>
+      </c>
+      <c r="F57" t="s">
         <v>38</v>
       </c>
-      <c r="F57" t="s">
-        <v>39</v>
-      </c>
       <c r="G57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H57" s="2">
         <v>46191</v>
@@ -2658,7 +2683,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
@@ -2667,16 +2692,16 @@
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E58" t="s">
+        <v>37</v>
+      </c>
+      <c r="F58" t="s">
         <v>38</v>
       </c>
-      <c r="F58" t="s">
-        <v>39</v>
-      </c>
       <c r="G58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H58" s="2">
         <v>46193</v>
@@ -2687,7 +2712,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B59" t="s">
         <v>10</v>
@@ -2696,16 +2721,16 @@
         <v>11</v>
       </c>
       <c r="D59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E59" t="s">
+        <v>37</v>
+      </c>
+      <c r="F59" t="s">
         <v>38</v>
       </c>
-      <c r="F59" t="s">
-        <v>39</v>
-      </c>
       <c r="G59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H59" s="2">
         <v>46190</v>
@@ -2716,7 +2741,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B60" t="s">
         <v>10</v>
@@ -2725,16 +2750,16 @@
         <v>11</v>
       </c>
       <c r="D60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E60" t="s">
+        <v>37</v>
+      </c>
+      <c r="F60" t="s">
         <v>38</v>
       </c>
-      <c r="F60" t="s">
-        <v>39</v>
-      </c>
       <c r="G60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H60" s="2">
         <v>46191</v>
@@ -2745,7 +2770,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B61" t="s">
         <v>10</v>
@@ -2754,16 +2779,16 @@
         <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E61" t="s">
+        <v>37</v>
+      </c>
+      <c r="F61" t="s">
         <v>38</v>
       </c>
-      <c r="F61" t="s">
-        <v>39</v>
-      </c>
       <c r="G61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H61" s="2">
         <v>46190</v>
@@ -2774,7 +2799,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
@@ -2783,16 +2808,16 @@
         <v>11</v>
       </c>
       <c r="D62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E62" t="s">
+        <v>37</v>
+      </c>
+      <c r="F62" t="s">
         <v>38</v>
       </c>
-      <c r="F62" t="s">
-        <v>39</v>
-      </c>
       <c r="G62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H62" s="2">
         <v>46190</v>
@@ -2803,25 +2828,25 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63" t="s">
+        <v>49</v>
+      </c>
+      <c r="C63" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" t="s">
         <v>92</v>
       </c>
-      <c r="B63" t="s">
-        <v>50</v>
-      </c>
-      <c r="C63" t="s">
-        <v>11</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>93</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>94</v>
       </c>
-      <c r="F63" t="s">
-        <v>95</v>
-      </c>
       <c r="G63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H63" s="2">
         <v>46171</v>
@@ -2832,25 +2857,25 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>95</v>
+      </c>
+      <c r="B64" t="s">
+        <v>49</v>
+      </c>
+      <c r="C64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" t="s">
+        <v>92</v>
+      </c>
+      <c r="E64" t="s">
+        <v>93</v>
+      </c>
+      <c r="F64" t="s">
         <v>96</v>
       </c>
-      <c r="B64" t="s">
-        <v>50</v>
-      </c>
-      <c r="C64" t="s">
-        <v>11</v>
-      </c>
-      <c r="D64" t="s">
-        <v>93</v>
-      </c>
-      <c r="E64" t="s">
-        <v>94</v>
-      </c>
-      <c r="F64" t="s">
-        <v>97</v>
-      </c>
       <c r="G64" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H64" s="2">
         <v>46171</v>
@@ -2861,25 +2886,25 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B65" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C65" t="s">
         <v>11</v>
       </c>
       <c r="D65" t="s">
+        <v>92</v>
+      </c>
+      <c r="E65" t="s">
         <v>93</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>94</v>
       </c>
-      <c r="F65" t="s">
-        <v>95</v>
-      </c>
       <c r="G65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H65" s="2">
         <v>46171</v>
@@ -2890,25 +2915,25 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C66" t="s">
         <v>11</v>
       </c>
       <c r="D66" t="s">
+        <v>92</v>
+      </c>
+      <c r="E66" t="s">
         <v>93</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>94</v>
       </c>
-      <c r="F66" t="s">
-        <v>95</v>
-      </c>
       <c r="G66" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H66" s="2">
         <v>46170</v>
@@ -2919,25 +2944,25 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B67" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
       </c>
       <c r="D67" t="s">
+        <v>92</v>
+      </c>
+      <c r="E67" t="s">
         <v>93</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>94</v>
       </c>
-      <c r="F67" t="s">
-        <v>95</v>
-      </c>
       <c r="G67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H67" s="2">
         <v>46171</v>
@@ -2948,25 +2973,25 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
       </c>
       <c r="D68" t="s">
+        <v>92</v>
+      </c>
+      <c r="E68" t="s">
         <v>93</v>
       </c>
-      <c r="E68" t="s">
-        <v>94</v>
-      </c>
       <c r="F68" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H68" s="2">
         <v>46154</v>
@@ -2977,25 +3002,25 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
       </c>
       <c r="D69" t="s">
+        <v>92</v>
+      </c>
+      <c r="E69" t="s">
         <v>93</v>
       </c>
-      <c r="E69" t="s">
-        <v>94</v>
-      </c>
       <c r="F69" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H69" s="2">
         <v>46154</v>
@@ -3006,25 +3031,25 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
       </c>
       <c r="D70" t="s">
+        <v>92</v>
+      </c>
+      <c r="E70" t="s">
         <v>93</v>
       </c>
-      <c r="E70" t="s">
-        <v>94</v>
-      </c>
       <c r="F70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H70" s="2">
         <v>46154</v>
@@ -3035,25 +3060,25 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
       </c>
       <c r="D71" t="s">
+        <v>92</v>
+      </c>
+      <c r="E71" t="s">
         <v>93</v>
       </c>
-      <c r="E71" t="s">
-        <v>94</v>
-      </c>
       <c r="F71" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G71" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H71" s="2">
         <v>46154</v>
@@ -3064,25 +3089,25 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
       </c>
       <c r="D72" t="s">
+        <v>92</v>
+      </c>
+      <c r="E72" t="s">
         <v>93</v>
       </c>
-      <c r="E72" t="s">
-        <v>94</v>
-      </c>
       <c r="F72" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H72" s="2">
         <v>46154</v>
@@ -3093,25 +3118,25 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>105</v>
+      </c>
+      <c r="B73" t="s">
         <v>106</v>
       </c>
-      <c r="B73" t="s">
-        <v>107</v>
-      </c>
       <c r="C73" t="s">
         <v>11</v>
       </c>
       <c r="D73" t="s">
+        <v>92</v>
+      </c>
+      <c r="E73" t="s">
         <v>93</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>94</v>
       </c>
-      <c r="F73" t="s">
-        <v>95</v>
-      </c>
       <c r="G73" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H73" s="2">
         <v>46253</v>
@@ -3122,25 +3147,25 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B74" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C74" t="s">
         <v>11</v>
       </c>
       <c r="D74" t="s">
+        <v>92</v>
+      </c>
+      <c r="E74" t="s">
         <v>93</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>94</v>
       </c>
-      <c r="F74" t="s">
-        <v>95</v>
-      </c>
       <c r="G74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H74" s="2">
         <v>46255</v>
@@ -3151,25 +3176,25 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C75" t="s">
         <v>11</v>
       </c>
       <c r="D75" t="s">
+        <v>92</v>
+      </c>
+      <c r="E75" t="s">
         <v>93</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>94</v>
       </c>
-      <c r="F75" t="s">
-        <v>95</v>
-      </c>
       <c r="G75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H75" s="2">
         <v>46255</v>
@@ -3180,25 +3205,25 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C76" t="s">
         <v>11</v>
       </c>
       <c r="D76" t="s">
+        <v>92</v>
+      </c>
+      <c r="E76" t="s">
         <v>93</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>94</v>
       </c>
-      <c r="F76" t="s">
-        <v>95</v>
-      </c>
       <c r="G76" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H76" s="2">
         <v>46261</v>
@@ -3209,25 +3234,25 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B77" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C77" t="s">
         <v>11</v>
       </c>
       <c r="D77" t="s">
+        <v>92</v>
+      </c>
+      <c r="E77" t="s">
         <v>93</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>94</v>
       </c>
-      <c r="F77" t="s">
-        <v>95</v>
-      </c>
       <c r="G77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H77" s="2">
         <v>46261</v>
@@ -3238,25 +3263,25 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B78" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C78" t="s">
         <v>11</v>
       </c>
       <c r="D78" t="s">
+        <v>92</v>
+      </c>
+      <c r="E78" t="s">
         <v>93</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>94</v>
       </c>
-      <c r="F78" t="s">
-        <v>95</v>
-      </c>
       <c r="G78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H78" s="2">
         <v>46254</v>
@@ -3267,25 +3292,25 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C79" t="s">
         <v>11</v>
       </c>
       <c r="D79" t="s">
+        <v>92</v>
+      </c>
+      <c r="E79" t="s">
         <v>93</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>94</v>
       </c>
-      <c r="F79" t="s">
-        <v>95</v>
-      </c>
       <c r="G79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H79" s="2">
         <v>46261</v>
@@ -3296,52 +3321,54 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C80" t="s">
         <v>11</v>
       </c>
       <c r="D80" t="s">
+        <v>92</v>
+      </c>
+      <c r="E80" t="s">
         <v>93</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>94</v>
       </c>
-      <c r="F80" t="s">
-        <v>95</v>
-      </c>
       <c r="G80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H80" s="2">
         <v>46269</v>
       </c>
-      <c r="I80" s="2"/>
+      <c r="I80" s="2">
+        <v>46269</v>
+      </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C81" t="s">
         <v>11</v>
       </c>
       <c r="D81" t="s">
+        <v>92</v>
+      </c>
+      <c r="E81" t="s">
         <v>93</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>94</v>
       </c>
-      <c r="F81" t="s">
-        <v>95</v>
-      </c>
       <c r="G81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H81" s="2">
         <v>46261</v>
@@ -3352,25 +3379,25 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B82" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
       </c>
       <c r="D82" t="s">
+        <v>92</v>
+      </c>
+      <c r="E82" t="s">
         <v>93</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>94</v>
       </c>
-      <c r="F82" t="s">
-        <v>95</v>
-      </c>
       <c r="G82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H82" s="2">
         <v>46262</v>
@@ -3381,25 +3408,25 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C83" t="s">
         <v>11</v>
       </c>
       <c r="D83" t="s">
+        <v>92</v>
+      </c>
+      <c r="E83" t="s">
         <v>93</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>94</v>
       </c>
-      <c r="F83" t="s">
-        <v>95</v>
-      </c>
       <c r="G83" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H83" s="2">
         <v>46185</v>
@@ -3410,25 +3437,25 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C84" t="s">
         <v>11</v>
       </c>
       <c r="D84" t="s">
+        <v>92</v>
+      </c>
+      <c r="E84" t="s">
         <v>93</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>94</v>
       </c>
-      <c r="F84" t="s">
-        <v>95</v>
-      </c>
       <c r="G84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H84" s="2">
         <v>46182</v>
@@ -3439,25 +3466,25 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C85" t="s">
         <v>11</v>
       </c>
       <c r="D85" t="s">
+        <v>92</v>
+      </c>
+      <c r="E85" t="s">
         <v>93</v>
       </c>
-      <c r="E85" t="s">
-        <v>94</v>
-      </c>
       <c r="F85" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H85" s="2">
         <v>46185</v>
@@ -3468,25 +3495,25 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B86" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C86" t="s">
         <v>11</v>
       </c>
       <c r="D86" t="s">
+        <v>92</v>
+      </c>
+      <c r="E86" t="s">
         <v>93</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>94</v>
       </c>
-      <c r="F86" t="s">
-        <v>95</v>
-      </c>
       <c r="G86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H86" s="2">
         <v>46148</v>
@@ -3497,25 +3524,25 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B87" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C87" t="s">
         <v>11</v>
       </c>
       <c r="D87" t="s">
+        <v>92</v>
+      </c>
+      <c r="E87" t="s">
         <v>93</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>94</v>
       </c>
-      <c r="F87" t="s">
-        <v>95</v>
-      </c>
       <c r="G87" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H87" s="2">
         <v>46261</v>
@@ -3526,25 +3553,25 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C88" t="s">
         <v>11</v>
       </c>
       <c r="D88" t="s">
+        <v>92</v>
+      </c>
+      <c r="E88" t="s">
         <v>93</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>94</v>
       </c>
-      <c r="F88" t="s">
-        <v>95</v>
-      </c>
       <c r="G88" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H88" s="2">
         <v>46254</v>
@@ -3555,25 +3582,25 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>122</v>
+      </c>
+      <c r="B89" t="s">
         <v>123</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
+        <v>36</v>
+      </c>
+      <c r="D89" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89" t="s">
         <v>124</v>
       </c>
-      <c r="C89" t="s">
-        <v>37</v>
-      </c>
-      <c r="D89" t="s">
-        <v>25</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>125</v>
       </c>
-      <c r="F89" t="s">
-        <v>126</v>
-      </c>
       <c r="G89" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H89" s="2">
         <v>46199</v>
@@ -3584,25 +3611,25 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B90" t="s">
+        <v>123</v>
+      </c>
+      <c r="C90" t="s">
+        <v>36</v>
+      </c>
+      <c r="D90" t="s">
+        <v>24</v>
+      </c>
+      <c r="E90" t="s">
         <v>124</v>
       </c>
-      <c r="C90" t="s">
-        <v>37</v>
-      </c>
-      <c r="D90" t="s">
-        <v>25</v>
-      </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>125</v>
       </c>
-      <c r="F90" t="s">
-        <v>126</v>
-      </c>
       <c r="G90" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H90" s="2">
         <v>46199</v>
@@ -3613,25 +3640,25 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B91" t="s">
+        <v>123</v>
+      </c>
+      <c r="C91" t="s">
+        <v>36</v>
+      </c>
+      <c r="D91" t="s">
+        <v>24</v>
+      </c>
+      <c r="E91" t="s">
         <v>124</v>
       </c>
-      <c r="C91" t="s">
-        <v>37</v>
-      </c>
-      <c r="D91" t="s">
-        <v>25</v>
-      </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>125</v>
       </c>
-      <c r="F91" t="s">
-        <v>126</v>
-      </c>
       <c r="G91" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H91" s="2">
         <v>46184</v>
@@ -3642,25 +3669,25 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B92" t="s">
+        <v>123</v>
+      </c>
+      <c r="C92" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" t="s">
+        <v>24</v>
+      </c>
+      <c r="E92" t="s">
         <v>124</v>
       </c>
-      <c r="C92" t="s">
-        <v>37</v>
-      </c>
-      <c r="D92" t="s">
-        <v>25</v>
-      </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>125</v>
       </c>
-      <c r="F92" t="s">
-        <v>126</v>
-      </c>
       <c r="G92" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H92" s="2">
         <v>46176</v>
@@ -3671,7 +3698,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B93" t="s">
         <v>10</v>
@@ -3680,16 +3707,16 @@
         <v>11</v>
       </c>
       <c r="D93" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E93" t="s">
+        <v>124</v>
+      </c>
+      <c r="F93" t="s">
         <v>125</v>
       </c>
-      <c r="F93" t="s">
-        <v>126</v>
-      </c>
       <c r="G93" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H93" s="2">
         <v>46218</v>
@@ -3700,7 +3727,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B94" t="s">
         <v>10</v>
@@ -3709,16 +3736,16 @@
         <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E94" t="s">
+        <v>124</v>
+      </c>
+      <c r="F94" t="s">
         <v>125</v>
       </c>
-      <c r="F94" t="s">
-        <v>126</v>
-      </c>
       <c r="G94" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H94" s="2">
         <v>46218</v>
@@ -3729,7 +3756,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B95" t="s">
         <v>10</v>
@@ -3738,16 +3765,16 @@
         <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E95" t="s">
+        <v>124</v>
+      </c>
+      <c r="F95" t="s">
         <v>125</v>
       </c>
-      <c r="F95" t="s">
-        <v>126</v>
-      </c>
       <c r="G95" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H95" s="2">
         <v>46218</v>
@@ -3758,7 +3785,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B96" t="s">
         <v>10</v>
@@ -3767,16 +3794,16 @@
         <v>11</v>
       </c>
       <c r="D96" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E96" t="s">
+        <v>124</v>
+      </c>
+      <c r="F96" t="s">
         <v>125</v>
       </c>
-      <c r="F96" t="s">
-        <v>126</v>
-      </c>
       <c r="G96" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H96" s="2">
         <v>46218</v>
@@ -3787,7 +3814,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B97" t="s">
         <v>10</v>
@@ -3796,16 +3823,16 @@
         <v>11</v>
       </c>
       <c r="D97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E97" t="s">
+        <v>124</v>
+      </c>
+      <c r="F97" t="s">
         <v>125</v>
       </c>
-      <c r="F97" t="s">
-        <v>126</v>
-      </c>
       <c r="G97" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H97" s="2">
         <v>46218</v>
@@ -3816,7 +3843,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B98" t="s">
         <v>10</v>
@@ -3825,16 +3852,16 @@
         <v>11</v>
       </c>
       <c r="D98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E98" t="s">
+        <v>124</v>
+      </c>
+      <c r="F98" t="s">
         <v>125</v>
       </c>
-      <c r="F98" t="s">
-        <v>126</v>
-      </c>
       <c r="G98" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H98" s="2">
         <v>46218</v>
@@ -3845,25 +3872,25 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>135</v>
+      </c>
+      <c r="B99" t="s">
+        <v>123</v>
+      </c>
+      <c r="C99" t="s">
+        <v>36</v>
+      </c>
+      <c r="D99" t="s">
+        <v>24</v>
+      </c>
+      <c r="E99" t="s">
+        <v>124</v>
+      </c>
+      <c r="F99" t="s">
+        <v>125</v>
+      </c>
+      <c r="G99" t="s">
         <v>136</v>
-      </c>
-      <c r="B99" t="s">
-        <v>124</v>
-      </c>
-      <c r="C99" t="s">
-        <v>37</v>
-      </c>
-      <c r="D99" t="s">
-        <v>25</v>
-      </c>
-      <c r="E99" t="s">
-        <v>125</v>
-      </c>
-      <c r="F99" t="s">
-        <v>126</v>
-      </c>
-      <c r="G99" t="s">
-        <v>137</v>
       </c>
       <c r="H99" s="2">
         <v>46220</v>
@@ -3874,25 +3901,25 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C100" t="s">
+        <v>36</v>
+      </c>
+      <c r="D100" t="s">
+        <v>24</v>
+      </c>
+      <c r="E100" t="s">
         <v>124</v>
       </c>
-      <c r="C100" t="s">
-        <v>37</v>
-      </c>
-      <c r="D100" t="s">
-        <v>25</v>
-      </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>125</v>
       </c>
-      <c r="F100" t="s">
-        <v>126</v>
-      </c>
       <c r="G100" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H100" s="2">
         <v>46220</v>
@@ -3903,25 +3930,25 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B101" t="s">
+        <v>123</v>
+      </c>
+      <c r="C101" t="s">
+        <v>36</v>
+      </c>
+      <c r="D101" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101" t="s">
         <v>124</v>
       </c>
-      <c r="C101" t="s">
-        <v>37</v>
-      </c>
-      <c r="D101" t="s">
-        <v>25</v>
-      </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>125</v>
       </c>
-      <c r="F101" t="s">
-        <v>126</v>
-      </c>
       <c r="G101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H101" s="2">
         <v>46220</v>
@@ -3932,25 +3959,25 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>139</v>
+      </c>
+      <c r="B102" t="s">
+        <v>123</v>
+      </c>
+      <c r="C102" t="s">
+        <v>36</v>
+      </c>
+      <c r="D102" t="s">
+        <v>24</v>
+      </c>
+      <c r="E102" t="s">
+        <v>124</v>
+      </c>
+      <c r="F102" t="s">
+        <v>125</v>
+      </c>
+      <c r="G102" t="s">
         <v>140</v>
-      </c>
-      <c r="B102" t="s">
-        <v>124</v>
-      </c>
-      <c r="C102" t="s">
-        <v>37</v>
-      </c>
-      <c r="D102" t="s">
-        <v>25</v>
-      </c>
-      <c r="E102" t="s">
-        <v>125</v>
-      </c>
-      <c r="F102" t="s">
-        <v>126</v>
-      </c>
-      <c r="G102" t="s">
-        <v>141</v>
       </c>
       <c r="H102" s="2">
         <v>46276</v>
@@ -3959,25 +3986,25 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B103" t="s">
+        <v>123</v>
+      </c>
+      <c r="C103" t="s">
+        <v>36</v>
+      </c>
+      <c r="D103" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103" t="s">
         <v>124</v>
       </c>
-      <c r="C103" t="s">
-        <v>37</v>
-      </c>
-      <c r="D103" t="s">
-        <v>25</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>125</v>
       </c>
-      <c r="F103" t="s">
-        <v>126</v>
-      </c>
       <c r="G103" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H103" s="2">
         <v>46276</v>
@@ -3986,25 +4013,25 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B104" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" t="s">
+        <v>36</v>
+      </c>
+      <c r="D104" t="s">
+        <v>24</v>
+      </c>
+      <c r="E104" t="s">
         <v>124</v>
       </c>
-      <c r="C104" t="s">
-        <v>37</v>
-      </c>
-      <c r="D104" t="s">
-        <v>25</v>
-      </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>125</v>
       </c>
-      <c r="F104" t="s">
-        <v>126</v>
-      </c>
       <c r="G104" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H104" s="2">
         <v>46276</v>
@@ -4013,25 +4040,25 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B105" t="s">
+        <v>123</v>
+      </c>
+      <c r="C105" t="s">
+        <v>36</v>
+      </c>
+      <c r="D105" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105" t="s">
         <v>124</v>
       </c>
-      <c r="C105" t="s">
-        <v>37</v>
-      </c>
-      <c r="D105" t="s">
-        <v>25</v>
-      </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>125</v>
       </c>
-      <c r="F105" t="s">
-        <v>126</v>
-      </c>
       <c r="G105" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H105" s="2">
         <v>46276</v>
@@ -4040,25 +4067,25 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B106" t="s">
+        <v>123</v>
+      </c>
+      <c r="C106" t="s">
+        <v>36</v>
+      </c>
+      <c r="D106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106" t="s">
         <v>124</v>
       </c>
-      <c r="C106" t="s">
-        <v>37</v>
-      </c>
-      <c r="D106" t="s">
-        <v>25</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>125</v>
       </c>
-      <c r="F106" t="s">
-        <v>126</v>
-      </c>
       <c r="G106" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H106" s="2">
         <v>46276</v>
@@ -4067,25 +4094,25 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B107" t="s">
+        <v>123</v>
+      </c>
+      <c r="C107" t="s">
+        <v>36</v>
+      </c>
+      <c r="D107" t="s">
+        <v>24</v>
+      </c>
+      <c r="E107" t="s">
         <v>124</v>
       </c>
-      <c r="C107" t="s">
-        <v>37</v>
-      </c>
-      <c r="D107" t="s">
-        <v>25</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>125</v>
       </c>
-      <c r="F107" t="s">
-        <v>126</v>
-      </c>
       <c r="G107" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H107" s="2">
         <v>46276</v>
@@ -4094,25 +4121,25 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B108" t="s">
+        <v>123</v>
+      </c>
+      <c r="C108" t="s">
+        <v>36</v>
+      </c>
+      <c r="D108" t="s">
+        <v>24</v>
+      </c>
+      <c r="E108" t="s">
         <v>124</v>
       </c>
-      <c r="C108" t="s">
-        <v>37</v>
-      </c>
-      <c r="D108" t="s">
-        <v>25</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>125</v>
       </c>
-      <c r="F108" t="s">
-        <v>126</v>
-      </c>
       <c r="G108" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H108" s="2">
         <v>46276</v>
@@ -4121,25 +4148,25 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B109" t="s">
+        <v>123</v>
+      </c>
+      <c r="C109" t="s">
+        <v>36</v>
+      </c>
+      <c r="D109" t="s">
+        <v>24</v>
+      </c>
+      <c r="E109" t="s">
         <v>124</v>
       </c>
-      <c r="C109" t="s">
-        <v>37</v>
-      </c>
-      <c r="D109" t="s">
-        <v>25</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>125</v>
       </c>
-      <c r="F109" t="s">
-        <v>126</v>
-      </c>
       <c r="G109" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H109" s="2">
         <v>46276</v>
@@ -4148,7 +4175,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B110" t="s">
         <v>10</v>
@@ -4157,16 +4184,16 @@
         <v>11</v>
       </c>
       <c r="D110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E110" t="s">
+        <v>124</v>
+      </c>
+      <c r="F110" t="s">
         <v>125</v>
       </c>
-      <c r="F110" t="s">
-        <v>126</v>
-      </c>
       <c r="G110" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H110" s="2">
         <v>46295</v>
@@ -4175,25 +4202,25 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B111" t="s">
+        <v>30</v>
+      </c>
+      <c r="C111" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111" t="s">
         <v>31</v>
       </c>
-      <c r="C111" t="s">
-        <v>11</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
+        <v>25</v>
+      </c>
+      <c r="F111" t="s">
         <v>32</v>
       </c>
-      <c r="E111" t="s">
-        <v>26</v>
-      </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>33</v>
-      </c>
-      <c r="G111" t="s">
-        <v>34</v>
       </c>
       <c r="H111" s="2">
         <v>46207</v>
@@ -4204,47 +4231,47 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B112" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C112" t="s">
         <v>11</v>
       </c>
       <c r="D112" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E112" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G112" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B113" t="s">
+        <v>30</v>
+      </c>
+      <c r="C113" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" t="s">
         <v>31</v>
       </c>
-      <c r="C113" t="s">
-        <v>11</v>
-      </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
+        <v>25</v>
+      </c>
+      <c r="F113" t="s">
         <v>32</v>
       </c>
-      <c r="E113" t="s">
-        <v>26</v>
-      </c>
-      <c r="F113" t="s">
-        <v>33</v>
-      </c>
       <c r="G113" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H113" s="2">
         <v>46207</v>
@@ -4255,25 +4282,25 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B114" t="s">
+        <v>30</v>
+      </c>
+      <c r="C114" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" t="s">
         <v>31</v>
       </c>
-      <c r="C114" t="s">
-        <v>11</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
+        <v>25</v>
+      </c>
+      <c r="F114" t="s">
         <v>32</v>
       </c>
-      <c r="E114" t="s">
-        <v>26</v>
-      </c>
-      <c r="F114" t="s">
-        <v>33</v>
-      </c>
       <c r="G114" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H114" s="2">
         <v>46207</v>
@@ -4284,25 +4311,25 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>153</v>
+      </c>
+      <c r="B115" t="s">
+        <v>23</v>
+      </c>
+      <c r="C115" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" t="s">
+        <v>24</v>
+      </c>
+      <c r="E115" t="s">
+        <v>25</v>
+      </c>
+      <c r="F115" t="s">
         <v>154</v>
       </c>
-      <c r="B115" t="s">
-        <v>24</v>
-      </c>
-      <c r="C115" t="s">
-        <v>11</v>
-      </c>
-      <c r="D115" t="s">
-        <v>25</v>
-      </c>
-      <c r="E115" t="s">
-        <v>26</v>
-      </c>
-      <c r="F115" t="s">
-        <v>155</v>
-      </c>
       <c r="G115" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H115" s="2">
         <v>46207</v>
@@ -4313,25 +4340,25 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B116" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C116" t="s">
         <v>11</v>
       </c>
       <c r="D116" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F116" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G116" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H116" s="2">
         <v>46217</v>
@@ -4342,25 +4369,25 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B117" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C117" t="s">
         <v>11</v>
       </c>
       <c r="D117" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E117" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F117" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G117" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H117" s="2">
         <v>46207</v>
@@ -4371,25 +4398,25 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B118" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
       </c>
       <c r="D118" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G118" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H118" s="2">
         <v>46207</v>
@@ -4400,25 +4427,25 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B119" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C119" t="s">
         <v>11</v>
       </c>
       <c r="D119" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E119" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F119" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G119" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H119" s="2">
         <v>46207</v>
@@ -4429,25 +4456,25 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C120" t="s">
         <v>11</v>
       </c>
       <c r="D120" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E120" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G120" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H120" s="2">
         <v>46207</v>
@@ -4458,52 +4485,52 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
+        <v>160</v>
+      </c>
+      <c r="B121" t="s">
+        <v>123</v>
+      </c>
+      <c r="C121" t="s">
+        <v>36</v>
+      </c>
+      <c r="D121" t="s">
+        <v>24</v>
+      </c>
+      <c r="E121" t="s">
+        <v>25</v>
+      </c>
+      <c r="F121" t="s">
         <v>161</v>
       </c>
-      <c r="B121" t="s">
-        <v>124</v>
-      </c>
-      <c r="C121" t="s">
-        <v>37</v>
-      </c>
-      <c r="D121" t="s">
-        <v>25</v>
-      </c>
-      <c r="E121" t="s">
-        <v>26</v>
-      </c>
-      <c r="F121" t="s">
-        <v>162</v>
-      </c>
       <c r="G121" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H121" s="2">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="I121" s="2"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B122" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C122" t="s">
         <v>11</v>
       </c>
       <c r="D122" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E122" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F122" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G122" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H122" s="2">
         <v>46280</v>
@@ -4512,25 +4539,25 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B123" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C123" t="s">
         <v>11</v>
       </c>
       <c r="D123" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E123" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F123" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G123" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H123" s="2">
         <v>46280</v>
@@ -4539,25 +4566,25 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B124" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C124" t="s">
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E124" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F124" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G124" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H124" s="2">
         <v>46280</v>
@@ -4566,25 +4593,25 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B125" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C125" t="s">
         <v>11</v>
       </c>
       <c r="D125" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E125" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F125" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G125" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H125" s="2">
         <v>46280</v>
@@ -4593,25 +4620,25 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B126" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C126" t="s">
         <v>11</v>
       </c>
       <c r="D126" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E126" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F126" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G126" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H126" s="2">
         <v>46280</v>
@@ -4620,25 +4647,25 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B127" t="s">
+        <v>30</v>
+      </c>
+      <c r="C127" t="s">
+        <v>11</v>
+      </c>
+      <c r="D127" t="s">
         <v>31</v>
       </c>
-      <c r="C127" t="s">
-        <v>11</v>
-      </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
+        <v>25</v>
+      </c>
+      <c r="F127" t="s">
         <v>32</v>
       </c>
-      <c r="E127" t="s">
-        <v>26</v>
-      </c>
-      <c r="F127" t="s">
-        <v>33</v>
-      </c>
       <c r="G127" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H127" s="2">
         <v>46215</v>
@@ -4649,25 +4676,25 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B128" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C128" t="s">
         <v>11</v>
       </c>
       <c r="D128" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E128" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F128" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G128" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H128" s="2">
         <v>46207</v>
@@ -4678,25 +4705,25 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B129" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C129" t="s">
         <v>11</v>
       </c>
       <c r="D129" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E129" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F129" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G129" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H129" s="2">
         <v>46275</v>
@@ -4705,25 +4732,25 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B130" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C130" t="s">
         <v>11</v>
       </c>
       <c r="D130" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E130" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F130" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G130" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H130" s="2">
         <v>46275</v>
@@ -4732,465 +4759,465 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
+        <v>171</v>
+      </c>
+      <c r="B131" t="s">
         <v>172</v>
       </c>
-      <c r="B131" t="s">
-        <v>173</v>
-      </c>
       <c r="C131" t="s">
         <v>11</v>
       </c>
       <c r="D131" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E131" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G131" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B132" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C132" t="s">
         <v>11</v>
       </c>
       <c r="D132" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E132" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G132" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B133" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E133" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G133" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B134" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C134" t="s">
         <v>11</v>
       </c>
       <c r="D134" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E134" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G134" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C135" t="s">
         <v>11</v>
       </c>
       <c r="D135" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E135" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G135" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B136" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C136" t="s">
         <v>11</v>
       </c>
       <c r="D136" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E136" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G136" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B137" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C137" t="s">
         <v>11</v>
       </c>
       <c r="D137" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E137" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G137" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B138" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C138" t="s">
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E138" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G138" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B139" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C139" t="s">
         <v>11</v>
       </c>
       <c r="D139" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E139" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G139" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B140" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C140" t="s">
         <v>11</v>
       </c>
       <c r="D140" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E140" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G140" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B141" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C141" t="s">
         <v>11</v>
       </c>
       <c r="D141" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E141" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G141" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B142" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C142" t="s">
         <v>11</v>
       </c>
       <c r="D142" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E142" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G142" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H142" s="2"/>
       <c r="I142" s="2"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B143" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C143" t="s">
         <v>11</v>
       </c>
       <c r="D143" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E143" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G143" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H143" s="2"/>
       <c r="I143" s="2"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B144" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C144" t="s">
         <v>11</v>
       </c>
       <c r="D144" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E144" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G144" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H144" s="2"/>
       <c r="I144" s="2"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B145" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C145" t="s">
         <v>11</v>
       </c>
       <c r="D145" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E145" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G145" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B146" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C146" t="s">
         <v>11</v>
       </c>
       <c r="D146" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E146" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G146" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B147" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C147" t="s">
         <v>11</v>
       </c>
       <c r="D147" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E147" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G147" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B148" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C148" t="s">
         <v>11</v>
       </c>
       <c r="D148" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E148" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G148" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B149" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C149" t="s">
         <v>11</v>
       </c>
       <c r="D149" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E149" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G149" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B150" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C150" t="s">
         <v>11</v>
       </c>
       <c r="D150" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E150" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G150" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H150" s="2"/>
       <c r="I150" s="2"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
+        <v>192</v>
+      </c>
+      <c r="B151" t="s">
+        <v>123</v>
+      </c>
+      <c r="C151" t="s">
+        <v>36</v>
+      </c>
+      <c r="D151" t="s">
+        <v>24</v>
+      </c>
+      <c r="E151" t="s">
+        <v>25</v>
+      </c>
+      <c r="F151" t="s">
+        <v>161</v>
+      </c>
+      <c r="G151" t="s">
         <v>193</v>
-      </c>
-      <c r="B151" t="s">
-        <v>124</v>
-      </c>
-      <c r="C151" t="s">
-        <v>37</v>
-      </c>
-      <c r="D151" t="s">
-        <v>25</v>
-      </c>
-      <c r="E151" t="s">
-        <v>26</v>
-      </c>
-      <c r="F151" t="s">
-        <v>162</v>
-      </c>
-      <c r="G151" t="s">
-        <v>194</v>
       </c>
       <c r="H151" s="2">
         <v>46239</v>
@@ -5201,25 +5228,25 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B152" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C152" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D152" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E152" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F152" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G152" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H152" s="2">
         <v>46270</v>
@@ -5228,25 +5255,25 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B153" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C153" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D153" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E153" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F153" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G153" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H153" s="2">
         <v>46270</v>
@@ -5255,25 +5282,25 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B154" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C154" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D154" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E154" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F154" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G154" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H154" s="2">
         <v>46239</v>
@@ -5284,25 +5311,25 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B155" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C155" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D155" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E155" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F155" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G155" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H155" s="2">
         <v>46262</v>
@@ -5313,81 +5340,83 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B156" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C156" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D156" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E156" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F156" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G156" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H156" s="2">
         <v>46270</v>
       </c>
-      <c r="I156" s="2"/>
+      <c r="I156" s="2">
+        <v>46261</v>
+      </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B157" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C157" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D157" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E157" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F157" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G157" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H157" s="2">
         <v>46262</v>
       </c>
       <c r="I157" s="2">
-        <v>46261</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B158" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C158" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D158" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E158" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F158" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G158" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H158" s="2">
         <v>46270</v>
@@ -5396,25 +5425,25 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B159" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C159" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D159" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E159" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F159" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G159" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H159" s="2">
         <v>46262</v>
@@ -5425,25 +5454,25 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>202</v>
+      </c>
+      <c r="B160" t="s">
         <v>203</v>
       </c>
-      <c r="B160" t="s">
-        <v>204</v>
-      </c>
       <c r="C160" t="s">
         <v>11</v>
       </c>
       <c r="D160" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E160" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F160" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G160" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H160" s="2">
         <v>46280</v>
@@ -5452,25 +5481,25 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B161" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C161" t="s">
         <v>11</v>
       </c>
       <c r="D161" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E161" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F161" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G161" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H161" s="2">
         <v>46280</v>
@@ -5479,25 +5508,25 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B162" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C162" t="s">
         <v>11</v>
       </c>
       <c r="D162" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E162" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F162" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G162" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H162" s="2">
         <v>46280</v>
@@ -5506,220 +5535,220 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B163" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C163" t="s">
         <v>11</v>
       </c>
       <c r="D163" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E163" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G163" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B164" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C164" t="s">
         <v>11</v>
       </c>
       <c r="D164" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E164" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G164" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B165" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C165" t="s">
         <v>11</v>
       </c>
       <c r="D165" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E165" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G165" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B166" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C166" t="s">
         <v>11</v>
       </c>
       <c r="D166" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E166" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G166" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B167" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C167" t="s">
         <v>11</v>
       </c>
       <c r="D167" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E167" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G167" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B168" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C168" t="s">
         <v>11</v>
       </c>
       <c r="D168" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E168" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G168" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B169" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C169" t="s">
         <v>11</v>
       </c>
       <c r="D169" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E169" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G169" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B170" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C170" t="s">
         <v>11</v>
       </c>
       <c r="D170" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E170" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G170" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B171" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C171" t="s">
         <v>11</v>
       </c>
       <c r="D171" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E171" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G171" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B172" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C172" t="s">
         <v>11</v>
       </c>
       <c r="D172" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E172" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G172" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
@@ -5742,6 +5771,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -6002,15 +6040,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19085706-475A-47B8-AC19-64F084D28E59}">
   <ds:schemaRefs>
@@ -6023,6 +6052,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{952F739C-0654-4468-9DC3-FF416434CCBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A02432C2-097A-4B88-A372-7C95D690C5C7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6039,12 +6076,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{952F739C-0654-4468-9DC3-FF416434CCBC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes.sharepoint.com/sites/DeLunaOperaes/Documentos Partilhados/GESTÃO DE FROTA/Controle de Frota - BID 2026/painel-frota-deluna-pronto-para-publicar/site_deploy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes.sharepoint.com/sites/DeLunaOperaes/Documentos Partilhados/GESTÃO DE FROTA/Automações Frota/Controle de Frota - BID 2026/painel-frota-deluna-pronto-para-publicar/site_deploy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_40453C32AA65790B7DE51D384C84BAC981E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A65D703-186D-41F9-B9DA-ED5AB1F58E41}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_40453C32AA65790B7DE51D384C84BAC981E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{886E27AA-2348-473C-8B5F-03DDF3F1A5EB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Placas_BID2026!$A$1:$I$172</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -5251,7 +5264,9 @@
       <c r="H152" s="2">
         <v>46270</v>
       </c>
-      <c r="I152" s="2"/>
+      <c r="I152" s="2">
+        <v>46263</v>
+      </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
@@ -5278,7 +5293,9 @@
       <c r="H153" s="2">
         <v>46270</v>
       </c>
-      <c r="I153" s="2"/>
+      <c r="I153" s="2">
+        <v>46263</v>
+      </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
@@ -5421,7 +5438,9 @@
       <c r="H158" s="2">
         <v>46270</v>
       </c>
-      <c r="I158" s="2"/>
+      <c r="I158" s="2">
+        <v>46262</v>
+      </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
@@ -5759,27 +5778,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -6040,26 +6038,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19085706-475A-47B8-AC19-64F084D28E59}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{952F739C-0654-4468-9DC3-FF416434CCBC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A02432C2-097A-4B88-A372-7C95D690C5C7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6076,4 +6076,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{952F739C-0654-4468-9DC3-FF416434CCBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19085706-475A-47B8-AC19-64F084D28E59}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -5,19 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes.sharepoint.com/sites/DeLunaOperaes/Documentos Partilhados/GESTÃO DE FROTA/Automações Frota/Controle de Frota - BID 2026/painel-frota-deluna-pronto-para-publicar/site_deploy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes.sharepoint.com/sites/DeLunaOperaes/Documentos Partilhados/GESTÃO DE FROTA/Automações Frota/Controle de Frota - BID 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_40453C32AA65790B7DE51D384C84BAC981E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{886E27AA-2348-473C-8B5F-03DDF3F1A5EB}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD5576AA-A00A-40B8-A9D6-2979E93CDFCE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Placas_BID2026" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Placas_BID2026!$A$1:$I$172</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="219">
   <si>
     <t>Placa</t>
   </si>
@@ -74,6 +71,9 @@
     <t>RJ/ES</t>
   </si>
   <si>
+    <t>Vuc Dedicado</t>
+  </si>
+  <si>
     <t>SPRINTER 317</t>
   </si>
   <si>
@@ -608,9 +608,6 @@
     <t>XXX4709</t>
   </si>
   <si>
-    <t>XXX4714</t>
-  </si>
-  <si>
     <t>XXX4715</t>
   </si>
   <si>
@@ -686,13 +683,13 @@
     <t>XXX5318</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>UVQ6I66</t>
+  </si>
+  <si>
     <t>Deluna</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Vuc Deluna</t>
   </si>
 </sst>
 </file>
@@ -1097,16 +1094,16 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
         <v>218</v>
       </c>
-      <c r="E2" t="s">
-        <v>216</v>
-      </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2">
@@ -1115,7 +1112,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -1124,16 +1121,16 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
         <v>218</v>
       </c>
-      <c r="E3" t="s">
-        <v>216</v>
-      </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2">
@@ -1142,7 +1139,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1151,16 +1148,16 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
         <v>218</v>
       </c>
-      <c r="E4" t="s">
-        <v>216</v>
-      </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2">
@@ -1169,25 +1166,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
         <v>218</v>
       </c>
-      <c r="E5" t="s">
-        <v>216</v>
-      </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2">
@@ -1196,25 +1193,25 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
       <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
         <v>218</v>
       </c>
-      <c r="E6" t="s">
-        <v>216</v>
-      </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2">
@@ -1223,25 +1220,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
         <v>218</v>
       </c>
-      <c r="E7" t="s">
-        <v>216</v>
-      </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2">
@@ -1250,25 +1247,25 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
       </c>
       <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
         <v>218</v>
       </c>
-      <c r="E8" t="s">
-        <v>216</v>
-      </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2">
@@ -1277,25 +1274,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
         <v>218</v>
       </c>
-      <c r="E9" t="s">
-        <v>216</v>
-      </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2">
@@ -1304,25 +1301,25 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H10" s="2">
         <v>46171</v>
@@ -1333,25 +1330,25 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" t="s">
-        <v>27</v>
       </c>
       <c r="H11" s="2">
         <v>46171</v>
@@ -1362,25 +1359,25 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H12" s="2">
         <v>46207</v>
@@ -1391,28 +1388,28 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" t="s">
-        <v>33</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I13" s="2">
         <v>46202</v>
@@ -1420,28 +1417,28 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" t="s">
-        <v>38</v>
-      </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I14" s="2">
         <v>46202</v>
@@ -1449,28 +1446,28 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I15" s="2">
         <v>46204</v>
@@ -1478,28 +1475,28 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I16" s="2">
         <v>46202</v>
@@ -1507,28 +1504,28 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I17" s="2">
         <v>46202</v>
@@ -1536,28 +1533,28 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" t="s">
         <v>44</v>
       </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" t="s">
-        <v>43</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I18" s="2">
         <v>46202</v>
@@ -1565,25 +1562,25 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H19" s="2">
         <v>46211</v>
@@ -1594,28 +1591,28 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I20" s="2">
         <v>46202</v>
@@ -1623,28 +1620,28 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I21" s="2">
         <v>46202</v>
@@ -1652,25 +1649,25 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H22" s="2">
         <v>46190</v>
@@ -1681,25 +1678,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
         <v>50</v>
       </c>
-      <c r="B23" t="s">
-        <v>49</v>
-      </c>
       <c r="C23" t="s">
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H23" s="2">
         <v>46190</v>
@@ -1710,25 +1707,25 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H24" s="2">
         <v>46189</v>
@@ -1739,25 +1736,25 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H25" s="2">
         <v>46189</v>
@@ -1768,25 +1765,25 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H26" s="2">
         <v>46189</v>
@@ -1797,25 +1794,25 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H27" s="2">
         <v>46189</v>
@@ -1826,25 +1823,25 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H28" s="2">
         <v>46190</v>
@@ -1855,25 +1852,25 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H29" s="2">
         <v>46190</v>
@@ -1884,25 +1881,25 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H30" s="2">
         <v>46189</v>
@@ -1913,25 +1910,25 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H31" s="2">
         <v>46189</v>
@@ -1942,25 +1939,25 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H32" s="2">
         <v>46190</v>
@@ -1971,25 +1968,25 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
         <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H33" s="2">
         <v>46190</v>
@@ -2000,25 +1997,25 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H34" s="2">
         <v>46190</v>
@@ -2029,25 +2026,25 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H35" s="2">
         <v>46190</v>
@@ -2058,25 +2055,25 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C36" t="s">
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H36" s="2">
         <v>46190</v>
@@ -2087,25 +2084,25 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H37" s="2">
         <v>46209</v>
@@ -2116,25 +2113,25 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" t="s">
         <v>66</v>
       </c>
-      <c r="B38" t="s">
-        <v>65</v>
-      </c>
       <c r="C38" t="s">
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H38" s="2">
         <v>46211</v>
@@ -2145,25 +2142,25 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H39" s="2">
         <v>46209</v>
@@ -2174,25 +2171,25 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H40" s="2">
         <v>46210</v>
@@ -2203,28 +2200,28 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C41" t="s">
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I41" s="2">
         <v>46205</v>
@@ -2232,25 +2229,25 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B42" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F42" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H42" s="2">
         <v>46209</v>
@@ -2261,25 +2258,25 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F43" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H43" s="2">
         <v>46209</v>
@@ -2290,28 +2287,28 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B44" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I44" s="2">
         <v>46205</v>
@@ -2319,25 +2316,25 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B45" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C45" t="s">
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E45" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F45" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H45" s="2">
         <v>46211</v>
@@ -2348,25 +2345,25 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E46" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G46" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H46" s="2">
         <v>46211</v>
@@ -2377,25 +2374,25 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C47" t="s">
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G47" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H47" s="2">
         <v>46211</v>
@@ -2406,28 +2403,28 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B48" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C48" t="s">
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E48" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G48" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I48" s="2">
         <v>46205</v>
@@ -2435,25 +2432,25 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C49" t="s">
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G49" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H49" s="2">
         <v>46217</v>
@@ -2464,7 +2461,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
@@ -2473,16 +2470,16 @@
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H50" s="2">
         <v>46190</v>
@@ -2493,7 +2490,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
@@ -2502,16 +2499,16 @@
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H51" s="2">
         <v>46190</v>
@@ -2522,7 +2519,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
@@ -2531,16 +2528,16 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H52" s="2">
         <v>46190</v>
@@ -2551,7 +2548,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
@@ -2560,16 +2557,16 @@
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H53" s="2">
         <v>46191</v>
@@ -2580,7 +2577,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
@@ -2589,16 +2586,16 @@
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H54" s="2">
         <v>46191</v>
@@ -2609,7 +2606,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
@@ -2618,16 +2615,16 @@
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E55" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H55" s="2">
         <v>46190</v>
@@ -2638,7 +2635,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
@@ -2647,16 +2644,16 @@
         <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E56" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H56" s="2">
         <v>46191</v>
@@ -2667,7 +2664,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
@@ -2676,16 +2673,16 @@
         <v>11</v>
       </c>
       <c r="D57" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H57" s="2">
         <v>46191</v>
@@ -2696,7 +2693,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
@@ -2705,16 +2702,16 @@
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H58" s="2">
         <v>46193</v>
@@ -2725,7 +2722,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B59" t="s">
         <v>10</v>
@@ -2734,16 +2731,16 @@
         <v>11</v>
       </c>
       <c r="D59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G59" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H59" s="2">
         <v>46190</v>
@@ -2754,7 +2751,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B60" t="s">
         <v>10</v>
@@ -2763,16 +2760,16 @@
         <v>11</v>
       </c>
       <c r="D60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E60" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H60" s="2">
         <v>46191</v>
@@ -2783,7 +2780,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B61" t="s">
         <v>10</v>
@@ -2792,16 +2789,16 @@
         <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E61" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H61" s="2">
         <v>46190</v>
@@ -2812,7 +2809,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
@@ -2821,16 +2818,16 @@
         <v>11</v>
       </c>
       <c r="D62" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E62" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F62" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G62" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H62" s="2">
         <v>46190</v>
@@ -2841,25 +2838,25 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C63" t="s">
         <v>11</v>
       </c>
       <c r="D63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E63" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F63" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H63" s="2">
         <v>46171</v>
@@ -2870,25 +2867,25 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B64" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C64" t="s">
         <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E64" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F64" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H64" s="2">
         <v>46171</v>
@@ -2899,25 +2896,25 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B65" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C65" t="s">
         <v>11</v>
       </c>
       <c r="D65" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E65" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F65" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G65" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H65" s="2">
         <v>46171</v>
@@ -2928,25 +2925,25 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B66" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C66" t="s">
         <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E66" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F66" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H66" s="2">
         <v>46170</v>
@@ -2957,25 +2954,25 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B67" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E67" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F67" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G67" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H67" s="2">
         <v>46171</v>
@@ -2986,25 +2983,25 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
       </c>
       <c r="D68" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E68" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F68" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H68" s="2">
         <v>46154</v>
@@ -3015,25 +3012,25 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
       </c>
       <c r="D69" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E69" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F69" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H69" s="2">
         <v>46154</v>
@@ -3044,25 +3041,25 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
       </c>
       <c r="D70" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E70" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F70" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H70" s="2">
         <v>46154</v>
@@ -3073,25 +3070,25 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
       </c>
       <c r="D71" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E71" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F71" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G71" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H71" s="2">
         <v>46154</v>
@@ -3102,25 +3099,25 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
       </c>
       <c r="D72" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E72" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F72" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H72" s="2">
         <v>46154</v>
@@ -3131,25 +3128,25 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B73" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C73" t="s">
         <v>11</v>
       </c>
       <c r="D73" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E73" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F73" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H73" s="2">
         <v>46253</v>
@@ -3160,25 +3157,25 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>108</v>
+      </c>
+      <c r="B74" t="s">
         <v>107</v>
       </c>
-      <c r="B74" t="s">
-        <v>106</v>
-      </c>
       <c r="C74" t="s">
         <v>11</v>
       </c>
       <c r="D74" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E74" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F74" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G74" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H74" s="2">
         <v>46255</v>
@@ -3189,25 +3186,25 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C75" t="s">
         <v>11</v>
       </c>
       <c r="D75" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E75" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F75" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G75" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H75" s="2">
         <v>46255</v>
@@ -3218,25 +3215,25 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B76" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C76" t="s">
         <v>11</v>
       </c>
       <c r="D76" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E76" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F76" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G76" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H76" s="2">
         <v>46261</v>
@@ -3247,25 +3244,25 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C77" t="s">
         <v>11</v>
       </c>
       <c r="D77" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E77" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F77" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G77" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H77" s="2">
         <v>46261</v>
@@ -3276,25 +3273,25 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B78" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C78" t="s">
         <v>11</v>
       </c>
       <c r="D78" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E78" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F78" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G78" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H78" s="2">
         <v>46254</v>
@@ -3305,25 +3302,25 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B79" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C79" t="s">
         <v>11</v>
       </c>
       <c r="D79" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E79" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F79" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G79" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H79" s="2">
         <v>46261</v>
@@ -3334,25 +3331,25 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B80" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C80" t="s">
         <v>11</v>
       </c>
       <c r="D80" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E80" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F80" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G80" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H80" s="2">
         <v>46269</v>
@@ -3363,25 +3360,25 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B81" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C81" t="s">
         <v>11</v>
       </c>
       <c r="D81" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E81" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F81" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G81" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H81" s="2">
         <v>46261</v>
@@ -3392,25 +3389,25 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B82" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
       </c>
       <c r="D82" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E82" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F82" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G82" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H82" s="2">
         <v>46262</v>
@@ -3421,25 +3418,25 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C83" t="s">
         <v>11</v>
       </c>
       <c r="D83" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E83" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F83" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G83" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H83" s="2">
         <v>46185</v>
@@ -3450,25 +3447,25 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C84" t="s">
         <v>11</v>
       </c>
       <c r="D84" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E84" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F84" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G84" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H84" s="2">
         <v>46182</v>
@@ -3479,25 +3476,25 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C85" t="s">
         <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E85" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F85" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G85" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H85" s="2">
         <v>46185</v>
@@ -3508,25 +3505,25 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C86" t="s">
         <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E86" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F86" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G86" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H86" s="2">
         <v>46148</v>
@@ -3537,25 +3534,25 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B87" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C87" t="s">
         <v>11</v>
       </c>
       <c r="D87" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E87" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F87" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G87" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H87" s="2">
         <v>46261</v>
@@ -3566,25 +3563,25 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C88" t="s">
         <v>11</v>
       </c>
       <c r="D88" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E88" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F88" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G88" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H88" s="2">
         <v>46254</v>
@@ -3595,25 +3592,25 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B89" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C89" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D89" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E89" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F89" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G89" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H89" s="2">
         <v>46199</v>
@@ -3624,25 +3621,25 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>127</v>
+      </c>
+      <c r="B90" t="s">
+        <v>124</v>
+      </c>
+      <c r="C90" t="s">
+        <v>37</v>
+      </c>
+      <c r="D90" t="s">
+        <v>25</v>
+      </c>
+      <c r="E90" t="s">
+        <v>125</v>
+      </c>
+      <c r="F90" t="s">
         <v>126</v>
       </c>
-      <c r="B90" t="s">
-        <v>123</v>
-      </c>
-      <c r="C90" t="s">
-        <v>36</v>
-      </c>
-      <c r="D90" t="s">
-        <v>24</v>
-      </c>
-      <c r="E90" t="s">
-        <v>124</v>
-      </c>
-      <c r="F90" t="s">
-        <v>125</v>
-      </c>
       <c r="G90" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H90" s="2">
         <v>46199</v>
@@ -3653,25 +3650,25 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B91" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C91" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D91" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E91" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F91" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G91" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H91" s="2">
         <v>46184</v>
@@ -3682,25 +3679,25 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B92" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C92" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D92" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E92" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F92" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H92" s="2">
         <v>46176</v>
@@ -3711,7 +3708,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B93" t="s">
         <v>10</v>
@@ -3720,16 +3717,16 @@
         <v>11</v>
       </c>
       <c r="D93" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E93" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F93" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G93" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H93" s="2">
         <v>46218</v>
@@ -3740,7 +3737,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B94" t="s">
         <v>10</v>
@@ -3749,16 +3746,16 @@
         <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F94" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G94" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H94" s="2">
         <v>46218</v>
@@ -3769,7 +3766,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B95" t="s">
         <v>10</v>
@@ -3778,16 +3775,16 @@
         <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E95" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F95" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G95" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H95" s="2">
         <v>46218</v>
@@ -3798,7 +3795,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B96" t="s">
         <v>10</v>
@@ -3807,16 +3804,16 @@
         <v>11</v>
       </c>
       <c r="D96" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E96" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F96" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G96" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H96" s="2">
         <v>46218</v>
@@ -3827,7 +3824,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B97" t="s">
         <v>10</v>
@@ -3836,16 +3833,16 @@
         <v>11</v>
       </c>
       <c r="D97" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E97" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F97" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G97" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H97" s="2">
         <v>46218</v>
@@ -3856,7 +3853,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B98" t="s">
         <v>10</v>
@@ -3865,16 +3862,16 @@
         <v>11</v>
       </c>
       <c r="D98" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E98" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F98" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G98" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H98" s="2">
         <v>46218</v>
@@ -3885,25 +3882,25 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B99" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C99" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D99" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E99" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F99" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G99" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H99" s="2">
         <v>46220</v>
@@ -3914,25 +3911,25 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>138</v>
+      </c>
+      <c r="B100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C100" t="s">
+        <v>37</v>
+      </c>
+      <c r="D100" t="s">
+        <v>25</v>
+      </c>
+      <c r="E100" t="s">
+        <v>125</v>
+      </c>
+      <c r="F100" t="s">
+        <v>126</v>
+      </c>
+      <c r="G100" t="s">
         <v>137</v>
-      </c>
-      <c r="B100" t="s">
-        <v>123</v>
-      </c>
-      <c r="C100" t="s">
-        <v>36</v>
-      </c>
-      <c r="D100" t="s">
-        <v>24</v>
-      </c>
-      <c r="E100" t="s">
-        <v>124</v>
-      </c>
-      <c r="F100" t="s">
-        <v>125</v>
-      </c>
-      <c r="G100" t="s">
-        <v>136</v>
       </c>
       <c r="H100" s="2">
         <v>46220</v>
@@ -3943,25 +3940,25 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B101" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D101" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E101" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F101" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G101" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H101" s="2">
         <v>46220</v>
@@ -3972,223 +3969,237 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B102" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C102" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D102" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E102" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F102" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G102" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H102" s="2">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="I102" s="2"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>142</v>
+      </c>
+      <c r="B103" t="s">
+        <v>124</v>
+      </c>
+      <c r="C103" t="s">
+        <v>37</v>
+      </c>
+      <c r="D103" t="s">
+        <v>25</v>
+      </c>
+      <c r="E103" t="s">
+        <v>125</v>
+      </c>
+      <c r="F103" t="s">
+        <v>126</v>
+      </c>
+      <c r="G103" t="s">
         <v>141</v>
-      </c>
-      <c r="B103" t="s">
-        <v>123</v>
-      </c>
-      <c r="C103" t="s">
-        <v>36</v>
-      </c>
-      <c r="D103" t="s">
-        <v>24</v>
-      </c>
-      <c r="E103" t="s">
-        <v>124</v>
-      </c>
-      <c r="F103" t="s">
-        <v>125</v>
-      </c>
-      <c r="G103" t="s">
-        <v>140</v>
       </c>
       <c r="H103" s="2">
         <v>46276</v>
       </c>
-      <c r="I103" s="2"/>
+      <c r="I103" s="2">
+        <v>46276</v>
+      </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B104" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C104" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D104" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E104" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F104" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G104" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H104" s="2">
         <v>46276</v>
       </c>
-      <c r="I104" s="2"/>
+      <c r="I104" s="2">
+        <v>46276</v>
+      </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B105" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D105" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E105" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F105" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G105" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H105" s="2">
         <v>46276</v>
       </c>
-      <c r="I105" s="2"/>
+      <c r="I105" s="2">
+        <v>46276</v>
+      </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B106" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C106" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D106" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E106" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F106" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G106" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H106" s="2">
         <v>46276</v>
       </c>
-      <c r="I106" s="2"/>
+      <c r="I106" s="2">
+        <v>46276</v>
+      </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B107" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C107" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D107" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E107" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F107" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G107" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H107" s="2">
         <v>46276</v>
       </c>
-      <c r="I107" s="2"/>
+      <c r="I107" s="2">
+        <v>46276</v>
+      </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B108" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C108" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D108" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E108" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F108" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G108" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H108" s="2">
         <v>46276</v>
       </c>
-      <c r="I108" s="2"/>
+      <c r="I108" s="2">
+        <v>46276</v>
+      </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B109" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C109" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D109" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E109" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F109" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G109" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H109" s="2">
         <v>46276</v>
       </c>
-      <c r="I109" s="2"/>
+      <c r="I109" s="2">
+        <v>46276</v>
+      </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B110" t="s">
         <v>10</v>
@@ -4197,16 +4208,16 @@
         <v>11</v>
       </c>
       <c r="D110" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E110" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F110" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G110" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H110" s="2">
         <v>46295</v>
@@ -4215,25 +4226,25 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B111" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C111" t="s">
         <v>11</v>
       </c>
       <c r="D111" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F111" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G111" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H111" s="2">
         <v>46207</v>
@@ -4244,47 +4255,47 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B112" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C112" t="s">
         <v>11</v>
       </c>
       <c r="D112" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E112" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G112" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B113" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C113" t="s">
         <v>11</v>
       </c>
       <c r="D113" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E113" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F113" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G113" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H113" s="2">
         <v>46207</v>
@@ -4295,25 +4306,25 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B114" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C114" t="s">
         <v>11</v>
       </c>
       <c r="D114" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E114" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F114" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G114" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H114" s="2">
         <v>46207</v>
@@ -4324,25 +4335,25 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B115" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C115" t="s">
         <v>11</v>
       </c>
       <c r="D115" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E115" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F115" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G115" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H115" s="2">
         <v>46207</v>
@@ -4353,25 +4364,25 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
+        <v>156</v>
+      </c>
+      <c r="B116" t="s">
+        <v>24</v>
+      </c>
+      <c r="C116" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" t="s">
+        <v>25</v>
+      </c>
+      <c r="E116" t="s">
+        <v>26</v>
+      </c>
+      <c r="F116" t="s">
         <v>155</v>
       </c>
-      <c r="B116" t="s">
-        <v>23</v>
-      </c>
-      <c r="C116" t="s">
-        <v>11</v>
-      </c>
-      <c r="D116" t="s">
-        <v>24</v>
-      </c>
-      <c r="E116" t="s">
-        <v>25</v>
-      </c>
-      <c r="F116" t="s">
-        <v>154</v>
-      </c>
       <c r="G116" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H116" s="2">
         <v>46217</v>
@@ -4382,25 +4393,25 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B117" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C117" t="s">
         <v>11</v>
       </c>
       <c r="D117" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E117" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F117" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G117" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H117" s="2">
         <v>46207</v>
@@ -4411,25 +4422,25 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B118" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
       </c>
       <c r="D118" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E118" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F118" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G118" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H118" s="2">
         <v>46207</v>
@@ -4440,25 +4451,25 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B119" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C119" t="s">
         <v>11</v>
       </c>
       <c r="D119" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E119" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F119" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G119" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H119" s="2">
         <v>46207</v>
@@ -4469,25 +4480,25 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B120" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C120" t="s">
         <v>11</v>
       </c>
       <c r="D120" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E120" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F120" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G120" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H120" s="2">
         <v>46207</v>
@@ -4498,25 +4509,25 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B121" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C121" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D121" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E121" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F121" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G121" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H121" s="2">
         <v>46280</v>
@@ -4525,52 +4536,54 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B122" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C122" t="s">
         <v>11</v>
       </c>
       <c r="D122" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E122" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F122" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G122" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H122" s="2">
         <v>46280</v>
       </c>
-      <c r="I122" s="2"/>
+      <c r="I122" s="2">
+        <v>46277</v>
+      </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B123" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C123" t="s">
         <v>11</v>
       </c>
       <c r="D123" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E123" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F123" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G123" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H123" s="2">
         <v>46280</v>
@@ -4579,25 +4592,25 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B124" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C124" t="s">
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E124" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F124" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G124" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H124" s="2">
         <v>46280</v>
@@ -4606,25 +4619,25 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B125" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C125" t="s">
         <v>11</v>
       </c>
       <c r="D125" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E125" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F125" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G125" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H125" s="2">
         <v>46280</v>
@@ -4633,25 +4646,25 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B126" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C126" t="s">
         <v>11</v>
       </c>
       <c r="D126" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E126" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F126" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G126" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H126" s="2">
         <v>46280</v>
@@ -4660,25 +4673,25 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B127" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C127" t="s">
         <v>11</v>
       </c>
       <c r="D127" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E127" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F127" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G127" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H127" s="2">
         <v>46215</v>
@@ -4689,25 +4702,25 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B128" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C128" t="s">
         <v>11</v>
       </c>
       <c r="D128" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E128" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F128" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G128" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H128" s="2">
         <v>46207</v>
@@ -4718,474 +4731,479 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B129" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C129" t="s">
         <v>11</v>
       </c>
       <c r="D129" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E129" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F129" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G129" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H129" s="2">
-        <v>46275</v>
+        <v>46290</v>
       </c>
       <c r="I129" s="2"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B130" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C130" t="s">
         <v>11</v>
       </c>
       <c r="D130" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E130" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F130" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G130" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H130" s="2">
-        <v>46275</v>
+        <v>46290</v>
       </c>
       <c r="I130" s="2"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B131" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C131" t="s">
         <v>11</v>
       </c>
       <c r="D131" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E131" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G131" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
+        <v>174</v>
+      </c>
+      <c r="B132" t="s">
         <v>173</v>
       </c>
-      <c r="B132" t="s">
-        <v>172</v>
-      </c>
       <c r="C132" t="s">
         <v>11</v>
       </c>
       <c r="D132" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E132" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G132" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B133" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E133" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G133" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B134" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C134" t="s">
         <v>11</v>
       </c>
       <c r="D134" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E134" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G134" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B135" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C135" t="s">
         <v>11</v>
       </c>
       <c r="D135" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E135" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G135" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B136" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C136" t="s">
         <v>11</v>
       </c>
       <c r="D136" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E136" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G136" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B137" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C137" t="s">
         <v>11</v>
       </c>
       <c r="D137" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E137" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G137" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B138" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C138" t="s">
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E138" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G138" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B139" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C139" t="s">
         <v>11</v>
       </c>
       <c r="D139" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E139" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G139" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B140" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C140" t="s">
         <v>11</v>
       </c>
       <c r="D140" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E140" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G140" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B141" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C141" t="s">
         <v>11</v>
       </c>
       <c r="D141" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E141" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G141" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B142" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C142" t="s">
         <v>11</v>
       </c>
       <c r="D142" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E142" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G142" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H142" s="2"/>
       <c r="I142" s="2"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B143" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C143" t="s">
         <v>11</v>
       </c>
       <c r="D143" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E143" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G143" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H143" s="2"/>
       <c r="I143" s="2"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B144" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C144" t="s">
         <v>11</v>
       </c>
       <c r="D144" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E144" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G144" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H144" s="2"/>
       <c r="I144" s="2"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B145" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C145" t="s">
         <v>11</v>
       </c>
       <c r="D145" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E145" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G145" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B146" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C146" t="s">
         <v>11</v>
       </c>
       <c r="D146" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E146" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G146" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B147" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C147" t="s">
         <v>11</v>
       </c>
       <c r="D147" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E147" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G147" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B148" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C148" t="s">
         <v>11</v>
       </c>
       <c r="D148" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E148" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G148" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="B149" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C149" t="s">
         <v>11</v>
       </c>
       <c r="D149" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E149" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="F149" t="s">
+        <v>162</v>
       </c>
       <c r="G149" t="s">
-        <v>140</v>
-      </c>
-      <c r="H149" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="H149" s="2">
+        <v>46290</v>
+      </c>
       <c r="I149" s="2"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
@@ -5193,19 +5211,19 @@
         <v>191</v>
       </c>
       <c r="B150" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C150" t="s">
         <v>11</v>
       </c>
       <c r="D150" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E150" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G150" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H150" s="2"/>
       <c r="I150" s="2"/>
@@ -5215,19 +5233,19 @@
         <v>192</v>
       </c>
       <c r="B151" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C151" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D151" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E151" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F151" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G151" t="s">
         <v>193</v>
@@ -5244,19 +5262,19 @@
         <v>194</v>
       </c>
       <c r="B152" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C152" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D152" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E152" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F152" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G152" t="s">
         <v>193</v>
@@ -5273,19 +5291,19 @@
         <v>195</v>
       </c>
       <c r="B153" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C153" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D153" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E153" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F153" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G153" t="s">
         <v>193</v>
@@ -5302,19 +5320,19 @@
         <v>196</v>
       </c>
       <c r="B154" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C154" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D154" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E154" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F154" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G154" t="s">
         <v>193</v>
@@ -5331,19 +5349,19 @@
         <v>197</v>
       </c>
       <c r="B155" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C155" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D155" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E155" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F155" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G155" t="s">
         <v>193</v>
@@ -5360,19 +5378,19 @@
         <v>198</v>
       </c>
       <c r="B156" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C156" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D156" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E156" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F156" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G156" t="s">
         <v>193</v>
@@ -5389,19 +5407,19 @@
         <v>199</v>
       </c>
       <c r="B157" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C157" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D157" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E157" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F157" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G157" t="s">
         <v>193</v>
@@ -5418,19 +5436,19 @@
         <v>200</v>
       </c>
       <c r="B158" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C158" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D158" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E158" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F158" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G158" t="s">
         <v>193</v>
@@ -5447,19 +5465,19 @@
         <v>201</v>
       </c>
       <c r="B159" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C159" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D159" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E159" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F159" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G159" t="s">
         <v>193</v>
@@ -5482,13 +5500,13 @@
         <v>11</v>
       </c>
       <c r="D160" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E160" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F160" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G160" t="s">
         <v>193</v>
@@ -5509,13 +5527,13 @@
         <v>11</v>
       </c>
       <c r="D161" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E161" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F161" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G161" t="s">
         <v>193</v>
@@ -5536,13 +5554,13 @@
         <v>11</v>
       </c>
       <c r="D162" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E162" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F162" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G162" t="s">
         <v>193</v>
@@ -5563,10 +5581,10 @@
         <v>11</v>
       </c>
       <c r="D163" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E163" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G163" t="s">
         <v>193</v>
@@ -5585,10 +5603,10 @@
         <v>11</v>
       </c>
       <c r="D164" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E164" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G164" t="s">
         <v>193</v>
@@ -5607,10 +5625,10 @@
         <v>11</v>
       </c>
       <c r="D165" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E165" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G165" t="s">
         <v>193</v>
@@ -5629,10 +5647,10 @@
         <v>11</v>
       </c>
       <c r="D166" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E166" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G166" t="s">
         <v>193</v>
@@ -5651,10 +5669,10 @@
         <v>11</v>
       </c>
       <c r="D167" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E167" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G167" t="s">
         <v>193</v>
@@ -5673,10 +5691,10 @@
         <v>11</v>
       </c>
       <c r="D168" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E168" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G168" t="s">
         <v>193</v>
@@ -5689,19 +5707,19 @@
         <v>212</v>
       </c>
       <c r="B169" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C169" t="s">
         <v>11</v>
       </c>
       <c r="D169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E169" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G169" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
@@ -5711,16 +5729,16 @@
         <v>213</v>
       </c>
       <c r="B170" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C170" t="s">
         <v>11</v>
       </c>
       <c r="D170" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E170" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G170" t="s">
         <v>193</v>
@@ -5733,16 +5751,16 @@
         <v>214</v>
       </c>
       <c r="B171" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C171" t="s">
         <v>11</v>
       </c>
       <c r="D171" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E171" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G171" t="s">
         <v>193</v>
@@ -5755,16 +5773,16 @@
         <v>215</v>
       </c>
       <c r="B172" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C172" t="s">
         <v>11</v>
       </c>
       <c r="D172" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E172" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G172" t="s">
         <v>193</v>
@@ -5778,8 +5796,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="100717af0b9d82d0b2a1c8234c4e76b0">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cd289fca9f75e9fc862e02817de8bf32" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <xsd:import namespace="a6b958bc-5708-46f2-92f1-bce61d011186"/>
     <xsd:element name="properties">
@@ -5875,7 +5893,7 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d7713e69-6b5e-48f9-bc66-ec74065ebb50" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d7713e69-6b5e-48f9-bc66-ec74065ebb50" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -5901,7 +5919,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a6b958bc-5708-46f2-92f1-bce61d011186" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -5920,7 +5938,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6039,15 +6057,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -6059,8 +6068,17 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A02432C2-097A-4B88-A372-7C95D690C5C7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9A0667C-3738-42E6-89EB-FC97E1A1B35D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -6079,15 +6097,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{952F739C-0654-4468-9DC3-FF416434CCBC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19085706-475A-47B8-AC19-64F084D28E59}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -6095,4 +6105,12 @@
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes.sharepoint.com/sites/DeLunaOperaes/Documentos Partilhados/GESTÃO DE FROTA/Automações Frota/Controle de Frota - BID 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD5576AA-A00A-40B8-A9D6-2979E93CDFCE}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12F098AE-A6D9-498F-90A1-710E6C8AD6FD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Placas_BID2026" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Placas_BID2026!$A$1:$O$172</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1852" uniqueCount="226">
   <si>
     <t>Placa</t>
   </si>
@@ -690,6 +693,27 @@
   </si>
   <si>
     <t>Deluna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRLV </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Contrato de arrendamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> inclusão na ANTT</t>
+  </si>
+  <si>
+    <t>GR e cadastro no mercado livre</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Contrato de comodato</t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>Cartão Velo</t>
   </si>
 </sst>
 </file>
@@ -1044,4751 +1068,6746 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I172"/>
+  <dimension ref="A1:O172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
-    <col min="7" max="9" width="16" customWidth="1"/>
+    <col min="1" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="34" customWidth="1"/>
+    <col min="13" max="15" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="K2" t="s">
         <v>218</v>
       </c>
-      <c r="F2" t="s">
+      <c r="L2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="M2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2">
         <v>46139</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="H3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="K3" t="s">
         <v>218</v>
       </c>
-      <c r="F3" t="s">
+      <c r="L3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
+      <c r="M3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2">
+      <c r="N3" s="2"/>
+      <c r="O3" s="2">
         <v>46139</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="H4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="K4" t="s">
         <v>218</v>
       </c>
-      <c r="F4" t="s">
+      <c r="L4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" t="s">
+      <c r="M4" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2">
+      <c r="N4" s="2"/>
+      <c r="O4" s="2">
         <v>46139</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
+      <c r="H5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="K5" t="s">
         <v>218</v>
       </c>
-      <c r="F5" t="s">
+      <c r="L5" t="s">
         <v>13</v>
       </c>
-      <c r="G5" t="s">
+      <c r="M5" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2">
+      <c r="N5" s="2"/>
+      <c r="O5" s="2">
         <v>46139</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
+      <c r="H6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
+      <c r="K6" t="s">
         <v>218</v>
       </c>
-      <c r="F6" t="s">
+      <c r="L6" t="s">
         <v>13</v>
       </c>
-      <c r="G6" t="s">
+      <c r="M6" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2">
+      <c r="N6" s="2"/>
+      <c r="O6" s="2">
         <v>46139</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
+      <c r="H7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="I7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" t="s">
+      <c r="K7" t="s">
         <v>218</v>
       </c>
-      <c r="F7" t="s">
+      <c r="L7" t="s">
         <v>13</v>
       </c>
-      <c r="G7" t="s">
+      <c r="M7" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2">
+      <c r="N7" s="2"/>
+      <c r="O7" s="2">
         <v>46139</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
+      <c r="H8" t="s">
         <v>18</v>
       </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="I8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" t="s">
         <v>12</v>
       </c>
-      <c r="E8" t="s">
+      <c r="K8" t="s">
         <v>218</v>
       </c>
-      <c r="F8" t="s">
+      <c r="L8" t="s">
         <v>13</v>
       </c>
-      <c r="G8" t="s">
+      <c r="M8" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2">
+      <c r="N8" s="2"/>
+      <c r="O8" s="2">
         <v>46139</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
+      <c r="H9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="I9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" t="s">
+      <c r="K9" t="s">
         <v>218</v>
       </c>
-      <c r="F9" t="s">
+      <c r="L9" t="s">
         <v>13</v>
       </c>
-      <c r="G9" t="s">
+      <c r="M9" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2">
+      <c r="N9" s="2"/>
+      <c r="O9" s="2">
         <v>46139</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>23</v>
       </c>
       <c r="B10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" t="s">
+        <v>224</v>
+      </c>
+      <c r="H10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="I10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" t="s">
         <v>25</v>
       </c>
-      <c r="E10" t="s">
+      <c r="K10" t="s">
         <v>26</v>
       </c>
-      <c r="F10" t="s">
+      <c r="L10" t="s">
         <v>27</v>
       </c>
-      <c r="G10" t="s">
+      <c r="M10" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="2">
+      <c r="N10" s="2">
         <v>46171</v>
       </c>
-      <c r="I10" s="2">
+      <c r="O10" s="2">
         <v>46171</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
       <c r="B11" t="s">
+        <v>224</v>
+      </c>
+      <c r="C11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E11" t="s">
+        <v>224</v>
+      </c>
+      <c r="F11" t="s">
+        <v>224</v>
+      </c>
+      <c r="H11" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="I11" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" t="s">
         <v>25</v>
       </c>
-      <c r="E11" t="s">
+      <c r="K11" t="s">
         <v>26</v>
       </c>
-      <c r="F11" t="s">
+      <c r="L11" t="s">
         <v>27</v>
       </c>
-      <c r="G11" t="s">
+      <c r="M11" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="2">
+      <c r="N11" s="2">
         <v>46171</v>
       </c>
-      <c r="I11" s="2">
+      <c r="O11" s="2">
         <v>46171</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
       <c r="B12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E12" t="s">
+        <v>224</v>
+      </c>
+      <c r="F12" t="s">
+        <v>224</v>
+      </c>
+      <c r="H12" t="s">
         <v>31</v>
       </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="I12" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" t="s">
         <v>32</v>
       </c>
-      <c r="E12" t="s">
+      <c r="K12" t="s">
         <v>26</v>
       </c>
-      <c r="F12" t="s">
+      <c r="L12" t="s">
         <v>33</v>
       </c>
-      <c r="G12" t="s">
+      <c r="M12" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="2">
+      <c r="N12" s="2">
         <v>46207</v>
       </c>
-      <c r="I12" s="2">
+      <c r="O12" s="2">
         <v>46206</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" t="s">
+      <c r="H13" t="s">
         <v>36</v>
       </c>
-      <c r="C13" t="s">
+      <c r="I13" t="s">
         <v>37</v>
       </c>
-      <c r="D13" t="s">
+      <c r="J13" t="s">
         <v>32</v>
       </c>
-      <c r="E13" t="s">
+      <c r="K13" t="s">
         <v>38</v>
       </c>
-      <c r="F13" t="s">
+      <c r="L13" t="s">
         <v>39</v>
       </c>
-      <c r="G13" t="s">
+      <c r="M13" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="N13" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I13" s="2">
+      <c r="O13" s="2">
         <v>46202</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="B14" t="s">
+      <c r="H14" t="s">
         <v>36</v>
       </c>
-      <c r="C14" t="s">
+      <c r="I14" t="s">
         <v>37</v>
       </c>
-      <c r="D14" t="s">
+      <c r="J14" t="s">
         <v>32</v>
       </c>
-      <c r="E14" t="s">
+      <c r="K14" t="s">
         <v>38</v>
       </c>
-      <c r="F14" t="s">
+      <c r="L14" t="s">
         <v>39</v>
       </c>
-      <c r="G14" t="s">
+      <c r="M14" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I14" s="2">
+      <c r="O14" s="2">
         <v>46202</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" t="s">
+      <c r="H15" t="s">
         <v>36</v>
       </c>
-      <c r="C15" t="s">
+      <c r="I15" t="s">
         <v>37</v>
       </c>
-      <c r="D15" t="s">
+      <c r="J15" t="s">
         <v>32</v>
       </c>
-      <c r="E15" t="s">
+      <c r="K15" t="s">
         <v>38</v>
       </c>
-      <c r="F15" t="s">
+      <c r="L15" t="s">
         <v>39</v>
       </c>
-      <c r="G15" t="s">
+      <c r="M15" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I15" s="2">
+      <c r="O15" s="2">
         <v>46204</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="s">
+      <c r="H16" t="s">
         <v>36</v>
       </c>
-      <c r="C16" t="s">
+      <c r="I16" t="s">
         <v>37</v>
       </c>
-      <c r="D16" t="s">
+      <c r="J16" t="s">
         <v>32</v>
       </c>
-      <c r="E16" t="s">
+      <c r="K16" t="s">
         <v>38</v>
       </c>
-      <c r="F16" t="s">
+      <c r="L16" t="s">
         <v>39</v>
       </c>
-      <c r="G16" t="s">
+      <c r="M16" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I16" s="2">
+      <c r="O16" s="2">
         <v>46202</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="s">
+      <c r="H17" t="s">
         <v>36</v>
       </c>
-      <c r="C17" t="s">
+      <c r="I17" t="s">
         <v>37</v>
       </c>
-      <c r="D17" t="s">
+      <c r="J17" t="s">
         <v>32</v>
       </c>
-      <c r="E17" t="s">
+      <c r="K17" t="s">
         <v>38</v>
       </c>
-      <c r="F17" t="s">
+      <c r="L17" t="s">
         <v>39</v>
       </c>
-      <c r="G17" t="s">
+      <c r="M17" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I17" s="2">
+      <c r="O17" s="2">
         <v>46202</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>45</v>
       </c>
-      <c r="B18" t="s">
+      <c r="H18" t="s">
         <v>36</v>
       </c>
-      <c r="C18" t="s">
+      <c r="I18" t="s">
         <v>37</v>
       </c>
-      <c r="D18" t="s">
+      <c r="J18" t="s">
         <v>32</v>
       </c>
-      <c r="E18" t="s">
+      <c r="K18" t="s">
         <v>38</v>
       </c>
-      <c r="F18" t="s">
+      <c r="L18" t="s">
         <v>39</v>
       </c>
-      <c r="G18" t="s">
+      <c r="M18" t="s">
         <v>44</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I18" s="2">
+      <c r="O18" s="2">
         <v>46202</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>46</v>
       </c>
       <c r="B19" t="s">
+        <v>224</v>
+      </c>
+      <c r="C19" t="s">
+        <v>224</v>
+      </c>
+      <c r="D19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E19" t="s">
+        <v>224</v>
+      </c>
+      <c r="F19" t="s">
+        <v>224</v>
+      </c>
+      <c r="H19" t="s">
         <v>36</v>
       </c>
-      <c r="C19" t="s">
+      <c r="I19" t="s">
         <v>37</v>
       </c>
-      <c r="D19" t="s">
+      <c r="J19" t="s">
         <v>32</v>
       </c>
-      <c r="E19" t="s">
+      <c r="K19" t="s">
         <v>38</v>
       </c>
-      <c r="F19" t="s">
+      <c r="L19" t="s">
         <v>39</v>
       </c>
-      <c r="G19" t="s">
+      <c r="M19" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="2">
+      <c r="N19" s="2">
         <v>46211</v>
       </c>
-      <c r="I19" s="2">
+      <c r="O19" s="2">
         <v>46211</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
-      <c r="B20" t="s">
+      <c r="H20" t="s">
         <v>36</v>
       </c>
-      <c r="C20" t="s">
+      <c r="I20" t="s">
         <v>37</v>
       </c>
-      <c r="D20" t="s">
+      <c r="J20" t="s">
         <v>32</v>
       </c>
-      <c r="E20" t="s">
+      <c r="K20" t="s">
         <v>38</v>
       </c>
-      <c r="F20" t="s">
+      <c r="L20" t="s">
         <v>39</v>
       </c>
-      <c r="G20" t="s">
+      <c r="M20" t="s">
         <v>44</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I20" s="2">
+      <c r="O20" s="2">
         <v>46202</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
-      <c r="B21" t="s">
+      <c r="H21" t="s">
         <v>36</v>
       </c>
-      <c r="C21" t="s">
+      <c r="I21" t="s">
         <v>37</v>
       </c>
-      <c r="D21" t="s">
+      <c r="J21" t="s">
         <v>32</v>
       </c>
-      <c r="E21" t="s">
+      <c r="K21" t="s">
         <v>38</v>
       </c>
-      <c r="F21" t="s">
+      <c r="L21" t="s">
         <v>39</v>
       </c>
-      <c r="G21" t="s">
+      <c r="M21" t="s">
         <v>44</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I21" s="2">
+      <c r="O21" s="2">
         <v>46202</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>49</v>
       </c>
       <c r="B22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C22" t="s">
+        <v>224</v>
+      </c>
+      <c r="D22" t="s">
+        <v>224</v>
+      </c>
+      <c r="E22" t="s">
+        <v>224</v>
+      </c>
+      <c r="F22" t="s">
+        <v>224</v>
+      </c>
+      <c r="H22" t="s">
         <v>50</v>
       </c>
-      <c r="C22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="I22" t="s">
+        <v>11</v>
+      </c>
+      <c r="J22" t="s">
         <v>32</v>
       </c>
-      <c r="E22" t="s">
+      <c r="K22" t="s">
         <v>38</v>
       </c>
-      <c r="F22" t="s">
+      <c r="L22" t="s">
         <v>39</v>
       </c>
-      <c r="G22" t="s">
+      <c r="M22" t="s">
         <v>28</v>
       </c>
-      <c r="H22" s="2">
+      <c r="N22" s="2">
         <v>46190</v>
       </c>
-      <c r="I22" s="2">
+      <c r="O22" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>51</v>
       </c>
       <c r="B23" t="s">
+        <v>224</v>
+      </c>
+      <c r="C23" t="s">
+        <v>224</v>
+      </c>
+      <c r="D23" t="s">
+        <v>224</v>
+      </c>
+      <c r="E23" t="s">
+        <v>224</v>
+      </c>
+      <c r="F23" t="s">
+        <v>224</v>
+      </c>
+      <c r="H23" t="s">
         <v>50</v>
       </c>
-      <c r="C23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="I23" t="s">
+        <v>11</v>
+      </c>
+      <c r="J23" t="s">
         <v>32</v>
       </c>
-      <c r="E23" t="s">
+      <c r="K23" t="s">
         <v>38</v>
       </c>
-      <c r="F23" t="s">
+      <c r="L23" t="s">
         <v>39</v>
       </c>
-      <c r="G23" t="s">
+      <c r="M23" t="s">
         <v>28</v>
       </c>
-      <c r="H23" s="2">
+      <c r="N23" s="2">
         <v>46190</v>
       </c>
-      <c r="I23" s="2">
+      <c r="O23" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
       <c r="B24" t="s">
+        <v>224</v>
+      </c>
+      <c r="C24" t="s">
+        <v>224</v>
+      </c>
+      <c r="D24" t="s">
+        <v>224</v>
+      </c>
+      <c r="E24" t="s">
+        <v>224</v>
+      </c>
+      <c r="F24" t="s">
+        <v>224</v>
+      </c>
+      <c r="H24" t="s">
         <v>50</v>
       </c>
-      <c r="C24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="I24" t="s">
+        <v>11</v>
+      </c>
+      <c r="J24" t="s">
         <v>32</v>
       </c>
-      <c r="E24" t="s">
+      <c r="K24" t="s">
         <v>38</v>
       </c>
-      <c r="F24" t="s">
+      <c r="L24" t="s">
         <v>39</v>
       </c>
-      <c r="G24" t="s">
+      <c r="M24" t="s">
         <v>28</v>
       </c>
-      <c r="H24" s="2">
+      <c r="N24" s="2">
         <v>46189</v>
       </c>
-      <c r="I24" s="2">
+      <c r="O24" s="2">
         <v>46185</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>53</v>
       </c>
       <c r="B25" t="s">
+        <v>224</v>
+      </c>
+      <c r="C25" t="s">
+        <v>224</v>
+      </c>
+      <c r="D25" t="s">
+        <v>224</v>
+      </c>
+      <c r="E25" t="s">
+        <v>224</v>
+      </c>
+      <c r="F25" t="s">
+        <v>224</v>
+      </c>
+      <c r="H25" t="s">
         <v>50</v>
       </c>
-      <c r="C25" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="I25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J25" t="s">
         <v>32</v>
       </c>
-      <c r="E25" t="s">
+      <c r="K25" t="s">
         <v>38</v>
       </c>
-      <c r="F25" t="s">
+      <c r="L25" t="s">
         <v>39</v>
       </c>
-      <c r="G25" t="s">
+      <c r="M25" t="s">
         <v>28</v>
       </c>
-      <c r="H25" s="2">
+      <c r="N25" s="2">
         <v>46189</v>
       </c>
-      <c r="I25" s="2">
+      <c r="O25" s="2">
         <v>46185</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>54</v>
       </c>
       <c r="B26" t="s">
+        <v>224</v>
+      </c>
+      <c r="C26" t="s">
+        <v>224</v>
+      </c>
+      <c r="D26" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" t="s">
+        <v>224</v>
+      </c>
+      <c r="F26" t="s">
+        <v>224</v>
+      </c>
+      <c r="H26" t="s">
         <v>50</v>
       </c>
-      <c r="C26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="I26" t="s">
+        <v>11</v>
+      </c>
+      <c r="J26" t="s">
         <v>32</v>
       </c>
-      <c r="E26" t="s">
+      <c r="K26" t="s">
         <v>38</v>
       </c>
-      <c r="F26" t="s">
+      <c r="L26" t="s">
         <v>39</v>
       </c>
-      <c r="G26" t="s">
+      <c r="M26" t="s">
         <v>28</v>
       </c>
-      <c r="H26" s="2">
+      <c r="N26" s="2">
         <v>46189</v>
       </c>
-      <c r="I26" s="2">
+      <c r="O26" s="2">
         <v>46185</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>55</v>
       </c>
       <c r="B27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C27" t="s">
+        <v>224</v>
+      </c>
+      <c r="D27" t="s">
+        <v>224</v>
+      </c>
+      <c r="E27" t="s">
+        <v>224</v>
+      </c>
+      <c r="F27" t="s">
+        <v>224</v>
+      </c>
+      <c r="H27" t="s">
         <v>50</v>
       </c>
-      <c r="C27" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="I27" t="s">
+        <v>11</v>
+      </c>
+      <c r="J27" t="s">
         <v>32</v>
       </c>
-      <c r="E27" t="s">
+      <c r="K27" t="s">
         <v>38</v>
       </c>
-      <c r="F27" t="s">
+      <c r="L27" t="s">
         <v>39</v>
       </c>
-      <c r="G27" t="s">
+      <c r="M27" t="s">
         <v>28</v>
       </c>
-      <c r="H27" s="2">
+      <c r="N27" s="2">
         <v>46189</v>
       </c>
-      <c r="I27" s="2">
+      <c r="O27" s="2">
         <v>46185</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>56</v>
       </c>
       <c r="B28" t="s">
+        <v>224</v>
+      </c>
+      <c r="C28" t="s">
+        <v>224</v>
+      </c>
+      <c r="D28" t="s">
+        <v>224</v>
+      </c>
+      <c r="E28" t="s">
+        <v>224</v>
+      </c>
+      <c r="F28" t="s">
+        <v>224</v>
+      </c>
+      <c r="H28" t="s">
         <v>50</v>
       </c>
-      <c r="C28" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="I28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J28" t="s">
         <v>32</v>
       </c>
-      <c r="E28" t="s">
+      <c r="K28" t="s">
         <v>38</v>
       </c>
-      <c r="F28" t="s">
+      <c r="L28" t="s">
         <v>39</v>
       </c>
-      <c r="G28" t="s">
+      <c r="M28" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="2">
+      <c r="N28" s="2">
         <v>46190</v>
       </c>
-      <c r="I28" s="2">
+      <c r="O28" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>57</v>
       </c>
       <c r="B29" t="s">
+        <v>224</v>
+      </c>
+      <c r="C29" t="s">
+        <v>224</v>
+      </c>
+      <c r="D29" t="s">
+        <v>224</v>
+      </c>
+      <c r="E29" t="s">
+        <v>224</v>
+      </c>
+      <c r="F29" t="s">
+        <v>224</v>
+      </c>
+      <c r="H29" t="s">
         <v>50</v>
       </c>
-      <c r="C29" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="I29" t="s">
+        <v>11</v>
+      </c>
+      <c r="J29" t="s">
         <v>32</v>
       </c>
-      <c r="E29" t="s">
+      <c r="K29" t="s">
         <v>38</v>
       </c>
-      <c r="F29" t="s">
+      <c r="L29" t="s">
         <v>39</v>
       </c>
-      <c r="G29" t="s">
+      <c r="M29" t="s">
         <v>34</v>
       </c>
-      <c r="H29" s="2">
+      <c r="N29" s="2">
         <v>46190</v>
       </c>
-      <c r="I29" s="2">
+      <c r="O29" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>58</v>
       </c>
       <c r="B30" t="s">
+        <v>224</v>
+      </c>
+      <c r="C30" t="s">
+        <v>224</v>
+      </c>
+      <c r="D30" t="s">
+        <v>224</v>
+      </c>
+      <c r="E30" t="s">
+        <v>224</v>
+      </c>
+      <c r="F30" t="s">
+        <v>224</v>
+      </c>
+      <c r="H30" t="s">
         <v>50</v>
       </c>
-      <c r="C30" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="I30" t="s">
+        <v>11</v>
+      </c>
+      <c r="J30" t="s">
         <v>32</v>
       </c>
-      <c r="E30" t="s">
+      <c r="K30" t="s">
         <v>38</v>
       </c>
-      <c r="F30" t="s">
+      <c r="L30" t="s">
         <v>39</v>
       </c>
-      <c r="G30" t="s">
+      <c r="M30" t="s">
         <v>34</v>
       </c>
-      <c r="H30" s="2">
+      <c r="N30" s="2">
         <v>46189</v>
       </c>
-      <c r="I30" s="2">
+      <c r="O30" s="2">
         <v>46185</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>59</v>
       </c>
       <c r="B31" t="s">
+        <v>224</v>
+      </c>
+      <c r="C31" t="s">
+        <v>224</v>
+      </c>
+      <c r="D31" t="s">
+        <v>224</v>
+      </c>
+      <c r="E31" t="s">
+        <v>224</v>
+      </c>
+      <c r="F31" t="s">
+        <v>224</v>
+      </c>
+      <c r="H31" t="s">
         <v>50</v>
       </c>
-      <c r="C31" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="I31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J31" t="s">
         <v>32</v>
       </c>
-      <c r="E31" t="s">
+      <c r="K31" t="s">
         <v>38</v>
       </c>
-      <c r="F31" t="s">
+      <c r="L31" t="s">
         <v>39</v>
       </c>
-      <c r="G31" t="s">
+      <c r="M31" t="s">
         <v>34</v>
       </c>
-      <c r="H31" s="2">
+      <c r="N31" s="2">
         <v>46189</v>
       </c>
-      <c r="I31" s="2">
+      <c r="O31" s="2">
         <v>46185</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>60</v>
       </c>
       <c r="B32" t="s">
+        <v>224</v>
+      </c>
+      <c r="C32" t="s">
+        <v>224</v>
+      </c>
+      <c r="D32" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" t="s">
+        <v>224</v>
+      </c>
+      <c r="F32" t="s">
+        <v>224</v>
+      </c>
+      <c r="H32" t="s">
         <v>50</v>
       </c>
-      <c r="C32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="I32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J32" t="s">
         <v>32</v>
       </c>
-      <c r="E32" t="s">
+      <c r="K32" t="s">
         <v>38</v>
       </c>
-      <c r="F32" t="s">
+      <c r="L32" t="s">
         <v>39</v>
       </c>
-      <c r="G32" t="s">
+      <c r="M32" t="s">
         <v>34</v>
       </c>
-      <c r="H32" s="2">
+      <c r="N32" s="2">
         <v>46190</v>
       </c>
-      <c r="I32" s="2">
+      <c r="O32" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>61</v>
       </c>
       <c r="B33" t="s">
+        <v>224</v>
+      </c>
+      <c r="C33" t="s">
+        <v>224</v>
+      </c>
+      <c r="D33" t="s">
+        <v>224</v>
+      </c>
+      <c r="E33" t="s">
+        <v>224</v>
+      </c>
+      <c r="F33" t="s">
+        <v>224</v>
+      </c>
+      <c r="H33" t="s">
         <v>50</v>
       </c>
-      <c r="C33" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="I33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J33" t="s">
         <v>32</v>
       </c>
-      <c r="E33" t="s">
+      <c r="K33" t="s">
         <v>38</v>
       </c>
-      <c r="F33" t="s">
+      <c r="L33" t="s">
         <v>39</v>
       </c>
-      <c r="G33" t="s">
+      <c r="M33" t="s">
         <v>44</v>
       </c>
-      <c r="H33" s="2">
+      <c r="N33" s="2">
         <v>46190</v>
       </c>
-      <c r="I33" s="2">
+      <c r="O33" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>62</v>
       </c>
       <c r="B34" t="s">
+        <v>224</v>
+      </c>
+      <c r="C34" t="s">
+        <v>224</v>
+      </c>
+      <c r="D34" t="s">
+        <v>224</v>
+      </c>
+      <c r="E34" t="s">
+        <v>224</v>
+      </c>
+      <c r="F34" t="s">
+        <v>224</v>
+      </c>
+      <c r="H34" t="s">
         <v>50</v>
       </c>
-      <c r="C34" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="I34" t="s">
+        <v>11</v>
+      </c>
+      <c r="J34" t="s">
         <v>32</v>
       </c>
-      <c r="E34" t="s">
+      <c r="K34" t="s">
         <v>38</v>
       </c>
-      <c r="F34" t="s">
+      <c r="L34" t="s">
         <v>39</v>
       </c>
-      <c r="G34" t="s">
+      <c r="M34" t="s">
         <v>44</v>
       </c>
-      <c r="H34" s="2">
+      <c r="N34" s="2">
         <v>46190</v>
       </c>
-      <c r="I34" s="2">
+      <c r="O34" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>63</v>
       </c>
       <c r="B35" t="s">
+        <v>224</v>
+      </c>
+      <c r="C35" t="s">
+        <v>224</v>
+      </c>
+      <c r="D35" t="s">
+        <v>224</v>
+      </c>
+      <c r="E35" t="s">
+        <v>224</v>
+      </c>
+      <c r="F35" t="s">
+        <v>224</v>
+      </c>
+      <c r="H35" t="s">
         <v>50</v>
       </c>
-      <c r="C35" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="I35" t="s">
+        <v>11</v>
+      </c>
+      <c r="J35" t="s">
         <v>32</v>
       </c>
-      <c r="E35" t="s">
+      <c r="K35" t="s">
         <v>38</v>
       </c>
-      <c r="F35" t="s">
+      <c r="L35" t="s">
         <v>39</v>
       </c>
-      <c r="G35" t="s">
+      <c r="M35" t="s">
         <v>44</v>
       </c>
-      <c r="H35" s="2">
+      <c r="N35" s="2">
         <v>46190</v>
       </c>
-      <c r="I35" s="2">
+      <c r="O35" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>64</v>
       </c>
       <c r="B36" t="s">
+        <v>224</v>
+      </c>
+      <c r="C36" t="s">
+        <v>224</v>
+      </c>
+      <c r="D36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E36" t="s">
+        <v>224</v>
+      </c>
+      <c r="F36" t="s">
+        <v>224</v>
+      </c>
+      <c r="H36" t="s">
         <v>50</v>
       </c>
-      <c r="C36" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="I36" t="s">
+        <v>11</v>
+      </c>
+      <c r="J36" t="s">
         <v>32</v>
       </c>
-      <c r="E36" t="s">
+      <c r="K36" t="s">
         <v>38</v>
       </c>
-      <c r="F36" t="s">
+      <c r="L36" t="s">
         <v>39</v>
       </c>
-      <c r="G36" t="s">
+      <c r="M36" t="s">
         <v>44</v>
       </c>
-      <c r="H36" s="2">
+      <c r="N36" s="2">
         <v>46190</v>
       </c>
-      <c r="I36" s="2">
+      <c r="O36" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>65</v>
       </c>
       <c r="B37" t="s">
+        <v>224</v>
+      </c>
+      <c r="C37" t="s">
+        <v>224</v>
+      </c>
+      <c r="D37" t="s">
+        <v>224</v>
+      </c>
+      <c r="E37" t="s">
+        <v>224</v>
+      </c>
+      <c r="F37" t="s">
+        <v>224</v>
+      </c>
+      <c r="H37" t="s">
         <v>66</v>
       </c>
-      <c r="C37" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="I37" t="s">
+        <v>11</v>
+      </c>
+      <c r="J37" t="s">
         <v>32</v>
       </c>
-      <c r="E37" t="s">
+      <c r="K37" t="s">
         <v>38</v>
       </c>
-      <c r="F37" t="s">
+      <c r="L37" t="s">
         <v>39</v>
       </c>
-      <c r="G37" t="s">
+      <c r="M37" t="s">
         <v>28</v>
       </c>
-      <c r="H37" s="2">
+      <c r="N37" s="2">
         <v>46209</v>
       </c>
-      <c r="I37" s="2">
+      <c r="O37" s="2">
         <v>46209</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>67</v>
       </c>
       <c r="B38" t="s">
+        <v>224</v>
+      </c>
+      <c r="C38" t="s">
+        <v>224</v>
+      </c>
+      <c r="D38" t="s">
+        <v>224</v>
+      </c>
+      <c r="E38" t="s">
+        <v>224</v>
+      </c>
+      <c r="F38" t="s">
+        <v>224</v>
+      </c>
+      <c r="H38" t="s">
         <v>66</v>
       </c>
-      <c r="C38" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="I38" t="s">
+        <v>11</v>
+      </c>
+      <c r="J38" t="s">
         <v>32</v>
       </c>
-      <c r="E38" t="s">
+      <c r="K38" t="s">
         <v>38</v>
       </c>
-      <c r="F38" t="s">
+      <c r="L38" t="s">
         <v>39</v>
       </c>
-      <c r="G38" t="s">
+      <c r="M38" t="s">
         <v>28</v>
       </c>
-      <c r="H38" s="2">
+      <c r="N38" s="2">
         <v>46211</v>
       </c>
-      <c r="I38" s="2">
+      <c r="O38" s="2">
         <v>46211</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>68</v>
       </c>
       <c r="B39" t="s">
+        <v>224</v>
+      </c>
+      <c r="C39" t="s">
+        <v>224</v>
+      </c>
+      <c r="D39" t="s">
+        <v>224</v>
+      </c>
+      <c r="E39" t="s">
+        <v>224</v>
+      </c>
+      <c r="F39" t="s">
+        <v>224</v>
+      </c>
+      <c r="H39" t="s">
         <v>66</v>
       </c>
-      <c r="C39" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="I39" t="s">
+        <v>11</v>
+      </c>
+      <c r="J39" t="s">
         <v>32</v>
       </c>
-      <c r="E39" t="s">
+      <c r="K39" t="s">
         <v>38</v>
       </c>
-      <c r="F39" t="s">
+      <c r="L39" t="s">
         <v>39</v>
       </c>
-      <c r="G39" t="s">
+      <c r="M39" t="s">
         <v>28</v>
       </c>
-      <c r="H39" s="2">
+      <c r="N39" s="2">
         <v>46209</v>
       </c>
-      <c r="I39" s="2">
+      <c r="O39" s="2">
         <v>46209</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>69</v>
       </c>
       <c r="B40" t="s">
+        <v>224</v>
+      </c>
+      <c r="C40" t="s">
+        <v>224</v>
+      </c>
+      <c r="D40" t="s">
+        <v>224</v>
+      </c>
+      <c r="E40" t="s">
+        <v>224</v>
+      </c>
+      <c r="F40" t="s">
+        <v>224</v>
+      </c>
+      <c r="H40" t="s">
         <v>66</v>
       </c>
-      <c r="C40" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="I40" t="s">
+        <v>11</v>
+      </c>
+      <c r="J40" t="s">
         <v>32</v>
       </c>
-      <c r="E40" t="s">
+      <c r="K40" t="s">
         <v>38</v>
       </c>
-      <c r="F40" t="s">
+      <c r="L40" t="s">
         <v>39</v>
       </c>
-      <c r="G40" t="s">
+      <c r="M40" t="s">
         <v>28</v>
       </c>
-      <c r="H40" s="2">
+      <c r="N40" s="2">
         <v>46210</v>
       </c>
-      <c r="I40" s="2">
+      <c r="O40" s="2">
         <v>46209</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>70</v>
       </c>
-      <c r="B41" t="s">
+      <c r="H41" t="s">
         <v>66</v>
       </c>
-      <c r="C41" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="I41" t="s">
+        <v>11</v>
+      </c>
+      <c r="J41" t="s">
         <v>32</v>
       </c>
-      <c r="E41" t="s">
+      <c r="K41" t="s">
         <v>38</v>
       </c>
-      <c r="F41" t="s">
+      <c r="L41" t="s">
         <v>39</v>
       </c>
-      <c r="G41" t="s">
+      <c r="M41" t="s">
         <v>28</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="N41" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I41" s="2">
+      <c r="O41" s="2">
         <v>46205</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>71</v>
       </c>
       <c r="B42" t="s">
+        <v>224</v>
+      </c>
+      <c r="C42" t="s">
+        <v>224</v>
+      </c>
+      <c r="D42" t="s">
+        <v>224</v>
+      </c>
+      <c r="E42" t="s">
+        <v>224</v>
+      </c>
+      <c r="F42" t="s">
+        <v>224</v>
+      </c>
+      <c r="H42" t="s">
         <v>66</v>
       </c>
-      <c r="C42" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="I42" t="s">
+        <v>11</v>
+      </c>
+      <c r="J42" t="s">
         <v>32</v>
       </c>
-      <c r="E42" t="s">
+      <c r="K42" t="s">
         <v>38</v>
       </c>
-      <c r="F42" t="s">
+      <c r="L42" t="s">
         <v>39</v>
       </c>
-      <c r="G42" t="s">
+      <c r="M42" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="2">
+      <c r="N42" s="2">
         <v>46209</v>
       </c>
-      <c r="I42" s="2">
+      <c r="O42" s="2">
         <v>46209</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>72</v>
       </c>
       <c r="B43" t="s">
+        <v>224</v>
+      </c>
+      <c r="C43" t="s">
+        <v>224</v>
+      </c>
+      <c r="D43" t="s">
+        <v>224</v>
+      </c>
+      <c r="E43" t="s">
+        <v>224</v>
+      </c>
+      <c r="F43" t="s">
+        <v>224</v>
+      </c>
+      <c r="H43" t="s">
         <v>66</v>
       </c>
-      <c r="C43" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="I43" t="s">
+        <v>11</v>
+      </c>
+      <c r="J43" t="s">
         <v>32</v>
       </c>
-      <c r="E43" t="s">
+      <c r="K43" t="s">
         <v>38</v>
       </c>
-      <c r="F43" t="s">
+      <c r="L43" t="s">
         <v>39</v>
       </c>
-      <c r="G43" t="s">
+      <c r="M43" t="s">
         <v>28</v>
       </c>
-      <c r="H43" s="2">
+      <c r="N43" s="2">
         <v>46209</v>
       </c>
-      <c r="I43" s="2">
+      <c r="O43" s="2">
         <v>46209</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>73</v>
       </c>
-      <c r="B44" t="s">
+      <c r="H44" t="s">
         <v>66</v>
       </c>
-      <c r="C44" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="I44" t="s">
+        <v>11</v>
+      </c>
+      <c r="J44" t="s">
         <v>32</v>
       </c>
-      <c r="E44" t="s">
+      <c r="K44" t="s">
         <v>38</v>
       </c>
-      <c r="F44" t="s">
+      <c r="L44" t="s">
         <v>39</v>
       </c>
-      <c r="G44" t="s">
+      <c r="M44" t="s">
         <v>28</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="N44" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="2">
+      <c r="O44" s="2">
         <v>46205</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>74</v>
       </c>
       <c r="B45" t="s">
+        <v>224</v>
+      </c>
+      <c r="C45" t="s">
+        <v>224</v>
+      </c>
+      <c r="D45" t="s">
+        <v>224</v>
+      </c>
+      <c r="E45" t="s">
+        <v>224</v>
+      </c>
+      <c r="F45" t="s">
+        <v>224</v>
+      </c>
+      <c r="H45" t="s">
         <v>66</v>
       </c>
-      <c r="C45" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="I45" t="s">
+        <v>11</v>
+      </c>
+      <c r="J45" t="s">
         <v>32</v>
       </c>
-      <c r="E45" t="s">
+      <c r="K45" t="s">
         <v>38</v>
       </c>
-      <c r="F45" t="s">
+      <c r="L45" t="s">
         <v>39</v>
       </c>
-      <c r="G45" t="s">
+      <c r="M45" t="s">
         <v>28</v>
       </c>
-      <c r="H45" s="2">
+      <c r="N45" s="2">
         <v>46211</v>
       </c>
-      <c r="I45" s="2">
+      <c r="O45" s="2">
         <v>46211</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>75</v>
       </c>
       <c r="B46" t="s">
+        <v>224</v>
+      </c>
+      <c r="C46" t="s">
+        <v>224</v>
+      </c>
+      <c r="D46" t="s">
+        <v>224</v>
+      </c>
+      <c r="E46" t="s">
+        <v>224</v>
+      </c>
+      <c r="F46" t="s">
+        <v>224</v>
+      </c>
+      <c r="H46" t="s">
         <v>66</v>
       </c>
-      <c r="C46" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="I46" t="s">
+        <v>11</v>
+      </c>
+      <c r="J46" t="s">
         <v>32</v>
       </c>
-      <c r="E46" t="s">
+      <c r="K46" t="s">
         <v>38</v>
       </c>
-      <c r="F46" t="s">
+      <c r="L46" t="s">
         <v>39</v>
       </c>
-      <c r="G46" t="s">
+      <c r="M46" t="s">
         <v>34</v>
       </c>
-      <c r="H46" s="2">
+      <c r="N46" s="2">
         <v>46211</v>
       </c>
-      <c r="I46" s="2">
+      <c r="O46" s="2">
         <v>46211</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>76</v>
       </c>
       <c r="B47" t="s">
+        <v>224</v>
+      </c>
+      <c r="C47" t="s">
+        <v>224</v>
+      </c>
+      <c r="D47" t="s">
+        <v>224</v>
+      </c>
+      <c r="E47" t="s">
+        <v>224</v>
+      </c>
+      <c r="F47" t="s">
+        <v>224</v>
+      </c>
+      <c r="H47" t="s">
         <v>66</v>
       </c>
-      <c r="C47" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="I47" t="s">
+        <v>11</v>
+      </c>
+      <c r="J47" t="s">
         <v>32</v>
       </c>
-      <c r="E47" t="s">
+      <c r="K47" t="s">
         <v>38</v>
       </c>
-      <c r="F47" t="s">
+      <c r="L47" t="s">
         <v>39</v>
       </c>
-      <c r="G47" t="s">
+      <c r="M47" t="s">
         <v>34</v>
       </c>
-      <c r="H47" s="2">
+      <c r="N47" s="2">
         <v>46211</v>
       </c>
-      <c r="I47" s="2">
+      <c r="O47" s="2">
         <v>46211</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>77</v>
       </c>
-      <c r="B48" t="s">
+      <c r="H48" t="s">
         <v>66</v>
       </c>
-      <c r="C48" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="I48" t="s">
+        <v>11</v>
+      </c>
+      <c r="J48" t="s">
         <v>32</v>
       </c>
-      <c r="E48" t="s">
+      <c r="K48" t="s">
         <v>38</v>
       </c>
-      <c r="F48" t="s">
+      <c r="L48" t="s">
         <v>39</v>
       </c>
-      <c r="G48" t="s">
+      <c r="M48" t="s">
         <v>34</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="N48" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I48" s="2">
+      <c r="O48" s="2">
         <v>46205</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>78</v>
       </c>
       <c r="B49" t="s">
+        <v>224</v>
+      </c>
+      <c r="C49" t="s">
+        <v>224</v>
+      </c>
+      <c r="D49" t="s">
+        <v>224</v>
+      </c>
+      <c r="E49" t="s">
+        <v>224</v>
+      </c>
+      <c r="F49" t="s">
+        <v>224</v>
+      </c>
+      <c r="H49" t="s">
         <v>66</v>
       </c>
-      <c r="C49" t="s">
-        <v>11</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="I49" t="s">
+        <v>11</v>
+      </c>
+      <c r="J49" t="s">
         <v>32</v>
       </c>
-      <c r="E49" t="s">
+      <c r="K49" t="s">
         <v>38</v>
       </c>
-      <c r="F49" t="s">
+      <c r="L49" t="s">
         <v>39</v>
       </c>
-      <c r="G49" t="s">
+      <c r="M49" t="s">
         <v>34</v>
       </c>
-      <c r="H49" s="2">
+      <c r="N49" s="2">
         <v>46217</v>
       </c>
-      <c r="I49" s="2">
+      <c r="O49" s="2">
         <v>46218</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>79</v>
       </c>
       <c r="B50" t="s">
+        <v>224</v>
+      </c>
+      <c r="C50" t="s">
+        <v>224</v>
+      </c>
+      <c r="D50" t="s">
+        <v>224</v>
+      </c>
+      <c r="E50" t="s">
+        <v>224</v>
+      </c>
+      <c r="F50" t="s">
+        <v>224</v>
+      </c>
+      <c r="H50" t="s">
         <v>10</v>
       </c>
-      <c r="C50" t="s">
-        <v>11</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="I50" t="s">
+        <v>11</v>
+      </c>
+      <c r="J50" t="s">
         <v>32</v>
       </c>
-      <c r="E50" t="s">
+      <c r="K50" t="s">
         <v>38</v>
       </c>
-      <c r="F50" t="s">
+      <c r="L50" t="s">
         <v>39</v>
       </c>
-      <c r="G50" t="s">
+      <c r="M50" t="s">
         <v>28</v>
       </c>
-      <c r="H50" s="2">
+      <c r="N50" s="2">
         <v>46190</v>
       </c>
-      <c r="I50" s="2">
+      <c r="O50" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>80</v>
       </c>
       <c r="B51" t="s">
+        <v>224</v>
+      </c>
+      <c r="C51" t="s">
+        <v>224</v>
+      </c>
+      <c r="D51" t="s">
+        <v>224</v>
+      </c>
+      <c r="E51" t="s">
+        <v>224</v>
+      </c>
+      <c r="F51" t="s">
+        <v>224</v>
+      </c>
+      <c r="H51" t="s">
         <v>10</v>
       </c>
-      <c r="C51" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="I51" t="s">
+        <v>11</v>
+      </c>
+      <c r="J51" t="s">
         <v>32</v>
       </c>
-      <c r="E51" t="s">
+      <c r="K51" t="s">
         <v>38</v>
       </c>
-      <c r="F51" t="s">
+      <c r="L51" t="s">
         <v>39</v>
       </c>
-      <c r="G51" t="s">
+      <c r="M51" t="s">
         <v>28</v>
       </c>
-      <c r="H51" s="2">
+      <c r="N51" s="2">
         <v>46190</v>
       </c>
-      <c r="I51" s="2">
+      <c r="O51" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>81</v>
       </c>
       <c r="B52" t="s">
+        <v>224</v>
+      </c>
+      <c r="C52" t="s">
+        <v>224</v>
+      </c>
+      <c r="D52" t="s">
+        <v>224</v>
+      </c>
+      <c r="E52" t="s">
+        <v>224</v>
+      </c>
+      <c r="F52" t="s">
+        <v>224</v>
+      </c>
+      <c r="H52" t="s">
         <v>10</v>
       </c>
-      <c r="C52" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="I52" t="s">
+        <v>11</v>
+      </c>
+      <c r="J52" t="s">
         <v>32</v>
       </c>
-      <c r="E52" t="s">
+      <c r="K52" t="s">
         <v>38</v>
       </c>
-      <c r="F52" t="s">
+      <c r="L52" t="s">
         <v>39</v>
       </c>
-      <c r="G52" t="s">
+      <c r="M52" t="s">
         <v>28</v>
       </c>
-      <c r="H52" s="2">
+      <c r="N52" s="2">
         <v>46190</v>
       </c>
-      <c r="I52" s="2">
+      <c r="O52" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>82</v>
       </c>
       <c r="B53" t="s">
+        <v>224</v>
+      </c>
+      <c r="C53" t="s">
+        <v>224</v>
+      </c>
+      <c r="D53" t="s">
+        <v>224</v>
+      </c>
+      <c r="E53" t="s">
+        <v>224</v>
+      </c>
+      <c r="F53" t="s">
+        <v>224</v>
+      </c>
+      <c r="H53" t="s">
         <v>10</v>
       </c>
-      <c r="C53" t="s">
-        <v>11</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="I53" t="s">
+        <v>11</v>
+      </c>
+      <c r="J53" t="s">
         <v>32</v>
       </c>
-      <c r="E53" t="s">
+      <c r="K53" t="s">
         <v>38</v>
       </c>
-      <c r="F53" t="s">
+      <c r="L53" t="s">
         <v>39</v>
       </c>
-      <c r="G53" t="s">
+      <c r="M53" t="s">
         <v>28</v>
       </c>
-      <c r="H53" s="2">
+      <c r="N53" s="2">
         <v>46191</v>
       </c>
-      <c r="I53" s="2">
+      <c r="O53" s="2">
         <v>46191</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>83</v>
       </c>
       <c r="B54" t="s">
+        <v>224</v>
+      </c>
+      <c r="C54" t="s">
+        <v>224</v>
+      </c>
+      <c r="D54" t="s">
+        <v>224</v>
+      </c>
+      <c r="E54" t="s">
+        <v>224</v>
+      </c>
+      <c r="F54" t="s">
+        <v>224</v>
+      </c>
+      <c r="H54" t="s">
         <v>10</v>
       </c>
-      <c r="C54" t="s">
-        <v>11</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="I54" t="s">
+        <v>11</v>
+      </c>
+      <c r="J54" t="s">
         <v>32</v>
       </c>
-      <c r="E54" t="s">
+      <c r="K54" t="s">
         <v>38</v>
       </c>
-      <c r="F54" t="s">
+      <c r="L54" t="s">
         <v>39</v>
       </c>
-      <c r="G54" t="s">
+      <c r="M54" t="s">
         <v>28</v>
       </c>
-      <c r="H54" s="2">
+      <c r="N54" s="2">
         <v>46191</v>
       </c>
-      <c r="I54" s="2">
+      <c r="O54" s="2">
         <v>46191</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>84</v>
       </c>
       <c r="B55" t="s">
+        <v>224</v>
+      </c>
+      <c r="C55" t="s">
+        <v>224</v>
+      </c>
+      <c r="D55" t="s">
+        <v>224</v>
+      </c>
+      <c r="E55" t="s">
+        <v>224</v>
+      </c>
+      <c r="F55" t="s">
+        <v>224</v>
+      </c>
+      <c r="H55" t="s">
         <v>10</v>
       </c>
-      <c r="C55" t="s">
-        <v>11</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="I55" t="s">
+        <v>11</v>
+      </c>
+      <c r="J55" t="s">
         <v>32</v>
       </c>
-      <c r="E55" t="s">
+      <c r="K55" t="s">
         <v>38</v>
       </c>
-      <c r="F55" t="s">
+      <c r="L55" t="s">
         <v>39</v>
       </c>
-      <c r="G55" t="s">
+      <c r="M55" t="s">
         <v>28</v>
       </c>
-      <c r="H55" s="2">
+      <c r="N55" s="2">
         <v>46190</v>
       </c>
-      <c r="I55" s="2">
+      <c r="O55" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>85</v>
       </c>
       <c r="B56" t="s">
+        <v>224</v>
+      </c>
+      <c r="C56" t="s">
+        <v>224</v>
+      </c>
+      <c r="D56" t="s">
+        <v>224</v>
+      </c>
+      <c r="E56" t="s">
+        <v>224</v>
+      </c>
+      <c r="F56" t="s">
+        <v>224</v>
+      </c>
+      <c r="H56" t="s">
         <v>10</v>
       </c>
-      <c r="C56" t="s">
-        <v>11</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="I56" t="s">
+        <v>11</v>
+      </c>
+      <c r="J56" t="s">
         <v>32</v>
       </c>
-      <c r="E56" t="s">
+      <c r="K56" t="s">
         <v>38</v>
       </c>
-      <c r="F56" t="s">
+      <c r="L56" t="s">
         <v>39</v>
       </c>
-      <c r="G56" t="s">
+      <c r="M56" t="s">
         <v>28</v>
       </c>
-      <c r="H56" s="2">
+      <c r="N56" s="2">
         <v>46191</v>
       </c>
-      <c r="I56" s="2">
+      <c r="O56" s="2">
         <v>46191</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>86</v>
       </c>
       <c r="B57" t="s">
+        <v>224</v>
+      </c>
+      <c r="C57" t="s">
+        <v>224</v>
+      </c>
+      <c r="D57" t="s">
+        <v>224</v>
+      </c>
+      <c r="E57" t="s">
+        <v>224</v>
+      </c>
+      <c r="F57" t="s">
+        <v>224</v>
+      </c>
+      <c r="H57" t="s">
         <v>10</v>
       </c>
-      <c r="C57" t="s">
-        <v>11</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="I57" t="s">
+        <v>11</v>
+      </c>
+      <c r="J57" t="s">
         <v>32</v>
       </c>
-      <c r="E57" t="s">
+      <c r="K57" t="s">
         <v>38</v>
       </c>
-      <c r="F57" t="s">
+      <c r="L57" t="s">
         <v>39</v>
       </c>
-      <c r="G57" t="s">
+      <c r="M57" t="s">
         <v>28</v>
       </c>
-      <c r="H57" s="2">
+      <c r="N57" s="2">
         <v>46191</v>
       </c>
-      <c r="I57" s="2">
+      <c r="O57" s="2">
         <v>46191</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>87</v>
       </c>
       <c r="B58" t="s">
+        <v>224</v>
+      </c>
+      <c r="C58" t="s">
+        <v>224</v>
+      </c>
+      <c r="D58" t="s">
+        <v>224</v>
+      </c>
+      <c r="E58" t="s">
+        <v>224</v>
+      </c>
+      <c r="F58" t="s">
+        <v>224</v>
+      </c>
+      <c r="H58" t="s">
         <v>10</v>
       </c>
-      <c r="C58" t="s">
-        <v>11</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="I58" t="s">
+        <v>11</v>
+      </c>
+      <c r="J58" t="s">
         <v>32</v>
       </c>
-      <c r="E58" t="s">
+      <c r="K58" t="s">
         <v>38</v>
       </c>
-      <c r="F58" t="s">
+      <c r="L58" t="s">
         <v>39</v>
       </c>
-      <c r="G58" t="s">
+      <c r="M58" t="s">
         <v>28</v>
       </c>
-      <c r="H58" s="2">
+      <c r="N58" s="2">
         <v>46193</v>
       </c>
-      <c r="I58" s="2">
+      <c r="O58" s="2">
         <v>46193</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>88</v>
       </c>
       <c r="B59" t="s">
+        <v>224</v>
+      </c>
+      <c r="C59" t="s">
+        <v>224</v>
+      </c>
+      <c r="D59" t="s">
+        <v>224</v>
+      </c>
+      <c r="E59" t="s">
+        <v>224</v>
+      </c>
+      <c r="F59" t="s">
+        <v>224</v>
+      </c>
+      <c r="H59" t="s">
         <v>10</v>
       </c>
-      <c r="C59" t="s">
-        <v>11</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="I59" t="s">
+        <v>11</v>
+      </c>
+      <c r="J59" t="s">
         <v>32</v>
       </c>
-      <c r="E59" t="s">
+      <c r="K59" t="s">
         <v>38</v>
       </c>
-      <c r="F59" t="s">
+      <c r="L59" t="s">
         <v>39</v>
       </c>
-      <c r="G59" t="s">
+      <c r="M59" t="s">
         <v>34</v>
       </c>
-      <c r="H59" s="2">
+      <c r="N59" s="2">
         <v>46190</v>
       </c>
-      <c r="I59" s="2">
+      <c r="O59" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>89</v>
       </c>
       <c r="B60" t="s">
+        <v>224</v>
+      </c>
+      <c r="C60" t="s">
+        <v>224</v>
+      </c>
+      <c r="D60" t="s">
+        <v>224</v>
+      </c>
+      <c r="E60" t="s">
+        <v>224</v>
+      </c>
+      <c r="F60" t="s">
+        <v>224</v>
+      </c>
+      <c r="H60" t="s">
         <v>10</v>
       </c>
-      <c r="C60" t="s">
-        <v>11</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="I60" t="s">
+        <v>11</v>
+      </c>
+      <c r="J60" t="s">
         <v>32</v>
       </c>
-      <c r="E60" t="s">
+      <c r="K60" t="s">
         <v>38</v>
       </c>
-      <c r="F60" t="s">
+      <c r="L60" t="s">
         <v>39</v>
       </c>
-      <c r="G60" t="s">
+      <c r="M60" t="s">
         <v>34</v>
       </c>
-      <c r="H60" s="2">
+      <c r="N60" s="2">
         <v>46191</v>
       </c>
-      <c r="I60" s="2">
+      <c r="O60" s="2">
         <v>46191</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>90</v>
       </c>
       <c r="B61" t="s">
+        <v>224</v>
+      </c>
+      <c r="C61" t="s">
+        <v>224</v>
+      </c>
+      <c r="D61" t="s">
+        <v>224</v>
+      </c>
+      <c r="E61" t="s">
+        <v>224</v>
+      </c>
+      <c r="F61" t="s">
+        <v>224</v>
+      </c>
+      <c r="H61" t="s">
         <v>10</v>
       </c>
-      <c r="C61" t="s">
-        <v>11</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="I61" t="s">
+        <v>11</v>
+      </c>
+      <c r="J61" t="s">
         <v>32</v>
       </c>
-      <c r="E61" t="s">
+      <c r="K61" t="s">
         <v>38</v>
       </c>
-      <c r="F61" t="s">
+      <c r="L61" t="s">
         <v>39</v>
       </c>
-      <c r="G61" t="s">
+      <c r="M61" t="s">
         <v>34</v>
       </c>
-      <c r="H61" s="2">
+      <c r="N61" s="2">
         <v>46190</v>
       </c>
-      <c r="I61" s="2">
+      <c r="O61" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>91</v>
       </c>
       <c r="B62" t="s">
+        <v>224</v>
+      </c>
+      <c r="C62" t="s">
+        <v>224</v>
+      </c>
+      <c r="D62" t="s">
+        <v>224</v>
+      </c>
+      <c r="E62" t="s">
+        <v>224</v>
+      </c>
+      <c r="F62" t="s">
+        <v>224</v>
+      </c>
+      <c r="H62" t="s">
         <v>10</v>
       </c>
-      <c r="C62" t="s">
-        <v>11</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="I62" t="s">
+        <v>11</v>
+      </c>
+      <c r="J62" t="s">
         <v>32</v>
       </c>
-      <c r="E62" t="s">
+      <c r="K62" t="s">
         <v>38</v>
       </c>
-      <c r="F62" t="s">
+      <c r="L62" t="s">
         <v>39</v>
       </c>
-      <c r="G62" t="s">
+      <c r="M62" t="s">
         <v>34</v>
       </c>
-      <c r="H62" s="2">
+      <c r="N62" s="2">
         <v>46190</v>
       </c>
-      <c r="I62" s="2">
+      <c r="O62" s="2">
         <v>46190</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>92</v>
       </c>
       <c r="B63" t="s">
+        <v>224</v>
+      </c>
+      <c r="C63" t="s">
+        <v>224</v>
+      </c>
+      <c r="D63" t="s">
+        <v>224</v>
+      </c>
+      <c r="E63" t="s">
+        <v>224</v>
+      </c>
+      <c r="F63" t="s">
+        <v>224</v>
+      </c>
+      <c r="H63" t="s">
         <v>50</v>
       </c>
-      <c r="C63" t="s">
-        <v>11</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="I63" t="s">
+        <v>11</v>
+      </c>
+      <c r="J63" t="s">
         <v>93</v>
       </c>
-      <c r="E63" t="s">
+      <c r="K63" t="s">
         <v>94</v>
       </c>
-      <c r="F63" t="s">
+      <c r="L63" t="s">
         <v>95</v>
       </c>
-      <c r="G63" t="s">
+      <c r="M63" t="s">
         <v>28</v>
       </c>
-      <c r="H63" s="2">
+      <c r="N63" s="2">
         <v>46171</v>
       </c>
-      <c r="I63" s="2">
+      <c r="O63" s="2">
         <v>46171</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>96</v>
       </c>
       <c r="B64" t="s">
+        <v>224</v>
+      </c>
+      <c r="C64" t="s">
+        <v>224</v>
+      </c>
+      <c r="D64" t="s">
+        <v>224</v>
+      </c>
+      <c r="E64" t="s">
+        <v>224</v>
+      </c>
+      <c r="F64" t="s">
+        <v>224</v>
+      </c>
+      <c r="H64" t="s">
         <v>50</v>
       </c>
-      <c r="C64" t="s">
-        <v>11</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="I64" t="s">
+        <v>11</v>
+      </c>
+      <c r="J64" t="s">
         <v>93</v>
       </c>
-      <c r="E64" t="s">
+      <c r="K64" t="s">
         <v>94</v>
       </c>
-      <c r="F64" t="s">
+      <c r="L64" t="s">
         <v>97</v>
       </c>
-      <c r="G64" t="s">
+      <c r="M64" t="s">
         <v>28</v>
       </c>
-      <c r="H64" s="2">
+      <c r="N64" s="2">
         <v>46171</v>
       </c>
-      <c r="I64" s="2">
+      <c r="O64" s="2">
         <v>46171</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>98</v>
       </c>
       <c r="B65" t="s">
+        <v>224</v>
+      </c>
+      <c r="C65" t="s">
+        <v>224</v>
+      </c>
+      <c r="D65" t="s">
+        <v>224</v>
+      </c>
+      <c r="E65" t="s">
+        <v>224</v>
+      </c>
+      <c r="F65" t="s">
+        <v>224</v>
+      </c>
+      <c r="H65" t="s">
         <v>50</v>
       </c>
-      <c r="C65" t="s">
-        <v>11</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="I65" t="s">
+        <v>11</v>
+      </c>
+      <c r="J65" t="s">
         <v>93</v>
       </c>
-      <c r="E65" t="s">
+      <c r="K65" t="s">
         <v>94</v>
       </c>
-      <c r="F65" t="s">
+      <c r="L65" t="s">
         <v>95</v>
       </c>
-      <c r="G65" t="s">
+      <c r="M65" t="s">
         <v>28</v>
       </c>
-      <c r="H65" s="2">
+      <c r="N65" s="2">
         <v>46171</v>
       </c>
-      <c r="I65" s="2">
+      <c r="O65" s="2">
         <v>46171</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>99</v>
       </c>
       <c r="B66" t="s">
+        <v>224</v>
+      </c>
+      <c r="C66" t="s">
+        <v>224</v>
+      </c>
+      <c r="D66" t="s">
+        <v>224</v>
+      </c>
+      <c r="E66" t="s">
+        <v>224</v>
+      </c>
+      <c r="F66" t="s">
+        <v>224</v>
+      </c>
+      <c r="H66" t="s">
         <v>50</v>
       </c>
-      <c r="C66" t="s">
-        <v>11</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="I66" t="s">
+        <v>11</v>
+      </c>
+      <c r="J66" t="s">
         <v>93</v>
       </c>
-      <c r="E66" t="s">
+      <c r="K66" t="s">
         <v>94</v>
       </c>
-      <c r="F66" t="s">
+      <c r="L66" t="s">
         <v>95</v>
       </c>
-      <c r="G66" t="s">
+      <c r="M66" t="s">
         <v>28</v>
       </c>
-      <c r="H66" s="2">
+      <c r="N66" s="2">
         <v>46170</v>
       </c>
-      <c r="I66" s="2">
+      <c r="O66" s="2">
         <v>46170</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>100</v>
       </c>
       <c r="B67" t="s">
+        <v>224</v>
+      </c>
+      <c r="C67" t="s">
+        <v>224</v>
+      </c>
+      <c r="D67" t="s">
+        <v>224</v>
+      </c>
+      <c r="E67" t="s">
+        <v>224</v>
+      </c>
+      <c r="F67" t="s">
+        <v>224</v>
+      </c>
+      <c r="H67" t="s">
         <v>50</v>
       </c>
-      <c r="C67" t="s">
-        <v>11</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="I67" t="s">
+        <v>11</v>
+      </c>
+      <c r="J67" t="s">
         <v>93</v>
       </c>
-      <c r="E67" t="s">
+      <c r="K67" t="s">
         <v>94</v>
       </c>
-      <c r="F67" t="s">
+      <c r="L67" t="s">
         <v>95</v>
       </c>
-      <c r="G67" t="s">
+      <c r="M67" t="s">
         <v>28</v>
       </c>
-      <c r="H67" s="2">
+      <c r="N67" s="2">
         <v>46171</v>
       </c>
-      <c r="I67" s="2">
+      <c r="O67" s="2">
         <v>46171</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>101</v>
       </c>
       <c r="B68" t="s">
+        <v>224</v>
+      </c>
+      <c r="C68" t="s">
+        <v>224</v>
+      </c>
+      <c r="D68" t="s">
+        <v>224</v>
+      </c>
+      <c r="E68" t="s">
+        <v>224</v>
+      </c>
+      <c r="F68" t="s">
+        <v>224</v>
+      </c>
+      <c r="H68" t="s">
         <v>24</v>
       </c>
-      <c r="C68" t="s">
-        <v>11</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="I68" t="s">
+        <v>11</v>
+      </c>
+      <c r="J68" t="s">
         <v>93</v>
       </c>
-      <c r="E68" t="s">
+      <c r="K68" t="s">
         <v>94</v>
       </c>
-      <c r="F68" t="s">
+      <c r="L68" t="s">
         <v>97</v>
       </c>
-      <c r="G68" t="s">
+      <c r="M68" t="s">
         <v>28</v>
       </c>
-      <c r="H68" s="2">
+      <c r="N68" s="2">
         <v>46154</v>
       </c>
-      <c r="I68" s="2">
+      <c r="O68" s="2">
         <v>46154</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>102</v>
       </c>
       <c r="B69" t="s">
+        <v>224</v>
+      </c>
+      <c r="C69" t="s">
+        <v>224</v>
+      </c>
+      <c r="D69" t="s">
+        <v>224</v>
+      </c>
+      <c r="E69" t="s">
+        <v>224</v>
+      </c>
+      <c r="F69" t="s">
+        <v>224</v>
+      </c>
+      <c r="H69" t="s">
         <v>24</v>
       </c>
-      <c r="C69" t="s">
-        <v>11</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="I69" t="s">
+        <v>11</v>
+      </c>
+      <c r="J69" t="s">
         <v>93</v>
       </c>
-      <c r="E69" t="s">
+      <c r="K69" t="s">
         <v>94</v>
       </c>
-      <c r="F69" t="s">
+      <c r="L69" t="s">
         <v>97</v>
       </c>
-      <c r="G69" t="s">
+      <c r="M69" t="s">
         <v>28</v>
       </c>
-      <c r="H69" s="2">
+      <c r="N69" s="2">
         <v>46154</v>
       </c>
-      <c r="I69" s="2">
+      <c r="O69" s="2">
         <v>46154</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>103</v>
       </c>
       <c r="B70" t="s">
+        <v>224</v>
+      </c>
+      <c r="C70" t="s">
+        <v>224</v>
+      </c>
+      <c r="D70" t="s">
+        <v>224</v>
+      </c>
+      <c r="E70" t="s">
+        <v>224</v>
+      </c>
+      <c r="F70" t="s">
+        <v>224</v>
+      </c>
+      <c r="H70" t="s">
         <v>24</v>
       </c>
-      <c r="C70" t="s">
-        <v>11</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="I70" t="s">
+        <v>11</v>
+      </c>
+      <c r="J70" t="s">
         <v>93</v>
       </c>
-      <c r="E70" t="s">
+      <c r="K70" t="s">
         <v>94</v>
       </c>
-      <c r="F70" t="s">
+      <c r="L70" t="s">
         <v>97</v>
       </c>
-      <c r="G70" t="s">
+      <c r="M70" t="s">
         <v>28</v>
       </c>
-      <c r="H70" s="2">
+      <c r="N70" s="2">
         <v>46154</v>
       </c>
-      <c r="I70" s="2">
+      <c r="O70" s="2">
         <v>46154</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>104</v>
       </c>
       <c r="B71" t="s">
+        <v>224</v>
+      </c>
+      <c r="C71" t="s">
+        <v>224</v>
+      </c>
+      <c r="D71" t="s">
+        <v>224</v>
+      </c>
+      <c r="E71" t="s">
+        <v>224</v>
+      </c>
+      <c r="F71" t="s">
+        <v>224</v>
+      </c>
+      <c r="H71" t="s">
         <v>24</v>
       </c>
-      <c r="C71" t="s">
-        <v>11</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="I71" t="s">
+        <v>11</v>
+      </c>
+      <c r="J71" t="s">
         <v>93</v>
       </c>
-      <c r="E71" t="s">
+      <c r="K71" t="s">
         <v>94</v>
       </c>
-      <c r="F71" t="s">
+      <c r="L71" t="s">
         <v>97</v>
       </c>
-      <c r="G71" t="s">
+      <c r="M71" t="s">
         <v>28</v>
       </c>
-      <c r="H71" s="2">
+      <c r="N71" s="2">
         <v>46154</v>
       </c>
-      <c r="I71" s="2">
+      <c r="O71" s="2">
         <v>46154</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>105</v>
       </c>
       <c r="B72" t="s">
+        <v>224</v>
+      </c>
+      <c r="C72" t="s">
+        <v>224</v>
+      </c>
+      <c r="D72" t="s">
+        <v>224</v>
+      </c>
+      <c r="E72" t="s">
+        <v>224</v>
+      </c>
+      <c r="F72" t="s">
+        <v>224</v>
+      </c>
+      <c r="H72" t="s">
         <v>24</v>
       </c>
-      <c r="C72" t="s">
-        <v>11</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="I72" t="s">
+        <v>11</v>
+      </c>
+      <c r="J72" t="s">
         <v>93</v>
       </c>
-      <c r="E72" t="s">
+      <c r="K72" t="s">
         <v>94</v>
       </c>
-      <c r="F72" t="s">
+      <c r="L72" t="s">
         <v>97</v>
       </c>
-      <c r="G72" t="s">
+      <c r="M72" t="s">
         <v>28</v>
       </c>
-      <c r="H72" s="2">
+      <c r="N72" s="2">
         <v>46154</v>
       </c>
-      <c r="I72" s="2">
+      <c r="O72" s="2">
         <v>46154</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>106</v>
       </c>
       <c r="B73" t="s">
+        <v>224</v>
+      </c>
+      <c r="C73" t="s">
+        <v>224</v>
+      </c>
+      <c r="D73" t="s">
+        <v>224</v>
+      </c>
+      <c r="E73" t="s">
+        <v>224</v>
+      </c>
+      <c r="F73" t="s">
+        <v>224</v>
+      </c>
+      <c r="H73" t="s">
         <v>107</v>
       </c>
-      <c r="C73" t="s">
-        <v>11</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="I73" t="s">
+        <v>11</v>
+      </c>
+      <c r="J73" t="s">
         <v>93</v>
       </c>
-      <c r="E73" t="s">
+      <c r="K73" t="s">
         <v>94</v>
       </c>
-      <c r="F73" t="s">
+      <c r="L73" t="s">
         <v>95</v>
       </c>
-      <c r="G73" t="s">
+      <c r="M73" t="s">
         <v>34</v>
       </c>
-      <c r="H73" s="2">
+      <c r="N73" s="2">
         <v>46253</v>
       </c>
-      <c r="I73" s="2">
+      <c r="O73" s="2">
         <v>46253</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>108</v>
       </c>
       <c r="B74" t="s">
+        <v>224</v>
+      </c>
+      <c r="C74" t="s">
+        <v>224</v>
+      </c>
+      <c r="D74" t="s">
+        <v>224</v>
+      </c>
+      <c r="E74" t="s">
+        <v>224</v>
+      </c>
+      <c r="F74" t="s">
+        <v>224</v>
+      </c>
+      <c r="H74" t="s">
         <v>107</v>
       </c>
-      <c r="C74" t="s">
-        <v>11</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="I74" t="s">
+        <v>11</v>
+      </c>
+      <c r="J74" t="s">
         <v>93</v>
       </c>
-      <c r="E74" t="s">
+      <c r="K74" t="s">
         <v>94</v>
       </c>
-      <c r="F74" t="s">
+      <c r="L74" t="s">
         <v>95</v>
       </c>
-      <c r="G74" t="s">
+      <c r="M74" t="s">
         <v>34</v>
       </c>
-      <c r="H74" s="2">
+      <c r="N74" s="2">
         <v>46255</v>
       </c>
-      <c r="I74" s="2">
+      <c r="O74" s="2">
         <v>46255</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>109</v>
       </c>
       <c r="B75" t="s">
+        <v>224</v>
+      </c>
+      <c r="C75" t="s">
+        <v>224</v>
+      </c>
+      <c r="D75" t="s">
+        <v>224</v>
+      </c>
+      <c r="E75" t="s">
+        <v>224</v>
+      </c>
+      <c r="F75" t="s">
+        <v>224</v>
+      </c>
+      <c r="H75" t="s">
         <v>107</v>
       </c>
-      <c r="C75" t="s">
-        <v>11</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="I75" t="s">
+        <v>11</v>
+      </c>
+      <c r="J75" t="s">
         <v>93</v>
       </c>
-      <c r="E75" t="s">
+      <c r="K75" t="s">
         <v>94</v>
       </c>
-      <c r="F75" t="s">
+      <c r="L75" t="s">
         <v>95</v>
       </c>
-      <c r="G75" t="s">
+      <c r="M75" t="s">
         <v>34</v>
       </c>
-      <c r="H75" s="2">
+      <c r="N75" s="2">
         <v>46255</v>
       </c>
-      <c r="I75" s="2">
+      <c r="O75" s="2">
         <v>46255</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>110</v>
       </c>
       <c r="B76" t="s">
+        <v>224</v>
+      </c>
+      <c r="C76" t="s">
+        <v>224</v>
+      </c>
+      <c r="D76" t="s">
+        <v>224</v>
+      </c>
+      <c r="E76" t="s">
+        <v>224</v>
+      </c>
+      <c r="F76" t="s">
+        <v>224</v>
+      </c>
+      <c r="H76" t="s">
         <v>107</v>
       </c>
-      <c r="C76" t="s">
-        <v>11</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="I76" t="s">
+        <v>11</v>
+      </c>
+      <c r="J76" t="s">
         <v>93</v>
       </c>
-      <c r="E76" t="s">
+      <c r="K76" t="s">
         <v>94</v>
       </c>
-      <c r="F76" t="s">
+      <c r="L76" t="s">
         <v>95</v>
       </c>
-      <c r="G76" t="s">
+      <c r="M76" t="s">
         <v>34</v>
       </c>
-      <c r="H76" s="2">
+      <c r="N76" s="2">
         <v>46261</v>
       </c>
-      <c r="I76" s="2">
+      <c r="O76" s="2">
         <v>46261</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>111</v>
       </c>
       <c r="B77" t="s">
+        <v>224</v>
+      </c>
+      <c r="C77" t="s">
+        <v>224</v>
+      </c>
+      <c r="D77" t="s">
+        <v>224</v>
+      </c>
+      <c r="E77" t="s">
+        <v>224</v>
+      </c>
+      <c r="F77" t="s">
+        <v>224</v>
+      </c>
+      <c r="H77" t="s">
         <v>107</v>
       </c>
-      <c r="C77" t="s">
-        <v>11</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="I77" t="s">
+        <v>11</v>
+      </c>
+      <c r="J77" t="s">
         <v>93</v>
       </c>
-      <c r="E77" t="s">
+      <c r="K77" t="s">
         <v>94</v>
       </c>
-      <c r="F77" t="s">
+      <c r="L77" t="s">
         <v>95</v>
       </c>
-      <c r="G77" t="s">
+      <c r="M77" t="s">
         <v>34</v>
       </c>
-      <c r="H77" s="2">
+      <c r="N77" s="2">
         <v>46261</v>
       </c>
-      <c r="I77" s="2">
+      <c r="O77" s="2">
         <v>46261</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>112</v>
       </c>
       <c r="B78" t="s">
+        <v>224</v>
+      </c>
+      <c r="C78" t="s">
+        <v>224</v>
+      </c>
+      <c r="D78" t="s">
+        <v>224</v>
+      </c>
+      <c r="E78" t="s">
+        <v>224</v>
+      </c>
+      <c r="F78" t="s">
+        <v>224</v>
+      </c>
+      <c r="H78" t="s">
         <v>66</v>
       </c>
-      <c r="C78" t="s">
-        <v>11</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="I78" t="s">
+        <v>11</v>
+      </c>
+      <c r="J78" t="s">
         <v>93</v>
       </c>
-      <c r="E78" t="s">
+      <c r="K78" t="s">
         <v>94</v>
       </c>
-      <c r="F78" t="s">
+      <c r="L78" t="s">
         <v>95</v>
       </c>
-      <c r="G78" t="s">
+      <c r="M78" t="s">
         <v>34</v>
       </c>
-      <c r="H78" s="2">
+      <c r="N78" s="2">
         <v>46254</v>
       </c>
-      <c r="I78" s="2">
+      <c r="O78" s="2">
         <v>46254</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>113</v>
       </c>
       <c r="B79" t="s">
+        <v>224</v>
+      </c>
+      <c r="C79" t="s">
+        <v>224</v>
+      </c>
+      <c r="D79" t="s">
+        <v>224</v>
+      </c>
+      <c r="E79" t="s">
+        <v>224</v>
+      </c>
+      <c r="F79" t="s">
+        <v>224</v>
+      </c>
+      <c r="H79" t="s">
         <v>66</v>
       </c>
-      <c r="C79" t="s">
-        <v>11</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="I79" t="s">
+        <v>11</v>
+      </c>
+      <c r="J79" t="s">
         <v>93</v>
       </c>
-      <c r="E79" t="s">
+      <c r="K79" t="s">
         <v>94</v>
       </c>
-      <c r="F79" t="s">
+      <c r="L79" t="s">
         <v>95</v>
       </c>
-      <c r="G79" t="s">
+      <c r="M79" t="s">
         <v>34</v>
       </c>
-      <c r="H79" s="2">
+      <c r="N79" s="2">
         <v>46261</v>
       </c>
-      <c r="I79" s="2">
+      <c r="O79" s="2">
         <v>46261</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>114</v>
       </c>
       <c r="B80" t="s">
+        <v>224</v>
+      </c>
+      <c r="C80" t="s">
+        <v>224</v>
+      </c>
+      <c r="D80" t="s">
+        <v>224</v>
+      </c>
+      <c r="E80" t="s">
+        <v>224</v>
+      </c>
+      <c r="F80" t="s">
+        <v>224</v>
+      </c>
+      <c r="H80" t="s">
         <v>66</v>
       </c>
-      <c r="C80" t="s">
-        <v>11</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="I80" t="s">
+        <v>11</v>
+      </c>
+      <c r="J80" t="s">
         <v>93</v>
       </c>
-      <c r="E80" t="s">
+      <c r="K80" t="s">
         <v>94</v>
       </c>
-      <c r="F80" t="s">
+      <c r="L80" t="s">
         <v>95</v>
       </c>
-      <c r="G80" t="s">
+      <c r="M80" t="s">
         <v>34</v>
       </c>
-      <c r="H80" s="2">
+      <c r="N80" s="2">
         <v>46269</v>
       </c>
-      <c r="I80" s="2">
+      <c r="O80" s="2">
         <v>46269</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>115</v>
       </c>
       <c r="B81" t="s">
+        <v>224</v>
+      </c>
+      <c r="C81" t="s">
+        <v>224</v>
+      </c>
+      <c r="D81" t="s">
+        <v>224</v>
+      </c>
+      <c r="E81" t="s">
+        <v>224</v>
+      </c>
+      <c r="F81" t="s">
+        <v>224</v>
+      </c>
+      <c r="H81" t="s">
         <v>66</v>
       </c>
-      <c r="C81" t="s">
-        <v>11</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="I81" t="s">
+        <v>11</v>
+      </c>
+      <c r="J81" t="s">
         <v>93</v>
       </c>
-      <c r="E81" t="s">
+      <c r="K81" t="s">
         <v>94</v>
       </c>
-      <c r="F81" t="s">
+      <c r="L81" t="s">
         <v>95</v>
       </c>
-      <c r="G81" t="s">
+      <c r="M81" t="s">
         <v>34</v>
       </c>
-      <c r="H81" s="2">
+      <c r="N81" s="2">
         <v>46261</v>
       </c>
-      <c r="I81" s="2">
+      <c r="O81" s="2">
         <v>46261</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>116</v>
       </c>
       <c r="B82" t="s">
+        <v>224</v>
+      </c>
+      <c r="C82" t="s">
+        <v>224</v>
+      </c>
+      <c r="D82" t="s">
+        <v>224</v>
+      </c>
+      <c r="E82" t="s">
+        <v>224</v>
+      </c>
+      <c r="F82" t="s">
+        <v>224</v>
+      </c>
+      <c r="H82" t="s">
         <v>66</v>
       </c>
-      <c r="C82" t="s">
-        <v>11</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="I82" t="s">
+        <v>11</v>
+      </c>
+      <c r="J82" t="s">
         <v>93</v>
       </c>
-      <c r="E82" t="s">
+      <c r="K82" t="s">
         <v>94</v>
       </c>
-      <c r="F82" t="s">
+      <c r="L82" t="s">
         <v>95</v>
       </c>
-      <c r="G82" t="s">
+      <c r="M82" t="s">
         <v>34</v>
       </c>
-      <c r="H82" s="2">
+      <c r="N82" s="2">
         <v>46262</v>
       </c>
-      <c r="I82" s="2">
+      <c r="O82" s="2">
         <v>46262</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>117</v>
       </c>
       <c r="B83" t="s">
+        <v>224</v>
+      </c>
+      <c r="C83" t="s">
+        <v>224</v>
+      </c>
+      <c r="D83" t="s">
+        <v>224</v>
+      </c>
+      <c r="E83" t="s">
+        <v>224</v>
+      </c>
+      <c r="F83" t="s">
+        <v>224</v>
+      </c>
+      <c r="H83" t="s">
         <v>24</v>
       </c>
-      <c r="C83" t="s">
-        <v>11</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="I83" t="s">
+        <v>11</v>
+      </c>
+      <c r="J83" t="s">
         <v>93</v>
       </c>
-      <c r="E83" t="s">
+      <c r="K83" t="s">
         <v>94</v>
       </c>
-      <c r="F83" t="s">
+      <c r="L83" t="s">
         <v>95</v>
       </c>
-      <c r="G83" t="s">
+      <c r="M83" t="s">
         <v>34</v>
       </c>
-      <c r="H83" s="2">
+      <c r="N83" s="2">
         <v>46185</v>
       </c>
-      <c r="I83" s="2">
+      <c r="O83" s="2">
         <v>46185</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>118</v>
       </c>
       <c r="B84" t="s">
+        <v>224</v>
+      </c>
+      <c r="C84" t="s">
+        <v>224</v>
+      </c>
+      <c r="D84" t="s">
+        <v>224</v>
+      </c>
+      <c r="E84" t="s">
+        <v>224</v>
+      </c>
+      <c r="F84" t="s">
+        <v>224</v>
+      </c>
+      <c r="H84" t="s">
         <v>24</v>
       </c>
-      <c r="C84" t="s">
-        <v>11</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="I84" t="s">
+        <v>11</v>
+      </c>
+      <c r="J84" t="s">
         <v>93</v>
       </c>
-      <c r="E84" t="s">
+      <c r="K84" t="s">
         <v>94</v>
       </c>
-      <c r="F84" t="s">
+      <c r="L84" t="s">
         <v>95</v>
       </c>
-      <c r="G84" t="s">
+      <c r="M84" t="s">
         <v>34</v>
       </c>
-      <c r="H84" s="2">
+      <c r="N84" s="2">
         <v>46182</v>
       </c>
-      <c r="I84" s="2">
+      <c r="O84" s="2">
         <v>46181</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>119</v>
       </c>
       <c r="B85" t="s">
+        <v>224</v>
+      </c>
+      <c r="C85" t="s">
+        <v>224</v>
+      </c>
+      <c r="D85" t="s">
+        <v>224</v>
+      </c>
+      <c r="E85" t="s">
+        <v>224</v>
+      </c>
+      <c r="F85" t="s">
+        <v>224</v>
+      </c>
+      <c r="H85" t="s">
         <v>24</v>
       </c>
-      <c r="C85" t="s">
-        <v>11</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="I85" t="s">
+        <v>11</v>
+      </c>
+      <c r="J85" t="s">
         <v>93</v>
       </c>
-      <c r="E85" t="s">
+      <c r="K85" t="s">
         <v>94</v>
       </c>
-      <c r="F85" t="s">
+      <c r="L85" t="s">
         <v>97</v>
       </c>
-      <c r="G85" t="s">
+      <c r="M85" t="s">
         <v>34</v>
       </c>
-      <c r="H85" s="2">
+      <c r="N85" s="2">
         <v>46185</v>
       </c>
-      <c r="I85" s="2">
+      <c r="O85" s="2">
         <v>46183</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>120</v>
       </c>
       <c r="B86" t="s">
+        <v>224</v>
+      </c>
+      <c r="C86" t="s">
+        <v>224</v>
+      </c>
+      <c r="D86" t="s">
+        <v>224</v>
+      </c>
+      <c r="E86" t="s">
+        <v>224</v>
+      </c>
+      <c r="F86" t="s">
+        <v>224</v>
+      </c>
+      <c r="H86" t="s">
         <v>24</v>
       </c>
-      <c r="C86" t="s">
-        <v>11</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="I86" t="s">
+        <v>11</v>
+      </c>
+      <c r="J86" t="s">
         <v>93</v>
       </c>
-      <c r="E86" t="s">
+      <c r="K86" t="s">
         <v>94</v>
       </c>
-      <c r="F86" t="s">
+      <c r="L86" t="s">
         <v>95</v>
       </c>
-      <c r="G86" t="s">
+      <c r="M86" t="s">
         <v>34</v>
       </c>
-      <c r="H86" s="2">
+      <c r="N86" s="2">
         <v>46148</v>
       </c>
-      <c r="I86" s="2">
+      <c r="O86" s="2">
         <v>46176</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>121</v>
       </c>
       <c r="B87" t="s">
+        <v>224</v>
+      </c>
+      <c r="C87" t="s">
+        <v>224</v>
+      </c>
+      <c r="D87" t="s">
+        <v>224</v>
+      </c>
+      <c r="E87" t="s">
+        <v>224</v>
+      </c>
+      <c r="F87" t="s">
+        <v>224</v>
+      </c>
+      <c r="H87" t="s">
         <v>66</v>
       </c>
-      <c r="C87" t="s">
-        <v>11</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="I87" t="s">
+        <v>11</v>
+      </c>
+      <c r="J87" t="s">
         <v>93</v>
       </c>
-      <c r="E87" t="s">
+      <c r="K87" t="s">
         <v>94</v>
       </c>
-      <c r="F87" t="s">
+      <c r="L87" t="s">
         <v>95</v>
       </c>
-      <c r="G87" t="s">
+      <c r="M87" t="s">
         <v>44</v>
       </c>
-      <c r="H87" s="2">
+      <c r="N87" s="2">
         <v>46261</v>
       </c>
-      <c r="I87" s="2">
+      <c r="O87" s="2">
         <v>46261</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>122</v>
       </c>
       <c r="B88" t="s">
+        <v>224</v>
+      </c>
+      <c r="C88" t="s">
+        <v>224</v>
+      </c>
+      <c r="D88" t="s">
+        <v>224</v>
+      </c>
+      <c r="E88" t="s">
+        <v>224</v>
+      </c>
+      <c r="F88" t="s">
+        <v>224</v>
+      </c>
+      <c r="H88" t="s">
         <v>24</v>
       </c>
-      <c r="C88" t="s">
-        <v>11</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="I88" t="s">
+        <v>11</v>
+      </c>
+      <c r="J88" t="s">
         <v>93</v>
       </c>
-      <c r="E88" t="s">
+      <c r="K88" t="s">
         <v>94</v>
       </c>
-      <c r="F88" t="s">
+      <c r="L88" t="s">
         <v>95</v>
       </c>
-      <c r="G88" t="s">
+      <c r="M88" t="s">
         <v>44</v>
       </c>
-      <c r="H88" s="2">
+      <c r="N88" s="2">
         <v>46254</v>
       </c>
-      <c r="I88" s="2">
+      <c r="O88" s="2">
         <v>46254</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>123</v>
       </c>
       <c r="B89" t="s">
+        <v>224</v>
+      </c>
+      <c r="C89" t="s">
+        <v>224</v>
+      </c>
+      <c r="D89" t="s">
+        <v>224</v>
+      </c>
+      <c r="E89" t="s">
+        <v>224</v>
+      </c>
+      <c r="F89" t="s">
+        <v>224</v>
+      </c>
+      <c r="H89" t="s">
         <v>124</v>
       </c>
-      <c r="C89" t="s">
+      <c r="I89" t="s">
         <v>37</v>
       </c>
-      <c r="D89" t="s">
+      <c r="J89" t="s">
         <v>25</v>
       </c>
-      <c r="E89" t="s">
+      <c r="K89" t="s">
         <v>125</v>
       </c>
-      <c r="F89" t="s">
+      <c r="L89" t="s">
         <v>126</v>
       </c>
-      <c r="G89" t="s">
+      <c r="M89" t="s">
         <v>28</v>
       </c>
-      <c r="H89" s="2">
+      <c r="N89" s="2">
         <v>46199</v>
       </c>
-      <c r="I89" s="2">
+      <c r="O89" s="2">
         <v>46199</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>127</v>
       </c>
       <c r="B90" t="s">
+        <v>224</v>
+      </c>
+      <c r="C90" t="s">
+        <v>224</v>
+      </c>
+      <c r="D90" t="s">
+        <v>224</v>
+      </c>
+      <c r="E90" t="s">
+        <v>224</v>
+      </c>
+      <c r="F90" t="s">
+        <v>224</v>
+      </c>
+      <c r="H90" t="s">
         <v>124</v>
       </c>
-      <c r="C90" t="s">
+      <c r="I90" t="s">
         <v>37</v>
       </c>
-      <c r="D90" t="s">
+      <c r="J90" t="s">
         <v>25</v>
       </c>
-      <c r="E90" t="s">
+      <c r="K90" t="s">
         <v>125</v>
       </c>
-      <c r="F90" t="s">
+      <c r="L90" t="s">
         <v>126</v>
       </c>
-      <c r="G90" t="s">
+      <c r="M90" t="s">
         <v>28</v>
       </c>
-      <c r="H90" s="2">
+      <c r="N90" s="2">
         <v>46199</v>
       </c>
-      <c r="I90" s="2">
+      <c r="O90" s="2">
         <v>46199</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>128</v>
       </c>
       <c r="B91" t="s">
+        <v>224</v>
+      </c>
+      <c r="C91" t="s">
+        <v>224</v>
+      </c>
+      <c r="D91" t="s">
+        <v>224</v>
+      </c>
+      <c r="E91" t="s">
+        <v>224</v>
+      </c>
+      <c r="F91" t="s">
+        <v>224</v>
+      </c>
+      <c r="H91" t="s">
         <v>124</v>
       </c>
-      <c r="C91" t="s">
+      <c r="I91" t="s">
         <v>37</v>
       </c>
-      <c r="D91" t="s">
+      <c r="J91" t="s">
         <v>25</v>
       </c>
-      <c r="E91" t="s">
+      <c r="K91" t="s">
         <v>125</v>
       </c>
-      <c r="F91" t="s">
+      <c r="L91" t="s">
         <v>126</v>
       </c>
-      <c r="G91" t="s">
+      <c r="M91" t="s">
         <v>28</v>
       </c>
-      <c r="H91" s="2">
+      <c r="N91" s="2">
         <v>46184</v>
       </c>
-      <c r="I91" s="2">
+      <c r="O91" s="2">
         <v>46184</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>129</v>
       </c>
       <c r="B92" t="s">
+        <v>224</v>
+      </c>
+      <c r="C92" t="s">
+        <v>224</v>
+      </c>
+      <c r="D92" t="s">
+        <v>224</v>
+      </c>
+      <c r="E92" t="s">
+        <v>224</v>
+      </c>
+      <c r="F92" t="s">
+        <v>224</v>
+      </c>
+      <c r="H92" t="s">
         <v>124</v>
       </c>
-      <c r="C92" t="s">
+      <c r="I92" t="s">
         <v>37</v>
       </c>
-      <c r="D92" t="s">
+      <c r="J92" t="s">
         <v>25</v>
       </c>
-      <c r="E92" t="s">
+      <c r="K92" t="s">
         <v>125</v>
       </c>
-      <c r="F92" t="s">
+      <c r="L92" t="s">
         <v>126</v>
       </c>
-      <c r="G92" t="s">
+      <c r="M92" t="s">
         <v>28</v>
       </c>
-      <c r="H92" s="2">
+      <c r="N92" s="2">
         <v>46176</v>
       </c>
-      <c r="I92" s="2">
+      <c r="O92" s="2">
         <v>46176</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>130</v>
       </c>
       <c r="B93" t="s">
+        <v>224</v>
+      </c>
+      <c r="C93" t="s">
+        <v>224</v>
+      </c>
+      <c r="D93" t="s">
+        <v>224</v>
+      </c>
+      <c r="E93" t="s">
+        <v>224</v>
+      </c>
+      <c r="F93" t="s">
+        <v>224</v>
+      </c>
+      <c r="H93" t="s">
         <v>10</v>
       </c>
-      <c r="C93" t="s">
-        <v>11</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="I93" t="s">
+        <v>11</v>
+      </c>
+      <c r="J93" t="s">
         <v>25</v>
       </c>
-      <c r="E93" t="s">
+      <c r="K93" t="s">
         <v>125</v>
       </c>
-      <c r="F93" t="s">
+      <c r="L93" t="s">
         <v>126</v>
       </c>
-      <c r="G93" t="s">
+      <c r="M93" t="s">
         <v>28</v>
       </c>
-      <c r="H93" s="2">
+      <c r="N93" s="2">
         <v>46218</v>
       </c>
-      <c r="I93" s="2">
+      <c r="O93" s="2">
         <v>46218</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>131</v>
       </c>
       <c r="B94" t="s">
+        <v>224</v>
+      </c>
+      <c r="C94" t="s">
+        <v>224</v>
+      </c>
+      <c r="D94" t="s">
+        <v>224</v>
+      </c>
+      <c r="E94" t="s">
+        <v>224</v>
+      </c>
+      <c r="F94" t="s">
+        <v>224</v>
+      </c>
+      <c r="G94" t="s">
+        <v>224</v>
+      </c>
+      <c r="H94" t="s">
         <v>10</v>
       </c>
-      <c r="C94" t="s">
-        <v>11</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="I94" t="s">
+        <v>11</v>
+      </c>
+      <c r="J94" t="s">
         <v>25</v>
       </c>
-      <c r="E94" t="s">
+      <c r="K94" t="s">
         <v>125</v>
       </c>
-      <c r="F94" t="s">
+      <c r="L94" t="s">
         <v>126</v>
       </c>
-      <c r="G94" t="s">
+      <c r="M94" t="s">
         <v>28</v>
       </c>
-      <c r="H94" s="2">
+      <c r="N94" s="2">
         <v>46218</v>
       </c>
-      <c r="I94" s="2">
+      <c r="O94" s="2">
         <v>46218</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>132</v>
       </c>
       <c r="B95" t="s">
+        <v>224</v>
+      </c>
+      <c r="C95" t="s">
+        <v>224</v>
+      </c>
+      <c r="D95" t="s">
+        <v>224</v>
+      </c>
+      <c r="E95" t="s">
+        <v>224</v>
+      </c>
+      <c r="F95" t="s">
+        <v>224</v>
+      </c>
+      <c r="G95" t="s">
+        <v>224</v>
+      </c>
+      <c r="H95" t="s">
         <v>10</v>
       </c>
-      <c r="C95" t="s">
-        <v>11</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="I95" t="s">
+        <v>11</v>
+      </c>
+      <c r="J95" t="s">
         <v>25</v>
       </c>
-      <c r="E95" t="s">
+      <c r="K95" t="s">
         <v>125</v>
       </c>
-      <c r="F95" t="s">
+      <c r="L95" t="s">
         <v>126</v>
       </c>
-      <c r="G95" t="s">
+      <c r="M95" t="s">
         <v>28</v>
       </c>
-      <c r="H95" s="2">
+      <c r="N95" s="2">
         <v>46218</v>
       </c>
-      <c r="I95" s="2">
+      <c r="O95" s="2">
         <v>46218</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>133</v>
       </c>
       <c r="B96" t="s">
+        <v>224</v>
+      </c>
+      <c r="C96" t="s">
+        <v>224</v>
+      </c>
+      <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
+        <v>224</v>
+      </c>
+      <c r="F96" t="s">
+        <v>224</v>
+      </c>
+      <c r="G96" t="s">
+        <v>224</v>
+      </c>
+      <c r="H96" t="s">
         <v>10</v>
       </c>
-      <c r="C96" t="s">
-        <v>11</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="I96" t="s">
+        <v>11</v>
+      </c>
+      <c r="J96" t="s">
         <v>25</v>
       </c>
-      <c r="E96" t="s">
+      <c r="K96" t="s">
         <v>125</v>
       </c>
-      <c r="F96" t="s">
+      <c r="L96" t="s">
         <v>126</v>
       </c>
-      <c r="G96" t="s">
+      <c r="M96" t="s">
         <v>28</v>
       </c>
-      <c r="H96" s="2">
+      <c r="N96" s="2">
         <v>46218</v>
       </c>
-      <c r="I96" s="2">
+      <c r="O96" s="2">
         <v>46218</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>134</v>
       </c>
       <c r="B97" t="s">
+        <v>224</v>
+      </c>
+      <c r="C97" t="s">
+        <v>224</v>
+      </c>
+      <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
+        <v>224</v>
+      </c>
+      <c r="F97" t="s">
+        <v>224</v>
+      </c>
+      <c r="G97" t="s">
+        <v>224</v>
+      </c>
+      <c r="H97" t="s">
         <v>10</v>
       </c>
-      <c r="C97" t="s">
-        <v>11</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="I97" t="s">
+        <v>11</v>
+      </c>
+      <c r="J97" t="s">
         <v>25</v>
       </c>
-      <c r="E97" t="s">
+      <c r="K97" t="s">
         <v>125</v>
       </c>
-      <c r="F97" t="s">
+      <c r="L97" t="s">
         <v>126</v>
       </c>
-      <c r="G97" t="s">
+      <c r="M97" t="s">
         <v>28</v>
       </c>
-      <c r="H97" s="2">
+      <c r="N97" s="2">
         <v>46218</v>
       </c>
-      <c r="I97" s="2">
+      <c r="O97" s="2">
         <v>46218</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>135</v>
       </c>
       <c r="B98" t="s">
+        <v>224</v>
+      </c>
+      <c r="C98" t="s">
+        <v>224</v>
+      </c>
+      <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
+        <v>224</v>
+      </c>
+      <c r="F98" t="s">
+        <v>224</v>
+      </c>
+      <c r="G98" t="s">
+        <v>224</v>
+      </c>
+      <c r="H98" t="s">
         <v>10</v>
       </c>
-      <c r="C98" t="s">
-        <v>11</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="I98" t="s">
+        <v>11</v>
+      </c>
+      <c r="J98" t="s">
         <v>25</v>
       </c>
-      <c r="E98" t="s">
+      <c r="K98" t="s">
         <v>125</v>
       </c>
-      <c r="F98" t="s">
+      <c r="L98" t="s">
         <v>126</v>
       </c>
-      <c r="G98" t="s">
+      <c r="M98" t="s">
         <v>28</v>
       </c>
-      <c r="H98" s="2">
+      <c r="N98" s="2">
         <v>46218</v>
       </c>
-      <c r="I98" s="2">
+      <c r="O98" s="2">
         <v>46218</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>136</v>
       </c>
       <c r="B99" t="s">
+        <v>224</v>
+      </c>
+      <c r="C99" t="s">
+        <v>224</v>
+      </c>
+      <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
+        <v>224</v>
+      </c>
+      <c r="F99" t="s">
+        <v>224</v>
+      </c>
+      <c r="G99" t="s">
+        <v>224</v>
+      </c>
+      <c r="H99" t="s">
         <v>124</v>
       </c>
-      <c r="C99" t="s">
+      <c r="I99" t="s">
         <v>37</v>
       </c>
-      <c r="D99" t="s">
+      <c r="J99" t="s">
         <v>25</v>
       </c>
-      <c r="E99" t="s">
+      <c r="K99" t="s">
         <v>125</v>
       </c>
-      <c r="F99" t="s">
+      <c r="L99" t="s">
         <v>126</v>
       </c>
-      <c r="G99" t="s">
+      <c r="M99" t="s">
         <v>137</v>
       </c>
-      <c r="H99" s="2">
+      <c r="N99" s="2">
         <v>46220</v>
       </c>
-      <c r="I99" s="2">
+      <c r="O99" s="2">
         <v>46227</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>138</v>
       </c>
       <c r="B100" t="s">
+        <v>224</v>
+      </c>
+      <c r="C100" t="s">
+        <v>224</v>
+      </c>
+      <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
+        <v>224</v>
+      </c>
+      <c r="F100" t="s">
+        <v>224</v>
+      </c>
+      <c r="G100" t="s">
+        <v>224</v>
+      </c>
+      <c r="H100" t="s">
         <v>124</v>
       </c>
-      <c r="C100" t="s">
+      <c r="I100" t="s">
         <v>37</v>
       </c>
-      <c r="D100" t="s">
+      <c r="J100" t="s">
         <v>25</v>
       </c>
-      <c r="E100" t="s">
+      <c r="K100" t="s">
         <v>125</v>
       </c>
-      <c r="F100" t="s">
+      <c r="L100" t="s">
         <v>126</v>
       </c>
-      <c r="G100" t="s">
+      <c r="M100" t="s">
         <v>137</v>
       </c>
-      <c r="H100" s="2">
+      <c r="N100" s="2">
         <v>46220</v>
       </c>
-      <c r="I100" s="2">
+      <c r="O100" s="2">
         <v>46227</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>139</v>
       </c>
       <c r="B101" t="s">
+        <v>224</v>
+      </c>
+      <c r="C101" t="s">
+        <v>224</v>
+      </c>
+      <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
+        <v>224</v>
+      </c>
+      <c r="F101" t="s">
+        <v>224</v>
+      </c>
+      <c r="G101" t="s">
+        <v>224</v>
+      </c>
+      <c r="H101" t="s">
         <v>124</v>
       </c>
-      <c r="C101" t="s">
+      <c r="I101" t="s">
         <v>37</v>
       </c>
-      <c r="D101" t="s">
+      <c r="J101" t="s">
         <v>25</v>
       </c>
-      <c r="E101" t="s">
+      <c r="K101" t="s">
         <v>125</v>
       </c>
-      <c r="F101" t="s">
+      <c r="L101" t="s">
         <v>126</v>
       </c>
-      <c r="G101" t="s">
+      <c r="M101" t="s">
         <v>137</v>
       </c>
-      <c r="H101" s="2">
+      <c r="N101" s="2">
         <v>46220</v>
       </c>
-      <c r="I101" s="2">
+      <c r="O101" s="2">
         <v>46230</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>140</v>
       </c>
       <c r="B102" t="s">
+        <v>224</v>
+      </c>
+      <c r="C102" t="s">
+        <v>224</v>
+      </c>
+      <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
+        <v>224</v>
+      </c>
+      <c r="F102" t="s">
+        <v>224</v>
+      </c>
+      <c r="G102" t="s">
+        <v>224</v>
+      </c>
+      <c r="H102" t="s">
         <v>124</v>
       </c>
-      <c r="C102" t="s">
+      <c r="I102" t="s">
         <v>37</v>
       </c>
-      <c r="D102" t="s">
+      <c r="J102" t="s">
         <v>25</v>
       </c>
-      <c r="E102" t="s">
+      <c r="K102" t="s">
         <v>125</v>
       </c>
-      <c r="F102" t="s">
+      <c r="L102" t="s">
         <v>126</v>
       </c>
-      <c r="G102" t="s">
+      <c r="M102" t="s">
         <v>141</v>
       </c>
-      <c r="H102" s="2">
+      <c r="N102" s="2">
         <v>46281</v>
       </c>
-      <c r="I102" s="2"/>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O102" s="2"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>142</v>
       </c>
       <c r="B103" t="s">
+        <v>224</v>
+      </c>
+      <c r="C103" t="s">
+        <v>224</v>
+      </c>
+      <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
+        <v>224</v>
+      </c>
+      <c r="F103" t="s">
+        <v>224</v>
+      </c>
+      <c r="G103" t="s">
+        <v>224</v>
+      </c>
+      <c r="H103" t="s">
         <v>124</v>
       </c>
-      <c r="C103" t="s">
+      <c r="I103" t="s">
         <v>37</v>
       </c>
-      <c r="D103" t="s">
+      <c r="J103" t="s">
         <v>25</v>
       </c>
-      <c r="E103" t="s">
+      <c r="K103" t="s">
         <v>125</v>
       </c>
-      <c r="F103" t="s">
+      <c r="L103" t="s">
         <v>126</v>
       </c>
-      <c r="G103" t="s">
+      <c r="M103" t="s">
         <v>141</v>
       </c>
-      <c r="H103" s="2">
+      <c r="N103" s="2">
         <v>46276</v>
       </c>
-      <c r="I103" s="2">
+      <c r="O103" s="2">
         <v>46276</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>143</v>
       </c>
       <c r="B104" t="s">
+        <v>224</v>
+      </c>
+      <c r="C104" t="s">
+        <v>224</v>
+      </c>
+      <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
+        <v>224</v>
+      </c>
+      <c r="F104" t="s">
+        <v>224</v>
+      </c>
+      <c r="G104" t="s">
+        <v>224</v>
+      </c>
+      <c r="H104" t="s">
         <v>124</v>
       </c>
-      <c r="C104" t="s">
+      <c r="I104" t="s">
         <v>37</v>
       </c>
-      <c r="D104" t="s">
+      <c r="J104" t="s">
         <v>25</v>
       </c>
-      <c r="E104" t="s">
+      <c r="K104" t="s">
         <v>125</v>
       </c>
-      <c r="F104" t="s">
+      <c r="L104" t="s">
         <v>126</v>
       </c>
-      <c r="G104" t="s">
+      <c r="M104" t="s">
         <v>141</v>
       </c>
-      <c r="H104" s="2">
+      <c r="N104" s="2">
         <v>46276</v>
       </c>
-      <c r="I104" s="2">
+      <c r="O104" s="2">
         <v>46276</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>144</v>
       </c>
       <c r="B105" t="s">
+        <v>224</v>
+      </c>
+      <c r="C105" t="s">
+        <v>224</v>
+      </c>
+      <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
+        <v>224</v>
+      </c>
+      <c r="F105" t="s">
+        <v>224</v>
+      </c>
+      <c r="G105" t="s">
+        <v>224</v>
+      </c>
+      <c r="H105" t="s">
         <v>124</v>
       </c>
-      <c r="C105" t="s">
+      <c r="I105" t="s">
         <v>37</v>
       </c>
-      <c r="D105" t="s">
+      <c r="J105" t="s">
         <v>25</v>
       </c>
-      <c r="E105" t="s">
+      <c r="K105" t="s">
         <v>125</v>
       </c>
-      <c r="F105" t="s">
+      <c r="L105" t="s">
         <v>126</v>
       </c>
-      <c r="G105" t="s">
+      <c r="M105" t="s">
         <v>141</v>
       </c>
-      <c r="H105" s="2">
+      <c r="N105" s="2">
         <v>46276</v>
       </c>
-      <c r="I105" s="2">
+      <c r="O105" s="2">
         <v>46276</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>145</v>
       </c>
       <c r="B106" t="s">
+        <v>224</v>
+      </c>
+      <c r="C106" t="s">
+        <v>224</v>
+      </c>
+      <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
+        <v>224</v>
+      </c>
+      <c r="F106" t="s">
+        <v>224</v>
+      </c>
+      <c r="G106" t="s">
+        <v>224</v>
+      </c>
+      <c r="H106" t="s">
         <v>124</v>
       </c>
-      <c r="C106" t="s">
+      <c r="I106" t="s">
         <v>37</v>
       </c>
-      <c r="D106" t="s">
+      <c r="J106" t="s">
         <v>25</v>
       </c>
-      <c r="E106" t="s">
+      <c r="K106" t="s">
         <v>125</v>
       </c>
-      <c r="F106" t="s">
+      <c r="L106" t="s">
         <v>126</v>
       </c>
-      <c r="G106" t="s">
+      <c r="M106" t="s">
         <v>141</v>
       </c>
-      <c r="H106" s="2">
+      <c r="N106" s="2">
         <v>46276</v>
       </c>
-      <c r="I106" s="2">
+      <c r="O106" s="2">
         <v>46276</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>146</v>
       </c>
       <c r="B107" t="s">
+        <v>224</v>
+      </c>
+      <c r="C107" t="s">
+        <v>224</v>
+      </c>
+      <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
+        <v>224</v>
+      </c>
+      <c r="F107" t="s">
+        <v>224</v>
+      </c>
+      <c r="G107" t="s">
+        <v>224</v>
+      </c>
+      <c r="H107" t="s">
         <v>124</v>
       </c>
-      <c r="C107" t="s">
+      <c r="I107" t="s">
         <v>37</v>
       </c>
-      <c r="D107" t="s">
+      <c r="J107" t="s">
         <v>25</v>
       </c>
-      <c r="E107" t="s">
+      <c r="K107" t="s">
         <v>125</v>
       </c>
-      <c r="F107" t="s">
+      <c r="L107" t="s">
         <v>126</v>
       </c>
-      <c r="G107" t="s">
+      <c r="M107" t="s">
         <v>141</v>
       </c>
-      <c r="H107" s="2">
+      <c r="N107" s="2">
         <v>46276</v>
       </c>
-      <c r="I107" s="2">
+      <c r="O107" s="2">
         <v>46276</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>147</v>
       </c>
       <c r="B108" t="s">
+        <v>224</v>
+      </c>
+      <c r="C108" t="s">
+        <v>224</v>
+      </c>
+      <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
+        <v>224</v>
+      </c>
+      <c r="F108" t="s">
+        <v>224</v>
+      </c>
+      <c r="G108" t="s">
+        <v>224</v>
+      </c>
+      <c r="H108" t="s">
         <v>124</v>
       </c>
-      <c r="C108" t="s">
+      <c r="I108" t="s">
         <v>37</v>
       </c>
-      <c r="D108" t="s">
+      <c r="J108" t="s">
         <v>25</v>
       </c>
-      <c r="E108" t="s">
+      <c r="K108" t="s">
         <v>125</v>
       </c>
-      <c r="F108" t="s">
+      <c r="L108" t="s">
         <v>126</v>
       </c>
-      <c r="G108" t="s">
+      <c r="M108" t="s">
         <v>141</v>
       </c>
-      <c r="H108" s="2">
+      <c r="N108" s="2">
         <v>46276</v>
       </c>
-      <c r="I108" s="2">
+      <c r="O108" s="2">
         <v>46276</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>148</v>
       </c>
       <c r="B109" t="s">
+        <v>224</v>
+      </c>
+      <c r="C109" t="s">
+        <v>224</v>
+      </c>
+      <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
+        <v>224</v>
+      </c>
+      <c r="F109" t="s">
+        <v>224</v>
+      </c>
+      <c r="G109" t="s">
+        <v>224</v>
+      </c>
+      <c r="H109" t="s">
         <v>124</v>
       </c>
-      <c r="C109" t="s">
+      <c r="I109" t="s">
         <v>37</v>
       </c>
-      <c r="D109" t="s">
+      <c r="J109" t="s">
         <v>25</v>
       </c>
-      <c r="E109" t="s">
+      <c r="K109" t="s">
         <v>125</v>
       </c>
-      <c r="F109" t="s">
+      <c r="L109" t="s">
         <v>126</v>
       </c>
-      <c r="G109" t="s">
+      <c r="M109" t="s">
         <v>141</v>
       </c>
-      <c r="H109" s="2">
+      <c r="N109" s="2">
         <v>46276</v>
       </c>
-      <c r="I109" s="2">
+      <c r="O109" s="2">
         <v>46276</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>149</v>
       </c>
       <c r="B110" t="s">
+        <v>224</v>
+      </c>
+      <c r="C110" t="s">
+        <v>224</v>
+      </c>
+      <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
+        <v>224</v>
+      </c>
+      <c r="F110" t="s">
+        <v>224</v>
+      </c>
+      <c r="G110" t="s">
+        <v>224</v>
+      </c>
+      <c r="H110" t="s">
         <v>10</v>
       </c>
-      <c r="C110" t="s">
-        <v>11</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="I110" t="s">
+        <v>11</v>
+      </c>
+      <c r="J110" t="s">
         <v>25</v>
       </c>
-      <c r="E110" t="s">
+      <c r="K110" t="s">
         <v>125</v>
       </c>
-      <c r="F110" t="s">
+      <c r="L110" t="s">
         <v>126</v>
       </c>
-      <c r="G110" t="s">
+      <c r="M110" t="s">
         <v>141</v>
       </c>
-      <c r="H110" s="2">
+      <c r="N110" s="2">
         <v>46295</v>
       </c>
-      <c r="I110" s="2"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O110" s="2"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>150</v>
       </c>
       <c r="B111" t="s">
+        <v>224</v>
+      </c>
+      <c r="C111" t="s">
+        <v>224</v>
+      </c>
+      <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
+        <v>224</v>
+      </c>
+      <c r="F111" t="s">
+        <v>224</v>
+      </c>
+      <c r="G111" t="s">
+        <v>224</v>
+      </c>
+      <c r="H111" t="s">
         <v>31</v>
       </c>
-      <c r="C111" t="s">
-        <v>11</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="I111" t="s">
+        <v>11</v>
+      </c>
+      <c r="J111" t="s">
         <v>32</v>
       </c>
-      <c r="E111" t="s">
+      <c r="K111" t="s">
         <v>26</v>
       </c>
-      <c r="F111" t="s">
+      <c r="L111" t="s">
         <v>33</v>
       </c>
-      <c r="G111" t="s">
+      <c r="M111" t="s">
         <v>34</v>
       </c>
-      <c r="H111" s="2">
+      <c r="N111" s="2">
         <v>46207</v>
       </c>
-      <c r="I111" s="2">
+      <c r="O111" s="2">
         <v>46206</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>151</v>
       </c>
-      <c r="B112" t="s">
+      <c r="H112" t="s">
         <v>31</v>
       </c>
-      <c r="C112" t="s">
-        <v>11</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="I112" t="s">
+        <v>11</v>
+      </c>
+      <c r="J112" t="s">
         <v>25</v>
       </c>
-      <c r="E112" t="s">
+      <c r="K112" t="s">
         <v>26</v>
       </c>
-      <c r="G112" t="s">
+      <c r="M112" t="s">
         <v>141</v>
       </c>
-      <c r="H112" s="2"/>
-      <c r="I112" s="2"/>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>152</v>
       </c>
       <c r="B113" t="s">
+        <v>224</v>
+      </c>
+      <c r="C113" t="s">
+        <v>224</v>
+      </c>
+      <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
+        <v>224</v>
+      </c>
+      <c r="F113" t="s">
+        <v>224</v>
+      </c>
+      <c r="G113" t="s">
+        <v>224</v>
+      </c>
+      <c r="H113" t="s">
         <v>31</v>
       </c>
-      <c r="C113" t="s">
-        <v>11</v>
-      </c>
-      <c r="D113" t="s">
+      <c r="I113" t="s">
+        <v>11</v>
+      </c>
+      <c r="J113" t="s">
         <v>32</v>
       </c>
-      <c r="E113" t="s">
+      <c r="K113" t="s">
         <v>26</v>
       </c>
-      <c r="F113" t="s">
+      <c r="L113" t="s">
         <v>33</v>
       </c>
-      <c r="G113" t="s">
+      <c r="M113" t="s">
         <v>44</v>
       </c>
-      <c r="H113" s="2">
+      <c r="N113" s="2">
         <v>46207</v>
       </c>
-      <c r="I113" s="2">
+      <c r="O113" s="2">
         <v>46206</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>153</v>
       </c>
       <c r="B114" t="s">
+        <v>224</v>
+      </c>
+      <c r="C114" t="s">
+        <v>224</v>
+      </c>
+      <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
+        <v>224</v>
+      </c>
+      <c r="F114" t="s">
+        <v>224</v>
+      </c>
+      <c r="G114" t="s">
+        <v>224</v>
+      </c>
+      <c r="H114" t="s">
         <v>31</v>
       </c>
-      <c r="C114" t="s">
-        <v>11</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="I114" t="s">
+        <v>11</v>
+      </c>
+      <c r="J114" t="s">
         <v>32</v>
       </c>
-      <c r="E114" t="s">
+      <c r="K114" t="s">
         <v>26</v>
       </c>
-      <c r="F114" t="s">
+      <c r="L114" t="s">
         <v>33</v>
       </c>
-      <c r="G114" t="s">
+      <c r="M114" t="s">
         <v>44</v>
       </c>
-      <c r="H114" s="2">
+      <c r="N114" s="2">
         <v>46207</v>
       </c>
-      <c r="I114" s="2">
+      <c r="O114" s="2">
         <v>46206</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>154</v>
       </c>
       <c r="B115" t="s">
+        <v>224</v>
+      </c>
+      <c r="C115" t="s">
+        <v>224</v>
+      </c>
+      <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
+        <v>224</v>
+      </c>
+      <c r="F115" t="s">
+        <v>224</v>
+      </c>
+      <c r="G115" t="s">
+        <v>224</v>
+      </c>
+      <c r="H115" t="s">
         <v>24</v>
       </c>
-      <c r="C115" t="s">
-        <v>11</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="I115" t="s">
+        <v>11</v>
+      </c>
+      <c r="J115" t="s">
         <v>25</v>
       </c>
-      <c r="E115" t="s">
+      <c r="K115" t="s">
         <v>26</v>
       </c>
-      <c r="F115" t="s">
+      <c r="L115" t="s">
         <v>155</v>
       </c>
-      <c r="G115" t="s">
+      <c r="M115" t="s">
         <v>44</v>
       </c>
-      <c r="H115" s="2">
+      <c r="N115" s="2">
         <v>46207</v>
       </c>
-      <c r="I115" s="2">
+      <c r="O115" s="2">
         <v>46204</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>156</v>
       </c>
       <c r="B116" t="s">
+        <v>224</v>
+      </c>
+      <c r="C116" t="s">
+        <v>224</v>
+      </c>
+      <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
+        <v>224</v>
+      </c>
+      <c r="F116" t="s">
+        <v>224</v>
+      </c>
+      <c r="G116" t="s">
+        <v>224</v>
+      </c>
+      <c r="H116" t="s">
         <v>24</v>
       </c>
-      <c r="C116" t="s">
-        <v>11</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="I116" t="s">
+        <v>11</v>
+      </c>
+      <c r="J116" t="s">
         <v>25</v>
       </c>
-      <c r="E116" t="s">
+      <c r="K116" t="s">
         <v>26</v>
       </c>
-      <c r="F116" t="s">
+      <c r="L116" t="s">
         <v>155</v>
       </c>
-      <c r="G116" t="s">
+      <c r="M116" t="s">
         <v>44</v>
       </c>
-      <c r="H116" s="2">
+      <c r="N116" s="2">
         <v>46217</v>
       </c>
-      <c r="I116" s="2">
+      <c r="O116" s="2">
         <v>46214</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>157</v>
       </c>
       <c r="B117" t="s">
+        <v>224</v>
+      </c>
+      <c r="C117" t="s">
+        <v>224</v>
+      </c>
+      <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
+        <v>224</v>
+      </c>
+      <c r="F117" t="s">
+        <v>224</v>
+      </c>
+      <c r="G117" t="s">
+        <v>224</v>
+      </c>
+      <c r="H117" t="s">
         <v>24</v>
       </c>
-      <c r="C117" t="s">
-        <v>11</v>
-      </c>
-      <c r="D117" t="s">
+      <c r="I117" t="s">
+        <v>11</v>
+      </c>
+      <c r="J117" t="s">
         <v>25</v>
       </c>
-      <c r="E117" t="s">
+      <c r="K117" t="s">
         <v>26</v>
       </c>
-      <c r="F117" t="s">
+      <c r="L117" t="s">
         <v>155</v>
       </c>
-      <c r="G117" t="s">
+      <c r="M117" t="s">
         <v>44</v>
       </c>
-      <c r="H117" s="2">
+      <c r="N117" s="2">
         <v>46207</v>
       </c>
-      <c r="I117" s="2">
+      <c r="O117" s="2">
         <v>46204</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>158</v>
       </c>
       <c r="B118" t="s">
+        <v>224</v>
+      </c>
+      <c r="C118" t="s">
+        <v>224</v>
+      </c>
+      <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
+        <v>224</v>
+      </c>
+      <c r="F118" t="s">
+        <v>224</v>
+      </c>
+      <c r="G118" t="s">
+        <v>224</v>
+      </c>
+      <c r="H118" t="s">
         <v>24</v>
       </c>
-      <c r="C118" t="s">
-        <v>11</v>
-      </c>
-      <c r="D118" t="s">
+      <c r="I118" t="s">
+        <v>11</v>
+      </c>
+      <c r="J118" t="s">
         <v>25</v>
       </c>
-      <c r="E118" t="s">
+      <c r="K118" t="s">
         <v>26</v>
       </c>
-      <c r="F118" t="s">
+      <c r="L118" t="s">
         <v>155</v>
       </c>
-      <c r="G118" t="s">
+      <c r="M118" t="s">
         <v>44</v>
       </c>
-      <c r="H118" s="2">
+      <c r="N118" s="2">
         <v>46207</v>
       </c>
-      <c r="I118" s="2">
+      <c r="O118" s="2">
         <v>46204</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>159</v>
       </c>
       <c r="B119" t="s">
+        <v>224</v>
+      </c>
+      <c r="C119" t="s">
+        <v>224</v>
+      </c>
+      <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
+        <v>224</v>
+      </c>
+      <c r="F119" t="s">
+        <v>224</v>
+      </c>
+      <c r="G119" t="s">
+        <v>224</v>
+      </c>
+      <c r="H119" t="s">
         <v>24</v>
       </c>
-      <c r="C119" t="s">
-        <v>11</v>
-      </c>
-      <c r="D119" t="s">
+      <c r="I119" t="s">
+        <v>11</v>
+      </c>
+      <c r="J119" t="s">
         <v>25</v>
       </c>
-      <c r="E119" t="s">
+      <c r="K119" t="s">
         <v>26</v>
       </c>
-      <c r="F119" t="s">
+      <c r="L119" t="s">
         <v>155</v>
       </c>
-      <c r="G119" t="s">
+      <c r="M119" t="s">
         <v>44</v>
       </c>
-      <c r="H119" s="2">
+      <c r="N119" s="2">
         <v>46207</v>
       </c>
-      <c r="I119" s="2">
+      <c r="O119" s="2">
         <v>46204</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>160</v>
       </c>
       <c r="B120" t="s">
+        <v>224</v>
+      </c>
+      <c r="C120" t="s">
+        <v>224</v>
+      </c>
+      <c r="D120" t="s">
+        <v>224</v>
+      </c>
+      <c r="E120" t="s">
+        <v>224</v>
+      </c>
+      <c r="F120" t="s">
+        <v>224</v>
+      </c>
+      <c r="G120" t="s">
+        <v>224</v>
+      </c>
+      <c r="H120" t="s">
         <v>24</v>
       </c>
-      <c r="C120" t="s">
-        <v>11</v>
-      </c>
-      <c r="D120" t="s">
+      <c r="I120" t="s">
+        <v>11</v>
+      </c>
+      <c r="J120" t="s">
         <v>25</v>
       </c>
-      <c r="E120" t="s">
+      <c r="K120" t="s">
         <v>26</v>
       </c>
-      <c r="F120" t="s">
+      <c r="L120" t="s">
         <v>155</v>
       </c>
-      <c r="G120" t="s">
+      <c r="M120" t="s">
         <v>44</v>
       </c>
-      <c r="H120" s="2">
+      <c r="N120" s="2">
         <v>46207</v>
       </c>
-      <c r="I120" s="2">
+      <c r="O120" s="2">
         <v>46204</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>161</v>
       </c>
       <c r="B121" t="s">
+        <v>224</v>
+      </c>
+      <c r="C121" t="s">
+        <v>224</v>
+      </c>
+      <c r="D121" t="s">
+        <v>224</v>
+      </c>
+      <c r="E121" t="s">
+        <v>224</v>
+      </c>
+      <c r="F121" t="s">
+        <v>224</v>
+      </c>
+      <c r="G121" t="s">
+        <v>224</v>
+      </c>
+      <c r="H121" t="s">
         <v>124</v>
       </c>
-      <c r="C121" t="s">
+      <c r="I121" t="s">
         <v>37</v>
       </c>
-      <c r="D121" t="s">
+      <c r="J121" t="s">
         <v>25</v>
       </c>
-      <c r="E121" t="s">
+      <c r="K121" t="s">
         <v>26</v>
       </c>
-      <c r="F121" t="s">
+      <c r="L121" t="s">
         <v>162</v>
       </c>
-      <c r="G121" t="s">
+      <c r="M121" t="s">
         <v>137</v>
       </c>
-      <c r="H121" s="2">
+      <c r="N121" s="2">
         <v>46280</v>
       </c>
-      <c r="I121" s="2"/>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O121" s="2"/>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>163</v>
       </c>
       <c r="B122" t="s">
+        <v>224</v>
+      </c>
+      <c r="C122" t="s">
+        <v>224</v>
+      </c>
+      <c r="D122" t="s">
+        <v>224</v>
+      </c>
+      <c r="E122" t="s">
+        <v>224</v>
+      </c>
+      <c r="F122" t="s">
+        <v>224</v>
+      </c>
+      <c r="G122" t="s">
+        <v>224</v>
+      </c>
+      <c r="H122" t="s">
         <v>107</v>
       </c>
-      <c r="C122" t="s">
-        <v>11</v>
-      </c>
-      <c r="D122" t="s">
+      <c r="I122" t="s">
+        <v>11</v>
+      </c>
+      <c r="J122" t="s">
         <v>25</v>
       </c>
-      <c r="E122" t="s">
+      <c r="K122" t="s">
         <v>26</v>
       </c>
-      <c r="F122" t="s">
+      <c r="L122" t="s">
         <v>155</v>
       </c>
-      <c r="G122" t="s">
+      <c r="M122" t="s">
         <v>137</v>
       </c>
-      <c r="H122" s="2">
+      <c r="N122" s="2">
         <v>46280</v>
       </c>
-      <c r="I122" s="2">
+      <c r="O122" s="2">
         <v>46277</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>164</v>
       </c>
       <c r="B123" t="s">
+        <v>224</v>
+      </c>
+      <c r="C123" t="s">
+        <v>224</v>
+      </c>
+      <c r="D123" t="s">
+        <v>224</v>
+      </c>
+      <c r="E123" t="s">
+        <v>224</v>
+      </c>
+      <c r="F123" t="s">
+        <v>224</v>
+      </c>
+      <c r="G123" t="s">
+        <v>224</v>
+      </c>
+      <c r="H123" t="s">
         <v>107</v>
       </c>
-      <c r="C123" t="s">
-        <v>11</v>
-      </c>
-      <c r="D123" t="s">
+      <c r="I123" t="s">
+        <v>11</v>
+      </c>
+      <c r="J123" t="s">
         <v>25</v>
       </c>
-      <c r="E123" t="s">
+      <c r="K123" t="s">
         <v>26</v>
       </c>
-      <c r="F123" t="s">
+      <c r="L123" t="s">
         <v>155</v>
       </c>
-      <c r="G123" t="s">
+      <c r="M123" t="s">
         <v>137</v>
       </c>
-      <c r="H123" s="2">
+      <c r="N123" s="2">
         <v>46280</v>
       </c>
-      <c r="I123" s="2"/>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O123" s="2"/>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>165</v>
       </c>
       <c r="B124" t="s">
+        <v>224</v>
+      </c>
+      <c r="C124" t="s">
+        <v>224</v>
+      </c>
+      <c r="D124" t="s">
+        <v>224</v>
+      </c>
+      <c r="E124" t="s">
+        <v>224</v>
+      </c>
+      <c r="F124" t="s">
+        <v>224</v>
+      </c>
+      <c r="G124" t="s">
+        <v>224</v>
+      </c>
+      <c r="H124" t="s">
         <v>107</v>
       </c>
-      <c r="C124" t="s">
-        <v>11</v>
-      </c>
-      <c r="D124" t="s">
+      <c r="I124" t="s">
+        <v>11</v>
+      </c>
+      <c r="J124" t="s">
         <v>25</v>
       </c>
-      <c r="E124" t="s">
+      <c r="K124" t="s">
         <v>26</v>
       </c>
-      <c r="F124" t="s">
+      <c r="L124" t="s">
         <v>155</v>
       </c>
-      <c r="G124" t="s">
+      <c r="M124" t="s">
         <v>137</v>
       </c>
-      <c r="H124" s="2">
+      <c r="N124" s="2">
         <v>46280</v>
       </c>
-      <c r="I124" s="2"/>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O124" s="2"/>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>166</v>
       </c>
       <c r="B125" t="s">
+        <v>224</v>
+      </c>
+      <c r="C125" t="s">
+        <v>224</v>
+      </c>
+      <c r="D125" t="s">
+        <v>224</v>
+      </c>
+      <c r="E125" t="s">
+        <v>224</v>
+      </c>
+      <c r="F125" t="s">
+        <v>224</v>
+      </c>
+      <c r="G125" t="s">
+        <v>224</v>
+      </c>
+      <c r="H125" t="s">
         <v>107</v>
       </c>
-      <c r="C125" t="s">
-        <v>11</v>
-      </c>
-      <c r="D125" t="s">
+      <c r="I125" t="s">
+        <v>11</v>
+      </c>
+      <c r="J125" t="s">
         <v>25</v>
       </c>
-      <c r="E125" t="s">
+      <c r="K125" t="s">
         <v>26</v>
       </c>
-      <c r="F125" t="s">
+      <c r="L125" t="s">
         <v>155</v>
       </c>
-      <c r="G125" t="s">
+      <c r="M125" t="s">
         <v>137</v>
       </c>
-      <c r="H125" s="2">
+      <c r="N125" s="2">
         <v>46280</v>
       </c>
-      <c r="I125" s="2"/>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O125" s="2"/>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>167</v>
       </c>
       <c r="B126" t="s">
+        <v>224</v>
+      </c>
+      <c r="C126" t="s">
+        <v>224</v>
+      </c>
+      <c r="D126" t="s">
+        <v>224</v>
+      </c>
+      <c r="E126" t="s">
+        <v>224</v>
+      </c>
+      <c r="F126" t="s">
+        <v>224</v>
+      </c>
+      <c r="G126" t="s">
+        <v>224</v>
+      </c>
+      <c r="H126" t="s">
         <v>107</v>
       </c>
-      <c r="C126" t="s">
-        <v>11</v>
-      </c>
-      <c r="D126" t="s">
+      <c r="I126" t="s">
+        <v>11</v>
+      </c>
+      <c r="J126" t="s">
         <v>25</v>
       </c>
-      <c r="E126" t="s">
+      <c r="K126" t="s">
         <v>26</v>
       </c>
-      <c r="F126" t="s">
+      <c r="L126" t="s">
         <v>155</v>
       </c>
-      <c r="G126" t="s">
+      <c r="M126" t="s">
         <v>137</v>
       </c>
-      <c r="H126" s="2">
+      <c r="N126" s="2">
         <v>46280</v>
       </c>
-      <c r="I126" s="2"/>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O126" s="2"/>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>168</v>
       </c>
       <c r="B127" t="s">
+        <v>224</v>
+      </c>
+      <c r="C127" t="s">
+        <v>224</v>
+      </c>
+      <c r="D127" t="s">
+        <v>224</v>
+      </c>
+      <c r="E127" t="s">
+        <v>224</v>
+      </c>
+      <c r="F127" t="s">
+        <v>224</v>
+      </c>
+      <c r="G127" t="s">
+        <v>224</v>
+      </c>
+      <c r="H127" t="s">
         <v>31</v>
       </c>
-      <c r="C127" t="s">
-        <v>11</v>
-      </c>
-      <c r="D127" t="s">
+      <c r="I127" t="s">
+        <v>11</v>
+      </c>
+      <c r="J127" t="s">
         <v>32</v>
       </c>
-      <c r="E127" t="s">
+      <c r="K127" t="s">
         <v>26</v>
       </c>
-      <c r="F127" t="s">
+      <c r="L127" t="s">
         <v>33</v>
       </c>
-      <c r="G127" t="s">
+      <c r="M127" t="s">
         <v>137</v>
       </c>
-      <c r="H127" s="2">
+      <c r="N127" s="2">
         <v>46215</v>
       </c>
-      <c r="I127" s="2">
+      <c r="O127" s="2">
         <v>46212</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>169</v>
       </c>
       <c r="B128" t="s">
+        <v>224</v>
+      </c>
+      <c r="C128" t="s">
+        <v>224</v>
+      </c>
+      <c r="D128" t="s">
+        <v>224</v>
+      </c>
+      <c r="E128" t="s">
+        <v>224</v>
+      </c>
+      <c r="F128" t="s">
+        <v>224</v>
+      </c>
+      <c r="G128" t="s">
+        <v>224</v>
+      </c>
+      <c r="H128" t="s">
         <v>24</v>
       </c>
-      <c r="C128" t="s">
-        <v>11</v>
-      </c>
-      <c r="D128" t="s">
+      <c r="I128" t="s">
+        <v>11</v>
+      </c>
+      <c r="J128" t="s">
         <v>25</v>
       </c>
-      <c r="E128" t="s">
+      <c r="K128" t="s">
         <v>26</v>
       </c>
-      <c r="F128" t="s">
+      <c r="L128" t="s">
         <v>155</v>
       </c>
-      <c r="G128" t="s">
+      <c r="M128" t="s">
         <v>137</v>
       </c>
-      <c r="H128" s="2">
+      <c r="N128" s="2">
         <v>46207</v>
       </c>
-      <c r="I128" s="2">
+      <c r="O128" s="2">
         <v>46204</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>170</v>
       </c>
       <c r="B129" t="s">
+        <v>224</v>
+      </c>
+      <c r="C129" t="s">
+        <v>224</v>
+      </c>
+      <c r="D129" t="s">
+        <v>224</v>
+      </c>
+      <c r="E129" t="s">
+        <v>224</v>
+      </c>
+      <c r="F129" t="s">
+        <v>224</v>
+      </c>
+      <c r="G129" t="s">
+        <v>224</v>
+      </c>
+      <c r="H129" t="s">
         <v>24</v>
       </c>
-      <c r="C129" t="s">
-        <v>11</v>
-      </c>
-      <c r="D129" t="s">
+      <c r="I129" t="s">
+        <v>11</v>
+      </c>
+      <c r="J129" t="s">
         <v>25</v>
       </c>
-      <c r="E129" t="s">
+      <c r="K129" t="s">
         <v>26</v>
       </c>
-      <c r="F129" t="s">
+      <c r="L129" t="s">
         <v>162</v>
       </c>
-      <c r="G129" t="s">
+      <c r="M129" t="s">
         <v>137</v>
       </c>
-      <c r="H129" s="2">
+      <c r="N129" s="2">
         <v>46290</v>
       </c>
-      <c r="I129" s="2"/>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O129" s="2"/>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>171</v>
       </c>
       <c r="B130" t="s">
+        <v>224</v>
+      </c>
+      <c r="C130" t="s">
+        <v>224</v>
+      </c>
+      <c r="D130" t="s">
+        <v>224</v>
+      </c>
+      <c r="E130" t="s">
+        <v>224</v>
+      </c>
+      <c r="F130" t="s">
+        <v>224</v>
+      </c>
+      <c r="G130" t="s">
+        <v>224</v>
+      </c>
+      <c r="H130" t="s">
         <v>24</v>
       </c>
-      <c r="C130" t="s">
-        <v>11</v>
-      </c>
-      <c r="D130" t="s">
+      <c r="I130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J130" t="s">
         <v>25</v>
       </c>
-      <c r="E130" t="s">
+      <c r="K130" t="s">
         <v>26</v>
       </c>
-      <c r="F130" t="s">
+      <c r="L130" t="s">
         <v>162</v>
       </c>
-      <c r="G130" t="s">
+      <c r="M130" t="s">
         <v>137</v>
       </c>
-      <c r="H130" s="2">
+      <c r="N130" s="2">
         <v>46290</v>
       </c>
-      <c r="I130" s="2"/>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O130" s="2"/>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>172</v>
       </c>
-      <c r="B131" t="s">
+      <c r="H131" t="s">
         <v>173</v>
       </c>
-      <c r="C131" t="s">
-        <v>11</v>
-      </c>
-      <c r="D131" t="s">
+      <c r="I131" t="s">
+        <v>11</v>
+      </c>
+      <c r="J131" t="s">
         <v>25</v>
       </c>
-      <c r="E131" t="s">
+      <c r="K131" t="s">
         <v>26</v>
       </c>
-      <c r="G131" t="s">
+      <c r="M131" t="s">
         <v>141</v>
       </c>
-      <c r="H131" s="2"/>
-      <c r="I131" s="2"/>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>174</v>
       </c>
-      <c r="B132" t="s">
+      <c r="H132" t="s">
         <v>173</v>
       </c>
-      <c r="C132" t="s">
-        <v>11</v>
-      </c>
-      <c r="D132" t="s">
+      <c r="I132" t="s">
+        <v>11</v>
+      </c>
+      <c r="J132" t="s">
         <v>25</v>
       </c>
-      <c r="E132" t="s">
+      <c r="K132" t="s">
         <v>26</v>
       </c>
-      <c r="G132" t="s">
+      <c r="M132" t="s">
         <v>141</v>
       </c>
-      <c r="H132" s="2"/>
-      <c r="I132" s="2"/>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>175</v>
       </c>
-      <c r="B133" t="s">
+      <c r="H133" t="s">
         <v>173</v>
       </c>
-      <c r="C133" t="s">
-        <v>11</v>
-      </c>
-      <c r="D133" t="s">
+      <c r="I133" t="s">
+        <v>11</v>
+      </c>
+      <c r="J133" t="s">
         <v>25</v>
       </c>
-      <c r="E133" t="s">
+      <c r="K133" t="s">
         <v>26</v>
       </c>
-      <c r="G133" t="s">
+      <c r="M133" t="s">
         <v>141</v>
       </c>
-      <c r="H133" s="2"/>
-      <c r="I133" s="2"/>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>176</v>
       </c>
-      <c r="B134" t="s">
+      <c r="H134" t="s">
         <v>173</v>
       </c>
-      <c r="C134" t="s">
-        <v>11</v>
-      </c>
-      <c r="D134" t="s">
+      <c r="I134" t="s">
+        <v>11</v>
+      </c>
+      <c r="J134" t="s">
         <v>25</v>
       </c>
-      <c r="E134" t="s">
+      <c r="K134" t="s">
         <v>26</v>
       </c>
-      <c r="G134" t="s">
+      <c r="M134" t="s">
         <v>141</v>
       </c>
-      <c r="H134" s="2"/>
-      <c r="I134" s="2"/>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>177</v>
       </c>
-      <c r="B135" t="s">
+      <c r="H135" t="s">
         <v>173</v>
       </c>
-      <c r="C135" t="s">
-        <v>11</v>
-      </c>
-      <c r="D135" t="s">
+      <c r="I135" t="s">
+        <v>11</v>
+      </c>
+      <c r="J135" t="s">
         <v>25</v>
       </c>
-      <c r="E135" t="s">
+      <c r="K135" t="s">
         <v>26</v>
       </c>
-      <c r="G135" t="s">
+      <c r="M135" t="s">
         <v>141</v>
       </c>
-      <c r="H135" s="2"/>
-      <c r="I135" s="2"/>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>178</v>
       </c>
-      <c r="B136" t="s">
+      <c r="H136" t="s">
         <v>173</v>
       </c>
-      <c r="C136" t="s">
-        <v>11</v>
-      </c>
-      <c r="D136" t="s">
+      <c r="I136" t="s">
+        <v>11</v>
+      </c>
+      <c r="J136" t="s">
         <v>25</v>
       </c>
-      <c r="E136" t="s">
+      <c r="K136" t="s">
         <v>26</v>
       </c>
-      <c r="G136" t="s">
+      <c r="M136" t="s">
         <v>141</v>
       </c>
-      <c r="H136" s="2"/>
-      <c r="I136" s="2"/>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>179</v>
       </c>
-      <c r="B137" t="s">
+      <c r="H137" t="s">
         <v>173</v>
       </c>
-      <c r="C137" t="s">
-        <v>11</v>
-      </c>
-      <c r="D137" t="s">
+      <c r="I137" t="s">
+        <v>11</v>
+      </c>
+      <c r="J137" t="s">
         <v>25</v>
       </c>
-      <c r="E137" t="s">
+      <c r="K137" t="s">
         <v>26</v>
       </c>
-      <c r="G137" t="s">
+      <c r="M137" t="s">
         <v>141</v>
       </c>
-      <c r="H137" s="2"/>
-      <c r="I137" s="2"/>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>180</v>
       </c>
-      <c r="B138" t="s">
+      <c r="H138" t="s">
         <v>31</v>
       </c>
-      <c r="C138" t="s">
-        <v>11</v>
-      </c>
-      <c r="D138" t="s">
+      <c r="I138" t="s">
+        <v>11</v>
+      </c>
+      <c r="J138" t="s">
         <v>25</v>
       </c>
-      <c r="E138" t="s">
+      <c r="K138" t="s">
         <v>26</v>
       </c>
-      <c r="G138" t="s">
+      <c r="M138" t="s">
         <v>141</v>
       </c>
-      <c r="H138" s="2"/>
-      <c r="I138" s="2"/>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>181</v>
       </c>
-      <c r="B139" t="s">
+      <c r="H139" t="s">
         <v>31</v>
       </c>
-      <c r="C139" t="s">
-        <v>11</v>
-      </c>
-      <c r="D139" t="s">
+      <c r="I139" t="s">
+        <v>11</v>
+      </c>
+      <c r="J139" t="s">
         <v>25</v>
       </c>
-      <c r="E139" t="s">
+      <c r="K139" t="s">
         <v>26</v>
       </c>
-      <c r="G139" t="s">
+      <c r="M139" t="s">
         <v>141</v>
       </c>
-      <c r="H139" s="2"/>
-      <c r="I139" s="2"/>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>182</v>
       </c>
-      <c r="B140" t="s">
+      <c r="H140" t="s">
         <v>31</v>
       </c>
-      <c r="C140" t="s">
-        <v>11</v>
-      </c>
-      <c r="D140" t="s">
+      <c r="I140" t="s">
+        <v>11</v>
+      </c>
+      <c r="J140" t="s">
         <v>25</v>
       </c>
-      <c r="E140" t="s">
+      <c r="K140" t="s">
         <v>26</v>
       </c>
-      <c r="G140" t="s">
+      <c r="M140" t="s">
         <v>141</v>
       </c>
-      <c r="H140" s="2"/>
-      <c r="I140" s="2"/>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>183</v>
       </c>
-      <c r="B141" t="s">
+      <c r="H141" t="s">
         <v>31</v>
       </c>
-      <c r="C141" t="s">
-        <v>11</v>
-      </c>
-      <c r="D141" t="s">
+      <c r="I141" t="s">
+        <v>11</v>
+      </c>
+      <c r="J141" t="s">
         <v>25</v>
       </c>
-      <c r="E141" t="s">
+      <c r="K141" t="s">
         <v>26</v>
       </c>
-      <c r="G141" t="s">
+      <c r="M141" t="s">
         <v>141</v>
       </c>
-      <c r="H141" s="2"/>
-      <c r="I141" s="2"/>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>184</v>
       </c>
-      <c r="B142" t="s">
+      <c r="H142" t="s">
         <v>31</v>
       </c>
-      <c r="C142" t="s">
-        <v>11</v>
-      </c>
-      <c r="D142" t="s">
+      <c r="I142" t="s">
+        <v>11</v>
+      </c>
+      <c r="J142" t="s">
         <v>25</v>
       </c>
-      <c r="E142" t="s">
+      <c r="K142" t="s">
         <v>26</v>
       </c>
-      <c r="G142" t="s">
+      <c r="M142" t="s">
         <v>141</v>
       </c>
-      <c r="H142" s="2"/>
-      <c r="I142" s="2"/>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N142" s="2"/>
+      <c r="O142" s="2"/>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>185</v>
       </c>
-      <c r="B143" t="s">
+      <c r="H143" t="s">
         <v>31</v>
       </c>
-      <c r="C143" t="s">
-        <v>11</v>
-      </c>
-      <c r="D143" t="s">
+      <c r="I143" t="s">
+        <v>11</v>
+      </c>
+      <c r="J143" t="s">
         <v>25</v>
       </c>
-      <c r="E143" t="s">
+      <c r="K143" t="s">
         <v>26</v>
       </c>
-      <c r="G143" t="s">
+      <c r="M143" t="s">
         <v>141</v>
       </c>
-      <c r="H143" s="2"/>
-      <c r="I143" s="2"/>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>186</v>
       </c>
-      <c r="B144" t="s">
+      <c r="H144" t="s">
         <v>31</v>
       </c>
-      <c r="C144" t="s">
-        <v>11</v>
-      </c>
-      <c r="D144" t="s">
+      <c r="I144" t="s">
+        <v>11</v>
+      </c>
+      <c r="J144" t="s">
         <v>25</v>
       </c>
-      <c r="E144" t="s">
+      <c r="K144" t="s">
         <v>26</v>
       </c>
-      <c r="G144" t="s">
+      <c r="M144" t="s">
         <v>141</v>
       </c>
-      <c r="H144" s="2"/>
-      <c r="I144" s="2"/>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N144" s="2"/>
+      <c r="O144" s="2"/>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>187</v>
       </c>
-      <c r="B145" t="s">
+      <c r="H145" t="s">
         <v>31</v>
       </c>
-      <c r="C145" t="s">
-        <v>11</v>
-      </c>
-      <c r="D145" t="s">
+      <c r="I145" t="s">
+        <v>11</v>
+      </c>
+      <c r="J145" t="s">
         <v>25</v>
       </c>
-      <c r="E145" t="s">
+      <c r="K145" t="s">
         <v>26</v>
       </c>
-      <c r="G145" t="s">
+      <c r="M145" t="s">
         <v>141</v>
       </c>
-      <c r="H145" s="2"/>
-      <c r="I145" s="2"/>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>188</v>
       </c>
-      <c r="B146" t="s">
+      <c r="H146" t="s">
         <v>31</v>
       </c>
-      <c r="C146" t="s">
-        <v>11</v>
-      </c>
-      <c r="D146" t="s">
+      <c r="I146" t="s">
+        <v>11</v>
+      </c>
+      <c r="J146" t="s">
         <v>25</v>
       </c>
-      <c r="E146" t="s">
+      <c r="K146" t="s">
         <v>26</v>
       </c>
-      <c r="G146" t="s">
+      <c r="M146" t="s">
         <v>141</v>
       </c>
-      <c r="H146" s="2"/>
-      <c r="I146" s="2"/>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>189</v>
       </c>
-      <c r="B147" t="s">
+      <c r="H147" t="s">
         <v>31</v>
       </c>
-      <c r="C147" t="s">
-        <v>11</v>
-      </c>
-      <c r="D147" t="s">
+      <c r="I147" t="s">
+        <v>11</v>
+      </c>
+      <c r="J147" t="s">
         <v>25</v>
       </c>
-      <c r="E147" t="s">
+      <c r="K147" t="s">
         <v>26</v>
       </c>
-      <c r="G147" t="s">
+      <c r="M147" t="s">
         <v>141</v>
       </c>
-      <c r="H147" s="2"/>
-      <c r="I147" s="2"/>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N147" s="2"/>
+      <c r="O147" s="2"/>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>190</v>
       </c>
-      <c r="B148" t="s">
+      <c r="H148" t="s">
         <v>31</v>
       </c>
-      <c r="C148" t="s">
-        <v>11</v>
-      </c>
-      <c r="D148" t="s">
+      <c r="I148" t="s">
+        <v>11</v>
+      </c>
+      <c r="J148" t="s">
         <v>25</v>
       </c>
-      <c r="E148" t="s">
+      <c r="K148" t="s">
         <v>26</v>
       </c>
-      <c r="G148" t="s">
+      <c r="M148" t="s">
         <v>141</v>
       </c>
-      <c r="H148" s="2"/>
-      <c r="I148" s="2"/>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N148" s="2"/>
+      <c r="O148" s="2"/>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>217</v>
       </c>
       <c r="B149" t="s">
+        <v>224</v>
+      </c>
+      <c r="C149" t="s">
+        <v>224</v>
+      </c>
+      <c r="D149" t="s">
+        <v>224</v>
+      </c>
+      <c r="E149" t="s">
+        <v>224</v>
+      </c>
+      <c r="F149" t="s">
+        <v>224</v>
+      </c>
+      <c r="G149" t="s">
+        <v>224</v>
+      </c>
+      <c r="H149" t="s">
         <v>24</v>
       </c>
-      <c r="C149" t="s">
-        <v>11</v>
-      </c>
-      <c r="D149" t="s">
+      <c r="I149" t="s">
+        <v>11</v>
+      </c>
+      <c r="J149" t="s">
         <v>25</v>
       </c>
-      <c r="E149" t="s">
+      <c r="K149" t="s">
         <v>26</v>
       </c>
-      <c r="F149" t="s">
+      <c r="L149" t="s">
         <v>162</v>
       </c>
-      <c r="G149" t="s">
+      <c r="M149" t="s">
         <v>141</v>
       </c>
-      <c r="H149" s="2">
+      <c r="N149" s="2">
         <v>46290</v>
       </c>
-      <c r="I149" s="2"/>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O149" s="2"/>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>191</v>
       </c>
-      <c r="B150" t="s">
+      <c r="H150" t="s">
         <v>24</v>
       </c>
-      <c r="C150" t="s">
-        <v>11</v>
-      </c>
-      <c r="D150" t="s">
+      <c r="I150" t="s">
+        <v>11</v>
+      </c>
+      <c r="J150" t="s">
         <v>25</v>
       </c>
-      <c r="E150" t="s">
+      <c r="K150" t="s">
         <v>26</v>
       </c>
-      <c r="G150" t="s">
+      <c r="M150" t="s">
         <v>141</v>
       </c>
-      <c r="H150" s="2"/>
-      <c r="I150" s="2"/>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N150" s="2"/>
+      <c r="O150" s="2"/>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>192</v>
       </c>
       <c r="B151" t="s">
+        <v>224</v>
+      </c>
+      <c r="C151" t="s">
+        <v>224</v>
+      </c>
+      <c r="D151" t="s">
+        <v>224</v>
+      </c>
+      <c r="E151" t="s">
+        <v>224</v>
+      </c>
+      <c r="F151" t="s">
+        <v>224</v>
+      </c>
+      <c r="G151" t="s">
+        <v>224</v>
+      </c>
+      <c r="H151" t="s">
         <v>124</v>
       </c>
-      <c r="C151" t="s">
+      <c r="I151" t="s">
         <v>37</v>
       </c>
-      <c r="D151" t="s">
+      <c r="J151" t="s">
         <v>25</v>
       </c>
-      <c r="E151" t="s">
+      <c r="K151" t="s">
         <v>26</v>
       </c>
-      <c r="F151" t="s">
+      <c r="L151" t="s">
         <v>162</v>
       </c>
-      <c r="G151" t="s">
+      <c r="M151" t="s">
         <v>193</v>
       </c>
-      <c r="H151" s="2">
+      <c r="N151" s="2">
         <v>46239</v>
       </c>
-      <c r="I151" s="2">
+      <c r="O151" s="2">
         <v>46235</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>194</v>
       </c>
       <c r="B152" t="s">
+        <v>224</v>
+      </c>
+      <c r="C152" t="s">
+        <v>224</v>
+      </c>
+      <c r="D152" t="s">
+        <v>224</v>
+      </c>
+      <c r="E152" t="s">
+        <v>224</v>
+      </c>
+      <c r="F152" t="s">
+        <v>224</v>
+      </c>
+      <c r="G152" t="s">
+        <v>224</v>
+      </c>
+      <c r="H152" t="s">
         <v>124</v>
       </c>
-      <c r="C152" t="s">
+      <c r="I152" t="s">
         <v>37</v>
       </c>
-      <c r="D152" t="s">
+      <c r="J152" t="s">
         <v>25</v>
       </c>
-      <c r="E152" t="s">
+      <c r="K152" t="s">
         <v>26</v>
       </c>
-      <c r="F152" t="s">
+      <c r="L152" t="s">
         <v>162</v>
       </c>
-      <c r="G152" t="s">
+      <c r="M152" t="s">
         <v>193</v>
       </c>
-      <c r="H152" s="2">
+      <c r="N152" s="2">
         <v>46270</v>
       </c>
-      <c r="I152" s="2">
+      <c r="O152" s="2">
         <v>46263</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>195</v>
       </c>
       <c r="B153" t="s">
+        <v>224</v>
+      </c>
+      <c r="C153" t="s">
+        <v>224</v>
+      </c>
+      <c r="D153" t="s">
+        <v>224</v>
+      </c>
+      <c r="E153" t="s">
+        <v>224</v>
+      </c>
+      <c r="F153" t="s">
+        <v>224</v>
+      </c>
+      <c r="G153" t="s">
+        <v>224</v>
+      </c>
+      <c r="H153" t="s">
         <v>124</v>
       </c>
-      <c r="C153" t="s">
+      <c r="I153" t="s">
         <v>37</v>
       </c>
-      <c r="D153" t="s">
+      <c r="J153" t="s">
         <v>25</v>
       </c>
-      <c r="E153" t="s">
+      <c r="K153" t="s">
         <v>26</v>
       </c>
-      <c r="F153" t="s">
+      <c r="L153" t="s">
         <v>162</v>
       </c>
-      <c r="G153" t="s">
+      <c r="M153" t="s">
         <v>193</v>
       </c>
-      <c r="H153" s="2">
+      <c r="N153" s="2">
         <v>46270</v>
       </c>
-      <c r="I153" s="2">
+      <c r="O153" s="2">
         <v>46263</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>196</v>
       </c>
       <c r="B154" t="s">
+        <v>224</v>
+      </c>
+      <c r="C154" t="s">
+        <v>224</v>
+      </c>
+      <c r="D154" t="s">
+        <v>224</v>
+      </c>
+      <c r="E154" t="s">
+        <v>224</v>
+      </c>
+      <c r="F154" t="s">
+        <v>224</v>
+      </c>
+      <c r="G154" t="s">
+        <v>224</v>
+      </c>
+      <c r="H154" t="s">
         <v>124</v>
       </c>
-      <c r="C154" t="s">
+      <c r="I154" t="s">
         <v>37</v>
       </c>
-      <c r="D154" t="s">
+      <c r="J154" t="s">
         <v>25</v>
       </c>
-      <c r="E154" t="s">
+      <c r="K154" t="s">
         <v>26</v>
       </c>
-      <c r="F154" t="s">
+      <c r="L154" t="s">
         <v>162</v>
       </c>
-      <c r="G154" t="s">
+      <c r="M154" t="s">
         <v>193</v>
       </c>
-      <c r="H154" s="2">
+      <c r="N154" s="2">
         <v>46239</v>
       </c>
-      <c r="I154" s="2">
+      <c r="O154" s="2">
         <v>46235</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>197</v>
       </c>
       <c r="B155" t="s">
+        <v>224</v>
+      </c>
+      <c r="C155" t="s">
+        <v>224</v>
+      </c>
+      <c r="D155" t="s">
+        <v>224</v>
+      </c>
+      <c r="E155" t="s">
+        <v>224</v>
+      </c>
+      <c r="F155" t="s">
+        <v>224</v>
+      </c>
+      <c r="G155" t="s">
+        <v>224</v>
+      </c>
+      <c r="H155" t="s">
         <v>124</v>
       </c>
-      <c r="C155" t="s">
+      <c r="I155" t="s">
         <v>37</v>
       </c>
-      <c r="D155" t="s">
+      <c r="J155" t="s">
         <v>25</v>
       </c>
-      <c r="E155" t="s">
+      <c r="K155" t="s">
         <v>26</v>
       </c>
-      <c r="F155" t="s">
+      <c r="L155" t="s">
         <v>162</v>
       </c>
-      <c r="G155" t="s">
+      <c r="M155" t="s">
         <v>193</v>
       </c>
-      <c r="H155" s="2">
+      <c r="N155" s="2">
         <v>46262</v>
       </c>
-      <c r="I155" s="2">
+      <c r="O155" s="2">
         <v>46261</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>198</v>
       </c>
       <c r="B156" t="s">
+        <v>224</v>
+      </c>
+      <c r="C156" t="s">
+        <v>224</v>
+      </c>
+      <c r="D156" t="s">
+        <v>224</v>
+      </c>
+      <c r="E156" t="s">
+        <v>224</v>
+      </c>
+      <c r="F156" t="s">
+        <v>224</v>
+      </c>
+      <c r="G156" t="s">
+        <v>224</v>
+      </c>
+      <c r="H156" t="s">
         <v>124</v>
       </c>
-      <c r="C156" t="s">
+      <c r="I156" t="s">
         <v>37</v>
       </c>
-      <c r="D156" t="s">
+      <c r="J156" t="s">
         <v>25</v>
       </c>
-      <c r="E156" t="s">
+      <c r="K156" t="s">
         <v>26</v>
       </c>
-      <c r="F156" t="s">
+      <c r="L156" t="s">
         <v>162</v>
       </c>
-      <c r="G156" t="s">
+      <c r="M156" t="s">
         <v>193</v>
       </c>
-      <c r="H156" s="2">
+      <c r="N156" s="2">
         <v>46270</v>
       </c>
-      <c r="I156" s="2">
+      <c r="O156" s="2">
         <v>46261</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>199</v>
       </c>
       <c r="B157" t="s">
+        <v>224</v>
+      </c>
+      <c r="C157" t="s">
+        <v>224</v>
+      </c>
+      <c r="D157" t="s">
+        <v>224</v>
+      </c>
+      <c r="E157" t="s">
+        <v>224</v>
+      </c>
+      <c r="F157" t="s">
+        <v>224</v>
+      </c>
+      <c r="G157" t="s">
+        <v>224</v>
+      </c>
+      <c r="H157" t="s">
         <v>124</v>
       </c>
-      <c r="C157" t="s">
+      <c r="I157" t="s">
         <v>37</v>
       </c>
-      <c r="D157" t="s">
+      <c r="J157" t="s">
         <v>25</v>
       </c>
-      <c r="E157" t="s">
+      <c r="K157" t="s">
         <v>26</v>
       </c>
-      <c r="F157" t="s">
+      <c r="L157" t="s">
         <v>162</v>
       </c>
-      <c r="G157" t="s">
+      <c r="M157" t="s">
         <v>193</v>
       </c>
-      <c r="H157" s="2">
+      <c r="N157" s="2">
         <v>46262</v>
       </c>
-      <c r="I157" s="2">
+      <c r="O157" s="2">
         <v>46256</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>200</v>
       </c>
       <c r="B158" t="s">
+        <v>224</v>
+      </c>
+      <c r="C158" t="s">
+        <v>224</v>
+      </c>
+      <c r="D158" t="s">
+        <v>224</v>
+      </c>
+      <c r="E158" t="s">
+        <v>224</v>
+      </c>
+      <c r="F158" t="s">
+        <v>224</v>
+      </c>
+      <c r="G158" t="s">
+        <v>224</v>
+      </c>
+      <c r="H158" t="s">
         <v>124</v>
       </c>
-      <c r="C158" t="s">
+      <c r="I158" t="s">
         <v>37</v>
       </c>
-      <c r="D158" t="s">
+      <c r="J158" t="s">
         <v>25</v>
       </c>
-      <c r="E158" t="s">
+      <c r="K158" t="s">
         <v>26</v>
       </c>
-      <c r="F158" t="s">
+      <c r="L158" t="s">
         <v>162</v>
       </c>
-      <c r="G158" t="s">
+      <c r="M158" t="s">
         <v>193</v>
       </c>
-      <c r="H158" s="2">
+      <c r="N158" s="2">
         <v>46270</v>
       </c>
-      <c r="I158" s="2">
+      <c r="O158" s="2">
         <v>46262</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>201</v>
       </c>
       <c r="B159" t="s">
+        <v>224</v>
+      </c>
+      <c r="C159" t="s">
+        <v>224</v>
+      </c>
+      <c r="D159" t="s">
+        <v>224</v>
+      </c>
+      <c r="E159" t="s">
+        <v>224</v>
+      </c>
+      <c r="F159" t="s">
+        <v>224</v>
+      </c>
+      <c r="G159" t="s">
+        <v>224</v>
+      </c>
+      <c r="H159" t="s">
         <v>124</v>
       </c>
-      <c r="C159" t="s">
+      <c r="I159" t="s">
         <v>37</v>
       </c>
-      <c r="D159" t="s">
+      <c r="J159" t="s">
         <v>25</v>
       </c>
-      <c r="E159" t="s">
+      <c r="K159" t="s">
         <v>26</v>
       </c>
-      <c r="F159" t="s">
+      <c r="L159" t="s">
         <v>162</v>
       </c>
-      <c r="G159" t="s">
+      <c r="M159" t="s">
         <v>193</v>
       </c>
-      <c r="H159" s="2">
+      <c r="N159" s="2">
         <v>46262</v>
       </c>
-      <c r="I159" s="2">
+      <c r="O159" s="2">
         <v>46261</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>202</v>
       </c>
       <c r="B160" t="s">
+        <v>224</v>
+      </c>
+      <c r="C160" t="s">
+        <v>224</v>
+      </c>
+      <c r="D160" t="s">
+        <v>224</v>
+      </c>
+      <c r="E160" t="s">
+        <v>224</v>
+      </c>
+      <c r="F160" t="s">
+        <v>224</v>
+      </c>
+      <c r="G160" t="s">
+        <v>224</v>
+      </c>
+      <c r="H160" t="s">
         <v>203</v>
       </c>
-      <c r="C160" t="s">
-        <v>11</v>
-      </c>
-      <c r="D160" t="s">
+      <c r="I160" t="s">
+        <v>11</v>
+      </c>
+      <c r="J160" t="s">
         <v>25</v>
       </c>
-      <c r="E160" t="s">
+      <c r="K160" t="s">
         <v>26</v>
       </c>
-      <c r="F160" t="s">
+      <c r="L160" t="s">
         <v>162</v>
       </c>
-      <c r="G160" t="s">
+      <c r="M160" t="s">
         <v>193</v>
       </c>
-      <c r="H160" s="2">
+      <c r="N160" s="2">
         <v>46280</v>
       </c>
-      <c r="I160" s="2"/>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O160" s="2"/>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>204</v>
       </c>
       <c r="B161" t="s">
+        <v>224</v>
+      </c>
+      <c r="C161" t="s">
+        <v>224</v>
+      </c>
+      <c r="D161" t="s">
+        <v>224</v>
+      </c>
+      <c r="E161" t="s">
+        <v>224</v>
+      </c>
+      <c r="F161" t="s">
+        <v>224</v>
+      </c>
+      <c r="G161" t="s">
+        <v>224</v>
+      </c>
+      <c r="H161" t="s">
         <v>203</v>
       </c>
-      <c r="C161" t="s">
-        <v>11</v>
-      </c>
-      <c r="D161" t="s">
+      <c r="I161" t="s">
+        <v>11</v>
+      </c>
+      <c r="J161" t="s">
         <v>25</v>
       </c>
-      <c r="E161" t="s">
+      <c r="K161" t="s">
         <v>26</v>
       </c>
-      <c r="F161" t="s">
+      <c r="L161" t="s">
         <v>162</v>
       </c>
-      <c r="G161" t="s">
+      <c r="M161" t="s">
         <v>193</v>
       </c>
-      <c r="H161" s="2">
+      <c r="N161" s="2">
         <v>46280</v>
       </c>
-      <c r="I161" s="2"/>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O161" s="2"/>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>205</v>
       </c>
       <c r="B162" t="s">
+        <v>224</v>
+      </c>
+      <c r="C162" t="s">
+        <v>224</v>
+      </c>
+      <c r="D162" t="s">
+        <v>224</v>
+      </c>
+      <c r="E162" t="s">
+        <v>224</v>
+      </c>
+      <c r="F162" t="s">
+        <v>224</v>
+      </c>
+      <c r="G162" t="s">
+        <v>224</v>
+      </c>
+      <c r="H162" t="s">
         <v>203</v>
       </c>
-      <c r="C162" t="s">
-        <v>11</v>
-      </c>
-      <c r="D162" t="s">
+      <c r="I162" t="s">
+        <v>11</v>
+      </c>
+      <c r="J162" t="s">
         <v>25</v>
       </c>
-      <c r="E162" t="s">
+      <c r="K162" t="s">
         <v>26</v>
       </c>
-      <c r="F162" t="s">
+      <c r="L162" t="s">
         <v>162</v>
       </c>
-      <c r="G162" t="s">
+      <c r="M162" t="s">
         <v>193</v>
       </c>
-      <c r="H162" s="2">
+      <c r="N162" s="2">
         <v>46280</v>
       </c>
-      <c r="I162" s="2"/>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O162" s="2"/>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>206</v>
       </c>
-      <c r="B163" t="s">
+      <c r="H163" t="s">
         <v>203</v>
       </c>
-      <c r="C163" t="s">
-        <v>11</v>
-      </c>
-      <c r="D163" t="s">
+      <c r="I163" t="s">
+        <v>11</v>
+      </c>
+      <c r="J163" t="s">
         <v>25</v>
       </c>
-      <c r="E163" t="s">
+      <c r="K163" t="s">
         <v>26</v>
       </c>
-      <c r="G163" t="s">
+      <c r="M163" t="s">
         <v>193</v>
       </c>
-      <c r="H163" s="2"/>
-      <c r="I163" s="2"/>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N163" s="2"/>
+      <c r="O163" s="2"/>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>207</v>
       </c>
-      <c r="B164" t="s">
+      <c r="H164" t="s">
         <v>203</v>
       </c>
-      <c r="C164" t="s">
-        <v>11</v>
-      </c>
-      <c r="D164" t="s">
+      <c r="I164" t="s">
+        <v>11</v>
+      </c>
+      <c r="J164" t="s">
         <v>25</v>
       </c>
-      <c r="E164" t="s">
+      <c r="K164" t="s">
         <v>26</v>
       </c>
-      <c r="G164" t="s">
+      <c r="M164" t="s">
         <v>193</v>
       </c>
-      <c r="H164" s="2"/>
-      <c r="I164" s="2"/>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N164" s="2"/>
+      <c r="O164" s="2"/>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>208</v>
       </c>
-      <c r="B165" t="s">
+      <c r="H165" t="s">
         <v>203</v>
       </c>
-      <c r="C165" t="s">
-        <v>11</v>
-      </c>
-      <c r="D165" t="s">
+      <c r="I165" t="s">
+        <v>11</v>
+      </c>
+      <c r="J165" t="s">
         <v>25</v>
       </c>
-      <c r="E165" t="s">
+      <c r="K165" t="s">
         <v>26</v>
       </c>
-      <c r="G165" t="s">
+      <c r="M165" t="s">
         <v>193</v>
       </c>
-      <c r="H165" s="2"/>
-      <c r="I165" s="2"/>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N165" s="2"/>
+      <c r="O165" s="2"/>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>209</v>
       </c>
-      <c r="B166" t="s">
+      <c r="H166" t="s">
         <v>203</v>
       </c>
-      <c r="C166" t="s">
-        <v>11</v>
-      </c>
-      <c r="D166" t="s">
+      <c r="I166" t="s">
+        <v>11</v>
+      </c>
+      <c r="J166" t="s">
         <v>25</v>
       </c>
-      <c r="E166" t="s">
+      <c r="K166" t="s">
         <v>26</v>
       </c>
-      <c r="G166" t="s">
+      <c r="M166" t="s">
         <v>193</v>
       </c>
-      <c r="H166" s="2"/>
-      <c r="I166" s="2"/>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N166" s="2"/>
+      <c r="O166" s="2"/>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>210</v>
       </c>
-      <c r="B167" t="s">
+      <c r="H167" t="s">
         <v>203</v>
       </c>
-      <c r="C167" t="s">
-        <v>11</v>
-      </c>
-      <c r="D167" t="s">
+      <c r="I167" t="s">
+        <v>11</v>
+      </c>
+      <c r="J167" t="s">
         <v>25</v>
       </c>
-      <c r="E167" t="s">
+      <c r="K167" t="s">
         <v>26</v>
       </c>
-      <c r="G167" t="s">
+      <c r="M167" t="s">
         <v>193</v>
       </c>
-      <c r="H167" s="2"/>
-      <c r="I167" s="2"/>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N167" s="2"/>
+      <c r="O167" s="2"/>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>211</v>
       </c>
-      <c r="B168" t="s">
+      <c r="H168" t="s">
         <v>203</v>
       </c>
-      <c r="C168" t="s">
-        <v>11</v>
-      </c>
-      <c r="D168" t="s">
+      <c r="I168" t="s">
+        <v>11</v>
+      </c>
+      <c r="J168" t="s">
         <v>25</v>
       </c>
-      <c r="E168" t="s">
+      <c r="K168" t="s">
         <v>26</v>
       </c>
-      <c r="G168" t="s">
+      <c r="M168" t="s">
         <v>193</v>
       </c>
-      <c r="H168" s="2"/>
-      <c r="I168" s="2"/>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N168" s="2"/>
+      <c r="O168" s="2"/>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>212</v>
       </c>
-      <c r="B169" t="s">
+      <c r="H169" t="s">
         <v>24</v>
       </c>
-      <c r="C169" t="s">
-        <v>11</v>
-      </c>
-      <c r="D169" t="s">
+      <c r="I169" t="s">
+        <v>11</v>
+      </c>
+      <c r="J169" t="s">
         <v>25</v>
       </c>
-      <c r="E169" t="s">
+      <c r="K169" t="s">
         <v>26</v>
       </c>
-      <c r="G169" t="s">
+      <c r="M169" t="s">
         <v>44</v>
       </c>
-      <c r="H169" s="2"/>
-      <c r="I169" s="2"/>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N169" s="2"/>
+      <c r="O169" s="2"/>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>213</v>
       </c>
-      <c r="B170" t="s">
+      <c r="H170" t="s">
         <v>24</v>
       </c>
-      <c r="C170" t="s">
-        <v>11</v>
-      </c>
-      <c r="D170" t="s">
+      <c r="I170" t="s">
+        <v>11</v>
+      </c>
+      <c r="J170" t="s">
         <v>25</v>
       </c>
-      <c r="E170" t="s">
+      <c r="K170" t="s">
         <v>26</v>
       </c>
-      <c r="G170" t="s">
+      <c r="M170" t="s">
         <v>193</v>
       </c>
-      <c r="H170" s="2"/>
-      <c r="I170" s="2"/>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N170" s="2"/>
+      <c r="O170" s="2"/>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>214</v>
       </c>
-      <c r="B171" t="s">
+      <c r="H171" t="s">
         <v>24</v>
       </c>
-      <c r="C171" t="s">
-        <v>11</v>
-      </c>
-      <c r="D171" t="s">
+      <c r="I171" t="s">
+        <v>11</v>
+      </c>
+      <c r="J171" t="s">
         <v>25</v>
       </c>
-      <c r="E171" t="s">
+      <c r="K171" t="s">
         <v>26</v>
       </c>
-      <c r="G171" t="s">
+      <c r="M171" t="s">
         <v>193</v>
       </c>
-      <c r="H171" s="2"/>
-      <c r="I171" s="2"/>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="N171" s="2"/>
+      <c r="O171" s="2"/>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>215</v>
       </c>
-      <c r="B172" t="s">
+      <c r="H172" t="s">
         <v>24</v>
       </c>
-      <c r="C172" t="s">
-        <v>11</v>
-      </c>
-      <c r="D172" t="s">
+      <c r="I172" t="s">
+        <v>11</v>
+      </c>
+      <c r="J172" t="s">
         <v>25</v>
       </c>
-      <c r="E172" t="s">
+      <c r="K172" t="s">
         <v>26</v>
       </c>
-      <c r="G172" t="s">
+      <c r="M172" t="s">
         <v>193</v>
       </c>
-      <c r="H172" s="2"/>
-      <c r="I172" s="2"/>
+      <c r="N172" s="2"/>
+      <c r="O172" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5796,8 +7815,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="100717af0b9d82d0b2a1c8234c4e76b0">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cd289fca9f75e9fc862e02817de8bf32" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <xsd:import namespace="a6b958bc-5708-46f2-92f1-bce61d011186"/>
     <xsd:element name="properties">
@@ -5893,7 +7912,7 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d7713e69-6b5e-48f9-bc66-ec74065ebb50" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d7713e69-6b5e-48f9-bc66-ec74065ebb50" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -5919,7 +7938,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a6b958bc-5708-46f2-92f1-bce61d011186" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -5938,7 +7957,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6078,7 +8097,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9A0667C-3738-42E6-89EB-FC97E1A1B35D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes.sharepoint.com/sites/DeLunaOperaes/Documentos Partilhados/GESTÃO DE FROTA/Automações Frota/Controle de Frota - BID 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12F098AE-A6D9-498F-90A1-710E6C8AD6FD}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02897751-8C48-4E8A-A402-966DADFDAC8D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1852" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="226">
   <si>
     <t>Placa</t>
   </si>
@@ -1071,11 +1071,21 @@
   <dimension ref="A1:O172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="34" customWidth="1"/>
-    <col min="13" max="15" width="16" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="44.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -1129,6 +1139,24 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
+      <c r="B2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G2" t="s">
+        <v>224</v>
+      </c>
       <c r="H2" t="s">
         <v>10</v>
       </c>
@@ -1156,6 +1184,24 @@
       <c r="A3" t="s">
         <v>15</v>
       </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G3" t="s">
+        <v>224</v>
+      </c>
       <c r="H3" t="s">
         <v>10</v>
       </c>
@@ -1183,6 +1229,24 @@
       <c r="A4" t="s">
         <v>16</v>
       </c>
+      <c r="B4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D4" t="s">
+        <v>224</v>
+      </c>
+      <c r="E4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G4" t="s">
+        <v>224</v>
+      </c>
       <c r="H4" t="s">
         <v>10</v>
       </c>
@@ -1210,6 +1274,24 @@
       <c r="A5" t="s">
         <v>17</v>
       </c>
+      <c r="B5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F5" t="s">
+        <v>224</v>
+      </c>
+      <c r="G5" t="s">
+        <v>224</v>
+      </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
@@ -1237,6 +1319,24 @@
       <c r="A6" t="s">
         <v>19</v>
       </c>
+      <c r="B6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F6" t="s">
+        <v>224</v>
+      </c>
+      <c r="G6" t="s">
+        <v>224</v>
+      </c>
       <c r="H6" t="s">
         <v>18</v>
       </c>
@@ -1264,6 +1364,24 @@
       <c r="A7" t="s">
         <v>20</v>
       </c>
+      <c r="B7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F7" t="s">
+        <v>224</v>
+      </c>
+      <c r="G7" t="s">
+        <v>224</v>
+      </c>
       <c r="H7" t="s">
         <v>18</v>
       </c>
@@ -1291,6 +1409,24 @@
       <c r="A8" t="s">
         <v>21</v>
       </c>
+      <c r="B8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D8" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" t="s">
+        <v>224</v>
+      </c>
+      <c r="F8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G8" t="s">
+        <v>224</v>
+      </c>
       <c r="H8" t="s">
         <v>18</v>
       </c>
@@ -1318,6 +1454,24 @@
       <c r="A9" t="s">
         <v>22</v>
       </c>
+      <c r="B9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" t="s">
+        <v>224</v>
+      </c>
+      <c r="F9" t="s">
+        <v>224</v>
+      </c>
+      <c r="G9" t="s">
+        <v>224</v>
+      </c>
       <c r="H9" t="s">
         <v>18</v>
       </c>
@@ -1360,6 +1514,9 @@
       <c r="F10" t="s">
         <v>224</v>
       </c>
+      <c r="G10" t="s">
+        <v>224</v>
+      </c>
       <c r="H10" t="s">
         <v>24</v>
       </c>
@@ -1404,6 +1561,9 @@
       <c r="F11" t="s">
         <v>224</v>
       </c>
+      <c r="G11" t="s">
+        <v>224</v>
+      </c>
       <c r="H11" t="s">
         <v>24</v>
       </c>
@@ -1448,6 +1608,9 @@
       <c r="F12" t="s">
         <v>224</v>
       </c>
+      <c r="G12" t="s">
+        <v>224</v>
+      </c>
       <c r="H12" t="s">
         <v>31</v>
       </c>
@@ -1477,6 +1640,24 @@
       <c r="A13" t="s">
         <v>35</v>
       </c>
+      <c r="B13" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" t="s">
+        <v>224</v>
+      </c>
+      <c r="E13" t="s">
+        <v>224</v>
+      </c>
+      <c r="F13" t="s">
+        <v>224</v>
+      </c>
+      <c r="G13" t="s">
+        <v>224</v>
+      </c>
       <c r="H13" t="s">
         <v>36</v>
       </c>
@@ -1506,6 +1687,24 @@
       <c r="A14" t="s">
         <v>40</v>
       </c>
+      <c r="B14" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D14" t="s">
+        <v>224</v>
+      </c>
+      <c r="E14" t="s">
+        <v>224</v>
+      </c>
+      <c r="F14" t="s">
+        <v>224</v>
+      </c>
+      <c r="G14" t="s">
+        <v>224</v>
+      </c>
       <c r="H14" t="s">
         <v>36</v>
       </c>
@@ -1535,6 +1734,24 @@
       <c r="A15" t="s">
         <v>41</v>
       </c>
+      <c r="B15" t="s">
+        <v>224</v>
+      </c>
+      <c r="C15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D15" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" t="s">
+        <v>224</v>
+      </c>
+      <c r="F15" t="s">
+        <v>224</v>
+      </c>
+      <c r="G15" t="s">
+        <v>224</v>
+      </c>
       <c r="H15" t="s">
         <v>36</v>
       </c>
@@ -1564,6 +1781,24 @@
       <c r="A16" t="s">
         <v>42</v>
       </c>
+      <c r="B16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C16" t="s">
+        <v>224</v>
+      </c>
+      <c r="D16" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" t="s">
+        <v>224</v>
+      </c>
+      <c r="F16" t="s">
+        <v>224</v>
+      </c>
+      <c r="G16" t="s">
+        <v>224</v>
+      </c>
       <c r="H16" t="s">
         <v>36</v>
       </c>
@@ -1593,6 +1828,24 @@
       <c r="A17" t="s">
         <v>43</v>
       </c>
+      <c r="B17" t="s">
+        <v>224</v>
+      </c>
+      <c r="C17" t="s">
+        <v>224</v>
+      </c>
+      <c r="D17" t="s">
+        <v>224</v>
+      </c>
+      <c r="E17" t="s">
+        <v>224</v>
+      </c>
+      <c r="F17" t="s">
+        <v>224</v>
+      </c>
+      <c r="G17" t="s">
+        <v>224</v>
+      </c>
       <c r="H17" t="s">
         <v>36</v>
       </c>
@@ -1622,6 +1875,24 @@
       <c r="A18" t="s">
         <v>45</v>
       </c>
+      <c r="B18" t="s">
+        <v>224</v>
+      </c>
+      <c r="C18" t="s">
+        <v>224</v>
+      </c>
+      <c r="D18" t="s">
+        <v>224</v>
+      </c>
+      <c r="E18" t="s">
+        <v>224</v>
+      </c>
+      <c r="F18" t="s">
+        <v>224</v>
+      </c>
+      <c r="G18" t="s">
+        <v>224</v>
+      </c>
       <c r="H18" t="s">
         <v>36</v>
       </c>
@@ -1666,6 +1937,9 @@
       <c r="F19" t="s">
         <v>224</v>
       </c>
+      <c r="G19" t="s">
+        <v>224</v>
+      </c>
       <c r="H19" t="s">
         <v>36</v>
       </c>
@@ -1695,6 +1969,24 @@
       <c r="A20" t="s">
         <v>47</v>
       </c>
+      <c r="B20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" t="s">
+        <v>224</v>
+      </c>
+      <c r="D20" t="s">
+        <v>224</v>
+      </c>
+      <c r="E20" t="s">
+        <v>224</v>
+      </c>
+      <c r="F20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G20" t="s">
+        <v>224</v>
+      </c>
       <c r="H20" t="s">
         <v>36</v>
       </c>
@@ -1724,6 +2016,24 @@
       <c r="A21" t="s">
         <v>48</v>
       </c>
+      <c r="B21" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" t="s">
+        <v>224</v>
+      </c>
+      <c r="D21" t="s">
+        <v>224</v>
+      </c>
+      <c r="E21" t="s">
+        <v>224</v>
+      </c>
+      <c r="F21" t="s">
+        <v>224</v>
+      </c>
+      <c r="G21" t="s">
+        <v>224</v>
+      </c>
       <c r="H21" t="s">
         <v>36</v>
       </c>
@@ -1768,6 +2078,9 @@
       <c r="F22" t="s">
         <v>224</v>
       </c>
+      <c r="G22" t="s">
+        <v>224</v>
+      </c>
       <c r="H22" t="s">
         <v>50</v>
       </c>
@@ -1812,6 +2125,9 @@
       <c r="F23" t="s">
         <v>224</v>
       </c>
+      <c r="G23" t="s">
+        <v>224</v>
+      </c>
       <c r="H23" t="s">
         <v>50</v>
       </c>
@@ -1856,6 +2172,9 @@
       <c r="F24" t="s">
         <v>224</v>
       </c>
+      <c r="G24" t="s">
+        <v>224</v>
+      </c>
       <c r="H24" t="s">
         <v>50</v>
       </c>
@@ -1900,6 +2219,9 @@
       <c r="F25" t="s">
         <v>224</v>
       </c>
+      <c r="G25" t="s">
+        <v>224</v>
+      </c>
       <c r="H25" t="s">
         <v>50</v>
       </c>
@@ -1944,6 +2266,9 @@
       <c r="F26" t="s">
         <v>224</v>
       </c>
+      <c r="G26" t="s">
+        <v>224</v>
+      </c>
       <c r="H26" t="s">
         <v>50</v>
       </c>
@@ -1988,6 +2313,9 @@
       <c r="F27" t="s">
         <v>224</v>
       </c>
+      <c r="G27" t="s">
+        <v>224</v>
+      </c>
       <c r="H27" t="s">
         <v>50</v>
       </c>
@@ -2032,6 +2360,9 @@
       <c r="F28" t="s">
         <v>224</v>
       </c>
+      <c r="G28" t="s">
+        <v>224</v>
+      </c>
       <c r="H28" t="s">
         <v>50</v>
       </c>
@@ -2076,6 +2407,9 @@
       <c r="F29" t="s">
         <v>224</v>
       </c>
+      <c r="G29" t="s">
+        <v>224</v>
+      </c>
       <c r="H29" t="s">
         <v>50</v>
       </c>
@@ -2120,6 +2454,9 @@
       <c r="F30" t="s">
         <v>224</v>
       </c>
+      <c r="G30" t="s">
+        <v>224</v>
+      </c>
       <c r="H30" t="s">
         <v>50</v>
       </c>
@@ -2164,6 +2501,9 @@
       <c r="F31" t="s">
         <v>224</v>
       </c>
+      <c r="G31" t="s">
+        <v>224</v>
+      </c>
       <c r="H31" t="s">
         <v>50</v>
       </c>
@@ -2208,6 +2548,9 @@
       <c r="F32" t="s">
         <v>224</v>
       </c>
+      <c r="G32" t="s">
+        <v>224</v>
+      </c>
       <c r="H32" t="s">
         <v>50</v>
       </c>
@@ -2252,6 +2595,9 @@
       <c r="F33" t="s">
         <v>224</v>
       </c>
+      <c r="G33" t="s">
+        <v>224</v>
+      </c>
       <c r="H33" t="s">
         <v>50</v>
       </c>
@@ -2296,6 +2642,9 @@
       <c r="F34" t="s">
         <v>224</v>
       </c>
+      <c r="G34" t="s">
+        <v>224</v>
+      </c>
       <c r="H34" t="s">
         <v>50</v>
       </c>
@@ -2340,6 +2689,9 @@
       <c r="F35" t="s">
         <v>224</v>
       </c>
+      <c r="G35" t="s">
+        <v>224</v>
+      </c>
       <c r="H35" t="s">
         <v>50</v>
       </c>
@@ -2384,6 +2736,9 @@
       <c r="F36" t="s">
         <v>224</v>
       </c>
+      <c r="G36" t="s">
+        <v>224</v>
+      </c>
       <c r="H36" t="s">
         <v>50</v>
       </c>
@@ -2428,6 +2783,9 @@
       <c r="F37" t="s">
         <v>224</v>
       </c>
+      <c r="G37" t="s">
+        <v>224</v>
+      </c>
       <c r="H37" t="s">
         <v>66</v>
       </c>
@@ -2472,6 +2830,9 @@
       <c r="F38" t="s">
         <v>224</v>
       </c>
+      <c r="G38" t="s">
+        <v>224</v>
+      </c>
       <c r="H38" t="s">
         <v>66</v>
       </c>
@@ -2516,6 +2877,9 @@
       <c r="F39" t="s">
         <v>224</v>
       </c>
+      <c r="G39" t="s">
+        <v>224</v>
+      </c>
       <c r="H39" t="s">
         <v>66</v>
       </c>
@@ -2560,6 +2924,9 @@
       <c r="F40" t="s">
         <v>224</v>
       </c>
+      <c r="G40" t="s">
+        <v>224</v>
+      </c>
       <c r="H40" t="s">
         <v>66</v>
       </c>
@@ -2589,6 +2956,24 @@
       <c r="A41" t="s">
         <v>70</v>
       </c>
+      <c r="B41" t="s">
+        <v>224</v>
+      </c>
+      <c r="C41" t="s">
+        <v>224</v>
+      </c>
+      <c r="D41" t="s">
+        <v>224</v>
+      </c>
+      <c r="E41" t="s">
+        <v>224</v>
+      </c>
+      <c r="F41" t="s">
+        <v>224</v>
+      </c>
+      <c r="G41" t="s">
+        <v>224</v>
+      </c>
       <c r="H41" t="s">
         <v>66</v>
       </c>
@@ -2633,6 +3018,9 @@
       <c r="F42" t="s">
         <v>224</v>
       </c>
+      <c r="G42" t="s">
+        <v>224</v>
+      </c>
       <c r="H42" t="s">
         <v>66</v>
       </c>
@@ -2677,6 +3065,9 @@
       <c r="F43" t="s">
         <v>224</v>
       </c>
+      <c r="G43" t="s">
+        <v>224</v>
+      </c>
       <c r="H43" t="s">
         <v>66</v>
       </c>
@@ -2706,6 +3097,24 @@
       <c r="A44" t="s">
         <v>73</v>
       </c>
+      <c r="B44" t="s">
+        <v>224</v>
+      </c>
+      <c r="C44" t="s">
+        <v>224</v>
+      </c>
+      <c r="D44" t="s">
+        <v>224</v>
+      </c>
+      <c r="E44" t="s">
+        <v>224</v>
+      </c>
+      <c r="F44" t="s">
+        <v>224</v>
+      </c>
+      <c r="G44" t="s">
+        <v>224</v>
+      </c>
       <c r="H44" t="s">
         <v>66</v>
       </c>
@@ -2750,6 +3159,9 @@
       <c r="F45" t="s">
         <v>224</v>
       </c>
+      <c r="G45" t="s">
+        <v>224</v>
+      </c>
       <c r="H45" t="s">
         <v>66</v>
       </c>
@@ -2794,6 +3206,9 @@
       <c r="F46" t="s">
         <v>224</v>
       </c>
+      <c r="G46" t="s">
+        <v>224</v>
+      </c>
       <c r="H46" t="s">
         <v>66</v>
       </c>
@@ -2838,6 +3253,9 @@
       <c r="F47" t="s">
         <v>224</v>
       </c>
+      <c r="G47" t="s">
+        <v>224</v>
+      </c>
       <c r="H47" t="s">
         <v>66</v>
       </c>
@@ -2867,6 +3285,24 @@
       <c r="A48" t="s">
         <v>77</v>
       </c>
+      <c r="B48" t="s">
+        <v>224</v>
+      </c>
+      <c r="C48" t="s">
+        <v>224</v>
+      </c>
+      <c r="D48" t="s">
+        <v>224</v>
+      </c>
+      <c r="E48" t="s">
+        <v>224</v>
+      </c>
+      <c r="F48" t="s">
+        <v>224</v>
+      </c>
+      <c r="G48" t="s">
+        <v>224</v>
+      </c>
       <c r="H48" t="s">
         <v>66</v>
       </c>
@@ -2911,6 +3347,9 @@
       <c r="F49" t="s">
         <v>224</v>
       </c>
+      <c r="G49" t="s">
+        <v>224</v>
+      </c>
       <c r="H49" t="s">
         <v>66</v>
       </c>
@@ -2955,6 +3394,9 @@
       <c r="F50" t="s">
         <v>224</v>
       </c>
+      <c r="G50" t="s">
+        <v>224</v>
+      </c>
       <c r="H50" t="s">
         <v>10</v>
       </c>
@@ -2999,6 +3441,9 @@
       <c r="F51" t="s">
         <v>224</v>
       </c>
+      <c r="G51" t="s">
+        <v>224</v>
+      </c>
       <c r="H51" t="s">
         <v>10</v>
       </c>
@@ -3043,6 +3488,9 @@
       <c r="F52" t="s">
         <v>224</v>
       </c>
+      <c r="G52" t="s">
+        <v>224</v>
+      </c>
       <c r="H52" t="s">
         <v>10</v>
       </c>
@@ -3087,6 +3535,9 @@
       <c r="F53" t="s">
         <v>224</v>
       </c>
+      <c r="G53" t="s">
+        <v>224</v>
+      </c>
       <c r="H53" t="s">
         <v>10</v>
       </c>
@@ -3131,6 +3582,9 @@
       <c r="F54" t="s">
         <v>224</v>
       </c>
+      <c r="G54" t="s">
+        <v>224</v>
+      </c>
       <c r="H54" t="s">
         <v>10</v>
       </c>
@@ -3175,6 +3629,9 @@
       <c r="F55" t="s">
         <v>224</v>
       </c>
+      <c r="G55" t="s">
+        <v>224</v>
+      </c>
       <c r="H55" t="s">
         <v>10</v>
       </c>
@@ -3219,6 +3676,9 @@
       <c r="F56" t="s">
         <v>224</v>
       </c>
+      <c r="G56" t="s">
+        <v>224</v>
+      </c>
       <c r="H56" t="s">
         <v>10</v>
       </c>
@@ -3263,6 +3723,9 @@
       <c r="F57" t="s">
         <v>224</v>
       </c>
+      <c r="G57" t="s">
+        <v>224</v>
+      </c>
       <c r="H57" t="s">
         <v>10</v>
       </c>
@@ -3307,6 +3770,9 @@
       <c r="F58" t="s">
         <v>224</v>
       </c>
+      <c r="G58" t="s">
+        <v>224</v>
+      </c>
       <c r="H58" t="s">
         <v>10</v>
       </c>
@@ -3351,6 +3817,9 @@
       <c r="F59" t="s">
         <v>224</v>
       </c>
+      <c r="G59" t="s">
+        <v>224</v>
+      </c>
       <c r="H59" t="s">
         <v>10</v>
       </c>
@@ -3395,6 +3864,9 @@
       <c r="F60" t="s">
         <v>224</v>
       </c>
+      <c r="G60" t="s">
+        <v>224</v>
+      </c>
       <c r="H60" t="s">
         <v>10</v>
       </c>
@@ -3439,6 +3911,9 @@
       <c r="F61" t="s">
         <v>224</v>
       </c>
+      <c r="G61" t="s">
+        <v>224</v>
+      </c>
       <c r="H61" t="s">
         <v>10</v>
       </c>
@@ -3483,6 +3958,9 @@
       <c r="F62" t="s">
         <v>224</v>
       </c>
+      <c r="G62" t="s">
+        <v>224</v>
+      </c>
       <c r="H62" t="s">
         <v>10</v>
       </c>
@@ -3527,6 +4005,9 @@
       <c r="F63" t="s">
         <v>224</v>
       </c>
+      <c r="G63" t="s">
+        <v>224</v>
+      </c>
       <c r="H63" t="s">
         <v>50</v>
       </c>
@@ -3571,6 +4052,9 @@
       <c r="F64" t="s">
         <v>224</v>
       </c>
+      <c r="G64" t="s">
+        <v>224</v>
+      </c>
       <c r="H64" t="s">
         <v>50</v>
       </c>
@@ -3615,6 +4099,9 @@
       <c r="F65" t="s">
         <v>224</v>
       </c>
+      <c r="G65" t="s">
+        <v>224</v>
+      </c>
       <c r="H65" t="s">
         <v>50</v>
       </c>
@@ -3659,6 +4146,9 @@
       <c r="F66" t="s">
         <v>224</v>
       </c>
+      <c r="G66" t="s">
+        <v>224</v>
+      </c>
       <c r="H66" t="s">
         <v>50</v>
       </c>
@@ -3703,6 +4193,9 @@
       <c r="F67" t="s">
         <v>224</v>
       </c>
+      <c r="G67" t="s">
+        <v>224</v>
+      </c>
       <c r="H67" t="s">
         <v>50</v>
       </c>
@@ -3747,6 +4240,9 @@
       <c r="F68" t="s">
         <v>224</v>
       </c>
+      <c r="G68" t="s">
+        <v>224</v>
+      </c>
       <c r="H68" t="s">
         <v>24</v>
       </c>
@@ -3791,6 +4287,9 @@
       <c r="F69" t="s">
         <v>224</v>
       </c>
+      <c r="G69" t="s">
+        <v>224</v>
+      </c>
       <c r="H69" t="s">
         <v>24</v>
       </c>
@@ -3835,6 +4334,9 @@
       <c r="F70" t="s">
         <v>224</v>
       </c>
+      <c r="G70" t="s">
+        <v>224</v>
+      </c>
       <c r="H70" t="s">
         <v>24</v>
       </c>
@@ -3879,6 +4381,9 @@
       <c r="F71" t="s">
         <v>224</v>
       </c>
+      <c r="G71" t="s">
+        <v>224</v>
+      </c>
       <c r="H71" t="s">
         <v>24</v>
       </c>
@@ -3923,6 +4428,9 @@
       <c r="F72" t="s">
         <v>224</v>
       </c>
+      <c r="G72" t="s">
+        <v>224</v>
+      </c>
       <c r="H72" t="s">
         <v>24</v>
       </c>
@@ -3967,6 +4475,9 @@
       <c r="F73" t="s">
         <v>224</v>
       </c>
+      <c r="G73" t="s">
+        <v>224</v>
+      </c>
       <c r="H73" t="s">
         <v>107</v>
       </c>
@@ -4011,6 +4522,9 @@
       <c r="F74" t="s">
         <v>224</v>
       </c>
+      <c r="G74" t="s">
+        <v>224</v>
+      </c>
       <c r="H74" t="s">
         <v>107</v>
       </c>
@@ -4055,6 +4569,9 @@
       <c r="F75" t="s">
         <v>224</v>
       </c>
+      <c r="G75" t="s">
+        <v>224</v>
+      </c>
       <c r="H75" t="s">
         <v>107</v>
       </c>
@@ -4099,6 +4616,9 @@
       <c r="F76" t="s">
         <v>224</v>
       </c>
+      <c r="G76" t="s">
+        <v>224</v>
+      </c>
       <c r="H76" t="s">
         <v>107</v>
       </c>
@@ -4143,6 +4663,9 @@
       <c r="F77" t="s">
         <v>224</v>
       </c>
+      <c r="G77" t="s">
+        <v>224</v>
+      </c>
       <c r="H77" t="s">
         <v>107</v>
       </c>
@@ -4187,6 +4710,9 @@
       <c r="F78" t="s">
         <v>224</v>
       </c>
+      <c r="G78" t="s">
+        <v>224</v>
+      </c>
       <c r="H78" t="s">
         <v>66</v>
       </c>
@@ -4231,6 +4757,9 @@
       <c r="F79" t="s">
         <v>224</v>
       </c>
+      <c r="G79" t="s">
+        <v>224</v>
+      </c>
       <c r="H79" t="s">
         <v>66</v>
       </c>
@@ -4275,6 +4804,9 @@
       <c r="F80" t="s">
         <v>224</v>
       </c>
+      <c r="G80" t="s">
+        <v>224</v>
+      </c>
       <c r="H80" t="s">
         <v>66</v>
       </c>
@@ -4319,6 +4851,9 @@
       <c r="F81" t="s">
         <v>224</v>
       </c>
+      <c r="G81" t="s">
+        <v>224</v>
+      </c>
       <c r="H81" t="s">
         <v>66</v>
       </c>
@@ -4363,6 +4898,9 @@
       <c r="F82" t="s">
         <v>224</v>
       </c>
+      <c r="G82" t="s">
+        <v>224</v>
+      </c>
       <c r="H82" t="s">
         <v>66</v>
       </c>
@@ -4407,6 +4945,9 @@
       <c r="F83" t="s">
         <v>224</v>
       </c>
+      <c r="G83" t="s">
+        <v>224</v>
+      </c>
       <c r="H83" t="s">
         <v>24</v>
       </c>
@@ -4451,6 +4992,9 @@
       <c r="F84" t="s">
         <v>224</v>
       </c>
+      <c r="G84" t="s">
+        <v>224</v>
+      </c>
       <c r="H84" t="s">
         <v>24</v>
       </c>
@@ -4495,6 +5039,9 @@
       <c r="F85" t="s">
         <v>224</v>
       </c>
+      <c r="G85" t="s">
+        <v>224</v>
+      </c>
       <c r="H85" t="s">
         <v>24</v>
       </c>
@@ -4539,6 +5086,9 @@
       <c r="F86" t="s">
         <v>224</v>
       </c>
+      <c r="G86" t="s">
+        <v>224</v>
+      </c>
       <c r="H86" t="s">
         <v>24</v>
       </c>
@@ -4583,6 +5133,9 @@
       <c r="F87" t="s">
         <v>224</v>
       </c>
+      <c r="G87" t="s">
+        <v>224</v>
+      </c>
       <c r="H87" t="s">
         <v>66</v>
       </c>
@@ -4627,6 +5180,9 @@
       <c r="F88" t="s">
         <v>224</v>
       </c>
+      <c r="G88" t="s">
+        <v>224</v>
+      </c>
       <c r="H88" t="s">
         <v>24</v>
       </c>
@@ -4671,6 +5227,9 @@
       <c r="F89" t="s">
         <v>224</v>
       </c>
+      <c r="G89" t="s">
+        <v>224</v>
+      </c>
       <c r="H89" t="s">
         <v>124</v>
       </c>
@@ -4715,6 +5274,9 @@
       <c r="F90" t="s">
         <v>224</v>
       </c>
+      <c r="G90" t="s">
+        <v>224</v>
+      </c>
       <c r="H90" t="s">
         <v>124</v>
       </c>
@@ -4759,6 +5321,9 @@
       <c r="F91" t="s">
         <v>224</v>
       </c>
+      <c r="G91" t="s">
+        <v>224</v>
+      </c>
       <c r="H91" t="s">
         <v>124</v>
       </c>
@@ -4803,6 +5368,9 @@
       <c r="F92" t="s">
         <v>224</v>
       </c>
+      <c r="G92" t="s">
+        <v>224</v>
+      </c>
       <c r="H92" t="s">
         <v>124</v>
       </c>
@@ -4845,6 +5413,9 @@
         <v>224</v>
       </c>
       <c r="F93" t="s">
+        <v>224</v>
+      </c>
+      <c r="G93" t="s">
         <v>224</v>
       </c>
       <c r="H93" t="s">
@@ -7815,6 +8386,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -8075,18 +8658,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -8097,6 +8668,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8115,17 +8697,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
   <ds:schemaRefs>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes.sharepoint.com/sites/DeLunaOperaes/Documentos Partilhados/GESTÃO DE FROTA/Automações Frota/Controle de Frota - BID 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02897751-8C48-4E8A-A402-966DADFDAC8D}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ED79F99-47E5-4CCB-A2B8-4BE23D5BFCD3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="226">
   <si>
     <t>Placa</t>
   </si>
@@ -5823,24 +5823,6 @@
       <c r="A102" t="s">
         <v>140</v>
       </c>
-      <c r="B102" t="s">
-        <v>224</v>
-      </c>
-      <c r="C102" t="s">
-        <v>224</v>
-      </c>
-      <c r="D102" t="s">
-        <v>224</v>
-      </c>
-      <c r="E102" t="s">
-        <v>224</v>
-      </c>
-      <c r="F102" t="s">
-        <v>224</v>
-      </c>
-      <c r="G102" t="s">
-        <v>224</v>
-      </c>
       <c r="H102" t="s">
         <v>124</v>
       </c>
@@ -6197,24 +6179,6 @@
       <c r="A110" t="s">
         <v>149</v>
       </c>
-      <c r="B110" t="s">
-        <v>224</v>
-      </c>
-      <c r="C110" t="s">
-        <v>224</v>
-      </c>
-      <c r="D110" t="s">
-        <v>224</v>
-      </c>
-      <c r="E110" t="s">
-        <v>224</v>
-      </c>
-      <c r="F110" t="s">
-        <v>224</v>
-      </c>
-      <c r="G110" t="s">
-        <v>224</v>
-      </c>
       <c r="H110" t="s">
         <v>10</v>
       </c>
@@ -6687,24 +6651,6 @@
       <c r="A121" t="s">
         <v>161</v>
       </c>
-      <c r="B121" t="s">
-        <v>224</v>
-      </c>
-      <c r="C121" t="s">
-        <v>224</v>
-      </c>
-      <c r="D121" t="s">
-        <v>224</v>
-      </c>
-      <c r="E121" t="s">
-        <v>224</v>
-      </c>
-      <c r="F121" t="s">
-        <v>224</v>
-      </c>
-      <c r="G121" t="s">
-        <v>224</v>
-      </c>
       <c r="H121" t="s">
         <v>124</v>
       </c>
@@ -6782,21 +6728,6 @@
       <c r="B123" t="s">
         <v>224</v>
       </c>
-      <c r="C123" t="s">
-        <v>224</v>
-      </c>
-      <c r="D123" t="s">
-        <v>224</v>
-      </c>
-      <c r="E123" t="s">
-        <v>224</v>
-      </c>
-      <c r="F123" t="s">
-        <v>224</v>
-      </c>
-      <c r="G123" t="s">
-        <v>224</v>
-      </c>
       <c r="H123" t="s">
         <v>107</v>
       </c>
@@ -6818,30 +6749,14 @@
       <c r="N123" s="2">
         <v>46280</v>
       </c>
-      <c r="O123" s="2"/>
+      <c r="O123" s="2">
+        <v>46280</v>
+      </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>165</v>
       </c>
-      <c r="B124" t="s">
-        <v>224</v>
-      </c>
-      <c r="C124" t="s">
-        <v>224</v>
-      </c>
-      <c r="D124" t="s">
-        <v>224</v>
-      </c>
-      <c r="E124" t="s">
-        <v>224</v>
-      </c>
-      <c r="F124" t="s">
-        <v>224</v>
-      </c>
-      <c r="G124" t="s">
-        <v>224</v>
-      </c>
       <c r="H124" t="s">
         <v>107</v>
       </c>
@@ -6869,24 +6784,6 @@
       <c r="A125" t="s">
         <v>166</v>
       </c>
-      <c r="B125" t="s">
-        <v>224</v>
-      </c>
-      <c r="C125" t="s">
-        <v>224</v>
-      </c>
-      <c r="D125" t="s">
-        <v>224</v>
-      </c>
-      <c r="E125" t="s">
-        <v>224</v>
-      </c>
-      <c r="F125" t="s">
-        <v>224</v>
-      </c>
-      <c r="G125" t="s">
-        <v>224</v>
-      </c>
       <c r="H125" t="s">
         <v>107</v>
       </c>
@@ -6917,21 +6814,6 @@
       <c r="B126" t="s">
         <v>224</v>
       </c>
-      <c r="C126" t="s">
-        <v>224</v>
-      </c>
-      <c r="D126" t="s">
-        <v>224</v>
-      </c>
-      <c r="E126" t="s">
-        <v>224</v>
-      </c>
-      <c r="F126" t="s">
-        <v>224</v>
-      </c>
-      <c r="G126" t="s">
-        <v>224</v>
-      </c>
       <c r="H126" t="s">
         <v>107</v>
       </c>
@@ -6953,7 +6835,9 @@
       <c r="N126" s="2">
         <v>46280</v>
       </c>
-      <c r="O126" s="2"/>
+      <c r="O126" s="2">
+        <v>46280</v>
+      </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
@@ -7053,24 +6937,6 @@
       <c r="A129" t="s">
         <v>170</v>
       </c>
-      <c r="B129" t="s">
-        <v>224</v>
-      </c>
-      <c r="C129" t="s">
-        <v>224</v>
-      </c>
-      <c r="D129" t="s">
-        <v>224</v>
-      </c>
-      <c r="E129" t="s">
-        <v>224</v>
-      </c>
-      <c r="F129" t="s">
-        <v>224</v>
-      </c>
-      <c r="G129" t="s">
-        <v>224</v>
-      </c>
       <c r="H129" t="s">
         <v>24</v>
       </c>
@@ -7098,24 +6964,6 @@
       <c r="A130" t="s">
         <v>171</v>
       </c>
-      <c r="B130" t="s">
-        <v>224</v>
-      </c>
-      <c r="C130" t="s">
-        <v>224</v>
-      </c>
-      <c r="D130" t="s">
-        <v>224</v>
-      </c>
-      <c r="E130" t="s">
-        <v>224</v>
-      </c>
-      <c r="F130" t="s">
-        <v>224</v>
-      </c>
-      <c r="G130" t="s">
-        <v>224</v>
-      </c>
       <c r="H130" t="s">
         <v>24</v>
       </c>
@@ -7539,24 +7387,6 @@
       <c r="A149" t="s">
         <v>217</v>
       </c>
-      <c r="B149" t="s">
-        <v>224</v>
-      </c>
-      <c r="C149" t="s">
-        <v>224</v>
-      </c>
-      <c r="D149" t="s">
-        <v>224</v>
-      </c>
-      <c r="E149" t="s">
-        <v>224</v>
-      </c>
-      <c r="F149" t="s">
-        <v>224</v>
-      </c>
-      <c r="G149" t="s">
-        <v>224</v>
-      </c>
       <c r="H149" t="s">
         <v>24</v>
       </c>
@@ -8029,24 +7859,6 @@
       <c r="A160" t="s">
         <v>202</v>
       </c>
-      <c r="B160" t="s">
-        <v>224</v>
-      </c>
-      <c r="C160" t="s">
-        <v>224</v>
-      </c>
-      <c r="D160" t="s">
-        <v>224</v>
-      </c>
-      <c r="E160" t="s">
-        <v>224</v>
-      </c>
-      <c r="F160" t="s">
-        <v>224</v>
-      </c>
-      <c r="G160" t="s">
-        <v>224</v>
-      </c>
       <c r="H160" t="s">
         <v>203</v>
       </c>
@@ -8074,24 +7886,6 @@
       <c r="A161" t="s">
         <v>204</v>
       </c>
-      <c r="B161" t="s">
-        <v>224</v>
-      </c>
-      <c r="C161" t="s">
-        <v>224</v>
-      </c>
-      <c r="D161" t="s">
-        <v>224</v>
-      </c>
-      <c r="E161" t="s">
-        <v>224</v>
-      </c>
-      <c r="F161" t="s">
-        <v>224</v>
-      </c>
-      <c r="G161" t="s">
-        <v>224</v>
-      </c>
       <c r="H161" t="s">
         <v>203</v>
       </c>
@@ -8118,24 +7912,6 @@
     <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>205</v>
-      </c>
-      <c r="B162" t="s">
-        <v>224</v>
-      </c>
-      <c r="C162" t="s">
-        <v>224</v>
-      </c>
-      <c r="D162" t="s">
-        <v>224</v>
-      </c>
-      <c r="E162" t="s">
-        <v>224</v>
-      </c>
-      <c r="F162" t="s">
-        <v>224</v>
-      </c>
-      <c r="G162" t="s">
-        <v>224</v>
       </c>
       <c r="H162" t="s">
         <v>203</v>
@@ -8398,6 +8174,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -8658,15 +8443,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
@@ -8679,6 +8455,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8695,12 +8479,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes.sharepoint.com/sites/DeLunaOperaes/Documentos Partilhados/GESTÃO DE FROTA/Automações Frota/Controle de Frota - BID 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ED79F99-47E5-4CCB-A2B8-4BE23D5BFCD3}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E13A7FD-D60D-4D1E-B945-3112BFF78E00}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="226">
   <si>
     <t>Placa</t>
   </si>
@@ -6728,6 +6728,9 @@
       <c r="B123" t="s">
         <v>224</v>
       </c>
+      <c r="G123" t="s">
+        <v>224</v>
+      </c>
       <c r="H123" t="s">
         <v>107</v>
       </c>
@@ -6812,6 +6815,9 @@
         <v>167</v>
       </c>
       <c r="B126" t="s">
+        <v>224</v>
+      </c>
+      <c r="G126" t="s">
         <v>224</v>
       </c>
       <c r="H126" t="s">
@@ -8162,27 +8168,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -8443,26 +8428,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8479,4 +8466,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes.sharepoint.com/sites/DeLunaOperaes/Documentos Partilhados/GESTÃO DE FROTA/Automações Frota/Controle de Frota - BID 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E13A7FD-D60D-4D1E-B945-3112BFF78E00}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6B2DB6-3263-4FCB-AD08-8300BD0B6C7A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="226">
   <si>
     <t>Placa</t>
   </si>
@@ -6760,6 +6760,9 @@
       <c r="A124" t="s">
         <v>165</v>
       </c>
+      <c r="B124" t="s">
+        <v>224</v>
+      </c>
       <c r="H124" t="s">
         <v>107</v>
       </c>
@@ -6781,7 +6784,9 @@
       <c r="N124" s="2">
         <v>46280</v>
       </c>
-      <c r="O124" s="2"/>
+      <c r="O124" s="2">
+        <v>46282</v>
+      </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
@@ -8429,6 +8434,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -8438,15 +8452,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8469,6 +8474,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -8477,12 +8490,4 @@
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes.sharepoint.com/sites/DeLunaOperaes/Documentos Partilhados/GESTÃO DE FROTA/Automações Frota/Controle de Frota - BID 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6B2DB6-3263-4FCB-AD08-8300BD0B6C7A}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{775D1555-62D1-4FF7-8D89-F4856389C7FA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="226">
   <si>
     <t>Placa</t>
   </si>
@@ -6792,6 +6792,12 @@
       <c r="A125" t="s">
         <v>166</v>
       </c>
+      <c r="B125" t="s">
+        <v>224</v>
+      </c>
+      <c r="G125" t="s">
+        <v>224</v>
+      </c>
       <c r="H125" t="s">
         <v>107</v>
       </c>
@@ -6813,7 +6819,9 @@
       <c r="N125" s="2">
         <v>46280</v>
       </c>
-      <c r="O125" s="2"/>
+      <c r="O125" s="2">
+        <v>46282</v>
+      </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
@@ -8173,6 +8181,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -8433,15 +8450,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -8455,6 +8463,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8473,14 +8489,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB8D4A7B-939F-4694-B7C0-6835EBA3E9EA}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7395330A-15F7-4931-89AE-CA4C79DC4C5D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -803,6 +803,8 @@
       <sheetName val="06.10"/>
       <sheetName val="07.10"/>
       <sheetName val="08.10"/>
+      <sheetName val="09.10"/>
+      <sheetName val="13.10"/>
       <sheetName val="LOGISTICS"/>
     </sheetNames>
     <sheetDataSet>
@@ -811,7 +813,9 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7">
         <row r="1">
           <cell r="A1" t="str">
             <v>DISPONIBILIDADE X UTILIZAÇÃO</v>
@@ -842,7 +846,7 @@
             <v>SMG14</v>
           </cell>
           <cell r="C3" t="str">
-            <v>ATIVA</v>
+            <v>SEM DRIVER</v>
           </cell>
           <cell r="D3" t="str">
             <v>LOCALIZA</v>
@@ -893,7 +897,7 @@
             <v>SMG14</v>
           </cell>
           <cell r="C6" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D6" t="str">
             <v>LOCALIZA</v>
@@ -961,7 +965,7 @@
             <v>SRJ8</v>
           </cell>
           <cell r="C10" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D10" t="str">
             <v>LOCALIZA</v>
@@ -1001,7 +1005,7 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E12">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="13">
@@ -1018,7 +1022,7 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E13">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="14">
@@ -1035,7 +1039,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E14">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="15">
@@ -1052,7 +1056,7 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E15">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="16">
@@ -1086,7 +1090,7 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E17">
-            <v>46297</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="18">
@@ -1103,7 +1107,7 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E18">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="19">
@@ -1120,7 +1124,7 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E19">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="20">
@@ -1137,7 +1141,7 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E20">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="21">
@@ -1148,7 +1152,7 @@
             <v>SMG14</v>
           </cell>
           <cell r="C21" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D21" t="str">
             <v>VAMOS</v>
@@ -1171,7 +1175,7 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E22">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="23">
@@ -1188,7 +1192,7 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E23">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="24">
@@ -1205,7 +1209,7 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E24">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="25">
@@ -1222,7 +1226,7 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E25">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="26">
@@ -1256,7 +1260,7 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E27">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="28">
@@ -1273,7 +1277,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E28">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="29">
@@ -1290,7 +1294,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E29">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="30">
@@ -1307,7 +1311,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E30">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="31">
@@ -1341,7 +1345,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E32">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="33">
@@ -1375,7 +1379,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E34">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="35">
@@ -1392,7 +1396,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E35">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="36">
@@ -1409,7 +1413,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E36">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="37">
@@ -1426,7 +1430,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E37">
-            <v>46296</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="38">
@@ -1443,7 +1447,7 @@
             <v>TKS</v>
           </cell>
           <cell r="E38">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="39">
@@ -1471,13 +1475,13 @@
             <v>SRJ10</v>
           </cell>
           <cell r="C40" t="str">
-            <v>SEM DRIVER</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D40" t="str">
             <v>DELUNA</v>
           </cell>
           <cell r="E40">
-            <v>46291</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="41">
@@ -1494,7 +1498,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E41">
-            <v>46298</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="42">
@@ -1505,7 +1509,7 @@
             <v>SRJ10</v>
           </cell>
           <cell r="C42" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D42" t="str">
             <v>LOCALIZA</v>
@@ -1528,7 +1532,7 @@
             <v>TKS</v>
           </cell>
           <cell r="E43">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="44">
@@ -1562,7 +1566,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E45">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="46">
@@ -1579,7 +1583,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E46">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="47">
@@ -1596,7 +1600,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E47">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="48">
@@ -1613,7 +1617,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E48">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="49">
@@ -1624,13 +1628,13 @@
             <v>SRJ10</v>
           </cell>
           <cell r="C49" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D49" t="str">
             <v>DELUNA</v>
           </cell>
           <cell r="E49">
-            <v>46285</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="50">
@@ -1647,7 +1651,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E50">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="51">
@@ -1664,7 +1668,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E51">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="52">
@@ -1681,7 +1685,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E52">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="53">
@@ -1698,7 +1702,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E53">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="54">
@@ -1715,7 +1719,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E54">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="55">
@@ -1732,7 +1736,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E55">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="56">
@@ -1800,7 +1804,7 @@
             <v>TKS</v>
           </cell>
           <cell r="E59">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="60">
@@ -1811,7 +1815,7 @@
             <v>SRJ10</v>
           </cell>
           <cell r="C60" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>SEM DRIVER</v>
           </cell>
           <cell r="D60" t="str">
             <v>TKS</v>
@@ -1834,7 +1838,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E61">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="62">
@@ -1868,7 +1872,7 @@
             <v>TKS</v>
           </cell>
           <cell r="E63">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="64">
@@ -1885,7 +1889,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E64">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="65">
@@ -1919,7 +1923,7 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E66">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="67">
@@ -1970,7 +1974,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E69">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="70">
@@ -1987,7 +1991,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E70">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="71">
@@ -2038,7 +2042,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E73">
-            <v>46165</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="74">
@@ -2072,7 +2076,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E75">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="76">
@@ -2089,7 +2093,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E76">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="77">
@@ -2106,7 +2110,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E77">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="78">
@@ -2123,7 +2127,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E78">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="79">
@@ -2157,7 +2161,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E80">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="81">
@@ -2174,7 +2178,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E81">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="82">
@@ -2191,7 +2195,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E82">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="83">
@@ -2242,7 +2246,7 @@
             <v>EVM</v>
           </cell>
           <cell r="E85">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="86">
@@ -2276,7 +2280,7 @@
             <v>EVM</v>
           </cell>
           <cell r="E87">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="88">
@@ -2287,13 +2291,13 @@
             <v>SES1</v>
           </cell>
           <cell r="C88" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D88" t="str">
             <v>TKS</v>
           </cell>
           <cell r="E88">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="89">
@@ -2310,7 +2314,7 @@
             <v>TKS</v>
           </cell>
           <cell r="E89">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="90">
@@ -2327,7 +2331,7 @@
             <v>TKS</v>
           </cell>
           <cell r="E90">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="91">
@@ -2344,7 +2348,7 @@
             <v>TKS</v>
           </cell>
           <cell r="E91">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="92">
@@ -2378,7 +2382,7 @@
             <v>TKS</v>
           </cell>
           <cell r="E93">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="94">
@@ -2395,7 +2399,7 @@
             <v>TKS</v>
           </cell>
           <cell r="E94">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="95">
@@ -2412,7 +2416,7 @@
             <v>TKS</v>
           </cell>
           <cell r="E95">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="96">
@@ -2429,7 +2433,7 @@
             <v>TKS</v>
           </cell>
           <cell r="E96">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="97">
@@ -2446,7 +2450,7 @@
             <v>TKS</v>
           </cell>
           <cell r="E97">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="98">
@@ -2497,7 +2501,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E100">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="101">
@@ -2514,7 +2518,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E101">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="102">
@@ -2531,7 +2535,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E102">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="103">
@@ -2548,7 +2552,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E103">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="104">
@@ -2565,7 +2569,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E104">
-            <v>46288</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="105">
@@ -2576,13 +2580,13 @@
             <v>SMG14</v>
           </cell>
           <cell r="C105" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D105" t="str">
             <v>ARVAL</v>
           </cell>
           <cell r="E105">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="106">
@@ -2599,7 +2603,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E106">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="107">
@@ -2616,7 +2620,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E107">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="108">
@@ -2650,7 +2654,7 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E109">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="110">
@@ -2667,29 +2671,29 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E110">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111" t="str">
-            <v>UAB4J92</v>
+            <v>TBK4I32</v>
           </cell>
           <cell r="B111" t="str">
-            <v>SMG14</v>
+            <v>SMG3</v>
           </cell>
           <cell r="C111" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D111" t="str">
-            <v>LOCALIZA</v>
+            <v>ARVAL</v>
           </cell>
           <cell r="E111">
-            <v>46185</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112" t="str">
-            <v>TBK4I32</v>
+            <v>TBK9C75</v>
           </cell>
           <cell r="B112" t="str">
             <v>SMG3</v>
@@ -2701,12 +2705,12 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E112">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113" t="str">
-            <v>TBK9C75</v>
+            <v>TBK9C77</v>
           </cell>
           <cell r="B113" t="str">
             <v>SMG3</v>
@@ -2718,12 +2722,12 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E113">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114" t="str">
-            <v>TBK9C77</v>
+            <v>TBK9C84</v>
           </cell>
           <cell r="B114" t="str">
             <v>SMG3</v>
@@ -2735,12 +2739,12 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E114">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115" t="str">
-            <v>TBK9C84</v>
+            <v>TBK9D02</v>
           </cell>
           <cell r="B115" t="str">
             <v>SMG3</v>
@@ -2752,12 +2756,12 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E115">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116" t="str">
-            <v>TBK9D02</v>
+            <v>TBK9D22</v>
           </cell>
           <cell r="B116" t="str">
             <v>SMG3</v>
@@ -2769,12 +2773,12 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E116">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117" t="str">
-            <v>TBK9D22</v>
+            <v>TBK9D72</v>
           </cell>
           <cell r="B117" t="str">
             <v>SMG3</v>
@@ -2786,12 +2790,12 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E117">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118" t="str">
-            <v>TBK9D72</v>
+            <v>TBK9E06</v>
           </cell>
           <cell r="B118" t="str">
             <v>SMG3</v>
@@ -2803,12 +2807,12 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E118">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119" t="str">
-            <v>TBK9E06</v>
+            <v>TBK9F06</v>
           </cell>
           <cell r="B119" t="str">
             <v>SMG3</v>
@@ -2820,12 +2824,12 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E119">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120" t="str">
-            <v>TBK9F06</v>
+            <v>TBK9F08</v>
           </cell>
           <cell r="B120" t="str">
             <v>SMG3</v>
@@ -2837,12 +2841,12 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E120">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121" t="str">
-            <v>TBK9F08</v>
+            <v>TBK9F24</v>
           </cell>
           <cell r="B121" t="str">
             <v>SMG3</v>
@@ -2854,46 +2858,46 @@
             <v>ARVAL</v>
           </cell>
           <cell r="E121">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122" t="str">
-            <v>TBK9F24</v>
+            <v>TBK9F49</v>
           </cell>
           <cell r="B122" t="str">
             <v>SMG3</v>
           </cell>
           <cell r="C122" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D122" t="str">
             <v>ARVAL</v>
           </cell>
           <cell r="E122">
-            <v>46302</v>
+            <v>46298</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123" t="str">
-            <v>TBK9F49</v>
+            <v>UAW8I45</v>
           </cell>
           <cell r="B123" t="str">
             <v>SMG3</v>
           </cell>
           <cell r="C123" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D123" t="str">
-            <v>ARVAL</v>
+            <v>TKS</v>
           </cell>
           <cell r="E123">
-            <v>46298</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124" t="str">
-            <v>UAW8I45</v>
+            <v>UAW8I48</v>
           </cell>
           <cell r="B124" t="str">
             <v>SMG3</v>
@@ -2905,12 +2909,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E124">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125" t="str">
-            <v>UAW8I48</v>
+            <v>UAW8I53</v>
           </cell>
           <cell r="B125" t="str">
             <v>SMG3</v>
@@ -2927,7 +2931,7 @@
         </row>
         <row r="126">
           <cell r="A126" t="str">
-            <v>UAW8I53</v>
+            <v>UAW8I56</v>
           </cell>
           <cell r="B126" t="str">
             <v>SMG3</v>
@@ -2939,12 +2943,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E126">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127" t="str">
-            <v>UAW8I56</v>
+            <v>UAX2B53</v>
           </cell>
           <cell r="B127" t="str">
             <v>SMG3</v>
@@ -2956,12 +2960,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E127">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128" t="str">
-            <v>UAX2B53</v>
+            <v>TEE1H79</v>
           </cell>
           <cell r="B128" t="str">
             <v>SMG3</v>
@@ -2970,15 +2974,15 @@
             <v>ATIVA</v>
           </cell>
           <cell r="D128" t="str">
-            <v>TKS</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E128">
-            <v>46302</v>
+            <v>46301</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129" t="str">
-            <v>TEE1H79</v>
+            <v>TEI0H81</v>
           </cell>
           <cell r="B129" t="str">
             <v>SMG3</v>
@@ -2990,46 +2994,46 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E129">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130" t="str">
-            <v>TEI0H81</v>
+            <v>TEI0I01</v>
           </cell>
           <cell r="B130" t="str">
             <v>SMG3</v>
           </cell>
           <cell r="C130" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D130" t="str">
             <v>VAMOS</v>
           </cell>
           <cell r="E130">
-            <v>46294</v>
+            <v>46302</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131" t="str">
-            <v>TEI0I01</v>
+            <v>TEO9D70</v>
           </cell>
           <cell r="B131" t="str">
             <v>SMG3</v>
           </cell>
           <cell r="C131" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D131" t="str">
             <v>VAMOS</v>
           </cell>
           <cell r="E131">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132" t="str">
-            <v>TEO9D70</v>
+            <v>TEQ4C51</v>
           </cell>
           <cell r="B132" t="str">
             <v>SMG3</v>
@@ -3041,63 +3045,63 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E132">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133" t="str">
-            <v>TEQ4C51</v>
+            <v>TEV9A36</v>
           </cell>
           <cell r="B133" t="str">
             <v>SMG3</v>
           </cell>
           <cell r="C133" t="str">
-            <v>ATIVA</v>
+            <v>SEM DRIVER</v>
           </cell>
           <cell r="D133" t="str">
             <v>VAMOS</v>
           </cell>
           <cell r="E133">
-            <v>46302</v>
+            <v>46295</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134" t="str">
-            <v>TEV9A36</v>
+            <v>TEV9A41</v>
           </cell>
           <cell r="B134" t="str">
             <v>SMG3</v>
           </cell>
           <cell r="C134" t="str">
-            <v>SEM DRIVER</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D134" t="str">
             <v>VAMOS</v>
           </cell>
           <cell r="E134">
-            <v>46295</v>
+            <v>46262</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135" t="str">
-            <v>TEV9A41</v>
+            <v>TEV9A99</v>
           </cell>
           <cell r="B135" t="str">
             <v>SMG3</v>
           </cell>
           <cell r="C135" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D135" t="str">
             <v>VAMOS</v>
           </cell>
           <cell r="E135">
-            <v>46262</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136" t="str">
-            <v>TEV9A99</v>
+            <v>TEW5I45</v>
           </cell>
           <cell r="B136" t="str">
             <v>SMG3</v>
@@ -3109,12 +3113,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E136">
-            <v>46302</v>
+            <v>46301</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137" t="str">
-            <v>TEW5I45</v>
+            <v>TEW5I46</v>
           </cell>
           <cell r="B137" t="str">
             <v>SMG3</v>
@@ -3126,12 +3130,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E137">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138" t="str">
-            <v>TEW5I46</v>
+            <v>TEW5I96</v>
           </cell>
           <cell r="B138" t="str">
             <v>SMG3</v>
@@ -3143,12 +3147,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E138">
-            <v>46301</v>
+            <v>46299</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139" t="str">
-            <v>TEW5I96</v>
+            <v>TEW5I97</v>
           </cell>
           <cell r="B139" t="str">
             <v>SMG3</v>
@@ -3160,12 +3164,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E139">
-            <v>46299</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140" t="str">
-            <v>TEW5I97</v>
+            <v>TEY7J32</v>
           </cell>
           <cell r="B140" t="str">
             <v>SMG3</v>
@@ -3182,58 +3186,58 @@
         </row>
         <row r="141">
           <cell r="A141" t="str">
-            <v>TEY7J32</v>
+            <v>TEY7J34</v>
           </cell>
           <cell r="B141" t="str">
             <v>SMG3</v>
           </cell>
           <cell r="C141" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D141" t="str">
             <v>VAMOS</v>
           </cell>
           <cell r="E141">
-            <v>46302</v>
+            <v>46244</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142" t="str">
-            <v>TEY7J34</v>
+            <v>TEY7J41</v>
           </cell>
           <cell r="B142" t="str">
             <v>SMG3</v>
           </cell>
           <cell r="C142" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D142" t="str">
             <v>VAMOS</v>
           </cell>
           <cell r="E142">
-            <v>46244</v>
+            <v>46260</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143" t="str">
-            <v>TEY7J41</v>
+            <v>TOL2C54</v>
           </cell>
           <cell r="B143" t="str">
-            <v>SMG3</v>
+            <v>SRJ1</v>
           </cell>
           <cell r="C143" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D143" t="str">
-            <v>VAMOS</v>
+            <v>PRALOG</v>
           </cell>
           <cell r="E143">
-            <v>46260</v>
+            <v>46298</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144" t="str">
-            <v>TOL2C54</v>
+            <v>TBR2C79</v>
           </cell>
           <cell r="B144" t="str">
             <v>SRJ1</v>
@@ -3242,15 +3246,15 @@
             <v>ATIVA</v>
           </cell>
           <cell r="D144" t="str">
-            <v>PRALOG</v>
+            <v>TKS</v>
           </cell>
           <cell r="E144">
-            <v>46298</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145" t="str">
-            <v>TBR2C79</v>
+            <v>TBR2C83</v>
           </cell>
           <cell r="B145" t="str">
             <v>SRJ1</v>
@@ -3262,12 +3266,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E145">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146" t="str">
-            <v>TBR2C83</v>
+            <v>TBR2C94</v>
           </cell>
           <cell r="B146" t="str">
             <v>SRJ1</v>
@@ -3279,12 +3283,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E146">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147" t="str">
-            <v>TBR2C94</v>
+            <v>TBR2C95</v>
           </cell>
           <cell r="B147" t="str">
             <v>SRJ1</v>
@@ -3301,24 +3305,24 @@
         </row>
         <row r="148">
           <cell r="A148" t="str">
-            <v>TBR2C95</v>
+            <v>TBR4A71</v>
           </cell>
           <cell r="B148" t="str">
             <v>SRJ1</v>
           </cell>
           <cell r="C148" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D148" t="str">
             <v>TKS</v>
           </cell>
           <cell r="E148">
-            <v>46302</v>
+            <v>46240</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149" t="str">
-            <v>TBR4A71</v>
+            <v>TBR4B05</v>
           </cell>
           <cell r="B149" t="str">
             <v>SRJ1</v>
@@ -3330,46 +3334,46 @@
             <v>TKS</v>
           </cell>
           <cell r="E149">
-            <v>46240</v>
+            <v>46298</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150" t="str">
-            <v>TBR4B05</v>
+            <v>TBR6F25</v>
           </cell>
           <cell r="B150" t="str">
             <v>SRJ1</v>
           </cell>
           <cell r="C150" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D150" t="str">
             <v>TKS</v>
           </cell>
           <cell r="E150">
-            <v>46298</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151" t="str">
-            <v>TBR6F25</v>
+            <v>TBR8I51</v>
           </cell>
           <cell r="B151" t="str">
             <v>SRJ1</v>
           </cell>
           <cell r="C151" t="str">
-            <v>ATIVA</v>
+            <v>SEM DRIVER</v>
           </cell>
           <cell r="D151" t="str">
             <v>TKS</v>
           </cell>
           <cell r="E151">
-            <v>46302</v>
+            <v>46295</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152" t="str">
-            <v>TBR8I51</v>
+            <v>TBW6I39</v>
           </cell>
           <cell r="B152" t="str">
             <v>SRJ1</v>
@@ -3381,46 +3385,46 @@
             <v>TKS</v>
           </cell>
           <cell r="E152">
-            <v>46295</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153" t="str">
-            <v>TBW6I39</v>
+            <v>TBW6I43</v>
           </cell>
           <cell r="B153" t="str">
             <v>SRJ1</v>
           </cell>
           <cell r="C153" t="str">
-            <v>SEM DRIVER</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D153" t="str">
             <v>TKS</v>
           </cell>
           <cell r="E153">
-            <v>46298</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154" t="str">
-            <v>TBW6I43</v>
+            <v>TDC0E08</v>
           </cell>
           <cell r="B154" t="str">
-            <v>SRJ1</v>
+            <v>SRJ5</v>
           </cell>
           <cell r="C154" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D154" t="str">
-            <v>TKS</v>
+            <v>UNIDAS</v>
           </cell>
           <cell r="E154">
-            <v>46302</v>
+            <v>46211</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155" t="str">
-            <v>TDC0E08</v>
+            <v>TXJ6H46</v>
           </cell>
           <cell r="B155" t="str">
             <v>SRJ5</v>
@@ -3432,29 +3436,29 @@
             <v>UNIDAS</v>
           </cell>
           <cell r="E155">
-            <v>46211</v>
+            <v>46231</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156" t="str">
-            <v>TXJ6H46</v>
+            <v>TTU1G18</v>
           </cell>
           <cell r="B156" t="str">
-            <v>SRJ5</v>
+            <v>SRJ10</v>
           </cell>
           <cell r="C156" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D156" t="str">
-            <v>UNIDAS</v>
+            <v>DELUNA</v>
           </cell>
           <cell r="E156">
-            <v>46231</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157" t="str">
-            <v>TTU1G18</v>
+            <v>TUI1F41</v>
           </cell>
           <cell r="B157" t="str">
             <v>SRJ10</v>
@@ -3466,12 +3470,12 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E157">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158" t="str">
-            <v>TUI1F41</v>
+            <v>SRT1J76</v>
           </cell>
           <cell r="B158" t="str">
             <v>SRJ10</v>
@@ -3483,12 +3487,12 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E158">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159" t="str">
-            <v>SRT1J76</v>
+            <v>TBX1D75</v>
           </cell>
           <cell r="B159" t="str">
             <v>SRJ10</v>
@@ -3497,15 +3501,15 @@
             <v>ATIVA</v>
           </cell>
           <cell r="D159" t="str">
-            <v>DELUNA</v>
+            <v>TKS</v>
           </cell>
           <cell r="E159">
-            <v>46288</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160" t="str">
-            <v>TBX1D75</v>
+            <v>TBX1F43</v>
           </cell>
           <cell r="B160" t="str">
             <v>SRJ10</v>
@@ -3517,12 +3521,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E160">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161" t="str">
-            <v>TBX1F43</v>
+            <v>TBX2A34</v>
           </cell>
           <cell r="B161" t="str">
             <v>SRJ10</v>
@@ -3534,12 +3538,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E161">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162" t="str">
-            <v>TBX2A34</v>
+            <v>TBX2A37</v>
           </cell>
           <cell r="B162" t="str">
             <v>SRJ10</v>
@@ -3551,12 +3555,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E162">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163" t="str">
-            <v>TBX2A37</v>
+            <v>TBX2A46</v>
           </cell>
           <cell r="B163" t="str">
             <v>SRJ10</v>
@@ -3568,12 +3572,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E163">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164" t="str">
-            <v>TBX2A46</v>
+            <v>TBX2A66</v>
           </cell>
           <cell r="B164" t="str">
             <v>SRJ10</v>
@@ -3585,12 +3589,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E164">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165" t="str">
-            <v>TBX2A66</v>
+            <v>TBX2A81</v>
           </cell>
           <cell r="B165" t="str">
             <v>SRJ10</v>
@@ -3602,12 +3606,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E165">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166" t="str">
-            <v>TBX2A81</v>
+            <v>TBX2A84</v>
           </cell>
           <cell r="B166" t="str">
             <v>SRJ10</v>
@@ -3619,12 +3623,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E166">
-            <v>46299</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167" t="str">
-            <v>TBX2A84</v>
+            <v>TBX2B71</v>
           </cell>
           <cell r="B167" t="str">
             <v>SRJ10</v>
@@ -3636,12 +3640,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E167">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168" t="str">
-            <v>TBX2B71</v>
+            <v>TBX2E39</v>
           </cell>
           <cell r="B168" t="str">
             <v>SRJ10</v>
@@ -3653,12 +3657,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E168">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169" t="str">
-            <v>TBX2E39</v>
+            <v>TBX8H67</v>
           </cell>
           <cell r="B169" t="str">
             <v>SRJ10</v>
@@ -3670,12 +3674,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E169">
-            <v>46302</v>
+            <v>46301</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170" t="str">
-            <v>TBX8H67</v>
+            <v>TBY2F62</v>
           </cell>
           <cell r="B170" t="str">
             <v>SRJ10</v>
@@ -3687,15 +3691,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E170">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171" t="str">
-            <v>TBY2F62</v>
+            <v>TBR2C82</v>
           </cell>
           <cell r="B171" t="str">
-            <v>SRJ10</v>
+            <v>SRJ13</v>
           </cell>
           <cell r="C171" t="str">
             <v>ATIVA</v>
@@ -3704,15 +3708,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E171">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172" t="str">
-            <v>TBR2C82</v>
+            <v>TBR2C93</v>
           </cell>
           <cell r="B172" t="str">
-            <v>SRJ13</v>
+            <v>SRJ15</v>
           </cell>
           <cell r="C172" t="str">
             <v>ATIVA</v>
@@ -3721,15 +3725,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E172">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173" t="str">
-            <v>TBR2C93</v>
+            <v>TBR8I01</v>
           </cell>
           <cell r="B173" t="str">
-            <v>SRJ15</v>
+            <v>SRJ13</v>
           </cell>
           <cell r="C173" t="str">
             <v>ATIVA</v>
@@ -3738,15 +3742,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E173">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174" t="str">
-            <v>TBR8I01</v>
+            <v>TBW6F03</v>
           </cell>
           <cell r="B174" t="str">
-            <v>SRJ13</v>
+            <v>SRJ15</v>
           </cell>
           <cell r="C174" t="str">
             <v>ATIVA</v>
@@ -3755,15 +3759,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E174">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175" t="str">
-            <v>TBW6F03</v>
+            <v>TBW6I38</v>
           </cell>
           <cell r="B175" t="str">
-            <v>SRJ15</v>
+            <v>SRJ13</v>
           </cell>
           <cell r="C175" t="str">
             <v>ATIVA</v>
@@ -3772,15 +3776,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E175">
-            <v>46299</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176" t="str">
-            <v>TBW6I38</v>
+            <v>TBW6I45</v>
           </cell>
           <cell r="B176" t="str">
-            <v>SRJ13</v>
+            <v>SRJ15</v>
           </cell>
           <cell r="C176" t="str">
             <v>ATIVA</v>
@@ -3789,12 +3793,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E176">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177" t="str">
-            <v>TBW6I45</v>
+            <v>TBW6I61</v>
           </cell>
           <cell r="B177" t="str">
             <v>SRJ15</v>
@@ -3806,15 +3810,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E177">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178" t="str">
-            <v>TBW6I61</v>
+            <v>TBW6I90</v>
           </cell>
           <cell r="B178" t="str">
-            <v>SRJ15</v>
+            <v>SRJ13</v>
           </cell>
           <cell r="C178" t="str">
             <v>ATIVA</v>
@@ -3828,41 +3832,41 @@
         </row>
         <row r="179">
           <cell r="A179" t="str">
-            <v>TBW6I90</v>
+            <v>TXT4F98</v>
           </cell>
           <cell r="B179" t="str">
-            <v>SRJ13</v>
+            <v>SRJ8</v>
           </cell>
           <cell r="C179" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D179" t="str">
-            <v>TKS</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E179">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180" t="str">
-            <v>TXT4F98</v>
+            <v>TBW6I46</v>
           </cell>
           <cell r="B180" t="str">
-            <v>SRJ8</v>
+            <v>SRJ6</v>
           </cell>
           <cell r="C180" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D180" t="str">
-            <v>VAMOS</v>
+            <v>TKS</v>
           </cell>
           <cell r="E180">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181" t="str">
-            <v>TBW6I46</v>
+            <v>TBW6I74</v>
           </cell>
           <cell r="B181" t="str">
             <v>SRJ6</v>
@@ -3874,12 +3878,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E181">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182" t="str">
-            <v>TBW6I74</v>
+            <v>TBW6I79</v>
           </cell>
           <cell r="B182" t="str">
             <v>SRJ6</v>
@@ -3891,29 +3895,29 @@
             <v>TKS</v>
           </cell>
           <cell r="E182">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183" t="str">
-            <v>TBW6I79</v>
+            <v>TWY6H59</v>
           </cell>
           <cell r="B183" t="str">
-            <v>SRJ6</v>
+            <v>SRJ7</v>
           </cell>
           <cell r="C183" t="str">
-            <v>ATIVA</v>
+            <v>TROCAR PLACA</v>
           </cell>
           <cell r="D183" t="str">
-            <v>TKS</v>
+            <v>LOCALIZA/PORTAL</v>
           </cell>
           <cell r="E183">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184" t="str">
-            <v>TWY6H59</v>
+            <v>TXQ7J27</v>
           </cell>
           <cell r="B184" t="str">
             <v>SRJ7</v>
@@ -3925,32 +3929,32 @@
             <v>LOCALIZA/PORTAL</v>
           </cell>
           <cell r="E184">
-            <v>46302</v>
+            <v>46249</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185" t="str">
-            <v>TXQ7J27</v>
+            <v>TBK7B84</v>
           </cell>
           <cell r="B185" t="str">
-            <v>SRJ7</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C185" t="str">
-            <v>TROCAR PLACA</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D185" t="str">
-            <v>LOCALIZA/PORTAL</v>
+            <v>TKS</v>
           </cell>
           <cell r="E185">
-            <v>46249</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186" t="str">
-            <v>TBK7B84</v>
+            <v>TBK9F96</v>
           </cell>
           <cell r="B186" t="str">
-            <v>SRJ4</v>
+            <v>SRJ7</v>
           </cell>
           <cell r="C186" t="str">
             <v>ATIVA</v>
@@ -3959,12 +3963,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E186">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187" t="str">
-            <v>TBK9F96</v>
+            <v>TBK9G06</v>
           </cell>
           <cell r="B187" t="str">
             <v>SRJ7</v>
@@ -3976,15 +3980,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E187">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188" t="str">
-            <v>TBK9G06</v>
+            <v>TBX1B61</v>
           </cell>
           <cell r="B188" t="str">
-            <v>SRJ7</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C188" t="str">
             <v>ATIVA</v>
@@ -3993,32 +3997,32 @@
             <v>TKS</v>
           </cell>
           <cell r="E188">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189" t="str">
-            <v>TBX1B61</v>
+            <v>TBX1D60</v>
           </cell>
           <cell r="B189" t="str">
             <v>SRJ4</v>
           </cell>
           <cell r="C189" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D189" t="str">
             <v>TKS</v>
           </cell>
           <cell r="E189">
-            <v>46301</v>
+            <v>46298</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190" t="str">
-            <v>TBX1D60</v>
+            <v>TBX1F44</v>
           </cell>
           <cell r="B190" t="str">
-            <v>SRJ4</v>
+            <v>SRJ7</v>
           </cell>
           <cell r="C190" t="str">
             <v>MANUTENÇÃO</v>
@@ -4027,12 +4031,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E190">
-            <v>46298</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191" t="str">
-            <v>TBX1F44</v>
+            <v>TBX8I41</v>
           </cell>
           <cell r="B191" t="str">
             <v>SRJ7</v>
@@ -4044,15 +4048,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E191">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192" t="str">
-            <v>TBX8I41</v>
+            <v>TBX9E32</v>
           </cell>
           <cell r="B192" t="str">
-            <v>SRJ7</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C192" t="str">
             <v>ATIVA</v>
@@ -4061,12 +4065,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E192">
-            <v>46302</v>
+            <v>46300</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193" t="str">
-            <v>TBX9E32</v>
+            <v>TBZ7G02</v>
           </cell>
           <cell r="B193" t="str">
             <v>SRJ4</v>
@@ -4078,15 +4082,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E193">
-            <v>46300</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194" t="str">
-            <v>TBZ7G02</v>
+            <v>TBZ7G44</v>
           </cell>
           <cell r="B194" t="str">
-            <v>SRJ4</v>
+            <v>SRJ7</v>
           </cell>
           <cell r="C194" t="str">
             <v>ATIVA</v>
@@ -4095,15 +4099,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E194">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195" t="str">
-            <v>TBZ7G44</v>
+            <v>TBZ7H39</v>
           </cell>
           <cell r="B195" t="str">
-            <v>SRJ7</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C195" t="str">
             <v>ATIVA</v>
@@ -4112,46 +4116,46 @@
             <v>TKS</v>
           </cell>
           <cell r="E195">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196" t="str">
-            <v>TBZ7H39</v>
+            <v>TBF2C82</v>
           </cell>
           <cell r="B196" t="str">
-            <v>SRJ4</v>
+            <v>SRJ8</v>
           </cell>
           <cell r="C196" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D196" t="str">
             <v>TKS</v>
           </cell>
           <cell r="E196">
-            <v>46302</v>
+            <v>46292</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197" t="str">
-            <v>TBF2C82</v>
+            <v>TBF2D60</v>
           </cell>
           <cell r="B197" t="str">
             <v>SRJ8</v>
           </cell>
           <cell r="C197" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D197" t="str">
             <v>TKS</v>
           </cell>
           <cell r="E197">
-            <v>46292</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198" t="str">
-            <v>TBF2D60</v>
+            <v>TBJ9G10</v>
           </cell>
           <cell r="B198" t="str">
             <v>SRJ8</v>
@@ -4163,12 +4167,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E198">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199" t="str">
-            <v>TBJ9G10</v>
+            <v>TBS8E55</v>
           </cell>
           <cell r="B199" t="str">
             <v>SRJ8</v>
@@ -4180,12 +4184,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E199">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200" t="str">
-            <v>TBS8E55</v>
+            <v>TBS8E61</v>
           </cell>
           <cell r="B200" t="str">
             <v>SRJ8</v>
@@ -4197,12 +4201,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E200">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201" t="str">
-            <v>TBS8E61</v>
+            <v>TBS8E64</v>
           </cell>
           <cell r="B201" t="str">
             <v>SRJ8</v>
@@ -4214,12 +4218,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E201">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202" t="str">
-            <v>TBS8E64</v>
+            <v>TBS8E80</v>
           </cell>
           <cell r="B202" t="str">
             <v>SRJ8</v>
@@ -4231,12 +4235,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E202">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203" t="str">
-            <v>TBS8E80</v>
+            <v>TBS8E98</v>
           </cell>
           <cell r="B203" t="str">
             <v>SRJ8</v>
@@ -4248,12 +4252,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E203">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204" t="str">
-            <v>TBS8E98</v>
+            <v>TBS8E99</v>
           </cell>
           <cell r="B204" t="str">
             <v>SRJ8</v>
@@ -4265,12 +4269,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E204">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205" t="str">
-            <v>TBS8E99</v>
+            <v>TBX1B64</v>
           </cell>
           <cell r="B205" t="str">
             <v>SRJ8</v>
@@ -4282,12 +4286,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E205">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206" t="str">
-            <v>TBX1B64</v>
+            <v>TBX2B93</v>
           </cell>
           <cell r="B206" t="str">
             <v>SRJ8</v>
@@ -4299,12 +4303,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E206">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207" t="str">
-            <v>TBX2B93</v>
+            <v>TBX8C60</v>
           </cell>
           <cell r="B207" t="str">
             <v>SRJ8</v>
@@ -4316,12 +4320,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E207">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208" t="str">
-            <v>TBX8C60</v>
+            <v>TBX8E15</v>
           </cell>
           <cell r="B208" t="str">
             <v>SRJ8</v>
@@ -4333,12 +4337,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E208">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209" t="str">
-            <v>TBX8E15</v>
+            <v>TBX8I51</v>
           </cell>
           <cell r="B209" t="str">
             <v>SRJ8</v>
@@ -4350,12 +4354,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E209">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210" t="str">
-            <v>TBX8I51</v>
+            <v>TBX8I52</v>
           </cell>
           <cell r="B210" t="str">
             <v>SRJ8</v>
@@ -4367,12 +4371,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E210">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211" t="str">
-            <v>TBX8I52</v>
+            <v>TBX8I56</v>
           </cell>
           <cell r="B211" t="str">
             <v>SRJ8</v>
@@ -4384,12 +4388,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E211">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212" t="str">
-            <v>TBX8I56</v>
+            <v>TBZ8F73</v>
           </cell>
           <cell r="B212" t="str">
             <v>SRJ8</v>
@@ -4401,15 +4405,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E212">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213" t="str">
-            <v>TBZ8F73</v>
+            <v>UAS8F84</v>
           </cell>
           <cell r="B213" t="str">
-            <v>SRJ8</v>
+            <v>SES1</v>
           </cell>
           <cell r="C213" t="str">
             <v>ATIVA</v>
@@ -4418,12 +4422,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E213">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214" t="str">
-            <v>UAS8F84</v>
+            <v>UAT5H20</v>
           </cell>
           <cell r="B214" t="str">
             <v>SES1</v>
@@ -4435,12 +4439,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E214">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215" t="str">
-            <v>UAT5H20</v>
+            <v>UAT5H31</v>
           </cell>
           <cell r="B215" t="str">
             <v>SES1</v>
@@ -4452,12 +4456,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E215">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216" t="str">
-            <v>UAT5H31</v>
+            <v>TUE6J97</v>
           </cell>
           <cell r="B216" t="str">
             <v>SES1</v>
@@ -4466,106 +4470,106 @@
             <v>ATIVA</v>
           </cell>
           <cell r="D216" t="str">
-            <v>TKS</v>
+            <v>DELUNA</v>
           </cell>
           <cell r="E216">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217" t="str">
-            <v>TEP3E52</v>
+            <v>TUF6J97</v>
           </cell>
           <cell r="B217" t="str">
-            <v>SMG14</v>
+            <v>SES1</v>
           </cell>
           <cell r="C217" t="str">
-            <v>ATIVA</v>
+            <v>SEM DRIVER</v>
           </cell>
           <cell r="D217" t="str">
-            <v>LOCALIZA</v>
+            <v>DELUNA</v>
           </cell>
           <cell r="E217">
-            <v>46279</v>
+            <v>46302</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218" t="str">
-            <v>TUE6J97</v>
+            <v>TUF6J98</v>
           </cell>
           <cell r="B218" t="str">
             <v>SES1</v>
           </cell>
           <cell r="C218" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D218" t="str">
             <v>DELUNA</v>
           </cell>
           <cell r="E218">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219" t="str">
-            <v>TUF6J97</v>
+            <v>TUF6J99</v>
           </cell>
           <cell r="B219" t="str">
             <v>SES1</v>
           </cell>
           <cell r="C219" t="str">
-            <v>SEM DRIVER</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D219" t="str">
             <v>DELUNA</v>
           </cell>
           <cell r="E219">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220" t="str">
-            <v>TUF6J98</v>
+            <v>TZN9E53</v>
           </cell>
           <cell r="B220" t="str">
-            <v>SES1</v>
+            <v>SES2</v>
           </cell>
           <cell r="C220" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D220" t="str">
-            <v>DELUNA</v>
+            <v>LOCALIZA</v>
           </cell>
           <cell r="E220">
-            <v>46296</v>
+            <v>46300</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221" t="str">
-            <v>TUF6J99</v>
+            <v>TZN9E54</v>
           </cell>
           <cell r="B221" t="str">
-            <v>SES1</v>
+            <v>SES2</v>
           </cell>
           <cell r="C221" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D221" t="str">
-            <v>DELUNA</v>
+            <v>LOCALIZA</v>
           </cell>
           <cell r="E221">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222" t="str">
-            <v>TZN9E53</v>
+            <v>TZN9E56</v>
           </cell>
           <cell r="B222" t="str">
             <v>SES2</v>
           </cell>
           <cell r="C222" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D222" t="str">
             <v>LOCALIZA</v>
@@ -4576,7 +4580,7 @@
         </row>
         <row r="223">
           <cell r="A223" t="str">
-            <v>TZN9E54</v>
+            <v>TZN9E40</v>
           </cell>
           <cell r="B223" t="str">
             <v>SES2</v>
@@ -4588,29 +4592,29 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E223">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224" t="str">
-            <v>TZN9E56</v>
+            <v>TZN9E41</v>
           </cell>
           <cell r="B224" t="str">
             <v>SES2</v>
           </cell>
           <cell r="C224" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D224" t="str">
             <v>LOCALIZA</v>
           </cell>
           <cell r="E224">
-            <v>46300</v>
+            <v>46266</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225" t="str">
-            <v>TZN9E40</v>
+            <v>TZN9E46</v>
           </cell>
           <cell r="B225" t="str">
             <v>SES2</v>
@@ -4622,29 +4626,29 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E225">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226" t="str">
-            <v>TZN9E41</v>
+            <v>TZN9E59</v>
           </cell>
           <cell r="B226" t="str">
             <v>SES2</v>
           </cell>
           <cell r="C226" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D226" t="str">
             <v>LOCALIZA</v>
           </cell>
           <cell r="E226">
-            <v>46266</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227" t="str">
-            <v>TZN9E46</v>
+            <v>TZN9E61</v>
           </cell>
           <cell r="B227" t="str">
             <v>SES2</v>
@@ -4656,12 +4660,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E227">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228" t="str">
-            <v>TZN9E59</v>
+            <v>TZN9E44</v>
           </cell>
           <cell r="B228" t="str">
             <v>SES2</v>
@@ -4673,12 +4677,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E228">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229" t="str">
-            <v>TZN9E61</v>
+            <v>TZN9E51</v>
           </cell>
           <cell r="B229" t="str">
             <v>SES2</v>
@@ -4690,12 +4694,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E229">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230" t="str">
-            <v>TZN9E44</v>
+            <v>TZN9E60</v>
           </cell>
           <cell r="B230" t="str">
             <v>SES2</v>
@@ -4707,12 +4711,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E230">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231" t="str">
-            <v>TZN9E51</v>
+            <v>TZN9E66</v>
           </cell>
           <cell r="B231" t="str">
             <v>SES2</v>
@@ -4724,12 +4728,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E231">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232" t="str">
-            <v>TZN9E60</v>
+            <v>TZN9E67</v>
           </cell>
           <cell r="B232" t="str">
             <v>SES2</v>
@@ -4741,15 +4745,15 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E232">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233" t="str">
-            <v>TZN9E66</v>
+            <v>TZK7G89</v>
           </cell>
           <cell r="B233" t="str">
-            <v>SES2</v>
+            <v>SMG14</v>
           </cell>
           <cell r="C233" t="str">
             <v>ATIVA</v>
@@ -4758,15 +4762,15 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E233">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234" t="str">
-            <v>TZN9E67</v>
+            <v>TZK7G92</v>
           </cell>
           <cell r="B234" t="str">
-            <v>SES2</v>
+            <v>SMG14</v>
           </cell>
           <cell r="C234" t="str">
             <v>ATIVA</v>
@@ -4775,12 +4779,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E234">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235" t="str">
-            <v>TZK7G89</v>
+            <v>TZK7G95</v>
           </cell>
           <cell r="B235" t="str">
             <v>SMG14</v>
@@ -4792,12 +4796,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E235">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236" t="str">
-            <v>TZK7G92</v>
+            <v>TZK7H02</v>
           </cell>
           <cell r="B236" t="str">
             <v>SMG14</v>
@@ -4809,12 +4813,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E236">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237" t="str">
-            <v>TZK7G95</v>
+            <v>TZK7H03</v>
           </cell>
           <cell r="B237" t="str">
             <v>SMG14</v>
@@ -4826,12 +4830,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E237">
-            <v>46302</v>
+            <v>46300</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238" t="str">
-            <v>TZK7H02</v>
+            <v>TZK7G86</v>
           </cell>
           <cell r="B238" t="str">
             <v>SMG14</v>
@@ -4843,12 +4847,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E238">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239" t="str">
-            <v>TZK7H03</v>
+            <v>TZK7G88</v>
           </cell>
           <cell r="B239" t="str">
             <v>SMG14</v>
@@ -4860,12 +4864,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E239">
-            <v>46300</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240" t="str">
-            <v>TZK7G86</v>
+            <v>TZK7G93</v>
           </cell>
           <cell r="B240" t="str">
             <v>SMG14</v>
@@ -4877,12 +4881,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E240">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241" t="str">
-            <v>TZK7G88</v>
+            <v>TZK7G96</v>
           </cell>
           <cell r="B241" t="str">
             <v>SMG14</v>
@@ -4894,63 +4898,63 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E241">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242" t="str">
-            <v>TZK7G93</v>
+            <v>EKP2A86</v>
           </cell>
           <cell r="B242" t="str">
-            <v>SMG14</v>
+            <v>SMG3</v>
           </cell>
           <cell r="C242" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D242" t="str">
-            <v>LOCALIZA</v>
+            <v>TKS</v>
           </cell>
           <cell r="E242">
-            <v>46302</v>
+            <v>46281</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243" t="str">
-            <v>TZK7G96</v>
+            <v>UDD2F67</v>
           </cell>
           <cell r="B243" t="str">
-            <v>SMG14</v>
+            <v>SMG3</v>
           </cell>
           <cell r="C243" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D243" t="str">
-            <v>LOCALIZA</v>
+            <v>TKS</v>
           </cell>
           <cell r="E243">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244" t="str">
-            <v>EKP2A86</v>
+            <v>UGE6I11</v>
           </cell>
           <cell r="B244" t="str">
             <v>SMG3</v>
           </cell>
           <cell r="C244" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D244" t="str">
             <v>TKS</v>
           </cell>
           <cell r="E244">
-            <v>46281</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245" t="str">
-            <v>UDD2F67</v>
+            <v>UGQ5E06</v>
           </cell>
           <cell r="B245" t="str">
             <v>SMG3</v>
@@ -4962,21 +4966,21 @@
             <v>TKS</v>
           </cell>
           <cell r="E245">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246" t="str">
-            <v>UGE6I11</v>
+            <v>TXS8A77</v>
           </cell>
           <cell r="B246" t="str">
             <v>SMG3</v>
           </cell>
           <cell r="C246" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D246" t="str">
-            <v>TKS</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E246">
             <v>46302</v>
@@ -4984,41 +4988,41 @@
         </row>
         <row r="247">
           <cell r="A247" t="str">
-            <v>UGQ5E06</v>
+            <v>TXS8A78</v>
           </cell>
           <cell r="B247" t="str">
             <v>SMG3</v>
           </cell>
           <cell r="C247" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D247" t="str">
-            <v>TKS</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E247">
-            <v>46302</v>
+            <v>46299</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248" t="str">
-            <v>TXS8A77</v>
+            <v>TXS8A80</v>
           </cell>
           <cell r="B248" t="str">
             <v>SMG3</v>
           </cell>
           <cell r="C248" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D248" t="str">
             <v>VAMOS</v>
           </cell>
           <cell r="E248">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249" t="str">
-            <v>TXS8A78</v>
+            <v>TXS8A86</v>
           </cell>
           <cell r="B249" t="str">
             <v>SMG3</v>
@@ -5030,12 +5034,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E249">
-            <v>46299</v>
+            <v>46288</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250" t="str">
-            <v>TXS8A80</v>
+            <v>TXS8A91</v>
           </cell>
           <cell r="B250" t="str">
             <v>SMG3</v>
@@ -5052,41 +5056,41 @@
         </row>
         <row r="251">
           <cell r="A251" t="str">
-            <v>TXS8A86</v>
+            <v>TZK7G21</v>
           </cell>
           <cell r="B251" t="str">
-            <v>SMG3</v>
+            <v>SRJ1</v>
           </cell>
           <cell r="C251" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D251" t="str">
-            <v>VAMOS</v>
+            <v>LOCALIZA</v>
           </cell>
           <cell r="E251">
-            <v>46288</v>
+            <v>46302</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252" t="str">
-            <v>TXS8A91</v>
+            <v>TZK7G22</v>
           </cell>
           <cell r="B252" t="str">
-            <v>SMG3</v>
+            <v>SRJ1</v>
           </cell>
           <cell r="C252" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D252" t="str">
-            <v>VAMOS</v>
+            <v>LOCALIZA</v>
           </cell>
           <cell r="E252">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253" t="str">
-            <v>TZK7G21</v>
+            <v>TZK7G23</v>
           </cell>
           <cell r="B253" t="str">
             <v>SRJ1</v>
@@ -5098,29 +5102,29 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E253">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254" t="str">
-            <v>TZK7G22</v>
+            <v>TZK7G25</v>
           </cell>
           <cell r="B254" t="str">
             <v>SRJ1</v>
           </cell>
           <cell r="C254" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO / PLACA RESERVA</v>
           </cell>
           <cell r="D254" t="str">
             <v>LOCALIZA</v>
           </cell>
           <cell r="E254">
-            <v>46301</v>
+            <v>46284</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255" t="str">
-            <v>TZK7G23</v>
+            <v>TZM0A63</v>
           </cell>
           <cell r="B255" t="str">
             <v>SRJ1</v>
@@ -5137,24 +5141,24 @@
         </row>
         <row r="256">
           <cell r="A256" t="str">
-            <v>TZK7G25</v>
+            <v>TZK7G30</v>
           </cell>
           <cell r="B256" t="str">
             <v>SRJ1</v>
           </cell>
           <cell r="C256" t="str">
-            <v>MANUTENÇÃO / PLACA RESERVA</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D256" t="str">
             <v>LOCALIZA</v>
           </cell>
           <cell r="E256">
-            <v>46284</v>
+            <v>46302</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257" t="str">
-            <v>TZM0A63</v>
+            <v>TZK7G32</v>
           </cell>
           <cell r="B257" t="str">
             <v>SRJ1</v>
@@ -5166,12 +5170,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E257">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258" t="str">
-            <v>TZK7G30</v>
+            <v>TZK7G41</v>
           </cell>
           <cell r="B258" t="str">
             <v>SRJ1</v>
@@ -5188,7 +5192,7 @@
         </row>
         <row r="259">
           <cell r="A259" t="str">
-            <v>TZK7G32</v>
+            <v>TZK7G42</v>
           </cell>
           <cell r="B259" t="str">
             <v>SRJ1</v>
@@ -5200,12 +5204,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E259">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260" t="str">
-            <v>TZK7G41</v>
+            <v>TZK7G43</v>
           </cell>
           <cell r="B260" t="str">
             <v>SRJ1</v>
@@ -5217,12 +5221,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E260">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261" t="str">
-            <v>TZK7G42</v>
+            <v>TZK7G04</v>
           </cell>
           <cell r="B261" t="str">
             <v>SRJ1</v>
@@ -5234,12 +5238,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E261">
-            <v>46302</v>
+            <v>46301</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262" t="str">
-            <v>TZK7G43</v>
+            <v>TZK7G05</v>
           </cell>
           <cell r="B262" t="str">
             <v>SRJ1</v>
@@ -5251,12 +5255,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E262">
-            <v>46300</v>
+            <v>46302</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263" t="str">
-            <v>TZK7G04</v>
+            <v>TZK7G07</v>
           </cell>
           <cell r="B263" t="str">
             <v>SRJ1</v>
@@ -5268,12 +5272,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E263">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264" t="str">
-            <v>TZK7G05</v>
+            <v>TZK7G09</v>
           </cell>
           <cell r="B264" t="str">
             <v>SRJ1</v>
@@ -5285,12 +5289,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E264">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265" t="str">
-            <v>TZK7G07</v>
+            <v>TZK7G10</v>
           </cell>
           <cell r="B265" t="str">
             <v>SRJ1</v>
@@ -5302,46 +5306,46 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E265">
-            <v>46301</v>
+            <v>46302</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266" t="str">
-            <v>TZK7G09</v>
+            <v>TXJ6H38</v>
           </cell>
           <cell r="B266" t="str">
-            <v>SRJ1</v>
+            <v>SRJ10</v>
           </cell>
           <cell r="C266" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D266" t="str">
-            <v>LOCALIZA</v>
+            <v>UNIDAS</v>
           </cell>
           <cell r="E266">
-            <v>46302</v>
+            <v>46301</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267" t="str">
-            <v>TZK7G10</v>
+            <v>TXJ6H73</v>
           </cell>
           <cell r="B267" t="str">
-            <v>SRJ1</v>
+            <v>SRJ10</v>
           </cell>
           <cell r="C267" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D267" t="str">
-            <v>LOCALIZA</v>
+            <v>UNIDAS</v>
           </cell>
           <cell r="E267">
-            <v>46302</v>
+            <v>46300</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268" t="str">
-            <v>TXJ6H38</v>
+            <v>TZK0E28</v>
           </cell>
           <cell r="B268" t="str">
             <v>SRJ10</v>
@@ -5350,15 +5354,15 @@
             <v>ATIVA</v>
           </cell>
           <cell r="D268" t="str">
-            <v>UNIDAS</v>
+            <v>LOCALIZA</v>
           </cell>
           <cell r="E268">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269" t="str">
-            <v>TXJ6H73</v>
+            <v>TZK7F76</v>
           </cell>
           <cell r="B269" t="str">
             <v>SRJ10</v>
@@ -5367,15 +5371,15 @@
             <v>ATIVA</v>
           </cell>
           <cell r="D269" t="str">
-            <v>UNIDAS</v>
+            <v>LOCALIZA</v>
           </cell>
           <cell r="E269">
-            <v>46300</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270" t="str">
-            <v>TZK0E28</v>
+            <v>TZK7F79</v>
           </cell>
           <cell r="B270" t="str">
             <v>SRJ10</v>
@@ -5387,12 +5391,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E270">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271" t="str">
-            <v>TZK7F76</v>
+            <v>TZK7F80</v>
           </cell>
           <cell r="B271" t="str">
             <v>SRJ10</v>
@@ -5404,29 +5408,29 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E271">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272" t="str">
-            <v>TZK7F79</v>
+            <v>TZK7F81</v>
           </cell>
           <cell r="B272" t="str">
             <v>SRJ10</v>
           </cell>
           <cell r="C272" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D272" t="str">
             <v>LOCALIZA</v>
           </cell>
           <cell r="E272">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273" t="str">
-            <v>TZK7F80</v>
+            <v>TZK7F83</v>
           </cell>
           <cell r="B273" t="str">
             <v>SRJ10</v>
@@ -5438,12 +5442,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E273">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274" t="str">
-            <v>TZK7F81</v>
+            <v>TZK7F87</v>
           </cell>
           <cell r="B274" t="str">
             <v>SRJ10</v>
@@ -5460,7 +5464,7 @@
         </row>
         <row r="275">
           <cell r="A275" t="str">
-            <v>TZK7F83</v>
+            <v>TZK7F88</v>
           </cell>
           <cell r="B275" t="str">
             <v>SRJ10</v>
@@ -5472,12 +5476,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E275">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276" t="str">
-            <v>TZK7F87</v>
+            <v>TZK7F90</v>
           </cell>
           <cell r="B276" t="str">
             <v>SRJ10</v>
@@ -5489,12 +5493,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E276">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277" t="str">
-            <v>TZK7F88</v>
+            <v>TZK7F91</v>
           </cell>
           <cell r="B277" t="str">
             <v>SRJ10</v>
@@ -5506,12 +5510,12 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E277">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278" t="str">
-            <v>TZK7F90</v>
+            <v>TZK7G13</v>
           </cell>
           <cell r="B278" t="str">
             <v>SRJ10</v>
@@ -5523,46 +5527,46 @@
             <v>LOCALIZA</v>
           </cell>
           <cell r="E278">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279" t="str">
-            <v>TZK7F91</v>
+            <v>TDY1G59</v>
           </cell>
           <cell r="B279" t="str">
-            <v>SRJ10</v>
+            <v>SRJ7</v>
           </cell>
           <cell r="C279" t="str">
-            <v>ATIVA</v>
+            <v>TROCAR PLACA</v>
           </cell>
           <cell r="D279" t="str">
-            <v>LOCALIZA</v>
+            <v>LOCALIZA/PORTAL</v>
           </cell>
           <cell r="E279">
-            <v>46302</v>
+            <v>46169</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280" t="str">
-            <v>TZK7G13</v>
+            <v>TET8E19</v>
           </cell>
           <cell r="B280" t="str">
-            <v>SRJ10</v>
+            <v>SRJ7</v>
           </cell>
           <cell r="C280" t="str">
-            <v>ATIVA</v>
+            <v>TROCAR PLACA</v>
           </cell>
           <cell r="D280" t="str">
-            <v>LOCALIZA</v>
+            <v>LOCALIZA/PORTAL</v>
           </cell>
           <cell r="E280">
-            <v>46302</v>
+            <v>46246</v>
           </cell>
         </row>
         <row r="281">
           <cell r="A281" t="str">
-            <v>TDY1G59</v>
+            <v>TYI9E76</v>
           </cell>
           <cell r="B281" t="str">
             <v>SRJ7</v>
@@ -5574,97 +5578,97 @@
             <v>LOCALIZA/PORTAL</v>
           </cell>
           <cell r="E281">
-            <v>46169</v>
+            <v>46283</v>
           </cell>
         </row>
         <row r="282">
           <cell r="A282" t="str">
-            <v>TET8E19</v>
+            <v>TZI2C82</v>
           </cell>
           <cell r="B282" t="str">
-            <v>SRJ7</v>
+            <v>SRJ8</v>
           </cell>
           <cell r="C282" t="str">
-            <v>TROCAR PLACA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D282" t="str">
-            <v>LOCALIZA/PORTAL</v>
+            <v>LM TRANPORTES</v>
           </cell>
           <cell r="E282">
-            <v>46246</v>
+            <v>46255</v>
           </cell>
         </row>
         <row r="283">
           <cell r="A283" t="str">
-            <v>TYI9E76</v>
+            <v>TZI2D97</v>
           </cell>
           <cell r="B283" t="str">
-            <v>SRJ7</v>
+            <v>SRJ8</v>
           </cell>
           <cell r="C283" t="str">
-            <v>TROCAR PLACA</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D283" t="str">
-            <v>LOCALIZA/PORTAL</v>
+            <v>LM TRANPORTES</v>
           </cell>
           <cell r="E283">
-            <v>46283</v>
+            <v>46302</v>
           </cell>
         </row>
         <row r="284">
           <cell r="A284" t="str">
-            <v>TZI2C82</v>
+            <v>TZI3I07</v>
           </cell>
           <cell r="B284" t="str">
             <v>SRJ8</v>
           </cell>
           <cell r="C284" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D284" t="str">
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E284">
-            <v>46255</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="285">
           <cell r="A285" t="str">
-            <v>TZI2D97</v>
+            <v>TZI3I10</v>
           </cell>
           <cell r="B285" t="str">
             <v>SRJ8</v>
           </cell>
           <cell r="C285" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D285" t="str">
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E285">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="286">
           <cell r="A286" t="str">
-            <v>TZI3I07</v>
+            <v>TZI3I17</v>
           </cell>
           <cell r="B286" t="str">
             <v>SRJ8</v>
           </cell>
           <cell r="C286" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D286" t="str">
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E286">
-            <v>46302</v>
+            <v>46272</v>
           </cell>
         </row>
         <row r="287">
           <cell r="A287" t="str">
-            <v>TZI3I10</v>
+            <v>TZO8I81</v>
           </cell>
           <cell r="B287" t="str">
             <v>SRJ8</v>
@@ -5676,29 +5680,29 @@
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E287">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="288">
           <cell r="A288" t="str">
-            <v>TZI3I17</v>
+            <v>UDC6J75</v>
           </cell>
           <cell r="B288" t="str">
             <v>SRJ8</v>
           </cell>
           <cell r="C288" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D288" t="str">
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E288">
-            <v>46272</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="289">
           <cell r="A289" t="str">
-            <v>TZO8I81</v>
+            <v>UDL1B21</v>
           </cell>
           <cell r="B289" t="str">
             <v>SRJ8</v>
@@ -5710,12 +5714,12 @@
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E289">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="290">
           <cell r="A290" t="str">
-            <v>UDC6J75</v>
+            <v>UFI2I06</v>
           </cell>
           <cell r="B290" t="str">
             <v>SRJ8</v>
@@ -5727,12 +5731,12 @@
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E290">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="291">
           <cell r="A291" t="str">
-            <v>UDL1B21</v>
+            <v>TZI6A44</v>
           </cell>
           <cell r="B291" t="str">
             <v>SRJ8</v>
@@ -5741,15 +5745,15 @@
             <v>ATIVA</v>
           </cell>
           <cell r="D291" t="str">
-            <v>LM TRANPORTES</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E291">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="292">
           <cell r="A292" t="str">
-            <v>UFI2I06</v>
+            <v>TZI6A49</v>
           </cell>
           <cell r="B292" t="str">
             <v>SRJ8</v>
@@ -5758,15 +5762,15 @@
             <v>ATIVA</v>
           </cell>
           <cell r="D292" t="str">
-            <v>LM TRANPORTES</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E292">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="293">
           <cell r="A293" t="str">
-            <v>TZI6A44</v>
+            <v>TZV1F05</v>
           </cell>
           <cell r="B293" t="str">
             <v>SRJ8</v>
@@ -5778,12 +5782,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E293">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="294">
           <cell r="A294" t="str">
-            <v>TZI6A49</v>
+            <v>TZV1F01</v>
           </cell>
           <cell r="B294" t="str">
             <v>SRJ8</v>
@@ -5795,12 +5799,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E294">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="295">
           <cell r="A295" t="str">
-            <v>TZV1F05</v>
+            <v>TZV1E99</v>
           </cell>
           <cell r="B295" t="str">
             <v>SRJ8</v>
@@ -5812,12 +5816,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E295">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="296">
           <cell r="A296" t="str">
-            <v>TZV1F01</v>
+            <v>TZV1E97</v>
           </cell>
           <cell r="B296" t="str">
             <v>SRJ8</v>
@@ -5829,12 +5833,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E296">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="297">
           <cell r="A297" t="str">
-            <v>TZV1E99</v>
+            <v>TZV1E89</v>
           </cell>
           <cell r="B297" t="str">
             <v>SRJ8</v>
@@ -5846,12 +5850,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E297">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="298">
           <cell r="A298" t="str">
-            <v>TZV1E97</v>
+            <v>TZV1E88</v>
           </cell>
           <cell r="B298" t="str">
             <v>SRJ8</v>
@@ -5863,12 +5867,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E298">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="299">
           <cell r="A299" t="str">
-            <v>TZV1E89</v>
+            <v>TZV1E86</v>
           </cell>
           <cell r="B299" t="str">
             <v>SRJ8</v>
@@ -5880,15 +5884,15 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E299">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="300">
           <cell r="A300" t="str">
-            <v>TZV1E88</v>
+            <v>TZP6B28</v>
           </cell>
           <cell r="B300" t="str">
-            <v>SRJ8</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C300" t="str">
             <v>ATIVA</v>
@@ -5897,32 +5901,32 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E300">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="301">
           <cell r="A301" t="str">
-            <v>TZV1E86</v>
+            <v>TZQ7B50</v>
           </cell>
           <cell r="B301" t="str">
-            <v>SRJ8</v>
+            <v>SRJ7</v>
           </cell>
           <cell r="C301" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D301" t="str">
             <v>VAMOS</v>
           </cell>
           <cell r="E301">
-            <v>46302</v>
+            <v>46298</v>
           </cell>
         </row>
         <row r="302">
           <cell r="A302" t="str">
-            <v>TZP6B28</v>
+            <v>TZQ7B51</v>
           </cell>
           <cell r="B302" t="str">
-            <v>SRJ4</v>
+            <v>SRJ7</v>
           </cell>
           <cell r="C302" t="str">
             <v>ATIVA</v>
@@ -5931,32 +5935,32 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E302">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="303">
           <cell r="A303" t="str">
-            <v>TZQ7B50</v>
+            <v>TZQ7B52</v>
           </cell>
           <cell r="B303" t="str">
-            <v>SRJ7</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C303" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D303" t="str">
             <v>VAMOS</v>
           </cell>
           <cell r="E303">
-            <v>46298</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="304">
           <cell r="A304" t="str">
-            <v>TZQ7B51</v>
+            <v>TZQ7B53</v>
           </cell>
           <cell r="B304" t="str">
-            <v>SRJ7</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C304" t="str">
             <v>ATIVA</v>
@@ -5965,46 +5969,46 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E304">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="305">
           <cell r="A305" t="str">
-            <v>TZQ7B52</v>
+            <v>TZI0C46</v>
           </cell>
           <cell r="B305" t="str">
-            <v>SRJ4</v>
+            <v>SRJ1</v>
           </cell>
           <cell r="C305" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D305" t="str">
-            <v>VAMOS</v>
+            <v>LM TRANPORTES</v>
           </cell>
           <cell r="E305">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="306">
           <cell r="A306" t="str">
-            <v>TZQ7B53</v>
+            <v>TJV0G47</v>
           </cell>
           <cell r="B306" t="str">
-            <v>SRJ4</v>
+            <v>SRJ1</v>
           </cell>
           <cell r="C306" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D306" t="str">
-            <v>VAMOS</v>
+            <v>LM TRANPORTES</v>
           </cell>
           <cell r="E306">
-            <v>46288</v>
+            <v>46302</v>
           </cell>
         </row>
         <row r="307">
           <cell r="A307" t="str">
-            <v>TZI0C46</v>
+            <v>QSR8G51</v>
           </cell>
           <cell r="B307" t="str">
             <v>SRJ1</v>
@@ -6016,12 +6020,12 @@
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E307">
-            <v>46302</v>
+            <v>46290</v>
           </cell>
         </row>
         <row r="308">
           <cell r="A308" t="str">
-            <v>TJV0G47</v>
+            <v>TLQ1J14</v>
           </cell>
           <cell r="B308" t="str">
             <v>SRJ1</v>
@@ -6033,12 +6037,12 @@
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E308">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="309">
           <cell r="A309" t="str">
-            <v>QSR8G51</v>
+            <v>QSW6D63</v>
           </cell>
           <cell r="B309" t="str">
             <v>SRJ1</v>
@@ -6050,46 +6054,46 @@
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E309">
-            <v>46290</v>
+            <v>46302</v>
           </cell>
         </row>
         <row r="310">
           <cell r="A310" t="str">
-            <v>TLQ1J14</v>
+            <v>TZM0A64</v>
           </cell>
           <cell r="B310" t="str">
-            <v>SRJ1</v>
+            <v>SRJ10</v>
           </cell>
           <cell r="C310" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D310" t="str">
-            <v>LM TRANPORTES</v>
+            <v>LOCALIZA</v>
           </cell>
           <cell r="E310">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="311">
           <cell r="A311" t="str">
-            <v>QSW6D63</v>
+            <v>UGT4I35</v>
           </cell>
           <cell r="B311" t="str">
-            <v>SRJ1</v>
+            <v>SRJ10</v>
           </cell>
           <cell r="C311" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D311" t="str">
-            <v>LM TRANPORTES</v>
+            <v>TKS</v>
           </cell>
           <cell r="E311">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="312">
           <cell r="A312" t="str">
-            <v>TZM0A64</v>
+            <v>UFR5D56</v>
           </cell>
           <cell r="B312" t="str">
             <v>SRJ10</v>
@@ -6098,15 +6102,15 @@
             <v>ATIVA</v>
           </cell>
           <cell r="D312" t="str">
-            <v>LOCALIZA</v>
+            <v>TKS</v>
           </cell>
           <cell r="E312">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="313">
           <cell r="A313" t="str">
-            <v>UGT4I35</v>
+            <v>UGD7H04</v>
           </cell>
           <cell r="B313" t="str">
             <v>SRJ10</v>
@@ -6123,7 +6127,7 @@
         </row>
         <row r="314">
           <cell r="A314" t="str">
-            <v>UFR5D56</v>
+            <v>UFS2F07</v>
           </cell>
           <cell r="B314" t="str">
             <v>SRJ10</v>
@@ -6135,12 +6139,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E314">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="315">
           <cell r="A315" t="str">
-            <v>UGD7H04</v>
+            <v>UDJ5F85</v>
           </cell>
           <cell r="B315" t="str">
             <v>SRJ10</v>
@@ -6152,15 +6156,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E315">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="316">
           <cell r="A316" t="str">
-            <v>UFS2F07</v>
+            <v>UCE5B49</v>
           </cell>
           <cell r="B316" t="str">
-            <v>SRJ10</v>
+            <v>SMG3</v>
           </cell>
           <cell r="C316" t="str">
             <v>ATIVA</v>
@@ -6169,15 +6173,15 @@
             <v>TKS</v>
           </cell>
           <cell r="E316">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="317">
           <cell r="A317" t="str">
-            <v>UDJ5F85</v>
+            <v>UCE5E77</v>
           </cell>
           <cell r="B317" t="str">
-            <v>SRJ10</v>
+            <v>SMG3</v>
           </cell>
           <cell r="C317" t="str">
             <v>ATIVA</v>
@@ -6186,12 +6190,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E317">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="318">
           <cell r="A318" t="str">
-            <v>UCE5B49</v>
+            <v>UCE5C45</v>
           </cell>
           <cell r="B318" t="str">
             <v>SMG3</v>
@@ -6203,12 +6207,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E318">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="319">
           <cell r="A319" t="str">
-            <v>UCE5E77</v>
+            <v>UAE9E74</v>
           </cell>
           <cell r="B319" t="str">
             <v>SMG3</v>
@@ -6217,15 +6221,15 @@
             <v>ATIVA</v>
           </cell>
           <cell r="D319" t="str">
-            <v>TKS</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E319">
-            <v>46302</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="320">
           <cell r="A320" t="str">
-            <v>UCE5C45</v>
+            <v>UAE9E78</v>
           </cell>
           <cell r="B320" t="str">
             <v>SMG3</v>
@@ -6234,32 +6238,32 @@
             <v>ATIVA</v>
           </cell>
           <cell r="D320" t="str">
-            <v>TKS</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E320">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="321">
           <cell r="A321" t="str">
-            <v>TYK8A44</v>
+            <v>UAF1F90</v>
           </cell>
           <cell r="B321" t="str">
-            <v>SRJ7</v>
+            <v>SMG3</v>
           </cell>
           <cell r="C321" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D321" t="str">
-            <v>LOCALIZA</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E321">
-            <v>46299</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="322">
           <cell r="A322" t="str">
-            <v>UAE9E74</v>
+            <v>UAF1F91</v>
           </cell>
           <cell r="B322" t="str">
             <v>SMG3</v>
@@ -6271,12 +6275,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E322">
-            <v>0</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="323">
           <cell r="A323" t="str">
-            <v>UAE9E78</v>
+            <v>UAE9E89</v>
           </cell>
           <cell r="B323" t="str">
             <v>SMG3</v>
@@ -6288,100 +6292,100 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E323">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="324">
           <cell r="A324" t="str">
-            <v>UAF1F90</v>
+            <v>TYD1F90</v>
           </cell>
           <cell r="B324" t="str">
-            <v>SMG3</v>
+            <v>SRJ7</v>
           </cell>
           <cell r="C324" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D324" t="str">
-            <v>VAMOS</v>
+            <v>LOCALIZA</v>
           </cell>
           <cell r="E324">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="325">
           <cell r="A325" t="str">
-            <v>UAF1F91</v>
+            <v>UCM6G40</v>
           </cell>
           <cell r="B325" t="str">
-            <v>SMG3</v>
+            <v>SES2</v>
           </cell>
           <cell r="C325" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D325" t="str">
-            <v>VAMOS</v>
+            <v>LM TRANPORTES</v>
           </cell>
           <cell r="E325">
-            <v>46302</v>
+            <v>46288</v>
           </cell>
         </row>
         <row r="326">
           <cell r="A326" t="str">
-            <v>UAE9E89</v>
+            <v>UCM7F89</v>
           </cell>
           <cell r="B326" t="str">
-            <v>SMG3</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C326" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D326" t="str">
-            <v>VAMOS</v>
+            <v>LM TRANPORTES</v>
           </cell>
           <cell r="E326">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="327">
           <cell r="A327" t="str">
-            <v>TYD1F90</v>
+            <v>UCM7F91</v>
           </cell>
           <cell r="B327" t="str">
-            <v>SRJ7</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C327" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D327" t="str">
-            <v>LOCALIZA</v>
+            <v>LM TRANPORTES</v>
           </cell>
           <cell r="E327">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="328">
           <cell r="A328" t="str">
-            <v>UCM6G40</v>
+            <v>UCM5A93</v>
           </cell>
           <cell r="B328" t="str">
-            <v>SES2</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C328" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D328" t="str">
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E328">
-            <v>46288</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="329">
           <cell r="A329" t="str">
-            <v>UCM7F89</v>
+            <v>UCM6C20</v>
           </cell>
           <cell r="B329" t="str">
-            <v>SRJ4</v>
+            <v>SRJ8</v>
           </cell>
           <cell r="C329" t="str">
             <v>ATIVA</v>
@@ -6390,80 +6394,80 @@
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E329">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="330">
           <cell r="A330" t="str">
-            <v>UCM7F91</v>
+            <v>UAG5E18</v>
           </cell>
           <cell r="B330" t="str">
-            <v>SRJ4</v>
+            <v>SMG3</v>
           </cell>
           <cell r="C330" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D330" t="str">
-            <v>LM TRANPORTES</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E330">
-            <v>46302</v>
+            <v>46300</v>
           </cell>
         </row>
         <row r="331">
           <cell r="A331" t="str">
-            <v>UCM5A93</v>
+            <v>UAG5E23</v>
           </cell>
           <cell r="B331" t="str">
-            <v>SRJ4</v>
+            <v>SMG3</v>
           </cell>
           <cell r="C331" t="str">
-            <v>ATIVA</v>
+            <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D331" t="str">
-            <v>LM TRANPORTES</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E331">
-            <v>46302</v>
+            <v>46294</v>
           </cell>
         </row>
         <row r="332">
           <cell r="A332" t="str">
-            <v>UCM6C20</v>
+            <v>UAG5E44</v>
           </cell>
           <cell r="B332" t="str">
-            <v>SRJ8</v>
+            <v>SMG3</v>
           </cell>
           <cell r="C332" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D332" t="str">
-            <v>LM TRANPORTES</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E332">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="333">
           <cell r="A333" t="str">
-            <v>UAG5E18</v>
+            <v>UCN5H68</v>
           </cell>
           <cell r="B333" t="str">
-            <v>SMG3</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C333" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D333" t="str">
-            <v>VAMOS</v>
+            <v>LM TRANPORTES</v>
           </cell>
           <cell r="E333">
-            <v>46300</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="334">
           <cell r="A334" t="str">
-            <v>UAG5E23</v>
+            <v>UAG5E39</v>
           </cell>
           <cell r="B334" t="str">
             <v>SMG3</v>
@@ -6475,12 +6479,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E334">
-            <v>46294</v>
+            <v>46289</v>
           </cell>
         </row>
         <row r="335">
           <cell r="A335" t="str">
-            <v>UAG5E44</v>
+            <v>UAG5E54</v>
           </cell>
           <cell r="B335" t="str">
             <v>SMG3</v>
@@ -6492,12 +6496,12 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E335">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="336">
           <cell r="A336" t="str">
-            <v>UCN5H68</v>
+            <v>UCN5H71</v>
           </cell>
           <cell r="B336" t="str">
             <v>SRJ4</v>
@@ -6509,49 +6513,49 @@
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E336">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="337">
           <cell r="A337" t="str">
-            <v>UAG5E39</v>
+            <v xml:space="preserve">UCO0B60 </v>
           </cell>
           <cell r="B337" t="str">
-            <v>SMG3</v>
+            <v>SES2</v>
           </cell>
           <cell r="C337" t="str">
             <v>MANUTENÇÃO</v>
           </cell>
           <cell r="D337" t="str">
-            <v>VAMOS</v>
+            <v>LM TRANPORTES</v>
           </cell>
           <cell r="E337">
-            <v>46289</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="338">
           <cell r="A338" t="str">
-            <v>UAG5E54</v>
+            <v xml:space="preserve">UCN5I89  </v>
           </cell>
           <cell r="B338" t="str">
-            <v>SMG3</v>
+            <v>SES2</v>
           </cell>
           <cell r="C338" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D338" t="str">
-            <v>VAMOS</v>
+            <v>LM TRANPORTES</v>
           </cell>
           <cell r="E338">
-            <v>46302</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="339">
           <cell r="A339" t="str">
-            <v>UCN5H71</v>
+            <v xml:space="preserve">UCN5J01 </v>
           </cell>
           <cell r="B339" t="str">
-            <v>SRJ4</v>
+            <v>SES2</v>
           </cell>
           <cell r="C339" t="str">
             <v>ATIVA</v>
@@ -6560,12 +6564,12 @@
             <v>LM TRANPORTES</v>
           </cell>
           <cell r="E339">
-            <v>46302</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="340">
           <cell r="A340" t="str">
-            <v xml:space="preserve">UCO0B60 </v>
+            <v xml:space="preserve">UCN5I81  </v>
           </cell>
           <cell r="B340" t="str">
             <v>SES2</v>
@@ -6582,58 +6586,58 @@
         </row>
         <row r="341">
           <cell r="A341" t="str">
-            <v xml:space="preserve">UCN5I89  </v>
+            <v>TZR6A70</v>
           </cell>
           <cell r="B341" t="str">
-            <v>SES2</v>
+            <v>SMG3</v>
           </cell>
           <cell r="C341" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D341" t="str">
-            <v>LM TRANPORTES</v>
+            <v>LOCALIZA</v>
           </cell>
           <cell r="E341">
-            <v>0</v>
+            <v>46300</v>
           </cell>
         </row>
         <row r="342">
           <cell r="A342" t="str">
-            <v xml:space="preserve">UCN5J01 </v>
+            <v>UCM5J76</v>
           </cell>
           <cell r="B342" t="str">
-            <v>SES2</v>
+            <v>SMG3</v>
           </cell>
           <cell r="C342" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D342" t="str">
-            <v>LM TRANPORTES</v>
+            <v>TKS</v>
           </cell>
           <cell r="E342">
-            <v>0</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="343">
           <cell r="A343" t="str">
-            <v xml:space="preserve">UCN5I81  </v>
+            <v>UCL8B30</v>
           </cell>
           <cell r="B343" t="str">
-            <v>SES2</v>
+            <v>SMG3</v>
           </cell>
           <cell r="C343" t="str">
-            <v>MANUTENÇÃO</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D343" t="str">
-            <v>LM TRANPORTES</v>
+            <v>TKS</v>
           </cell>
           <cell r="E343">
-            <v>0</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="344">
           <cell r="A344" t="str">
-            <v>TZR6A70</v>
+            <v>UCL7J83</v>
           </cell>
           <cell r="B344" t="str">
             <v>SMG3</v>
@@ -6642,15 +6646,15 @@
             <v>ATIVA</v>
           </cell>
           <cell r="D344" t="str">
-            <v>LOCALIZA</v>
+            <v>TKS</v>
           </cell>
           <cell r="E344">
-            <v>46300</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="345">
           <cell r="A345" t="str">
-            <v>UCM5J76</v>
+            <v>UCL8B44</v>
           </cell>
           <cell r="B345" t="str">
             <v>SMG3</v>
@@ -6662,12 +6666,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E345">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="346">
           <cell r="A346" t="str">
-            <v>UCL8B30</v>
+            <v>UCL8B10</v>
           </cell>
           <cell r="B346" t="str">
             <v>SMG3</v>
@@ -6679,12 +6683,12 @@
             <v>TKS</v>
           </cell>
           <cell r="E346">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="347">
           <cell r="A347" t="str">
-            <v>UCL7J83</v>
+            <v>UCL7J84</v>
           </cell>
           <cell r="B347" t="str">
             <v>SMG3</v>
@@ -6701,7 +6705,7 @@
         </row>
         <row r="348">
           <cell r="A348" t="str">
-            <v>UCL8B44</v>
+            <v>UCL8A66</v>
           </cell>
           <cell r="B348" t="str">
             <v>SMG3</v>
@@ -6713,63 +6717,63 @@
             <v>TKS</v>
           </cell>
           <cell r="E348">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="349">
           <cell r="A349" t="str">
-            <v>UCL8B10</v>
+            <v>UVL9F73</v>
           </cell>
           <cell r="B349" t="str">
-            <v>SMG3</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C349" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D349" t="str">
-            <v>TKS</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E349">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="350">
           <cell r="A350" t="str">
-            <v>UCL7J84</v>
+            <v>UCN5I92</v>
           </cell>
           <cell r="B350" t="str">
-            <v>SMG3</v>
+            <v>SES2</v>
           </cell>
           <cell r="C350" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D350" t="str">
-            <v>TKS</v>
+            <v>LM TRANPORTES</v>
           </cell>
           <cell r="E350">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="351">
           <cell r="A351" t="str">
-            <v>UCL8A66</v>
+            <v>UVL9F71</v>
           </cell>
           <cell r="B351" t="str">
-            <v>SMG3</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C351" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D351" t="str">
-            <v>TKS</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E351">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="352">
           <cell r="A352" t="str">
-            <v>UVL9F73</v>
+            <v>UVL9F72</v>
           </cell>
           <cell r="B352" t="str">
             <v>SRJ4</v>
@@ -6781,29 +6785,29 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E352">
-            <v>46289</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="353">
           <cell r="A353" t="str">
-            <v>UCN5I92</v>
+            <v>UVL9F75</v>
           </cell>
           <cell r="B353" t="str">
-            <v>SES2</v>
+            <v>SRJ4</v>
           </cell>
           <cell r="C353" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D353" t="str">
-            <v>LM TRANPORTES</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E353">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="354">
           <cell r="A354" t="str">
-            <v>UVL9F71</v>
+            <v>UVL9F77</v>
           </cell>
           <cell r="B354" t="str">
             <v>SRJ4</v>
@@ -6815,66 +6819,66 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E354">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="355">
           <cell r="A355" t="str">
-            <v>UVL9F72</v>
+            <v>TUG6J78</v>
           </cell>
           <cell r="B355" t="str">
-            <v>SRJ4</v>
+            <v>SES1</v>
           </cell>
           <cell r="C355" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D355" t="str">
-            <v>VAMOS</v>
+            <v>DELUNA</v>
           </cell>
           <cell r="E355">
-            <v>46302</v>
+            <v>46300</v>
           </cell>
         </row>
         <row r="356">
           <cell r="A356" t="str">
-            <v>UVL9F75</v>
+            <v>TUG6J79</v>
           </cell>
           <cell r="B356" t="str">
-            <v>SRJ4</v>
+            <v>SRJ10</v>
           </cell>
           <cell r="C356" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D356" t="str">
-            <v>VAMOS</v>
+            <v>DELUNA</v>
           </cell>
           <cell r="E356">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="357">
           <cell r="A357" t="str">
-            <v>UVL9F77</v>
+            <v>TUG6J80</v>
           </cell>
           <cell r="B357" t="str">
-            <v>SRJ4</v>
+            <v>SRJ10</v>
           </cell>
           <cell r="C357" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D357" t="str">
-            <v>VAMOS</v>
+            <v>DELUNA</v>
           </cell>
           <cell r="E357">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="358">
           <cell r="A358" t="str">
-            <v>TUG6J78</v>
+            <v>TUG6J81</v>
           </cell>
           <cell r="B358" t="str">
-            <v>SES1</v>
+            <v>SRJ10</v>
           </cell>
           <cell r="C358" t="str">
             <v>ATIVA</v>
@@ -6883,12 +6887,12 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E358">
-            <v>46300</v>
+            <v>46302</v>
           </cell>
         </row>
         <row r="359">
           <cell r="A359" t="str">
-            <v>TUG6J79</v>
+            <v>SSE4G34</v>
           </cell>
           <cell r="B359" t="str">
             <v>SRJ10</v>
@@ -6900,12 +6904,12 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E359">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="360">
           <cell r="A360" t="str">
-            <v>TUG6J80</v>
+            <v>TTC0H70</v>
           </cell>
           <cell r="B360" t="str">
             <v>SRJ10</v>
@@ -6917,66 +6921,66 @@
             <v>DELUNA</v>
           </cell>
           <cell r="E360">
-            <v>46301</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="361">
           <cell r="A361" t="str">
-            <v>TUG6J81</v>
+            <v>UVN4F22</v>
           </cell>
           <cell r="B361" t="str">
-            <v>SRJ10</v>
+            <v>SRJ9</v>
           </cell>
           <cell r="C361" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D361" t="str">
-            <v>DELUNA</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E361">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="362">
           <cell r="A362" t="str">
-            <v>SSE4G34</v>
+            <v>UVN4F19</v>
           </cell>
           <cell r="B362" t="str">
-            <v>SRJ10</v>
+            <v>SRJ9</v>
           </cell>
           <cell r="C362" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D362" t="str">
-            <v>DELUNA</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E362">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="363">
           <cell r="A363" t="str">
-            <v>TTC0H70</v>
+            <v>UVN4F28</v>
           </cell>
           <cell r="B363" t="str">
-            <v>SRJ10</v>
+            <v>SRJ8</v>
           </cell>
           <cell r="C363" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D363" t="str">
-            <v>DELUNA</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E363">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="364">
           <cell r="A364" t="str">
-            <v>UVN4F22</v>
+            <v>UVN4F21</v>
           </cell>
           <cell r="B364" t="str">
-            <v>SRJ9</v>
+            <v>SRJ8</v>
           </cell>
           <cell r="C364" t="str">
             <v>ATIVA</v>
@@ -6990,7 +6994,7 @@
         </row>
         <row r="365">
           <cell r="A365" t="str">
-            <v>UVN4F19</v>
+            <v>UVN4F23</v>
           </cell>
           <cell r="B365" t="str">
             <v>SRJ9</v>
@@ -7002,130 +7006,79 @@
             <v>VAMOS</v>
           </cell>
           <cell r="E365">
-            <v>46301</v>
+            <v>46302</v>
           </cell>
         </row>
         <row r="366">
           <cell r="A366" t="str">
-            <v>UVN4F28</v>
+            <v>UCM5G87</v>
           </cell>
           <cell r="B366" t="str">
-            <v>SRJ8</v>
+            <v>SRJ10</v>
           </cell>
           <cell r="C366" t="str">
-            <v>ATIVA</v>
+            <v>SEM DRIVER</v>
           </cell>
           <cell r="D366" t="str">
-            <v>VAMOS</v>
+            <v>TKS</v>
           </cell>
           <cell r="E366">
-            <v>46302</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="367">
           <cell r="A367" t="str">
-            <v>UVN4F21</v>
+            <v>UCM5J77</v>
           </cell>
           <cell r="B367" t="str">
-            <v>SRJ8</v>
+            <v>SMG3</v>
           </cell>
           <cell r="C367" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D367" t="str">
-            <v>VAMOS</v>
+            <v>TKS</v>
           </cell>
           <cell r="E367">
-            <v>46302</v>
+            <v>46303</v>
           </cell>
         </row>
         <row r="368">
           <cell r="A368" t="str">
-            <v>UVN4F23</v>
+            <v>TXO1C04</v>
           </cell>
           <cell r="B368" t="str">
-            <v>SRJ9</v>
+            <v>SES1</v>
           </cell>
           <cell r="C368" t="str">
             <v>ATIVA</v>
           </cell>
           <cell r="D368" t="str">
-            <v>VAMOS</v>
+            <v>LOCALIZA</v>
           </cell>
           <cell r="E368">
-            <v>46302</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="369">
           <cell r="A369" t="str">
-            <v>UCM5G87</v>
+            <v>UVW1D21</v>
           </cell>
           <cell r="B369" t="str">
-            <v>SRJ10</v>
+            <v>SRJ9</v>
           </cell>
           <cell r="C369" t="str">
-            <v>SEM DRIVER</v>
+            <v>ATIVA</v>
           </cell>
           <cell r="D369" t="str">
-            <v>TKS</v>
+            <v>VAMOS</v>
           </cell>
           <cell r="E369">
             <v>0</v>
           </cell>
         </row>
-        <row r="370">
-          <cell r="A370" t="str">
-            <v>UCM5J77</v>
-          </cell>
-          <cell r="B370" t="str">
-            <v>SMG3</v>
-          </cell>
-          <cell r="C370" t="str">
-            <v>ATIVA</v>
-          </cell>
-          <cell r="D370" t="str">
-            <v>TKS</v>
-          </cell>
-          <cell r="E370">
-            <v>46302</v>
-          </cell>
-        </row>
-        <row r="371">
-          <cell r="A371" t="str">
-            <v>TXO1C04</v>
-          </cell>
-          <cell r="B371" t="str">
-            <v>SES1</v>
-          </cell>
-          <cell r="C371" t="str">
-            <v>ATIVA</v>
-          </cell>
-          <cell r="D371" t="str">
-            <v>LOCALIZA</v>
-          </cell>
-          <cell r="E371">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="372">
-          <cell r="A372" t="str">
-            <v>UVW1D21</v>
-          </cell>
-          <cell r="B372" t="str">
-            <v>SRJ9</v>
-          </cell>
-          <cell r="C372" t="str">
-            <v>ATIVA</v>
-          </cell>
-          <cell r="D372" t="str">
-            <v>VAMOS</v>
-          </cell>
-          <cell r="E372">
-            <v>0</v>
-          </cell>
-        </row>
       </sheetData>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="8"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7492,7 +7445,7 @@
       </c>
       <c r="R1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -7500,8 +7453,8 @@
         <v>9</v>
       </c>
       <c r="B2" s="2">
-        <f>VLOOKUP(A2,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A2,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C2">
         <f ca="1">B2-$R$1</f>
@@ -7553,12 +7506,12 @@
         <v>14</v>
       </c>
       <c r="B3" s="2">
-        <f>VLOOKUP(A3,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46301</v>
+        <f>VLOOKUP(A3,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C66" ca="1" si="0">B3-$R$1</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D3" t="s">
         <v>186</v>
@@ -7606,12 +7559,12 @@
         <v>15</v>
       </c>
       <c r="B4" s="2">
-        <f>VLOOKUP(A4,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A4,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D4" t="s">
         <v>186</v>
@@ -7659,8 +7612,8 @@
         <v>16</v>
       </c>
       <c r="B5" s="2">
-        <f>VLOOKUP(A5,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A5,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
@@ -7712,12 +7665,12 @@
         <v>18</v>
       </c>
       <c r="B6" s="2">
-        <f>VLOOKUP(A6,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46296</v>
+        <f>VLOOKUP(A6,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="D6" t="s">
         <v>186</v>
@@ -7765,12 +7718,12 @@
         <v>19</v>
       </c>
       <c r="B7" s="2">
-        <f>VLOOKUP(A7,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A7,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D7" t="s">
         <v>186</v>
@@ -7818,8 +7771,8 @@
         <v>20</v>
       </c>
       <c r="B8" s="2">
-        <f>VLOOKUP(A8,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A8,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
@@ -7871,12 +7824,12 @@
         <v>21</v>
       </c>
       <c r="B9" s="2">
-        <f>VLOOKUP(A9,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A9,'[1]13.10'!$A:$E,5,0)</f>
         <v>46300</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D9" t="s">
         <v>186</v>
@@ -7924,12 +7877,12 @@
         <v>22</v>
       </c>
       <c r="B10" s="2">
-        <f>VLOOKUP(A10,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46301</v>
+        <f>VLOOKUP(A10,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D10" t="s">
         <v>186</v>
@@ -7979,8 +7932,8 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <f>VLOOKUP(A11,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A11,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
@@ -8034,12 +7987,12 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <f>VLOOKUP(A12,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A12,'[1]13.10'!$A:$E,5,0)</f>
         <v>46298</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D12" t="s">
         <v>186</v>
@@ -8089,8 +8042,8 @@
         <v>32</v>
       </c>
       <c r="B13" s="2">
-        <f>VLOOKUP(A13,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A13,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
@@ -8144,8 +8097,8 @@
         <v>37</v>
       </c>
       <c r="B14" s="2">
-        <f>VLOOKUP(A14,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A14,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
@@ -8199,8 +8152,8 @@
         <v>38</v>
       </c>
       <c r="B15" s="2">
-        <f>VLOOKUP(A15,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A15,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
@@ -8254,8 +8207,8 @@
         <v>39</v>
       </c>
       <c r="B16" s="2">
-        <f>VLOOKUP(A16,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A16,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
@@ -8309,8 +8262,8 @@
         <v>40</v>
       </c>
       <c r="B17" s="2">
-        <f>VLOOKUP(A17,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A17,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
@@ -8364,8 +8317,8 @@
         <v>41</v>
       </c>
       <c r="B18" s="2">
-        <f>VLOOKUP(A18,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A18,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
@@ -8419,8 +8372,8 @@
         <v>42</v>
       </c>
       <c r="B19" s="2">
-        <f>VLOOKUP(A19,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A19,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
@@ -8474,8 +8427,8 @@
         <v>43</v>
       </c>
       <c r="B20" s="2">
-        <f>VLOOKUP(A20,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A20,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
@@ -8529,12 +8482,12 @@
         <v>44</v>
       </c>
       <c r="B21" s="2">
-        <f>VLOOKUP(A21,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A21,'[1]13.10'!$A:$E,5,0)</f>
         <v>46300</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D21" t="s">
         <v>186</v>
@@ -8584,12 +8537,12 @@
         <v>45</v>
       </c>
       <c r="B22" s="2">
-        <f>VLOOKUP(A22,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A22,'[1]13.10'!$A:$E,5,0)</f>
         <v>46301</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D22" t="s">
         <v>186</v>
@@ -8639,12 +8592,12 @@
         <v>47</v>
       </c>
       <c r="B23" s="2">
-        <f>VLOOKUP(A23,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A23,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D23" t="s">
         <v>186</v>
@@ -8694,12 +8647,12 @@
         <v>48</v>
       </c>
       <c r="B24" s="2">
-        <f>VLOOKUP(A24,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46301</v>
+        <f>VLOOKUP(A24,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D24" t="s">
         <v>186</v>
@@ -8749,8 +8702,8 @@
         <v>49</v>
       </c>
       <c r="B25" s="2">
-        <f>VLOOKUP(A25,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A25,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="0"/>
@@ -8804,12 +8757,12 @@
         <v>50</v>
       </c>
       <c r="B26" s="2">
-        <f>VLOOKUP(A26,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A26,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D26" t="s">
         <v>186</v>
@@ -8859,12 +8812,12 @@
         <v>51</v>
       </c>
       <c r="B27" s="2">
-        <f>VLOOKUP(A27,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A27,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D27" t="s">
         <v>186</v>
@@ -8914,12 +8867,12 @@
         <v>52</v>
       </c>
       <c r="B28" s="2">
-        <f>VLOOKUP(A28,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46301</v>
+        <f>VLOOKUP(A28,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D28" t="s">
         <v>186</v>
@@ -8969,8 +8922,8 @@
         <v>53</v>
       </c>
       <c r="B29" s="2">
-        <f>VLOOKUP(A29,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A29,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="0"/>
@@ -9024,12 +8977,12 @@
         <v>54</v>
       </c>
       <c r="B30" s="2">
-        <f>VLOOKUP(A30,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A30,'[1]13.10'!$A:$E,5,0)</f>
         <v>46284</v>
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="0"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="D30" t="s">
         <v>186</v>
@@ -9079,12 +9032,12 @@
         <v>55</v>
       </c>
       <c r="B31" s="2">
-        <f>VLOOKUP(A31,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A31,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D31" t="s">
         <v>186</v>
@@ -9134,8 +9087,8 @@
         <v>56</v>
       </c>
       <c r="B32" s="2">
-        <f>VLOOKUP(A32,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A32,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="0"/>
@@ -9189,12 +9142,12 @@
         <v>57</v>
       </c>
       <c r="B33" s="2">
-        <f>VLOOKUP(A33,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A33,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D33" t="s">
         <v>186</v>
@@ -9244,8 +9197,8 @@
         <v>58</v>
       </c>
       <c r="B34" s="2">
-        <f>VLOOKUP(A34,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A34,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="0"/>
@@ -9299,12 +9252,12 @@
         <v>59</v>
       </c>
       <c r="B35" s="2">
-        <f>VLOOKUP(A35,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46300</v>
+        <f>VLOOKUP(A35,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D35" t="s">
         <v>186</v>
@@ -9354,12 +9307,12 @@
         <v>60</v>
       </c>
       <c r="B36" s="2">
-        <f>VLOOKUP(A36,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A36,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D36" t="s">
         <v>186</v>
@@ -9409,12 +9362,12 @@
         <v>61</v>
       </c>
       <c r="B37" s="2">
-        <f>VLOOKUP(A37,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A37,'[1]13.10'!$A:$E,5,0)</f>
         <v>46266</v>
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="0"/>
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="D37" t="s">
         <v>186</v>
@@ -9464,8 +9417,8 @@
         <v>63</v>
       </c>
       <c r="B38" s="2">
-        <f>VLOOKUP(A38,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A38,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="0"/>
@@ -9519,8 +9472,8 @@
         <v>64</v>
       </c>
       <c r="B39" s="2">
-        <f>VLOOKUP(A39,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A39,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="0"/>
@@ -9574,8 +9527,8 @@
         <v>65</v>
       </c>
       <c r="B40" s="2">
-        <f>VLOOKUP(A40,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A40,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="0"/>
@@ -9629,12 +9582,12 @@
         <v>66</v>
       </c>
       <c r="B41" s="2">
-        <f>VLOOKUP(A41,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A41,'[1]13.10'!$A:$E,5,0)</f>
         <v>46300</v>
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D41" t="s">
         <v>186</v>
@@ -9684,8 +9637,8 @@
         <v>67</v>
       </c>
       <c r="B42" s="2">
-        <f>VLOOKUP(A42,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A42,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="0"/>
@@ -9739,8 +9692,8 @@
         <v>68</v>
       </c>
       <c r="B43" s="2">
-        <f>VLOOKUP(A43,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A43,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="0"/>
@@ -9794,12 +9747,12 @@
         <v>69</v>
       </c>
       <c r="B44" s="2">
-        <f>VLOOKUP(A44,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46301</v>
+        <f>VLOOKUP(A44,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D44" t="s">
         <v>186</v>
@@ -9849,8 +9802,8 @@
         <v>70</v>
       </c>
       <c r="B45" s="2">
-        <f>VLOOKUP(A45,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A45,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="0"/>
@@ -9904,8 +9857,8 @@
         <v>71</v>
       </c>
       <c r="B46" s="2">
-        <f>VLOOKUP(A46,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A46,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="0"/>
@@ -9959,8 +9912,8 @@
         <v>72</v>
       </c>
       <c r="B47" s="2">
-        <f>VLOOKUP(A47,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A47,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="0"/>
@@ -10014,12 +9967,12 @@
         <v>73</v>
       </c>
       <c r="B48" s="2">
-        <f>VLOOKUP(A48,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A48,'[1]13.10'!$A:$E,5,0)</f>
         <v>46300</v>
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D48" t="s">
         <v>186</v>
@@ -10069,8 +10022,8 @@
         <v>74</v>
       </c>
       <c r="B49" s="2">
-        <f>VLOOKUP(A49,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A49,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="0"/>
@@ -10124,8 +10077,8 @@
         <v>75</v>
       </c>
       <c r="B50" s="2">
-        <f>VLOOKUP(A50,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A50,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="0"/>
@@ -10179,8 +10132,8 @@
         <v>76</v>
       </c>
       <c r="B51" s="2">
-        <f>VLOOKUP(A51,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A51,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="0"/>
@@ -10234,8 +10187,8 @@
         <v>77</v>
       </c>
       <c r="B52" s="2">
-        <f>VLOOKUP(A52,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A52,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="0"/>
@@ -10289,8 +10242,8 @@
         <v>78</v>
       </c>
       <c r="B53" s="2">
-        <f>VLOOKUP(A53,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A53,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="0"/>
@@ -10344,8 +10297,8 @@
         <v>79</v>
       </c>
       <c r="B54" s="2">
-        <f>VLOOKUP(A54,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A54,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="0"/>
@@ -10399,8 +10352,8 @@
         <v>80</v>
       </c>
       <c r="B55" s="2">
-        <f>VLOOKUP(A55,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A55,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="0"/>
@@ -10454,12 +10407,12 @@
         <v>81</v>
       </c>
       <c r="B56" s="2">
-        <f>VLOOKUP(A56,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A56,'[1]13.10'!$A:$E,5,0)</f>
         <v>46296</v>
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D56" t="s">
         <v>186</v>
@@ -10509,12 +10462,12 @@
         <v>82</v>
       </c>
       <c r="B57" s="2">
-        <f>VLOOKUP(A57,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A57,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D57" t="s">
         <v>186</v>
@@ -10564,12 +10517,12 @@
         <v>83</v>
       </c>
       <c r="B58" s="2">
-        <f>VLOOKUP(A58,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46301</v>
+        <f>VLOOKUP(A58,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D58" t="s">
         <v>186</v>
@@ -10619,8 +10572,8 @@
         <v>84</v>
       </c>
       <c r="B59" s="2">
-        <f>VLOOKUP(A59,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A59,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="0"/>
@@ -10674,8 +10627,8 @@
         <v>85</v>
       </c>
       <c r="B60" s="2">
-        <f>VLOOKUP(A60,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A60,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="0"/>
@@ -10729,8 +10682,8 @@
         <v>86</v>
       </c>
       <c r="B61" s="2">
-        <f>VLOOKUP(A61,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A61,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="0"/>
@@ -10784,8 +10737,8 @@
         <v>87</v>
       </c>
       <c r="B62" s="2">
-        <f>VLOOKUP(A62,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A62,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="0"/>
@@ -10839,12 +10792,12 @@
         <v>88</v>
       </c>
       <c r="B63" s="2">
-        <f>VLOOKUP(A63,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46301</v>
+        <f>VLOOKUP(A63,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D63" t="s">
         <v>186</v>
@@ -10894,8 +10847,8 @@
         <v>92</v>
       </c>
       <c r="B64" s="2">
-        <f>VLOOKUP(A64,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A64,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="0"/>
@@ -10949,12 +10902,12 @@
         <v>94</v>
       </c>
       <c r="B65" s="2">
-        <f>VLOOKUP(A65,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A65,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D65" t="s">
         <v>186</v>
@@ -11004,12 +10957,12 @@
         <v>95</v>
       </c>
       <c r="B66" s="2">
-        <f>VLOOKUP(A66,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A66,'[1]13.10'!$A:$E,5,0)</f>
         <v>46290</v>
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="0"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D66" t="s">
         <v>186</v>
@@ -11059,12 +11012,12 @@
         <v>96</v>
       </c>
       <c r="B67" s="2">
-        <f>VLOOKUP(A67,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A67,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C67">
         <f t="shared" ref="C67:C130" ca="1" si="1">B67-$R$1</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D67" t="s">
         <v>186</v>
@@ -11114,12 +11067,12 @@
         <v>97</v>
       </c>
       <c r="B68" s="2">
-        <f>VLOOKUP(A68,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A68,'[1]13.10'!$A:$E,5,0)</f>
         <v>46255</v>
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="1"/>
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="D68" t="s">
         <v>186</v>
@@ -11169,12 +11122,12 @@
         <v>98</v>
       </c>
       <c r="B69" s="2">
-        <f>VLOOKUP(A69,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A69,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D69" t="s">
         <v>186</v>
@@ -11224,8 +11177,8 @@
         <v>99</v>
       </c>
       <c r="B70" s="2">
-        <f>VLOOKUP(A70,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A70,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="1"/>
@@ -11279,8 +11232,8 @@
         <v>100</v>
       </c>
       <c r="B71" s="2">
-        <f>VLOOKUP(A71,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A71,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="1"/>
@@ -11334,12 +11287,12 @@
         <v>101</v>
       </c>
       <c r="B72" s="2">
-        <f>VLOOKUP(A72,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A72,'[1]13.10'!$A:$E,5,0)</f>
         <v>46272</v>
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="1"/>
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -11389,8 +11342,8 @@
         <v>102</v>
       </c>
       <c r="B73" s="2">
-        <f>VLOOKUP(A73,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A73,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="1"/>
@@ -11444,8 +11397,8 @@
         <v>104</v>
       </c>
       <c r="B74" s="2">
-        <f>VLOOKUP(A74,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A74,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="1"/>
@@ -11499,8 +11452,8 @@
         <v>105</v>
       </c>
       <c r="B75" s="2">
-        <f>VLOOKUP(A75,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A75,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="1"/>
@@ -11554,8 +11507,8 @@
         <v>106</v>
       </c>
       <c r="B76" s="2">
-        <f>VLOOKUP(A76,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A76,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="1"/>
@@ -11609,8 +11562,8 @@
         <v>107</v>
       </c>
       <c r="B77" s="2">
-        <f>VLOOKUP(A77,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A77,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="1"/>
@@ -11664,12 +11617,12 @@
         <v>108</v>
       </c>
       <c r="B78" s="2">
-        <f>VLOOKUP(A78,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A78,'[1]13.10'!$A:$E,5,0)</f>
         <v>46288</v>
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="1"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D78" t="s">
         <v>186</v>
@@ -11719,7 +11672,7 @@
         <v>109</v>
       </c>
       <c r="B79" s="2" t="e">
-        <f>VLOOKUP(A79,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A79,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C79" t="e">
@@ -11774,8 +11727,8 @@
         <v>110</v>
       </c>
       <c r="B80" s="2">
-        <f>VLOOKUP(A80,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A80,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="1"/>
@@ -11829,7 +11782,7 @@
         <v>111</v>
       </c>
       <c r="B81" s="2" t="e">
-        <f>VLOOKUP(A81,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A81,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C81" t="e">
@@ -11884,7 +11837,7 @@
         <v>112</v>
       </c>
       <c r="B82" s="2" t="e">
-        <f>VLOOKUP(A82,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A82,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C82" t="e">
@@ -11939,8 +11892,8 @@
         <v>113</v>
       </c>
       <c r="B83" s="2">
-        <f>VLOOKUP(A83,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A83,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="1"/>
@@ -11994,8 +11947,8 @@
         <v>114</v>
       </c>
       <c r="B84" s="2">
-        <f>VLOOKUP(A84,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A84,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="1"/>
@@ -12049,8 +12002,8 @@
         <v>115</v>
       </c>
       <c r="B85" s="2">
-        <f>VLOOKUP(A85,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A85,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="1"/>
@@ -12104,8 +12057,8 @@
         <v>116</v>
       </c>
       <c r="B86" s="2">
-        <f>VLOOKUP(A86,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A86,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="1"/>
@@ -12159,7 +12112,7 @@
         <v>117</v>
       </c>
       <c r="B87" s="2" t="e">
-        <f>VLOOKUP(A87,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A87,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C87" t="e">
@@ -12214,8 +12167,8 @@
         <v>118</v>
       </c>
       <c r="B88" s="2">
-        <f>VLOOKUP(A88,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A88,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="1"/>
@@ -12269,8 +12222,8 @@
         <v>119</v>
       </c>
       <c r="B89" s="2">
-        <f>VLOOKUP(A89,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A89,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="1"/>
@@ -12324,8 +12277,8 @@
         <v>123</v>
       </c>
       <c r="B90" s="2">
-        <f>VLOOKUP(A90,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A90,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="1"/>
@@ -12379,8 +12332,8 @@
         <v>124</v>
       </c>
       <c r="B91" s="2">
-        <f>VLOOKUP(A91,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A91,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="1"/>
@@ -12434,12 +12387,12 @@
         <v>125</v>
       </c>
       <c r="B92" s="2">
-        <f>VLOOKUP(A92,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A92,'[1]13.10'!$A:$E,5,0)</f>
         <v>46281</v>
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="1"/>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -12489,8 +12442,8 @@
         <v>126</v>
       </c>
       <c r="B93" s="2">
-        <f>VLOOKUP(A93,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A93,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="1"/>
@@ -12544,8 +12497,8 @@
         <v>127</v>
       </c>
       <c r="B94" s="2">
-        <f>VLOOKUP(A94,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A94,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="1"/>
@@ -12599,8 +12552,8 @@
         <v>128</v>
       </c>
       <c r="B95" s="2">
-        <f>VLOOKUP(A95,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A95,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="1"/>
@@ -12654,8 +12607,8 @@
         <v>129</v>
       </c>
       <c r="B96" s="2">
-        <f>VLOOKUP(A96,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A96,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="1"/>
@@ -12709,12 +12662,12 @@
         <v>130</v>
       </c>
       <c r="B97" s="2">
-        <f>VLOOKUP(A97,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A97,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D97" t="s">
         <v>186</v>
@@ -12764,8 +12717,8 @@
         <v>131</v>
       </c>
       <c r="B98" s="2">
-        <f>VLOOKUP(A98,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A98,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="1"/>
@@ -12819,8 +12772,8 @@
         <v>132</v>
       </c>
       <c r="B99" s="2">
-        <f>VLOOKUP(A99,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A99,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="1"/>
@@ -12874,8 +12827,8 @@
         <v>133</v>
       </c>
       <c r="B100" s="2">
-        <f>VLOOKUP(A100,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A100,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="1"/>
@@ -12929,8 +12882,8 @@
         <v>134</v>
       </c>
       <c r="B101" s="2">
-        <f>VLOOKUP(A101,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A101,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="1"/>
@@ -12984,8 +12937,8 @@
         <v>135</v>
       </c>
       <c r="B102" s="2">
-        <f>VLOOKUP(A102,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A102,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C102">
         <f t="shared" ca="1" si="1"/>
@@ -13039,8 +12992,8 @@
         <v>136</v>
       </c>
       <c r="B103" s="2">
-        <f>VLOOKUP(A103,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A103,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C103">
         <f t="shared" ca="1" si="1"/>
@@ -13094,8 +13047,8 @@
         <v>137</v>
       </c>
       <c r="B104" s="2">
-        <f>VLOOKUP(A104,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A104,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C104">
         <f t="shared" ca="1" si="1"/>
@@ -13149,8 +13102,8 @@
         <v>138</v>
       </c>
       <c r="B105" s="2">
-        <f>VLOOKUP(A105,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A105,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C105">
         <f t="shared" ca="1" si="1"/>
@@ -13204,8 +13157,8 @@
         <v>139</v>
       </c>
       <c r="B106" s="2">
-        <f>VLOOKUP(A106,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A106,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C106">
         <f t="shared" ca="1" si="1"/>
@@ -13259,8 +13212,8 @@
         <v>140</v>
       </c>
       <c r="B107" s="2">
-        <f>VLOOKUP(A107,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A107,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C107">
         <f t="shared" ca="1" si="1"/>
@@ -13314,12 +13267,12 @@
         <v>141</v>
       </c>
       <c r="B108" s="2">
-        <f>VLOOKUP(A108,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A108,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C108">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
@@ -13369,8 +13322,8 @@
         <v>142</v>
       </c>
       <c r="B109" s="2">
-        <f>VLOOKUP(A109,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A109,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C109">
         <f t="shared" ca="1" si="1"/>
@@ -13424,12 +13377,12 @@
         <v>143</v>
       </c>
       <c r="B110" s="2">
-        <f>VLOOKUP(A110,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A110,'[1]13.10'!$A:$E,5,0)</f>
         <v>0</v>
       </c>
       <c r="C110">
         <f t="shared" ca="1" si="1"/>
-        <v>-46303</v>
+        <v>-46304</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -13479,8 +13432,8 @@
         <v>144</v>
       </c>
       <c r="B111" s="2">
-        <f>VLOOKUP(A111,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A111,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C111">
         <f t="shared" ca="1" si="1"/>
@@ -13534,7 +13487,7 @@
         <v>187</v>
       </c>
       <c r="B112" s="2" t="e">
-        <f>VLOOKUP(A112,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A112,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C112" t="e">
@@ -13567,8 +13520,8 @@
         <v>145</v>
       </c>
       <c r="B113" s="2">
-        <f>VLOOKUP(A113,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A113,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C113">
         <f t="shared" ca="1" si="1"/>
@@ -13622,12 +13575,12 @@
         <v>146</v>
       </c>
       <c r="B114" s="2">
-        <f>VLOOKUP(A114,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46288</v>
+        <f>VLOOKUP(A114,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C114">
         <f t="shared" ca="1" si="1"/>
-        <v>-15</v>
+        <v>-1</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -13677,8 +13630,8 @@
         <v>147</v>
       </c>
       <c r="B115" s="2">
-        <f>VLOOKUP(A115,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A115,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C115">
         <f t="shared" ca="1" si="1"/>
@@ -13732,8 +13685,8 @@
         <v>149</v>
       </c>
       <c r="B116" s="2">
-        <f>VLOOKUP(A116,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A116,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C116">
         <f t="shared" ca="1" si="1"/>
@@ -13787,8 +13740,8 @@
         <v>150</v>
       </c>
       <c r="B117" s="2">
-        <f>VLOOKUP(A117,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A117,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C117">
         <f t="shared" ca="1" si="1"/>
@@ -13842,8 +13795,8 @@
         <v>151</v>
       </c>
       <c r="B118" s="2">
-        <f>VLOOKUP(A118,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A118,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C118">
         <f t="shared" ca="1" si="1"/>
@@ -13897,8 +13850,8 @@
         <v>152</v>
       </c>
       <c r="B119" s="2">
-        <f>VLOOKUP(A119,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A119,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C119">
         <f t="shared" ca="1" si="1"/>
@@ -13952,12 +13905,12 @@
         <v>153</v>
       </c>
       <c r="B120" s="2">
-        <f>VLOOKUP(A120,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46301</v>
+        <f>VLOOKUP(A120,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C120">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D120" t="s">
         <v>186</v>
@@ -14007,12 +13960,12 @@
         <v>154</v>
       </c>
       <c r="B121" s="2">
-        <f>VLOOKUP(A121,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A121,'[1]13.10'!$A:$E,5,0)</f>
         <v>0</v>
       </c>
       <c r="C121">
         <f t="shared" ca="1" si="1"/>
-        <v>-46303</v>
+        <v>-46304</v>
       </c>
       <c r="J121" t="s">
         <v>120</v>
@@ -14042,12 +13995,12 @@
         <v>156</v>
       </c>
       <c r="B122" s="2">
-        <f>VLOOKUP(A122,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46289</v>
+        <f>VLOOKUP(A122,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C122">
         <f t="shared" ca="1" si="1"/>
-        <v>-14</v>
+        <v>-1</v>
       </c>
       <c r="D122" t="s">
         <v>186</v>
@@ -14097,8 +14050,8 @@
         <v>157</v>
       </c>
       <c r="B123" s="2">
-        <f>VLOOKUP(A123,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A123,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C123">
         <f t="shared" ca="1" si="1"/>
@@ -14152,8 +14105,8 @@
         <v>158</v>
       </c>
       <c r="B124" s="2">
-        <f>VLOOKUP(A124,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A124,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C124">
         <f t="shared" ca="1" si="1"/>
@@ -14207,8 +14160,8 @@
         <v>159</v>
       </c>
       <c r="B125" s="2">
-        <f>VLOOKUP(A125,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A125,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C125">
         <f t="shared" ca="1" si="1"/>
@@ -14262,8 +14215,8 @@
         <v>160</v>
       </c>
       <c r="B126" s="2">
-        <f>VLOOKUP(A126,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A126,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C126">
         <f t="shared" ca="1" si="1"/>
@@ -14317,12 +14270,12 @@
         <v>161</v>
       </c>
       <c r="B127" s="2">
-        <f>VLOOKUP(A127,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46301</v>
+        <f>VLOOKUP(A127,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C127">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D127" t="s">
         <v>186</v>
@@ -14372,8 +14325,8 @@
         <v>162</v>
       </c>
       <c r="B128" s="2">
-        <f>VLOOKUP(A128,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A128,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C128">
         <f t="shared" ca="1" si="1"/>
@@ -14427,8 +14380,8 @@
         <v>163</v>
       </c>
       <c r="B129" s="2">
-        <f>VLOOKUP(A129,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A129,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C129">
         <f t="shared" ca="1" si="1"/>
@@ -14482,12 +14435,12 @@
         <v>164</v>
       </c>
       <c r="B130" s="2">
-        <f>VLOOKUP(A130,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A130,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C130">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D130" t="s">
         <v>186</v>
@@ -14537,7 +14490,7 @@
         <v>188</v>
       </c>
       <c r="B131" s="2" t="e">
-        <f>VLOOKUP(A131,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A131,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C131" t="e">
@@ -14590,7 +14543,7 @@
         <v>189</v>
       </c>
       <c r="B132" s="2" t="e">
-        <f>VLOOKUP(A132,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A132,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C132" t="e">
@@ -14623,7 +14576,7 @@
         <v>190</v>
       </c>
       <c r="B133" s="2" t="e">
-        <f>VLOOKUP(A133,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A133,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C133" t="e">
@@ -14656,7 +14609,7 @@
         <v>191</v>
       </c>
       <c r="B134" s="2" t="e">
-        <f>VLOOKUP(A134,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A134,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C134" t="e">
@@ -14689,7 +14642,7 @@
         <v>192</v>
       </c>
       <c r="B135" s="2" t="e">
-        <f>VLOOKUP(A135,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A135,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C135" t="e">
@@ -14722,7 +14675,7 @@
         <v>193</v>
       </c>
       <c r="B136" s="2" t="e">
-        <f>VLOOKUP(A136,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A136,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C136" t="e">
@@ -14755,7 +14708,7 @@
         <v>194</v>
       </c>
       <c r="B137" s="2" t="e">
-        <f>VLOOKUP(A137,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A137,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C137" t="e">
@@ -14788,7 +14741,7 @@
         <v>195</v>
       </c>
       <c r="B138" s="2" t="e">
-        <f>VLOOKUP(A138,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A138,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C138" t="e">
@@ -14821,7 +14774,7 @@
         <v>196</v>
       </c>
       <c r="B139" s="2" t="e">
-        <f>VLOOKUP(A139,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A139,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C139" t="e">
@@ -14854,7 +14807,7 @@
         <v>197</v>
       </c>
       <c r="B140" s="2" t="e">
-        <f>VLOOKUP(A140,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A140,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C140" t="e">
@@ -14887,7 +14840,7 @@
         <v>198</v>
       </c>
       <c r="B141" s="2" t="e">
-        <f>VLOOKUP(A141,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A141,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C141" t="e">
@@ -14920,7 +14873,7 @@
         <v>199</v>
       </c>
       <c r="B142" s="2" t="e">
-        <f>VLOOKUP(A142,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A142,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C142" t="e">
@@ -14950,7 +14903,7 @@
         <v>200</v>
       </c>
       <c r="B143" s="2" t="e">
-        <f>VLOOKUP(A143,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A143,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C143" t="e">
@@ -14983,7 +14936,7 @@
         <v>201</v>
       </c>
       <c r="B144" s="2" t="e">
-        <f>VLOOKUP(A144,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A144,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C144" t="e">
@@ -15016,7 +14969,7 @@
         <v>202</v>
       </c>
       <c r="B145" s="2" t="e">
-        <f>VLOOKUP(A145,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A145,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C145" t="e">
@@ -15049,7 +15002,7 @@
         <v>203</v>
       </c>
       <c r="B146" s="2" t="e">
-        <f>VLOOKUP(A146,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A146,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C146" t="e">
@@ -15082,7 +15035,7 @@
         <v>204</v>
       </c>
       <c r="B147" s="2" t="e">
-        <f>VLOOKUP(A147,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A147,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C147" t="e">
@@ -15115,7 +15068,7 @@
         <v>205</v>
       </c>
       <c r="B148" s="2" t="e">
-        <f>VLOOKUP(A148,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A148,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C148" t="e">
@@ -15148,7 +15101,7 @@
         <v>206</v>
       </c>
       <c r="B149" s="2" t="e">
-        <f>VLOOKUP(A149,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A149,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C149" t="e">
@@ -15180,7 +15133,7 @@
         <v>207</v>
       </c>
       <c r="B150" s="2" t="e">
-        <f>VLOOKUP(A150,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A150,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C150" t="e">
@@ -15213,8 +15166,8 @@
         <v>166</v>
       </c>
       <c r="B151" s="2">
-        <f>VLOOKUP(A151,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A151,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C151">
         <f t="shared" ca="1" si="2"/>
@@ -15268,8 +15221,8 @@
         <v>167</v>
       </c>
       <c r="B152" s="2">
-        <f>VLOOKUP(A152,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A152,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C152">
         <f t="shared" ca="1" si="2"/>
@@ -15323,8 +15276,8 @@
         <v>168</v>
       </c>
       <c r="B153" s="2">
-        <f>VLOOKUP(A153,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A153,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C153">
         <f t="shared" ca="1" si="2"/>
@@ -15378,8 +15331,8 @@
         <v>169</v>
       </c>
       <c r="B154" s="2">
-        <f>VLOOKUP(A154,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A154,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C154">
         <f t="shared" ca="1" si="2"/>
@@ -15433,12 +15386,12 @@
         <v>170</v>
       </c>
       <c r="B155" s="2">
-        <f>VLOOKUP(A155,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A155,'[1]13.10'!$A:$E,5,0)</f>
         <v>46294</v>
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -15488,12 +15441,12 @@
         <v>171</v>
       </c>
       <c r="B156" s="2">
-        <f>VLOOKUP(A156,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A156,'[1]13.10'!$A:$E,5,0)</f>
         <v>46289</v>
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D156" t="s">
         <v>186</v>
@@ -15543,8 +15496,8 @@
         <v>172</v>
       </c>
       <c r="B157" s="2">
-        <f>VLOOKUP(A157,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A157,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
@@ -15598,8 +15551,8 @@
         <v>173</v>
       </c>
       <c r="B158" s="2">
-        <f>VLOOKUP(A158,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A158,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C158">
         <f t="shared" ca="1" si="2"/>
@@ -15653,12 +15606,12 @@
         <v>174</v>
       </c>
       <c r="B159" s="2">
-        <f>VLOOKUP(A159,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A159,'[1]13.10'!$A:$E,5,0)</f>
         <v>46300</v>
       </c>
       <c r="C159">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D159" t="s">
         <v>186</v>
@@ -15708,8 +15661,8 @@
         <v>175</v>
       </c>
       <c r="B160" s="2">
-        <f>VLOOKUP(A160,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46302</v>
+        <f>VLOOKUP(A160,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
@@ -15763,12 +15716,12 @@
         <v>177</v>
       </c>
       <c r="B161" s="2">
-        <f>VLOOKUP(A161,'[1]08.10'!$A:$E,5,0)</f>
-        <v>46301</v>
+        <f>VLOOKUP(A161,'[1]13.10'!$A:$E,5,0)</f>
+        <v>46303</v>
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -15818,12 +15771,12 @@
         <v>178</v>
       </c>
       <c r="B162" s="2">
-        <f>VLOOKUP(A162,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A162,'[1]13.10'!$A:$E,5,0)</f>
         <v>46302</v>
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -15873,7 +15826,7 @@
         <v>208</v>
       </c>
       <c r="B163" s="2" t="e">
-        <f>VLOOKUP(A163,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A163,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C163" t="e">
@@ -15906,7 +15859,7 @@
         <v>209</v>
       </c>
       <c r="B164" s="2" t="e">
-        <f>VLOOKUP(A164,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A164,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C164" t="e">
@@ -15939,12 +15892,12 @@
         <v>210</v>
       </c>
       <c r="B165" s="2">
-        <f>VLOOKUP(A165,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A165,'[1]13.10'!$A:$E,5,0)</f>
         <v>0</v>
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
-        <v>-46303</v>
+        <v>-46304</v>
       </c>
       <c r="J165" t="s">
         <v>176</v>
@@ -15972,7 +15925,7 @@
         <v>211</v>
       </c>
       <c r="B166" s="2" t="e">
-        <f>VLOOKUP(A166,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A166,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C166" t="e">
@@ -16005,7 +15958,7 @@
         <v>212</v>
       </c>
       <c r="B167" s="2" t="e">
-        <f>VLOOKUP(A167,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A167,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C167" t="e">
@@ -16038,7 +15991,7 @@
         <v>213</v>
       </c>
       <c r="B168" s="2" t="e">
-        <f>VLOOKUP(A168,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A168,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C168" t="e">
@@ -16071,7 +16024,7 @@
         <v>214</v>
       </c>
       <c r="B169" s="2" t="e">
-        <f>VLOOKUP(A169,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A169,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C169" t="e">
@@ -16104,7 +16057,7 @@
         <v>215</v>
       </c>
       <c r="B170" s="2" t="e">
-        <f>VLOOKUP(A170,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A170,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C170" t="e">
@@ -16137,7 +16090,7 @@
         <v>216</v>
       </c>
       <c r="B171" s="2" t="e">
-        <f>VLOOKUP(A171,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A171,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C171" t="e">
@@ -16170,7 +16123,7 @@
         <v>217</v>
       </c>
       <c r="B172" s="2" t="e">
-        <f>VLOOKUP(A172,'[1]08.10'!$A:$E,5,0)</f>
+        <f>VLOOKUP(A172,'[1]13.10'!$A:$E,5,0)</f>
         <v>#N/A</v>
       </c>
       <c r="C172" t="e">
@@ -16204,15 +16157,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16477,21 +16427,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16516,9 +16466,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="289" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D26FC5A-B25D-4735-9AB9-0F465880D586}"/>
+  <xr:revisionPtr revIDLastSave="308" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05CC8815-D88A-4741-913B-499228F7DEC3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4706" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4742" uniqueCount="470">
   <si>
     <t>Placa</t>
   </si>
@@ -8834,7 +8834,9 @@
       <c r="O131" t="s">
         <v>217</v>
       </c>
-      <c r="P131" s="2"/>
+      <c r="P131" s="2">
+        <v>46295</v>
+      </c>
       <c r="Q131" s="2">
         <v>46295</v>
       </c>
@@ -8850,6 +8852,24 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D132" t="s">
+        <v>184</v>
+      </c>
+      <c r="E132" t="s">
+        <v>184</v>
+      </c>
+      <c r="F132" t="s">
+        <v>184</v>
+      </c>
+      <c r="G132" t="s">
+        <v>184</v>
+      </c>
+      <c r="H132" t="s">
+        <v>184</v>
+      </c>
+      <c r="I132" t="s">
+        <v>184</v>
+      </c>
       <c r="J132" t="s">
         <v>163</v>
       </c>
@@ -8868,8 +8888,12 @@
       <c r="O132" t="s">
         <v>217</v>
       </c>
-      <c r="P132" s="2"/>
-      <c r="Q132" s="2"/>
+      <c r="P132" s="2">
+        <v>46295</v>
+      </c>
+      <c r="Q132" s="2">
+        <v>46295</v>
+      </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
@@ -8882,6 +8906,24 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D133" t="s">
+        <v>184</v>
+      </c>
+      <c r="E133" t="s">
+        <v>184</v>
+      </c>
+      <c r="F133" t="s">
+        <v>184</v>
+      </c>
+      <c r="G133" t="s">
+        <v>184</v>
+      </c>
+      <c r="H133" t="s">
+        <v>184</v>
+      </c>
+      <c r="I133" t="s">
+        <v>184</v>
+      </c>
       <c r="J133" t="s">
         <v>163</v>
       </c>
@@ -8900,8 +8942,12 @@
       <c r="O133" t="s">
         <v>217</v>
       </c>
-      <c r="P133" s="2"/>
-      <c r="Q133" s="2"/>
+      <c r="P133" s="2">
+        <v>46295</v>
+      </c>
+      <c r="Q133" s="2">
+        <v>46295</v>
+      </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
@@ -8914,6 +8960,24 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D134" t="s">
+        <v>184</v>
+      </c>
+      <c r="E134" t="s">
+        <v>184</v>
+      </c>
+      <c r="F134" t="s">
+        <v>184</v>
+      </c>
+      <c r="G134" t="s">
+        <v>184</v>
+      </c>
+      <c r="H134" t="s">
+        <v>184</v>
+      </c>
+      <c r="I134" t="s">
+        <v>184</v>
+      </c>
       <c r="J134" t="s">
         <v>163</v>
       </c>
@@ -8932,8 +8996,12 @@
       <c r="O134" t="s">
         <v>217</v>
       </c>
-      <c r="P134" s="2"/>
-      <c r="Q134" s="2"/>
+      <c r="P134" s="2">
+        <v>46295</v>
+      </c>
+      <c r="Q134" s="2">
+        <v>46295</v>
+      </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
@@ -8946,6 +9014,24 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D135" t="s">
+        <v>184</v>
+      </c>
+      <c r="E135" t="s">
+        <v>184</v>
+      </c>
+      <c r="F135" t="s">
+        <v>184</v>
+      </c>
+      <c r="G135" t="s">
+        <v>184</v>
+      </c>
+      <c r="H135" t="s">
+        <v>184</v>
+      </c>
+      <c r="I135" t="s">
+        <v>184</v>
+      </c>
       <c r="J135" t="s">
         <v>163</v>
       </c>
@@ -8964,8 +9050,12 @@
       <c r="O135" t="s">
         <v>217</v>
       </c>
-      <c r="P135" s="2"/>
-      <c r="Q135" s="2"/>
+      <c r="P135" s="2">
+        <v>46295</v>
+      </c>
+      <c r="Q135" s="2">
+        <v>46295</v>
+      </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
@@ -8978,6 +9068,24 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D136" t="s">
+        <v>184</v>
+      </c>
+      <c r="E136" t="s">
+        <v>184</v>
+      </c>
+      <c r="F136" t="s">
+        <v>184</v>
+      </c>
+      <c r="G136" t="s">
+        <v>184</v>
+      </c>
+      <c r="H136" t="s">
+        <v>184</v>
+      </c>
+      <c r="I136" t="s">
+        <v>184</v>
+      </c>
       <c r="J136" t="s">
         <v>163</v>
       </c>
@@ -8996,8 +9104,12 @@
       <c r="O136" t="s">
         <v>217</v>
       </c>
-      <c r="P136" s="2"/>
-      <c r="Q136" s="2"/>
+      <c r="P136" s="2">
+        <v>46295</v>
+      </c>
+      <c r="Q136" s="2">
+        <v>46295</v>
+      </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
@@ -9010,6 +9122,24 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D137" t="s">
+        <v>184</v>
+      </c>
+      <c r="E137" t="s">
+        <v>184</v>
+      </c>
+      <c r="F137" t="s">
+        <v>184</v>
+      </c>
+      <c r="G137" t="s">
+        <v>184</v>
+      </c>
+      <c r="H137" t="s">
+        <v>184</v>
+      </c>
+      <c r="I137" t="s">
+        <v>184</v>
+      </c>
       <c r="J137" t="s">
         <v>163</v>
       </c>
@@ -9028,8 +9158,12 @@
       <c r="O137" t="s">
         <v>217</v>
       </c>
-      <c r="P137" s="2"/>
-      <c r="Q137" s="2"/>
+      <c r="P137" s="2">
+        <v>46295</v>
+      </c>
+      <c r="Q137" s="2">
+        <v>46295</v>
+      </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
@@ -9092,8 +9226,12 @@
       <c r="O139" t="s">
         <v>217</v>
       </c>
-      <c r="P139" s="2"/>
-      <c r="Q139" s="2"/>
+      <c r="P139" s="2">
+        <v>46310</v>
+      </c>
+      <c r="Q139" s="2">
+        <v>46310</v>
+      </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
@@ -21663,6 +21801,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -21923,18 +22073,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
   <ds:schemaRefs>
@@ -21944,6 +22082,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21960,15 +22109,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="308" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05CC8815-D88A-4741-913B-499228F7DEC3}"/>
+  <xr:revisionPtr revIDLastSave="313" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3B58E4C-0EDB-4B4A-A0B7-54D968BCC70B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4742" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4754" uniqueCount="470">
   <si>
     <t>Placa</t>
   </si>
@@ -9563,6 +9563,24 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D150" t="s">
+        <v>184</v>
+      </c>
+      <c r="E150" t="s">
+        <v>184</v>
+      </c>
+      <c r="F150" t="s">
+        <v>184</v>
+      </c>
+      <c r="G150" t="s">
+        <v>184</v>
+      </c>
+      <c r="H150" t="s">
+        <v>184</v>
+      </c>
+      <c r="I150" t="s">
+        <v>184</v>
+      </c>
       <c r="J150" t="s">
         <v>22</v>
       </c>
@@ -10441,6 +10459,24 @@
       <c r="C169" t="e">
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
+      </c>
+      <c r="D169" t="s">
+        <v>184</v>
+      </c>
+      <c r="E169" t="s">
+        <v>184</v>
+      </c>
+      <c r="F169" t="s">
+        <v>184</v>
+      </c>
+      <c r="G169" t="s">
+        <v>184</v>
+      </c>
+      <c r="H169" t="s">
+        <v>184</v>
+      </c>
+      <c r="I169" t="s">
+        <v>184</v>
       </c>
       <c r="J169" t="s">
         <v>22</v>
@@ -21792,15 +21828,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -21810,6 +21837,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22074,20 +22110,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="313" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3B58E4C-0EDB-4B4A-A0B7-54D968BCC70B}"/>
+  <xr:revisionPtr revIDLastSave="316" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B8FF1C4-7F77-492D-8EB0-04250E7C32C9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4754" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4756" uniqueCount="470">
   <si>
     <t>Placa</t>
   </si>
@@ -9208,6 +9208,12 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D139" t="s">
+        <v>184</v>
+      </c>
+      <c r="I139" t="s">
+        <v>184</v>
+      </c>
       <c r="J139" t="s">
         <v>28</v>
       </c>
@@ -21828,6 +21834,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -21837,15 +21852,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22110,20 +22116,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="316" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B8FF1C4-7F77-492D-8EB0-04250E7C32C9}"/>
+  <xr:revisionPtr revIDLastSave="319" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{932C7D90-40A6-4D66-92CB-6BC3A58B9017}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="R1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C2">
         <f ca="1">B2-$R$1</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D2" t="s">
         <v>184</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C66" ca="1" si="0">B3-$R$1</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D3" t="s">
         <v>184</v>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D4" t="s">
         <v>184</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D5" t="s">
         <v>184</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D6" t="s">
         <v>184</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D7" t="s">
         <v>184</v>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D8" t="s">
         <v>184</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D9" t="s">
         <v>184</v>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D10" t="s">
         <v>184</v>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D11" t="s">
         <v>184</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D12" t="s">
         <v>184</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D13" t="s">
         <v>184</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D14" t="s">
         <v>184</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D15" t="s">
         <v>184</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D16" t="s">
         <v>184</v>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D17" t="s">
         <v>184</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D18" t="s">
         <v>184</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D19" t="s">
         <v>184</v>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D20" t="s">
         <v>184</v>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D21" t="s">
         <v>184</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D22" t="s">
         <v>184</v>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D23" t="s">
         <v>184</v>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D24" t="s">
         <v>184</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D25" t="s">
         <v>184</v>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D26" t="s">
         <v>184</v>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D27" t="s">
         <v>184</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D28" t="s">
         <v>184</v>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D29" t="s">
         <v>184</v>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="0"/>
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="D30" t="s">
         <v>184</v>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D31" t="s">
         <v>184</v>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D32" t="s">
         <v>184</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D33" t="s">
         <v>184</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D34" t="s">
         <v>184</v>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D35" t="s">
         <v>184</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D36" t="s">
         <v>184</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="0"/>
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="D37" t="s">
         <v>184</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D38" t="s">
         <v>184</v>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D39" t="s">
         <v>184</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D40" t="s">
         <v>184</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D41" t="s">
         <v>184</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D42" t="s">
         <v>184</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D43" t="s">
         <v>184</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D44" t="s">
         <v>184</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D45" t="s">
         <v>184</v>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D46" t="s">
         <v>184</v>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D47" t="s">
         <v>184</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D48" t="s">
         <v>184</v>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D49" t="s">
         <v>184</v>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D50" t="s">
         <v>184</v>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D51" t="s">
         <v>184</v>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D52" t="s">
         <v>184</v>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D53" t="s">
         <v>184</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D54" t="s">
         <v>184</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D55" t="s">
         <v>184</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="0"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D56" t="s">
         <v>184</v>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="0"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D57" t="s">
         <v>184</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D58" t="s">
         <v>184</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D59" t="s">
         <v>184</v>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D60" t="s">
         <v>184</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D61" t="s">
         <v>184</v>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D62" t="s">
         <v>184</v>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D63" t="s">
         <v>184</v>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D64" t="s">
         <v>184</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D65" t="s">
         <v>184</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="0"/>
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="D66" t="s">
         <v>184</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="C67">
         <f t="shared" ref="C67:C130" ca="1" si="1">B67-$R$1</f>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D67" t="s">
         <v>184</v>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="1"/>
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="D68" t="s">
         <v>184</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D69" t="s">
         <v>184</v>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D70" t="s">
         <v>184</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D71" t="s">
         <v>184</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="1"/>
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="D72" t="s">
         <v>184</v>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D73" t="s">
         <v>184</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D74" t="s">
         <v>184</v>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D75" t="s">
         <v>184</v>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D76" t="s">
         <v>184</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D77" t="s">
         <v>184</v>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="1"/>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="D78" t="s">
         <v>184</v>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D80" t="s">
         <v>184</v>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D83" t="s">
         <v>184</v>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D84" t="s">
         <v>184</v>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D85" t="s">
         <v>184</v>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D86" t="s">
         <v>184</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D88" t="s">
         <v>184</v>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D89" t="s">
         <v>184</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D90" t="s">
         <v>184</v>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D91" t="s">
         <v>184</v>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="1"/>
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="D92" t="s">
         <v>184</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D93" t="s">
         <v>184</v>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D94" t="s">
         <v>184</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D95" t="s">
         <v>184</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D96" t="s">
         <v>184</v>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D97" t="s">
         <v>184</v>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D98" t="s">
         <v>184</v>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D99" t="s">
         <v>184</v>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D100" t="s">
         <v>184</v>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D101" t="s">
         <v>184</v>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="C102">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D102" t="s">
         <v>184</v>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="C103">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D103" t="s">
         <v>184</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="C104">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D104" t="s">
         <v>184</v>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="C105">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D105" t="s">
         <v>184</v>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="C106">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D106" t="s">
         <v>184</v>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="C107">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D107" t="s">
         <v>184</v>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="C108">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D108" t="s">
         <v>184</v>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="C109">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D109" t="s">
         <v>184</v>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="C110">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D110" t="s">
         <v>184</v>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C111">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D111" t="s">
         <v>184</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C113">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D113" t="s">
         <v>184</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C114">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D114" t="s">
         <v>184</v>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="C115">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D115" t="s">
         <v>184</v>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C116">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D116" t="s">
         <v>184</v>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="C117">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D117" t="s">
         <v>184</v>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="C118">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D118" t="s">
         <v>184</v>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="C119">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D119" t="s">
         <v>184</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="C120">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D120" t="s">
         <v>184</v>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="C121">
         <f t="shared" ca="1" si="1"/>
-        <v>-46310</v>
+        <v>-46311</v>
       </c>
       <c r="J121" t="s">
         <v>118</v>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="C122">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D122" t="s">
         <v>184</v>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="C123">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D123" t="s">
         <v>184</v>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="C124">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D124" t="s">
         <v>184</v>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="C125">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D125" t="s">
         <v>184</v>
@@ -8522,7 +8522,7 @@
         <v>158</v>
       </c>
       <c r="B126" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C126">
         <f t="shared" ca="1" si="1"/>
@@ -8576,7 +8576,7 @@
         <v>159</v>
       </c>
       <c r="B127" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C127">
         <f t="shared" ca="1" si="1"/>
@@ -8630,7 +8630,7 @@
         <v>160</v>
       </c>
       <c r="B128" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C128">
         <f t="shared" ca="1" si="1"/>
@@ -8684,11 +8684,11 @@
         <v>161</v>
       </c>
       <c r="B129" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C129">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D129" t="s">
         <v>184</v>
@@ -8738,11 +8738,11 @@
         <v>162</v>
       </c>
       <c r="B130" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C130">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D130" t="s">
         <v>184</v>
@@ -8791,12 +8791,12 @@
       <c r="A131" t="s">
         <v>186</v>
       </c>
-      <c r="B131" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C131" t="e">
+      <c r="B131" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C131">
         <f t="shared" ref="C131:C192" ca="1" si="2">B131-$R$1</f>
-        <v>#N/A</v>
+        <v>-1</v>
       </c>
       <c r="D131" t="s">
         <v>184</v>
@@ -8845,12 +8845,12 @@
       <c r="A132" t="s">
         <v>187</v>
       </c>
-      <c r="B132" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C132" t="e">
+      <c r="B132" s="2">
+        <v>0</v>
+      </c>
+      <c r="C132">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46311</v>
       </c>
       <c r="D132" t="s">
         <v>184</v>
@@ -8899,12 +8899,12 @@
       <c r="A133" t="s">
         <v>188</v>
       </c>
-      <c r="B133" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C133" t="e">
+      <c r="B133" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C133">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-1</v>
       </c>
       <c r="D133" t="s">
         <v>184</v>
@@ -8953,12 +8953,12 @@
       <c r="A134" t="s">
         <v>189</v>
       </c>
-      <c r="B134" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C134" t="e">
+      <c r="B134" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C134">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-1</v>
       </c>
       <c r="D134" t="s">
         <v>184</v>
@@ -9007,12 +9007,12 @@
       <c r="A135" t="s">
         <v>190</v>
       </c>
-      <c r="B135" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C135" t="e">
+      <c r="B135" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C135">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-1</v>
       </c>
       <c r="D135" t="s">
         <v>184</v>
@@ -9061,12 +9061,12 @@
       <c r="A136" t="s">
         <v>191</v>
       </c>
-      <c r="B136" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C136" t="e">
+      <c r="B136" s="2">
+        <v>0</v>
+      </c>
+      <c r="C136">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46311</v>
       </c>
       <c r="D136" t="s">
         <v>184</v>
@@ -9115,12 +9115,12 @@
       <c r="A137" t="s">
         <v>192</v>
       </c>
-      <c r="B137" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C137" t="e">
+      <c r="B137" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C137">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-1</v>
       </c>
       <c r="D137" t="s">
         <v>184</v>
@@ -9613,7 +9613,7 @@
         <v>164</v>
       </c>
       <c r="B151" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C151">
         <f t="shared" ca="1" si="2"/>
@@ -9667,7 +9667,7 @@
         <v>165</v>
       </c>
       <c r="B152" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C152">
         <f t="shared" ca="1" si="2"/>
@@ -9721,7 +9721,7 @@
         <v>166</v>
       </c>
       <c r="B153" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C153">
         <f t="shared" ca="1" si="2"/>
@@ -9775,7 +9775,7 @@
         <v>167</v>
       </c>
       <c r="B154" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C154">
         <f t="shared" ca="1" si="2"/>
@@ -9829,7 +9829,7 @@
         <v>168</v>
       </c>
       <c r="B155" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="D156" t="s">
         <v>184</v>
@@ -9937,7 +9937,7 @@
         <v>170</v>
       </c>
       <c r="B157" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
@@ -9991,7 +9991,7 @@
         <v>171</v>
       </c>
       <c r="B158" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C158">
         <f t="shared" ca="1" si="2"/>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="C159">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D159" t="s">
         <v>184</v>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D160" t="s">
         <v>184</v>
@@ -10153,11 +10153,11 @@
         <v>175</v>
       </c>
       <c r="B161" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D161" t="s">
         <v>184</v>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D162" t="s">
         <v>184</v>
@@ -10332,7 +10332,7 @@
         <v>208</v>
       </c>
       <c r="B165" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="C173">
         <f t="shared" ca="1" si="2"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D173" t="s">
         <v>184</v>
@@ -10664,11 +10664,11 @@
         <v>227</v>
       </c>
       <c r="B174" s="2">
-        <v>46301</v>
+        <v>46310</v>
       </c>
       <c r="C174">
         <f t="shared" ca="1" si="2"/>
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="D174" t="s">
         <v>184</v>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="C175">
         <f t="shared" ca="1" si="2"/>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="D175" t="s">
         <v>184</v>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C176">
         <f t="shared" ca="1" si="2"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D176" t="s">
         <v>184</v>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="C177">
         <f t="shared" ca="1" si="2"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D177" t="s">
         <v>184</v>
@@ -10868,11 +10868,11 @@
         <v>231</v>
       </c>
       <c r="B178" s="2">
-        <v>46304</v>
+        <v>46310</v>
       </c>
       <c r="C178">
         <f t="shared" ca="1" si="2"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D178" t="s">
         <v>184</v>
@@ -10919,11 +10919,11 @@
         <v>232</v>
       </c>
       <c r="B179" s="2">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="C179">
         <f t="shared" ca="1" si="2"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="D179" t="s">
         <v>184</v>
@@ -10970,11 +10970,11 @@
         <v>233</v>
       </c>
       <c r="B180" s="2">
-        <v>46304</v>
+        <v>46310</v>
       </c>
       <c r="C180">
         <f t="shared" ca="1" si="2"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D180" t="s">
         <v>184</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C181">
         <f t="shared" ca="1" si="2"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D181" t="s">
         <v>184</v>
@@ -11072,7 +11072,7 @@
         <v>235</v>
       </c>
       <c r="B182" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C182">
         <f t="shared" ca="1" si="2"/>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="C183">
         <f t="shared" ca="1" si="2"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D183" t="s">
         <v>184</v>
@@ -11178,7 +11178,7 @@
       </c>
       <c r="C184">
         <f t="shared" ca="1" si="2"/>
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="D184" t="s">
         <v>184</v>
@@ -11225,7 +11225,7 @@
         <v>238</v>
       </c>
       <c r="B185" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C185">
         <f t="shared" ca="1" si="2"/>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C186">
         <f t="shared" ca="1" si="2"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D186" t="s">
         <v>184</v>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="C187">
         <f t="shared" ca="1" si="2"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D187" t="s">
         <v>184</v>
@@ -11378,7 +11378,7 @@
         <v>241</v>
       </c>
       <c r="B188" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C188">
         <f t="shared" ca="1" si="2"/>
@@ -11429,7 +11429,7 @@
         <v>242</v>
       </c>
       <c r="B189" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C189">
         <f t="shared" ca="1" si="2"/>
@@ -11480,11 +11480,11 @@
         <v>243</v>
       </c>
       <c r="B190" s="2">
-        <v>46298</v>
+        <v>46310</v>
       </c>
       <c r="C190">
         <f t="shared" ca="1" si="2"/>
-        <v>-12</v>
+        <v>-1</v>
       </c>
       <c r="D190" t="s">
         <v>184</v>
@@ -11531,7 +11531,7 @@
         <v>244</v>
       </c>
       <c r="B191" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C191">
         <f t="shared" ca="1" si="2"/>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C192">
         <f t="shared" ca="1" si="2"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D192" t="s">
         <v>184</v>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C193">
         <f t="shared" ref="C193:C256" ca="1" si="3">B193-$R$1</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D193" t="s">
         <v>184</v>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C194">
         <f t="shared" ca="1" si="3"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D194" t="s">
         <v>184</v>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C195">
         <f t="shared" ca="1" si="3"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D195" t="s">
         <v>184</v>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C198">
         <f t="shared" ca="1" si="3"/>
-        <v>-143</v>
+        <v>-144</v>
       </c>
       <c r="D198" t="s">
         <v>184</v>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="C199">
         <f t="shared" ca="1" si="3"/>
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="D199" t="s">
         <v>184</v>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C200">
         <f t="shared" ca="1" si="3"/>
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="D200" t="s">
         <v>184</v>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="C201">
         <f t="shared" ca="1" si="3"/>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="D201" t="s">
         <v>184</v>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C202">
         <f t="shared" ca="1" si="3"/>
-        <v>-273</v>
+        <v>-274</v>
       </c>
       <c r="D202" t="s">
         <v>184</v>
@@ -12143,7 +12143,7 @@
         <v>256</v>
       </c>
       <c r="B203" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C203">
         <f t="shared" ca="1" si="3"/>
@@ -12194,7 +12194,7 @@
         <v>257</v>
       </c>
       <c r="B204" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C204">
         <f t="shared" ca="1" si="3"/>
@@ -12245,7 +12245,7 @@
         <v>258</v>
       </c>
       <c r="B205" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C205">
         <f t="shared" ca="1" si="3"/>
@@ -12296,7 +12296,7 @@
         <v>259</v>
       </c>
       <c r="B206" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C206">
         <f t="shared" ca="1" si="3"/>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C207">
         <f t="shared" ca="1" si="3"/>
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="D207" t="s">
         <v>184</v>
@@ -12398,7 +12398,7 @@
         <v>261</v>
       </c>
       <c r="B208" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C208">
         <f t="shared" ca="1" si="3"/>
@@ -12449,7 +12449,7 @@
         <v>262</v>
       </c>
       <c r="B209" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C209">
         <f t="shared" ca="1" si="3"/>
@@ -12500,7 +12500,7 @@
         <v>263</v>
       </c>
       <c r="B210" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C210">
         <f t="shared" ca="1" si="3"/>
@@ -12551,7 +12551,7 @@
         <v>264</v>
       </c>
       <c r="B211" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C211">
         <f t="shared" ca="1" si="3"/>
@@ -12602,11 +12602,11 @@
         <v>265</v>
       </c>
       <c r="B212" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C212">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D212" t="s">
         <v>184</v>
@@ -12653,11 +12653,11 @@
         <v>266</v>
       </c>
       <c r="B213" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C213">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D213" t="s">
         <v>184</v>
@@ -12704,7 +12704,7 @@
         <v>267</v>
       </c>
       <c r="B214" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C214">
         <f t="shared" ca="1" si="3"/>
@@ -12755,11 +12755,11 @@
         <v>268</v>
       </c>
       <c r="B215" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C215">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D215" t="s">
         <v>184</v>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C216">
         <f t="shared" ca="1" si="3"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
@@ -12857,7 +12857,7 @@
         <v>270</v>
       </c>
       <c r="B217" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C217">
         <f t="shared" ca="1" si="3"/>
@@ -12908,7 +12908,7 @@
         <v>271</v>
       </c>
       <c r="B218" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C218">
         <f t="shared" ca="1" si="3"/>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C219">
         <f t="shared" ca="1" si="3"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D219" t="s">
         <v>184</v>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="C220">
         <f t="shared" ca="1" si="3"/>
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="D220" t="s">
         <v>184</v>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="C221">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D221" t="s">
         <v>184</v>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="C222">
         <f t="shared" ca="1" si="3"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D222" t="s">
         <v>184</v>
@@ -13167,7 +13167,7 @@
       </c>
       <c r="C223">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D223" t="s">
         <v>184</v>
@@ -13214,7 +13214,7 @@
         <v>277</v>
       </c>
       <c r="B224" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C224">
         <f t="shared" ca="1" si="3"/>
@@ -13265,7 +13265,7 @@
         <v>278</v>
       </c>
       <c r="B225" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C225">
         <f t="shared" ca="1" si="3"/>
@@ -13316,11 +13316,11 @@
         <v>279</v>
       </c>
       <c r="B226" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C226">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D226" t="s">
         <v>184</v>
@@ -13367,7 +13367,7 @@
         <v>280</v>
       </c>
       <c r="B227" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C227">
         <f t="shared" ca="1" si="3"/>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C228">
         <f t="shared" ca="1" si="3"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="D228" t="s">
         <v>184</v>
@@ -13469,7 +13469,7 @@
         <v>282</v>
       </c>
       <c r="B229" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C229">
         <f t="shared" ca="1" si="3"/>
@@ -13524,7 +13524,7 @@
       </c>
       <c r="C230">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D230" t="s">
         <v>184</v>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C231">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D231" t="s">
         <v>184</v>
@@ -13622,7 +13622,7 @@
         <v>285</v>
       </c>
       <c r="B232" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C232">
         <f t="shared" ca="1" si="3"/>
@@ -13673,7 +13673,7 @@
         <v>286</v>
       </c>
       <c r="B233" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C233">
         <f t="shared" ca="1" si="3"/>
@@ -13724,7 +13724,7 @@
         <v>287</v>
       </c>
       <c r="B234" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C234">
         <f t="shared" ca="1" si="3"/>
@@ -13775,7 +13775,7 @@
         <v>288</v>
       </c>
       <c r="B235" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C235">
         <f t="shared" ca="1" si="3"/>
@@ -13826,7 +13826,7 @@
         <v>289</v>
       </c>
       <c r="B236" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C236">
         <f t="shared" ca="1" si="3"/>
@@ -13877,11 +13877,11 @@
         <v>290</v>
       </c>
       <c r="B237" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C237">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D237" t="s">
         <v>184</v>
@@ -13928,7 +13928,7 @@
         <v>291</v>
       </c>
       <c r="B238" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C238">
         <f t="shared" ca="1" si="3"/>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="C239">
         <f t="shared" ca="1" si="3"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D239" t="s">
         <v>184</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="C240">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D240" t="s">
         <v>184</v>
@@ -14081,7 +14081,7 @@
         <v>294</v>
       </c>
       <c r="B241" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C241">
         <f t="shared" ca="1" si="3"/>
@@ -14132,7 +14132,7 @@
         <v>295</v>
       </c>
       <c r="B242" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C242">
         <f t="shared" ca="1" si="3"/>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C243">
         <f t="shared" ca="1" si="3"/>
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="D243" t="s">
         <v>184</v>
@@ -14234,7 +14234,7 @@
         <v>297</v>
       </c>
       <c r="B244" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C244">
         <f t="shared" ca="1" si="3"/>
@@ -14285,11 +14285,11 @@
         <v>298</v>
       </c>
       <c r="B245" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C245">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D245" t="s">
         <v>184</v>
@@ -14336,7 +14336,7 @@
         <v>299</v>
       </c>
       <c r="B246" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C246">
         <f t="shared" ca="1" si="3"/>
@@ -14387,7 +14387,7 @@
         <v>300</v>
       </c>
       <c r="B247" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C247">
         <f t="shared" ca="1" si="3"/>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C248">
         <f t="shared" ca="1" si="3"/>
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="D248" t="s">
         <v>184</v>
@@ -14489,7 +14489,7 @@
         <v>302</v>
       </c>
       <c r="B249" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C249">
         <f t="shared" ca="1" si="3"/>
@@ -14540,11 +14540,11 @@
         <v>303</v>
       </c>
       <c r="B250" s="2">
-        <v>46196</v>
+        <v>46310</v>
       </c>
       <c r="C250">
         <f t="shared" ca="1" si="3"/>
-        <v>-114</v>
+        <v>-1</v>
       </c>
       <c r="D250" t="s">
         <v>184</v>
@@ -14591,7 +14591,7 @@
         <v>304</v>
       </c>
       <c r="B251" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C251">
         <f t="shared" ca="1" si="3"/>
@@ -14642,7 +14642,7 @@
         <v>305</v>
       </c>
       <c r="B252" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C252">
         <f t="shared" ca="1" si="3"/>
@@ -14693,7 +14693,7 @@
         <v>306</v>
       </c>
       <c r="B253" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C253">
         <f t="shared" ca="1" si="3"/>
@@ -14744,11 +14744,11 @@
         <v>307</v>
       </c>
       <c r="B254" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C254">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D254" t="s">
         <v>184</v>
@@ -14799,7 +14799,7 @@
       </c>
       <c r="C255">
         <f t="shared" ca="1" si="3"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D255" t="s">
         <v>184</v>
@@ -14846,7 +14846,7 @@
         <v>309</v>
       </c>
       <c r="B256" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C256">
         <f t="shared" ca="1" si="3"/>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="C257">
         <f t="shared" ref="C257:C320" ca="1" si="4">B257-$R$1</f>
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="D257" t="s">
         <v>184</v>
@@ -14948,11 +14948,11 @@
         <v>311</v>
       </c>
       <c r="B258" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C258">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D258" t="s">
         <v>184</v>
@@ -14999,7 +14999,7 @@
         <v>312</v>
       </c>
       <c r="B259" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C259">
         <f t="shared" ca="1" si="4"/>
@@ -15050,11 +15050,11 @@
         <v>313</v>
       </c>
       <c r="B260" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C260">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D260" t="s">
         <v>184</v>
@@ -15101,7 +15101,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C261">
         <f t="shared" ca="1" si="4"/>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="C262">
         <f t="shared" ca="1" si="4"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D262" t="s">
         <v>184</v>
@@ -15203,7 +15203,7 @@
         <v>316</v>
       </c>
       <c r="B263" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C263">
         <f t="shared" ca="1" si="4"/>
@@ -15254,7 +15254,7 @@
         <v>317</v>
       </c>
       <c r="B264" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C264">
         <f t="shared" ca="1" si="4"/>
@@ -15305,11 +15305,11 @@
         <v>318</v>
       </c>
       <c r="B265" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C265">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D265" t="s">
         <v>184</v>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="C266">
         <f t="shared" ca="1" si="4"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D266" t="s">
         <v>184</v>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C267">
         <f t="shared" ca="1" si="4"/>
-        <v>-133</v>
+        <v>-134</v>
       </c>
       <c r="D267" t="s">
         <v>184</v>
@@ -15458,7 +15458,7 @@
         <v>321</v>
       </c>
       <c r="B268" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C268">
         <f t="shared" ca="1" si="4"/>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C269">
         <f t="shared" ca="1" si="4"/>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="D269" t="s">
         <v>184</v>
@@ -15560,7 +15560,7 @@
         <v>323</v>
       </c>
       <c r="B270" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C270">
         <f t="shared" ca="1" si="4"/>
@@ -15611,7 +15611,7 @@
         <v>324</v>
       </c>
       <c r="B271" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C271">
         <f t="shared" ca="1" si="4"/>
@@ -15662,11 +15662,11 @@
         <v>325</v>
       </c>
       <c r="B272" s="2">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="C272">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D272" t="s">
         <v>184</v>
@@ -15713,11 +15713,11 @@
         <v>326</v>
       </c>
       <c r="B273" s="2">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="C273">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D273" t="s">
         <v>184</v>
@@ -15764,7 +15764,7 @@
         <v>327</v>
       </c>
       <c r="B274" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C274">
         <f t="shared" ca="1" si="4"/>
@@ -15815,7 +15815,7 @@
         <v>328</v>
       </c>
       <c r="B275" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C275">
         <f t="shared" ca="1" si="4"/>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="C276">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D276" t="s">
         <v>184</v>
@@ -15917,7 +15917,7 @@
         <v>330</v>
       </c>
       <c r="B277" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C277">
         <f t="shared" ca="1" si="4"/>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="C278">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D278" t="s">
         <v>184</v>
@@ -16019,11 +16019,11 @@
         <v>332</v>
       </c>
       <c r="B279" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C279">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D279" t="s">
         <v>184</v>
@@ -16070,7 +16070,7 @@
         <v>333</v>
       </c>
       <c r="B280" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C280">
         <f t="shared" ca="1" si="4"/>
@@ -16121,7 +16121,7 @@
         <v>334</v>
       </c>
       <c r="B281" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C281">
         <f t="shared" ca="1" si="4"/>
@@ -16172,7 +16172,7 @@
         <v>335</v>
       </c>
       <c r="B282" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C282">
         <f t="shared" ca="1" si="4"/>
@@ -16223,7 +16223,7 @@
         <v>336</v>
       </c>
       <c r="B283" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C283">
         <f t="shared" ca="1" si="4"/>
@@ -16274,7 +16274,7 @@
         <v>337</v>
       </c>
       <c r="B284" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C284">
         <f t="shared" ca="1" si="4"/>
@@ -16325,7 +16325,7 @@
         <v>338</v>
       </c>
       <c r="B285" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C285">
         <f t="shared" ca="1" si="4"/>
@@ -16376,7 +16376,7 @@
         <v>339</v>
       </c>
       <c r="B286" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C286">
         <f t="shared" ca="1" si="4"/>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C287">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D287" t="s">
         <v>184</v>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="C288">
         <f t="shared" ca="1" si="4"/>
-        <v>-219</v>
+        <v>-220</v>
       </c>
       <c r="D288" t="s">
         <v>184</v>
@@ -16529,7 +16529,7 @@
         <v>342</v>
       </c>
       <c r="B289" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C289">
         <f t="shared" ca="1" si="4"/>
@@ -16580,7 +16580,7 @@
         <v>343</v>
       </c>
       <c r="B290" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C290">
         <f t="shared" ca="1" si="4"/>
@@ -16631,7 +16631,7 @@
         <v>344</v>
       </c>
       <c r="B291" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C291">
         <f t="shared" ca="1" si="4"/>
@@ -16682,7 +16682,7 @@
         <v>345</v>
       </c>
       <c r="B292" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C292">
         <f t="shared" ca="1" si="4"/>
@@ -16733,7 +16733,7 @@
         <v>346</v>
       </c>
       <c r="B293" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C293">
         <f t="shared" ca="1" si="4"/>
@@ -16784,7 +16784,7 @@
         <v>347</v>
       </c>
       <c r="B294" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C294">
         <f t="shared" ca="1" si="4"/>
@@ -16835,7 +16835,7 @@
         <v>348</v>
       </c>
       <c r="B295" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C295">
         <f t="shared" ca="1" si="4"/>
@@ -16886,7 +16886,7 @@
         <v>349</v>
       </c>
       <c r="B296" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C296">
         <f t="shared" ca="1" si="4"/>
@@ -16937,7 +16937,7 @@
         <v>350</v>
       </c>
       <c r="B297" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C297">
         <f t="shared" ca="1" si="4"/>
@@ -16988,7 +16988,7 @@
         <v>351</v>
       </c>
       <c r="B298" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C298">
         <f t="shared" ca="1" si="4"/>
@@ -17039,7 +17039,7 @@
         <v>352</v>
       </c>
       <c r="B299" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C299">
         <f t="shared" ca="1" si="4"/>
@@ -17090,7 +17090,7 @@
         <v>353</v>
       </c>
       <c r="B300" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C300">
         <f t="shared" ca="1" si="4"/>
@@ -17141,7 +17141,7 @@
         <v>354</v>
       </c>
       <c r="B301" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C301">
         <f t="shared" ca="1" si="4"/>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C302">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D302" t="s">
         <v>184</v>
@@ -17243,7 +17243,7 @@
         <v>356</v>
       </c>
       <c r="B303" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C303">
         <f t="shared" ca="1" si="4"/>
@@ -17294,7 +17294,7 @@
         <v>357</v>
       </c>
       <c r="B304" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C304">
         <f t="shared" ca="1" si="4"/>
@@ -17345,11 +17345,11 @@
         <v>358</v>
       </c>
       <c r="B305" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C305">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D305" t="s">
         <v>184</v>
@@ -17396,7 +17396,7 @@
         <v>359</v>
       </c>
       <c r="B306" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C306">
         <f t="shared" ca="1" si="4"/>
@@ -17447,11 +17447,11 @@
         <v>360</v>
       </c>
       <c r="B307" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C307">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D307" t="s">
         <v>184</v>
@@ -17498,7 +17498,7 @@
         <v>361</v>
       </c>
       <c r="B308" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C308">
         <f t="shared" ca="1" si="4"/>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="C309">
         <f t="shared" ca="1" si="4"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D309" t="s">
         <v>184</v>
@@ -17600,7 +17600,7 @@
         <v>363</v>
       </c>
       <c r="B310" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C310">
         <f t="shared" ca="1" si="4"/>
@@ -17651,7 +17651,7 @@
         <v>364</v>
       </c>
       <c r="B311" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C311">
         <f t="shared" ca="1" si="4"/>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="C312">
         <f t="shared" ca="1" si="4"/>
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="D312" t="s">
         <v>184</v>
@@ -17753,7 +17753,7 @@
         <v>366</v>
       </c>
       <c r="B313" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C313">
         <f t="shared" ca="1" si="4"/>
@@ -17804,11 +17804,11 @@
         <v>367</v>
       </c>
       <c r="B314" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C314">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D314" t="s">
         <v>184</v>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C315">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D315" t="s">
         <v>184</v>
@@ -17906,11 +17906,11 @@
         <v>369</v>
       </c>
       <c r="B316" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C316">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D316" t="s">
         <v>184</v>
@@ -17957,7 +17957,7 @@
         <v>370</v>
       </c>
       <c r="B317" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C317">
         <f t="shared" ca="1" si="4"/>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="C318">
         <f t="shared" ca="1" si="4"/>
-        <v>-66</v>
+        <v>-67</v>
       </c>
       <c r="D318" t="s">
         <v>184</v>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C319">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D319" t="s">
         <v>184</v>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C320">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D320" t="s">
         <v>184</v>
@@ -18161,7 +18161,7 @@
         <v>374</v>
       </c>
       <c r="B321" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C321">
         <f t="shared" ref="C321:C384" ca="1" si="5">B321-$R$1</f>
@@ -18216,7 +18216,7 @@
       </c>
       <c r="C322">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D322" t="s">
         <v>184</v>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C323">
         <f t="shared" ca="1" si="5"/>
-        <v>-70</v>
+        <v>-71</v>
       </c>
       <c r="D323" t="s">
         <v>184</v>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="C324">
         <f t="shared" ca="1" si="5"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D324" t="s">
         <v>184</v>
@@ -18365,7 +18365,7 @@
         <v>378</v>
       </c>
       <c r="B325" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C325">
         <f t="shared" ca="1" si="5"/>
@@ -18416,7 +18416,7 @@
         <v>379</v>
       </c>
       <c r="B326" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C326">
         <f t="shared" ca="1" si="5"/>
@@ -18467,11 +18467,11 @@
         <v>380</v>
       </c>
       <c r="B327" s="2">
-        <v>46304</v>
+        <v>46310</v>
       </c>
       <c r="C327">
         <f t="shared" ca="1" si="5"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D327" t="s">
         <v>184</v>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C328">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D328" t="s">
         <v>184</v>
@@ -18569,7 +18569,7 @@
         <v>382</v>
       </c>
       <c r="B329" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C329">
         <f t="shared" ca="1" si="5"/>
@@ -18620,11 +18620,11 @@
         <v>383</v>
       </c>
       <c r="B330" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C330">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D330" t="s">
         <v>184</v>
@@ -18671,7 +18671,7 @@
         <v>384</v>
       </c>
       <c r="B331" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C331">
         <f t="shared" ca="1" si="5"/>
@@ -18722,11 +18722,11 @@
         <v>385</v>
       </c>
       <c r="B332" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C332">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D332" t="s">
         <v>184</v>
@@ -18773,7 +18773,7 @@
         <v>386</v>
       </c>
       <c r="B333" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C333">
         <f t="shared" ca="1" si="5"/>
@@ -18824,11 +18824,11 @@
         <v>387</v>
       </c>
       <c r="B334" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C334">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D334" t="s">
         <v>184</v>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="C335">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D335" t="s">
         <v>184</v>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C336">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D336" t="s">
         <v>184</v>
@@ -18977,7 +18977,7 @@
         <v>390</v>
       </c>
       <c r="B337" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C337">
         <f t="shared" ca="1" si="5"/>
@@ -19028,7 +19028,7 @@
         <v>391</v>
       </c>
       <c r="B338" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C338">
         <f t="shared" ca="1" si="5"/>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C339">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D339" t="s">
         <v>184</v>
@@ -19130,7 +19130,7 @@
         <v>393</v>
       </c>
       <c r="B340" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C340">
         <f t="shared" ca="1" si="5"/>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C341">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D341" t="s">
         <v>184</v>
@@ -19232,7 +19232,7 @@
         <v>395</v>
       </c>
       <c r="B342" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C342">
         <f t="shared" ca="1" si="5"/>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="C343">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D343" t="s">
         <v>184</v>
@@ -19334,7 +19334,7 @@
         <v>397</v>
       </c>
       <c r="B344" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C344">
         <f t="shared" ca="1" si="5"/>
@@ -19385,7 +19385,7 @@
         <v>398</v>
       </c>
       <c r="B345" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C345">
         <f t="shared" ca="1" si="5"/>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C346">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D346" t="s">
         <v>184</v>
@@ -19487,7 +19487,7 @@
         <v>400</v>
       </c>
       <c r="B347" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C347">
         <f t="shared" ca="1" si="5"/>
@@ -19538,11 +19538,11 @@
         <v>401</v>
       </c>
       <c r="B348" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C348">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D348" t="s">
         <v>184</v>
@@ -19589,11 +19589,11 @@
         <v>402</v>
       </c>
       <c r="B349" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C349">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D349" t="s">
         <v>184</v>
@@ -19640,7 +19640,7 @@
         <v>403</v>
       </c>
       <c r="B350" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C350">
         <f t="shared" ca="1" si="5"/>
@@ -19691,7 +19691,7 @@
         <v>404</v>
       </c>
       <c r="B351" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C351">
         <f t="shared" ca="1" si="5"/>
@@ -19742,7 +19742,7 @@
         <v>405</v>
       </c>
       <c r="B352" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C352">
         <f t="shared" ca="1" si="5"/>
@@ -19793,7 +19793,7 @@
         <v>406</v>
       </c>
       <c r="B353" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C353">
         <f t="shared" ca="1" si="5"/>
@@ -19844,7 +19844,7 @@
         <v>407</v>
       </c>
       <c r="B354" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C354">
         <f t="shared" ca="1" si="5"/>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="C355">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D355" t="s">
         <v>184</v>
@@ -19946,7 +19946,7 @@
         <v>409</v>
       </c>
       <c r="B356" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C356">
         <f t="shared" ca="1" si="5"/>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C357">
         <f t="shared" ca="1" si="5"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D357" t="s">
         <v>184</v>
@@ -20052,7 +20052,7 @@
       </c>
       <c r="C358">
         <f t="shared" ca="1" si="5"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D358" t="s">
         <v>184</v>
@@ -20099,7 +20099,7 @@
         <v>412</v>
       </c>
       <c r="B359" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C359">
         <f t="shared" ca="1" si="5"/>
@@ -20150,11 +20150,11 @@
         <v>413</v>
       </c>
       <c r="B360" s="2">
-        <v>46300</v>
+        <v>46310</v>
       </c>
       <c r="C360">
         <f t="shared" ca="1" si="5"/>
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="D360" t="s">
         <v>184</v>
@@ -20201,7 +20201,7 @@
         <v>414</v>
       </c>
       <c r="B361" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C361">
         <f t="shared" ca="1" si="5"/>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C362">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D362" t="s">
         <v>184</v>
@@ -20303,7 +20303,7 @@
         <v>416</v>
       </c>
       <c r="B363" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C363">
         <f t="shared" ca="1" si="5"/>
@@ -20358,7 +20358,7 @@
       </c>
       <c r="C364">
         <f t="shared" ca="1" si="5"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="D364" t="s">
         <v>184</v>
@@ -20405,7 +20405,7 @@
         <v>418</v>
       </c>
       <c r="B365" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C365">
         <f t="shared" ca="1" si="5"/>
@@ -20456,11 +20456,11 @@
         <v>419</v>
       </c>
       <c r="B366" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C366">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D366" t="s">
         <v>184</v>
@@ -20507,7 +20507,7 @@
         <v>420</v>
       </c>
       <c r="B367" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C367">
         <f t="shared" ca="1" si="5"/>
@@ -20558,7 +20558,7 @@
         <v>421</v>
       </c>
       <c r="B368" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C368">
         <f t="shared" ca="1" si="5"/>
@@ -20609,7 +20609,7 @@
         <v>422</v>
       </c>
       <c r="B369" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C369">
         <f t="shared" ca="1" si="5"/>
@@ -20660,7 +20660,7 @@
         <v>423</v>
       </c>
       <c r="B370" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C370">
         <f t="shared" ca="1" si="5"/>
@@ -20711,7 +20711,7 @@
         <v>424</v>
       </c>
       <c r="B371" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C371">
         <f t="shared" ca="1" si="5"/>
@@ -20762,7 +20762,7 @@
         <v>425</v>
       </c>
       <c r="B372" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C372">
         <f t="shared" ca="1" si="5"/>
@@ -20813,11 +20813,11 @@
         <v>426</v>
       </c>
       <c r="B373" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C373">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D373" t="s">
         <v>184</v>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C374">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D374" t="s">
         <v>184</v>
@@ -20915,7 +20915,7 @@
         <v>428</v>
       </c>
       <c r="B375" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C375">
         <f t="shared" ca="1" si="5"/>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="C376">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D376" t="s">
         <v>184</v>
@@ -21017,11 +21017,11 @@
         <v>430</v>
       </c>
       <c r="B377" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="C377">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D377" t="s">
         <v>184</v>
@@ -21068,7 +21068,7 @@
         <v>431</v>
       </c>
       <c r="B378" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C378">
         <f t="shared" ca="1" si="5"/>
@@ -21119,7 +21119,7 @@
         <v>432</v>
       </c>
       <c r="B379" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C379">
         <f t="shared" ca="1" si="5"/>
@@ -21170,7 +21170,7 @@
         <v>433</v>
       </c>
       <c r="B380" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C380">
         <f t="shared" ca="1" si="5"/>
@@ -21221,7 +21221,7 @@
         <v>434</v>
       </c>
       <c r="B381" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C381">
         <f t="shared" ca="1" si="5"/>
@@ -21272,7 +21272,7 @@
         <v>435</v>
       </c>
       <c r="B382" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C382">
         <f t="shared" ca="1" si="5"/>
@@ -21323,7 +21323,7 @@
         <v>436</v>
       </c>
       <c r="B383" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C383">
         <f t="shared" ca="1" si="5"/>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C384">
         <f t="shared" ca="1" si="5"/>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="D384" t="s">
         <v>184</v>
@@ -21425,7 +21425,7 @@
         <v>438</v>
       </c>
       <c r="B385" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C385">
         <f t="shared" ref="C385:C392" ca="1" si="6">B385-$R$1</f>
@@ -21476,7 +21476,7 @@
         <v>439</v>
       </c>
       <c r="B386" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C386">
         <f t="shared" ca="1" si="6"/>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C387">
         <f t="shared" ca="1" si="6"/>
-        <v>-46310</v>
+        <v>-46311</v>
       </c>
       <c r="D387" t="s">
         <v>184</v>
@@ -21582,7 +21582,7 @@
       </c>
       <c r="C388">
         <f t="shared" ca="1" si="6"/>
-        <v>-46310</v>
+        <v>-46311</v>
       </c>
       <c r="D388" t="s">
         <v>184</v>
@@ -21633,7 +21633,7 @@
       </c>
       <c r="C389">
         <f t="shared" ca="1" si="6"/>
-        <v>-46310</v>
+        <v>-46311</v>
       </c>
       <c r="D389" t="s">
         <v>184</v>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="C390">
         <f t="shared" ca="1" si="6"/>
-        <v>-46310</v>
+        <v>-46311</v>
       </c>
       <c r="D390" t="s">
         <v>184</v>
@@ -21731,7 +21731,7 @@
         <v>444</v>
       </c>
       <c r="B391" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C391">
         <f t="shared" ca="1" si="6"/>
@@ -21782,7 +21782,7 @@
         <v>445</v>
       </c>
       <c r="B392" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C392">
         <f t="shared" ca="1" si="6"/>
@@ -21843,18 +21843,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -22115,6 +22103,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
   <ds:schemaRefs>
@@ -22124,17 +22124,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22151,4 +22140,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="347" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96CFA795-B8CD-4B06-A62C-023199387B7E}"/>
+  <xr:revisionPtr revIDLastSave="366" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36C5A12B-984C-4F9F-B390-FEF7F3BB1D19}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4778" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4790" uniqueCount="471">
   <si>
     <t>Placa</t>
   </si>
@@ -1446,6 +1446,9 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>UVX2H35</t>
   </si>
 </sst>
 </file>
@@ -1800,7 +1803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R392"/>
+  <dimension ref="A1:R393"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
@@ -10338,6 +10341,9 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D164" t="s">
+        <v>184</v>
+      </c>
       <c r="J164" t="s">
         <v>174</v>
       </c>
@@ -10356,8 +10362,12 @@
       <c r="O164" t="s">
         <v>217</v>
       </c>
-      <c r="P164" s="2"/>
-      <c r="Q164" s="2"/>
+      <c r="P164" s="2">
+        <v>46314</v>
+      </c>
+      <c r="Q164" s="2">
+        <v>46314</v>
+      </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
@@ -10424,6 +10434,9 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D166" t="s">
+        <v>469</v>
+      </c>
       <c r="J166" t="s">
         <v>174</v>
       </c>
@@ -10442,8 +10455,12 @@
       <c r="O166" t="s">
         <v>217</v>
       </c>
-      <c r="P166" s="2"/>
-      <c r="Q166" s="2"/>
+      <c r="P166" s="2">
+        <v>46314</v>
+      </c>
+      <c r="Q166" s="2">
+        <v>46314</v>
+      </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
@@ -10456,6 +10473,9 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D167" t="s">
+        <v>469</v>
+      </c>
       <c r="J167" t="s">
         <v>174</v>
       </c>
@@ -10474,8 +10494,12 @@
       <c r="O167" t="s">
         <v>217</v>
       </c>
-      <c r="P167" s="2"/>
-      <c r="Q167" s="2"/>
+      <c r="P167" s="2">
+        <v>46314</v>
+      </c>
+      <c r="Q167" s="2">
+        <v>46314</v>
+      </c>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
@@ -21504,7 +21528,7 @@
         <v>46311</v>
       </c>
       <c r="C385">
-        <f t="shared" ref="C385:C392" ca="1" si="6">B385-$R$1</f>
+        <f t="shared" ref="C385:C393" ca="1" si="6">B385-$R$1</f>
         <v>-3</v>
       </c>
       <c r="D385" t="s">
@@ -21904,21 +21928,58 @@
         <v>46023</v>
       </c>
     </row>
+    <row r="393" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>470</v>
+      </c>
+      <c r="C393">
+        <f t="shared" ca="1" si="6"/>
+        <v>-46314</v>
+      </c>
+      <c r="D393" t="s">
+        <v>184</v>
+      </c>
+      <c r="E393" t="s">
+        <v>184</v>
+      </c>
+      <c r="J393" t="s">
+        <v>174</v>
+      </c>
+      <c r="K393" t="s">
+        <v>11</v>
+      </c>
+      <c r="L393" t="s">
+        <v>23</v>
+      </c>
+      <c r="M393" t="s">
+        <v>24</v>
+      </c>
+      <c r="N393" t="s">
+        <v>146</v>
+      </c>
+      <c r="O393" t="s">
+        <v>217</v>
+      </c>
+      <c r="P393" s="2">
+        <v>46314</v>
+      </c>
+      <c r="Q393" s="2">
+        <v>46314</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:R392" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22183,21 +22244,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -22222,9 +22283,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="366" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36C5A12B-984C-4F9F-B390-FEF7F3BB1D19}"/>
+  <xr:revisionPtr revIDLastSave="367" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F41308C-8335-49FA-BF03-B7F80231AFD9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4790" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4781" uniqueCount="470">
   <si>
     <t>Placa</t>
   </si>
@@ -1446,9 +1446,6 @@
   </si>
   <si>
     <t>OK</t>
-  </si>
-  <si>
-    <t>UVX2H35</t>
   </si>
 </sst>
 </file>
@@ -1803,7 +1800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R393"/>
+  <dimension ref="A1:R392"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
@@ -21528,7 +21525,7 @@
         <v>46311</v>
       </c>
       <c r="C385">
-        <f t="shared" ref="C385:C393" ca="1" si="6">B385-$R$1</f>
+        <f t="shared" ref="C385:C392" ca="1" si="6">B385-$R$1</f>
         <v>-3</v>
       </c>
       <c r="D385" t="s">
@@ -21926,45 +21923,6 @@
       </c>
       <c r="Q392" s="2">
         <v>46023</v>
-      </c>
-    </row>
-    <row r="393" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A393" t="s">
-        <v>470</v>
-      </c>
-      <c r="C393">
-        <f t="shared" ca="1" si="6"/>
-        <v>-46314</v>
-      </c>
-      <c r="D393" t="s">
-        <v>184</v>
-      </c>
-      <c r="E393" t="s">
-        <v>184</v>
-      </c>
-      <c r="J393" t="s">
-        <v>174</v>
-      </c>
-      <c r="K393" t="s">
-        <v>11</v>
-      </c>
-      <c r="L393" t="s">
-        <v>23</v>
-      </c>
-      <c r="M393" t="s">
-        <v>24</v>
-      </c>
-      <c r="N393" t="s">
-        <v>146</v>
-      </c>
-      <c r="O393" t="s">
-        <v>217</v>
-      </c>
-      <c r="P393" s="2">
-        <v>46314</v>
-      </c>
-      <c r="Q393" s="2">
-        <v>46314</v>
       </c>
     </row>
   </sheetData>
@@ -21983,6 +21941,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -22243,18 +22213,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
   <ds:schemaRefs>
@@ -22264,6 +22222,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22280,15 +22249,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="367" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F41308C-8335-49FA-BF03-B7F80231AFD9}"/>
+  <xr:revisionPtr revIDLastSave="377" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4E0A04B-A060-47D3-97C0-E715C4A8B368}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4781" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4784" uniqueCount="470">
   <si>
     <t>Placa</t>
   </si>
@@ -9314,6 +9314,9 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D141" t="s">
+        <v>184</v>
+      </c>
       <c r="J141" t="s">
         <v>28</v>
       </c>
@@ -9332,8 +9335,12 @@
       <c r="O141" t="s">
         <v>217</v>
       </c>
-      <c r="P141" s="2"/>
-      <c r="Q141" s="2"/>
+      <c r="P141" s="2">
+        <v>46312</v>
+      </c>
+      <c r="Q141" s="2">
+        <v>46312</v>
+      </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
@@ -9503,6 +9510,9 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D147" t="s">
+        <v>184</v>
+      </c>
       <c r="J147" t="s">
         <v>28</v>
       </c>
@@ -9521,8 +9531,12 @@
       <c r="O147" t="s">
         <v>217</v>
       </c>
-      <c r="P147" s="2"/>
-      <c r="Q147" s="2"/>
+      <c r="P147" s="2">
+        <v>46312</v>
+      </c>
+      <c r="Q147" s="2">
+        <v>46312</v>
+      </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
@@ -9535,6 +9549,9 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D148" t="s">
+        <v>184</v>
+      </c>
       <c r="J148" t="s">
         <v>28</v>
       </c>
@@ -9553,8 +9570,12 @@
       <c r="O148" t="s">
         <v>217</v>
       </c>
-      <c r="P148" s="2"/>
-      <c r="Q148" s="2"/>
+      <c r="P148" s="2">
+        <v>46312</v>
+      </c>
+      <c r="Q148" s="2">
+        <v>46312</v>
+      </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
@@ -21932,15 +21953,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -21950,6 +21962,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22214,20 +22235,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="377" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4E0A04B-A060-47D3-97C0-E715C4A8B368}"/>
+  <xr:revisionPtr revIDLastSave="381" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96115E71-B3C0-4B1A-AE29-5AA97C99CFCC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="R1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1884,11 +1884,11 @@
         <v>9</v>
       </c>
       <c r="B2" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C2">
         <f ca="1">B2-$R$1</f>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D2" t="s">
         <v>184</v>
@@ -1936,11 +1936,11 @@
         <v>14</v>
       </c>
       <c r="B3" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C66" ca="1" si="0">B3-$R$1</f>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D3" t="s">
         <v>184</v>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D4" t="s">
         <v>184</v>
@@ -2040,11 +2040,11 @@
         <v>16</v>
       </c>
       <c r="B5" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D5" t="s">
         <v>184</v>
@@ -2092,11 +2092,11 @@
         <v>17</v>
       </c>
       <c r="B6" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D6" t="s">
         <v>184</v>
@@ -2144,11 +2144,11 @@
         <v>18</v>
       </c>
       <c r="B7" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D7" t="s">
         <v>184</v>
@@ -2196,11 +2196,11 @@
         <v>19</v>
       </c>
       <c r="B8" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="D8" t="s">
         <v>184</v>
@@ -2248,11 +2248,11 @@
         <v>20</v>
       </c>
       <c r="B9" s="2">
-        <v>46309</v>
+        <v>46312</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="D9" t="s">
         <v>184</v>
@@ -2300,11 +2300,11 @@
         <v>21</v>
       </c>
       <c r="B10" s="2">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D10" t="s">
         <v>184</v>
@@ -2354,11 +2354,11 @@
         <v>26</v>
       </c>
       <c r="B11" s="2">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D11" t="s">
         <v>184</v>
@@ -2408,11 +2408,11 @@
         <v>27</v>
       </c>
       <c r="B12" s="2">
-        <v>46298</v>
+        <v>46313</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="D12" t="s">
         <v>184</v>
@@ -2462,11 +2462,11 @@
         <v>31</v>
       </c>
       <c r="B13" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D13" t="s">
         <v>184</v>
@@ -2516,11 +2516,11 @@
         <v>36</v>
       </c>
       <c r="B14" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D14" t="s">
         <v>184</v>
@@ -2570,11 +2570,11 @@
         <v>37</v>
       </c>
       <c r="B15" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D15" t="s">
         <v>184</v>
@@ -2624,11 +2624,11 @@
         <v>38</v>
       </c>
       <c r="B16" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D16" t="s">
         <v>184</v>
@@ -2678,11 +2678,11 @@
         <v>39</v>
       </c>
       <c r="B17" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D17" t="s">
         <v>184</v>
@@ -2732,11 +2732,11 @@
         <v>40</v>
       </c>
       <c r="B18" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D18" t="s">
         <v>184</v>
@@ -2786,11 +2786,11 @@
         <v>41</v>
       </c>
       <c r="B19" s="2">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D19" t="s">
         <v>184</v>
@@ -2840,11 +2840,11 @@
         <v>42</v>
       </c>
       <c r="B20" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D20" t="s">
         <v>184</v>
@@ -2894,11 +2894,11 @@
         <v>43</v>
       </c>
       <c r="B21" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D21" t="s">
         <v>184</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D22" t="s">
         <v>184</v>
@@ -3002,11 +3002,11 @@
         <v>46</v>
       </c>
       <c r="B23" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D23" t="s">
         <v>184</v>
@@ -3056,11 +3056,11 @@
         <v>47</v>
       </c>
       <c r="B24" s="2">
-        <v>46308</v>
+        <v>46313</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="D24" t="s">
         <v>184</v>
@@ -3110,11 +3110,11 @@
         <v>48</v>
       </c>
       <c r="B25" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D25" t="s">
         <v>184</v>
@@ -3164,11 +3164,11 @@
         <v>49</v>
       </c>
       <c r="B26" s="2">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D26" t="s">
         <v>184</v>
@@ -3218,11 +3218,11 @@
         <v>50</v>
       </c>
       <c r="B27" s="2">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D27" t="s">
         <v>184</v>
@@ -3272,11 +3272,11 @@
         <v>51</v>
       </c>
       <c r="B28" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D28" t="s">
         <v>184</v>
@@ -3326,11 +3326,11 @@
         <v>52</v>
       </c>
       <c r="B29" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D29" t="s">
         <v>184</v>
@@ -3380,11 +3380,11 @@
         <v>53</v>
       </c>
       <c r="B30" s="2">
-        <v>46284</v>
+        <v>46314</v>
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="0"/>
-        <v>-30</v>
+        <v>-1</v>
       </c>
       <c r="D30" t="s">
         <v>184</v>
@@ -3434,11 +3434,11 @@
         <v>54</v>
       </c>
       <c r="B31" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D31" t="s">
         <v>184</v>
@@ -3488,11 +3488,11 @@
         <v>55</v>
       </c>
       <c r="B32" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D32" t="s">
         <v>184</v>
@@ -3542,11 +3542,11 @@
         <v>56</v>
       </c>
       <c r="B33" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D33" t="s">
         <v>184</v>
@@ -3596,11 +3596,11 @@
         <v>57</v>
       </c>
       <c r="B34" s="2">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D34" t="s">
         <v>184</v>
@@ -3650,11 +3650,11 @@
         <v>58</v>
       </c>
       <c r="B35" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D35" t="s">
         <v>184</v>
@@ -3704,11 +3704,11 @@
         <v>59</v>
       </c>
       <c r="B36" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D36" t="s">
         <v>184</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="0"/>
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="D37" t="s">
         <v>184</v>
@@ -3812,11 +3812,11 @@
         <v>62</v>
       </c>
       <c r="B38" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D38" t="s">
         <v>184</v>
@@ -3866,11 +3866,11 @@
         <v>63</v>
       </c>
       <c r="B39" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D39" t="s">
         <v>184</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="0"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D40" t="s">
         <v>184</v>
@@ -3974,11 +3974,11 @@
         <v>65</v>
       </c>
       <c r="B41" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D41" t="s">
         <v>184</v>
@@ -4028,11 +4028,11 @@
         <v>66</v>
       </c>
       <c r="B42" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D42" t="s">
         <v>184</v>
@@ -4082,11 +4082,11 @@
         <v>67</v>
       </c>
       <c r="B43" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D43" t="s">
         <v>184</v>
@@ -4136,11 +4136,11 @@
         <v>68</v>
       </c>
       <c r="B44" s="2">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D44" t="s">
         <v>184</v>
@@ -4190,11 +4190,11 @@
         <v>69</v>
       </c>
       <c r="B45" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D45" t="s">
         <v>184</v>
@@ -4244,11 +4244,11 @@
         <v>70</v>
       </c>
       <c r="B46" s="2">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D46" t="s">
         <v>184</v>
@@ -4298,11 +4298,11 @@
         <v>71</v>
       </c>
       <c r="B47" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D47" t="s">
         <v>184</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D48" t="s">
         <v>184</v>
@@ -4406,11 +4406,11 @@
         <v>73</v>
       </c>
       <c r="B49" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D49" t="s">
         <v>184</v>
@@ -4460,11 +4460,11 @@
         <v>74</v>
       </c>
       <c r="B50" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D50" t="s">
         <v>184</v>
@@ -4514,11 +4514,11 @@
         <v>75</v>
       </c>
       <c r="B51" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D51" t="s">
         <v>184</v>
@@ -4568,11 +4568,11 @@
         <v>76</v>
       </c>
       <c r="B52" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D52" t="s">
         <v>184</v>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D53" t="s">
         <v>184</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D54" t="s">
         <v>184</v>
@@ -4730,11 +4730,11 @@
         <v>79</v>
       </c>
       <c r="B55" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D55" t="s">
         <v>184</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="0"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="D56" t="s">
         <v>184</v>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="0"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D57" t="s">
         <v>184</v>
@@ -4892,11 +4892,11 @@
         <v>82</v>
       </c>
       <c r="B58" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D58" t="s">
         <v>184</v>
@@ -4946,11 +4946,11 @@
         <v>83</v>
       </c>
       <c r="B59" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D59" t="s">
         <v>184</v>
@@ -5000,11 +5000,11 @@
         <v>84</v>
       </c>
       <c r="B60" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D60" t="s">
         <v>184</v>
@@ -5054,11 +5054,11 @@
         <v>85</v>
       </c>
       <c r="B61" s="2">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="D61" t="s">
         <v>184</v>
@@ -5108,11 +5108,11 @@
         <v>86</v>
       </c>
       <c r="B62" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D62" t="s">
         <v>184</v>
@@ -5162,11 +5162,11 @@
         <v>87</v>
       </c>
       <c r="B63" s="2">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="0"/>
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="D63" t="s">
         <v>184</v>
@@ -5216,11 +5216,11 @@
         <v>90</v>
       </c>
       <c r="B64" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D64" t="s">
         <v>184</v>
@@ -5270,11 +5270,11 @@
         <v>92</v>
       </c>
       <c r="B65" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D65" t="s">
         <v>184</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="0"/>
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="D66" t="s">
         <v>184</v>
@@ -5378,11 +5378,11 @@
         <v>94</v>
       </c>
       <c r="B67" s="2">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="C67">
         <f t="shared" ref="C67:C130" ca="1" si="1">B67-$R$1</f>
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="D67" t="s">
         <v>184</v>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="1"/>
-        <v>-59</v>
+        <v>-60</v>
       </c>
       <c r="D68" t="s">
         <v>184</v>
@@ -5486,11 +5486,11 @@
         <v>96</v>
       </c>
       <c r="B69" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D69" t="s">
         <v>184</v>
@@ -5540,11 +5540,11 @@
         <v>97</v>
       </c>
       <c r="B70" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D70" t="s">
         <v>184</v>
@@ -5594,11 +5594,11 @@
         <v>98</v>
       </c>
       <c r="B71" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D71" t="s">
         <v>184</v>
@@ -5648,11 +5648,11 @@
         <v>99</v>
       </c>
       <c r="B72" s="2">
-        <v>46272</v>
+        <v>46314</v>
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="1"/>
-        <v>-42</v>
+        <v>-1</v>
       </c>
       <c r="D72" t="s">
         <v>184</v>
@@ -5702,11 +5702,11 @@
         <v>100</v>
       </c>
       <c r="B73" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D73" t="s">
         <v>184</v>
@@ -5756,11 +5756,11 @@
         <v>102</v>
       </c>
       <c r="B74" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D74" t="s">
         <v>184</v>
@@ -5810,11 +5810,11 @@
         <v>103</v>
       </c>
       <c r="B75" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D75" t="s">
         <v>184</v>
@@ -5864,11 +5864,11 @@
         <v>104</v>
       </c>
       <c r="B76" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D76" t="s">
         <v>184</v>
@@ -5918,11 +5918,11 @@
         <v>105</v>
       </c>
       <c r="B77" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D77" t="s">
         <v>184</v>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="1"/>
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="D78" t="s">
         <v>184</v>
@@ -6080,11 +6080,11 @@
         <v>108</v>
       </c>
       <c r="B80" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D80" t="s">
         <v>184</v>
@@ -6242,11 +6242,11 @@
         <v>111</v>
       </c>
       <c r="B83" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D83" t="s">
         <v>184</v>
@@ -6296,11 +6296,11 @@
         <v>112</v>
       </c>
       <c r="B84" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D84" t="s">
         <v>184</v>
@@ -6350,11 +6350,11 @@
         <v>113</v>
       </c>
       <c r="B85" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D85" t="s">
         <v>184</v>
@@ -6404,11 +6404,11 @@
         <v>114</v>
       </c>
       <c r="B86" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D86" t="s">
         <v>184</v>
@@ -6512,11 +6512,11 @@
         <v>116</v>
       </c>
       <c r="B88" s="2">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="1"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D88" t="s">
         <v>184</v>
@@ -6566,11 +6566,11 @@
         <v>117</v>
       </c>
       <c r="B89" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D89" t="s">
         <v>184</v>
@@ -6620,11 +6620,11 @@
         <v>121</v>
       </c>
       <c r="B90" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D90" t="s">
         <v>184</v>
@@ -6674,11 +6674,11 @@
         <v>122</v>
       </c>
       <c r="B91" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D91" t="s">
         <v>184</v>
@@ -6728,11 +6728,11 @@
         <v>123</v>
       </c>
       <c r="B92" s="2">
-        <v>46281</v>
+        <v>46314</v>
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="1"/>
-        <v>-33</v>
+        <v>-1</v>
       </c>
       <c r="D92" t="s">
         <v>184</v>
@@ -6782,11 +6782,11 @@
         <v>124</v>
       </c>
       <c r="B93" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D93" t="s">
         <v>184</v>
@@ -6836,11 +6836,11 @@
         <v>125</v>
       </c>
       <c r="B94" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D94" t="s">
         <v>184</v>
@@ -6890,11 +6890,11 @@
         <v>126</v>
       </c>
       <c r="B95" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D95" t="s">
         <v>184</v>
@@ -6944,11 +6944,11 @@
         <v>127</v>
       </c>
       <c r="B96" s="2">
-        <v>46307</v>
+        <v>46313</v>
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="1"/>
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="D96" t="s">
         <v>184</v>
@@ -6998,11 +6998,11 @@
         <v>128</v>
       </c>
       <c r="B97" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D97" t="s">
         <v>184</v>
@@ -7052,11 +7052,11 @@
         <v>129</v>
       </c>
       <c r="B98" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D98" t="s">
         <v>184</v>
@@ -7106,11 +7106,11 @@
         <v>130</v>
       </c>
       <c r="B99" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D99" t="s">
         <v>184</v>
@@ -7160,11 +7160,11 @@
         <v>131</v>
       </c>
       <c r="B100" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D100" t="s">
         <v>184</v>
@@ -7214,11 +7214,11 @@
         <v>132</v>
       </c>
       <c r="B101" s="2">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="1"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D101" t="s">
         <v>184</v>
@@ -7268,11 +7268,11 @@
         <v>133</v>
       </c>
       <c r="B102" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C102">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D102" t="s">
         <v>184</v>
@@ -7322,11 +7322,11 @@
         <v>134</v>
       </c>
       <c r="B103" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C103">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D103" t="s">
         <v>184</v>
@@ -7376,11 +7376,11 @@
         <v>135</v>
       </c>
       <c r="B104" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C104">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D104" t="s">
         <v>184</v>
@@ -7430,11 +7430,11 @@
         <v>136</v>
       </c>
       <c r="B105" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C105">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D105" t="s">
         <v>184</v>
@@ -7484,11 +7484,11 @@
         <v>137</v>
       </c>
       <c r="B106" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C106">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D106" t="s">
         <v>184</v>
@@ -7538,11 +7538,11 @@
         <v>138</v>
       </c>
       <c r="B107" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C107">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D107" t="s">
         <v>184</v>
@@ -7592,11 +7592,11 @@
         <v>139</v>
       </c>
       <c r="B108" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C108">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D108" t="s">
         <v>184</v>
@@ -7646,11 +7646,11 @@
         <v>140</v>
       </c>
       <c r="B109" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C109">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D109" t="s">
         <v>184</v>
@@ -7700,11 +7700,11 @@
         <v>141</v>
       </c>
       <c r="B110" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C110">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D110" t="s">
         <v>184</v>
@@ -7754,11 +7754,11 @@
         <v>142</v>
       </c>
       <c r="B111" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C111">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D111" t="s">
         <v>184</v>
@@ -7840,11 +7840,11 @@
         <v>143</v>
       </c>
       <c r="B113" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C113">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D113" t="s">
         <v>184</v>
@@ -7894,11 +7894,11 @@
         <v>144</v>
       </c>
       <c r="B114" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C114">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D114" t="s">
         <v>184</v>
@@ -7948,11 +7948,11 @@
         <v>145</v>
       </c>
       <c r="B115" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C115">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D115" t="s">
         <v>184</v>
@@ -8002,11 +8002,11 @@
         <v>147</v>
       </c>
       <c r="B116" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C116">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D116" t="s">
         <v>184</v>
@@ -8056,11 +8056,11 @@
         <v>148</v>
       </c>
       <c r="B117" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C117">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D117" t="s">
         <v>184</v>
@@ -8110,11 +8110,11 @@
         <v>149</v>
       </c>
       <c r="B118" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C118">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D118" t="s">
         <v>184</v>
@@ -8164,11 +8164,11 @@
         <v>150</v>
       </c>
       <c r="B119" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C119">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D119" t="s">
         <v>184</v>
@@ -8218,11 +8218,11 @@
         <v>151</v>
       </c>
       <c r="B120" s="2">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C120">
         <f t="shared" ca="1" si="1"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D120" t="s">
         <v>184</v>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="C121">
         <f t="shared" ca="1" si="1"/>
-        <v>-46314</v>
+        <v>-46315</v>
       </c>
       <c r="D121" t="s">
         <v>469</v>
@@ -8326,11 +8326,11 @@
         <v>154</v>
       </c>
       <c r="B122" s="2">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C122">
         <f t="shared" ca="1" si="1"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D122" t="s">
         <v>184</v>
@@ -8380,11 +8380,11 @@
         <v>155</v>
       </c>
       <c r="B123" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C123">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D123" t="s">
         <v>184</v>
@@ -8434,11 +8434,11 @@
         <v>156</v>
       </c>
       <c r="B124" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C124">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D124" t="s">
         <v>184</v>
@@ -8488,11 +8488,11 @@
         <v>157</v>
       </c>
       <c r="B125" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C125">
         <f t="shared" ca="1" si="1"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D125" t="s">
         <v>184</v>
@@ -8542,11 +8542,11 @@
         <v>158</v>
       </c>
       <c r="B126" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C126">
         <f t="shared" ca="1" si="1"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D126" t="s">
         <v>184</v>
@@ -8596,11 +8596,11 @@
         <v>159</v>
       </c>
       <c r="B127" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C127">
         <f t="shared" ca="1" si="1"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D127" t="s">
         <v>184</v>
@@ -8650,11 +8650,11 @@
         <v>160</v>
       </c>
       <c r="B128" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C128">
         <f t="shared" ca="1" si="1"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D128" t="s">
         <v>184</v>
@@ -8704,11 +8704,11 @@
         <v>161</v>
       </c>
       <c r="B129" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C129">
         <f t="shared" ca="1" si="1"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D129" t="s">
         <v>184</v>
@@ -8758,11 +8758,11 @@
         <v>162</v>
       </c>
       <c r="B130" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C130">
         <f t="shared" ca="1" si="1"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D130" t="s">
         <v>184</v>
@@ -8812,11 +8812,11 @@
         <v>186</v>
       </c>
       <c r="B131" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C131">
         <f t="shared" ref="C131:C192" ca="1" si="2">B131-$R$1</f>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D131" t="s">
         <v>184</v>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="C132">
         <f t="shared" ca="1" si="2"/>
-        <v>-46314</v>
+        <v>-46315</v>
       </c>
       <c r="D132" t="s">
         <v>184</v>
@@ -8920,11 +8920,11 @@
         <v>188</v>
       </c>
       <c r="B133" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C133">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D133" t="s">
         <v>184</v>
@@ -8974,11 +8974,11 @@
         <v>189</v>
       </c>
       <c r="B134" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C134">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D134" t="s">
         <v>184</v>
@@ -9028,11 +9028,11 @@
         <v>190</v>
       </c>
       <c r="B135" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C135">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D135" t="s">
         <v>184</v>
@@ -9082,11 +9082,11 @@
         <v>191</v>
       </c>
       <c r="B136" s="2">
-        <v>0</v>
+        <v>46314</v>
       </c>
       <c r="C136">
         <f t="shared" ca="1" si="2"/>
-        <v>-46314</v>
+        <v>-1</v>
       </c>
       <c r="D136" t="s">
         <v>184</v>
@@ -9136,11 +9136,11 @@
         <v>192</v>
       </c>
       <c r="B137" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C137">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D137" t="s">
         <v>184</v>
@@ -9666,11 +9666,11 @@
         <v>164</v>
       </c>
       <c r="B151" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C151">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D151" t="s">
         <v>184</v>
@@ -9720,11 +9720,11 @@
         <v>165</v>
       </c>
       <c r="B152" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C152">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D152" t="s">
         <v>184</v>
@@ -9774,11 +9774,11 @@
         <v>166</v>
       </c>
       <c r="B153" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C153">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D153" t="s">
         <v>184</v>
@@ -9828,11 +9828,11 @@
         <v>167</v>
       </c>
       <c r="B154" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C154">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D154" t="s">
         <v>184</v>
@@ -9882,11 +9882,11 @@
         <v>168</v>
       </c>
       <c r="B155" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D155" t="s">
         <v>184</v>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="D156" t="s">
         <v>184</v>
@@ -9990,11 +9990,11 @@
         <v>170</v>
       </c>
       <c r="B157" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D157" t="s">
         <v>184</v>
@@ -10044,11 +10044,11 @@
         <v>171</v>
       </c>
       <c r="B158" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C158">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D158" t="s">
         <v>184</v>
@@ -10098,11 +10098,11 @@
         <v>172</v>
       </c>
       <c r="B159" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C159">
         <f t="shared" ca="1" si="2"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D159" t="s">
         <v>184</v>
@@ -10152,11 +10152,11 @@
         <v>173</v>
       </c>
       <c r="B160" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D160" t="s">
         <v>184</v>
@@ -10206,11 +10206,11 @@
         <v>175</v>
       </c>
       <c r="B161" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D161" t="s">
         <v>184</v>
@@ -10260,11 +10260,11 @@
         <v>176</v>
       </c>
       <c r="B162" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D162" t="s">
         <v>184</v>
@@ -10392,11 +10392,11 @@
         <v>208</v>
       </c>
       <c r="B165" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D165" t="s">
         <v>469</v>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="C173">
         <f t="shared" ca="1" si="2"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D173" t="s">
         <v>184</v>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="C174">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D174" t="s">
         <v>184</v>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="C175">
         <f t="shared" ca="1" si="2"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D175" t="s">
         <v>184</v>
@@ -10884,11 +10884,11 @@
         <v>229</v>
       </c>
       <c r="B176" s="2">
-        <v>46305</v>
+        <v>46314</v>
       </c>
       <c r="C176">
         <f t="shared" ca="1" si="2"/>
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="D176" t="s">
         <v>184</v>
@@ -10935,11 +10935,11 @@
         <v>230</v>
       </c>
       <c r="B177" s="2">
-        <v>46304</v>
+        <v>46314</v>
       </c>
       <c r="C177">
         <f t="shared" ca="1" si="2"/>
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="D177" t="s">
         <v>184</v>
@@ -10986,11 +10986,11 @@
         <v>231</v>
       </c>
       <c r="B178" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C178">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D178" t="s">
         <v>184</v>
@@ -11037,11 +11037,11 @@
         <v>232</v>
       </c>
       <c r="B179" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C179">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D179" t="s">
         <v>184</v>
@@ -11088,11 +11088,11 @@
         <v>233</v>
       </c>
       <c r="B180" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C180">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D180" t="s">
         <v>184</v>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="C181">
         <f t="shared" ca="1" si="2"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D181" t="s">
         <v>184</v>
@@ -11190,11 +11190,11 @@
         <v>235</v>
       </c>
       <c r="B182" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C182">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D182" t="s">
         <v>184</v>
@@ -11241,11 +11241,11 @@
         <v>236</v>
       </c>
       <c r="B183" s="2">
-        <v>46303</v>
+        <v>46314</v>
       </c>
       <c r="C183">
         <f t="shared" ca="1" si="2"/>
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="D183" t="s">
         <v>184</v>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="C184">
         <f t="shared" ca="1" si="2"/>
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="D184" t="s">
         <v>184</v>
@@ -11343,11 +11343,11 @@
         <v>238</v>
       </c>
       <c r="B185" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C185">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D185" t="s">
         <v>184</v>
@@ -11394,11 +11394,11 @@
         <v>239</v>
       </c>
       <c r="B186" s="2">
-        <v>46301</v>
+        <v>46314</v>
       </c>
       <c r="C186">
         <f t="shared" ca="1" si="2"/>
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="D186" t="s">
         <v>184</v>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="C187">
         <f t="shared" ca="1" si="2"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D187" t="s">
         <v>184</v>
@@ -11496,11 +11496,11 @@
         <v>241</v>
       </c>
       <c r="B188" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C188">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D188" t="s">
         <v>184</v>
@@ -11547,11 +11547,11 @@
         <v>242</v>
       </c>
       <c r="B189" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C189">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D189" t="s">
         <v>184</v>
@@ -11598,11 +11598,11 @@
         <v>243</v>
       </c>
       <c r="B190" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C190">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D190" t="s">
         <v>184</v>
@@ -11649,11 +11649,11 @@
         <v>244</v>
       </c>
       <c r="B191" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C191">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D191" t="s">
         <v>184</v>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="C192">
         <f t="shared" ca="1" si="2"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D192" t="s">
         <v>184</v>
@@ -11751,11 +11751,11 @@
         <v>246</v>
       </c>
       <c r="B193" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C193">
         <f t="shared" ref="C193:C256" ca="1" si="3">B193-$R$1</f>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D193" t="s">
         <v>184</v>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="C194">
         <f t="shared" ca="1" si="3"/>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="D194" t="s">
         <v>184</v>
@@ -11853,11 +11853,11 @@
         <v>248</v>
       </c>
       <c r="B195" s="2">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="C195">
         <f t="shared" ca="1" si="3"/>
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="D195" t="s">
         <v>184</v>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="C198">
         <f t="shared" ca="1" si="3"/>
-        <v>-147</v>
+        <v>-148</v>
       </c>
       <c r="D198" t="s">
         <v>184</v>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="C199">
         <f t="shared" ca="1" si="3"/>
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="D199" t="s">
         <v>184</v>
@@ -12112,7 +12112,7 @@
       </c>
       <c r="C200">
         <f t="shared" ca="1" si="3"/>
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="D200" t="s">
         <v>184</v>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="C201">
         <f t="shared" ca="1" si="3"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D201" t="s">
         <v>184</v>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="C202">
         <f t="shared" ca="1" si="3"/>
-        <v>-277</v>
+        <v>-278</v>
       </c>
       <c r="D202" t="s">
         <v>184</v>
@@ -12261,11 +12261,11 @@
         <v>256</v>
       </c>
       <c r="B203" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C203">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D203" t="s">
         <v>184</v>
@@ -12312,11 +12312,11 @@
         <v>257</v>
       </c>
       <c r="B204" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C204">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D204" t="s">
         <v>184</v>
@@ -12363,11 +12363,11 @@
         <v>258</v>
       </c>
       <c r="B205" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C205">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D205" t="s">
         <v>184</v>
@@ -12414,11 +12414,11 @@
         <v>259</v>
       </c>
       <c r="B206" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C206">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D206" t="s">
         <v>184</v>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="C207">
         <f t="shared" ca="1" si="3"/>
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="D207" t="s">
         <v>184</v>
@@ -12516,11 +12516,11 @@
         <v>261</v>
       </c>
       <c r="B208" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C208">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D208" t="s">
         <v>184</v>
@@ -12567,11 +12567,11 @@
         <v>262</v>
       </c>
       <c r="B209" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C209">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D209" t="s">
         <v>184</v>
@@ -12618,11 +12618,11 @@
         <v>263</v>
       </c>
       <c r="B210" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C210">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D210" t="s">
         <v>184</v>
@@ -12669,11 +12669,11 @@
         <v>264</v>
       </c>
       <c r="B211" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C211">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D211" t="s">
         <v>184</v>
@@ -12720,11 +12720,11 @@
         <v>265</v>
       </c>
       <c r="B212" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C212">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D212" t="s">
         <v>184</v>
@@ -12771,11 +12771,11 @@
         <v>266</v>
       </c>
       <c r="B213" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C213">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D213" t="s">
         <v>184</v>
@@ -12822,11 +12822,11 @@
         <v>267</v>
       </c>
       <c r="B214" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C214">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D214" t="s">
         <v>184</v>
@@ -12873,11 +12873,11 @@
         <v>268</v>
       </c>
       <c r="B215" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C215">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D215" t="s">
         <v>184</v>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C216">
         <f t="shared" ca="1" si="3"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
@@ -12975,11 +12975,11 @@
         <v>270</v>
       </c>
       <c r="B217" s="2">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="C217">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="D217" t="s">
         <v>184</v>
@@ -13026,11 +13026,11 @@
         <v>271</v>
       </c>
       <c r="B218" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C218">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D218" t="s">
         <v>184</v>
@@ -13081,7 +13081,7 @@
       </c>
       <c r="C219">
         <f t="shared" ca="1" si="3"/>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="D219" t="s">
         <v>184</v>
@@ -13132,7 +13132,7 @@
       </c>
       <c r="C220">
         <f t="shared" ca="1" si="3"/>
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="D220" t="s">
         <v>184</v>
@@ -13179,11 +13179,11 @@
         <v>274</v>
       </c>
       <c r="B221" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C221">
         <f t="shared" ca="1" si="3"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D221" t="s">
         <v>184</v>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="C222">
         <f t="shared" ca="1" si="3"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D222" t="s">
         <v>184</v>
@@ -13281,11 +13281,11 @@
         <v>276</v>
       </c>
       <c r="B223" s="2">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C223">
         <f t="shared" ca="1" si="3"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D223" t="s">
         <v>184</v>
@@ -13332,11 +13332,11 @@
         <v>277</v>
       </c>
       <c r="B224" s="2">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="C224">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="D224" t="s">
         <v>184</v>
@@ -13383,11 +13383,11 @@
         <v>278</v>
       </c>
       <c r="B225" s="2">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="C225">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="D225" t="s">
         <v>184</v>
@@ -13434,11 +13434,11 @@
         <v>279</v>
       </c>
       <c r="B226" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C226">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D226" t="s">
         <v>184</v>
@@ -13485,11 +13485,11 @@
         <v>280</v>
       </c>
       <c r="B227" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C227">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D227" t="s">
         <v>184</v>
@@ -13540,7 +13540,7 @@
       </c>
       <c r="C228">
         <f t="shared" ca="1" si="3"/>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="D228" t="s">
         <v>184</v>
@@ -13587,11 +13587,11 @@
         <v>282</v>
       </c>
       <c r="B229" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C229">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D229" t="s">
         <v>184</v>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="C230">
         <f t="shared" ca="1" si="3"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D230" t="s">
         <v>184</v>
@@ -13689,11 +13689,11 @@
         <v>284</v>
       </c>
       <c r="B231" s="2">
-        <v>46308</v>
+        <v>46313</v>
       </c>
       <c r="C231">
         <f t="shared" ca="1" si="3"/>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="D231" t="s">
         <v>184</v>
@@ -13740,11 +13740,11 @@
         <v>285</v>
       </c>
       <c r="B232" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C232">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D232" t="s">
         <v>184</v>
@@ -13791,11 +13791,11 @@
         <v>286</v>
       </c>
       <c r="B233" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C233">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D233" t="s">
         <v>184</v>
@@ -13842,11 +13842,11 @@
         <v>287</v>
       </c>
       <c r="B234" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C234">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D234" t="s">
         <v>184</v>
@@ -13893,11 +13893,11 @@
         <v>288</v>
       </c>
       <c r="B235" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C235">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D235" t="s">
         <v>184</v>
@@ -13944,11 +13944,11 @@
         <v>289</v>
       </c>
       <c r="B236" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C236">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D236" t="s">
         <v>184</v>
@@ -13995,11 +13995,11 @@
         <v>290</v>
       </c>
       <c r="B237" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C237">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D237" t="s">
         <v>184</v>
@@ -14046,11 +14046,11 @@
         <v>291</v>
       </c>
       <c r="B238" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C238">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D238" t="s">
         <v>184</v>
@@ -14101,7 +14101,7 @@
       </c>
       <c r="C239">
         <f t="shared" ca="1" si="3"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D239" t="s">
         <v>184</v>
@@ -14148,11 +14148,11 @@
         <v>293</v>
       </c>
       <c r="B240" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C240">
         <f t="shared" ca="1" si="3"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D240" t="s">
         <v>184</v>
@@ -14199,11 +14199,11 @@
         <v>294</v>
       </c>
       <c r="B241" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C241">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D241" t="s">
         <v>184</v>
@@ -14250,11 +14250,11 @@
         <v>295</v>
       </c>
       <c r="B242" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C242">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D242" t="s">
         <v>184</v>
@@ -14301,11 +14301,11 @@
         <v>296</v>
       </c>
       <c r="B243" s="2">
-        <v>46274</v>
+        <v>46314</v>
       </c>
       <c r="C243">
         <f t="shared" ca="1" si="3"/>
-        <v>-40</v>
+        <v>-1</v>
       </c>
       <c r="D243" t="s">
         <v>184</v>
@@ -14352,11 +14352,11 @@
         <v>297</v>
       </c>
       <c r="B244" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C244">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D244" t="s">
         <v>184</v>
@@ -14403,11 +14403,11 @@
         <v>298</v>
       </c>
       <c r="B245" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C245">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D245" t="s">
         <v>184</v>
@@ -14454,11 +14454,11 @@
         <v>299</v>
       </c>
       <c r="B246" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C246">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D246" t="s">
         <v>184</v>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="C247">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D247" t="s">
         <v>184</v>
@@ -14560,7 +14560,7 @@
       </c>
       <c r="C248">
         <f t="shared" ca="1" si="3"/>
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="D248" t="s">
         <v>184</v>
@@ -14607,11 +14607,11 @@
         <v>302</v>
       </c>
       <c r="B249" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C249">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D249" t="s">
         <v>184</v>
@@ -14658,11 +14658,11 @@
         <v>303</v>
       </c>
       <c r="B250" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C250">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D250" t="s">
         <v>184</v>
@@ -14709,11 +14709,11 @@
         <v>304</v>
       </c>
       <c r="B251" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C251">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D251" t="s">
         <v>184</v>
@@ -14760,11 +14760,11 @@
         <v>305</v>
       </c>
       <c r="B252" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C252">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D252" t="s">
         <v>184</v>
@@ -14811,11 +14811,11 @@
         <v>306</v>
       </c>
       <c r="B253" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C253">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D253" t="s">
         <v>184</v>
@@ -14862,11 +14862,11 @@
         <v>307</v>
       </c>
       <c r="B254" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C254">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D254" t="s">
         <v>184</v>
@@ -14917,7 +14917,7 @@
       </c>
       <c r="C255">
         <f t="shared" ca="1" si="3"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D255" t="s">
         <v>184</v>
@@ -14964,11 +14964,11 @@
         <v>309</v>
       </c>
       <c r="B256" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C256">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D256" t="s">
         <v>184</v>
@@ -15019,7 +15019,7 @@
       </c>
       <c r="C257">
         <f t="shared" ref="C257:C320" ca="1" si="4">B257-$R$1</f>
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="D257" t="s">
         <v>184</v>
@@ -15066,11 +15066,11 @@
         <v>311</v>
       </c>
       <c r="B258" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C258">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D258" t="s">
         <v>184</v>
@@ -15117,11 +15117,11 @@
         <v>312</v>
       </c>
       <c r="B259" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C259">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D259" t="s">
         <v>184</v>
@@ -15168,11 +15168,11 @@
         <v>313</v>
       </c>
       <c r="B260" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C260">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D260" t="s">
         <v>184</v>
@@ -15219,11 +15219,11 @@
         <v>314</v>
       </c>
       <c r="B261" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C261">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D261" t="s">
         <v>184</v>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C262">
         <f t="shared" ca="1" si="4"/>
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="D262" t="s">
         <v>184</v>
@@ -15321,11 +15321,11 @@
         <v>316</v>
       </c>
       <c r="B263" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C263">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D263" t="s">
         <v>184</v>
@@ -15372,11 +15372,11 @@
         <v>317</v>
       </c>
       <c r="B264" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C264">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D264" t="s">
         <v>184</v>
@@ -15423,11 +15423,11 @@
         <v>318</v>
       </c>
       <c r="B265" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C265">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D265" t="s">
         <v>184</v>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="C266">
         <f t="shared" ca="1" si="4"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D266" t="s">
         <v>184</v>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="C267">
         <f t="shared" ca="1" si="4"/>
-        <v>-137</v>
+        <v>-138</v>
       </c>
       <c r="D267" t="s">
         <v>184</v>
@@ -15576,11 +15576,11 @@
         <v>321</v>
       </c>
       <c r="B268" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C268">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D268" t="s">
         <v>184</v>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="C269">
         <f t="shared" ca="1" si="4"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D269" t="s">
         <v>184</v>
@@ -15678,11 +15678,11 @@
         <v>323</v>
       </c>
       <c r="B270" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C270">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D270" t="s">
         <v>184</v>
@@ -15729,11 +15729,11 @@
         <v>324</v>
       </c>
       <c r="B271" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C271">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D271" t="s">
         <v>184</v>
@@ -15780,11 +15780,11 @@
         <v>325</v>
       </c>
       <c r="B272" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C272">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D272" t="s">
         <v>184</v>
@@ -15831,11 +15831,11 @@
         <v>326</v>
       </c>
       <c r="B273" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C273">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D273" t="s">
         <v>184</v>
@@ -15882,11 +15882,11 @@
         <v>327</v>
       </c>
       <c r="B274" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C274">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D274" t="s">
         <v>184</v>
@@ -15933,11 +15933,11 @@
         <v>328</v>
       </c>
       <c r="B275" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C275">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D275" t="s">
         <v>184</v>
@@ -15984,11 +15984,11 @@
         <v>329</v>
       </c>
       <c r="B276" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C276">
         <f t="shared" ca="1" si="4"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D276" t="s">
         <v>184</v>
@@ -16035,11 +16035,11 @@
         <v>330</v>
       </c>
       <c r="B277" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C277">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D277" t="s">
         <v>184</v>
@@ -16086,11 +16086,11 @@
         <v>331</v>
       </c>
       <c r="B278" s="2">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="C278">
         <f t="shared" ca="1" si="4"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D278" t="s">
         <v>184</v>
@@ -16137,11 +16137,11 @@
         <v>332</v>
       </c>
       <c r="B279" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C279">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D279" t="s">
         <v>184</v>
@@ -16188,11 +16188,11 @@
         <v>333</v>
       </c>
       <c r="B280" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C280">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D280" t="s">
         <v>184</v>
@@ -16239,11 +16239,11 @@
         <v>334</v>
       </c>
       <c r="B281" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C281">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D281" t="s">
         <v>184</v>
@@ -16290,11 +16290,11 @@
         <v>335</v>
       </c>
       <c r="B282" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C282">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D282" t="s">
         <v>184</v>
@@ -16341,7 +16341,7 @@
         <v>336</v>
       </c>
       <c r="B283" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C283">
         <f t="shared" ca="1" si="4"/>
@@ -16392,11 +16392,11 @@
         <v>337</v>
       </c>
       <c r="B284" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C284">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D284" t="s">
         <v>184</v>
@@ -16443,11 +16443,11 @@
         <v>338</v>
       </c>
       <c r="B285" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C285">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D285" t="s">
         <v>184</v>
@@ -16494,11 +16494,11 @@
         <v>339</v>
       </c>
       <c r="B286" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C286">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D286" t="s">
         <v>184</v>
@@ -16545,11 +16545,11 @@
         <v>340</v>
       </c>
       <c r="B287" s="2">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="C287">
         <f t="shared" ca="1" si="4"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="D287" t="s">
         <v>184</v>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="C288">
         <f t="shared" ca="1" si="4"/>
-        <v>-223</v>
+        <v>-224</v>
       </c>
       <c r="D288" t="s">
         <v>184</v>
@@ -16647,11 +16647,11 @@
         <v>342</v>
       </c>
       <c r="B289" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C289">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D289" t="s">
         <v>184</v>
@@ -16698,11 +16698,11 @@
         <v>343</v>
       </c>
       <c r="B290" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C290">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D290" t="s">
         <v>184</v>
@@ -16749,11 +16749,11 @@
         <v>344</v>
       </c>
       <c r="B291" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C291">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D291" t="s">
         <v>184</v>
@@ -16800,11 +16800,11 @@
         <v>345</v>
       </c>
       <c r="B292" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C292">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D292" t="s">
         <v>184</v>
@@ -16851,11 +16851,11 @@
         <v>346</v>
       </c>
       <c r="B293" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C293">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D293" t="s">
         <v>184</v>
@@ -16906,7 +16906,7 @@
       </c>
       <c r="C294">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D294" t="s">
         <v>184</v>
@@ -16953,11 +16953,11 @@
         <v>348</v>
       </c>
       <c r="B295" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C295">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D295" t="s">
         <v>184</v>
@@ -17004,11 +17004,11 @@
         <v>349</v>
       </c>
       <c r="B296" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C296">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D296" t="s">
         <v>184</v>
@@ -17055,11 +17055,11 @@
         <v>350</v>
       </c>
       <c r="B297" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C297">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D297" t="s">
         <v>184</v>
@@ -17106,11 +17106,11 @@
         <v>351</v>
       </c>
       <c r="B298" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C298">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D298" t="s">
         <v>184</v>
@@ -17157,11 +17157,11 @@
         <v>352</v>
       </c>
       <c r="B299" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C299">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D299" t="s">
         <v>184</v>
@@ -17208,11 +17208,11 @@
         <v>353</v>
       </c>
       <c r="B300" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C300">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D300" t="s">
         <v>184</v>
@@ -17259,11 +17259,11 @@
         <v>354</v>
       </c>
       <c r="B301" s="2">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="C301">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="D301" t="s">
         <v>184</v>
@@ -17310,11 +17310,11 @@
         <v>355</v>
       </c>
       <c r="B302" s="2">
-        <v>46309</v>
+        <v>46312</v>
       </c>
       <c r="C302">
         <f t="shared" ca="1" si="4"/>
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="D302" t="s">
         <v>184</v>
@@ -17361,11 +17361,11 @@
         <v>356</v>
       </c>
       <c r="B303" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C303">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D303" t="s">
         <v>184</v>
@@ -17412,11 +17412,11 @@
         <v>357</v>
       </c>
       <c r="B304" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C304">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D304" t="s">
         <v>184</v>
@@ -17463,11 +17463,11 @@
         <v>358</v>
       </c>
       <c r="B305" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C305">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D305" t="s">
         <v>184</v>
@@ -17514,11 +17514,11 @@
         <v>359</v>
       </c>
       <c r="B306" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C306">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D306" t="s">
         <v>184</v>
@@ -17565,11 +17565,11 @@
         <v>360</v>
       </c>
       <c r="B307" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C307">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D307" t="s">
         <v>184</v>
@@ -17616,11 +17616,11 @@
         <v>361</v>
       </c>
       <c r="B308" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C308">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D308" t="s">
         <v>184</v>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="C309">
         <f t="shared" ca="1" si="4"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D309" t="s">
         <v>184</v>
@@ -17718,11 +17718,11 @@
         <v>363</v>
       </c>
       <c r="B310" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C310">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D310" t="s">
         <v>184</v>
@@ -17769,11 +17769,11 @@
         <v>364</v>
       </c>
       <c r="B311" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C311">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D311" t="s">
         <v>184</v>
@@ -17824,7 +17824,7 @@
       </c>
       <c r="C312">
         <f t="shared" ca="1" si="4"/>
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="D312" t="s">
         <v>184</v>
@@ -17871,11 +17871,11 @@
         <v>366</v>
       </c>
       <c r="B313" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C313">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D313" t="s">
         <v>184</v>
@@ -17922,11 +17922,11 @@
         <v>367</v>
       </c>
       <c r="B314" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C314">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D314" t="s">
         <v>184</v>
@@ -17977,7 +17977,7 @@
       </c>
       <c r="C315">
         <f t="shared" ca="1" si="4"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D315" t="s">
         <v>184</v>
@@ -18024,11 +18024,11 @@
         <v>369</v>
       </c>
       <c r="B316" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C316">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D316" t="s">
         <v>184</v>
@@ -18075,11 +18075,11 @@
         <v>370</v>
       </c>
       <c r="B317" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C317">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D317" t="s">
         <v>184</v>
@@ -18130,7 +18130,7 @@
       </c>
       <c r="C318">
         <f t="shared" ca="1" si="4"/>
-        <v>-70</v>
+        <v>-71</v>
       </c>
       <c r="D318" t="s">
         <v>184</v>
@@ -18181,7 +18181,7 @@
       </c>
       <c r="C319">
         <f t="shared" ca="1" si="4"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D319" t="s">
         <v>184</v>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="C320">
         <f t="shared" ca="1" si="4"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D320" t="s">
         <v>184</v>
@@ -18279,11 +18279,11 @@
         <v>374</v>
       </c>
       <c r="B321" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C321">
         <f t="shared" ref="C321:C384" ca="1" si="5">B321-$R$1</f>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D321" t="s">
         <v>184</v>
@@ -18334,7 +18334,7 @@
       </c>
       <c r="C322">
         <f t="shared" ca="1" si="5"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D322" t="s">
         <v>184</v>
@@ -18385,7 +18385,7 @@
       </c>
       <c r="C323">
         <f t="shared" ca="1" si="5"/>
-        <v>-74</v>
+        <v>-75</v>
       </c>
       <c r="D323" t="s">
         <v>184</v>
@@ -18436,7 +18436,7 @@
       </c>
       <c r="C324">
         <f t="shared" ca="1" si="5"/>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="D324" t="s">
         <v>184</v>
@@ -18483,11 +18483,11 @@
         <v>378</v>
       </c>
       <c r="B325" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C325">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D325" t="s">
         <v>184</v>
@@ -18538,7 +18538,7 @@
       </c>
       <c r="C326">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D326" t="s">
         <v>184</v>
@@ -18585,11 +18585,11 @@
         <v>380</v>
       </c>
       <c r="B327" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C327">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D327" t="s">
         <v>184</v>
@@ -18636,11 +18636,11 @@
         <v>381</v>
       </c>
       <c r="B328" s="2">
-        <v>46309</v>
+        <v>46312</v>
       </c>
       <c r="C328">
         <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="D328" t="s">
         <v>184</v>
@@ -18687,11 +18687,11 @@
         <v>382</v>
       </c>
       <c r="B329" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C329">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D329" t="s">
         <v>184</v>
@@ -18738,11 +18738,11 @@
         <v>383</v>
       </c>
       <c r="B330" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C330">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D330" t="s">
         <v>184</v>
@@ -18789,11 +18789,11 @@
         <v>384</v>
       </c>
       <c r="B331" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C331">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D331" t="s">
         <v>184</v>
@@ -18840,11 +18840,11 @@
         <v>385</v>
       </c>
       <c r="B332" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C332">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D332" t="s">
         <v>184</v>
@@ -18891,11 +18891,11 @@
         <v>386</v>
       </c>
       <c r="B333" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C333">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D333" t="s">
         <v>184</v>
@@ -18942,11 +18942,11 @@
         <v>387</v>
       </c>
       <c r="B334" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C334">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D334" t="s">
         <v>184</v>
@@ -18993,11 +18993,11 @@
         <v>388</v>
       </c>
       <c r="B335" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C335">
         <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D335" t="s">
         <v>184</v>
@@ -19044,11 +19044,11 @@
         <v>389</v>
       </c>
       <c r="B336" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C336">
         <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D336" t="s">
         <v>184</v>
@@ -19095,11 +19095,11 @@
         <v>390</v>
       </c>
       <c r="B337" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C337">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D337" t="s">
         <v>184</v>
@@ -19146,11 +19146,11 @@
         <v>391</v>
       </c>
       <c r="B338" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C338">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D338" t="s">
         <v>184</v>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="C339">
         <f t="shared" ca="1" si="5"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D339" t="s">
         <v>184</v>
@@ -19248,11 +19248,11 @@
         <v>393</v>
       </c>
       <c r="B340" s="2">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C340">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D340" t="s">
         <v>184</v>
@@ -19299,11 +19299,11 @@
         <v>394</v>
       </c>
       <c r="B341" s="2">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="C341">
         <f t="shared" ca="1" si="5"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="D341" t="s">
         <v>184</v>
@@ -19350,11 +19350,11 @@
         <v>395</v>
       </c>
       <c r="B342" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C342">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D342" t="s">
         <v>184</v>
@@ -19405,7 +19405,7 @@
       </c>
       <c r="C343">
         <f t="shared" ca="1" si="5"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D343" t="s">
         <v>184</v>
@@ -19452,11 +19452,11 @@
         <v>397</v>
       </c>
       <c r="B344" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C344">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D344" t="s">
         <v>184</v>
@@ -19503,11 +19503,11 @@
         <v>398</v>
       </c>
       <c r="B345" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C345">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D345" t="s">
         <v>184</v>
@@ -19554,11 +19554,11 @@
         <v>399</v>
       </c>
       <c r="B346" s="2">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="C346">
         <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D346" t="s">
         <v>184</v>
@@ -19605,11 +19605,11 @@
         <v>400</v>
       </c>
       <c r="B347" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C347">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D347" t="s">
         <v>184</v>
@@ -19656,11 +19656,11 @@
         <v>401</v>
       </c>
       <c r="B348" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C348">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D348" t="s">
         <v>184</v>
@@ -19707,11 +19707,11 @@
         <v>402</v>
       </c>
       <c r="B349" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C349">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D349" t="s">
         <v>184</v>
@@ -19758,11 +19758,11 @@
         <v>403</v>
       </c>
       <c r="B350" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C350">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D350" t="s">
         <v>184</v>
@@ -19813,7 +19813,7 @@
       </c>
       <c r="C351">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D351" t="s">
         <v>184</v>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="C352">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D352" t="s">
         <v>184</v>
@@ -19911,11 +19911,11 @@
         <v>406</v>
       </c>
       <c r="B353" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="C353">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D353" t="s">
         <v>184</v>
@@ -19962,7 +19962,7 @@
         <v>407</v>
       </c>
       <c r="B354" s="2">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C354">
         <f t="shared" ca="1" si="5"/>
@@ -20013,7 +20013,7 @@
         <v>408</v>
       </c>
       <c r="B355" s="2">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C355">
         <f t="shared" ca="1" si="5"/>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="C356">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D356" t="s">
         <v>184</v>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="C357">
         <f t="shared" ca="1" si="5"/>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="D357" t="s">
         <v>184</v>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="C358">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D358" t="s">
         <v>184</v>
@@ -20221,7 +20221,7 @@
       </c>
       <c r="C359">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D359" t="s">
         <v>184</v>
@@ -20268,7 +20268,7 @@
         <v>413</v>
       </c>
       <c r="B360" s="2">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C360">
         <f t="shared" ca="1" si="5"/>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C361">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D361" t="s">
         <v>184</v>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C362">
         <f t="shared" ca="1" si="5"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D362" t="s">
         <v>184</v>
@@ -20425,7 +20425,7 @@
       </c>
       <c r="C363">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D363" t="s">
         <v>184</v>
@@ -20476,7 +20476,7 @@
       </c>
       <c r="C364">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D364" t="s">
         <v>184</v>
@@ -20523,7 +20523,7 @@
         <v>418</v>
       </c>
       <c r="B365" s="2">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C365">
         <f t="shared" ca="1" si="5"/>
@@ -20574,11 +20574,11 @@
         <v>419</v>
       </c>
       <c r="B366" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="C366">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D366" t="s">
         <v>184</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C367">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D367" t="s">
         <v>184</v>
@@ -20676,11 +20676,11 @@
         <v>421</v>
       </c>
       <c r="B368" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="C368">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D368" t="s">
         <v>184</v>
@@ -20727,11 +20727,11 @@
         <v>422</v>
       </c>
       <c r="B369" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="C369">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D369" t="s">
         <v>184</v>
@@ -20782,7 +20782,7 @@
       </c>
       <c r="C370">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D370" t="s">
         <v>184</v>
@@ -20829,7 +20829,7 @@
         <v>424</v>
       </c>
       <c r="B371" s="2">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C371">
         <f t="shared" ca="1" si="5"/>
@@ -20880,7 +20880,7 @@
         <v>425</v>
       </c>
       <c r="B372" s="2">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C372">
         <f t="shared" ca="1" si="5"/>
@@ -20931,7 +20931,7 @@
         <v>426</v>
       </c>
       <c r="B373" s="2">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C373">
         <f t="shared" ca="1" si="5"/>
@@ -20986,7 +20986,7 @@
       </c>
       <c r="C374">
         <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D374" t="s">
         <v>184</v>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="C375">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D375" t="s">
         <v>184</v>
@@ -21084,11 +21084,11 @@
         <v>429</v>
       </c>
       <c r="B376" s="2">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="C376">
         <f t="shared" ca="1" si="5"/>
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="D376" t="s">
         <v>184</v>
@@ -21139,7 +21139,7 @@
       </c>
       <c r="C377">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D377" t="s">
         <v>184</v>
@@ -21186,11 +21186,11 @@
         <v>431</v>
       </c>
       <c r="B378" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="C378">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D378" t="s">
         <v>184</v>
@@ -21237,7 +21237,7 @@
         <v>432</v>
       </c>
       <c r="B379" s="2">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C379">
         <f t="shared" ca="1" si="5"/>
@@ -21288,11 +21288,11 @@
         <v>433</v>
       </c>
       <c r="B380" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="C380">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D380" t="s">
         <v>184</v>
@@ -21339,11 +21339,11 @@
         <v>434</v>
       </c>
       <c r="B381" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="C381">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D381" t="s">
         <v>184</v>
@@ -21390,11 +21390,11 @@
         <v>435</v>
       </c>
       <c r="B382" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="C382">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D382" t="s">
         <v>184</v>
@@ -21445,7 +21445,7 @@
       </c>
       <c r="C383">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D383" t="s">
         <v>184</v>
@@ -21492,11 +21492,11 @@
         <v>437</v>
       </c>
       <c r="B384" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="C384">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D384" t="s">
         <v>184</v>
@@ -21547,7 +21547,7 @@
       </c>
       <c r="C385">
         <f t="shared" ref="C385:C392" ca="1" si="6">B385-$R$1</f>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D385" t="s">
         <v>184</v>
@@ -21594,11 +21594,11 @@
         <v>439</v>
       </c>
       <c r="B386" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="C386">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D386" t="s">
         <v>184</v>
@@ -21649,7 +21649,7 @@
       </c>
       <c r="C387">
         <f t="shared" ca="1" si="6"/>
-        <v>-46314</v>
+        <v>-46315</v>
       </c>
       <c r="D387" t="s">
         <v>184</v>
@@ -21700,7 +21700,7 @@
       </c>
       <c r="C388">
         <f t="shared" ca="1" si="6"/>
-        <v>-46314</v>
+        <v>-46315</v>
       </c>
       <c r="D388" t="s">
         <v>184</v>
@@ -21751,7 +21751,7 @@
       </c>
       <c r="C389">
         <f t="shared" ca="1" si="6"/>
-        <v>-46314</v>
+        <v>-46315</v>
       </c>
       <c r="D389" t="s">
         <v>184</v>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="C390">
         <f t="shared" ca="1" si="6"/>
-        <v>-46314</v>
+        <v>-46315</v>
       </c>
       <c r="D390" t="s">
         <v>184</v>
@@ -21853,7 +21853,7 @@
       </c>
       <c r="C391">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D391" t="s">
         <v>184</v>
@@ -21900,7 +21900,7 @@
         <v>445</v>
       </c>
       <c r="B392" s="2">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C392">
         <f t="shared" ca="1" si="6"/>
@@ -21947,7 +21947,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R392" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21965,15 +21964,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -22234,6 +22224,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
@@ -22246,14 +22245,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22270,4 +22261,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="381" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96115E71-B3C0-4B1A-AE29-5AA97C99CFCC}"/>
+  <xr:revisionPtr revIDLastSave="386" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EB43603-928F-47ED-B22B-17DF8268293F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="R1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1884,7 +1884,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C2">
         <f ca="1">B2-$R$1</f>
@@ -1936,7 +1936,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C66" ca="1" si="0">B3-$R$1</f>
@@ -1988,11 +1988,11 @@
         <v>15</v>
       </c>
       <c r="B4" s="2">
-        <v>46302</v>
+        <v>46315</v>
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="D4" t="s">
         <v>184</v>
@@ -2040,7 +2040,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
@@ -2092,7 +2092,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D7" t="s">
         <v>184</v>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D8" t="s">
         <v>184</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D9" t="s">
         <v>184</v>
@@ -2300,7 +2300,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
@@ -2354,7 +2354,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
@@ -2408,11 +2408,11 @@
         <v>27</v>
       </c>
       <c r="B12" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D12" t="s">
         <v>184</v>
@@ -2462,7 +2462,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
@@ -2516,7 +2516,7 @@
         <v>36</v>
       </c>
       <c r="B14" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
@@ -2570,7 +2570,7 @@
         <v>37</v>
       </c>
       <c r="B15" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D16" t="s">
         <v>184</v>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D17" t="s">
         <v>184</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D18" t="s">
         <v>184</v>
@@ -2786,7 +2786,7 @@
         <v>41</v>
       </c>
       <c r="B19" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D20" t="s">
         <v>184</v>
@@ -2894,7 +2894,7 @@
         <v>43</v>
       </c>
       <c r="B21" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="0"/>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D22" t="s">
         <v>184</v>
@@ -3002,7 +3002,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="0"/>
@@ -3056,11 +3056,11 @@
         <v>47</v>
       </c>
       <c r="B24" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D24" t="s">
         <v>184</v>
@@ -3110,7 +3110,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="0"/>
@@ -3164,7 +3164,7 @@
         <v>49</v>
       </c>
       <c r="B26" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="0"/>
@@ -3218,7 +3218,7 @@
         <v>50</v>
       </c>
       <c r="B27" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="0"/>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D28" t="s">
         <v>184</v>
@@ -3326,7 +3326,7 @@
         <v>52</v>
       </c>
       <c r="B29" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="0"/>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D30" t="s">
         <v>184</v>
@@ -3434,7 +3434,7 @@
         <v>54</v>
       </c>
       <c r="B31" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="0"/>
@@ -3488,7 +3488,7 @@
         <v>55</v>
       </c>
       <c r="B32" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="0"/>
@@ -3542,7 +3542,7 @@
         <v>56</v>
       </c>
       <c r="B33" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="0"/>
@@ -3596,7 +3596,7 @@
         <v>57</v>
       </c>
       <c r="B34" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="0"/>
@@ -3650,7 +3650,7 @@
         <v>58</v>
       </c>
       <c r="B35" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="0"/>
@@ -3704,7 +3704,7 @@
         <v>59</v>
       </c>
       <c r="B36" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="0"/>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="0"/>
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="D37" t="s">
         <v>184</v>
@@ -3812,7 +3812,7 @@
         <v>62</v>
       </c>
       <c r="B38" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="0"/>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D39" t="s">
         <v>184</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="0"/>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="D40" t="s">
         <v>184</v>
@@ -3974,7 +3974,7 @@
         <v>65</v>
       </c>
       <c r="B41" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="0"/>
@@ -4028,7 +4028,7 @@
         <v>66</v>
       </c>
       <c r="B42" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="0"/>
@@ -4082,7 +4082,7 @@
         <v>67</v>
       </c>
       <c r="B43" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="0"/>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D44" t="s">
         <v>184</v>
@@ -4190,7 +4190,7 @@
         <v>69</v>
       </c>
       <c r="B45" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="0"/>
@@ -4244,7 +4244,7 @@
         <v>70</v>
       </c>
       <c r="B46" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="0"/>
@@ -4298,7 +4298,7 @@
         <v>71</v>
       </c>
       <c r="B47" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="0"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="0"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D48" t="s">
         <v>184</v>
@@ -4406,7 +4406,7 @@
         <v>73</v>
       </c>
       <c r="B49" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="0"/>
@@ -4460,7 +4460,7 @@
         <v>74</v>
       </c>
       <c r="B50" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="0"/>
@@ -4514,11 +4514,11 @@
         <v>75</v>
       </c>
       <c r="B51" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D51" t="s">
         <v>184</v>
@@ -4568,7 +4568,7 @@
         <v>76</v>
       </c>
       <c r="B52" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="0"/>
@@ -4622,11 +4622,11 @@
         <v>77</v>
       </c>
       <c r="B53" s="2">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="D53" t="s">
         <v>184</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D54" t="s">
         <v>184</v>
@@ -4730,7 +4730,7 @@
         <v>79</v>
       </c>
       <c r="B55" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="0"/>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="0"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="D56" t="s">
         <v>184</v>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="0"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D57" t="s">
         <v>184</v>
@@ -4892,7 +4892,7 @@
         <v>82</v>
       </c>
       <c r="B58" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="0"/>
@@ -4946,7 +4946,7 @@
         <v>83</v>
       </c>
       <c r="B59" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="0"/>
@@ -5000,11 +5000,11 @@
         <v>84</v>
       </c>
       <c r="B60" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D60" t="s">
         <v>184</v>
@@ -5054,7 +5054,7 @@
         <v>85</v>
       </c>
       <c r="B61" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="0"/>
@@ -5108,11 +5108,11 @@
         <v>86</v>
       </c>
       <c r="B62" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D62" t="s">
         <v>184</v>
@@ -5162,11 +5162,11 @@
         <v>87</v>
       </c>
       <c r="B63" s="2">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D63" t="s">
         <v>184</v>
@@ -5216,11 +5216,11 @@
         <v>90</v>
       </c>
       <c r="B64" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D64" t="s">
         <v>184</v>
@@ -5270,7 +5270,7 @@
         <v>92</v>
       </c>
       <c r="B65" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="0"/>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="0"/>
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="D66" t="s">
         <v>184</v>
@@ -5378,7 +5378,7 @@
         <v>94</v>
       </c>
       <c r="B67" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C67">
         <f t="shared" ref="C67:C130" ca="1" si="1">B67-$R$1</f>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="1"/>
-        <v>-60</v>
+        <v>-61</v>
       </c>
       <c r="D68" t="s">
         <v>184</v>
@@ -5486,7 +5486,7 @@
         <v>96</v>
       </c>
       <c r="B69" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="1"/>
@@ -5540,7 +5540,7 @@
         <v>97</v>
       </c>
       <c r="B70" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="1"/>
@@ -5594,7 +5594,7 @@
         <v>98</v>
       </c>
       <c r="B71" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="1"/>
@@ -5648,7 +5648,7 @@
         <v>99</v>
       </c>
       <c r="B72" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="1"/>
@@ -5702,11 +5702,11 @@
         <v>100</v>
       </c>
       <c r="B73" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D73" t="s">
         <v>184</v>
@@ -5756,11 +5756,11 @@
         <v>102</v>
       </c>
       <c r="B74" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D74" t="s">
         <v>184</v>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D75" t="s">
         <v>184</v>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D76" t="s">
         <v>184</v>
@@ -5918,11 +5918,11 @@
         <v>105</v>
       </c>
       <c r="B77" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D77" t="s">
         <v>184</v>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="1"/>
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="D78" t="s">
         <v>184</v>
@@ -6080,7 +6080,7 @@
         <v>108</v>
       </c>
       <c r="B80" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="1"/>
@@ -6242,7 +6242,7 @@
         <v>111</v>
       </c>
       <c r="B83" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="1"/>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D84" t="s">
         <v>184</v>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D85" t="s">
         <v>184</v>
@@ -6404,7 +6404,7 @@
         <v>114</v>
       </c>
       <c r="B86" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="1"/>
@@ -6512,7 +6512,7 @@
         <v>116</v>
       </c>
       <c r="B88" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="1"/>
@@ -6566,7 +6566,7 @@
         <v>117</v>
       </c>
       <c r="B89" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="1"/>
@@ -6620,7 +6620,7 @@
         <v>121</v>
       </c>
       <c r="B90" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="1"/>
@@ -6674,7 +6674,7 @@
         <v>122</v>
       </c>
       <c r="B91" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="1"/>
@@ -6728,7 +6728,7 @@
         <v>123</v>
       </c>
       <c r="B92" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="1"/>
@@ -6782,7 +6782,7 @@
         <v>124</v>
       </c>
       <c r="B93" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="1"/>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D94" t="s">
         <v>184</v>
@@ -6890,7 +6890,7 @@
         <v>126</v>
       </c>
       <c r="B95" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="1"/>
@@ -6944,11 +6944,11 @@
         <v>127</v>
       </c>
       <c r="B96" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D96" t="s">
         <v>184</v>
@@ -6998,7 +6998,7 @@
         <v>128</v>
       </c>
       <c r="B97" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="1"/>
@@ -7052,7 +7052,7 @@
         <v>129</v>
       </c>
       <c r="B98" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="1"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D99" t="s">
         <v>184</v>
@@ -7160,7 +7160,7 @@
         <v>131</v>
       </c>
       <c r="B100" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="1"/>
@@ -7214,7 +7214,7 @@
         <v>132</v>
       </c>
       <c r="B101" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="1"/>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="C102">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D102" t="s">
         <v>184</v>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="C103">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D103" t="s">
         <v>184</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="C104">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D104" t="s">
         <v>184</v>
@@ -7430,11 +7430,11 @@
         <v>136</v>
       </c>
       <c r="B105" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C105">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D105" t="s">
         <v>184</v>
@@ -7484,7 +7484,7 @@
         <v>137</v>
       </c>
       <c r="B106" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C106">
         <f t="shared" ca="1" si="1"/>
@@ -7538,7 +7538,7 @@
         <v>138</v>
       </c>
       <c r="B107" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C107">
         <f t="shared" ca="1" si="1"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="C108">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D108" t="s">
         <v>184</v>
@@ -7646,7 +7646,7 @@
         <v>140</v>
       </c>
       <c r="B109" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C109">
         <f t="shared" ca="1" si="1"/>
@@ -7700,7 +7700,7 @@
         <v>141</v>
       </c>
       <c r="B110" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C110">
         <f t="shared" ca="1" si="1"/>
@@ -7754,11 +7754,11 @@
         <v>142</v>
       </c>
       <c r="B111" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C111">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D111" t="s">
         <v>184</v>
@@ -7840,11 +7840,11 @@
         <v>143</v>
       </c>
       <c r="B113" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C113">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D113" t="s">
         <v>184</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C114">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D114" t="s">
         <v>184</v>
@@ -7948,7 +7948,7 @@
         <v>145</v>
       </c>
       <c r="B115" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C115">
         <f t="shared" ca="1" si="1"/>
@@ -8002,7 +8002,7 @@
         <v>147</v>
       </c>
       <c r="B116" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C116">
         <f t="shared" ca="1" si="1"/>
@@ -8056,7 +8056,7 @@
         <v>148</v>
       </c>
       <c r="B117" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C117">
         <f t="shared" ca="1" si="1"/>
@@ -8110,7 +8110,7 @@
         <v>149</v>
       </c>
       <c r="B118" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C118">
         <f t="shared" ca="1" si="1"/>
@@ -8164,7 +8164,7 @@
         <v>150</v>
       </c>
       <c r="B119" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C119">
         <f t="shared" ca="1" si="1"/>
@@ -8218,7 +8218,7 @@
         <v>151</v>
       </c>
       <c r="B120" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C120">
         <f t="shared" ca="1" si="1"/>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="C121">
         <f t="shared" ca="1" si="1"/>
-        <v>-46315</v>
+        <v>-46316</v>
       </c>
       <c r="D121" t="s">
         <v>469</v>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="C122">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D122" t="s">
         <v>184</v>
@@ -8380,11 +8380,11 @@
         <v>155</v>
       </c>
       <c r="B123" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C123">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D123" t="s">
         <v>184</v>
@@ -8434,11 +8434,11 @@
         <v>156</v>
       </c>
       <c r="B124" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C124">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D124" t="s">
         <v>184</v>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="C125">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D125" t="s">
         <v>184</v>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="C126">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D126" t="s">
         <v>184</v>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="C127">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D127" t="s">
         <v>184</v>
@@ -8650,7 +8650,7 @@
         <v>160</v>
       </c>
       <c r="B128" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C128">
         <f t="shared" ca="1" si="1"/>
@@ -8704,7 +8704,7 @@
         <v>161</v>
       </c>
       <c r="B129" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C129">
         <f t="shared" ca="1" si="1"/>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="C130">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D130" t="s">
         <v>184</v>
@@ -8812,11 +8812,11 @@
         <v>186</v>
       </c>
       <c r="B131" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C131">
         <f t="shared" ref="C131:C192" ca="1" si="2">B131-$R$1</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D131" t="s">
         <v>184</v>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="C132">
         <f t="shared" ca="1" si="2"/>
-        <v>-46315</v>
+        <v>-46316</v>
       </c>
       <c r="D132" t="s">
         <v>184</v>
@@ -8920,7 +8920,7 @@
         <v>188</v>
       </c>
       <c r="B133" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C133">
         <f t="shared" ca="1" si="2"/>
@@ -8974,7 +8974,7 @@
         <v>189</v>
       </c>
       <c r="B134" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C134">
         <f t="shared" ca="1" si="2"/>
@@ -9028,7 +9028,7 @@
         <v>190</v>
       </c>
       <c r="B135" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C135">
         <f t="shared" ca="1" si="2"/>
@@ -9082,7 +9082,7 @@
         <v>191</v>
       </c>
       <c r="B136" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C136">
         <f t="shared" ca="1" si="2"/>
@@ -9136,7 +9136,7 @@
         <v>192</v>
       </c>
       <c r="B137" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C137">
         <f t="shared" ca="1" si="2"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="C151">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D151" t="s">
         <v>184</v>
@@ -9720,7 +9720,7 @@
         <v>165</v>
       </c>
       <c r="B152" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C152">
         <f t="shared" ca="1" si="2"/>
@@ -9774,7 +9774,7 @@
         <v>166</v>
       </c>
       <c r="B153" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C153">
         <f t="shared" ca="1" si="2"/>
@@ -9828,7 +9828,7 @@
         <v>167</v>
       </c>
       <c r="B154" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C154">
         <f t="shared" ca="1" si="2"/>
@@ -9882,7 +9882,7 @@
         <v>168</v>
       </c>
       <c r="B155" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="D156" t="s">
         <v>184</v>
@@ -9990,7 +9990,7 @@
         <v>170</v>
       </c>
       <c r="B157" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
@@ -10044,7 +10044,7 @@
         <v>171</v>
       </c>
       <c r="B158" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C158">
         <f t="shared" ca="1" si="2"/>
@@ -10098,7 +10098,7 @@
         <v>172</v>
       </c>
       <c r="B159" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C159">
         <f t="shared" ca="1" si="2"/>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D160" t="s">
         <v>184</v>
@@ -10206,7 +10206,7 @@
         <v>175</v>
       </c>
       <c r="B161" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
@@ -10260,7 +10260,7 @@
         <v>176</v>
       </c>
       <c r="B162" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
@@ -10392,7 +10392,7 @@
         <v>208</v>
       </c>
       <c r="B165" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="C173">
         <f t="shared" ca="1" si="2"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D173" t="s">
         <v>184</v>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="C174">
         <f t="shared" ca="1" si="2"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D174" t="s">
         <v>184</v>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="C175">
         <f t="shared" ca="1" si="2"/>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="D175" t="s">
         <v>184</v>
@@ -10884,7 +10884,7 @@
         <v>229</v>
       </c>
       <c r="B176" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C176">
         <f t="shared" ca="1" si="2"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="C177">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D177" t="s">
         <v>184</v>
@@ -10986,7 +10986,7 @@
         <v>231</v>
       </c>
       <c r="B178" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C178">
         <f t="shared" ca="1" si="2"/>
@@ -11037,7 +11037,7 @@
         <v>232</v>
       </c>
       <c r="B179" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C179">
         <f t="shared" ca="1" si="2"/>
@@ -11088,7 +11088,7 @@
         <v>233</v>
       </c>
       <c r="B180" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C180">
         <f t="shared" ca="1" si="2"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="C181">
         <f t="shared" ca="1" si="2"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D181" t="s">
         <v>184</v>
@@ -11190,7 +11190,7 @@
         <v>235</v>
       </c>
       <c r="B182" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C182">
         <f t="shared" ca="1" si="2"/>
@@ -11241,7 +11241,7 @@
         <v>236</v>
       </c>
       <c r="B183" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C183">
         <f t="shared" ca="1" si="2"/>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="C184">
         <f t="shared" ca="1" si="2"/>
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="D184" t="s">
         <v>184</v>
@@ -11343,7 +11343,7 @@
         <v>238</v>
       </c>
       <c r="B185" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C185">
         <f t="shared" ca="1" si="2"/>
@@ -11394,7 +11394,7 @@
         <v>239</v>
       </c>
       <c r="B186" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C186">
         <f t="shared" ca="1" si="2"/>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="C187">
         <f t="shared" ca="1" si="2"/>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="D187" t="s">
         <v>184</v>
@@ -11500,7 +11500,7 @@
       </c>
       <c r="C188">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D188" t="s">
         <v>184</v>
@@ -11547,7 +11547,7 @@
         <v>242</v>
       </c>
       <c r="B189" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C189">
         <f t="shared" ca="1" si="2"/>
@@ -11598,11 +11598,11 @@
         <v>243</v>
       </c>
       <c r="B190" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C190">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D190" t="s">
         <v>184</v>
@@ -11649,7 +11649,7 @@
         <v>244</v>
       </c>
       <c r="B191" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C191">
         <f t="shared" ca="1" si="2"/>
@@ -11700,11 +11700,11 @@
         <v>245</v>
       </c>
       <c r="B192" s="2">
-        <v>46301</v>
+        <v>46315</v>
       </c>
       <c r="C192">
         <f t="shared" ca="1" si="2"/>
-        <v>-14</v>
+        <v>-1</v>
       </c>
       <c r="D192" t="s">
         <v>184</v>
@@ -11751,7 +11751,7 @@
         <v>246</v>
       </c>
       <c r="B193" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C193">
         <f t="shared" ref="C193:C256" ca="1" si="3">B193-$R$1</f>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="C194">
         <f t="shared" ca="1" si="3"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D194" t="s">
         <v>184</v>
@@ -11853,11 +11853,11 @@
         <v>248</v>
       </c>
       <c r="B195" s="2">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="C195">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D195" t="s">
         <v>184</v>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="C198">
         <f t="shared" ca="1" si="3"/>
-        <v>-148</v>
+        <v>-149</v>
       </c>
       <c r="D198" t="s">
         <v>184</v>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="C199">
         <f t="shared" ca="1" si="3"/>
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="D199" t="s">
         <v>184</v>
@@ -12112,7 +12112,7 @@
       </c>
       <c r="C200">
         <f t="shared" ca="1" si="3"/>
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="D200" t="s">
         <v>184</v>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="C201">
         <f t="shared" ca="1" si="3"/>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="D201" t="s">
         <v>184</v>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="C202">
         <f t="shared" ca="1" si="3"/>
-        <v>-278</v>
+        <v>-279</v>
       </c>
       <c r="D202" t="s">
         <v>184</v>
@@ -12261,7 +12261,7 @@
         <v>256</v>
       </c>
       <c r="B203" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C203">
         <f t="shared" ca="1" si="3"/>
@@ -12312,11 +12312,11 @@
         <v>257</v>
       </c>
       <c r="B204" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C204">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D204" t="s">
         <v>184</v>
@@ -12363,11 +12363,11 @@
         <v>258</v>
       </c>
       <c r="B205" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C205">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D205" t="s">
         <v>184</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="C206">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D206" t="s">
         <v>184</v>
@@ -12465,11 +12465,11 @@
         <v>260</v>
       </c>
       <c r="B207" s="2">
-        <v>46263</v>
+        <v>46315</v>
       </c>
       <c r="C207">
         <f t="shared" ca="1" si="3"/>
-        <v>-52</v>
+        <v>-1</v>
       </c>
       <c r="D207" t="s">
         <v>184</v>
@@ -12516,7 +12516,7 @@
         <v>261</v>
       </c>
       <c r="B208" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C208">
         <f t="shared" ca="1" si="3"/>
@@ -12567,7 +12567,7 @@
         <v>262</v>
       </c>
       <c r="B209" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C209">
         <f t="shared" ca="1" si="3"/>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="C210">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D210" t="s">
         <v>184</v>
@@ -12669,7 +12669,7 @@
         <v>264</v>
       </c>
       <c r="B211" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C211">
         <f t="shared" ca="1" si="3"/>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="C212">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D212" t="s">
         <v>184</v>
@@ -12771,7 +12771,7 @@
         <v>266</v>
       </c>
       <c r="B213" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C213">
         <f t="shared" ca="1" si="3"/>
@@ -12826,7 +12826,7 @@
       </c>
       <c r="C214">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D214" t="s">
         <v>184</v>
@@ -12873,7 +12873,7 @@
         <v>268</v>
       </c>
       <c r="B215" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C215">
         <f t="shared" ca="1" si="3"/>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C216">
         <f t="shared" ca="1" si="3"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="C217">
         <f t="shared" ca="1" si="3"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D217" t="s">
         <v>184</v>
@@ -13026,7 +13026,7 @@
         <v>271</v>
       </c>
       <c r="B218" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C218">
         <f t="shared" ca="1" si="3"/>
@@ -13081,7 +13081,7 @@
       </c>
       <c r="C219">
         <f t="shared" ca="1" si="3"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D219" t="s">
         <v>184</v>
@@ -13132,7 +13132,7 @@
       </c>
       <c r="C220">
         <f t="shared" ca="1" si="3"/>
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="D220" t="s">
         <v>184</v>
@@ -13179,7 +13179,7 @@
         <v>274</v>
       </c>
       <c r="B221" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C221">
         <f t="shared" ca="1" si="3"/>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="C222">
         <f t="shared" ca="1" si="3"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D222" t="s">
         <v>184</v>
@@ -13281,7 +13281,7 @@
         <v>276</v>
       </c>
       <c r="B223" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C223">
         <f t="shared" ca="1" si="3"/>
@@ -13332,11 +13332,11 @@
         <v>277</v>
       </c>
       <c r="B224" s="2">
-        <v>46312</v>
+        <v>46315</v>
       </c>
       <c r="C224">
         <f t="shared" ca="1" si="3"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D224" t="s">
         <v>184</v>
@@ -13383,11 +13383,11 @@
         <v>278</v>
       </c>
       <c r="B225" s="2">
-        <v>46312</v>
+        <v>46315</v>
       </c>
       <c r="C225">
         <f t="shared" ca="1" si="3"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D225" t="s">
         <v>184</v>
@@ -13434,11 +13434,11 @@
         <v>279</v>
       </c>
       <c r="B226" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C226">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D226" t="s">
         <v>184</v>
@@ -13485,7 +13485,7 @@
         <v>280</v>
       </c>
       <c r="B227" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C227">
         <f t="shared" ca="1" si="3"/>
@@ -13540,7 +13540,7 @@
       </c>
       <c r="C228">
         <f t="shared" ca="1" si="3"/>
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="D228" t="s">
         <v>184</v>
@@ -13587,7 +13587,7 @@
         <v>282</v>
       </c>
       <c r="B229" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C229">
         <f t="shared" ca="1" si="3"/>
@@ -13638,11 +13638,11 @@
         <v>283</v>
       </c>
       <c r="B230" s="2">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="C230">
         <f t="shared" ca="1" si="3"/>
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="D230" t="s">
         <v>184</v>
@@ -13689,11 +13689,11 @@
         <v>284</v>
       </c>
       <c r="B231" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C231">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D231" t="s">
         <v>184</v>
@@ -13740,11 +13740,11 @@
         <v>285</v>
       </c>
       <c r="B232" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C232">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D232" t="s">
         <v>184</v>
@@ -13795,7 +13795,7 @@
       </c>
       <c r="C233">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D233" t="s">
         <v>184</v>
@@ -13842,11 +13842,11 @@
         <v>287</v>
       </c>
       <c r="B234" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C234">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D234" t="s">
         <v>184</v>
@@ -13893,7 +13893,7 @@
         <v>288</v>
       </c>
       <c r="B235" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C235">
         <f t="shared" ca="1" si="3"/>
@@ -13944,11 +13944,11 @@
         <v>289</v>
       </c>
       <c r="B236" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C236">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D236" t="s">
         <v>184</v>
@@ -13995,7 +13995,7 @@
         <v>290</v>
       </c>
       <c r="B237" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C237">
         <f t="shared" ca="1" si="3"/>
@@ -14046,7 +14046,7 @@
         <v>291</v>
       </c>
       <c r="B238" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C238">
         <f t="shared" ca="1" si="3"/>
@@ -14101,7 +14101,7 @@
       </c>
       <c r="C239">
         <f t="shared" ca="1" si="3"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D239" t="s">
         <v>184</v>
@@ -14148,7 +14148,7 @@
         <v>293</v>
       </c>
       <c r="B240" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C240">
         <f t="shared" ca="1" si="3"/>
@@ -14199,7 +14199,7 @@
         <v>294</v>
       </c>
       <c r="B241" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C241">
         <f t="shared" ca="1" si="3"/>
@@ -14250,11 +14250,11 @@
         <v>295</v>
       </c>
       <c r="B242" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C242">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D242" t="s">
         <v>184</v>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="C243">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D243" t="s">
         <v>184</v>
@@ -14352,11 +14352,11 @@
         <v>297</v>
       </c>
       <c r="B244" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C244">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D244" t="s">
         <v>184</v>
@@ -14403,7 +14403,7 @@
         <v>298</v>
       </c>
       <c r="B245" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C245">
         <f t="shared" ca="1" si="3"/>
@@ -14454,7 +14454,7 @@
         <v>299</v>
       </c>
       <c r="B246" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C246">
         <f t="shared" ca="1" si="3"/>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="C247">
         <f t="shared" ca="1" si="3"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D247" t="s">
         <v>184</v>
@@ -14560,7 +14560,7 @@
       </c>
       <c r="C248">
         <f t="shared" ca="1" si="3"/>
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="D248" t="s">
         <v>184</v>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C249">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D249" t="s">
         <v>184</v>
@@ -14658,7 +14658,7 @@
         <v>303</v>
       </c>
       <c r="B250" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C250">
         <f t="shared" ca="1" si="3"/>
@@ -14709,11 +14709,11 @@
         <v>304</v>
       </c>
       <c r="B251" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C251">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D251" t="s">
         <v>184</v>
@@ -14760,7 +14760,7 @@
         <v>305</v>
       </c>
       <c r="B252" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C252">
         <f t="shared" ca="1" si="3"/>
@@ -14811,7 +14811,7 @@
         <v>306</v>
       </c>
       <c r="B253" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C253">
         <f t="shared" ca="1" si="3"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="C254">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D254" t="s">
         <v>184</v>
@@ -14917,7 +14917,7 @@
       </c>
       <c r="C255">
         <f t="shared" ca="1" si="3"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D255" t="s">
         <v>184</v>
@@ -14964,7 +14964,7 @@
         <v>309</v>
       </c>
       <c r="B256" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C256">
         <f t="shared" ca="1" si="3"/>
@@ -15019,7 +15019,7 @@
       </c>
       <c r="C257">
         <f t="shared" ref="C257:C320" ca="1" si="4">B257-$R$1</f>
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="D257" t="s">
         <v>184</v>
@@ -15066,7 +15066,7 @@
         <v>311</v>
       </c>
       <c r="B258" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C258">
         <f t="shared" ca="1" si="4"/>
@@ -15117,11 +15117,11 @@
         <v>312</v>
       </c>
       <c r="B259" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C259">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D259" t="s">
         <v>184</v>
@@ -15168,7 +15168,7 @@
         <v>313</v>
       </c>
       <c r="B260" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C260">
         <f t="shared" ca="1" si="4"/>
@@ -15223,7 +15223,7 @@
       </c>
       <c r="C261">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D261" t="s">
         <v>184</v>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C262">
         <f t="shared" ca="1" si="4"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="D262" t="s">
         <v>184</v>
@@ -15321,7 +15321,7 @@
         <v>316</v>
       </c>
       <c r="B263" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C263">
         <f t="shared" ca="1" si="4"/>
@@ -15372,7 +15372,7 @@
         <v>317</v>
       </c>
       <c r="B264" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C264">
         <f t="shared" ca="1" si="4"/>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="C265">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D265" t="s">
         <v>184</v>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="C266">
         <f t="shared" ca="1" si="4"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D266" t="s">
         <v>184</v>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="C267">
         <f t="shared" ca="1" si="4"/>
-        <v>-138</v>
+        <v>-139</v>
       </c>
       <c r="D267" t="s">
         <v>184</v>
@@ -15576,11 +15576,11 @@
         <v>321</v>
       </c>
       <c r="B268" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C268">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D268" t="s">
         <v>184</v>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="C269">
         <f t="shared" ca="1" si="4"/>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="D269" t="s">
         <v>184</v>
@@ -15682,7 +15682,7 @@
       </c>
       <c r="C270">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D270" t="s">
         <v>184</v>
@@ -15729,7 +15729,7 @@
         <v>324</v>
       </c>
       <c r="B271" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C271">
         <f t="shared" ca="1" si="4"/>
@@ -15780,7 +15780,7 @@
         <v>325</v>
       </c>
       <c r="B272" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C272">
         <f t="shared" ca="1" si="4"/>
@@ -15831,7 +15831,7 @@
         <v>326</v>
       </c>
       <c r="B273" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C273">
         <f t="shared" ca="1" si="4"/>
@@ -15882,7 +15882,7 @@
         <v>327</v>
       </c>
       <c r="B274" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C274">
         <f t="shared" ca="1" si="4"/>
@@ -15933,7 +15933,7 @@
         <v>328</v>
       </c>
       <c r="B275" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C275">
         <f t="shared" ca="1" si="4"/>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="C276">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D276" t="s">
         <v>184</v>
@@ -16035,11 +16035,11 @@
         <v>330</v>
       </c>
       <c r="B277" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C277">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D277" t="s">
         <v>184</v>
@@ -16086,7 +16086,7 @@
         <v>331</v>
       </c>
       <c r="B278" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C278">
         <f t="shared" ca="1" si="4"/>
@@ -16137,7 +16137,7 @@
         <v>332</v>
       </c>
       <c r="B279" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C279">
         <f t="shared" ca="1" si="4"/>
@@ -16192,7 +16192,7 @@
       </c>
       <c r="C280">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D280" t="s">
         <v>184</v>
@@ -16239,7 +16239,7 @@
         <v>334</v>
       </c>
       <c r="B281" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C281">
         <f t="shared" ca="1" si="4"/>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="C282">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D282" t="s">
         <v>184</v>
@@ -16341,11 +16341,11 @@
         <v>336</v>
       </c>
       <c r="B283" s="2">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="C283">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D283" t="s">
         <v>184</v>
@@ -16392,7 +16392,7 @@
         <v>337</v>
       </c>
       <c r="B284" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C284">
         <f t="shared" ca="1" si="4"/>
@@ -16447,7 +16447,7 @@
       </c>
       <c r="C285">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D285" t="s">
         <v>184</v>
@@ -16494,7 +16494,7 @@
         <v>339</v>
       </c>
       <c r="B286" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C286">
         <f t="shared" ca="1" si="4"/>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="C287">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D287" t="s">
         <v>184</v>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="C288">
         <f t="shared" ca="1" si="4"/>
-        <v>-224</v>
+        <v>-225</v>
       </c>
       <c r="D288" t="s">
         <v>184</v>
@@ -16647,7 +16647,7 @@
         <v>342</v>
       </c>
       <c r="B289" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C289">
         <f t="shared" ca="1" si="4"/>
@@ -16698,7 +16698,7 @@
         <v>343</v>
       </c>
       <c r="B290" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C290">
         <f t="shared" ca="1" si="4"/>
@@ -16749,7 +16749,7 @@
         <v>344</v>
       </c>
       <c r="B291" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C291">
         <f t="shared" ca="1" si="4"/>
@@ -16800,7 +16800,7 @@
         <v>345</v>
       </c>
       <c r="B292" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C292">
         <f t="shared" ca="1" si="4"/>
@@ -16851,7 +16851,7 @@
         <v>346</v>
       </c>
       <c r="B293" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C293">
         <f t="shared" ca="1" si="4"/>
@@ -16906,7 +16906,7 @@
       </c>
       <c r="C294">
         <f t="shared" ca="1" si="4"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D294" t="s">
         <v>184</v>
@@ -16953,7 +16953,7 @@
         <v>348</v>
       </c>
       <c r="B295" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C295">
         <f t="shared" ca="1" si="4"/>
@@ -17004,7 +17004,7 @@
         <v>349</v>
       </c>
       <c r="B296" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C296">
         <f t="shared" ca="1" si="4"/>
@@ -17055,7 +17055,7 @@
         <v>350</v>
       </c>
       <c r="B297" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C297">
         <f t="shared" ca="1" si="4"/>
@@ -17106,7 +17106,7 @@
         <v>351</v>
       </c>
       <c r="B298" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C298">
         <f t="shared" ca="1" si="4"/>
@@ -17157,7 +17157,7 @@
         <v>352</v>
       </c>
       <c r="B299" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C299">
         <f t="shared" ca="1" si="4"/>
@@ -17208,7 +17208,7 @@
         <v>353</v>
       </c>
       <c r="B300" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C300">
         <f t="shared" ca="1" si="4"/>
@@ -17259,11 +17259,11 @@
         <v>354</v>
       </c>
       <c r="B301" s="2">
-        <v>46312</v>
+        <v>46315</v>
       </c>
       <c r="C301">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D301" t="s">
         <v>184</v>
@@ -17310,11 +17310,11 @@
         <v>355</v>
       </c>
       <c r="B302" s="2">
-        <v>46312</v>
+        <v>46315</v>
       </c>
       <c r="C302">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D302" t="s">
         <v>184</v>
@@ -17361,7 +17361,7 @@
         <v>356</v>
       </c>
       <c r="B303" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C303">
         <f t="shared" ca="1" si="4"/>
@@ -17412,7 +17412,7 @@
         <v>357</v>
       </c>
       <c r="B304" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C304">
         <f t="shared" ca="1" si="4"/>
@@ -17463,7 +17463,7 @@
         <v>358</v>
       </c>
       <c r="B305" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C305">
         <f t="shared" ca="1" si="4"/>
@@ -17518,7 +17518,7 @@
       </c>
       <c r="C306">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D306" t="s">
         <v>184</v>
@@ -17569,7 +17569,7 @@
       </c>
       <c r="C307">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D307" t="s">
         <v>184</v>
@@ -17616,7 +17616,7 @@
         <v>361</v>
       </c>
       <c r="B308" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C308">
         <f t="shared" ca="1" si="4"/>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="C309">
         <f t="shared" ca="1" si="4"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D309" t="s">
         <v>184</v>
@@ -17718,7 +17718,7 @@
         <v>363</v>
       </c>
       <c r="B310" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C310">
         <f t="shared" ca="1" si="4"/>
@@ -17769,7 +17769,7 @@
         <v>364</v>
       </c>
       <c r="B311" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C311">
         <f t="shared" ca="1" si="4"/>
@@ -17820,11 +17820,11 @@
         <v>365</v>
       </c>
       <c r="B312" s="2">
-        <v>46262</v>
+        <v>46315</v>
       </c>
       <c r="C312">
         <f t="shared" ca="1" si="4"/>
-        <v>-53</v>
+        <v>-1</v>
       </c>
       <c r="D312" t="s">
         <v>184</v>
@@ -17871,7 +17871,7 @@
         <v>366</v>
       </c>
       <c r="B313" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C313">
         <f t="shared" ca="1" si="4"/>
@@ -17922,7 +17922,7 @@
         <v>367</v>
       </c>
       <c r="B314" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C314">
         <f t="shared" ca="1" si="4"/>
@@ -17977,7 +17977,7 @@
       </c>
       <c r="C315">
         <f t="shared" ca="1" si="4"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D315" t="s">
         <v>184</v>
@@ -18024,7 +18024,7 @@
         <v>369</v>
       </c>
       <c r="B316" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C316">
         <f t="shared" ca="1" si="4"/>
@@ -18075,7 +18075,7 @@
         <v>370</v>
       </c>
       <c r="B317" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C317">
         <f t="shared" ca="1" si="4"/>
@@ -18130,7 +18130,7 @@
       </c>
       <c r="C318">
         <f t="shared" ca="1" si="4"/>
-        <v>-71</v>
+        <v>-72</v>
       </c>
       <c r="D318" t="s">
         <v>184</v>
@@ -18177,11 +18177,11 @@
         <v>372</v>
       </c>
       <c r="B319" s="2">
-        <v>46309</v>
+        <v>46315</v>
       </c>
       <c r="C319">
         <f t="shared" ca="1" si="4"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D319" t="s">
         <v>184</v>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="C320">
         <f t="shared" ca="1" si="4"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D320" t="s">
         <v>184</v>
@@ -18279,7 +18279,7 @@
         <v>374</v>
       </c>
       <c r="B321" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C321">
         <f t="shared" ref="C321:C384" ca="1" si="5">B321-$R$1</f>
@@ -18334,7 +18334,7 @@
       </c>
       <c r="C322">
         <f t="shared" ca="1" si="5"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D322" t="s">
         <v>184</v>
@@ -18385,7 +18385,7 @@
       </c>
       <c r="C323">
         <f t="shared" ca="1" si="5"/>
-        <v>-75</v>
+        <v>-76</v>
       </c>
       <c r="D323" t="s">
         <v>184</v>
@@ -18436,7 +18436,7 @@
       </c>
       <c r="C324">
         <f t="shared" ca="1" si="5"/>
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="D324" t="s">
         <v>184</v>
@@ -18483,11 +18483,11 @@
         <v>378</v>
       </c>
       <c r="B325" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C325">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D325" t="s">
         <v>184</v>
@@ -18534,11 +18534,11 @@
         <v>379</v>
       </c>
       <c r="B326" s="2">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="C326">
         <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D326" t="s">
         <v>184</v>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="C327">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D327" t="s">
         <v>184</v>
@@ -18636,11 +18636,11 @@
         <v>381</v>
       </c>
       <c r="B328" s="2">
-        <v>46312</v>
+        <v>46315</v>
       </c>
       <c r="C328">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D328" t="s">
         <v>184</v>
@@ -18691,7 +18691,7 @@
       </c>
       <c r="C329">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D329" t="s">
         <v>184</v>
@@ -18738,11 +18738,11 @@
         <v>383</v>
       </c>
       <c r="B330" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C330">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D330" t="s">
         <v>184</v>
@@ -18793,7 +18793,7 @@
       </c>
       <c r="C331">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D331" t="s">
         <v>184</v>
@@ -18840,7 +18840,7 @@
         <v>385</v>
       </c>
       <c r="B332" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C332">
         <f t="shared" ca="1" si="5"/>
@@ -18891,11 +18891,11 @@
         <v>386</v>
       </c>
       <c r="B333" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C333">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D333" t="s">
         <v>184</v>
@@ -18942,11 +18942,11 @@
         <v>387</v>
       </c>
       <c r="B334" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C334">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D334" t="s">
         <v>184</v>
@@ -18993,11 +18993,11 @@
         <v>388</v>
       </c>
       <c r="B335" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C335">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D335" t="s">
         <v>184</v>
@@ -19044,11 +19044,11 @@
         <v>389</v>
       </c>
       <c r="B336" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C336">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D336" t="s">
         <v>184</v>
@@ -19095,7 +19095,7 @@
         <v>390</v>
       </c>
       <c r="B337" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C337">
         <f t="shared" ca="1" si="5"/>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="C338">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D338" t="s">
         <v>184</v>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="C339">
         <f t="shared" ca="1" si="5"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D339" t="s">
         <v>184</v>
@@ -19248,11 +19248,11 @@
         <v>393</v>
       </c>
       <c r="B340" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C340">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D340" t="s">
         <v>184</v>
@@ -19299,7 +19299,7 @@
         <v>394</v>
       </c>
       <c r="B341" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C341">
         <f t="shared" ca="1" si="5"/>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="C342">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D342" t="s">
         <v>184</v>
@@ -19405,7 +19405,7 @@
       </c>
       <c r="C343">
         <f t="shared" ca="1" si="5"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D343" t="s">
         <v>184</v>
@@ -19452,7 +19452,7 @@
         <v>397</v>
       </c>
       <c r="B344" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C344">
         <f t="shared" ca="1" si="5"/>
@@ -19507,7 +19507,7 @@
       </c>
       <c r="C345">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D345" t="s">
         <v>184</v>
@@ -19554,11 +19554,11 @@
         <v>399</v>
       </c>
       <c r="B346" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C346">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D346" t="s">
         <v>184</v>
@@ -19605,7 +19605,7 @@
         <v>400</v>
       </c>
       <c r="B347" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C347">
         <f t="shared" ca="1" si="5"/>
@@ -19656,7 +19656,7 @@
         <v>401</v>
       </c>
       <c r="B348" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C348">
         <f t="shared" ca="1" si="5"/>
@@ -19707,7 +19707,7 @@
         <v>402</v>
       </c>
       <c r="B349" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C349">
         <f t="shared" ca="1" si="5"/>
@@ -19758,7 +19758,7 @@
         <v>403</v>
       </c>
       <c r="B350" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C350">
         <f t="shared" ca="1" si="5"/>
@@ -19813,7 +19813,7 @@
       </c>
       <c r="C351">
         <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D351" t="s">
         <v>184</v>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="C352">
         <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D352" t="s">
         <v>184</v>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="C353">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D353" t="s">
         <v>184</v>
@@ -19966,7 +19966,7 @@
       </c>
       <c r="C354">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D354" t="s">
         <v>184</v>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="C355">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D355" t="s">
         <v>184</v>
@@ -20064,11 +20064,11 @@
         <v>409</v>
       </c>
       <c r="B356" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C356">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D356" t="s">
         <v>184</v>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="C357">
         <f t="shared" ca="1" si="5"/>
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="D357" t="s">
         <v>184</v>
@@ -20166,11 +20166,11 @@
         <v>411</v>
       </c>
       <c r="B358" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C358">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D358" t="s">
         <v>184</v>
@@ -20217,11 +20217,11 @@
         <v>412</v>
       </c>
       <c r="B359" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C359">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D359" t="s">
         <v>184</v>
@@ -20268,7 +20268,7 @@
         <v>413</v>
       </c>
       <c r="B360" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C360">
         <f t="shared" ca="1" si="5"/>
@@ -20319,11 +20319,11 @@
         <v>414</v>
       </c>
       <c r="B361" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C361">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D361" t="s">
         <v>184</v>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C362">
         <f t="shared" ca="1" si="5"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D362" t="s">
         <v>184</v>
@@ -20425,7 +20425,7 @@
       </c>
       <c r="C363">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D363" t="s">
         <v>184</v>
@@ -20472,11 +20472,11 @@
         <v>417</v>
       </c>
       <c r="B364" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C364">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D364" t="s">
         <v>184</v>
@@ -20523,7 +20523,7 @@
         <v>418</v>
       </c>
       <c r="B365" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C365">
         <f t="shared" ca="1" si="5"/>
@@ -20574,7 +20574,7 @@
         <v>419</v>
       </c>
       <c r="B366" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C366">
         <f t="shared" ca="1" si="5"/>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C367">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D367" t="s">
         <v>184</v>
@@ -20676,7 +20676,7 @@
         <v>421</v>
       </c>
       <c r="B368" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C368">
         <f t="shared" ca="1" si="5"/>
@@ -20727,7 +20727,7 @@
         <v>422</v>
       </c>
       <c r="B369" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C369">
         <f t="shared" ca="1" si="5"/>
@@ -20778,7 +20778,7 @@
         <v>423</v>
       </c>
       <c r="B370" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C370">
         <f t="shared" ca="1" si="5"/>
@@ -20833,7 +20833,7 @@
       </c>
       <c r="C371">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D371" t="s">
         <v>184</v>
@@ -20880,7 +20880,7 @@
         <v>425</v>
       </c>
       <c r="B372" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C372">
         <f t="shared" ca="1" si="5"/>
@@ -20931,7 +20931,7 @@
         <v>426</v>
       </c>
       <c r="B373" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C373">
         <f t="shared" ca="1" si="5"/>
@@ -20986,7 +20986,7 @@
       </c>
       <c r="C374">
         <f t="shared" ca="1" si="5"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D374" t="s">
         <v>184</v>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="C375">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D375" t="s">
         <v>184</v>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="C376">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D376" t="s">
         <v>184</v>
@@ -21135,11 +21135,11 @@
         <v>430</v>
       </c>
       <c r="B377" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C377">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D377" t="s">
         <v>184</v>
@@ -21186,7 +21186,7 @@
         <v>431</v>
       </c>
       <c r="B378" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C378">
         <f t="shared" ca="1" si="5"/>
@@ -21237,7 +21237,7 @@
         <v>432</v>
       </c>
       <c r="B379" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C379">
         <f t="shared" ca="1" si="5"/>
@@ -21288,7 +21288,7 @@
         <v>433</v>
       </c>
       <c r="B380" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C380">
         <f t="shared" ca="1" si="5"/>
@@ -21339,7 +21339,7 @@
         <v>434</v>
       </c>
       <c r="B381" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C381">
         <f t="shared" ca="1" si="5"/>
@@ -21390,7 +21390,7 @@
         <v>435</v>
       </c>
       <c r="B382" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C382">
         <f t="shared" ca="1" si="5"/>
@@ -21445,7 +21445,7 @@
       </c>
       <c r="C383">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D383" t="s">
         <v>184</v>
@@ -21496,7 +21496,7 @@
       </c>
       <c r="C384">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D384" t="s">
         <v>184</v>
@@ -21547,7 +21547,7 @@
       </c>
       <c r="C385">
         <f t="shared" ref="C385:C392" ca="1" si="6">B385-$R$1</f>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D385" t="s">
         <v>184</v>
@@ -21598,7 +21598,7 @@
       </c>
       <c r="C386">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D386" t="s">
         <v>184</v>
@@ -21649,7 +21649,7 @@
       </c>
       <c r="C387">
         <f t="shared" ca="1" si="6"/>
-        <v>-46315</v>
+        <v>-46316</v>
       </c>
       <c r="D387" t="s">
         <v>184</v>
@@ -21700,7 +21700,7 @@
       </c>
       <c r="C388">
         <f t="shared" ca="1" si="6"/>
-        <v>-46315</v>
+        <v>-46316</v>
       </c>
       <c r="D388" t="s">
         <v>184</v>
@@ -21751,7 +21751,7 @@
       </c>
       <c r="C389">
         <f t="shared" ca="1" si="6"/>
-        <v>-46315</v>
+        <v>-46316</v>
       </c>
       <c r="D389" t="s">
         <v>184</v>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="C390">
         <f t="shared" ca="1" si="6"/>
-        <v>-46315</v>
+        <v>-46316</v>
       </c>
       <c r="D390" t="s">
         <v>184</v>
@@ -21849,11 +21849,11 @@
         <v>444</v>
       </c>
       <c r="B391" s="2">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="C391">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D391" t="s">
         <v>184</v>
@@ -21904,7 +21904,7 @@
       </c>
       <c r="C392">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D392" t="s">
         <v>184</v>
@@ -21952,18 +21952,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -22224,6 +22212,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -22234,17 +22234,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22263,6 +22252,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
   <ds:schemaRefs>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="386" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EB43603-928F-47ED-B22B-17DF8268293F}"/>
+  <xr:revisionPtr revIDLastSave="394" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B57AAC6-6A16-4198-96D3-1947EDABC0B8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4784" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4789" uniqueCount="470">
   <si>
     <t>Placa</t>
   </si>
@@ -9478,6 +9478,12 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D146" t="s">
+        <v>184</v>
+      </c>
+      <c r="I146" t="s">
+        <v>184</v>
+      </c>
       <c r="J146" t="s">
         <v>28</v>
       </c>
@@ -9496,8 +9502,12 @@
       <c r="O146" t="s">
         <v>217</v>
       </c>
-      <c r="P146" s="2"/>
-      <c r="Q146" s="2"/>
+      <c r="P146" s="2">
+        <v>46316</v>
+      </c>
+      <c r="Q146" s="2">
+        <v>46316</v>
+      </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
@@ -10637,6 +10647,9 @@
       <c r="D170" t="s">
         <v>469</v>
       </c>
+      <c r="I170" t="s">
+        <v>469</v>
+      </c>
       <c r="J170" t="s">
         <v>22</v>
       </c>
@@ -10673,6 +10686,12 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D171" t="s">
+        <v>469</v>
+      </c>
+      <c r="I171" t="s">
+        <v>469</v>
+      </c>
       <c r="J171" t="s">
         <v>22</v>
       </c>
@@ -10691,8 +10710,12 @@
       <c r="O171" t="s">
         <v>217</v>
       </c>
-      <c r="P171" s="2"/>
-      <c r="Q171" s="2"/>
+      <c r="P171" s="2">
+        <v>46310</v>
+      </c>
+      <c r="Q171" s="2">
+        <v>46310</v>
+      </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
@@ -10723,8 +10746,12 @@
       <c r="O172" t="s">
         <v>217</v>
       </c>
-      <c r="P172" s="2"/>
-      <c r="Q172" s="2"/>
+      <c r="P172" s="2">
+        <v>46310</v>
+      </c>
+      <c r="Q172" s="2">
+        <v>46310</v>
+      </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
@@ -21952,6 +21979,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -22212,18 +22251,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -22234,6 +22261,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22252,17 +22290,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
   <ds:schemaRefs>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="394" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B57AAC6-6A16-4198-96D3-1947EDABC0B8}"/>
+  <xr:revisionPtr revIDLastSave="397" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0111635B-02FF-4634-A966-CC2BEE136968}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="R1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C2">
         <f ca="1">B2-$R$1</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D2" t="s">
         <v>184</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C66" ca="1" si="0">B3-$R$1</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D3" t="s">
         <v>184</v>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D4" t="s">
         <v>184</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D5" t="s">
         <v>184</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D6" t="s">
         <v>184</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D7" t="s">
         <v>184</v>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D8" t="s">
         <v>184</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D9" t="s">
         <v>184</v>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D10" t="s">
         <v>184</v>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D11" t="s">
         <v>184</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D12" t="s">
         <v>184</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D13" t="s">
         <v>184</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D14" t="s">
         <v>184</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D15" t="s">
         <v>184</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D16" t="s">
         <v>184</v>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D17" t="s">
         <v>184</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D18" t="s">
         <v>184</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D19" t="s">
         <v>184</v>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D20" t="s">
         <v>184</v>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D21" t="s">
         <v>184</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D22" t="s">
         <v>184</v>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D23" t="s">
         <v>184</v>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D24" t="s">
         <v>184</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D25" t="s">
         <v>184</v>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D26" t="s">
         <v>184</v>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D27" t="s">
         <v>184</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D28" t="s">
         <v>184</v>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D29" t="s">
         <v>184</v>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D30" t="s">
         <v>184</v>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D31" t="s">
         <v>184</v>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D32" t="s">
         <v>184</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D33" t="s">
         <v>184</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D34" t="s">
         <v>184</v>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D35" t="s">
         <v>184</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D36" t="s">
         <v>184</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="0"/>
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="D37" t="s">
         <v>184</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D38" t="s">
         <v>184</v>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D39" t="s">
         <v>184</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="0"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D40" t="s">
         <v>184</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D41" t="s">
         <v>184</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D42" t="s">
         <v>184</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D43" t="s">
         <v>184</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D44" t="s">
         <v>184</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D45" t="s">
         <v>184</v>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D46" t="s">
         <v>184</v>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D47" t="s">
         <v>184</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="0"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D48" t="s">
         <v>184</v>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D49" t="s">
         <v>184</v>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D50" t="s">
         <v>184</v>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D51" t="s">
         <v>184</v>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D52" t="s">
         <v>184</v>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D53" t="s">
         <v>184</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D54" t="s">
         <v>184</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D55" t="s">
         <v>184</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="0"/>
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="D56" t="s">
         <v>184</v>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="0"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D57" t="s">
         <v>184</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D58" t="s">
         <v>184</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D59" t="s">
         <v>184</v>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D60" t="s">
         <v>184</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D61" t="s">
         <v>184</v>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D62" t="s">
         <v>184</v>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D63" t="s">
         <v>184</v>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D64" t="s">
         <v>184</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D65" t="s">
         <v>184</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="0"/>
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="D66" t="s">
         <v>184</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="C67">
         <f t="shared" ref="C67:C130" ca="1" si="1">B67-$R$1</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D67" t="s">
         <v>184</v>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="1"/>
-        <v>-61</v>
+        <v>-62</v>
       </c>
       <c r="D68" t="s">
         <v>184</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D69" t="s">
         <v>184</v>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D70" t="s">
         <v>184</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D71" t="s">
         <v>184</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D72" t="s">
         <v>184</v>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D73" t="s">
         <v>184</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D74" t="s">
         <v>184</v>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D75" t="s">
         <v>184</v>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D76" t="s">
         <v>184</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D77" t="s">
         <v>184</v>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="1"/>
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="D78" t="s">
         <v>184</v>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D80" t="s">
         <v>184</v>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D83" t="s">
         <v>184</v>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D84" t="s">
         <v>184</v>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D85" t="s">
         <v>184</v>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D86" t="s">
         <v>184</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D88" t="s">
         <v>184</v>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D89" t="s">
         <v>184</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D90" t="s">
         <v>184</v>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D91" t="s">
         <v>184</v>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D92" t="s">
         <v>184</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D93" t="s">
         <v>184</v>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D94" t="s">
         <v>184</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D95" t="s">
         <v>184</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D96" t="s">
         <v>184</v>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D97" t="s">
         <v>184</v>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D98" t="s">
         <v>184</v>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D99" t="s">
         <v>184</v>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D100" t="s">
         <v>184</v>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D101" t="s">
         <v>184</v>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="C102">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D102" t="s">
         <v>184</v>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="C103">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D103" t="s">
         <v>184</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="C104">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D104" t="s">
         <v>184</v>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="C105">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D105" t="s">
         <v>184</v>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="C106">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D106" t="s">
         <v>184</v>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="C107">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D107" t="s">
         <v>184</v>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="C108">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D108" t="s">
         <v>184</v>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="C109">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D109" t="s">
         <v>184</v>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="C110">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D110" t="s">
         <v>184</v>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C111">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D111" t="s">
         <v>184</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C113">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D113" t="s">
         <v>184</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C114">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D114" t="s">
         <v>184</v>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="C115">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D115" t="s">
         <v>184</v>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C116">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D116" t="s">
         <v>184</v>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="C117">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D117" t="s">
         <v>184</v>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="C118">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D118" t="s">
         <v>184</v>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="C119">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D119" t="s">
         <v>184</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="C120">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D120" t="s">
         <v>184</v>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="C121">
         <f t="shared" ca="1" si="1"/>
-        <v>-46316</v>
+        <v>-46317</v>
       </c>
       <c r="D121" t="s">
         <v>469</v>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="C122">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D122" t="s">
         <v>184</v>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="C123">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D123" t="s">
         <v>184</v>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="C124">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D124" t="s">
         <v>184</v>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="C125">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D125" t="s">
         <v>184</v>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="C126">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D126" t="s">
         <v>184</v>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="C127">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D127" t="s">
         <v>184</v>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="C128">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D128" t="s">
         <v>184</v>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="C129">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D129" t="s">
         <v>184</v>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="C130">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D130" t="s">
         <v>184</v>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="C131">
         <f t="shared" ref="C131:C192" ca="1" si="2">B131-$R$1</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D131" t="s">
         <v>184</v>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="C132">
         <f t="shared" ca="1" si="2"/>
-        <v>-46316</v>
+        <v>-46317</v>
       </c>
       <c r="D132" t="s">
         <v>184</v>
@@ -8924,7 +8924,7 @@
       </c>
       <c r="C133">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D133" t="s">
         <v>184</v>
@@ -8974,7 +8974,7 @@
         <v>189</v>
       </c>
       <c r="B134" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C134">
         <f t="shared" ca="1" si="2"/>
@@ -9028,7 +9028,7 @@
         <v>190</v>
       </c>
       <c r="B135" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C135">
         <f t="shared" ca="1" si="2"/>
@@ -9082,7 +9082,7 @@
         <v>191</v>
       </c>
       <c r="B136" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C136">
         <f t="shared" ca="1" si="2"/>
@@ -9136,7 +9136,7 @@
         <v>192</v>
       </c>
       <c r="B137" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C137">
         <f t="shared" ca="1" si="2"/>
@@ -9221,12 +9221,12 @@
       <c r="A139" t="s">
         <v>194</v>
       </c>
-      <c r="B139" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C139" t="e">
+      <c r="B139" s="2">
+        <v>46314</v>
+      </c>
+      <c r="C139">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-3</v>
       </c>
       <c r="D139" t="s">
         <v>184</v>
@@ -9407,12 +9407,12 @@
       <c r="A144" t="s">
         <v>199</v>
       </c>
-      <c r="B144" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C144" t="e">
+      <c r="B144" s="2">
+        <v>46314</v>
+      </c>
+      <c r="C144">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-3</v>
       </c>
       <c r="J144" t="s">
         <v>28</v>
@@ -9625,12 +9625,12 @@
       <c r="A150" t="s">
         <v>205</v>
       </c>
-      <c r="B150" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C150" t="e">
+      <c r="B150" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C150">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-1</v>
       </c>
       <c r="D150" t="s">
         <v>184</v>
@@ -9676,11 +9676,11 @@
         <v>164</v>
       </c>
       <c r="B151" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C151">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D151" t="s">
         <v>184</v>
@@ -9730,7 +9730,7 @@
         <v>165</v>
       </c>
       <c r="B152" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C152">
         <f t="shared" ca="1" si="2"/>
@@ -9784,7 +9784,7 @@
         <v>166</v>
       </c>
       <c r="B153" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C153">
         <f t="shared" ca="1" si="2"/>
@@ -9838,7 +9838,7 @@
         <v>167</v>
       </c>
       <c r="B154" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C154">
         <f t="shared" ca="1" si="2"/>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D155" t="s">
         <v>184</v>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="D156" t="s">
         <v>184</v>
@@ -10000,7 +10000,7 @@
         <v>170</v>
       </c>
       <c r="B157" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
@@ -10054,7 +10054,7 @@
         <v>171</v>
       </c>
       <c r="B158" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C158">
         <f t="shared" ca="1" si="2"/>
@@ -10108,7 +10108,7 @@
         <v>172</v>
       </c>
       <c r="B159" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C159">
         <f t="shared" ca="1" si="2"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D160" t="s">
         <v>184</v>
@@ -10216,7 +10216,7 @@
         <v>175</v>
       </c>
       <c r="B161" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D162" t="s">
         <v>184</v>
@@ -10323,12 +10323,12 @@
       <c r="A163" t="s">
         <v>206</v>
       </c>
-      <c r="B163" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C163" t="e">
+      <c r="B163" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C163">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-1</v>
       </c>
       <c r="D163" t="s">
         <v>184</v>
@@ -10362,12 +10362,12 @@
       <c r="A164" t="s">
         <v>207</v>
       </c>
-      <c r="B164" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C164" t="e">
+      <c r="B164" s="2">
+        <v>0</v>
+      </c>
+      <c r="C164">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46317</v>
       </c>
       <c r="D164" t="s">
         <v>184</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D165" t="s">
         <v>469</v>
@@ -10455,12 +10455,12 @@
       <c r="A166" t="s">
         <v>209</v>
       </c>
-      <c r="B166" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C166" t="e">
+      <c r="B166" s="2">
+        <v>0</v>
+      </c>
+      <c r="C166">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46317</v>
       </c>
       <c r="D166" t="s">
         <v>469</v>
@@ -10494,12 +10494,12 @@
       <c r="A167" t="s">
         <v>210</v>
       </c>
-      <c r="B167" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C167" t="e">
+      <c r="B167" s="2">
+        <v>0</v>
+      </c>
+      <c r="C167">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46317</v>
       </c>
       <c r="D167" t="s">
         <v>469</v>
@@ -10533,12 +10533,12 @@
       <c r="A168" t="s">
         <v>211</v>
       </c>
-      <c r="B168" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C168" t="e">
+      <c r="B168" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C168">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-1</v>
       </c>
       <c r="D168" t="s">
         <v>469</v>
@@ -10587,12 +10587,12 @@
       <c r="A169" t="s">
         <v>212</v>
       </c>
-      <c r="B169" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C169" t="e">
+      <c r="B169" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C169">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-1</v>
       </c>
       <c r="D169" t="s">
         <v>184</v>
@@ -10637,12 +10637,12 @@
       <c r="A170" t="s">
         <v>213</v>
       </c>
-      <c r="B170" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C170" t="e">
+      <c r="B170" s="2">
+        <v>0</v>
+      </c>
+      <c r="C170">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46317</v>
       </c>
       <c r="D170" t="s">
         <v>469</v>
@@ -10679,12 +10679,12 @@
       <c r="A171" t="s">
         <v>214</v>
       </c>
-      <c r="B171" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C171" t="e">
+      <c r="B171" s="2">
+        <v>0</v>
+      </c>
+      <c r="C171">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46317</v>
       </c>
       <c r="D171" t="s">
         <v>469</v>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="C173">
         <f t="shared" ca="1" si="2"/>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="D173" t="s">
         <v>184</v>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="C174">
         <f t="shared" ca="1" si="2"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D174" t="s">
         <v>184</v>
@@ -10864,7 +10864,7 @@
       </c>
       <c r="C175">
         <f t="shared" ca="1" si="2"/>
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="D175" t="s">
         <v>184</v>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="C176">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D176" t="s">
         <v>184</v>
@@ -10962,11 +10962,11 @@
         <v>230</v>
       </c>
       <c r="B177" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C177">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D177" t="s">
         <v>184</v>
@@ -11013,7 +11013,7 @@
         <v>231</v>
       </c>
       <c r="B178" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C178">
         <f t="shared" ca="1" si="2"/>
@@ -11064,7 +11064,7 @@
         <v>232</v>
       </c>
       <c r="B179" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C179">
         <f t="shared" ca="1" si="2"/>
@@ -11115,7 +11115,7 @@
         <v>233</v>
       </c>
       <c r="B180" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C180">
         <f t="shared" ca="1" si="2"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="C181">
         <f t="shared" ca="1" si="2"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D181" t="s">
         <v>184</v>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="C182">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D182" t="s">
         <v>184</v>
@@ -11268,7 +11268,7 @@
         <v>236</v>
       </c>
       <c r="B183" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C183">
         <f t="shared" ca="1" si="2"/>
@@ -11323,7 +11323,7 @@
       </c>
       <c r="C184">
         <f t="shared" ca="1" si="2"/>
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="D184" t="s">
         <v>184</v>
@@ -11370,7 +11370,7 @@
         <v>238</v>
       </c>
       <c r="B185" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C185">
         <f t="shared" ca="1" si="2"/>
@@ -11421,7 +11421,7 @@
         <v>239</v>
       </c>
       <c r="B186" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C186">
         <f t="shared" ca="1" si="2"/>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="C187">
         <f t="shared" ca="1" si="2"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D187" t="s">
         <v>184</v>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="C188">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D188" t="s">
         <v>184</v>
@@ -11574,7 +11574,7 @@
         <v>242</v>
       </c>
       <c r="B189" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C189">
         <f t="shared" ca="1" si="2"/>
@@ -11625,7 +11625,7 @@
         <v>243</v>
       </c>
       <c r="B190" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C190">
         <f t="shared" ca="1" si="2"/>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="C191">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D191" t="s">
         <v>184</v>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="C192">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D192" t="s">
         <v>184</v>
@@ -11782,7 +11782,7 @@
       </c>
       <c r="C193">
         <f t="shared" ref="C193:C256" ca="1" si="3">B193-$R$1</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D193" t="s">
         <v>184</v>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="C194">
         <f t="shared" ca="1" si="3"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D194" t="s">
         <v>184</v>
@@ -11880,7 +11880,7 @@
         <v>248</v>
       </c>
       <c r="B195" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C195">
         <f t="shared" ca="1" si="3"/>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="C198">
         <f t="shared" ca="1" si="3"/>
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="D198" t="s">
         <v>184</v>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="C199">
         <f t="shared" ca="1" si="3"/>
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="D199" t="s">
         <v>184</v>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="C200">
         <f t="shared" ca="1" si="3"/>
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="D200" t="s">
         <v>184</v>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="C201">
         <f t="shared" ca="1" si="3"/>
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="D201" t="s">
         <v>184</v>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="C202">
         <f t="shared" ca="1" si="3"/>
-        <v>-279</v>
+        <v>-280</v>
       </c>
       <c r="D202" t="s">
         <v>184</v>
@@ -12292,7 +12292,7 @@
       </c>
       <c r="C203">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D203" t="s">
         <v>184</v>
@@ -12339,7 +12339,7 @@
         <v>257</v>
       </c>
       <c r="B204" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C204">
         <f t="shared" ca="1" si="3"/>
@@ -12390,7 +12390,7 @@
         <v>258</v>
       </c>
       <c r="B205" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C205">
         <f t="shared" ca="1" si="3"/>
@@ -12441,11 +12441,11 @@
         <v>259</v>
       </c>
       <c r="B206" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C206">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D206" t="s">
         <v>184</v>
@@ -12492,7 +12492,7 @@
         <v>260</v>
       </c>
       <c r="B207" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C207">
         <f t="shared" ca="1" si="3"/>
@@ -12543,7 +12543,7 @@
         <v>261</v>
       </c>
       <c r="B208" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C208">
         <f t="shared" ca="1" si="3"/>
@@ -12594,7 +12594,7 @@
         <v>262</v>
       </c>
       <c r="B209" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C209">
         <f t="shared" ca="1" si="3"/>
@@ -12645,11 +12645,11 @@
         <v>263</v>
       </c>
       <c r="B210" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C210">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D210" t="s">
         <v>184</v>
@@ -12696,7 +12696,7 @@
         <v>264</v>
       </c>
       <c r="B211" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C211">
         <f t="shared" ca="1" si="3"/>
@@ -12747,11 +12747,11 @@
         <v>265</v>
       </c>
       <c r="B212" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C212">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D212" t="s">
         <v>184</v>
@@ -12798,7 +12798,7 @@
         <v>266</v>
       </c>
       <c r="B213" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C213">
         <f t="shared" ca="1" si="3"/>
@@ -12849,11 +12849,11 @@
         <v>267</v>
       </c>
       <c r="B214" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C214">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D214" t="s">
         <v>184</v>
@@ -12900,7 +12900,7 @@
         <v>268</v>
       </c>
       <c r="B215" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C215">
         <f t="shared" ca="1" si="3"/>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="C216">
         <f t="shared" ca="1" si="3"/>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
@@ -13006,7 +13006,7 @@
       </c>
       <c r="C217">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D217" t="s">
         <v>184</v>
@@ -13053,7 +13053,7 @@
         <v>271</v>
       </c>
       <c r="B218" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C218">
         <f t="shared" ca="1" si="3"/>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="C219">
         <f t="shared" ca="1" si="3"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D219" t="s">
         <v>184</v>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="C220">
         <f t="shared" ca="1" si="3"/>
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="D220" t="s">
         <v>184</v>
@@ -13206,7 +13206,7 @@
         <v>274</v>
       </c>
       <c r="B221" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C221">
         <f t="shared" ca="1" si="3"/>
@@ -13261,7 +13261,7 @@
       </c>
       <c r="C222">
         <f t="shared" ca="1" si="3"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D222" t="s">
         <v>184</v>
@@ -13308,7 +13308,7 @@
         <v>276</v>
       </c>
       <c r="B223" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C223">
         <f t="shared" ca="1" si="3"/>
@@ -13359,7 +13359,7 @@
         <v>277</v>
       </c>
       <c r="B224" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C224">
         <f t="shared" ca="1" si="3"/>
@@ -13410,7 +13410,7 @@
         <v>278</v>
       </c>
       <c r="B225" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C225">
         <f t="shared" ca="1" si="3"/>
@@ -13461,7 +13461,7 @@
         <v>279</v>
       </c>
       <c r="B226" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C226">
         <f t="shared" ca="1" si="3"/>
@@ -13512,7 +13512,7 @@
         <v>280</v>
       </c>
       <c r="B227" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C227">
         <f t="shared" ca="1" si="3"/>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="C228">
         <f t="shared" ca="1" si="3"/>
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="D228" t="s">
         <v>184</v>
@@ -13614,7 +13614,7 @@
         <v>282</v>
       </c>
       <c r="B229" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C229">
         <f t="shared" ca="1" si="3"/>
@@ -13665,7 +13665,7 @@
         <v>283</v>
       </c>
       <c r="B230" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C230">
         <f t="shared" ca="1" si="3"/>
@@ -13716,7 +13716,7 @@
         <v>284</v>
       </c>
       <c r="B231" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C231">
         <f t="shared" ca="1" si="3"/>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="C232">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D232" t="s">
         <v>184</v>
@@ -13818,11 +13818,11 @@
         <v>286</v>
       </c>
       <c r="B233" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C233">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D233" t="s">
         <v>184</v>
@@ -13869,7 +13869,7 @@
         <v>287</v>
       </c>
       <c r="B234" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C234">
         <f t="shared" ca="1" si="3"/>
@@ -13920,7 +13920,7 @@
         <v>288</v>
       </c>
       <c r="B235" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C235">
         <f t="shared" ca="1" si="3"/>
@@ -13971,7 +13971,7 @@
         <v>289</v>
       </c>
       <c r="B236" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C236">
         <f t="shared" ca="1" si="3"/>
@@ -14026,7 +14026,7 @@
       </c>
       <c r="C237">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D237" t="s">
         <v>184</v>
@@ -14073,7 +14073,7 @@
         <v>291</v>
       </c>
       <c r="B238" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C238">
         <f t="shared" ca="1" si="3"/>
@@ -14128,7 +14128,7 @@
       </c>
       <c r="C239">
         <f t="shared" ca="1" si="3"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D239" t="s">
         <v>184</v>
@@ -14175,7 +14175,7 @@
         <v>293</v>
       </c>
       <c r="B240" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C240">
         <f t="shared" ca="1" si="3"/>
@@ -14226,7 +14226,7 @@
         <v>294</v>
       </c>
       <c r="B241" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C241">
         <f t="shared" ca="1" si="3"/>
@@ -14277,7 +14277,7 @@
         <v>295</v>
       </c>
       <c r="B242" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C242">
         <f t="shared" ca="1" si="3"/>
@@ -14328,11 +14328,11 @@
         <v>296</v>
       </c>
       <c r="B243" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C243">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D243" t="s">
         <v>184</v>
@@ -14379,7 +14379,7 @@
         <v>297</v>
       </c>
       <c r="B244" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C244">
         <f t="shared" ca="1" si="3"/>
@@ -14430,7 +14430,7 @@
         <v>298</v>
       </c>
       <c r="B245" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C245">
         <f t="shared" ca="1" si="3"/>
@@ -14481,7 +14481,7 @@
         <v>299</v>
       </c>
       <c r="B246" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C246">
         <f t="shared" ca="1" si="3"/>
@@ -14532,11 +14532,11 @@
         <v>300</v>
       </c>
       <c r="B247" s="2">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="C247">
         <f t="shared" ca="1" si="3"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D247" t="s">
         <v>184</v>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="C248">
         <f t="shared" ca="1" si="3"/>
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="D248" t="s">
         <v>184</v>
@@ -14634,11 +14634,11 @@
         <v>302</v>
       </c>
       <c r="B249" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C249">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D249" t="s">
         <v>184</v>
@@ -14685,7 +14685,7 @@
         <v>303</v>
       </c>
       <c r="B250" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C250">
         <f t="shared" ca="1" si="3"/>
@@ -14736,7 +14736,7 @@
         <v>304</v>
       </c>
       <c r="B251" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C251">
         <f t="shared" ca="1" si="3"/>
@@ -14787,7 +14787,7 @@
         <v>305</v>
       </c>
       <c r="B252" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C252">
         <f t="shared" ca="1" si="3"/>
@@ -14838,7 +14838,7 @@
         <v>306</v>
       </c>
       <c r="B253" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C253">
         <f t="shared" ca="1" si="3"/>
@@ -14893,7 +14893,7 @@
       </c>
       <c r="C254">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D254" t="s">
         <v>184</v>
@@ -14944,7 +14944,7 @@
       </c>
       <c r="C255">
         <f t="shared" ca="1" si="3"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D255" t="s">
         <v>184</v>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="C256">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D256" t="s">
         <v>184</v>
@@ -15046,7 +15046,7 @@
       </c>
       <c r="C257">
         <f t="shared" ref="C257:C320" ca="1" si="4">B257-$R$1</f>
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="D257" t="s">
         <v>184</v>
@@ -15093,7 +15093,7 @@
         <v>311</v>
       </c>
       <c r="B258" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C258">
         <f t="shared" ca="1" si="4"/>
@@ -15144,7 +15144,7 @@
         <v>312</v>
       </c>
       <c r="B259" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C259">
         <f t="shared" ca="1" si="4"/>
@@ -15195,7 +15195,7 @@
         <v>313</v>
       </c>
       <c r="B260" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C260">
         <f t="shared" ca="1" si="4"/>
@@ -15246,11 +15246,11 @@
         <v>314</v>
       </c>
       <c r="B261" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C261">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D261" t="s">
         <v>184</v>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="C262">
         <f t="shared" ca="1" si="4"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="D262" t="s">
         <v>184</v>
@@ -15348,7 +15348,7 @@
         <v>316</v>
       </c>
       <c r="B263" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C263">
         <f t="shared" ca="1" si="4"/>
@@ -15399,7 +15399,7 @@
         <v>317</v>
       </c>
       <c r="B264" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C264">
         <f t="shared" ca="1" si="4"/>
@@ -15450,11 +15450,11 @@
         <v>318</v>
       </c>
       <c r="B265" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C265">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D265" t="s">
         <v>184</v>
@@ -15505,7 +15505,7 @@
       </c>
       <c r="C266">
         <f t="shared" ca="1" si="4"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D266" t="s">
         <v>184</v>
@@ -15556,7 +15556,7 @@
       </c>
       <c r="C267">
         <f t="shared" ca="1" si="4"/>
-        <v>-139</v>
+        <v>-140</v>
       </c>
       <c r="D267" t="s">
         <v>184</v>
@@ -15603,7 +15603,7 @@
         <v>321</v>
       </c>
       <c r="B268" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C268">
         <f t="shared" ca="1" si="4"/>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="C269">
         <f t="shared" ca="1" si="4"/>
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="D269" t="s">
         <v>184</v>
@@ -15705,11 +15705,11 @@
         <v>323</v>
       </c>
       <c r="B270" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C270">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D270" t="s">
         <v>184</v>
@@ -15756,7 +15756,7 @@
         <v>324</v>
       </c>
       <c r="B271" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C271">
         <f t="shared" ca="1" si="4"/>
@@ -15807,7 +15807,7 @@
         <v>325</v>
       </c>
       <c r="B272" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C272">
         <f t="shared" ca="1" si="4"/>
@@ -15858,7 +15858,7 @@
         <v>326</v>
       </c>
       <c r="B273" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C273">
         <f t="shared" ca="1" si="4"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="C274">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D274" t="s">
         <v>184</v>
@@ -15960,7 +15960,7 @@
         <v>328</v>
       </c>
       <c r="B275" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C275">
         <f t="shared" ca="1" si="4"/>
@@ -16011,11 +16011,11 @@
         <v>329</v>
       </c>
       <c r="B276" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C276">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D276" t="s">
         <v>184</v>
@@ -16062,7 +16062,7 @@
         <v>330</v>
       </c>
       <c r="B277" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C277">
         <f t="shared" ca="1" si="4"/>
@@ -16113,7 +16113,7 @@
         <v>331</v>
       </c>
       <c r="B278" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C278">
         <f t="shared" ca="1" si="4"/>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="C279">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D279" t="s">
         <v>184</v>
@@ -16215,11 +16215,11 @@
         <v>333</v>
       </c>
       <c r="B280" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C280">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D280" t="s">
         <v>184</v>
@@ -16266,7 +16266,7 @@
         <v>334</v>
       </c>
       <c r="B281" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C281">
         <f t="shared" ca="1" si="4"/>
@@ -16321,7 +16321,7 @@
       </c>
       <c r="C282">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D282" t="s">
         <v>184</v>
@@ -16368,7 +16368,7 @@
         <v>336</v>
       </c>
       <c r="B283" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C283">
         <f t="shared" ca="1" si="4"/>
@@ -16419,7 +16419,7 @@
         <v>337</v>
       </c>
       <c r="B284" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C284">
         <f t="shared" ca="1" si="4"/>
@@ -16474,7 +16474,7 @@
       </c>
       <c r="C285">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D285" t="s">
         <v>184</v>
@@ -16521,7 +16521,7 @@
         <v>339</v>
       </c>
       <c r="B286" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C286">
         <f t="shared" ca="1" si="4"/>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="C287">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D287" t="s">
         <v>184</v>
@@ -16627,7 +16627,7 @@
       </c>
       <c r="C288">
         <f t="shared" ca="1" si="4"/>
-        <v>-225</v>
+        <v>-226</v>
       </c>
       <c r="D288" t="s">
         <v>184</v>
@@ -16674,7 +16674,7 @@
         <v>342</v>
       </c>
       <c r="B289" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C289">
         <f t="shared" ca="1" si="4"/>
@@ -16725,7 +16725,7 @@
         <v>343</v>
       </c>
       <c r="B290" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C290">
         <f t="shared" ca="1" si="4"/>
@@ -16776,7 +16776,7 @@
         <v>344</v>
       </c>
       <c r="B291" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C291">
         <f t="shared" ca="1" si="4"/>
@@ -16827,7 +16827,7 @@
         <v>345</v>
       </c>
       <c r="B292" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C292">
         <f t="shared" ca="1" si="4"/>
@@ -16878,7 +16878,7 @@
         <v>346</v>
       </c>
       <c r="B293" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C293">
         <f t="shared" ca="1" si="4"/>
@@ -16929,11 +16929,11 @@
         <v>347</v>
       </c>
       <c r="B294" s="2">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="C294">
         <f t="shared" ca="1" si="4"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D294" t="s">
         <v>184</v>
@@ -16980,7 +16980,7 @@
         <v>348</v>
       </c>
       <c r="B295" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C295">
         <f t="shared" ca="1" si="4"/>
@@ -17031,7 +17031,7 @@
         <v>349</v>
       </c>
       <c r="B296" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C296">
         <f t="shared" ca="1" si="4"/>
@@ -17086,7 +17086,7 @@
       </c>
       <c r="C297">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D297" t="s">
         <v>184</v>
@@ -17133,7 +17133,7 @@
         <v>351</v>
       </c>
       <c r="B298" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C298">
         <f t="shared" ca="1" si="4"/>
@@ -17184,7 +17184,7 @@
         <v>352</v>
       </c>
       <c r="B299" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C299">
         <f t="shared" ca="1" si="4"/>
@@ -17235,7 +17235,7 @@
         <v>353</v>
       </c>
       <c r="B300" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C300">
         <f t="shared" ca="1" si="4"/>
@@ -17286,7 +17286,7 @@
         <v>354</v>
       </c>
       <c r="B301" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C301">
         <f t="shared" ca="1" si="4"/>
@@ -17337,7 +17337,7 @@
         <v>355</v>
       </c>
       <c r="B302" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C302">
         <f t="shared" ca="1" si="4"/>
@@ -17388,7 +17388,7 @@
         <v>356</v>
       </c>
       <c r="B303" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C303">
         <f t="shared" ca="1" si="4"/>
@@ -17439,7 +17439,7 @@
         <v>357</v>
       </c>
       <c r="B304" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C304">
         <f t="shared" ca="1" si="4"/>
@@ -17490,7 +17490,7 @@
         <v>358</v>
       </c>
       <c r="B305" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C305">
         <f t="shared" ca="1" si="4"/>
@@ -17541,11 +17541,11 @@
         <v>359</v>
       </c>
       <c r="B306" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C306">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D306" t="s">
         <v>184</v>
@@ -17592,11 +17592,11 @@
         <v>360</v>
       </c>
       <c r="B307" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C307">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D307" t="s">
         <v>184</v>
@@ -17643,7 +17643,7 @@
         <v>361</v>
       </c>
       <c r="B308" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C308">
         <f t="shared" ca="1" si="4"/>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="C309">
         <f t="shared" ca="1" si="4"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D309" t="s">
         <v>184</v>
@@ -17745,7 +17745,7 @@
         <v>363</v>
       </c>
       <c r="B310" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C310">
         <f t="shared" ca="1" si="4"/>
@@ -17796,7 +17796,7 @@
         <v>364</v>
       </c>
       <c r="B311" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C311">
         <f t="shared" ca="1" si="4"/>
@@ -17847,7 +17847,7 @@
         <v>365</v>
       </c>
       <c r="B312" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C312">
         <f t="shared" ca="1" si="4"/>
@@ -17898,7 +17898,7 @@
         <v>366</v>
       </c>
       <c r="B313" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C313">
         <f t="shared" ca="1" si="4"/>
@@ -17949,7 +17949,7 @@
         <v>367</v>
       </c>
       <c r="B314" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C314">
         <f t="shared" ca="1" si="4"/>
@@ -18004,7 +18004,7 @@
       </c>
       <c r="C315">
         <f t="shared" ca="1" si="4"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D315" t="s">
         <v>184</v>
@@ -18051,7 +18051,7 @@
         <v>369</v>
       </c>
       <c r="B316" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C316">
         <f t="shared" ca="1" si="4"/>
@@ -18102,7 +18102,7 @@
         <v>370</v>
       </c>
       <c r="B317" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C317">
         <f t="shared" ca="1" si="4"/>
@@ -18157,7 +18157,7 @@
       </c>
       <c r="C318">
         <f t="shared" ca="1" si="4"/>
-        <v>-72</v>
+        <v>-73</v>
       </c>
       <c r="D318" t="s">
         <v>184</v>
@@ -18204,7 +18204,7 @@
         <v>372</v>
       </c>
       <c r="B319" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C319">
         <f t="shared" ca="1" si="4"/>
@@ -18259,7 +18259,7 @@
       </c>
       <c r="C320">
         <f t="shared" ca="1" si="4"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D320" t="s">
         <v>184</v>
@@ -18306,7 +18306,7 @@
         <v>374</v>
       </c>
       <c r="B321" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C321">
         <f t="shared" ref="C321:C384" ca="1" si="5">B321-$R$1</f>
@@ -18361,7 +18361,7 @@
       </c>
       <c r="C322">
         <f t="shared" ca="1" si="5"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D322" t="s">
         <v>184</v>
@@ -18412,7 +18412,7 @@
       </c>
       <c r="C323">
         <f t="shared" ca="1" si="5"/>
-        <v>-76</v>
+        <v>-77</v>
       </c>
       <c r="D323" t="s">
         <v>184</v>
@@ -18463,7 +18463,7 @@
       </c>
       <c r="C324">
         <f t="shared" ca="1" si="5"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="D324" t="s">
         <v>184</v>
@@ -18510,7 +18510,7 @@
         <v>378</v>
       </c>
       <c r="B325" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C325">
         <f t="shared" ca="1" si="5"/>
@@ -18561,7 +18561,7 @@
         <v>379</v>
       </c>
       <c r="B326" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C326">
         <f t="shared" ca="1" si="5"/>
@@ -18612,11 +18612,11 @@
         <v>380</v>
       </c>
       <c r="B327" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C327">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D327" t="s">
         <v>184</v>
@@ -18663,7 +18663,7 @@
         <v>381</v>
       </c>
       <c r="B328" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C328">
         <f t="shared" ca="1" si="5"/>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="C329">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D329" t="s">
         <v>184</v>
@@ -18765,7 +18765,7 @@
         <v>383</v>
       </c>
       <c r="B330" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C330">
         <f t="shared" ca="1" si="5"/>
@@ -18820,7 +18820,7 @@
       </c>
       <c r="C331">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D331" t="s">
         <v>184</v>
@@ -18871,7 +18871,7 @@
       </c>
       <c r="C332">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D332" t="s">
         <v>184</v>
@@ -18918,7 +18918,7 @@
         <v>386</v>
       </c>
       <c r="B333" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C333">
         <f t="shared" ca="1" si="5"/>
@@ -18969,7 +18969,7 @@
         <v>387</v>
       </c>
       <c r="B334" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C334">
         <f t="shared" ca="1" si="5"/>
@@ -19024,7 +19024,7 @@
       </c>
       <c r="C335">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D335" t="s">
         <v>184</v>
@@ -19071,7 +19071,7 @@
         <v>389</v>
       </c>
       <c r="B336" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C336">
         <f t="shared" ca="1" si="5"/>
@@ -19126,7 +19126,7 @@
       </c>
       <c r="C337">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D337" t="s">
         <v>184</v>
@@ -19173,11 +19173,11 @@
         <v>391</v>
       </c>
       <c r="B338" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C338">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D338" t="s">
         <v>184</v>
@@ -19228,7 +19228,7 @@
       </c>
       <c r="C339">
         <f t="shared" ca="1" si="5"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D339" t="s">
         <v>184</v>
@@ -19275,7 +19275,7 @@
         <v>393</v>
       </c>
       <c r="B340" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C340">
         <f t="shared" ca="1" si="5"/>
@@ -19326,7 +19326,7 @@
         <v>394</v>
       </c>
       <c r="B341" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C341">
         <f t="shared" ca="1" si="5"/>
@@ -19377,11 +19377,11 @@
         <v>395</v>
       </c>
       <c r="B342" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C342">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D342" t="s">
         <v>184</v>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="C343">
         <f t="shared" ca="1" si="5"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D343" t="s">
         <v>184</v>
@@ -19479,7 +19479,7 @@
         <v>397</v>
       </c>
       <c r="B344" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C344">
         <f t="shared" ca="1" si="5"/>
@@ -19530,11 +19530,11 @@
         <v>398</v>
       </c>
       <c r="B345" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C345">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D345" t="s">
         <v>184</v>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="C346">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D346" t="s">
         <v>184</v>
@@ -19632,7 +19632,7 @@
         <v>400</v>
       </c>
       <c r="B347" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C347">
         <f t="shared" ca="1" si="5"/>
@@ -19687,7 +19687,7 @@
       </c>
       <c r="C348">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D348" t="s">
         <v>184</v>
@@ -19734,7 +19734,7 @@
         <v>402</v>
       </c>
       <c r="B349" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C349">
         <f t="shared" ca="1" si="5"/>
@@ -19785,7 +19785,7 @@
         <v>403</v>
       </c>
       <c r="B350" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C350">
         <f t="shared" ca="1" si="5"/>
@@ -19836,11 +19836,11 @@
         <v>404</v>
       </c>
       <c r="B351" s="2">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="C351">
         <f t="shared" ca="1" si="5"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D351" t="s">
         <v>184</v>
@@ -19891,7 +19891,7 @@
       </c>
       <c r="C352">
         <f t="shared" ca="1" si="5"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D352" t="s">
         <v>184</v>
@@ -19938,11 +19938,11 @@
         <v>406</v>
       </c>
       <c r="B353" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C353">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D353" t="s">
         <v>184</v>
@@ -19989,11 +19989,11 @@
         <v>407</v>
       </c>
       <c r="B354" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C354">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D354" t="s">
         <v>184</v>
@@ -20040,11 +20040,11 @@
         <v>408</v>
       </c>
       <c r="B355" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C355">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D355" t="s">
         <v>184</v>
@@ -20091,7 +20091,7 @@
         <v>409</v>
       </c>
       <c r="B356" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C356">
         <f t="shared" ca="1" si="5"/>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="C357">
         <f t="shared" ca="1" si="5"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="D357" t="s">
         <v>184</v>
@@ -20193,7 +20193,7 @@
         <v>411</v>
       </c>
       <c r="B358" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C358">
         <f t="shared" ca="1" si="5"/>
@@ -20244,7 +20244,7 @@
         <v>412</v>
       </c>
       <c r="B359" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C359">
         <f t="shared" ca="1" si="5"/>
@@ -20295,7 +20295,7 @@
         <v>413</v>
       </c>
       <c r="B360" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C360">
         <f t="shared" ca="1" si="5"/>
@@ -20346,7 +20346,7 @@
         <v>414</v>
       </c>
       <c r="B361" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C361">
         <f t="shared" ca="1" si="5"/>
@@ -20401,7 +20401,7 @@
       </c>
       <c r="C362">
         <f t="shared" ca="1" si="5"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D362" t="s">
         <v>184</v>
@@ -20452,7 +20452,7 @@
       </c>
       <c r="C363">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D363" t="s">
         <v>184</v>
@@ -20499,7 +20499,7 @@
         <v>417</v>
       </c>
       <c r="B364" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C364">
         <f t="shared" ca="1" si="5"/>
@@ -20550,7 +20550,7 @@
         <v>418</v>
       </c>
       <c r="B365" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C365">
         <f t="shared" ca="1" si="5"/>
@@ -20601,7 +20601,7 @@
         <v>419</v>
       </c>
       <c r="B366" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C366">
         <f t="shared" ca="1" si="5"/>
@@ -20652,11 +20652,11 @@
         <v>420</v>
       </c>
       <c r="B367" s="2">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="C367">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D367" t="s">
         <v>184</v>
@@ -20703,7 +20703,7 @@
         <v>421</v>
       </c>
       <c r="B368" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C368">
         <f t="shared" ca="1" si="5"/>
@@ -20754,7 +20754,7 @@
         <v>422</v>
       </c>
       <c r="B369" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C369">
         <f t="shared" ca="1" si="5"/>
@@ -20805,7 +20805,7 @@
         <v>423</v>
       </c>
       <c r="B370" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C370">
         <f t="shared" ca="1" si="5"/>
@@ -20856,11 +20856,11 @@
         <v>424</v>
       </c>
       <c r="B371" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C371">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D371" t="s">
         <v>184</v>
@@ -20911,7 +20911,7 @@
       </c>
       <c r="C372">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D372" t="s">
         <v>184</v>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="C373">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D373" t="s">
         <v>184</v>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="C374">
         <f t="shared" ca="1" si="5"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D374" t="s">
         <v>184</v>
@@ -21060,11 +21060,11 @@
         <v>428</v>
       </c>
       <c r="B375" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C375">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D375" t="s">
         <v>184</v>
@@ -21111,11 +21111,11 @@
         <v>429</v>
       </c>
       <c r="B376" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C376">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D376" t="s">
         <v>184</v>
@@ -21162,7 +21162,7 @@
         <v>430</v>
       </c>
       <c r="B377" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C377">
         <f t="shared" ca="1" si="5"/>
@@ -21213,7 +21213,7 @@
         <v>431</v>
       </c>
       <c r="B378" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C378">
         <f t="shared" ca="1" si="5"/>
@@ -21264,7 +21264,7 @@
         <v>432</v>
       </c>
       <c r="B379" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C379">
         <f t="shared" ca="1" si="5"/>
@@ -21315,7 +21315,7 @@
         <v>433</v>
       </c>
       <c r="B380" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C380">
         <f t="shared" ca="1" si="5"/>
@@ -21366,7 +21366,7 @@
         <v>434</v>
       </c>
       <c r="B381" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C381">
         <f t="shared" ca="1" si="5"/>
@@ -21417,7 +21417,7 @@
         <v>435</v>
       </c>
       <c r="B382" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C382">
         <f t="shared" ca="1" si="5"/>
@@ -21472,7 +21472,7 @@
       </c>
       <c r="C383">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D383" t="s">
         <v>184</v>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="C384">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D384" t="s">
         <v>184</v>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="C385">
         <f t="shared" ref="C385:C392" ca="1" si="6">B385-$R$1</f>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D385" t="s">
         <v>184</v>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="C386">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D386" t="s">
         <v>184</v>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="C387">
         <f t="shared" ca="1" si="6"/>
-        <v>-46316</v>
+        <v>-46317</v>
       </c>
       <c r="D387" t="s">
         <v>184</v>
@@ -21727,7 +21727,7 @@
       </c>
       <c r="C388">
         <f t="shared" ca="1" si="6"/>
-        <v>-46316</v>
+        <v>-46317</v>
       </c>
       <c r="D388" t="s">
         <v>184</v>
@@ -21778,7 +21778,7 @@
       </c>
       <c r="C389">
         <f t="shared" ca="1" si="6"/>
-        <v>-46316</v>
+        <v>-46317</v>
       </c>
       <c r="D389" t="s">
         <v>184</v>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="C390">
         <f t="shared" ca="1" si="6"/>
-        <v>-46316</v>
+        <v>-46317</v>
       </c>
       <c r="D390" t="s">
         <v>184</v>
@@ -21876,7 +21876,7 @@
         <v>444</v>
       </c>
       <c r="B391" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C391">
         <f t="shared" ca="1" si="6"/>
@@ -21931,7 +21931,7 @@
       </c>
       <c r="C392">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D392" t="s">
         <v>184</v>
@@ -21979,18 +21979,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -22251,6 +22239,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -22261,17 +22261,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22290,6 +22279,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
   <ds:schemaRefs>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="397" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0111635B-02FF-4634-A966-CC2BEE136968}"/>
+  <xr:revisionPtr revIDLastSave="409" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4690E41A-04C5-4D17-A888-FAADA2687195}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4789" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4794" uniqueCount="470">
   <si>
     <t>Placa</t>
   </si>
@@ -10333,6 +10333,21 @@
       <c r="D163" t="s">
         <v>184</v>
       </c>
+      <c r="E163" t="s">
+        <v>184</v>
+      </c>
+      <c r="F163" t="s">
+        <v>184</v>
+      </c>
+      <c r="G163" t="s">
+        <v>184</v>
+      </c>
+      <c r="H163" t="s">
+        <v>184</v>
+      </c>
+      <c r="I163" t="s">
+        <v>184</v>
+      </c>
       <c r="J163" t="s">
         <v>174</v>
       </c>
@@ -21979,6 +21994,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -22239,28 +22275,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22277,23 +22311,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="409" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4690E41A-04C5-4D17-A888-FAADA2687195}"/>
+  <xr:revisionPtr revIDLastSave="412" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4384867-FDD5-429D-896C-EC9519652E39}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4794" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4795" uniqueCount="470">
   <si>
     <t>Placa</t>
   </si>
@@ -9282,6 +9282,9 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D140" t="s">
+        <v>184</v>
+      </c>
       <c r="J140" t="s">
         <v>28</v>
       </c>
@@ -9300,8 +9303,12 @@
       <c r="O140" t="s">
         <v>217</v>
       </c>
-      <c r="P140" s="2"/>
-      <c r="Q140" s="2"/>
+      <c r="P140" s="2">
+        <v>46317</v>
+      </c>
+      <c r="Q140" s="2">
+        <v>46317</v>
+      </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
@@ -21994,6 +22001,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -22003,15 +22019,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22276,20 +22283,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="412" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4384867-FDD5-429D-896C-EC9519652E39}"/>
+  <xr:revisionPtr revIDLastSave="415" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA8658FF-1B76-424B-8C5C-E5B316CB0780}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4795" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4796" uniqueCount="470">
   <si>
     <t>Placa</t>
   </si>
@@ -9196,6 +9196,9 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D138" t="s">
+        <v>184</v>
+      </c>
       <c r="J138" t="s">
         <v>28</v>
       </c>
@@ -9214,8 +9217,12 @@
       <c r="O138" t="s">
         <v>217</v>
       </c>
-      <c r="P138" s="2"/>
-      <c r="Q138" s="2"/>
+      <c r="P138" s="2">
+        <v>46317</v>
+      </c>
+      <c r="Q138" s="2">
+        <v>46317</v>
+      </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
@@ -22001,15 +22008,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -22019,6 +22017,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22283,20 +22290,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="415" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA8658FF-1B76-424B-8C5C-E5B316CB0780}"/>
+  <xr:revisionPtr revIDLastSave="419" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B510526F-519D-4A89-BA19-0FBEA1F54C24}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4796" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4804" uniqueCount="470">
   <si>
     <t>Placa</t>
   </si>
@@ -9199,6 +9199,9 @@
       <c r="D138" t="s">
         <v>184</v>
       </c>
+      <c r="I138" t="s">
+        <v>184</v>
+      </c>
       <c r="J138" t="s">
         <v>28</v>
       </c>
@@ -9292,6 +9295,9 @@
       <c r="D140" t="s">
         <v>184</v>
       </c>
+      <c r="I140" t="s">
+        <v>184</v>
+      </c>
       <c r="J140" t="s">
         <v>28</v>
       </c>
@@ -9331,6 +9337,9 @@
       <c r="D141" t="s">
         <v>184</v>
       </c>
+      <c r="I141" t="s">
+        <v>184</v>
+      </c>
       <c r="J141" t="s">
         <v>28</v>
       </c>
@@ -9537,6 +9546,9 @@
       <c r="D147" t="s">
         <v>184</v>
       </c>
+      <c r="I147" t="s">
+        <v>184</v>
+      </c>
       <c r="J147" t="s">
         <v>28</v>
       </c>
@@ -9576,6 +9588,9 @@
       <c r="D148" t="s">
         <v>184</v>
       </c>
+      <c r="I148" t="s">
+        <v>184</v>
+      </c>
       <c r="J148" t="s">
         <v>28</v>
       </c>
@@ -10401,6 +10416,9 @@
       <c r="D164" t="s">
         <v>184</v>
       </c>
+      <c r="I164" t="s">
+        <v>184</v>
+      </c>
       <c r="J164" t="s">
         <v>174</v>
       </c>
@@ -10453,7 +10471,7 @@
         <v>469</v>
       </c>
       <c r="I165" t="s">
-        <v>469</v>
+        <v>184</v>
       </c>
       <c r="J165" t="s">
         <v>174</v>
@@ -10494,6 +10512,9 @@
       <c r="D166" t="s">
         <v>469</v>
       </c>
+      <c r="I166" t="s">
+        <v>184</v>
+      </c>
       <c r="J166" t="s">
         <v>174</v>
       </c>
@@ -10533,6 +10554,9 @@
       <c r="D167" t="s">
         <v>469</v>
       </c>
+      <c r="I167" t="s">
+        <v>184</v>
+      </c>
       <c r="J167" t="s">
         <v>174</v>
       </c>
@@ -10585,7 +10609,7 @@
         <v>469</v>
       </c>
       <c r="I168" t="s">
-        <v>469</v>
+        <v>184</v>
       </c>
       <c r="J168" t="s">
         <v>174</v>
@@ -10677,7 +10701,7 @@
         <v>469</v>
       </c>
       <c r="I170" t="s">
-        <v>469</v>
+        <v>184</v>
       </c>
       <c r="J170" t="s">
         <v>22</v>
@@ -10719,7 +10743,7 @@
         <v>469</v>
       </c>
       <c r="I171" t="s">
-        <v>469</v>
+        <v>184</v>
       </c>
       <c r="J171" t="s">
         <v>22</v>
@@ -22008,6 +22032,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -22017,15 +22050,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22290,20 +22314,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="419" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B510526F-519D-4A89-BA19-0FBEA1F54C24}"/>
+  <xr:revisionPtr revIDLastSave="423" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EFCB533-4294-4217-B035-64242ACBA7E3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Placas_BID2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Placas_BID2026!$A$1:$R$392</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Placas_BID2026!$A$1:$R$390</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4804" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4780" uniqueCount="466">
   <si>
     <t>Placa</t>
   </si>
@@ -785,12 +785,6 @@
     <t>TXS8A91</t>
   </si>
   <si>
-    <t>TXJ6H38</t>
-  </si>
-  <si>
-    <t>TXJ6H73</t>
-  </si>
-  <si>
     <t>SDT9F10</t>
   </si>
   <si>
@@ -1397,9 +1391,6 @@
     <t>317 SPRINTER C</t>
   </si>
   <si>
-    <t>KANGOO ADV 17</t>
-  </si>
-  <si>
     <t>KANGOO MAX ZE</t>
   </si>
   <si>
@@ -1440,9 +1431,6 @@
   </si>
   <si>
     <t>Pralog</t>
-  </si>
-  <si>
-    <t>Unidas</t>
   </si>
   <si>
     <t>OK</t>
@@ -1800,7 +1788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R392"/>
+  <dimension ref="A1:R390"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
@@ -8279,22 +8267,22 @@
         <v>-46317</v>
       </c>
       <c r="D121" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="E121" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F121" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G121" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="H121" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I121" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="J121" t="s">
         <v>118</v>
@@ -10456,19 +10444,19 @@
         <v>-2</v>
       </c>
       <c r="D165" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="E165" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F165" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G165" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="H165" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I165" t="s">
         <v>184</v>
@@ -10510,7 +10498,7 @@
         <v>-46317</v>
       </c>
       <c r="D166" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I166" t="s">
         <v>184</v>
@@ -10552,7 +10540,7 @@
         <v>-46317</v>
       </c>
       <c r="D167" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I167" t="s">
         <v>184</v>
@@ -10594,19 +10582,19 @@
         <v>-1</v>
       </c>
       <c r="D168" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="E168" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F168" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G168" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="H168" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I168" t="s">
         <v>184</v>
@@ -10698,7 +10686,7 @@
         <v>-46317</v>
       </c>
       <c r="D170" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I170" t="s">
         <v>184</v>
@@ -10740,7 +10728,7 @@
         <v>-46317</v>
       </c>
       <c r="D171" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I171" t="s">
         <v>184</v>
@@ -10848,7 +10836,7 @@
         <v>34</v>
       </c>
       <c r="N173" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P173" s="2">
         <v>46023</v>
@@ -10899,7 +10887,7 @@
         <v>34</v>
       </c>
       <c r="N174" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P174" s="2">
         <v>46023</v>
@@ -10950,7 +10938,7 @@
         <v>34</v>
       </c>
       <c r="N175" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P175" s="2">
         <v>46023</v>
@@ -11001,7 +10989,7 @@
         <v>34</v>
       </c>
       <c r="N176" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P176" s="2">
         <v>46023</v>
@@ -11052,7 +11040,7 @@
         <v>24</v>
       </c>
       <c r="N177" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P177" s="2">
         <v>46023</v>
@@ -11103,7 +11091,7 @@
         <v>24</v>
       </c>
       <c r="N178" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P178" s="2">
         <v>46023</v>
@@ -11154,7 +11142,7 @@
         <v>178</v>
       </c>
       <c r="N179" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P179" s="2">
         <v>46023</v>
@@ -11205,7 +11193,7 @@
         <v>178</v>
       </c>
       <c r="N180" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P180" s="2">
         <v>46023</v>
@@ -11256,7 +11244,7 @@
         <v>178</v>
       </c>
       <c r="N181" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P181" s="2">
         <v>46023</v>
@@ -11307,7 +11295,7 @@
         <v>178</v>
       </c>
       <c r="N182" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P182" s="2">
         <v>46023</v>
@@ -11358,7 +11346,7 @@
         <v>119</v>
       </c>
       <c r="N183" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P183" s="2">
         <v>46023</v>
@@ -11406,10 +11394,10 @@
         <v>29</v>
       </c>
       <c r="M184" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N184" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P184" s="2">
         <v>46023</v>
@@ -11457,10 +11445,10 @@
         <v>29</v>
       </c>
       <c r="M185" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N185" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P185" s="2">
         <v>46023</v>
@@ -11511,7 +11499,7 @@
         <v>24</v>
       </c>
       <c r="N186" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P186" s="2">
         <v>46023</v>
@@ -11562,7 +11550,7 @@
         <v>24</v>
       </c>
       <c r="N187" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P187" s="2">
         <v>46023</v>
@@ -11613,7 +11601,7 @@
         <v>24</v>
       </c>
       <c r="N188" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P188" s="2">
         <v>46023</v>
@@ -11664,7 +11652,7 @@
         <v>24</v>
       </c>
       <c r="N189" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P189" s="2">
         <v>46023</v>
@@ -11712,10 +11700,10 @@
         <v>23</v>
       </c>
       <c r="M190" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="N190" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P190" s="2">
         <v>46023</v>
@@ -11766,7 +11754,7 @@
         <v>178</v>
       </c>
       <c r="N191" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P191" s="2">
         <v>46023</v>
@@ -11834,7 +11822,7 @@
         <v>46315</v>
       </c>
       <c r="C193">
-        <f t="shared" ref="C193:C256" ca="1" si="3">B193-$R$1</f>
+        <f t="shared" ref="C193:C254" ca="1" si="3">B193-$R$1</f>
         <v>-2</v>
       </c>
       <c r="D193" t="s">
@@ -11856,7 +11844,7 @@
         <v>184</v>
       </c>
       <c r="J193" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="K193" t="s">
         <v>11</v>
@@ -11868,7 +11856,7 @@
         <v>119</v>
       </c>
       <c r="N193" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P193" s="2">
         <v>46023</v>
@@ -11919,7 +11907,7 @@
         <v>119</v>
       </c>
       <c r="N194" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P194" s="2">
         <v>46023</v>
@@ -11970,7 +11958,7 @@
         <v>24</v>
       </c>
       <c r="N195" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P195" s="2">
         <v>46023</v>
@@ -11983,12 +11971,12 @@
       <c r="A196" t="s">
         <v>249</v>
       </c>
-      <c r="B196" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C196" t="e">
+      <c r="B196" s="2">
+        <v>46167</v>
+      </c>
+      <c r="C196">
         <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
+        <v>-150</v>
       </c>
       <c r="D196" t="s">
         <v>184</v>
@@ -12009,19 +11997,19 @@
         <v>184</v>
       </c>
       <c r="J196" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K196" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L196" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M196" t="s">
-        <v>468</v>
+        <v>34</v>
       </c>
       <c r="N196" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="P196" s="2">
         <v>46023</v>
@@ -12034,12 +12022,12 @@
       <c r="A197" t="s">
         <v>250</v>
       </c>
-      <c r="B197" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C197" t="e">
+      <c r="B197" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C197">
         <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
+        <v>-31</v>
       </c>
       <c r="D197" t="s">
         <v>184</v>
@@ -12060,19 +12048,19 @@
         <v>184</v>
       </c>
       <c r="J197" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K197" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L197" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M197" t="s">
-        <v>468</v>
+        <v>34</v>
       </c>
       <c r="N197" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="P197" s="2">
         <v>46023</v>
@@ -12086,11 +12074,11 @@
         <v>251</v>
       </c>
       <c r="B198" s="2">
-        <v>46167</v>
+        <v>46281</v>
       </c>
       <c r="C198">
         <f t="shared" ca="1" si="3"/>
-        <v>-150</v>
+        <v>-36</v>
       </c>
       <c r="D198" t="s">
         <v>184</v>
@@ -12123,7 +12111,7 @@
         <v>34</v>
       </c>
       <c r="N198" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P198" s="2">
         <v>46023</v>
@@ -12137,11 +12125,11 @@
         <v>252</v>
       </c>
       <c r="B199" s="2">
-        <v>46286</v>
+        <v>46299</v>
       </c>
       <c r="C199">
         <f t="shared" ca="1" si="3"/>
-        <v>-31</v>
+        <v>-18</v>
       </c>
       <c r="D199" t="s">
         <v>184</v>
@@ -12162,19 +12150,19 @@
         <v>184</v>
       </c>
       <c r="J199" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K199" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L199" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M199" t="s">
         <v>34</v>
       </c>
       <c r="N199" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="P199" s="2">
         <v>46023</v>
@@ -12188,11 +12176,11 @@
         <v>253</v>
       </c>
       <c r="B200" s="2">
-        <v>46281</v>
+        <v>46037</v>
       </c>
       <c r="C200">
         <f t="shared" ca="1" si="3"/>
-        <v>-36</v>
+        <v>-280</v>
       </c>
       <c r="D200" t="s">
         <v>184</v>
@@ -12213,19 +12201,19 @@
         <v>184</v>
       </c>
       <c r="J200" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K200" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L200" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M200" t="s">
         <v>34</v>
       </c>
       <c r="N200" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="P200" s="2">
         <v>46023</v>
@@ -12239,11 +12227,11 @@
         <v>254</v>
       </c>
       <c r="B201" s="2">
-        <v>46299</v>
+        <v>46315</v>
       </c>
       <c r="C201">
         <f t="shared" ca="1" si="3"/>
-        <v>-18</v>
+        <v>-2</v>
       </c>
       <c r="D201" t="s">
         <v>184</v>
@@ -12276,7 +12264,7 @@
         <v>34</v>
       </c>
       <c r="N201" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="P201" s="2">
         <v>46023</v>
@@ -12290,11 +12278,11 @@
         <v>255</v>
       </c>
       <c r="B202" s="2">
-        <v>46037</v>
+        <v>46316</v>
       </c>
       <c r="C202">
         <f t="shared" ca="1" si="3"/>
-        <v>-280</v>
+        <v>-1</v>
       </c>
       <c r="D202" t="s">
         <v>184</v>
@@ -12327,7 +12315,7 @@
         <v>34</v>
       </c>
       <c r="N202" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="P202" s="2">
         <v>46023</v>
@@ -12341,11 +12329,11 @@
         <v>256</v>
       </c>
       <c r="B203" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C203">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D203" t="s">
         <v>184</v>
@@ -12366,19 +12354,19 @@
         <v>184</v>
       </c>
       <c r="J203" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K203" t="s">
         <v>11</v>
       </c>
       <c r="L203" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M203" t="s">
-        <v>34</v>
+        <v>178</v>
       </c>
       <c r="N203" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="P203" s="2">
         <v>46023</v>
@@ -12417,19 +12405,19 @@
         <v>184</v>
       </c>
       <c r="J204" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K204" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L204" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M204" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N204" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="P204" s="2">
         <v>46023</v>
@@ -12468,19 +12456,19 @@
         <v>184</v>
       </c>
       <c r="J205" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K205" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L205" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M205" t="s">
-        <v>178</v>
+        <v>24</v>
       </c>
       <c r="N205" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="P205" s="2">
         <v>46023</v>
@@ -12531,7 +12519,7 @@
         <v>24</v>
       </c>
       <c r="N206" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P206" s="2">
         <v>46023</v>
@@ -12582,7 +12570,7 @@
         <v>24</v>
       </c>
       <c r="N207" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P207" s="2">
         <v>46023</v>
@@ -12633,7 +12621,7 @@
         <v>24</v>
       </c>
       <c r="N208" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P208" s="2">
         <v>46023</v>
@@ -12684,7 +12672,7 @@
         <v>24</v>
       </c>
       <c r="N209" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P209" s="2">
         <v>46023</v>
@@ -12735,7 +12723,7 @@
         <v>24</v>
       </c>
       <c r="N210" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P210" s="2">
         <v>46023</v>
@@ -12786,7 +12774,7 @@
         <v>24</v>
       </c>
       <c r="N211" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P211" s="2">
         <v>46023</v>
@@ -12837,7 +12825,7 @@
         <v>24</v>
       </c>
       <c r="N212" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P212" s="2">
         <v>46023</v>
@@ -12888,7 +12876,7 @@
         <v>24</v>
       </c>
       <c r="N213" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P213" s="2">
         <v>46023</v>
@@ -12902,11 +12890,11 @@
         <v>267</v>
       </c>
       <c r="B214" s="2">
-        <v>46316</v>
+        <v>46300</v>
       </c>
       <c r="C214">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-17</v>
       </c>
       <c r="D214" t="s">
         <v>184</v>
@@ -12939,7 +12927,7 @@
         <v>24</v>
       </c>
       <c r="N214" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P214" s="2">
         <v>46023</v>
@@ -12953,11 +12941,11 @@
         <v>268</v>
       </c>
       <c r="B215" s="2">
-        <v>46316</v>
+        <v>46312</v>
       </c>
       <c r="C215">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="D215" t="s">
         <v>184</v>
@@ -12978,19 +12966,19 @@
         <v>184</v>
       </c>
       <c r="J215" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="K215" t="s">
         <v>33</v>
       </c>
       <c r="L215" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M215" t="s">
-        <v>24</v>
+        <v>178</v>
       </c>
       <c r="N215" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="P215" s="2">
         <v>46023</v>
@@ -13004,11 +12992,11 @@
         <v>269</v>
       </c>
       <c r="B216" s="2">
-        <v>46300</v>
+        <v>46316</v>
       </c>
       <c r="C216">
         <f t="shared" ca="1" si="3"/>
-        <v>-17</v>
+        <v>-1</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
@@ -13029,19 +13017,19 @@
         <v>184</v>
       </c>
       <c r="J216" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="K216" t="s">
         <v>33</v>
       </c>
       <c r="L216" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M216" t="s">
-        <v>24</v>
+        <v>178</v>
       </c>
       <c r="N216" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="P216" s="2">
         <v>46023</v>
@@ -13055,11 +13043,11 @@
         <v>270</v>
       </c>
       <c r="B217" s="2">
-        <v>46312</v>
+        <v>46303</v>
       </c>
       <c r="C217">
         <f t="shared" ca="1" si="3"/>
-        <v>-5</v>
+        <v>-14</v>
       </c>
       <c r="D217" t="s">
         <v>184</v>
@@ -13092,7 +13080,7 @@
         <v>178</v>
       </c>
       <c r="N217" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="P217" s="2">
         <v>46023</v>
@@ -13106,11 +13094,11 @@
         <v>271</v>
       </c>
       <c r="B218" s="2">
-        <v>46316</v>
+        <v>46285</v>
       </c>
       <c r="C218">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-32</v>
       </c>
       <c r="D218" t="s">
         <v>184</v>
@@ -13143,7 +13131,7 @@
         <v>178</v>
       </c>
       <c r="N218" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="P218" s="2">
         <v>46023</v>
@@ -13157,11 +13145,11 @@
         <v>272</v>
       </c>
       <c r="B219" s="2">
-        <v>46303</v>
+        <v>46316</v>
       </c>
       <c r="C219">
         <f t="shared" ca="1" si="3"/>
-        <v>-14</v>
+        <v>-1</v>
       </c>
       <c r="D219" t="s">
         <v>184</v>
@@ -13194,7 +13182,7 @@
         <v>178</v>
       </c>
       <c r="N219" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="P219" s="2">
         <v>46023</v>
@@ -13208,11 +13196,11 @@
         <v>273</v>
       </c>
       <c r="B220" s="2">
-        <v>46285</v>
+        <v>46307</v>
       </c>
       <c r="C220">
         <f t="shared" ca="1" si="3"/>
-        <v>-32</v>
+        <v>-10</v>
       </c>
       <c r="D220" t="s">
         <v>184</v>
@@ -13245,7 +13233,7 @@
         <v>178</v>
       </c>
       <c r="N220" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="P220" s="2">
         <v>46023</v>
@@ -13296,7 +13284,7 @@
         <v>178</v>
       </c>
       <c r="N221" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P221" s="2">
         <v>46023</v>
@@ -13310,11 +13298,11 @@
         <v>275</v>
       </c>
       <c r="B222" s="2">
-        <v>46307</v>
+        <v>46316</v>
       </c>
       <c r="C222">
         <f t="shared" ca="1" si="3"/>
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="D222" t="s">
         <v>184</v>
@@ -13347,7 +13335,7 @@
         <v>178</v>
       </c>
       <c r="N222" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P222" s="2">
         <v>46023</v>
@@ -13386,19 +13374,19 @@
         <v>184</v>
       </c>
       <c r="J223" t="s">
-        <v>118</v>
+        <v>461</v>
       </c>
       <c r="K223" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L223" t="s">
         <v>12</v>
       </c>
       <c r="M223" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="N223" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P223" s="2">
         <v>46023</v>
@@ -13437,10 +13425,10 @@
         <v>184</v>
       </c>
       <c r="J224" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="K224" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L224" t="s">
         <v>12</v>
@@ -13449,7 +13437,7 @@
         <v>178</v>
       </c>
       <c r="N224" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P224" s="2">
         <v>46023</v>
@@ -13488,7 +13476,7 @@
         <v>184</v>
       </c>
       <c r="J225" t="s">
-        <v>464</v>
+        <v>10</v>
       </c>
       <c r="K225" t="s">
         <v>11</v>
@@ -13497,10 +13485,10 @@
         <v>12</v>
       </c>
       <c r="M225" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="N225" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="P225" s="2">
         <v>46023</v>
@@ -13514,11 +13502,11 @@
         <v>279</v>
       </c>
       <c r="B226" s="2">
-        <v>46316</v>
+        <v>46292</v>
       </c>
       <c r="C226">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-25</v>
       </c>
       <c r="D226" t="s">
         <v>184</v>
@@ -13551,7 +13539,7 @@
         <v>178</v>
       </c>
       <c r="N226" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P226" s="2">
         <v>46023</v>
@@ -13602,7 +13590,7 @@
         <v>178</v>
       </c>
       <c r="N227" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P227" s="2">
         <v>46023</v>
@@ -13616,11 +13604,11 @@
         <v>281</v>
       </c>
       <c r="B228" s="2">
-        <v>46292</v>
+        <v>46316</v>
       </c>
       <c r="C228">
         <f t="shared" ca="1" si="3"/>
-        <v>-25</v>
+        <v>-1</v>
       </c>
       <c r="D228" t="s">
         <v>184</v>
@@ -13653,7 +13641,7 @@
         <v>178</v>
       </c>
       <c r="N228" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="P228" s="2">
         <v>46023</v>
@@ -13704,7 +13692,7 @@
         <v>178</v>
       </c>
       <c r="N229" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="P229" s="2">
         <v>46023</v>
@@ -13718,11 +13706,11 @@
         <v>283</v>
       </c>
       <c r="B230" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C230">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D230" t="s">
         <v>184</v>
@@ -13755,7 +13743,7 @@
         <v>178</v>
       </c>
       <c r="N230" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P230" s="2">
         <v>46023</v>
@@ -13806,7 +13794,7 @@
         <v>178</v>
       </c>
       <c r="N231" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P231" s="2">
         <v>46023</v>
@@ -13820,11 +13808,11 @@
         <v>285</v>
       </c>
       <c r="B232" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C232">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D232" t="s">
         <v>184</v>
@@ -13857,7 +13845,7 @@
         <v>178</v>
       </c>
       <c r="N232" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P232" s="2">
         <v>46023</v>
@@ -13908,7 +13896,7 @@
         <v>178</v>
       </c>
       <c r="N233" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P233" s="2">
         <v>46023</v>
@@ -13959,7 +13947,7 @@
         <v>178</v>
       </c>
       <c r="N234" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P234" s="2">
         <v>46023</v>
@@ -13973,11 +13961,11 @@
         <v>288</v>
       </c>
       <c r="B235" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C235">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D235" t="s">
         <v>184</v>
@@ -14010,7 +13998,7 @@
         <v>178</v>
       </c>
       <c r="N235" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P235" s="2">
         <v>46023</v>
@@ -14061,7 +14049,7 @@
         <v>178</v>
       </c>
       <c r="N236" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P236" s="2">
         <v>46023</v>
@@ -14075,11 +14063,11 @@
         <v>290</v>
       </c>
       <c r="B237" s="2">
-        <v>46315</v>
+        <v>46301</v>
       </c>
       <c r="C237">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="D237" t="s">
         <v>184</v>
@@ -14112,7 +14100,7 @@
         <v>178</v>
       </c>
       <c r="N237" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P237" s="2">
         <v>46023</v>
@@ -14163,7 +14151,7 @@
         <v>178</v>
       </c>
       <c r="N238" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P238" s="2">
         <v>46023</v>
@@ -14177,11 +14165,11 @@
         <v>292</v>
       </c>
       <c r="B239" s="2">
-        <v>46301</v>
+        <v>46316</v>
       </c>
       <c r="C239">
         <f t="shared" ca="1" si="3"/>
-        <v>-16</v>
+        <v>-1</v>
       </c>
       <c r="D239" t="s">
         <v>184</v>
@@ -14214,7 +14202,7 @@
         <v>178</v>
       </c>
       <c r="N239" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P239" s="2">
         <v>46023</v>
@@ -14262,10 +14250,10 @@
         <v>12</v>
       </c>
       <c r="M240" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="N240" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P240" s="2">
         <v>46023</v>
@@ -14313,10 +14301,10 @@
         <v>12</v>
       </c>
       <c r="M241" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="N241" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P241" s="2">
         <v>46023</v>
@@ -14364,10 +14352,10 @@
         <v>12</v>
       </c>
       <c r="M242" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="N242" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="P242" s="2">
         <v>46023</v>
@@ -14406,7 +14394,7 @@
         <v>184</v>
       </c>
       <c r="J243" t="s">
-        <v>10</v>
+        <v>461</v>
       </c>
       <c r="K243" t="s">
         <v>11</v>
@@ -14418,7 +14406,7 @@
         <v>119</v>
       </c>
       <c r="N243" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P243" s="2">
         <v>46023</v>
@@ -14457,7 +14445,7 @@
         <v>184</v>
       </c>
       <c r="J244" t="s">
-        <v>10</v>
+        <v>460</v>
       </c>
       <c r="K244" t="s">
         <v>11</v>
@@ -14466,10 +14454,10 @@
         <v>12</v>
       </c>
       <c r="M244" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="N244" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P244" s="2">
         <v>46023</v>
@@ -14508,7 +14496,7 @@
         <v>184</v>
       </c>
       <c r="J245" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K245" t="s">
         <v>11</v>
@@ -14517,10 +14505,10 @@
         <v>12</v>
       </c>
       <c r="M245" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="N245" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="P245" s="2">
         <v>46023</v>
@@ -14534,11 +14522,11 @@
         <v>299</v>
       </c>
       <c r="B246" s="2">
-        <v>46316</v>
+        <v>46282</v>
       </c>
       <c r="C246">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-35</v>
       </c>
       <c r="D246" t="s">
         <v>184</v>
@@ -14559,7 +14547,7 @@
         <v>184</v>
       </c>
       <c r="J246" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K246" t="s">
         <v>11</v>
@@ -14568,10 +14556,10 @@
         <v>12</v>
       </c>
       <c r="M246" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="N246" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="P246" s="2">
         <v>46023</v>
@@ -14610,7 +14598,7 @@
         <v>184</v>
       </c>
       <c r="J247" t="s">
-        <v>465</v>
+        <v>28</v>
       </c>
       <c r="K247" t="s">
         <v>11</v>
@@ -14622,7 +14610,7 @@
         <v>178</v>
       </c>
       <c r="N247" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P247" s="2">
         <v>46023</v>
@@ -14636,11 +14624,11 @@
         <v>301</v>
       </c>
       <c r="B248" s="2">
-        <v>46282</v>
+        <v>46316</v>
       </c>
       <c r="C248">
         <f t="shared" ca="1" si="3"/>
-        <v>-35</v>
+        <v>-1</v>
       </c>
       <c r="D248" t="s">
         <v>184</v>
@@ -14661,19 +14649,19 @@
         <v>184</v>
       </c>
       <c r="J248" t="s">
-        <v>465</v>
+        <v>22</v>
       </c>
       <c r="K248" t="s">
         <v>11</v>
       </c>
       <c r="L248" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M248" t="s">
-        <v>178</v>
+        <v>463</v>
       </c>
       <c r="N248" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="P248" s="2">
         <v>46023</v>
@@ -14712,19 +14700,19 @@
         <v>184</v>
       </c>
       <c r="J249" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K249" t="s">
         <v>11</v>
       </c>
       <c r="L249" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M249" t="s">
-        <v>178</v>
+        <v>463</v>
       </c>
       <c r="N249" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P249" s="2">
         <v>46023</v>
@@ -14772,10 +14760,10 @@
         <v>23</v>
       </c>
       <c r="M250" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N250" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P250" s="2">
         <v>46023</v>
@@ -14823,10 +14811,10 @@
         <v>23</v>
       </c>
       <c r="M251" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N251" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P251" s="2">
         <v>46023</v>
@@ -14840,11 +14828,11 @@
         <v>305</v>
       </c>
       <c r="B252" s="2">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="C252">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D252" t="s">
         <v>184</v>
@@ -14874,10 +14862,10 @@
         <v>23</v>
       </c>
       <c r="M252" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N252" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P252" s="2">
         <v>46023</v>
@@ -14891,11 +14879,11 @@
         <v>306</v>
       </c>
       <c r="B253" s="2">
-        <v>46316</v>
+        <v>46301</v>
       </c>
       <c r="C253">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-16</v>
       </c>
       <c r="D253" t="s">
         <v>184</v>
@@ -14925,10 +14913,10 @@
         <v>23</v>
       </c>
       <c r="M253" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N253" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P253" s="2">
         <v>46023</v>
@@ -14942,11 +14930,11 @@
         <v>307</v>
       </c>
       <c r="B254" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C254">
         <f t="shared" ca="1" si="3"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="D254" t="s">
         <v>184</v>
@@ -14976,10 +14964,10 @@
         <v>23</v>
       </c>
       <c r="M254" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N254" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P254" s="2">
         <v>46023</v>
@@ -14993,11 +14981,11 @@
         <v>308</v>
       </c>
       <c r="B255" s="2">
-        <v>46301</v>
+        <v>46207</v>
       </c>
       <c r="C255">
-        <f t="shared" ca="1" si="3"/>
-        <v>-16</v>
+        <f t="shared" ref="C255:C318" ca="1" si="4">B255-$R$1</f>
+        <v>-110</v>
       </c>
       <c r="D255" t="s">
         <v>184</v>
@@ -15027,10 +15015,10 @@
         <v>23</v>
       </c>
       <c r="M255" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N255" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P255" s="2">
         <v>46023</v>
@@ -15044,11 +15032,11 @@
         <v>309</v>
       </c>
       <c r="B256" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C256">
-        <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-1</v>
       </c>
       <c r="D256" t="s">
         <v>184</v>
@@ -15078,10 +15066,10 @@
         <v>23</v>
       </c>
       <c r="M256" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N256" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P256" s="2">
         <v>46023</v>
@@ -15095,11 +15083,11 @@
         <v>310</v>
       </c>
       <c r="B257" s="2">
-        <v>46207</v>
+        <v>46316</v>
       </c>
       <c r="C257">
-        <f t="shared" ref="C257:C320" ca="1" si="4">B257-$R$1</f>
-        <v>-110</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-1</v>
       </c>
       <c r="D257" t="s">
         <v>184</v>
@@ -15129,10 +15117,10 @@
         <v>23</v>
       </c>
       <c r="M257" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N257" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P257" s="2">
         <v>46023</v>
@@ -15180,10 +15168,10 @@
         <v>23</v>
       </c>
       <c r="M258" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N258" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="P258" s="2">
         <v>46023</v>
@@ -15231,10 +15219,10 @@
         <v>23</v>
       </c>
       <c r="M259" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N259" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="P259" s="2">
         <v>46023</v>
@@ -15248,11 +15236,11 @@
         <v>313</v>
       </c>
       <c r="B260" s="2">
-        <v>46316</v>
+        <v>46297</v>
       </c>
       <c r="C260">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-20</v>
       </c>
       <c r="D260" t="s">
         <v>184</v>
@@ -15282,10 +15270,10 @@
         <v>23</v>
       </c>
       <c r="M260" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N260" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="P260" s="2">
         <v>46023</v>
@@ -15333,10 +15321,10 @@
         <v>23</v>
       </c>
       <c r="M261" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N261" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="P261" s="2">
         <v>46023</v>
@@ -15350,11 +15338,11 @@
         <v>315</v>
       </c>
       <c r="B262" s="2">
-        <v>46297</v>
+        <v>46316</v>
       </c>
       <c r="C262">
         <f t="shared" ca="1" si="4"/>
-        <v>-20</v>
+        <v>-1</v>
       </c>
       <c r="D262" t="s">
         <v>184</v>
@@ -15384,10 +15372,10 @@
         <v>23</v>
       </c>
       <c r="M262" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N262" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="P262" s="2">
         <v>46023</v>
@@ -15435,10 +15423,10 @@
         <v>23</v>
       </c>
       <c r="M263" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N263" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="P263" s="2">
         <v>46023</v>
@@ -15452,11 +15440,11 @@
         <v>317</v>
       </c>
       <c r="B264" s="2">
-        <v>46316</v>
+        <v>46302</v>
       </c>
       <c r="C264">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-15</v>
       </c>
       <c r="D264" t="s">
         <v>184</v>
@@ -15486,10 +15474,10 @@
         <v>23</v>
       </c>
       <c r="M264" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="N264" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="P264" s="2">
         <v>46023</v>
@@ -15503,11 +15491,11 @@
         <v>318</v>
       </c>
       <c r="B265" s="2">
-        <v>46316</v>
+        <v>46177</v>
       </c>
       <c r="C265">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-140</v>
       </c>
       <c r="D265" t="s">
         <v>184</v>
@@ -15537,10 +15525,10 @@
         <v>23</v>
       </c>
       <c r="M265" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="N265" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="P265" s="2">
         <v>46023</v>
@@ -15554,11 +15542,11 @@
         <v>319</v>
       </c>
       <c r="B266" s="2">
-        <v>46302</v>
+        <v>46316</v>
       </c>
       <c r="C266">
         <f t="shared" ca="1" si="4"/>
-        <v>-15</v>
+        <v>-1</v>
       </c>
       <c r="D266" t="s">
         <v>184</v>
@@ -15588,10 +15576,10 @@
         <v>23</v>
       </c>
       <c r="M266" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="N266" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="P266" s="2">
         <v>46023</v>
@@ -15605,11 +15593,11 @@
         <v>320</v>
       </c>
       <c r="B267" s="2">
-        <v>46177</v>
+        <v>46299</v>
       </c>
       <c r="C267">
         <f t="shared" ca="1" si="4"/>
-        <v>-140</v>
+        <v>-18</v>
       </c>
       <c r="D267" t="s">
         <v>184</v>
@@ -15639,10 +15627,10 @@
         <v>23</v>
       </c>
       <c r="M267" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="N267" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="P267" s="2">
         <v>46023</v>
@@ -15690,10 +15678,10 @@
         <v>23</v>
       </c>
       <c r="M268" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="N268" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="P268" s="2">
         <v>46023</v>
@@ -15707,11 +15695,11 @@
         <v>322</v>
       </c>
       <c r="B269" s="2">
-        <v>46299</v>
+        <v>46316</v>
       </c>
       <c r="C269">
         <f t="shared" ca="1" si="4"/>
-        <v>-18</v>
+        <v>-1</v>
       </c>
       <c r="D269" t="s">
         <v>184</v>
@@ -15732,19 +15720,19 @@
         <v>184</v>
       </c>
       <c r="J269" t="s">
-        <v>22</v>
+        <v>225</v>
       </c>
       <c r="K269" t="s">
         <v>11</v>
       </c>
       <c r="L269" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M269" t="s">
-        <v>459</v>
+        <v>119</v>
       </c>
       <c r="N269" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="P269" s="2">
         <v>46023</v>
@@ -15783,19 +15771,19 @@
         <v>184</v>
       </c>
       <c r="J270" t="s">
-        <v>22</v>
+        <v>225</v>
       </c>
       <c r="K270" t="s">
         <v>11</v>
       </c>
       <c r="L270" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M270" t="s">
-        <v>459</v>
+        <v>119</v>
       </c>
       <c r="N270" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="P270" s="2">
         <v>46023</v>
@@ -15846,7 +15834,7 @@
         <v>119</v>
       </c>
       <c r="N271" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P271" s="2">
         <v>46023</v>
@@ -15860,11 +15848,11 @@
         <v>325</v>
       </c>
       <c r="B272" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C272">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D272" t="s">
         <v>184</v>
@@ -15897,7 +15885,7 @@
         <v>119</v>
       </c>
       <c r="N272" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P272" s="2">
         <v>46023</v>
@@ -15948,7 +15936,7 @@
         <v>119</v>
       </c>
       <c r="N273" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P273" s="2">
         <v>46023</v>
@@ -15962,11 +15950,11 @@
         <v>327</v>
       </c>
       <c r="B274" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C274">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D274" t="s">
         <v>184</v>
@@ -15999,7 +15987,7 @@
         <v>119</v>
       </c>
       <c r="N274" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P274" s="2">
         <v>46023</v>
@@ -16050,7 +16038,7 @@
         <v>119</v>
       </c>
       <c r="N275" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P275" s="2">
         <v>46023</v>
@@ -16101,7 +16089,7 @@
         <v>119</v>
       </c>
       <c r="N276" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P276" s="2">
         <v>46023</v>
@@ -16115,11 +16103,11 @@
         <v>330</v>
       </c>
       <c r="B277" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C277">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D277" t="s">
         <v>184</v>
@@ -16152,7 +16140,7 @@
         <v>119</v>
       </c>
       <c r="N277" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P277" s="2">
         <v>46023</v>
@@ -16191,19 +16179,19 @@
         <v>184</v>
       </c>
       <c r="J278" t="s">
-        <v>225</v>
+        <v>32</v>
       </c>
       <c r="K278" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L278" t="s">
         <v>29</v>
       </c>
       <c r="M278" t="s">
-        <v>119</v>
+        <v>463</v>
       </c>
       <c r="N278" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P278" s="2">
         <v>46023</v>
@@ -16217,11 +16205,11 @@
         <v>332</v>
       </c>
       <c r="B279" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C279">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D279" t="s">
         <v>184</v>
@@ -16242,19 +16230,19 @@
         <v>184</v>
       </c>
       <c r="J279" t="s">
-        <v>225</v>
+        <v>32</v>
       </c>
       <c r="K279" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L279" t="s">
         <v>29</v>
       </c>
       <c r="M279" t="s">
-        <v>119</v>
+        <v>463</v>
       </c>
       <c r="N279" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P279" s="2">
         <v>46023</v>
@@ -16268,11 +16256,11 @@
         <v>333</v>
       </c>
       <c r="B280" s="2">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="C280">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D280" t="s">
         <v>184</v>
@@ -16302,10 +16290,10 @@
         <v>29</v>
       </c>
       <c r="M280" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N280" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P280" s="2">
         <v>46023</v>
@@ -16353,10 +16341,10 @@
         <v>29</v>
       </c>
       <c r="M281" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N281" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P281" s="2">
         <v>46023</v>
@@ -16370,11 +16358,11 @@
         <v>335</v>
       </c>
       <c r="B282" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C282">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D282" t="s">
         <v>184</v>
@@ -16404,10 +16392,10 @@
         <v>29</v>
       </c>
       <c r="M282" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N282" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P282" s="2">
         <v>46023</v>
@@ -16421,11 +16409,11 @@
         <v>336</v>
       </c>
       <c r="B283" s="2">
-        <v>46316</v>
+        <v>46313</v>
       </c>
       <c r="C283">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="D283" t="s">
         <v>184</v>
@@ -16455,10 +16443,10 @@
         <v>29</v>
       </c>
       <c r="M283" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N283" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P283" s="2">
         <v>46023</v>
@@ -16506,10 +16494,10 @@
         <v>29</v>
       </c>
       <c r="M284" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N284" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P284" s="2">
         <v>46023</v>
@@ -16523,11 +16511,11 @@
         <v>338</v>
       </c>
       <c r="B285" s="2">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C285">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="D285" t="s">
         <v>184</v>
@@ -16557,10 +16545,10 @@
         <v>29</v>
       </c>
       <c r="M285" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N285" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P285" s="2">
         <v>46023</v>
@@ -16574,11 +16562,11 @@
         <v>339</v>
       </c>
       <c r="B286" s="2">
-        <v>46316</v>
+        <v>46091</v>
       </c>
       <c r="C286">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-226</v>
       </c>
       <c r="D286" t="s">
         <v>184</v>
@@ -16608,10 +16596,10 @@
         <v>29</v>
       </c>
       <c r="M286" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N286" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P286" s="2">
         <v>46023</v>
@@ -16625,11 +16613,11 @@
         <v>340</v>
       </c>
       <c r="B287" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C287">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D287" t="s">
         <v>184</v>
@@ -16659,10 +16647,10 @@
         <v>29</v>
       </c>
       <c r="M287" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N287" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P287" s="2">
         <v>46023</v>
@@ -16676,11 +16664,11 @@
         <v>341</v>
       </c>
       <c r="B288" s="2">
-        <v>46091</v>
+        <v>46316</v>
       </c>
       <c r="C288">
         <f t="shared" ca="1" si="4"/>
-        <v>-226</v>
+        <v>-1</v>
       </c>
       <c r="D288" t="s">
         <v>184</v>
@@ -16710,10 +16698,10 @@
         <v>29</v>
       </c>
       <c r="M288" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N288" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P288" s="2">
         <v>46023</v>
@@ -16752,7 +16740,7 @@
         <v>184</v>
       </c>
       <c r="J289" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="K289" t="s">
         <v>33</v>
@@ -16761,10 +16749,10 @@
         <v>29</v>
       </c>
       <c r="M289" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N289" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P289" s="2">
         <v>46023</v>
@@ -16803,7 +16791,7 @@
         <v>184</v>
       </c>
       <c r="J290" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="K290" t="s">
         <v>33</v>
@@ -16812,10 +16800,10 @@
         <v>29</v>
       </c>
       <c r="M290" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N290" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P290" s="2">
         <v>46023</v>
@@ -16863,10 +16851,10 @@
         <v>29</v>
       </c>
       <c r="M291" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N291" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P291" s="2">
         <v>46023</v>
@@ -16914,10 +16902,10 @@
         <v>29</v>
       </c>
       <c r="M292" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N292" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P292" s="2">
         <v>46023</v>
@@ -16965,10 +16953,10 @@
         <v>29</v>
       </c>
       <c r="M293" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N293" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P293" s="2">
         <v>46023</v>
@@ -17016,10 +17004,10 @@
         <v>29</v>
       </c>
       <c r="M294" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N294" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P294" s="2">
         <v>46023</v>
@@ -17033,11 +17021,11 @@
         <v>348</v>
       </c>
       <c r="B295" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C295">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D295" t="s">
         <v>184</v>
@@ -17067,10 +17055,10 @@
         <v>29</v>
       </c>
       <c r="M295" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N295" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P295" s="2">
         <v>46023</v>
@@ -17118,10 +17106,10 @@
         <v>29</v>
       </c>
       <c r="M296" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N296" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P296" s="2">
         <v>46023</v>
@@ -17135,11 +17123,11 @@
         <v>350</v>
       </c>
       <c r="B297" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C297">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D297" t="s">
         <v>184</v>
@@ -17169,10 +17157,10 @@
         <v>29</v>
       </c>
       <c r="M297" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N297" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P297" s="2">
         <v>46023</v>
@@ -17220,10 +17208,10 @@
         <v>29</v>
       </c>
       <c r="M298" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N298" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P298" s="2">
         <v>46023</v>
@@ -17271,10 +17259,10 @@
         <v>29</v>
       </c>
       <c r="M299" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N299" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P299" s="2">
         <v>46023</v>
@@ -17322,10 +17310,10 @@
         <v>29</v>
       </c>
       <c r="M300" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N300" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P300" s="2">
         <v>46023</v>
@@ -17370,13 +17358,13 @@
         <v>33</v>
       </c>
       <c r="L301" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M301" t="s">
-        <v>466</v>
+        <v>119</v>
       </c>
       <c r="N301" t="s">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="P301" s="2">
         <v>46023</v>
@@ -17421,13 +17409,13 @@
         <v>33</v>
       </c>
       <c r="L302" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M302" t="s">
-        <v>466</v>
+        <v>119</v>
       </c>
       <c r="N302" t="s">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="P302" s="2">
         <v>46023</v>
@@ -17625,13 +17613,13 @@
         <v>33</v>
       </c>
       <c r="L306" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M306" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="N306" t="s">
-        <v>120</v>
+        <v>449</v>
       </c>
       <c r="P306" s="2">
         <v>46023</v>
@@ -17645,11 +17633,11 @@
         <v>360</v>
       </c>
       <c r="B307" s="2">
-        <v>46316</v>
+        <v>46302</v>
       </c>
       <c r="C307">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-15</v>
       </c>
       <c r="D307" t="s">
         <v>184</v>
@@ -17676,13 +17664,13 @@
         <v>33</v>
       </c>
       <c r="L307" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M307" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="N307" t="s">
-        <v>120</v>
+        <v>449</v>
       </c>
       <c r="P307" s="2">
         <v>46023</v>
@@ -17733,7 +17721,7 @@
         <v>24</v>
       </c>
       <c r="N308" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P308" s="2">
         <v>46023</v>
@@ -17747,11 +17735,11 @@
         <v>362</v>
       </c>
       <c r="B309" s="2">
-        <v>46302</v>
+        <v>46316</v>
       </c>
       <c r="C309">
         <f t="shared" ca="1" si="4"/>
-        <v>-15</v>
+        <v>-1</v>
       </c>
       <c r="D309" t="s">
         <v>184</v>
@@ -17784,7 +17772,7 @@
         <v>24</v>
       </c>
       <c r="N309" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P309" s="2">
         <v>46023</v>
@@ -17835,7 +17823,7 @@
         <v>24</v>
       </c>
       <c r="N310" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P310" s="2">
         <v>46023</v>
@@ -17886,7 +17874,7 @@
         <v>24</v>
       </c>
       <c r="N311" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P311" s="2">
         <v>46023</v>
@@ -17931,13 +17919,13 @@
         <v>33</v>
       </c>
       <c r="L312" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="M312" t="s">
         <v>24</v>
       </c>
       <c r="N312" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="P312" s="2">
         <v>46023</v>
@@ -17951,11 +17939,11 @@
         <v>366</v>
       </c>
       <c r="B313" s="2">
-        <v>46316</v>
+        <v>46309</v>
       </c>
       <c r="C313">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="D313" t="s">
         <v>184</v>
@@ -17982,13 +17970,13 @@
         <v>33</v>
       </c>
       <c r="L313" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="M313" t="s">
         <v>24</v>
       </c>
       <c r="N313" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="P313" s="2">
         <v>46023</v>
@@ -18039,7 +18027,7 @@
         <v>24</v>
       </c>
       <c r="N314" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P314" s="2">
         <v>46023</v>
@@ -18053,11 +18041,11 @@
         <v>368</v>
       </c>
       <c r="B315" s="2">
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="C315">
         <f t="shared" ca="1" si="4"/>
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="D315" t="s">
         <v>184</v>
@@ -18084,7 +18072,7 @@
         <v>33</v>
       </c>
       <c r="L315" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M315" t="s">
         <v>24</v>
@@ -18104,11 +18092,11 @@
         <v>369</v>
       </c>
       <c r="B316" s="2">
-        <v>46316</v>
+        <v>46244</v>
       </c>
       <c r="C316">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-73</v>
       </c>
       <c r="D316" t="s">
         <v>184</v>
@@ -18135,7 +18123,7 @@
         <v>33</v>
       </c>
       <c r="L316" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M316" t="s">
         <v>24</v>
@@ -18180,19 +18168,19 @@
         <v>184</v>
       </c>
       <c r="J317" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="K317" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L317" t="s">
         <v>12</v>
       </c>
       <c r="M317" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="N317" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P317" s="2">
         <v>46023</v>
@@ -18206,11 +18194,11 @@
         <v>371</v>
       </c>
       <c r="B318" s="2">
-        <v>46244</v>
+        <v>46306</v>
       </c>
       <c r="C318">
         <f t="shared" ca="1" si="4"/>
-        <v>-73</v>
+        <v>-11</v>
       </c>
       <c r="D318" t="s">
         <v>184</v>
@@ -18231,19 +18219,19 @@
         <v>184</v>
       </c>
       <c r="J318" t="s">
-        <v>118</v>
+        <v>461</v>
       </c>
       <c r="K318" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L318" t="s">
         <v>12</v>
       </c>
       <c r="M318" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="N318" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P318" s="2">
         <v>46023</v>
@@ -18260,7 +18248,7 @@
         <v>46316</v>
       </c>
       <c r="C319">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ref="C319:C382" ca="1" si="5">B319-$R$1</f>
         <v>-1</v>
       </c>
       <c r="D319" t="s">
@@ -18294,7 +18282,7 @@
         <v>119</v>
       </c>
       <c r="N319" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P319" s="2">
         <v>46023</v>
@@ -18308,11 +18296,11 @@
         <v>373</v>
       </c>
       <c r="B320" s="2">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="C320">
-        <f t="shared" ca="1" si="4"/>
-        <v>-11</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-10</v>
       </c>
       <c r="D320" t="s">
         <v>184</v>
@@ -18333,7 +18321,7 @@
         <v>184</v>
       </c>
       <c r="J320" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="K320" t="s">
         <v>11</v>
@@ -18345,7 +18333,7 @@
         <v>119</v>
       </c>
       <c r="N320" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P320" s="2">
         <v>46023</v>
@@ -18359,11 +18347,11 @@
         <v>374</v>
       </c>
       <c r="B321" s="2">
-        <v>46316</v>
+        <v>46240</v>
       </c>
       <c r="C321">
-        <f t="shared" ref="C321:C384" ca="1" si="5">B321-$R$1</f>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-77</v>
       </c>
       <c r="D321" t="s">
         <v>184</v>
@@ -18384,7 +18372,7 @@
         <v>184</v>
       </c>
       <c r="J321" t="s">
-        <v>45</v>
+        <v>461</v>
       </c>
       <c r="K321" t="s">
         <v>11</v>
@@ -18396,7 +18384,7 @@
         <v>119</v>
       </c>
       <c r="N321" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P321" s="2">
         <v>46023</v>
@@ -18410,11 +18398,11 @@
         <v>375</v>
       </c>
       <c r="B322" s="2">
-        <v>46307</v>
+        <v>46298</v>
       </c>
       <c r="C322">
         <f t="shared" ca="1" si="5"/>
-        <v>-10</v>
+        <v>-19</v>
       </c>
       <c r="D322" t="s">
         <v>184</v>
@@ -18435,7 +18423,7 @@
         <v>184</v>
       </c>
       <c r="J322" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="K322" t="s">
         <v>11</v>
@@ -18447,7 +18435,7 @@
         <v>119</v>
       </c>
       <c r="N322" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P322" s="2">
         <v>46023</v>
@@ -18461,11 +18449,11 @@
         <v>376</v>
       </c>
       <c r="B323" s="2">
-        <v>46240</v>
+        <v>46316</v>
       </c>
       <c r="C323">
         <f t="shared" ca="1" si="5"/>
-        <v>-77</v>
+        <v>-1</v>
       </c>
       <c r="D323" t="s">
         <v>184</v>
@@ -18486,7 +18474,7 @@
         <v>184</v>
       </c>
       <c r="J323" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="K323" t="s">
         <v>11</v>
@@ -18498,7 +18486,7 @@
         <v>119</v>
       </c>
       <c r="N323" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P323" s="2">
         <v>46023</v>
@@ -18512,11 +18500,11 @@
         <v>377</v>
       </c>
       <c r="B324" s="2">
-        <v>46298</v>
+        <v>46316</v>
       </c>
       <c r="C324">
         <f t="shared" ca="1" si="5"/>
-        <v>-19</v>
+        <v>-1</v>
       </c>
       <c r="D324" t="s">
         <v>184</v>
@@ -18537,7 +18525,7 @@
         <v>184</v>
       </c>
       <c r="J324" t="s">
-        <v>464</v>
+        <v>45</v>
       </c>
       <c r="K324" t="s">
         <v>11</v>
@@ -18549,7 +18537,7 @@
         <v>119</v>
       </c>
       <c r="N324" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P324" s="2">
         <v>46023</v>
@@ -18588,7 +18576,7 @@
         <v>184</v>
       </c>
       <c r="J325" t="s">
-        <v>464</v>
+        <v>45</v>
       </c>
       <c r="K325" t="s">
         <v>11</v>
@@ -18600,7 +18588,7 @@
         <v>119</v>
       </c>
       <c r="N325" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P325" s="2">
         <v>46023</v>
@@ -18651,7 +18639,7 @@
         <v>119</v>
       </c>
       <c r="N326" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P326" s="2">
         <v>46023</v>
@@ -18665,11 +18653,11 @@
         <v>380</v>
       </c>
       <c r="B327" s="2">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="C327">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D327" t="s">
         <v>184</v>
@@ -18690,7 +18678,7 @@
         <v>184</v>
       </c>
       <c r="J327" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="K327" t="s">
         <v>11</v>
@@ -18699,10 +18687,10 @@
         <v>12</v>
       </c>
       <c r="M327" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="N327" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="P327" s="2">
         <v>46023</v>
@@ -18741,7 +18729,7 @@
         <v>184</v>
       </c>
       <c r="J328" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="K328" t="s">
         <v>11</v>
@@ -18750,10 +18738,10 @@
         <v>12</v>
       </c>
       <c r="M328" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="N328" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="P328" s="2">
         <v>46023</v>
@@ -18798,13 +18786,13 @@
         <v>11</v>
       </c>
       <c r="L329" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M329" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="N329" t="s">
-        <v>448</v>
+        <v>120</v>
       </c>
       <c r="P329" s="2">
         <v>46023</v>
@@ -18818,11 +18806,11 @@
         <v>383</v>
       </c>
       <c r="B330" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C330">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D330" t="s">
         <v>184</v>
@@ -18849,13 +18837,13 @@
         <v>11</v>
       </c>
       <c r="L330" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M330" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="N330" t="s">
-        <v>448</v>
+        <v>120</v>
       </c>
       <c r="P330" s="2">
         <v>46023</v>
@@ -18869,11 +18857,11 @@
         <v>384</v>
       </c>
       <c r="B331" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C331">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D331" t="s">
         <v>184</v>
@@ -18920,11 +18908,11 @@
         <v>385</v>
       </c>
       <c r="B332" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C332">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D332" t="s">
         <v>184</v>
@@ -18971,11 +18959,11 @@
         <v>386</v>
       </c>
       <c r="B333" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C333">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D333" t="s">
         <v>184</v>
@@ -19175,11 +19163,11 @@
         <v>390</v>
       </c>
       <c r="B337" s="2">
-        <v>46315</v>
+        <v>46307</v>
       </c>
       <c r="C337">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="D337" t="s">
         <v>184</v>
@@ -19277,11 +19265,11 @@
         <v>392</v>
       </c>
       <c r="B339" s="2">
-        <v>46307</v>
+        <v>46316</v>
       </c>
       <c r="C339">
         <f t="shared" ca="1" si="5"/>
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="D339" t="s">
         <v>184</v>
@@ -19353,19 +19341,19 @@
         <v>184</v>
       </c>
       <c r="J340" t="s">
-        <v>10</v>
+        <v>460</v>
       </c>
       <c r="K340" t="s">
         <v>11</v>
       </c>
       <c r="L340" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M340" t="s">
         <v>119</v>
       </c>
       <c r="N340" t="s">
-        <v>120</v>
+        <v>449</v>
       </c>
       <c r="P340" s="2">
         <v>46023</v>
@@ -19379,11 +19367,11 @@
         <v>394</v>
       </c>
       <c r="B341" s="2">
-        <v>46316</v>
+        <v>46308</v>
       </c>
       <c r="C341">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="D341" t="s">
         <v>184</v>
@@ -19404,19 +19392,19 @@
         <v>184</v>
       </c>
       <c r="J341" t="s">
-        <v>10</v>
+        <v>461</v>
       </c>
       <c r="K341" t="s">
         <v>11</v>
       </c>
       <c r="L341" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M341" t="s">
         <v>119</v>
       </c>
       <c r="N341" t="s">
-        <v>120</v>
+        <v>449</v>
       </c>
       <c r="P341" s="2">
         <v>46023</v>
@@ -19455,7 +19443,7 @@
         <v>184</v>
       </c>
       <c r="J342" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="K342" t="s">
         <v>11</v>
@@ -19467,7 +19455,7 @@
         <v>119</v>
       </c>
       <c r="N342" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P342" s="2">
         <v>46023</v>
@@ -19481,11 +19469,11 @@
         <v>396</v>
       </c>
       <c r="B343" s="2">
-        <v>46308</v>
+        <v>46316</v>
       </c>
       <c r="C343">
         <f t="shared" ca="1" si="5"/>
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="D343" t="s">
         <v>184</v>
@@ -19506,7 +19494,7 @@
         <v>184</v>
       </c>
       <c r="J343" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="K343" t="s">
         <v>11</v>
@@ -19518,7 +19506,7 @@
         <v>119</v>
       </c>
       <c r="N343" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P343" s="2">
         <v>46023</v>
@@ -19532,11 +19520,11 @@
         <v>397</v>
       </c>
       <c r="B344" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C344">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D344" t="s">
         <v>184</v>
@@ -19557,7 +19545,7 @@
         <v>184</v>
       </c>
       <c r="J344" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K344" t="s">
         <v>11</v>
@@ -19569,7 +19557,7 @@
         <v>119</v>
       </c>
       <c r="N344" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P344" s="2">
         <v>46023</v>
@@ -19608,7 +19596,7 @@
         <v>184</v>
       </c>
       <c r="J345" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K345" t="s">
         <v>11</v>
@@ -19620,7 +19608,7 @@
         <v>119</v>
       </c>
       <c r="N345" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P345" s="2">
         <v>46023</v>
@@ -19659,7 +19647,7 @@
         <v>184</v>
       </c>
       <c r="J346" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="K346" t="s">
         <v>11</v>
@@ -19671,7 +19659,7 @@
         <v>119</v>
       </c>
       <c r="N346" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P346" s="2">
         <v>46023</v>
@@ -19710,19 +19698,19 @@
         <v>184</v>
       </c>
       <c r="J347" t="s">
-        <v>464</v>
+        <v>22</v>
       </c>
       <c r="K347" t="s">
         <v>11</v>
       </c>
       <c r="L347" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M347" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="N347" t="s">
-        <v>451</v>
+        <v>120</v>
       </c>
       <c r="P347" s="2">
         <v>46023</v>
@@ -19736,11 +19724,11 @@
         <v>401</v>
       </c>
       <c r="B348" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C348">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D348" t="s">
         <v>184</v>
@@ -19761,7 +19749,7 @@
         <v>184</v>
       </c>
       <c r="J348" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="K348" t="s">
         <v>11</v>
@@ -19773,7 +19761,7 @@
         <v>119</v>
       </c>
       <c r="N348" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P348" s="2">
         <v>46023</v>
@@ -19812,19 +19800,19 @@
         <v>184</v>
       </c>
       <c r="J349" t="s">
-        <v>22</v>
+        <v>459</v>
       </c>
       <c r="K349" t="s">
         <v>11</v>
       </c>
       <c r="L349" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M349" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="N349" t="s">
-        <v>120</v>
+        <v>449</v>
       </c>
       <c r="P349" s="2">
         <v>46023</v>
@@ -19838,11 +19826,11 @@
         <v>403</v>
       </c>
       <c r="B350" s="2">
-        <v>46316</v>
+        <v>46310</v>
       </c>
       <c r="C350">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="D350" t="s">
         <v>184</v>
@@ -19863,7 +19851,7 @@
         <v>184</v>
       </c>
       <c r="J350" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="K350" t="s">
         <v>11</v>
@@ -19875,7 +19863,7 @@
         <v>119</v>
       </c>
       <c r="N350" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P350" s="2">
         <v>46023</v>
@@ -19914,19 +19902,19 @@
         <v>184</v>
       </c>
       <c r="J351" t="s">
-        <v>462</v>
+        <v>101</v>
       </c>
       <c r="K351" t="s">
         <v>11</v>
       </c>
       <c r="L351" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="M351" t="s">
         <v>119</v>
       </c>
       <c r="N351" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="P351" s="2">
         <v>46023</v>
@@ -19940,11 +19928,11 @@
         <v>405</v>
       </c>
       <c r="B352" s="2">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="C352">
         <f t="shared" ca="1" si="5"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="D352" t="s">
         <v>184</v>
@@ -19965,19 +19953,19 @@
         <v>184</v>
       </c>
       <c r="J352" t="s">
-        <v>462</v>
+        <v>28</v>
       </c>
       <c r="K352" t="s">
         <v>11</v>
       </c>
       <c r="L352" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="M352" t="s">
         <v>119</v>
       </c>
       <c r="N352" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="P352" s="2">
         <v>46023</v>
@@ -20016,7 +20004,7 @@
         <v>184</v>
       </c>
       <c r="J353" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="K353" t="s">
         <v>11</v>
@@ -20028,7 +20016,7 @@
         <v>119</v>
       </c>
       <c r="N353" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P353" s="2">
         <v>46023</v>
@@ -20067,19 +20055,19 @@
         <v>184</v>
       </c>
       <c r="J354" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="K354" t="s">
         <v>11</v>
       </c>
       <c r="L354" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M354" t="s">
         <v>119</v>
       </c>
       <c r="N354" t="s">
-        <v>449</v>
+        <v>120</v>
       </c>
       <c r="P354" s="2">
         <v>46023</v>
@@ -20093,11 +20081,11 @@
         <v>408</v>
       </c>
       <c r="B355" s="2">
-        <v>46316</v>
+        <v>46298</v>
       </c>
       <c r="C355">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-19</v>
       </c>
       <c r="D355" t="s">
         <v>184</v>
@@ -20118,19 +20106,19 @@
         <v>184</v>
       </c>
       <c r="J355" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="K355" t="s">
         <v>11</v>
       </c>
       <c r="L355" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M355" t="s">
         <v>119</v>
       </c>
       <c r="N355" t="s">
-        <v>449</v>
+        <v>120</v>
       </c>
       <c r="P355" s="2">
         <v>46023</v>
@@ -20169,7 +20157,7 @@
         <v>184</v>
       </c>
       <c r="J356" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="K356" t="s">
         <v>11</v>
@@ -20195,11 +20183,11 @@
         <v>410</v>
       </c>
       <c r="B357" s="2">
-        <v>46298</v>
+        <v>46316</v>
       </c>
       <c r="C357">
         <f t="shared" ca="1" si="5"/>
-        <v>-19</v>
+        <v>-1</v>
       </c>
       <c r="D357" t="s">
         <v>184</v>
@@ -20220,7 +20208,7 @@
         <v>184</v>
       </c>
       <c r="J357" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="K357" t="s">
         <v>11</v>
@@ -20271,7 +20259,7 @@
         <v>184</v>
       </c>
       <c r="J358" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="K358" t="s">
         <v>11</v>
@@ -20322,7 +20310,7 @@
         <v>184</v>
       </c>
       <c r="J359" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="K359" t="s">
         <v>11</v>
@@ -20348,11 +20336,11 @@
         <v>413</v>
       </c>
       <c r="B360" s="2">
-        <v>46316</v>
+        <v>46307</v>
       </c>
       <c r="C360">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="D360" t="s">
         <v>184</v>
@@ -20373,7 +20361,7 @@
         <v>184</v>
       </c>
       <c r="J360" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="K360" t="s">
         <v>11</v>
@@ -20399,11 +20387,11 @@
         <v>414</v>
       </c>
       <c r="B361" s="2">
-        <v>46316</v>
+        <v>46313</v>
       </c>
       <c r="C361">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="D361" t="s">
         <v>184</v>
@@ -20450,11 +20438,11 @@
         <v>415</v>
       </c>
       <c r="B362" s="2">
-        <v>46307</v>
+        <v>46316</v>
       </c>
       <c r="C362">
         <f t="shared" ca="1" si="5"/>
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="D362" t="s">
         <v>184</v>
@@ -20475,7 +20463,7 @@
         <v>184</v>
       </c>
       <c r="J362" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K362" t="s">
         <v>11</v>
@@ -20501,11 +20489,11 @@
         <v>416</v>
       </c>
       <c r="B363" s="2">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="C363">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D363" t="s">
         <v>184</v>
@@ -20526,7 +20514,7 @@
         <v>184</v>
       </c>
       <c r="J363" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="K363" t="s">
         <v>11</v>
@@ -20583,13 +20571,13 @@
         <v>11</v>
       </c>
       <c r="L364" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M364" t="s">
         <v>119</v>
       </c>
       <c r="N364" t="s">
-        <v>120</v>
+        <v>447</v>
       </c>
       <c r="P364" s="2">
         <v>46023</v>
@@ -20634,13 +20622,13 @@
         <v>11</v>
       </c>
       <c r="L365" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M365" t="s">
         <v>119</v>
       </c>
       <c r="N365" t="s">
-        <v>120</v>
+        <v>447</v>
       </c>
       <c r="P365" s="2">
         <v>46023</v>
@@ -20691,7 +20679,7 @@
         <v>119</v>
       </c>
       <c r="N366" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P366" s="2">
         <v>46023</v>
@@ -20742,7 +20730,7 @@
         <v>119</v>
       </c>
       <c r="N367" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P367" s="2">
         <v>46023</v>
@@ -20793,7 +20781,7 @@
         <v>119</v>
       </c>
       <c r="N368" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P368" s="2">
         <v>46023</v>
@@ -20844,7 +20832,7 @@
         <v>119</v>
       </c>
       <c r="N369" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P369" s="2">
         <v>46023</v>
@@ -20858,11 +20846,11 @@
         <v>423</v>
       </c>
       <c r="B370" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C370">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D370" t="s">
         <v>184</v>
@@ -20889,13 +20877,13 @@
         <v>11</v>
       </c>
       <c r="L370" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M370" t="s">
         <v>119</v>
       </c>
       <c r="N370" t="s">
-        <v>449</v>
+        <v>120</v>
       </c>
       <c r="P370" s="2">
         <v>46023</v>
@@ -20909,11 +20897,11 @@
         <v>424</v>
       </c>
       <c r="B371" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C371">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D371" t="s">
         <v>184</v>
@@ -20940,13 +20928,13 @@
         <v>11</v>
       </c>
       <c r="L371" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M371" t="s">
         <v>119</v>
       </c>
       <c r="N371" t="s">
-        <v>449</v>
+        <v>120</v>
       </c>
       <c r="P371" s="2">
         <v>46023</v>
@@ -20960,11 +20948,11 @@
         <v>425</v>
       </c>
       <c r="B372" s="2">
-        <v>46315</v>
+        <v>46309</v>
       </c>
       <c r="C372">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="D372" t="s">
         <v>184</v>
@@ -21011,11 +20999,11 @@
         <v>426</v>
       </c>
       <c r="B373" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C373">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D373" t="s">
         <v>184</v>
@@ -21062,11 +21050,11 @@
         <v>427</v>
       </c>
       <c r="B374" s="2">
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="C374">
         <f t="shared" ca="1" si="5"/>
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="D374" t="s">
         <v>184</v>
@@ -21291,19 +21279,19 @@
         <v>184</v>
       </c>
       <c r="J378" t="s">
-        <v>22</v>
+        <v>225</v>
       </c>
       <c r="K378" t="s">
         <v>11</v>
       </c>
       <c r="L378" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M378" t="s">
         <v>119</v>
       </c>
       <c r="N378" t="s">
-        <v>120</v>
+        <v>447</v>
       </c>
       <c r="P378" s="2">
         <v>46023</v>
@@ -21342,7 +21330,7 @@
         <v>184</v>
       </c>
       <c r="J379" t="s">
-        <v>22</v>
+        <v>225</v>
       </c>
       <c r="K379" t="s">
         <v>11</v>
@@ -21399,13 +21387,13 @@
         <v>11</v>
       </c>
       <c r="L380" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M380" t="s">
         <v>119</v>
       </c>
       <c r="N380" t="s">
-        <v>449</v>
+        <v>120</v>
       </c>
       <c r="P380" s="2">
         <v>46023</v>
@@ -21419,11 +21407,11 @@
         <v>434</v>
       </c>
       <c r="B381" s="2">
-        <v>46316</v>
+        <v>46312</v>
       </c>
       <c r="C381">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="D381" t="s">
         <v>184</v>
@@ -21444,19 +21432,19 @@
         <v>184</v>
       </c>
       <c r="J381" t="s">
-        <v>225</v>
+        <v>118</v>
       </c>
       <c r="K381" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L381" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M381" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="N381" t="s">
-        <v>120</v>
+        <v>449</v>
       </c>
       <c r="P381" s="2">
         <v>46023</v>
@@ -21470,11 +21458,11 @@
         <v>435</v>
       </c>
       <c r="B382" s="2">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="C382">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D382" t="s">
         <v>184</v>
@@ -21495,19 +21483,19 @@
         <v>184</v>
       </c>
       <c r="J382" t="s">
-        <v>225</v>
+        <v>118</v>
       </c>
       <c r="K382" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L382" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M382" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="N382" t="s">
-        <v>120</v>
+        <v>449</v>
       </c>
       <c r="P382" s="2">
         <v>46023</v>
@@ -21521,11 +21509,11 @@
         <v>436</v>
       </c>
       <c r="B383" s="2">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="C383">
-        <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <f t="shared" ref="C383:C390" ca="1" si="6">B383-$R$1</f>
+        <v>-6</v>
       </c>
       <c r="D383" t="s">
         <v>184</v>
@@ -21558,7 +21546,7 @@
         <v>24</v>
       </c>
       <c r="N383" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P383" s="2">
         <v>46023</v>
@@ -21575,7 +21563,7 @@
         <v>46314</v>
       </c>
       <c r="C384">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-3</v>
       </c>
       <c r="D384" t="s">
@@ -21609,7 +21597,7 @@
         <v>24</v>
       </c>
       <c r="N384" t="s">
-        <v>451</v>
+        <v>120</v>
       </c>
       <c r="P384" s="2">
         <v>46023</v>
@@ -21623,11 +21611,11 @@
         <v>438</v>
       </c>
       <c r="B385" s="2">
-        <v>46311</v>
+        <v>0</v>
       </c>
       <c r="C385">
-        <f t="shared" ref="C385:C392" ca="1" si="6">B385-$R$1</f>
-        <v>-6</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-46317</v>
       </c>
       <c r="D385" t="s">
         <v>184</v>
@@ -21648,19 +21636,19 @@
         <v>184</v>
       </c>
       <c r="J385" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="K385" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L385" t="s">
         <v>12</v>
       </c>
       <c r="M385" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="N385" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="P385" s="2">
         <v>46023</v>
@@ -21674,11 +21662,11 @@
         <v>439</v>
       </c>
       <c r="B386" s="2">
-        <v>46314</v>
+        <v>0</v>
       </c>
       <c r="C386">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>-46317</v>
       </c>
       <c r="D386" t="s">
         <v>184</v>
@@ -21699,19 +21687,19 @@
         <v>184</v>
       </c>
       <c r="J386" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="K386" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L386" t="s">
         <v>12</v>
       </c>
       <c r="M386" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="N386" t="s">
-        <v>120</v>
+        <v>458</v>
       </c>
       <c r="P386" s="2">
         <v>46023</v>
@@ -21762,7 +21750,7 @@
         <v>88</v>
       </c>
       <c r="N387" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P387" s="2">
         <v>46023</v>
@@ -21813,7 +21801,7 @@
         <v>88</v>
       </c>
       <c r="N388" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P388" s="2">
         <v>46023</v>
@@ -21827,11 +21815,11 @@
         <v>442</v>
       </c>
       <c r="B389" s="2">
-        <v>0</v>
+        <v>46316</v>
       </c>
       <c r="C389">
         <f t="shared" ca="1" si="6"/>
-        <v>-46317</v>
+        <v>-1</v>
       </c>
       <c r="D389" t="s">
         <v>184</v>
@@ -21852,7 +21840,7 @@
         <v>184</v>
       </c>
       <c r="J389" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="K389" t="s">
         <v>11</v>
@@ -21861,10 +21849,10 @@
         <v>12</v>
       </c>
       <c r="M389" t="s">
-        <v>88</v>
+        <v>178</v>
       </c>
       <c r="N389" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="P389" s="2">
         <v>46023</v>
@@ -21878,11 +21866,11 @@
         <v>443</v>
       </c>
       <c r="B390" s="2">
-        <v>0</v>
+        <v>46314</v>
       </c>
       <c r="C390">
         <f t="shared" ca="1" si="6"/>
-        <v>-46317</v>
+        <v>-3</v>
       </c>
       <c r="D390" t="s">
         <v>184</v>
@@ -21903,7 +21891,7 @@
         <v>184</v>
       </c>
       <c r="J390" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="K390" t="s">
         <v>11</v>
@@ -21912,117 +21900,15 @@
         <v>12</v>
       </c>
       <c r="M390" t="s">
-        <v>88</v>
+        <v>178</v>
       </c>
       <c r="N390" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="P390" s="2">
         <v>46023</v>
       </c>
       <c r="Q390" s="2">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="391" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A391" t="s">
-        <v>444</v>
-      </c>
-      <c r="B391" s="2">
-        <v>46316</v>
-      </c>
-      <c r="C391">
-        <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
-      </c>
-      <c r="D391" t="s">
-        <v>184</v>
-      </c>
-      <c r="E391" t="s">
-        <v>184</v>
-      </c>
-      <c r="F391" t="s">
-        <v>184</v>
-      </c>
-      <c r="G391" t="s">
-        <v>184</v>
-      </c>
-      <c r="H391" t="s">
-        <v>184</v>
-      </c>
-      <c r="I391" t="s">
-        <v>184</v>
-      </c>
-      <c r="J391" t="s">
-        <v>10</v>
-      </c>
-      <c r="K391" t="s">
-        <v>11</v>
-      </c>
-      <c r="L391" t="s">
-        <v>12</v>
-      </c>
-      <c r="M391" t="s">
-        <v>178</v>
-      </c>
-      <c r="N391" t="s">
-        <v>448</v>
-      </c>
-      <c r="P391" s="2">
-        <v>46023</v>
-      </c>
-      <c r="Q391" s="2">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="392" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A392" t="s">
-        <v>445</v>
-      </c>
-      <c r="B392" s="2">
-        <v>46314</v>
-      </c>
-      <c r="C392">
-        <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
-      </c>
-      <c r="D392" t="s">
-        <v>184</v>
-      </c>
-      <c r="E392" t="s">
-        <v>184</v>
-      </c>
-      <c r="F392" t="s">
-        <v>184</v>
-      </c>
-      <c r="G392" t="s">
-        <v>184</v>
-      </c>
-      <c r="H392" t="s">
-        <v>184</v>
-      </c>
-      <c r="I392" t="s">
-        <v>184</v>
-      </c>
-      <c r="J392" t="s">
-        <v>10</v>
-      </c>
-      <c r="K392" t="s">
-        <v>11</v>
-      </c>
-      <c r="L392" t="s">
-        <v>12</v>
-      </c>
-      <c r="M392" t="s">
-        <v>178</v>
-      </c>
-      <c r="N392" t="s">
-        <v>451</v>
-      </c>
-      <c r="P392" s="2">
-        <v>46023</v>
-      </c>
-      <c r="Q392" s="2">
         <v>46023</v>
       </c>
     </row>
@@ -22032,15 +21918,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -22050,6 +21927,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22314,20 +22200,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="423" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EFCB533-4294-4217-B035-64242ACBA7E3}"/>
+  <xr:revisionPtr revIDLastSave="429" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F01D7193-DF4E-4937-99F7-5035515D903B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4780" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4786" uniqueCount="466">
   <si>
     <t>Placa</t>
   </si>
@@ -9425,6 +9425,24 @@
         <f t="shared" ca="1" si="2"/>
         <v>-3</v>
       </c>
+      <c r="D144" t="s">
+        <v>184</v>
+      </c>
+      <c r="E144" t="s">
+        <v>184</v>
+      </c>
+      <c r="F144" t="s">
+        <v>184</v>
+      </c>
+      <c r="G144" t="s">
+        <v>184</v>
+      </c>
+      <c r="H144" t="s">
+        <v>184</v>
+      </c>
+      <c r="I144" t="s">
+        <v>184</v>
+      </c>
       <c r="J144" t="s">
         <v>28</v>
       </c>
@@ -21918,6 +21936,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -21927,15 +21954,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22200,20 +22218,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="429" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F01D7193-DF4E-4937-99F7-5035515D903B}"/>
+  <xr:revisionPtr revIDLastSave="440" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{270C6A77-B1B7-4DB2-B60E-2ED701F49D1B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Placas_BID2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Placas_BID2026!$A$1:$R$390</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Placas_BID2026!$A$1:$R$391</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4786" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4795" uniqueCount="467">
   <si>
     <t>Placa</t>
   </si>
@@ -1434,6 +1434,9 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>UVX7D97</t>
   </si>
 </sst>
 </file>
@@ -1788,7 +1791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R390"/>
+  <dimension ref="A1:R391"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
@@ -8803,7 +8806,7 @@
         <v>46315</v>
       </c>
       <c r="C131">
-        <f t="shared" ref="C131:C192" ca="1" si="2">B131-$R$1</f>
+        <f t="shared" ref="C131:C193" ca="1" si="2">B131-$R$1</f>
         <v>-2</v>
       </c>
       <c r="D131" t="s">
@@ -8905,69 +8908,57 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
+        <v>466</v>
+      </c>
+      <c r="B133" s="2">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <f t="shared" ref="C133" ca="1" si="3">B133-$R$1</f>
+        <v>-46317</v>
+      </c>
+      <c r="D133" t="s">
+        <v>184</v>
+      </c>
+      <c r="I133" t="s">
+        <v>184</v>
+      </c>
+      <c r="J133" t="s">
+        <v>28</v>
+      </c>
+      <c r="K133" t="s">
+        <v>11</v>
+      </c>
+      <c r="L133" t="s">
+        <v>23</v>
+      </c>
+      <c r="M133" t="s">
+        <v>24</v>
+      </c>
+      <c r="N133" t="s">
+        <v>146</v>
+      </c>
+      <c r="O133" t="s">
+        <v>217</v>
+      </c>
+      <c r="P133" s="2">
+        <v>46309</v>
+      </c>
+      <c r="Q133" s="2">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
         <v>188</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B134" s="2">
         <v>46315</v>
       </c>
-      <c r="C133">
+      <c r="C134">
         <f t="shared" ca="1" si="2"/>
         <v>-2</v>
       </c>
-      <c r="D133" t="s">
-        <v>184</v>
-      </c>
-      <c r="E133" t="s">
-        <v>184</v>
-      </c>
-      <c r="F133" t="s">
-        <v>184</v>
-      </c>
-      <c r="G133" t="s">
-        <v>184</v>
-      </c>
-      <c r="H133" t="s">
-        <v>184</v>
-      </c>
-      <c r="I133" t="s">
-        <v>184</v>
-      </c>
-      <c r="J133" t="s">
-        <v>163</v>
-      </c>
-      <c r="K133" t="s">
-        <v>11</v>
-      </c>
-      <c r="L133" t="s">
-        <v>23</v>
-      </c>
-      <c r="M133" t="s">
-        <v>24</v>
-      </c>
-      <c r="N133" t="s">
-        <v>146</v>
-      </c>
-      <c r="O133" t="s">
-        <v>217</v>
-      </c>
-      <c r="P133" s="2">
-        <v>46295</v>
-      </c>
-      <c r="Q133" s="2">
-        <v>46295</v>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>189</v>
-      </c>
-      <c r="B134" s="2">
-        <v>46316</v>
-      </c>
-      <c r="C134">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
-      </c>
       <c r="D134" t="s">
         <v>184</v>
       </c>
@@ -9013,7 +9004,7 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B135" s="2">
         <v>46316</v>
@@ -9067,7 +9058,7 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B136" s="2">
         <v>46316</v>
@@ -9121,7 +9112,7 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B137" s="2">
         <v>46316</v>
@@ -9175,112 +9166,124 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
+        <v>192</v>
+      </c>
+      <c r="B138" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C138">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="D138" t="s">
+        <v>184</v>
+      </c>
+      <c r="E138" t="s">
+        <v>184</v>
+      </c>
+      <c r="F138" t="s">
+        <v>184</v>
+      </c>
+      <c r="G138" t="s">
+        <v>184</v>
+      </c>
+      <c r="H138" t="s">
+        <v>184</v>
+      </c>
+      <c r="I138" t="s">
+        <v>184</v>
+      </c>
+      <c r="J138" t="s">
+        <v>163</v>
+      </c>
+      <c r="K138" t="s">
+        <v>11</v>
+      </c>
+      <c r="L138" t="s">
+        <v>23</v>
+      </c>
+      <c r="M138" t="s">
+        <v>24</v>
+      </c>
+      <c r="N138" t="s">
+        <v>146</v>
+      </c>
+      <c r="O138" t="s">
+        <v>217</v>
+      </c>
+      <c r="P138" s="2">
+        <v>46295</v>
+      </c>
+      <c r="Q138" s="2">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
         <v>193</v>
       </c>
-      <c r="B138" s="2" t="e">
+      <c r="B139" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C138" t="e">
+      <c r="C139" t="e">
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="D138" t="s">
-        <v>184</v>
-      </c>
-      <c r="I138" t="s">
-        <v>184</v>
-      </c>
-      <c r="J138" t="s">
+      <c r="D139" t="s">
+        <v>184</v>
+      </c>
+      <c r="I139" t="s">
+        <v>184</v>
+      </c>
+      <c r="J139" t="s">
         <v>28</v>
       </c>
-      <c r="K138" t="s">
-        <v>11</v>
-      </c>
-      <c r="L138" t="s">
+      <c r="K139" t="s">
+        <v>11</v>
+      </c>
+      <c r="L139" t="s">
         <v>23</v>
       </c>
-      <c r="M138" t="s">
+      <c r="M139" t="s">
         <v>24</v>
       </c>
-      <c r="N138" t="s">
+      <c r="N139" t="s">
         <v>146</v>
       </c>
-      <c r="O138" t="s">
+      <c r="O139" t="s">
         <v>217</v>
       </c>
-      <c r="P138" s="2">
+      <c r="P139" s="2">
         <v>46317</v>
       </c>
-      <c r="Q138" s="2">
+      <c r="Q139" s="2">
         <v>46317</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
         <v>194</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B140" s="2">
         <v>46314</v>
       </c>
-      <c r="C139">
+      <c r="C140">
         <f t="shared" ca="1" si="2"/>
         <v>-3</v>
       </c>
-      <c r="D139" t="s">
-        <v>184</v>
-      </c>
-      <c r="E139" t="s">
-        <v>184</v>
-      </c>
-      <c r="F139" t="s">
-        <v>184</v>
-      </c>
-      <c r="G139" t="s">
-        <v>184</v>
-      </c>
-      <c r="H139" t="s">
-        <v>184</v>
-      </c>
-      <c r="I139" t="s">
-        <v>184</v>
-      </c>
-      <c r="J139" t="s">
-        <v>28</v>
-      </c>
-      <c r="K139" t="s">
-        <v>11</v>
-      </c>
-      <c r="L139" t="s">
-        <v>23</v>
-      </c>
-      <c r="M139" t="s">
-        <v>24</v>
-      </c>
-      <c r="N139" t="s">
-        <v>146</v>
-      </c>
-      <c r="O139" t="s">
-        <v>217</v>
-      </c>
-      <c r="P139" s="2">
-        <v>46310</v>
-      </c>
-      <c r="Q139" s="2">
-        <v>46310</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>195</v>
-      </c>
-      <c r="B140" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C140" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
       <c r="D140" t="s">
+        <v>184</v>
+      </c>
+      <c r="E140" t="s">
+        <v>184</v>
+      </c>
+      <c r="F140" t="s">
+        <v>184</v>
+      </c>
+      <c r="G140" t="s">
+        <v>184</v>
+      </c>
+      <c r="H140" t="s">
         <v>184</v>
       </c>
       <c r="I140" t="s">
@@ -9305,15 +9308,15 @@
         <v>217</v>
       </c>
       <c r="P140" s="2">
-        <v>46317</v>
+        <v>46310</v>
       </c>
       <c r="Q140" s="2">
-        <v>46317</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B141" s="2" t="e">
         <v>#N/A</v>
@@ -9347,15 +9350,15 @@
         <v>217</v>
       </c>
       <c r="P141" s="2">
-        <v>46312</v>
+        <v>46317</v>
       </c>
       <c r="Q141" s="2">
-        <v>46312</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B142" s="2" t="e">
         <v>#N/A</v>
@@ -9364,6 +9367,12 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D142" t="s">
+        <v>184</v>
+      </c>
+      <c r="I142" t="s">
+        <v>184</v>
+      </c>
       <c r="J142" t="s">
         <v>28</v>
       </c>
@@ -9376,15 +9385,22 @@
       <c r="M142" t="s">
         <v>24</v>
       </c>
+      <c r="N142" t="s">
+        <v>146</v>
+      </c>
       <c r="O142" t="s">
         <v>217</v>
       </c>
-      <c r="P142" s="2"/>
-      <c r="Q142" s="2"/>
+      <c r="P142" s="2">
+        <v>46312</v>
+      </c>
+      <c r="Q142" s="2">
+        <v>46312</v>
+      </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B143" s="2" t="e">
         <v>#N/A</v>
@@ -9405,9 +9421,6 @@
       <c r="M143" t="s">
         <v>24</v>
       </c>
-      <c r="N143" t="s">
-        <v>146</v>
-      </c>
       <c r="O143" t="s">
         <v>217</v>
       </c>
@@ -9416,64 +9429,64 @@
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>198</v>
+      </c>
+      <c r="B144" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C144" t="e">
+        <f t="shared" ca="1" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="J144" t="s">
+        <v>28</v>
+      </c>
+      <c r="K144" t="s">
+        <v>11</v>
+      </c>
+      <c r="L144" t="s">
+        <v>23</v>
+      </c>
+      <c r="M144" t="s">
+        <v>24</v>
+      </c>
+      <c r="N144" t="s">
+        <v>146</v>
+      </c>
+      <c r="O144" t="s">
+        <v>217</v>
+      </c>
+      <c r="P144" s="2"/>
+      <c r="Q144" s="2"/>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
         <v>199</v>
       </c>
-      <c r="B144" s="2">
+      <c r="B145" s="2">
         <v>46314</v>
       </c>
-      <c r="C144">
+      <c r="C145">
         <f t="shared" ca="1" si="2"/>
         <v>-3</v>
       </c>
-      <c r="D144" t="s">
-        <v>184</v>
-      </c>
-      <c r="E144" t="s">
-        <v>184</v>
-      </c>
-      <c r="F144" t="s">
-        <v>184</v>
-      </c>
-      <c r="G144" t="s">
-        <v>184</v>
-      </c>
-      <c r="H144" t="s">
-        <v>184</v>
-      </c>
-      <c r="I144" t="s">
-        <v>184</v>
-      </c>
-      <c r="J144" t="s">
-        <v>28</v>
-      </c>
-      <c r="K144" t="s">
-        <v>11</v>
-      </c>
-      <c r="L144" t="s">
-        <v>23</v>
-      </c>
-      <c r="M144" t="s">
-        <v>24</v>
-      </c>
-      <c r="N144" t="s">
-        <v>146</v>
-      </c>
-      <c r="O144" t="s">
-        <v>217</v>
-      </c>
-      <c r="P144" s="2"/>
-      <c r="Q144" s="2"/>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>200</v>
-      </c>
-      <c r="B145" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C145" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+      <c r="D145" t="s">
+        <v>184</v>
+      </c>
+      <c r="E145" t="s">
+        <v>184</v>
+      </c>
+      <c r="F145" t="s">
+        <v>184</v>
+      </c>
+      <c r="G145" t="s">
+        <v>184</v>
+      </c>
+      <c r="H145" t="s">
+        <v>184</v>
+      </c>
+      <c r="I145" t="s">
+        <v>184</v>
       </c>
       <c r="J145" t="s">
         <v>28</v>
@@ -9498,7 +9511,7 @@
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B146" s="2" t="e">
         <v>#N/A</v>
@@ -9507,12 +9520,6 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="D146" t="s">
-        <v>184</v>
-      </c>
-      <c r="I146" t="s">
-        <v>184</v>
-      </c>
       <c r="J146" t="s">
         <v>28</v>
       </c>
@@ -9531,16 +9538,12 @@
       <c r="O146" t="s">
         <v>217</v>
       </c>
-      <c r="P146" s="2">
-        <v>46316</v>
-      </c>
-      <c r="Q146" s="2">
-        <v>46316</v>
-      </c>
+      <c r="P146" s="2"/>
+      <c r="Q146" s="2"/>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B147" s="2" t="e">
         <v>#N/A</v>
@@ -9574,15 +9577,15 @@
         <v>217</v>
       </c>
       <c r="P147" s="2">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="Q147" s="2">
-        <v>46312</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B148" s="2" t="e">
         <v>#N/A</v>
@@ -9624,7 +9627,7 @@
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B149" s="2" t="e">
         <v>#N/A</v>
@@ -9633,8 +9636,14 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D149" t="s">
+        <v>184</v>
+      </c>
+      <c r="I149" t="s">
+        <v>184</v>
+      </c>
       <c r="J149" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K149" t="s">
         <v>11</v>
@@ -9646,44 +9655,28 @@
         <v>24</v>
       </c>
       <c r="N149" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="O149" t="s">
         <v>217</v>
       </c>
       <c r="P149" s="2">
-        <v>46290</v>
-      </c>
-      <c r="Q149" s="2"/>
+        <v>46312</v>
+      </c>
+      <c r="Q149" s="2">
+        <v>46312</v>
+      </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>205</v>
-      </c>
-      <c r="B150" s="2">
-        <v>46316</v>
-      </c>
-      <c r="C150">
+        <v>204</v>
+      </c>
+      <c r="B150" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C150" t="e">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
-      </c>
-      <c r="D150" t="s">
-        <v>184</v>
-      </c>
-      <c r="E150" t="s">
-        <v>184</v>
-      </c>
-      <c r="F150" t="s">
-        <v>184</v>
-      </c>
-      <c r="G150" t="s">
-        <v>184</v>
-      </c>
-      <c r="H150" t="s">
-        <v>184</v>
-      </c>
-      <c r="I150" t="s">
-        <v>184</v>
+        <v>#N/A</v>
       </c>
       <c r="J150" t="s">
         <v>22</v>
@@ -9703,12 +9696,14 @@
       <c r="O150" t="s">
         <v>217</v>
       </c>
-      <c r="P150" s="2"/>
+      <c r="P150" s="2">
+        <v>46290</v>
+      </c>
       <c r="Q150" s="2"/>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="B151" s="2">
         <v>46316</v>
@@ -9736,10 +9731,10 @@
         <v>184</v>
       </c>
       <c r="J151" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="K151" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L151" t="s">
         <v>23</v>
@@ -9753,16 +9748,12 @@
       <c r="O151" t="s">
         <v>217</v>
       </c>
-      <c r="P151" s="2">
-        <v>46239</v>
-      </c>
-      <c r="Q151" s="2">
-        <v>46235</v>
-      </c>
+      <c r="P151" s="2"/>
+      <c r="Q151" s="2"/>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B152" s="2">
         <v>46316</v>
@@ -9808,15 +9799,15 @@
         <v>217</v>
       </c>
       <c r="P152" s="2">
-        <v>46270</v>
+        <v>46239</v>
       </c>
       <c r="Q152" s="2">
-        <v>46263</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B153" s="2">
         <v>46316</v>
@@ -9870,7 +9861,7 @@
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B154" s="2">
         <v>46316</v>
@@ -9916,22 +9907,22 @@
         <v>217</v>
       </c>
       <c r="P154" s="2">
-        <v>46239</v>
+        <v>46270</v>
       </c>
       <c r="Q154" s="2">
-        <v>46235</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B155" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D155" t="s">
         <v>184</v>
@@ -9970,22 +9961,22 @@
         <v>217</v>
       </c>
       <c r="P155" s="2">
-        <v>46262</v>
+        <v>46239</v>
       </c>
       <c r="Q155" s="2">
-        <v>46261</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B156" s="2">
-        <v>46289</v>
+        <v>46315</v>
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
-        <v>-28</v>
+        <v>-2</v>
       </c>
       <c r="D156" t="s">
         <v>184</v>
@@ -10024,7 +10015,7 @@
         <v>217</v>
       </c>
       <c r="P156" s="2">
-        <v>46270</v>
+        <v>46262</v>
       </c>
       <c r="Q156" s="2">
         <v>46261</v>
@@ -10032,14 +10023,14 @@
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B157" s="2">
-        <v>46316</v>
+        <v>46289</v>
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-28</v>
       </c>
       <c r="D157" t="s">
         <v>184</v>
@@ -10078,15 +10069,15 @@
         <v>217</v>
       </c>
       <c r="P157" s="2">
-        <v>46262</v>
+        <v>46270</v>
       </c>
       <c r="Q157" s="2">
-        <v>46256</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B158" s="2">
         <v>46316</v>
@@ -10132,15 +10123,15 @@
         <v>217</v>
       </c>
       <c r="P158" s="2">
-        <v>46270</v>
+        <v>46262</v>
       </c>
       <c r="Q158" s="2">
-        <v>46262</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B159" s="2">
         <v>46316</v>
@@ -10186,22 +10177,22 @@
         <v>217</v>
       </c>
       <c r="P159" s="2">
+        <v>46270</v>
+      </c>
+      <c r="Q159" s="2">
         <v>46262</v>
-      </c>
-      <c r="Q159" s="2">
-        <v>46261</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B160" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D160" t="s">
         <v>184</v>
@@ -10222,10 +10213,10 @@
         <v>184</v>
       </c>
       <c r="J160" t="s">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="K160" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L160" t="s">
         <v>23</v>
@@ -10240,22 +10231,22 @@
         <v>217</v>
       </c>
       <c r="P160" s="2">
-        <v>46280</v>
+        <v>46262</v>
       </c>
       <c r="Q160" s="2">
-        <v>46289</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B161" s="2">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D161" t="s">
         <v>184</v>
@@ -10302,14 +10293,14 @@
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B162" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D162" t="s">
         <v>184</v>
@@ -10356,14 +10347,14 @@
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="B163" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C163">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D163" t="s">
         <v>184</v>
@@ -10396,30 +10387,42 @@
         <v>24</v>
       </c>
       <c r="N163" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="O163" t="s">
         <v>217</v>
       </c>
       <c r="P163" s="2">
-        <v>46304</v>
+        <v>46280</v>
       </c>
       <c r="Q163" s="2">
-        <v>46304</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B164" s="2">
-        <v>0</v>
+        <v>46316</v>
       </c>
       <c r="C164">
         <f t="shared" ca="1" si="2"/>
-        <v>-46317</v>
+        <v>-1</v>
       </c>
       <c r="D164" t="s">
+        <v>184</v>
+      </c>
+      <c r="E164" t="s">
+        <v>184</v>
+      </c>
+      <c r="F164" t="s">
+        <v>184</v>
+      </c>
+      <c r="G164" t="s">
+        <v>184</v>
+      </c>
+      <c r="H164" t="s">
         <v>184</v>
       </c>
       <c r="I164" t="s">
@@ -10444,37 +10447,25 @@
         <v>217</v>
       </c>
       <c r="P164" s="2">
-        <v>46314</v>
+        <v>46304</v>
       </c>
       <c r="Q164" s="2">
-        <v>46314</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B165" s="2">
-        <v>46315</v>
+        <v>0</v>
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-46317</v>
       </c>
       <c r="D165" t="s">
-        <v>465</v>
-      </c>
-      <c r="E165" t="s">
-        <v>465</v>
-      </c>
-      <c r="F165" t="s">
-        <v>465</v>
-      </c>
-      <c r="G165" t="s">
-        <v>465</v>
-      </c>
-      <c r="H165" t="s">
-        <v>465</v>
+        <v>184</v>
       </c>
       <c r="I165" t="s">
         <v>184</v>
@@ -10498,26 +10489,38 @@
         <v>217</v>
       </c>
       <c r="P165" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="Q165" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B166" s="2">
-        <v>0</v>
+        <v>46315</v>
       </c>
       <c r="C166">
         <f t="shared" ca="1" si="2"/>
-        <v>-46317</v>
+        <v>-2</v>
       </c>
       <c r="D166" t="s">
         <v>465</v>
       </c>
+      <c r="E166" t="s">
+        <v>465</v>
+      </c>
+      <c r="F166" t="s">
+        <v>465</v>
+      </c>
+      <c r="G166" t="s">
+        <v>465</v>
+      </c>
+      <c r="H166" t="s">
+        <v>465</v>
+      </c>
       <c r="I166" t="s">
         <v>184</v>
       </c>
@@ -10540,15 +10543,15 @@
         <v>217</v>
       </c>
       <c r="P166" s="2">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="Q166" s="2">
-        <v>46314</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B167" s="2">
         <v>0</v>
@@ -10590,30 +10593,18 @@
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B168" s="2">
-        <v>46316</v>
+        <v>0</v>
       </c>
       <c r="C168">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-46317</v>
       </c>
       <c r="D168" t="s">
         <v>465</v>
       </c>
-      <c r="E168" t="s">
-        <v>465</v>
-      </c>
-      <c r="F168" t="s">
-        <v>465</v>
-      </c>
-      <c r="G168" t="s">
-        <v>465</v>
-      </c>
-      <c r="H168" t="s">
-        <v>465</v>
-      </c>
       <c r="I168" t="s">
         <v>184</v>
       </c>
@@ -10636,15 +10627,15 @@
         <v>217</v>
       </c>
       <c r="P168" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="Q168" s="2">
-        <v>46310</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B169" s="2">
         <v>46316</v>
@@ -10654,25 +10645,25 @@
         <v>-1</v>
       </c>
       <c r="D169" t="s">
-        <v>184</v>
+        <v>465</v>
       </c>
       <c r="E169" t="s">
-        <v>184</v>
+        <v>465</v>
       </c>
       <c r="F169" t="s">
-        <v>184</v>
+        <v>465</v>
       </c>
       <c r="G169" t="s">
-        <v>184</v>
+        <v>465</v>
       </c>
       <c r="H169" t="s">
-        <v>184</v>
+        <v>465</v>
       </c>
       <c r="I169" t="s">
         <v>184</v>
       </c>
       <c r="J169" t="s">
-        <v>22</v>
+        <v>174</v>
       </c>
       <c r="K169" t="s">
         <v>11</v>
@@ -10684,27 +10675,43 @@
         <v>24</v>
       </c>
       <c r="N169" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="O169" t="s">
         <v>217</v>
       </c>
-      <c r="P169" s="2"/>
-      <c r="Q169" s="2"/>
+      <c r="P169" s="2">
+        <v>46310</v>
+      </c>
+      <c r="Q169" s="2">
+        <v>46310</v>
+      </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B170" s="2">
-        <v>0</v>
+        <v>46316</v>
       </c>
       <c r="C170">
         <f t="shared" ca="1" si="2"/>
-        <v>-46317</v>
+        <v>-1</v>
       </c>
       <c r="D170" t="s">
-        <v>465</v>
+        <v>184</v>
+      </c>
+      <c r="E170" t="s">
+        <v>184</v>
+      </c>
+      <c r="F170" t="s">
+        <v>184</v>
+      </c>
+      <c r="G170" t="s">
+        <v>184</v>
+      </c>
+      <c r="H170" t="s">
+        <v>184</v>
       </c>
       <c r="I170" t="s">
         <v>184</v>
@@ -10722,21 +10729,17 @@
         <v>24</v>
       </c>
       <c r="N170" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="O170" t="s">
         <v>217</v>
       </c>
-      <c r="P170" s="2">
-        <v>46310</v>
-      </c>
-      <c r="Q170" s="2">
-        <v>46310</v>
-      </c>
+      <c r="P170" s="2"/>
+      <c r="Q170" s="2"/>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B171" s="2">
         <v>0</v>
@@ -10778,255 +10781,246 @@
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
+        <v>214</v>
+      </c>
+      <c r="B172" s="2">
+        <v>0</v>
+      </c>
+      <c r="C172">
+        <f t="shared" ca="1" si="2"/>
+        <v>-46317</v>
+      </c>
+      <c r="D172" t="s">
+        <v>465</v>
+      </c>
+      <c r="I172" t="s">
+        <v>184</v>
+      </c>
+      <c r="J172" t="s">
+        <v>22</v>
+      </c>
+      <c r="K172" t="s">
+        <v>11</v>
+      </c>
+      <c r="L172" t="s">
+        <v>23</v>
+      </c>
+      <c r="M172" t="s">
+        <v>24</v>
+      </c>
+      <c r="N172" t="s">
+        <v>146</v>
+      </c>
+      <c r="O172" t="s">
+        <v>217</v>
+      </c>
+      <c r="P172" s="2">
+        <v>46310</v>
+      </c>
+      <c r="Q172" s="2">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
         <v>215</v>
       </c>
-      <c r="B172" s="2" t="e">
+      <c r="B173" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C172" t="e">
+      <c r="C173" t="e">
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="J172" t="s">
+      <c r="J173" t="s">
         <v>22</v>
       </c>
-      <c r="K172" t="s">
-        <v>11</v>
-      </c>
-      <c r="L172" t="s">
+      <c r="K173" t="s">
+        <v>11</v>
+      </c>
+      <c r="L173" t="s">
         <v>23</v>
       </c>
-      <c r="M172" t="s">
+      <c r="M173" t="s">
         <v>24</v>
       </c>
-      <c r="N172" t="s">
+      <c r="N173" t="s">
         <v>146</v>
       </c>
-      <c r="O172" t="s">
+      <c r="O173" t="s">
         <v>217</v>
       </c>
-      <c r="P172" s="2">
+      <c r="P173" s="2">
         <v>46310</v>
       </c>
-      <c r="Q172" s="2">
+      <c r="Q173" s="2">
         <v>46310</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
         <v>226</v>
       </c>
-      <c r="B173" s="2">
+      <c r="B174" s="2">
         <v>46300</v>
       </c>
-      <c r="C173">
+      <c r="C174">
         <f t="shared" ca="1" si="2"/>
         <v>-17</v>
       </c>
-      <c r="D173" t="s">
-        <v>184</v>
-      </c>
-      <c r="E173" t="s">
-        <v>184</v>
-      </c>
-      <c r="F173" t="s">
-        <v>184</v>
-      </c>
-      <c r="G173" t="s">
-        <v>184</v>
-      </c>
-      <c r="H173" t="s">
-        <v>184</v>
-      </c>
-      <c r="I173" t="s">
-        <v>184</v>
-      </c>
-      <c r="J173" t="s">
+      <c r="D174" t="s">
+        <v>184</v>
+      </c>
+      <c r="E174" t="s">
+        <v>184</v>
+      </c>
+      <c r="F174" t="s">
+        <v>184</v>
+      </c>
+      <c r="G174" t="s">
+        <v>184</v>
+      </c>
+      <c r="H174" t="s">
+        <v>184</v>
+      </c>
+      <c r="I174" t="s">
+        <v>184</v>
+      </c>
+      <c r="J174" t="s">
         <v>32</v>
       </c>
-      <c r="K173" t="s">
+      <c r="K174" t="s">
         <v>33</v>
       </c>
-      <c r="L173" t="s">
+      <c r="L174" t="s">
         <v>23</v>
       </c>
-      <c r="M173" t="s">
+      <c r="M174" t="s">
         <v>34</v>
       </c>
-      <c r="N173" t="s">
+      <c r="N174" t="s">
         <v>444</v>
       </c>
-      <c r="P173" s="2">
-        <v>46023</v>
-      </c>
-      <c r="Q173" s="2">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
+      <c r="P174" s="2">
+        <v>46023</v>
+      </c>
+      <c r="Q174" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
         <v>227</v>
       </c>
-      <c r="B174" s="2">
+      <c r="B175" s="2">
         <v>46310</v>
       </c>
-      <c r="C174">
+      <c r="C175">
         <f t="shared" ca="1" si="2"/>
         <v>-7</v>
       </c>
-      <c r="D174" t="s">
-        <v>184</v>
-      </c>
-      <c r="E174" t="s">
-        <v>184</v>
-      </c>
-      <c r="F174" t="s">
-        <v>184</v>
-      </c>
-      <c r="G174" t="s">
-        <v>184</v>
-      </c>
-      <c r="H174" t="s">
-        <v>184</v>
-      </c>
-      <c r="I174" t="s">
-        <v>184</v>
-      </c>
-      <c r="J174" t="s">
+      <c r="D175" t="s">
+        <v>184</v>
+      </c>
+      <c r="E175" t="s">
+        <v>184</v>
+      </c>
+      <c r="F175" t="s">
+        <v>184</v>
+      </c>
+      <c r="G175" t="s">
+        <v>184</v>
+      </c>
+      <c r="H175" t="s">
+        <v>184</v>
+      </c>
+      <c r="I175" t="s">
+        <v>184</v>
+      </c>
+      <c r="J175" t="s">
         <v>32</v>
       </c>
-      <c r="K174" t="s">
+      <c r="K175" t="s">
         <v>33</v>
       </c>
-      <c r="L174" t="s">
+      <c r="L175" t="s">
         <v>23</v>
       </c>
-      <c r="M174" t="s">
+      <c r="M175" t="s">
         <v>34</v>
       </c>
-      <c r="N174" t="s">
+      <c r="N175" t="s">
         <v>444</v>
       </c>
-      <c r="P174" s="2">
-        <v>46023</v>
-      </c>
-      <c r="Q174" s="2">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
+      <c r="P175" s="2">
+        <v>46023</v>
+      </c>
+      <c r="Q175" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
         <v>228</v>
       </c>
-      <c r="B175" s="2">
+      <c r="B176" s="2">
         <v>46299</v>
       </c>
-      <c r="C175">
+      <c r="C176">
         <f t="shared" ca="1" si="2"/>
         <v>-18</v>
       </c>
-      <c r="D175" t="s">
-        <v>184</v>
-      </c>
-      <c r="E175" t="s">
-        <v>184</v>
-      </c>
-      <c r="F175" t="s">
-        <v>184</v>
-      </c>
-      <c r="G175" t="s">
-        <v>184</v>
-      </c>
-      <c r="H175" t="s">
-        <v>184</v>
-      </c>
-      <c r="I175" t="s">
-        <v>184</v>
-      </c>
-      <c r="J175" t="s">
+      <c r="D176" t="s">
+        <v>184</v>
+      </c>
+      <c r="E176" t="s">
+        <v>184</v>
+      </c>
+      <c r="F176" t="s">
+        <v>184</v>
+      </c>
+      <c r="G176" t="s">
+        <v>184</v>
+      </c>
+      <c r="H176" t="s">
+        <v>184</v>
+      </c>
+      <c r="I176" t="s">
+        <v>184</v>
+      </c>
+      <c r="J176" t="s">
         <v>32</v>
       </c>
-      <c r="K175" t="s">
+      <c r="K176" t="s">
         <v>33</v>
       </c>
-      <c r="L175" t="s">
+      <c r="L176" t="s">
         <v>23</v>
       </c>
-      <c r="M175" t="s">
+      <c r="M176" t="s">
         <v>34</v>
       </c>
-      <c r="N175" t="s">
+      <c r="N176" t="s">
         <v>444</v>
       </c>
-      <c r="P175" s="2">
-        <v>46023</v>
-      </c>
-      <c r="Q175" s="2">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
+      <c r="P176" s="2">
+        <v>46023</v>
+      </c>
+      <c r="Q176" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
         <v>229</v>
       </c>
-      <c r="B176" s="2">
+      <c r="B177" s="2">
         <v>46315</v>
       </c>
-      <c r="C176">
+      <c r="C177">
         <f t="shared" ca="1" si="2"/>
         <v>-2</v>
       </c>
-      <c r="D176" t="s">
-        <v>184</v>
-      </c>
-      <c r="E176" t="s">
-        <v>184</v>
-      </c>
-      <c r="F176" t="s">
-        <v>184</v>
-      </c>
-      <c r="G176" t="s">
-        <v>184</v>
-      </c>
-      <c r="H176" t="s">
-        <v>184</v>
-      </c>
-      <c r="I176" t="s">
-        <v>184</v>
-      </c>
-      <c r="J176" t="s">
-        <v>32</v>
-      </c>
-      <c r="K176" t="s">
-        <v>33</v>
-      </c>
-      <c r="L176" t="s">
-        <v>23</v>
-      </c>
-      <c r="M176" t="s">
-        <v>34</v>
-      </c>
-      <c r="N176" t="s">
-        <v>444</v>
-      </c>
-      <c r="P176" s="2">
-        <v>46023</v>
-      </c>
-      <c r="Q176" s="2">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
-        <v>230</v>
-      </c>
-      <c r="B177" s="2">
-        <v>46316</v>
-      </c>
-      <c r="C177">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
-      </c>
       <c r="D177" t="s">
         <v>184</v>
       </c>
@@ -11055,10 +11049,10 @@
         <v>23</v>
       </c>
       <c r="M177" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="N177" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="P177" s="2">
         <v>46023</v>
@@ -11069,7 +11063,7 @@
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B178" s="2">
         <v>46316</v>
@@ -11120,7 +11114,7 @@
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B179" s="2">
         <v>46316</v>
@@ -11148,19 +11142,19 @@
         <v>184</v>
       </c>
       <c r="J179" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="K179" t="s">
         <v>33</v>
       </c>
       <c r="L179" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M179" t="s">
-        <v>178</v>
+        <v>24</v>
       </c>
       <c r="N179" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="P179" s="2">
         <v>46023</v>
@@ -11171,7 +11165,7 @@
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B180" s="2">
         <v>46316</v>
@@ -11222,14 +11216,14 @@
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B181" s="2">
-        <v>46302</v>
+        <v>46316</v>
       </c>
       <c r="C181">
         <f t="shared" ca="1" si="2"/>
-        <v>-15</v>
+        <v>-1</v>
       </c>
       <c r="D181" t="s">
         <v>184</v>
@@ -11250,10 +11244,10 @@
         <v>184</v>
       </c>
       <c r="J181" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="K181" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L181" t="s">
         <v>12</v>
@@ -11273,14 +11267,14 @@
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B182" s="2">
-        <v>46315</v>
+        <v>46302</v>
       </c>
       <c r="C182">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-15</v>
       </c>
       <c r="D182" t="s">
         <v>184</v>
@@ -11324,14 +11318,14 @@
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B183" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C183">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D183" t="s">
         <v>184</v>
@@ -11352,19 +11346,19 @@
         <v>184</v>
       </c>
       <c r="J183" t="s">
-        <v>225</v>
+        <v>10</v>
       </c>
       <c r="K183" t="s">
         <v>11</v>
       </c>
       <c r="L183" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M183" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="N183" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="P183" s="2">
         <v>46023</v>
@@ -11375,14 +11369,14 @@
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B184" s="2">
-        <v>46266</v>
+        <v>46316</v>
       </c>
       <c r="C184">
         <f t="shared" ca="1" si="2"/>
-        <v>-51</v>
+        <v>-1</v>
       </c>
       <c r="D184" t="s">
         <v>184</v>
@@ -11403,19 +11397,19 @@
         <v>184</v>
       </c>
       <c r="J184" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="K184" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L184" t="s">
         <v>29</v>
       </c>
       <c r="M184" t="s">
-        <v>463</v>
+        <v>119</v>
       </c>
       <c r="N184" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="P184" s="2">
         <v>46023</v>
@@ -11426,14 +11420,14 @@
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B185" s="2">
-        <v>46316</v>
+        <v>46266</v>
       </c>
       <c r="C185">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-51</v>
       </c>
       <c r="D185" t="s">
         <v>184</v>
@@ -11477,7 +11471,7 @@
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B186" s="2">
         <v>46316</v>
@@ -11505,19 +11499,19 @@
         <v>184</v>
       </c>
       <c r="J186" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="K186" t="s">
         <v>33</v>
       </c>
       <c r="L186" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="M186" t="s">
-        <v>24</v>
+        <v>463</v>
       </c>
       <c r="N186" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P186" s="2">
         <v>46023</v>
@@ -11528,14 +11522,14 @@
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B187" s="2">
-        <v>46304</v>
+        <v>46316</v>
       </c>
       <c r="C187">
         <f t="shared" ca="1" si="2"/>
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="D187" t="s">
         <v>184</v>
@@ -11579,14 +11573,14 @@
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B188" s="2">
-        <v>46313</v>
+        <v>46304</v>
       </c>
       <c r="C188">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-13</v>
       </c>
       <c r="D188" t="s">
         <v>184</v>
@@ -11613,13 +11607,13 @@
         <v>33</v>
       </c>
       <c r="L188" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M188" t="s">
         <v>24</v>
       </c>
       <c r="N188" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P188" s="2">
         <v>46023</v>
@@ -11630,14 +11624,14 @@
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B189" s="2">
-        <v>46316</v>
+        <v>46313</v>
       </c>
       <c r="C189">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="D189" t="s">
         <v>184</v>
@@ -11664,13 +11658,13 @@
         <v>33</v>
       </c>
       <c r="L189" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="M189" t="s">
         <v>24</v>
       </c>
       <c r="N189" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P189" s="2">
         <v>46023</v>
@@ -11681,7 +11675,7 @@
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B190" s="2">
         <v>46316</v>
@@ -11709,19 +11703,19 @@
         <v>184</v>
       </c>
       <c r="J190" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="K190" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L190" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M190" t="s">
-        <v>464</v>
+        <v>24</v>
       </c>
       <c r="N190" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P190" s="2">
         <v>46023</v>
@@ -11732,14 +11726,14 @@
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B191" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C191">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D191" t="s">
         <v>184</v>
@@ -11760,19 +11754,19 @@
         <v>184</v>
       </c>
       <c r="J191" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="K191" t="s">
         <v>11</v>
       </c>
       <c r="L191" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M191" t="s">
-        <v>178</v>
+        <v>464</v>
       </c>
       <c r="N191" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="P191" s="2">
         <v>46023</v>
@@ -11783,7 +11777,7 @@
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B192" s="2">
         <v>46315</v>
@@ -11817,13 +11811,13 @@
         <v>11</v>
       </c>
       <c r="L192" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M192" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="N192" t="s">
-        <v>120</v>
+        <v>446</v>
       </c>
       <c r="P192" s="2">
         <v>46023</v>
@@ -11834,13 +11828,13 @@
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B193" s="2">
         <v>46315</v>
       </c>
       <c r="C193">
-        <f t="shared" ref="C193:C254" ca="1" si="3">B193-$R$1</f>
+        <f t="shared" ca="1" si="2"/>
         <v>-2</v>
       </c>
       <c r="D193" t="s">
@@ -11862,19 +11856,19 @@
         <v>184</v>
       </c>
       <c r="J193" t="s">
-        <v>461</v>
+        <v>10</v>
       </c>
       <c r="K193" t="s">
         <v>11</v>
       </c>
       <c r="L193" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M193" t="s">
         <v>119</v>
       </c>
       <c r="N193" t="s">
-        <v>449</v>
+        <v>120</v>
       </c>
       <c r="P193" s="2">
         <v>46023</v>
@@ -11885,14 +11879,14 @@
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B194" s="2">
-        <v>46303</v>
+        <v>46315</v>
       </c>
       <c r="C194">
-        <f t="shared" ca="1" si="3"/>
-        <v>-14</v>
+        <f t="shared" ref="C194:C255" ca="1" si="4">B194-$R$1</f>
+        <v>-2</v>
       </c>
       <c r="D194" t="s">
         <v>184</v>
@@ -11913,19 +11907,19 @@
         <v>184</v>
       </c>
       <c r="J194" t="s">
-        <v>22</v>
+        <v>461</v>
       </c>
       <c r="K194" t="s">
         <v>11</v>
       </c>
       <c r="L194" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M194" t="s">
         <v>119</v>
       </c>
       <c r="N194" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P194" s="2">
         <v>46023</v>
@@ -11936,14 +11930,14 @@
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B195" s="2">
-        <v>46316</v>
+        <v>46303</v>
       </c>
       <c r="C195">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-14</v>
       </c>
       <c r="D195" t="s">
         <v>184</v>
@@ -11964,19 +11958,19 @@
         <v>184</v>
       </c>
       <c r="J195" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="K195" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L195" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="M195" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="N195" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P195" s="2">
         <v>46023</v>
@@ -11987,14 +11981,14 @@
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B196" s="2">
-        <v>46167</v>
+        <v>46316</v>
       </c>
       <c r="C196">
-        <f t="shared" ca="1" si="3"/>
-        <v>-150</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-1</v>
       </c>
       <c r="D196" t="s">
         <v>184</v>
@@ -12015,19 +12009,19 @@
         <v>184</v>
       </c>
       <c r="J196" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="K196" t="s">
         <v>33</v>
       </c>
       <c r="L196" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M196" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N196" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="P196" s="2">
         <v>46023</v>
@@ -12038,14 +12032,14 @@
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B197" s="2">
-        <v>46286</v>
+        <v>46167</v>
       </c>
       <c r="C197">
-        <f t="shared" ca="1" si="3"/>
-        <v>-31</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-150</v>
       </c>
       <c r="D197" t="s">
         <v>184</v>
@@ -12089,14 +12083,14 @@
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B198" s="2">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="C198">
-        <f t="shared" ca="1" si="3"/>
-        <v>-36</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-31</v>
       </c>
       <c r="D198" t="s">
         <v>184</v>
@@ -12140,14 +12134,14 @@
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B199" s="2">
-        <v>46299</v>
+        <v>46281</v>
       </c>
       <c r="C199">
-        <f t="shared" ca="1" si="3"/>
-        <v>-18</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-36</v>
       </c>
       <c r="D199" t="s">
         <v>184</v>
@@ -12168,19 +12162,19 @@
         <v>184</v>
       </c>
       <c r="J199" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K199" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L199" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M199" t="s">
         <v>34</v>
       </c>
       <c r="N199" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="P199" s="2">
         <v>46023</v>
@@ -12191,14 +12185,14 @@
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B200" s="2">
-        <v>46037</v>
+        <v>46299</v>
       </c>
       <c r="C200">
-        <f t="shared" ca="1" si="3"/>
-        <v>-280</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-18</v>
       </c>
       <c r="D200" t="s">
         <v>184</v>
@@ -12242,14 +12236,14 @@
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B201" s="2">
-        <v>46315</v>
+        <v>46037</v>
       </c>
       <c r="C201">
-        <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-280</v>
       </c>
       <c r="D201" t="s">
         <v>184</v>
@@ -12293,14 +12287,14 @@
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B202" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C202">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-2</v>
       </c>
       <c r="D202" t="s">
         <v>184</v>
@@ -12344,13 +12338,13 @@
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B203" s="2">
         <v>46316</v>
       </c>
       <c r="C203">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D203" t="s">
@@ -12372,19 +12366,19 @@
         <v>184</v>
       </c>
       <c r="J203" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K203" t="s">
         <v>11</v>
       </c>
       <c r="L203" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="M203" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="N203" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="P203" s="2">
         <v>46023</v>
@@ -12395,13 +12389,13 @@
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B204" s="2">
         <v>46316</v>
       </c>
       <c r="C204">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D204" t="s">
@@ -12423,19 +12417,19 @@
         <v>184</v>
       </c>
       <c r="J204" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K204" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L204" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M204" t="s">
-        <v>24</v>
+        <v>178</v>
       </c>
       <c r="N204" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="P204" s="2">
         <v>46023</v>
@@ -12446,13 +12440,13 @@
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B205" s="2">
         <v>46316</v>
       </c>
       <c r="C205">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D205" t="s">
@@ -12497,13 +12491,13 @@
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B206" s="2">
         <v>46316</v>
       </c>
       <c r="C206">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D206" t="s">
@@ -12548,13 +12542,13 @@
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B207" s="2">
         <v>46316</v>
       </c>
       <c r="C207">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D207" t="s">
@@ -12599,13 +12593,13 @@
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B208" s="2">
         <v>46316</v>
       </c>
       <c r="C208">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D208" t="s">
@@ -12650,13 +12644,13 @@
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B209" s="2">
         <v>46316</v>
       </c>
       <c r="C209">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D209" t="s">
@@ -12701,13 +12695,13 @@
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B210" s="2">
         <v>46316</v>
       </c>
       <c r="C210">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D210" t="s">
@@ -12752,13 +12746,13 @@
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B211" s="2">
         <v>46316</v>
       </c>
       <c r="C211">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D211" t="s">
@@ -12803,13 +12797,13 @@
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B212" s="2">
         <v>46316</v>
       </c>
       <c r="C212">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D212" t="s">
@@ -12854,13 +12848,13 @@
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B213" s="2">
         <v>46316</v>
       </c>
       <c r="C213">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D213" t="s">
@@ -12905,14 +12899,14 @@
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B214" s="2">
-        <v>46300</v>
+        <v>46316</v>
       </c>
       <c r="C214">
-        <f t="shared" ca="1" si="3"/>
-        <v>-17</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-1</v>
       </c>
       <c r="D214" t="s">
         <v>184</v>
@@ -12956,14 +12950,14 @@
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B215" s="2">
-        <v>46312</v>
+        <v>46300</v>
       </c>
       <c r="C215">
-        <f t="shared" ca="1" si="3"/>
-        <v>-5</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-17</v>
       </c>
       <c r="D215" t="s">
         <v>184</v>
@@ -12984,19 +12978,19 @@
         <v>184</v>
       </c>
       <c r="J215" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="K215" t="s">
         <v>33</v>
       </c>
       <c r="L215" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M215" t="s">
-        <v>178</v>
+        <v>24</v>
       </c>
       <c r="N215" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="P215" s="2">
         <v>46023</v>
@@ -13007,14 +13001,14 @@
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B216" s="2">
-        <v>46316</v>
+        <v>46312</v>
       </c>
       <c r="C216">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-5</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
@@ -13058,14 +13052,14 @@
     </row>
     <row r="217" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B217" s="2">
-        <v>46303</v>
+        <v>46316</v>
       </c>
       <c r="C217">
-        <f t="shared" ca="1" si="3"/>
-        <v>-14</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-1</v>
       </c>
       <c r="D217" t="s">
         <v>184</v>
@@ -13109,14 +13103,14 @@
     </row>
     <row r="218" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B218" s="2">
-        <v>46285</v>
+        <v>46303</v>
       </c>
       <c r="C218">
-        <f t="shared" ca="1" si="3"/>
-        <v>-32</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-14</v>
       </c>
       <c r="D218" t="s">
         <v>184</v>
@@ -13160,14 +13154,14 @@
     </row>
     <row r="219" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B219" s="2">
-        <v>46316</v>
+        <v>46285</v>
       </c>
       <c r="C219">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-32</v>
       </c>
       <c r="D219" t="s">
         <v>184</v>
@@ -13200,7 +13194,7 @@
         <v>178</v>
       </c>
       <c r="N219" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="P219" s="2">
         <v>46023</v>
@@ -13211,14 +13205,14 @@
     </row>
     <row r="220" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B220" s="2">
-        <v>46307</v>
+        <v>46316</v>
       </c>
       <c r="C220">
-        <f t="shared" ca="1" si="3"/>
-        <v>-10</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-1</v>
       </c>
       <c r="D220" t="s">
         <v>184</v>
@@ -13262,14 +13256,14 @@
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B221" s="2">
-        <v>46316</v>
+        <v>46307</v>
       </c>
       <c r="C221">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-10</v>
       </c>
       <c r="D221" t="s">
         <v>184</v>
@@ -13313,13 +13307,13 @@
     </row>
     <row r="222" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B222" s="2">
         <v>46316</v>
       </c>
       <c r="C222">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D222" t="s">
@@ -13364,13 +13358,13 @@
     </row>
     <row r="223" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B223" s="2">
         <v>46316</v>
       </c>
       <c r="C223">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D223" t="s">
@@ -13392,19 +13386,19 @@
         <v>184</v>
       </c>
       <c r="J223" t="s">
-        <v>461</v>
+        <v>118</v>
       </c>
       <c r="K223" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L223" t="s">
         <v>12</v>
       </c>
       <c r="M223" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="N223" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="P223" s="2">
         <v>46023</v>
@@ -13415,13 +13409,13 @@
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B224" s="2">
         <v>46316</v>
       </c>
       <c r="C224">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D224" t="s">
@@ -13443,7 +13437,7 @@
         <v>184</v>
       </c>
       <c r="J224" t="s">
-        <v>10</v>
+        <v>461</v>
       </c>
       <c r="K224" t="s">
         <v>11</v>
@@ -13452,10 +13446,10 @@
         <v>12</v>
       </c>
       <c r="M224" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="N224" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P224" s="2">
         <v>46023</v>
@@ -13466,13 +13460,13 @@
     </row>
     <row r="225" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B225" s="2">
         <v>46316</v>
       </c>
       <c r="C225">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D225" t="s">
@@ -13517,14 +13511,14 @@
     </row>
     <row r="226" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B226" s="2">
-        <v>46292</v>
+        <v>46316</v>
       </c>
       <c r="C226">
-        <f t="shared" ca="1" si="3"/>
-        <v>-25</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-1</v>
       </c>
       <c r="D226" t="s">
         <v>184</v>
@@ -13557,7 +13551,7 @@
         <v>178</v>
       </c>
       <c r="N226" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="P226" s="2">
         <v>46023</v>
@@ -13568,14 +13562,14 @@
     </row>
     <row r="227" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B227" s="2">
-        <v>46316</v>
+        <v>46292</v>
       </c>
       <c r="C227">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-25</v>
       </c>
       <c r="D227" t="s">
         <v>184</v>
@@ -13619,13 +13613,13 @@
     </row>
     <row r="228" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B228" s="2">
         <v>46316</v>
       </c>
       <c r="C228">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D228" t="s">
@@ -13659,7 +13653,7 @@
         <v>178</v>
       </c>
       <c r="N228" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P228" s="2">
         <v>46023</v>
@@ -13670,13 +13664,13 @@
     </row>
     <row r="229" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B229" s="2">
         <v>46316</v>
       </c>
       <c r="C229">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D229" t="s">
@@ -13721,14 +13715,14 @@
     </row>
     <row r="230" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B230" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C230">
-        <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-1</v>
       </c>
       <c r="D230" t="s">
         <v>184</v>
@@ -13772,14 +13766,14 @@
     </row>
     <row r="231" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B231" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C231">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-2</v>
       </c>
       <c r="D231" t="s">
         <v>184</v>
@@ -13823,13 +13817,13 @@
     </row>
     <row r="232" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B232" s="2">
         <v>46316</v>
       </c>
       <c r="C232">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D232" t="s">
@@ -13874,13 +13868,13 @@
     </row>
     <row r="233" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B233" s="2">
         <v>46316</v>
       </c>
       <c r="C233">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D233" t="s">
@@ -13925,13 +13919,13 @@
     </row>
     <row r="234" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B234" s="2">
         <v>46316</v>
       </c>
       <c r="C234">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D234" t="s">
@@ -13976,14 +13970,14 @@
     </row>
     <row r="235" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B235" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C235">
-        <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-1</v>
       </c>
       <c r="D235" t="s">
         <v>184</v>
@@ -14027,14 +14021,14 @@
     </row>
     <row r="236" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B236" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C236">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-2</v>
       </c>
       <c r="D236" t="s">
         <v>184</v>
@@ -14078,14 +14072,14 @@
     </row>
     <row r="237" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B237" s="2">
-        <v>46301</v>
+        <v>46316</v>
       </c>
       <c r="C237">
-        <f t="shared" ca="1" si="3"/>
-        <v>-16</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-1</v>
       </c>
       <c r="D237" t="s">
         <v>184</v>
@@ -14129,14 +14123,14 @@
     </row>
     <row r="238" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B238" s="2">
-        <v>46316</v>
+        <v>46301</v>
       </c>
       <c r="C238">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-16</v>
       </c>
       <c r="D238" t="s">
         <v>184</v>
@@ -14180,13 +14174,13 @@
     </row>
     <row r="239" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B239" s="2">
         <v>46316</v>
       </c>
       <c r="C239">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D239" t="s">
@@ -14231,13 +14225,13 @@
     </row>
     <row r="240" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B240" s="2">
         <v>46316</v>
       </c>
       <c r="C240">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D240" t="s">
@@ -14268,10 +14262,10 @@
         <v>12</v>
       </c>
       <c r="M240" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="N240" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="P240" s="2">
         <v>46023</v>
@@ -14282,13 +14276,13 @@
     </row>
     <row r="241" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B241" s="2">
         <v>46316</v>
       </c>
       <c r="C241">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D241" t="s">
@@ -14333,13 +14327,13 @@
     </row>
     <row r="242" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B242" s="2">
         <v>46316</v>
       </c>
       <c r="C242">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D242" t="s">
@@ -14370,10 +14364,10 @@
         <v>12</v>
       </c>
       <c r="M242" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="N242" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P242" s="2">
         <v>46023</v>
@@ -14384,13 +14378,13 @@
     </row>
     <row r="243" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B243" s="2">
         <v>46316</v>
       </c>
       <c r="C243">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D243" t="s">
@@ -14412,7 +14406,7 @@
         <v>184</v>
       </c>
       <c r="J243" t="s">
-        <v>461</v>
+        <v>10</v>
       </c>
       <c r="K243" t="s">
         <v>11</v>
@@ -14421,10 +14415,10 @@
         <v>12</v>
       </c>
       <c r="M243" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="N243" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="P243" s="2">
         <v>46023</v>
@@ -14435,13 +14429,13 @@
     </row>
     <row r="244" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B244" s="2">
         <v>46316</v>
       </c>
       <c r="C244">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D244" t="s">
@@ -14463,7 +14457,7 @@
         <v>184</v>
       </c>
       <c r="J244" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K244" t="s">
         <v>11</v>
@@ -14486,13 +14480,13 @@
     </row>
     <row r="245" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B245" s="2">
         <v>46316</v>
       </c>
       <c r="C245">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D245" t="s">
@@ -14514,7 +14508,7 @@
         <v>184</v>
       </c>
       <c r="J245" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K245" t="s">
         <v>11</v>
@@ -14523,10 +14517,10 @@
         <v>12</v>
       </c>
       <c r="M245" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="N245" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P245" s="2">
         <v>46023</v>
@@ -14537,14 +14531,14 @@
     </row>
     <row r="246" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B246" s="2">
-        <v>46282</v>
+        <v>46316</v>
       </c>
       <c r="C246">
-        <f t="shared" ca="1" si="3"/>
-        <v>-35</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-1</v>
       </c>
       <c r="D246" t="s">
         <v>184</v>
@@ -14588,14 +14582,14 @@
     </row>
     <row r="247" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B247" s="2">
-        <v>46316</v>
+        <v>46282</v>
       </c>
       <c r="C247">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-35</v>
       </c>
       <c r="D247" t="s">
         <v>184</v>
@@ -14616,7 +14610,7 @@
         <v>184</v>
       </c>
       <c r="J247" t="s">
-        <v>28</v>
+        <v>462</v>
       </c>
       <c r="K247" t="s">
         <v>11</v>
@@ -14628,7 +14622,7 @@
         <v>178</v>
       </c>
       <c r="N247" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="P247" s="2">
         <v>46023</v>
@@ -14639,13 +14633,13 @@
     </row>
     <row r="248" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B248" s="2">
         <v>46316</v>
       </c>
       <c r="C248">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D248" t="s">
@@ -14667,19 +14661,19 @@
         <v>184</v>
       </c>
       <c r="J248" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K248" t="s">
         <v>11</v>
       </c>
       <c r="L248" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M248" t="s">
-        <v>463</v>
+        <v>178</v>
       </c>
       <c r="N248" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="P248" s="2">
         <v>46023</v>
@@ -14690,13 +14684,13 @@
     </row>
     <row r="249" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B249" s="2">
         <v>46316</v>
       </c>
       <c r="C249">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D249" t="s">
@@ -14741,13 +14735,13 @@
     </row>
     <row r="250" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B250" s="2">
         <v>46316</v>
       </c>
       <c r="C250">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D250" t="s">
@@ -14792,13 +14786,13 @@
     </row>
     <row r="251" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B251" s="2">
         <v>46316</v>
       </c>
       <c r="C251">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1</v>
       </c>
       <c r="D251" t="s">
@@ -14843,14 +14837,14 @@
     </row>
     <row r="252" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B252" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C252">
-        <f t="shared" ca="1" si="3"/>
-        <v>-3</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-1</v>
       </c>
       <c r="D252" t="s">
         <v>184</v>
@@ -14894,14 +14888,14 @@
     </row>
     <row r="253" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B253" s="2">
-        <v>46301</v>
+        <v>46314</v>
       </c>
       <c r="C253">
-        <f t="shared" ca="1" si="3"/>
-        <v>-16</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-3</v>
       </c>
       <c r="D253" t="s">
         <v>184</v>
@@ -14945,14 +14939,14 @@
     </row>
     <row r="254" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B254" s="2">
-        <v>46315</v>
+        <v>46301</v>
       </c>
       <c r="C254">
-        <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-16</v>
       </c>
       <c r="D254" t="s">
         <v>184</v>
@@ -14996,14 +14990,14 @@
     </row>
     <row r="255" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B255" s="2">
-        <v>46207</v>
+        <v>46315</v>
       </c>
       <c r="C255">
-        <f t="shared" ref="C255:C318" ca="1" si="4">B255-$R$1</f>
-        <v>-110</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-2</v>
       </c>
       <c r="D255" t="s">
         <v>184</v>
@@ -15047,14 +15041,14 @@
     </row>
     <row r="256" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B256" s="2">
-        <v>46316</v>
+        <v>46207</v>
       </c>
       <c r="C256">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <f t="shared" ref="C256:C319" ca="1" si="5">B256-$R$1</f>
+        <v>-110</v>
       </c>
       <c r="D256" t="s">
         <v>184</v>
@@ -15087,7 +15081,7 @@
         <v>463</v>
       </c>
       <c r="N256" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="P256" s="2">
         <v>46023</v>
@@ -15098,13 +15092,13 @@
     </row>
     <row r="257" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B257" s="2">
         <v>46316</v>
       </c>
       <c r="C257">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D257" t="s">
@@ -15138,7 +15132,7 @@
         <v>463</v>
       </c>
       <c r="N257" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P257" s="2">
         <v>46023</v>
@@ -15149,13 +15143,13 @@
     </row>
     <row r="258" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B258" s="2">
         <v>46316</v>
       </c>
       <c r="C258">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D258" t="s">
@@ -15200,13 +15194,13 @@
     </row>
     <row r="259" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B259" s="2">
         <v>46316</v>
       </c>
       <c r="C259">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D259" t="s">
@@ -15240,7 +15234,7 @@
         <v>463</v>
       </c>
       <c r="N259" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="P259" s="2">
         <v>46023</v>
@@ -15251,14 +15245,14 @@
     </row>
     <row r="260" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B260" s="2">
-        <v>46297</v>
+        <v>46316</v>
       </c>
       <c r="C260">
-        <f t="shared" ca="1" si="4"/>
-        <v>-20</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="D260" t="s">
         <v>184</v>
@@ -15302,14 +15296,14 @@
     </row>
     <row r="261" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B261" s="2">
-        <v>46316</v>
+        <v>46297</v>
       </c>
       <c r="C261">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-20</v>
       </c>
       <c r="D261" t="s">
         <v>184</v>
@@ -15353,13 +15347,13 @@
     </row>
     <row r="262" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B262" s="2">
         <v>46316</v>
       </c>
       <c r="C262">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D262" t="s">
@@ -15404,13 +15398,13 @@
     </row>
     <row r="263" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B263" s="2">
         <v>46316</v>
       </c>
       <c r="C263">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D263" t="s">
@@ -15455,14 +15449,14 @@
     </row>
     <row r="264" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B264" s="2">
-        <v>46302</v>
+        <v>46316</v>
       </c>
       <c r="C264">
-        <f t="shared" ca="1" si="4"/>
-        <v>-15</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="D264" t="s">
         <v>184</v>
@@ -15492,10 +15486,10 @@
         <v>23</v>
       </c>
       <c r="M264" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="N264" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="P264" s="2">
         <v>46023</v>
@@ -15506,14 +15500,14 @@
     </row>
     <row r="265" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B265" s="2">
-        <v>46177</v>
+        <v>46302</v>
       </c>
       <c r="C265">
-        <f t="shared" ca="1" si="4"/>
-        <v>-140</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-15</v>
       </c>
       <c r="D265" t="s">
         <v>184</v>
@@ -15557,14 +15551,14 @@
     </row>
     <row r="266" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B266" s="2">
-        <v>46316</v>
+        <v>46177</v>
       </c>
       <c r="C266">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-140</v>
       </c>
       <c r="D266" t="s">
         <v>184</v>
@@ -15608,14 +15602,14 @@
     </row>
     <row r="267" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B267" s="2">
-        <v>46299</v>
+        <v>46316</v>
       </c>
       <c r="C267">
-        <f t="shared" ca="1" si="4"/>
-        <v>-18</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="D267" t="s">
         <v>184</v>
@@ -15659,14 +15653,14 @@
     </row>
     <row r="268" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B268" s="2">
-        <v>46316</v>
+        <v>46299</v>
       </c>
       <c r="C268">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-18</v>
       </c>
       <c r="D268" t="s">
         <v>184</v>
@@ -15710,13 +15704,13 @@
     </row>
     <row r="269" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B269" s="2">
         <v>46316</v>
       </c>
       <c r="C269">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D269" t="s">
@@ -15738,19 +15732,19 @@
         <v>184</v>
       </c>
       <c r="J269" t="s">
-        <v>225</v>
+        <v>22</v>
       </c>
       <c r="K269" t="s">
         <v>11</v>
       </c>
       <c r="L269" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M269" t="s">
-        <v>119</v>
+        <v>456</v>
       </c>
       <c r="N269" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="P269" s="2">
         <v>46023</v>
@@ -15761,13 +15755,13 @@
     </row>
     <row r="270" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B270" s="2">
         <v>46316</v>
       </c>
       <c r="C270">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D270" t="s">
@@ -15812,13 +15806,13 @@
     </row>
     <row r="271" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B271" s="2">
         <v>46316</v>
       </c>
       <c r="C271">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D271" t="s">
@@ -15863,14 +15857,14 @@
     </row>
     <row r="272" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B272" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C272">
-        <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="D272" t="s">
         <v>184</v>
@@ -15914,14 +15908,14 @@
     </row>
     <row r="273" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B273" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C273">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-2</v>
       </c>
       <c r="D273" t="s">
         <v>184</v>
@@ -15965,13 +15959,13 @@
     </row>
     <row r="274" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B274" s="2">
         <v>46316</v>
       </c>
       <c r="C274">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D274" t="s">
@@ -16016,13 +16010,13 @@
     </row>
     <row r="275" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B275" s="2">
         <v>46316</v>
       </c>
       <c r="C275">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D275" t="s">
@@ -16067,13 +16061,13 @@
     </row>
     <row r="276" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B276" s="2">
         <v>46316</v>
       </c>
       <c r="C276">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D276" t="s">
@@ -16118,14 +16112,14 @@
     </row>
     <row r="277" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B277" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C277">
-        <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="D277" t="s">
         <v>184</v>
@@ -16169,14 +16163,14 @@
     </row>
     <row r="278" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B278" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C278">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-2</v>
       </c>
       <c r="D278" t="s">
         <v>184</v>
@@ -16197,19 +16191,19 @@
         <v>184</v>
       </c>
       <c r="J278" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="K278" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L278" t="s">
         <v>29</v>
       </c>
       <c r="M278" t="s">
-        <v>463</v>
+        <v>119</v>
       </c>
       <c r="N278" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="P278" s="2">
         <v>46023</v>
@@ -16220,13 +16214,13 @@
     </row>
     <row r="279" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B279" s="2">
         <v>46316</v>
       </c>
       <c r="C279">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D279" t="s">
@@ -16271,14 +16265,14 @@
     </row>
     <row r="280" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B280" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C280">
-        <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="D280" t="s">
         <v>184</v>
@@ -16322,14 +16316,14 @@
     </row>
     <row r="281" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B281" s="2">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="C281">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-3</v>
       </c>
       <c r="D281" t="s">
         <v>184</v>
@@ -16373,13 +16367,13 @@
     </row>
     <row r="282" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B282" s="2">
         <v>46316</v>
       </c>
       <c r="C282">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D282" t="s">
@@ -16424,14 +16418,14 @@
     </row>
     <row r="283" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B283" s="2">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="C283">
-        <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="D283" t="s">
         <v>184</v>
@@ -16475,14 +16469,14 @@
     </row>
     <row r="284" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B284" s="2">
-        <v>46316</v>
+        <v>46313</v>
       </c>
       <c r="C284">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-4</v>
       </c>
       <c r="D284" t="s">
         <v>184</v>
@@ -16526,14 +16520,14 @@
     </row>
     <row r="285" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B285" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C285">
-        <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="D285" t="s">
         <v>184</v>
@@ -16577,14 +16571,14 @@
     </row>
     <row r="286" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B286" s="2">
-        <v>46091</v>
+        <v>46314</v>
       </c>
       <c r="C286">
-        <f t="shared" ca="1" si="4"/>
-        <v>-226</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-3</v>
       </c>
       <c r="D286" t="s">
         <v>184</v>
@@ -16628,14 +16622,14 @@
     </row>
     <row r="287" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B287" s="2">
-        <v>46316</v>
+        <v>46091</v>
       </c>
       <c r="C287">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-226</v>
       </c>
       <c r="D287" t="s">
         <v>184</v>
@@ -16679,13 +16673,13 @@
     </row>
     <row r="288" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B288" s="2">
         <v>46316</v>
       </c>
       <c r="C288">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D288" t="s">
@@ -16730,13 +16724,13 @@
     </row>
     <row r="289" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B289" s="2">
         <v>46316</v>
       </c>
       <c r="C289">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D289" t="s">
@@ -16758,7 +16752,7 @@
         <v>184</v>
       </c>
       <c r="J289" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="K289" t="s">
         <v>33</v>
@@ -16781,13 +16775,13 @@
     </row>
     <row r="290" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B290" s="2">
         <v>46316</v>
       </c>
       <c r="C290">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D290" t="s">
@@ -16832,13 +16826,13 @@
     </row>
     <row r="291" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B291" s="2">
         <v>46316</v>
       </c>
       <c r="C291">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D291" t="s">
@@ -16883,13 +16877,13 @@
     </row>
     <row r="292" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B292" s="2">
         <v>46316</v>
       </c>
       <c r="C292">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D292" t="s">
@@ -16934,13 +16928,13 @@
     </row>
     <row r="293" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B293" s="2">
         <v>46316</v>
       </c>
       <c r="C293">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D293" t="s">
@@ -16985,13 +16979,13 @@
     </row>
     <row r="294" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B294" s="2">
         <v>46316</v>
       </c>
       <c r="C294">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D294" t="s">
@@ -17036,14 +17030,14 @@
     </row>
     <row r="295" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B295" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C295">
-        <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="D295" t="s">
         <v>184</v>
@@ -17087,14 +17081,14 @@
     </row>
     <row r="296" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B296" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C296">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-2</v>
       </c>
       <c r="D296" t="s">
         <v>184</v>
@@ -17138,13 +17132,13 @@
     </row>
     <row r="297" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B297" s="2">
         <v>46316</v>
       </c>
       <c r="C297">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D297" t="s">
@@ -17189,13 +17183,13 @@
     </row>
     <row r="298" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B298" s="2">
         <v>46316</v>
       </c>
       <c r="C298">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D298" t="s">
@@ -17240,13 +17234,13 @@
     </row>
     <row r="299" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B299" s="2">
         <v>46316</v>
       </c>
       <c r="C299">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D299" t="s">
@@ -17291,13 +17285,13 @@
     </row>
     <row r="300" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B300" s="2">
         <v>46316</v>
       </c>
       <c r="C300">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D300" t="s">
@@ -17342,13 +17336,13 @@
     </row>
     <row r="301" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B301" s="2">
         <v>46316</v>
       </c>
       <c r="C301">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D301" t="s">
@@ -17376,13 +17370,13 @@
         <v>33</v>
       </c>
       <c r="L301" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M301" t="s">
-        <v>119</v>
+        <v>463</v>
       </c>
       <c r="N301" t="s">
-        <v>120</v>
+        <v>448</v>
       </c>
       <c r="P301" s="2">
         <v>46023</v>
@@ -17393,13 +17387,13 @@
     </row>
     <row r="302" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B302" s="2">
         <v>46316</v>
       </c>
       <c r="C302">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D302" t="s">
@@ -17444,13 +17438,13 @@
     </row>
     <row r="303" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B303" s="2">
         <v>46316</v>
       </c>
       <c r="C303">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D303" t="s">
@@ -17495,13 +17489,13 @@
     </row>
     <row r="304" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B304" s="2">
         <v>46316</v>
       </c>
       <c r="C304">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D304" t="s">
@@ -17546,13 +17540,13 @@
     </row>
     <row r="305" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B305" s="2">
         <v>46316</v>
       </c>
       <c r="C305">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D305" t="s">
@@ -17597,13 +17591,13 @@
     </row>
     <row r="306" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B306" s="2">
         <v>46316</v>
       </c>
       <c r="C306">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D306" t="s">
@@ -17631,13 +17625,13 @@
         <v>33</v>
       </c>
       <c r="L306" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M306" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="N306" t="s">
-        <v>449</v>
+        <v>120</v>
       </c>
       <c r="P306" s="2">
         <v>46023</v>
@@ -17648,14 +17642,14 @@
     </row>
     <row r="307" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B307" s="2">
-        <v>46302</v>
+        <v>46316</v>
       </c>
       <c r="C307">
-        <f t="shared" ca="1" si="4"/>
-        <v>-15</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="D307" t="s">
         <v>184</v>
@@ -17699,14 +17693,14 @@
     </row>
     <row r="308" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B308" s="2">
-        <v>46316</v>
+        <v>46302</v>
       </c>
       <c r="C308">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-15</v>
       </c>
       <c r="D308" t="s">
         <v>184</v>
@@ -17750,13 +17744,13 @@
     </row>
     <row r="309" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B309" s="2">
         <v>46316</v>
       </c>
       <c r="C309">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D309" t="s">
@@ -17801,13 +17795,13 @@
     </row>
     <row r="310" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B310" s="2">
         <v>46316</v>
       </c>
       <c r="C310">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D310" t="s">
@@ -17852,13 +17846,13 @@
     </row>
     <row r="311" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B311" s="2">
         <v>46316</v>
       </c>
       <c r="C311">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D311" t="s">
@@ -17903,13 +17897,13 @@
     </row>
     <row r="312" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B312" s="2">
         <v>46316</v>
       </c>
       <c r="C312">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D312" t="s">
@@ -17937,13 +17931,13 @@
         <v>33</v>
       </c>
       <c r="L312" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M312" t="s">
         <v>24</v>
       </c>
       <c r="N312" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P312" s="2">
         <v>46023</v>
@@ -17954,14 +17948,14 @@
     </row>
     <row r="313" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B313" s="2">
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="C313">
-        <f t="shared" ca="1" si="4"/>
-        <v>-8</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="D313" t="s">
         <v>184</v>
@@ -18005,14 +17999,14 @@
     </row>
     <row r="314" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B314" s="2">
-        <v>46316</v>
+        <v>46309</v>
       </c>
       <c r="C314">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-8</v>
       </c>
       <c r="D314" t="s">
         <v>184</v>
@@ -18056,13 +18050,13 @@
     </row>
     <row r="315" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B315" s="2">
         <v>46316</v>
       </c>
       <c r="C315">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="D315" t="s">
@@ -18090,13 +18084,13 @@
         <v>33</v>
       </c>
       <c r="L315" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="M315" t="s">
         <v>24</v>
       </c>
       <c r="N315" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P315" s="2">
         <v>46023</v>
@@ -18107,14 +18101,14 @@
     </row>
     <row r="316" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B316" s="2">
-        <v>46244</v>
+        <v>46316</v>
       </c>
       <c r="C316">
-        <f t="shared" ca="1" si="4"/>
-        <v>-73</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="D316" t="s">
         <v>184</v>
@@ -18158,14 +18152,14 @@
     </row>
     <row r="317" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B317" s="2">
-        <v>46316</v>
+        <v>46244</v>
       </c>
       <c r="C317">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-73</v>
       </c>
       <c r="D317" t="s">
         <v>184</v>
@@ -18186,16 +18180,16 @@
         <v>184</v>
       </c>
       <c r="J317" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="K317" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L317" t="s">
         <v>12</v>
       </c>
       <c r="M317" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="N317" t="s">
         <v>449</v>
@@ -18209,14 +18203,14 @@
     </row>
     <row r="318" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B318" s="2">
-        <v>46306</v>
+        <v>46316</v>
       </c>
       <c r="C318">
-        <f t="shared" ca="1" si="4"/>
-        <v>-11</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="D318" t="s">
         <v>184</v>
@@ -18237,7 +18231,7 @@
         <v>184</v>
       </c>
       <c r="J318" t="s">
-        <v>461</v>
+        <v>45</v>
       </c>
       <c r="K318" t="s">
         <v>11</v>
@@ -18260,14 +18254,14 @@
     </row>
     <row r="319" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B319" s="2">
-        <v>46316</v>
+        <v>46306</v>
       </c>
       <c r="C319">
-        <f t="shared" ref="C319:C382" ca="1" si="5">B319-$R$1</f>
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-11</v>
       </c>
       <c r="D319" t="s">
         <v>184</v>
@@ -18288,7 +18282,7 @@
         <v>184</v>
       </c>
       <c r="J319" t="s">
-        <v>45</v>
+        <v>461</v>
       </c>
       <c r="K319" t="s">
         <v>11</v>
@@ -18311,14 +18305,14 @@
     </row>
     <row r="320" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B320" s="2">
-        <v>46307</v>
+        <v>46316</v>
       </c>
       <c r="C320">
-        <f t="shared" ca="1" si="5"/>
-        <v>-10</v>
+        <f t="shared" ref="C320:C383" ca="1" si="6">B320-$R$1</f>
+        <v>-1</v>
       </c>
       <c r="D320" t="s">
         <v>184</v>
@@ -18339,7 +18333,7 @@
         <v>184</v>
       </c>
       <c r="J320" t="s">
-        <v>461</v>
+        <v>45</v>
       </c>
       <c r="K320" t="s">
         <v>11</v>
@@ -18362,14 +18356,14 @@
     </row>
     <row r="321" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B321" s="2">
-        <v>46240</v>
+        <v>46307</v>
       </c>
       <c r="C321">
-        <f t="shared" ca="1" si="5"/>
-        <v>-77</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-10</v>
       </c>
       <c r="D321" t="s">
         <v>184</v>
@@ -18413,14 +18407,14 @@
     </row>
     <row r="322" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B322" s="2">
-        <v>46298</v>
+        <v>46240</v>
       </c>
       <c r="C322">
-        <f t="shared" ca="1" si="5"/>
-        <v>-19</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-77</v>
       </c>
       <c r="D322" t="s">
         <v>184</v>
@@ -18464,14 +18458,14 @@
     </row>
     <row r="323" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B323" s="2">
-        <v>46316</v>
+        <v>46298</v>
       </c>
       <c r="C323">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-19</v>
       </c>
       <c r="D323" t="s">
         <v>184</v>
@@ -18515,13 +18509,13 @@
     </row>
     <row r="324" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B324" s="2">
         <v>46316</v>
       </c>
       <c r="C324">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D324" t="s">
@@ -18543,7 +18537,7 @@
         <v>184</v>
       </c>
       <c r="J324" t="s">
-        <v>45</v>
+        <v>461</v>
       </c>
       <c r="K324" t="s">
         <v>11</v>
@@ -18566,13 +18560,13 @@
     </row>
     <row r="325" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B325" s="2">
         <v>46316</v>
       </c>
       <c r="C325">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D325" t="s">
@@ -18617,13 +18611,13 @@
     </row>
     <row r="326" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B326" s="2">
         <v>46316</v>
       </c>
       <c r="C326">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D326" t="s">
@@ -18668,14 +18662,14 @@
     </row>
     <row r="327" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B327" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C327">
-        <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-1</v>
       </c>
       <c r="D327" t="s">
         <v>184</v>
@@ -18696,7 +18690,7 @@
         <v>184</v>
       </c>
       <c r="J327" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="K327" t="s">
         <v>11</v>
@@ -18705,10 +18699,10 @@
         <v>12</v>
       </c>
       <c r="M327" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="N327" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P327" s="2">
         <v>46023</v>
@@ -18719,14 +18713,14 @@
     </row>
     <row r="328" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B328" s="2">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="C328">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-3</v>
       </c>
       <c r="D328" t="s">
         <v>184</v>
@@ -18770,14 +18764,14 @@
     </row>
     <row r="329" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B329" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C329">
-        <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-1</v>
       </c>
       <c r="D329" t="s">
         <v>184</v>
@@ -18804,13 +18798,13 @@
         <v>11</v>
       </c>
       <c r="L329" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M329" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="N329" t="s">
-        <v>120</v>
+        <v>446</v>
       </c>
       <c r="P329" s="2">
         <v>46023</v>
@@ -18821,14 +18815,14 @@
     </row>
     <row r="330" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B330" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C330">
-        <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-3</v>
       </c>
       <c r="D330" t="s">
         <v>184</v>
@@ -18872,14 +18866,14 @@
     </row>
     <row r="331" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B331" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C331">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-2</v>
       </c>
       <c r="D331" t="s">
         <v>184</v>
@@ -18923,13 +18917,13 @@
     </row>
     <row r="332" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B332" s="2">
         <v>46316</v>
       </c>
       <c r="C332">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D332" t="s">
@@ -18974,14 +18968,14 @@
     </row>
     <row r="333" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B333" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C333">
-        <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-1</v>
       </c>
       <c r="D333" t="s">
         <v>184</v>
@@ -19025,14 +19019,14 @@
     </row>
     <row r="334" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B334" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C334">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-2</v>
       </c>
       <c r="D334" t="s">
         <v>184</v>
@@ -19076,14 +19070,14 @@
     </row>
     <row r="335" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B335" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C335">
-        <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-1</v>
       </c>
       <c r="D335" t="s">
         <v>184</v>
@@ -19127,14 +19121,14 @@
     </row>
     <row r="336" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B336" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C336">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-2</v>
       </c>
       <c r="D336" t="s">
         <v>184</v>
@@ -19178,14 +19172,14 @@
     </row>
     <row r="337" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B337" s="2">
-        <v>46307</v>
+        <v>46316</v>
       </c>
       <c r="C337">
-        <f t="shared" ca="1" si="5"/>
-        <v>-10</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-1</v>
       </c>
       <c r="D337" t="s">
         <v>184</v>
@@ -19229,14 +19223,14 @@
     </row>
     <row r="338" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B338" s="2">
-        <v>46316</v>
+        <v>46307</v>
       </c>
       <c r="C338">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-10</v>
       </c>
       <c r="D338" t="s">
         <v>184</v>
@@ -19280,13 +19274,13 @@
     </row>
     <row r="339" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B339" s="2">
         <v>46316</v>
       </c>
       <c r="C339">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D339" t="s">
@@ -19331,13 +19325,13 @@
     </row>
     <row r="340" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B340" s="2">
         <v>46316</v>
       </c>
       <c r="C340">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D340" t="s">
@@ -19359,19 +19353,19 @@
         <v>184</v>
       </c>
       <c r="J340" t="s">
-        <v>460</v>
+        <v>10</v>
       </c>
       <c r="K340" t="s">
         <v>11</v>
       </c>
       <c r="L340" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M340" t="s">
         <v>119</v>
       </c>
       <c r="N340" t="s">
-        <v>449</v>
+        <v>120</v>
       </c>
       <c r="P340" s="2">
         <v>46023</v>
@@ -19382,14 +19376,14 @@
     </row>
     <row r="341" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B341" s="2">
-        <v>46308</v>
+        <v>46316</v>
       </c>
       <c r="C341">
-        <f t="shared" ca="1" si="5"/>
-        <v>-9</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-1</v>
       </c>
       <c r="D341" t="s">
         <v>184</v>
@@ -19410,7 +19404,7 @@
         <v>184</v>
       </c>
       <c r="J341" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K341" t="s">
         <v>11</v>
@@ -19433,14 +19427,14 @@
     </row>
     <row r="342" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B342" s="2">
-        <v>46316</v>
+        <v>46308</v>
       </c>
       <c r="C342">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-9</v>
       </c>
       <c r="D342" t="s">
         <v>184</v>
@@ -19461,7 +19455,7 @@
         <v>184</v>
       </c>
       <c r="J342" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K342" t="s">
         <v>11</v>
@@ -19484,13 +19478,13 @@
     </row>
     <row r="343" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B343" s="2">
         <v>46316</v>
       </c>
       <c r="C343">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D343" t="s">
@@ -19535,14 +19529,14 @@
     </row>
     <row r="344" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B344" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C344">
-        <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-1</v>
       </c>
       <c r="D344" t="s">
         <v>184</v>
@@ -19563,7 +19557,7 @@
         <v>184</v>
       </c>
       <c r="J344" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K344" t="s">
         <v>11</v>
@@ -19586,14 +19580,14 @@
     </row>
     <row r="345" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B345" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C345">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-2</v>
       </c>
       <c r="D345" t="s">
         <v>184</v>
@@ -19637,14 +19631,14 @@
     </row>
     <row r="346" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B346" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C346">
-        <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-1</v>
       </c>
       <c r="D346" t="s">
         <v>184</v>
@@ -19665,7 +19659,7 @@
         <v>184</v>
       </c>
       <c r="J346" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K346" t="s">
         <v>11</v>
@@ -19688,14 +19682,14 @@
     </row>
     <row r="347" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B347" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C347">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-2</v>
       </c>
       <c r="D347" t="s">
         <v>184</v>
@@ -19716,19 +19710,19 @@
         <v>184</v>
       </c>
       <c r="J347" t="s">
-        <v>22</v>
+        <v>460</v>
       </c>
       <c r="K347" t="s">
         <v>11</v>
       </c>
       <c r="L347" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M347" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="N347" t="s">
-        <v>120</v>
+        <v>449</v>
       </c>
       <c r="P347" s="2">
         <v>46023</v>
@@ -19739,13 +19733,13 @@
     </row>
     <row r="348" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B348" s="2">
         <v>46316</v>
       </c>
       <c r="C348">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D348" t="s">
@@ -19767,19 +19761,19 @@
         <v>184</v>
       </c>
       <c r="J348" t="s">
-        <v>459</v>
+        <v>22</v>
       </c>
       <c r="K348" t="s">
         <v>11</v>
       </c>
       <c r="L348" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M348" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="N348" t="s">
-        <v>449</v>
+        <v>120</v>
       </c>
       <c r="P348" s="2">
         <v>46023</v>
@@ -19790,13 +19784,13 @@
     </row>
     <row r="349" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B349" s="2">
         <v>46316</v>
       </c>
       <c r="C349">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D349" t="s">
@@ -19841,14 +19835,14 @@
     </row>
     <row r="350" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B350" s="2">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="C350">
-        <f t="shared" ca="1" si="5"/>
-        <v>-7</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-1</v>
       </c>
       <c r="D350" t="s">
         <v>184</v>
@@ -19892,14 +19886,14 @@
     </row>
     <row r="351" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B351" s="2">
-        <v>46316</v>
+        <v>46310</v>
       </c>
       <c r="C351">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-7</v>
       </c>
       <c r="D351" t="s">
         <v>184</v>
@@ -19920,19 +19914,19 @@
         <v>184</v>
       </c>
       <c r="J351" t="s">
-        <v>101</v>
+        <v>459</v>
       </c>
       <c r="K351" t="s">
         <v>11</v>
       </c>
       <c r="L351" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M351" t="s">
         <v>119</v>
       </c>
       <c r="N351" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P351" s="2">
         <v>46023</v>
@@ -19943,13 +19937,13 @@
     </row>
     <row r="352" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B352" s="2">
         <v>46316</v>
       </c>
       <c r="C352">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D352" t="s">
@@ -19971,7 +19965,7 @@
         <v>184</v>
       </c>
       <c r="J352" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="K352" t="s">
         <v>11</v>
@@ -19994,13 +19988,13 @@
     </row>
     <row r="353" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B353" s="2">
         <v>46316</v>
       </c>
       <c r="C353">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D353" t="s">
@@ -20045,13 +20039,13 @@
     </row>
     <row r="354" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B354" s="2">
         <v>46316</v>
       </c>
       <c r="C354">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D354" t="s">
@@ -20073,19 +20067,19 @@
         <v>184</v>
       </c>
       <c r="J354" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="K354" t="s">
         <v>11</v>
       </c>
       <c r="L354" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M354" t="s">
         <v>119</v>
       </c>
       <c r="N354" t="s">
-        <v>120</v>
+        <v>447</v>
       </c>
       <c r="P354" s="2">
         <v>46023</v>
@@ -20096,14 +20090,14 @@
     </row>
     <row r="355" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B355" s="2">
-        <v>46298</v>
+        <v>46316</v>
       </c>
       <c r="C355">
-        <f t="shared" ca="1" si="5"/>
-        <v>-19</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-1</v>
       </c>
       <c r="D355" t="s">
         <v>184</v>
@@ -20147,14 +20141,14 @@
     </row>
     <row r="356" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B356" s="2">
-        <v>46316</v>
+        <v>46298</v>
       </c>
       <c r="C356">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-19</v>
       </c>
       <c r="D356" t="s">
         <v>184</v>
@@ -20175,7 +20169,7 @@
         <v>184</v>
       </c>
       <c r="J356" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="K356" t="s">
         <v>11</v>
@@ -20198,13 +20192,13 @@
     </row>
     <row r="357" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B357" s="2">
         <v>46316</v>
       </c>
       <c r="C357">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D357" t="s">
@@ -20249,13 +20243,13 @@
     </row>
     <row r="358" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B358" s="2">
         <v>46316</v>
       </c>
       <c r="C358">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D358" t="s">
@@ -20277,7 +20271,7 @@
         <v>184</v>
       </c>
       <c r="J358" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="K358" t="s">
         <v>11</v>
@@ -20300,13 +20294,13 @@
     </row>
     <row r="359" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B359" s="2">
         <v>46316</v>
       </c>
       <c r="C359">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D359" t="s">
@@ -20351,14 +20345,14 @@
     </row>
     <row r="360" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B360" s="2">
-        <v>46307</v>
+        <v>46316</v>
       </c>
       <c r="C360">
-        <f t="shared" ca="1" si="5"/>
-        <v>-10</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-1</v>
       </c>
       <c r="D360" t="s">
         <v>184</v>
@@ -20379,7 +20373,7 @@
         <v>184</v>
       </c>
       <c r="J360" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="K360" t="s">
         <v>11</v>
@@ -20402,14 +20396,14 @@
     </row>
     <row r="361" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B361" s="2">
-        <v>46313</v>
+        <v>46307</v>
       </c>
       <c r="C361">
-        <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-10</v>
       </c>
       <c r="D361" t="s">
         <v>184</v>
@@ -20430,7 +20424,7 @@
         <v>184</v>
       </c>
       <c r="J361" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="K361" t="s">
         <v>11</v>
@@ -20453,14 +20447,14 @@
     </row>
     <row r="362" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B362" s="2">
-        <v>46316</v>
+        <v>46313</v>
       </c>
       <c r="C362">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-4</v>
       </c>
       <c r="D362" t="s">
         <v>184</v>
@@ -20481,7 +20475,7 @@
         <v>184</v>
       </c>
       <c r="J362" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="K362" t="s">
         <v>11</v>
@@ -20504,13 +20498,13 @@
     </row>
     <row r="363" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B363" s="2">
         <v>46316</v>
       </c>
       <c r="C363">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D363" t="s">
@@ -20555,13 +20549,13 @@
     </row>
     <row r="364" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B364" s="2">
         <v>46316</v>
       </c>
       <c r="C364">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D364" t="s">
@@ -20589,13 +20583,13 @@
         <v>11</v>
       </c>
       <c r="L364" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M364" t="s">
         <v>119</v>
       </c>
       <c r="N364" t="s">
-        <v>447</v>
+        <v>120</v>
       </c>
       <c r="P364" s="2">
         <v>46023</v>
@@ -20606,13 +20600,13 @@
     </row>
     <row r="365" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B365" s="2">
         <v>46316</v>
       </c>
       <c r="C365">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D365" t="s">
@@ -20657,13 +20651,13 @@
     </row>
     <row r="366" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B366" s="2">
         <v>46316</v>
       </c>
       <c r="C366">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D366" t="s">
@@ -20708,13 +20702,13 @@
     </row>
     <row r="367" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B367" s="2">
         <v>46316</v>
       </c>
       <c r="C367">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D367" t="s">
@@ -20759,13 +20753,13 @@
     </row>
     <row r="368" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B368" s="2">
         <v>46316</v>
       </c>
       <c r="C368">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D368" t="s">
@@ -20810,13 +20804,13 @@
     </row>
     <row r="369" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B369" s="2">
         <v>46316</v>
       </c>
       <c r="C369">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D369" t="s">
@@ -20861,14 +20855,14 @@
     </row>
     <row r="370" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B370" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C370">
-        <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-1</v>
       </c>
       <c r="D370" t="s">
         <v>184</v>
@@ -20895,13 +20889,13 @@
         <v>11</v>
       </c>
       <c r="L370" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M370" t="s">
         <v>119</v>
       </c>
       <c r="N370" t="s">
-        <v>120</v>
+        <v>447</v>
       </c>
       <c r="P370" s="2">
         <v>46023</v>
@@ -20912,13 +20906,13 @@
     </row>
     <row r="371" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B371" s="2">
         <v>46315</v>
       </c>
       <c r="C371">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-2</v>
       </c>
       <c r="D371" t="s">
@@ -20963,14 +20957,14 @@
     </row>
     <row r="372" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B372" s="2">
-        <v>46309</v>
+        <v>46315</v>
       </c>
       <c r="C372">
-        <f t="shared" ca="1" si="5"/>
-        <v>-8</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-2</v>
       </c>
       <c r="D372" t="s">
         <v>184</v>
@@ -21014,14 +21008,14 @@
     </row>
     <row r="373" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B373" s="2">
-        <v>46316</v>
+        <v>46309</v>
       </c>
       <c r="C373">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-8</v>
       </c>
       <c r="D373" t="s">
         <v>184</v>
@@ -21065,13 +21059,13 @@
     </row>
     <row r="374" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B374" s="2">
         <v>46316</v>
       </c>
       <c r="C374">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D374" t="s">
@@ -21116,13 +21110,13 @@
     </row>
     <row r="375" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B375" s="2">
         <v>46316</v>
       </c>
       <c r="C375">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D375" t="s">
@@ -21167,13 +21161,13 @@
     </row>
     <row r="376" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B376" s="2">
         <v>46316</v>
       </c>
       <c r="C376">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D376" t="s">
@@ -21218,13 +21212,13 @@
     </row>
     <row r="377" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B377" s="2">
         <v>46316</v>
       </c>
       <c r="C377">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D377" t="s">
@@ -21269,13 +21263,13 @@
     </row>
     <row r="378" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B378" s="2">
         <v>46316</v>
       </c>
       <c r="C378">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D378" t="s">
@@ -21297,19 +21291,19 @@
         <v>184</v>
       </c>
       <c r="J378" t="s">
-        <v>225</v>
+        <v>22</v>
       </c>
       <c r="K378" t="s">
         <v>11</v>
       </c>
       <c r="L378" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M378" t="s">
         <v>119</v>
       </c>
       <c r="N378" t="s">
-        <v>447</v>
+        <v>120</v>
       </c>
       <c r="P378" s="2">
         <v>46023</v>
@@ -21320,13 +21314,13 @@
     </row>
     <row r="379" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B379" s="2">
         <v>46316</v>
       </c>
       <c r="C379">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D379" t="s">
@@ -21354,13 +21348,13 @@
         <v>11</v>
       </c>
       <c r="L379" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M379" t="s">
         <v>119</v>
       </c>
       <c r="N379" t="s">
-        <v>120</v>
+        <v>447</v>
       </c>
       <c r="P379" s="2">
         <v>46023</v>
@@ -21371,13 +21365,13 @@
     </row>
     <row r="380" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B380" s="2">
         <v>46316</v>
       </c>
       <c r="C380">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
       <c r="D380" t="s">
@@ -21422,14 +21416,14 @@
     </row>
     <row r="381" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B381" s="2">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="C381">
-        <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-1</v>
       </c>
       <c r="D381" t="s">
         <v>184</v>
@@ -21450,19 +21444,19 @@
         <v>184</v>
       </c>
       <c r="J381" t="s">
-        <v>118</v>
+        <v>225</v>
       </c>
       <c r="K381" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L381" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M381" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="N381" t="s">
-        <v>449</v>
+        <v>120</v>
       </c>
       <c r="P381" s="2">
         <v>46023</v>
@@ -21473,14 +21467,14 @@
     </row>
     <row r="382" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B382" s="2">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="C382">
-        <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-5</v>
       </c>
       <c r="D382" t="s">
         <v>184</v>
@@ -21524,14 +21518,14 @@
     </row>
     <row r="383" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B383" s="2">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C383">
-        <f t="shared" ref="C383:C390" ca="1" si="6">B383-$R$1</f>
-        <v>-6</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-3</v>
       </c>
       <c r="D383" t="s">
         <v>184</v>
@@ -21575,14 +21569,14 @@
     </row>
     <row r="384" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B384" s="2">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="C384">
-        <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <f t="shared" ref="C384:C391" ca="1" si="7">B384-$R$1</f>
+        <v>-6</v>
       </c>
       <c r="D384" t="s">
         <v>184</v>
@@ -21615,7 +21609,7 @@
         <v>24</v>
       </c>
       <c r="N384" t="s">
-        <v>120</v>
+        <v>449</v>
       </c>
       <c r="P384" s="2">
         <v>46023</v>
@@ -21626,14 +21620,14 @@
     </row>
     <row r="385" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B385" s="2">
-        <v>0</v>
+        <v>46314</v>
       </c>
       <c r="C385">
-        <f t="shared" ca="1" si="6"/>
-        <v>-46317</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>-3</v>
       </c>
       <c r="D385" t="s">
         <v>184</v>
@@ -21654,19 +21648,19 @@
         <v>184</v>
       </c>
       <c r="J385" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="K385" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L385" t="s">
         <v>12</v>
       </c>
       <c r="M385" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="N385" t="s">
-        <v>458</v>
+        <v>120</v>
       </c>
       <c r="P385" s="2">
         <v>46023</v>
@@ -21677,13 +21671,13 @@
     </row>
     <row r="386" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B386" s="2">
         <v>0</v>
       </c>
       <c r="C386">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="7"/>
         <v>-46317</v>
       </c>
       <c r="D386" t="s">
@@ -21728,13 +21722,13 @@
     </row>
     <row r="387" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B387" s="2">
         <v>0</v>
       </c>
       <c r="C387">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="7"/>
         <v>-46317</v>
       </c>
       <c r="D387" t="s">
@@ -21779,13 +21773,13 @@
     </row>
     <row r="388" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B388" s="2">
         <v>0</v>
       </c>
       <c r="C388">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="7"/>
         <v>-46317</v>
       </c>
       <c r="D388" t="s">
@@ -21830,14 +21824,14 @@
     </row>
     <row r="389" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B389" s="2">
-        <v>46316</v>
+        <v>0</v>
       </c>
       <c r="C389">
-        <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>-46317</v>
       </c>
       <c r="D389" t="s">
         <v>184</v>
@@ -21858,7 +21852,7 @@
         <v>184</v>
       </c>
       <c r="J389" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="K389" t="s">
         <v>11</v>
@@ -21867,10 +21861,10 @@
         <v>12</v>
       </c>
       <c r="M389" t="s">
-        <v>178</v>
+        <v>88</v>
       </c>
       <c r="N389" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="P389" s="2">
         <v>46023</v>
@@ -21881,14 +21875,14 @@
     </row>
     <row r="390" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B390" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C390">
-        <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>-1</v>
       </c>
       <c r="D390" t="s">
         <v>184</v>
@@ -21921,30 +21915,73 @@
         <v>178</v>
       </c>
       <c r="N390" t="s">
+        <v>446</v>
+      </c>
+      <c r="P390" s="2">
+        <v>46023</v>
+      </c>
+      <c r="Q390" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="391" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>443</v>
+      </c>
+      <c r="B391" s="2">
+        <v>46314</v>
+      </c>
+      <c r="C391">
+        <f t="shared" ca="1" si="7"/>
+        <v>-3</v>
+      </c>
+      <c r="D391" t="s">
+        <v>184</v>
+      </c>
+      <c r="E391" t="s">
+        <v>184</v>
+      </c>
+      <c r="F391" t="s">
+        <v>184</v>
+      </c>
+      <c r="G391" t="s">
+        <v>184</v>
+      </c>
+      <c r="H391" t="s">
+        <v>184</v>
+      </c>
+      <c r="I391" t="s">
+        <v>184</v>
+      </c>
+      <c r="J391" t="s">
+        <v>10</v>
+      </c>
+      <c r="K391" t="s">
+        <v>11</v>
+      </c>
+      <c r="L391" t="s">
+        <v>12</v>
+      </c>
+      <c r="M391" t="s">
+        <v>178</v>
+      </c>
+      <c r="N391" t="s">
         <v>449</v>
       </c>
-      <c r="P390" s="2">
-        <v>46023</v>
-      </c>
-      <c r="Q390" s="2">
+      <c r="P391" s="2">
+        <v>46023</v>
+      </c>
+      <c r="Q391" s="2">
         <v>46023</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R391" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -21954,6 +21991,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22218,20 +22264,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="440" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{270C6A77-B1B7-4DB2-B60E-2ED701F49D1B}"/>
+  <xr:revisionPtr revIDLastSave="446" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F743263-5561-4440-98BF-18E2B83EC2C2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="R1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1875,11 +1875,11 @@
         <v>9</v>
       </c>
       <c r="B2" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C2">
         <f ca="1">B2-$R$1</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D2" t="s">
         <v>184</v>
@@ -1927,7 +1927,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C66" ca="1" si="0">B3-$R$1</f>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D4" t="s">
         <v>184</v>
@@ -2031,11 +2031,11 @@
         <v>16</v>
       </c>
       <c r="B5" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D5" t="s">
         <v>184</v>
@@ -2083,11 +2083,11 @@
         <v>17</v>
       </c>
       <c r="B6" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D6" t="s">
         <v>184</v>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D7" t="s">
         <v>184</v>
@@ -2187,11 +2187,11 @@
         <v>19</v>
       </c>
       <c r="B8" s="2">
-        <v>46311</v>
+        <v>46317</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D8" t="s">
         <v>184</v>
@@ -2239,11 +2239,11 @@
         <v>20</v>
       </c>
       <c r="B9" s="2">
-        <v>46312</v>
+        <v>46317</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D9" t="s">
         <v>184</v>
@@ -2291,11 +2291,11 @@
         <v>21</v>
       </c>
       <c r="B10" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D10" t="s">
         <v>184</v>
@@ -2345,11 +2345,11 @@
         <v>26</v>
       </c>
       <c r="B11" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D11" t="s">
         <v>184</v>
@@ -2399,11 +2399,11 @@
         <v>27</v>
       </c>
       <c r="B12" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D12" t="s">
         <v>184</v>
@@ -2453,11 +2453,11 @@
         <v>31</v>
       </c>
       <c r="B13" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D13" t="s">
         <v>184</v>
@@ -2507,11 +2507,11 @@
         <v>36</v>
       </c>
       <c r="B14" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D14" t="s">
         <v>184</v>
@@ -2561,11 +2561,11 @@
         <v>37</v>
       </c>
       <c r="B15" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D15" t="s">
         <v>184</v>
@@ -2615,11 +2615,11 @@
         <v>38</v>
       </c>
       <c r="B16" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D16" t="s">
         <v>184</v>
@@ -2669,11 +2669,11 @@
         <v>39</v>
       </c>
       <c r="B17" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D17" t="s">
         <v>184</v>
@@ -2723,11 +2723,11 @@
         <v>40</v>
       </c>
       <c r="B18" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D18" t="s">
         <v>184</v>
@@ -2777,11 +2777,11 @@
         <v>41</v>
       </c>
       <c r="B19" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D19" t="s">
         <v>184</v>
@@ -2831,11 +2831,11 @@
         <v>42</v>
       </c>
       <c r="B20" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D20" t="s">
         <v>184</v>
@@ -2885,11 +2885,11 @@
         <v>43</v>
       </c>
       <c r="B21" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D21" t="s">
         <v>184</v>
@@ -2939,11 +2939,11 @@
         <v>44</v>
       </c>
       <c r="B22" s="2">
-        <v>46309</v>
+        <v>46317</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="0"/>
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="D22" t="s">
         <v>184</v>
@@ -2993,11 +2993,11 @@
         <v>46</v>
       </c>
       <c r="B23" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D23" t="s">
         <v>184</v>
@@ -3047,11 +3047,11 @@
         <v>47</v>
       </c>
       <c r="B24" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D24" t="s">
         <v>184</v>
@@ -3101,11 +3101,11 @@
         <v>48</v>
       </c>
       <c r="B25" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D25" t="s">
         <v>184</v>
@@ -3155,11 +3155,11 @@
         <v>49</v>
       </c>
       <c r="B26" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D26" t="s">
         <v>184</v>
@@ -3209,7 +3209,7 @@
         <v>50</v>
       </c>
       <c r="B27" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="0"/>
@@ -3263,11 +3263,11 @@
         <v>51</v>
       </c>
       <c r="B28" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D28" t="s">
         <v>184</v>
@@ -3317,11 +3317,11 @@
         <v>52</v>
       </c>
       <c r="B29" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D29" t="s">
         <v>184</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D30" t="s">
         <v>184</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D31" t="s">
         <v>184</v>
@@ -3479,11 +3479,11 @@
         <v>55</v>
       </c>
       <c r="B32" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D32" t="s">
         <v>184</v>
@@ -3533,11 +3533,11 @@
         <v>56</v>
       </c>
       <c r="B33" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D33" t="s">
         <v>184</v>
@@ -3587,11 +3587,11 @@
         <v>57</v>
       </c>
       <c r="B34" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D34" t="s">
         <v>184</v>
@@ -3641,7 +3641,7 @@
         <v>58</v>
       </c>
       <c r="B35" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="0"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D36" t="s">
         <v>184</v>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="0"/>
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="D37" t="s">
         <v>184</v>
@@ -3803,11 +3803,11 @@
         <v>62</v>
       </c>
       <c r="B38" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D38" t="s">
         <v>184</v>
@@ -3857,11 +3857,11 @@
         <v>63</v>
       </c>
       <c r="B39" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D39" t="s">
         <v>184</v>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="0"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D40" t="s">
         <v>184</v>
@@ -3965,11 +3965,11 @@
         <v>65</v>
       </c>
       <c r="B41" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D41" t="s">
         <v>184</v>
@@ -4019,11 +4019,11 @@
         <v>66</v>
       </c>
       <c r="B42" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D42" t="s">
         <v>184</v>
@@ -4073,11 +4073,11 @@
         <v>67</v>
       </c>
       <c r="B43" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D43" t="s">
         <v>184</v>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D44" t="s">
         <v>184</v>
@@ -4181,11 +4181,11 @@
         <v>69</v>
       </c>
       <c r="B45" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D45" t="s">
         <v>184</v>
@@ -4235,11 +4235,11 @@
         <v>70</v>
       </c>
       <c r="B46" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D46" t="s">
         <v>184</v>
@@ -4289,11 +4289,11 @@
         <v>71</v>
       </c>
       <c r="B47" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D47" t="s">
         <v>184</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="0"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D48" t="s">
         <v>184</v>
@@ -4397,11 +4397,11 @@
         <v>73</v>
       </c>
       <c r="B49" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D49" t="s">
         <v>184</v>
@@ -4451,11 +4451,11 @@
         <v>74</v>
       </c>
       <c r="B50" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D50" t="s">
         <v>184</v>
@@ -4505,11 +4505,11 @@
         <v>75</v>
       </c>
       <c r="B51" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D51" t="s">
         <v>184</v>
@@ -4559,11 +4559,11 @@
         <v>76</v>
       </c>
       <c r="B52" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D52" t="s">
         <v>184</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D53" t="s">
         <v>184</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="0"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D54" t="s">
         <v>184</v>
@@ -4721,11 +4721,11 @@
         <v>79</v>
       </c>
       <c r="B55" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D55" t="s">
         <v>184</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="0"/>
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="D56" t="s">
         <v>184</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="0"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D57" t="s">
         <v>184</v>
@@ -4883,11 +4883,11 @@
         <v>82</v>
       </c>
       <c r="B58" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D58" t="s">
         <v>184</v>
@@ -4937,11 +4937,11 @@
         <v>83</v>
       </c>
       <c r="B59" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D59" t="s">
         <v>184</v>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D60" t="s">
         <v>184</v>
@@ -5045,11 +5045,11 @@
         <v>85</v>
       </c>
       <c r="B61" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D61" t="s">
         <v>184</v>
@@ -5099,11 +5099,11 @@
         <v>86</v>
       </c>
       <c r="B62" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D62" t="s">
         <v>184</v>
@@ -5153,11 +5153,11 @@
         <v>87</v>
       </c>
       <c r="B63" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D63" t="s">
         <v>184</v>
@@ -5207,11 +5207,11 @@
         <v>90</v>
       </c>
       <c r="B64" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D64" t="s">
         <v>184</v>
@@ -5261,7 +5261,7 @@
         <v>92</v>
       </c>
       <c r="B65" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="0"/>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="0"/>
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="D66" t="s">
         <v>184</v>
@@ -5369,11 +5369,11 @@
         <v>94</v>
       </c>
       <c r="B67" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C67">
         <f t="shared" ref="C67:C130" ca="1" si="1">B67-$R$1</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D67" t="s">
         <v>184</v>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="1"/>
-        <v>-62</v>
+        <v>-63</v>
       </c>
       <c r="D68" t="s">
         <v>184</v>
@@ -5477,11 +5477,11 @@
         <v>96</v>
       </c>
       <c r="B69" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D69" t="s">
         <v>184</v>
@@ -5531,7 +5531,7 @@
         <v>97</v>
       </c>
       <c r="B70" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="1"/>
@@ -5585,11 +5585,11 @@
         <v>98</v>
       </c>
       <c r="B71" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D71" t="s">
         <v>184</v>
@@ -5639,11 +5639,11 @@
         <v>99</v>
       </c>
       <c r="B72" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D72" t="s">
         <v>184</v>
@@ -5693,11 +5693,11 @@
         <v>100</v>
       </c>
       <c r="B73" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D73" t="s">
         <v>184</v>
@@ -5747,11 +5747,11 @@
         <v>102</v>
       </c>
       <c r="B74" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D74" t="s">
         <v>184</v>
@@ -5801,11 +5801,11 @@
         <v>103</v>
       </c>
       <c r="B75" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D75" t="s">
         <v>184</v>
@@ -5855,11 +5855,11 @@
         <v>104</v>
       </c>
       <c r="B76" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D76" t="s">
         <v>184</v>
@@ -5909,11 +5909,11 @@
         <v>105</v>
       </c>
       <c r="B77" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D77" t="s">
         <v>184</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="1"/>
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="D78" t="s">
         <v>184</v>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D80" t="s">
         <v>184</v>
@@ -6233,11 +6233,11 @@
         <v>111</v>
       </c>
       <c r="B83" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D83" t="s">
         <v>184</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D84" t="s">
         <v>184</v>
@@ -6341,11 +6341,11 @@
         <v>113</v>
       </c>
       <c r="B85" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D85" t="s">
         <v>184</v>
@@ -6395,11 +6395,11 @@
         <v>114</v>
       </c>
       <c r="B86" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D86" t="s">
         <v>184</v>
@@ -6503,11 +6503,11 @@
         <v>116</v>
       </c>
       <c r="B88" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D88" t="s">
         <v>184</v>
@@ -6557,11 +6557,11 @@
         <v>117</v>
       </c>
       <c r="B89" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D89" t="s">
         <v>184</v>
@@ -6611,11 +6611,11 @@
         <v>121</v>
       </c>
       <c r="B90" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D90" t="s">
         <v>184</v>
@@ -6665,11 +6665,11 @@
         <v>122</v>
       </c>
       <c r="B91" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D91" t="s">
         <v>184</v>
@@ -6719,11 +6719,11 @@
         <v>123</v>
       </c>
       <c r="B92" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D92" t="s">
         <v>184</v>
@@ -6773,11 +6773,11 @@
         <v>124</v>
       </c>
       <c r="B93" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D93" t="s">
         <v>184</v>
@@ -6827,11 +6827,11 @@
         <v>125</v>
       </c>
       <c r="B94" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D94" t="s">
         <v>184</v>
@@ -6881,7 +6881,7 @@
         <v>126</v>
       </c>
       <c r="B95" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="1"/>
@@ -6935,11 +6935,11 @@
         <v>127</v>
       </c>
       <c r="B96" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D96" t="s">
         <v>184</v>
@@ -6989,11 +6989,11 @@
         <v>128</v>
       </c>
       <c r="B97" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D97" t="s">
         <v>184</v>
@@ -7043,11 +7043,11 @@
         <v>129</v>
       </c>
       <c r="B98" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D98" t="s">
         <v>184</v>
@@ -7097,11 +7097,11 @@
         <v>130</v>
       </c>
       <c r="B99" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D99" t="s">
         <v>184</v>
@@ -7151,11 +7151,11 @@
         <v>131</v>
       </c>
       <c r="B100" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D100" t="s">
         <v>184</v>
@@ -7205,7 +7205,7 @@
         <v>132</v>
       </c>
       <c r="B101" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="1"/>
@@ -7259,11 +7259,11 @@
         <v>133</v>
       </c>
       <c r="B102" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C102">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D102" t="s">
         <v>184</v>
@@ -7313,11 +7313,11 @@
         <v>134</v>
       </c>
       <c r="B103" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C103">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D103" t="s">
         <v>184</v>
@@ -7367,11 +7367,11 @@
         <v>135</v>
       </c>
       <c r="B104" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C104">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D104" t="s">
         <v>184</v>
@@ -7421,11 +7421,11 @@
         <v>136</v>
       </c>
       <c r="B105" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C105">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D105" t="s">
         <v>184</v>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="C106">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D106" t="s">
         <v>184</v>
@@ -7529,11 +7529,11 @@
         <v>138</v>
       </c>
       <c r="B107" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C107">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D107" t="s">
         <v>184</v>
@@ -7583,11 +7583,11 @@
         <v>139</v>
       </c>
       <c r="B108" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C108">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D108" t="s">
         <v>184</v>
@@ -7637,11 +7637,11 @@
         <v>140</v>
       </c>
       <c r="B109" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C109">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D109" t="s">
         <v>184</v>
@@ -7691,11 +7691,11 @@
         <v>141</v>
       </c>
       <c r="B110" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C110">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D110" t="s">
         <v>184</v>
@@ -7745,11 +7745,11 @@
         <v>142</v>
       </c>
       <c r="B111" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C111">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D111" t="s">
         <v>184</v>
@@ -7831,7 +7831,7 @@
         <v>143</v>
       </c>
       <c r="B113" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C113">
         <f t="shared" ca="1" si="1"/>
@@ -7885,11 +7885,11 @@
         <v>144</v>
       </c>
       <c r="B114" s="2">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="C114">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="D114" t="s">
         <v>184</v>
@@ -7939,11 +7939,11 @@
         <v>145</v>
       </c>
       <c r="B115" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C115">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D115" t="s">
         <v>184</v>
@@ -7993,11 +7993,11 @@
         <v>147</v>
       </c>
       <c r="B116" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C116">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D116" t="s">
         <v>184</v>
@@ -8047,11 +8047,11 @@
         <v>148</v>
       </c>
       <c r="B117" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C117">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D117" t="s">
         <v>184</v>
@@ -8101,11 +8101,11 @@
         <v>149</v>
       </c>
       <c r="B118" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C118">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D118" t="s">
         <v>184</v>
@@ -8155,11 +8155,11 @@
         <v>150</v>
       </c>
       <c r="B119" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C119">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D119" t="s">
         <v>184</v>
@@ -8209,11 +8209,11 @@
         <v>151</v>
       </c>
       <c r="B120" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C120">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D120" t="s">
         <v>184</v>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C121">
         <f t="shared" ca="1" si="1"/>
-        <v>-46317</v>
+        <v>-46318</v>
       </c>
       <c r="D121" t="s">
         <v>465</v>
@@ -8317,11 +8317,11 @@
         <v>154</v>
       </c>
       <c r="B122" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C122">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D122" t="s">
         <v>184</v>
@@ -8371,11 +8371,11 @@
         <v>155</v>
       </c>
       <c r="B123" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C123">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D123" t="s">
         <v>184</v>
@@ -8425,11 +8425,11 @@
         <v>156</v>
       </c>
       <c r="B124" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C124">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D124" t="s">
         <v>184</v>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="C125">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D125" t="s">
         <v>184</v>
@@ -8533,11 +8533,11 @@
         <v>158</v>
       </c>
       <c r="B126" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C126">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D126" t="s">
         <v>184</v>
@@ -8587,11 +8587,11 @@
         <v>159</v>
       </c>
       <c r="B127" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C127">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D127" t="s">
         <v>184</v>
@@ -8641,11 +8641,11 @@
         <v>160</v>
       </c>
       <c r="B128" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C128">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D128" t="s">
         <v>184</v>
@@ -8695,11 +8695,11 @@
         <v>161</v>
       </c>
       <c r="B129" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C129">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D129" t="s">
         <v>184</v>
@@ -8749,11 +8749,11 @@
         <v>162</v>
       </c>
       <c r="B130" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C130">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D130" t="s">
         <v>184</v>
@@ -8803,11 +8803,11 @@
         <v>186</v>
       </c>
       <c r="B131" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C131">
         <f t="shared" ref="C131:C193" ca="1" si="2">B131-$R$1</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D131" t="s">
         <v>184</v>
@@ -8857,11 +8857,11 @@
         <v>187</v>
       </c>
       <c r="B132" s="2">
-        <v>0</v>
+        <v>46300</v>
       </c>
       <c r="C132">
         <f t="shared" ca="1" si="2"/>
-        <v>-46317</v>
+        <v>-18</v>
       </c>
       <c r="D132" t="s">
         <v>184</v>
@@ -8910,12 +8910,12 @@
       <c r="A133" t="s">
         <v>466</v>
       </c>
-      <c r="B133" s="2">
-        <v>0</v>
-      </c>
-      <c r="C133">
+      <c r="B133" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C133" t="e">
         <f t="shared" ref="C133" ca="1" si="3">B133-$R$1</f>
-        <v>-46317</v>
+        <v>#N/A</v>
       </c>
       <c r="D133" t="s">
         <v>184</v>
@@ -8953,11 +8953,11 @@
         <v>188</v>
       </c>
       <c r="B134" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C134">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D134" t="s">
         <v>184</v>
@@ -9007,7 +9007,7 @@
         <v>189</v>
       </c>
       <c r="B135" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C135">
         <f t="shared" ca="1" si="2"/>
@@ -9061,7 +9061,7 @@
         <v>190</v>
       </c>
       <c r="B136" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C136">
         <f t="shared" ca="1" si="2"/>
@@ -9115,7 +9115,7 @@
         <v>191</v>
       </c>
       <c r="B137" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C137">
         <f t="shared" ca="1" si="2"/>
@@ -9169,7 +9169,7 @@
         <v>192</v>
       </c>
       <c r="B138" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C138">
         <f t="shared" ca="1" si="2"/>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C140">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D140" t="s">
         <v>184</v>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="C145">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D145" t="s">
         <v>184</v>
@@ -9706,7 +9706,7 @@
         <v>205</v>
       </c>
       <c r="B151" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C151">
         <f t="shared" ca="1" si="2"/>
@@ -9756,7 +9756,7 @@
         <v>164</v>
       </c>
       <c r="B152" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C152">
         <f t="shared" ca="1" si="2"/>
@@ -9810,7 +9810,7 @@
         <v>165</v>
       </c>
       <c r="B153" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C153">
         <f t="shared" ca="1" si="2"/>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="C154">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D154" t="s">
         <v>184</v>
@@ -9918,7 +9918,7 @@
         <v>167</v>
       </c>
       <c r="B155" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
@@ -9972,11 +9972,11 @@
         <v>168</v>
       </c>
       <c r="B156" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D156" t="s">
         <v>184</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="D157" t="s">
         <v>184</v>
@@ -10080,7 +10080,7 @@
         <v>170</v>
       </c>
       <c r="B158" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C158">
         <f t="shared" ca="1" si="2"/>
@@ -10134,7 +10134,7 @@
         <v>171</v>
       </c>
       <c r="B159" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C159">
         <f t="shared" ca="1" si="2"/>
@@ -10188,7 +10188,7 @@
         <v>172</v>
       </c>
       <c r="B160" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
@@ -10242,11 +10242,11 @@
         <v>173</v>
       </c>
       <c r="B161" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D161" t="s">
         <v>184</v>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D162" t="s">
         <v>184</v>
@@ -10350,11 +10350,11 @@
         <v>176</v>
       </c>
       <c r="B163" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C163">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D163" t="s">
         <v>184</v>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="C164">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D164" t="s">
         <v>184</v>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
-        <v>-46317</v>
+        <v>-46318</v>
       </c>
       <c r="D165" t="s">
         <v>184</v>
@@ -10500,11 +10500,11 @@
         <v>208</v>
       </c>
       <c r="B166" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C166">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D166" t="s">
         <v>465</v>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="C167">
         <f t="shared" ca="1" si="2"/>
-        <v>-46317</v>
+        <v>-46318</v>
       </c>
       <c r="D167" t="s">
         <v>465</v>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C168">
         <f t="shared" ca="1" si="2"/>
-        <v>-46317</v>
+        <v>-46318</v>
       </c>
       <c r="D168" t="s">
         <v>465</v>
@@ -10638,7 +10638,7 @@
         <v>211</v>
       </c>
       <c r="B169" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C169">
         <f t="shared" ca="1" si="2"/>
@@ -10692,7 +10692,7 @@
         <v>212</v>
       </c>
       <c r="B170" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C170">
         <f t="shared" ca="1" si="2"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="C171">
         <f t="shared" ca="1" si="2"/>
-        <v>-46317</v>
+        <v>-46318</v>
       </c>
       <c r="D171" t="s">
         <v>465</v>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="C172">
         <f t="shared" ca="1" si="2"/>
-        <v>-46317</v>
+        <v>-46318</v>
       </c>
       <c r="D172" t="s">
         <v>465</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="C174">
         <f t="shared" ca="1" si="2"/>
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="D174" t="s">
         <v>184</v>
@@ -10913,11 +10913,11 @@
         <v>227</v>
       </c>
       <c r="B175" s="2">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="C175">
         <f t="shared" ca="1" si="2"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="D175" t="s">
         <v>184</v>
@@ -10968,7 +10968,7 @@
       </c>
       <c r="C176">
         <f t="shared" ca="1" si="2"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="D176" t="s">
         <v>184</v>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="C177">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D177" t="s">
         <v>184</v>
@@ -11066,7 +11066,7 @@
         <v>230</v>
       </c>
       <c r="B178" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C178">
         <f t="shared" ca="1" si="2"/>
@@ -11117,7 +11117,7 @@
         <v>231</v>
       </c>
       <c r="B179" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C179">
         <f t="shared" ca="1" si="2"/>
@@ -11168,7 +11168,7 @@
         <v>232</v>
       </c>
       <c r="B180" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C180">
         <f t="shared" ca="1" si="2"/>
@@ -11219,7 +11219,7 @@
         <v>233</v>
       </c>
       <c r="B181" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C181">
         <f t="shared" ca="1" si="2"/>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="C182">
         <f t="shared" ca="1" si="2"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D182" t="s">
         <v>184</v>
@@ -11321,11 +11321,11 @@
         <v>235</v>
       </c>
       <c r="B183" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C183">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D183" t="s">
         <v>184</v>
@@ -11372,7 +11372,7 @@
         <v>236</v>
       </c>
       <c r="B184" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C184">
         <f t="shared" ca="1" si="2"/>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="C185">
         <f t="shared" ca="1" si="2"/>
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="D185" t="s">
         <v>184</v>
@@ -11474,7 +11474,7 @@
         <v>238</v>
       </c>
       <c r="B186" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C186">
         <f t="shared" ca="1" si="2"/>
@@ -11525,7 +11525,7 @@
         <v>239</v>
       </c>
       <c r="B187" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C187">
         <f t="shared" ca="1" si="2"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="C188">
         <f t="shared" ca="1" si="2"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D188" t="s">
         <v>184</v>
@@ -11627,11 +11627,11 @@
         <v>241</v>
       </c>
       <c r="B189" s="2">
-        <v>46313</v>
+        <v>46317</v>
       </c>
       <c r="C189">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D189" t="s">
         <v>184</v>
@@ -11678,7 +11678,7 @@
         <v>242</v>
       </c>
       <c r="B190" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C190">
         <f t="shared" ca="1" si="2"/>
@@ -11729,7 +11729,7 @@
         <v>243</v>
       </c>
       <c r="B191" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C191">
         <f t="shared" ca="1" si="2"/>
@@ -11780,11 +11780,11 @@
         <v>244</v>
       </c>
       <c r="B192" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C192">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D192" t="s">
         <v>184</v>
@@ -11835,7 +11835,7 @@
       </c>
       <c r="C193">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D193" t="s">
         <v>184</v>
@@ -11882,11 +11882,11 @@
         <v>246</v>
       </c>
       <c r="B194" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C194">
         <f t="shared" ref="C194:C255" ca="1" si="4">B194-$R$1</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D194" t="s">
         <v>184</v>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="C195">
         <f t="shared" ca="1" si="4"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D195" t="s">
         <v>184</v>
@@ -11984,7 +11984,7 @@
         <v>248</v>
       </c>
       <c r="B196" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C196">
         <f t="shared" ca="1" si="4"/>
@@ -12039,7 +12039,7 @@
       </c>
       <c r="C197">
         <f t="shared" ca="1" si="4"/>
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="D197" t="s">
         <v>184</v>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="C198">
         <f t="shared" ca="1" si="4"/>
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="D198" t="s">
         <v>184</v>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="C199">
         <f t="shared" ca="1" si="4"/>
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="D199" t="s">
         <v>184</v>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C200">
         <f t="shared" ca="1" si="4"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="D200" t="s">
         <v>184</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C201">
         <f t="shared" ca="1" si="4"/>
-        <v>-280</v>
+        <v>-281</v>
       </c>
       <c r="D201" t="s">
         <v>184</v>
@@ -12290,11 +12290,11 @@
         <v>254</v>
       </c>
       <c r="B202" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C202">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D202" t="s">
         <v>184</v>
@@ -12341,7 +12341,7 @@
         <v>255</v>
       </c>
       <c r="B203" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C203">
         <f t="shared" ca="1" si="4"/>
@@ -12392,7 +12392,7 @@
         <v>256</v>
       </c>
       <c r="B204" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C204">
         <f t="shared" ca="1" si="4"/>
@@ -12443,7 +12443,7 @@
         <v>257</v>
       </c>
       <c r="B205" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C205">
         <f t="shared" ca="1" si="4"/>
@@ -12494,7 +12494,7 @@
         <v>258</v>
       </c>
       <c r="B206" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C206">
         <f t="shared" ca="1" si="4"/>
@@ -12545,7 +12545,7 @@
         <v>259</v>
       </c>
       <c r="B207" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C207">
         <f t="shared" ca="1" si="4"/>
@@ -12596,7 +12596,7 @@
         <v>260</v>
       </c>
       <c r="B208" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C208">
         <f t="shared" ca="1" si="4"/>
@@ -12647,7 +12647,7 @@
         <v>261</v>
       </c>
       <c r="B209" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C209">
         <f t="shared" ca="1" si="4"/>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="C210">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D210" t="s">
         <v>184</v>
@@ -12749,7 +12749,7 @@
         <v>263</v>
       </c>
       <c r="B211" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C211">
         <f t="shared" ca="1" si="4"/>
@@ -12800,7 +12800,7 @@
         <v>264</v>
       </c>
       <c r="B212" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C212">
         <f t="shared" ca="1" si="4"/>
@@ -12851,7 +12851,7 @@
         <v>265</v>
       </c>
       <c r="B213" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C213">
         <f t="shared" ca="1" si="4"/>
@@ -12902,7 +12902,7 @@
         <v>266</v>
       </c>
       <c r="B214" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C214">
         <f t="shared" ca="1" si="4"/>
@@ -12957,7 +12957,7 @@
       </c>
       <c r="C215">
         <f t="shared" ca="1" si="4"/>
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="D215" t="s">
         <v>184</v>
@@ -13008,7 +13008,7 @@
       </c>
       <c r="C216">
         <f t="shared" ca="1" si="4"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
@@ -13055,7 +13055,7 @@
         <v>269</v>
       </c>
       <c r="B217" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C217">
         <f t="shared" ca="1" si="4"/>
@@ -13110,7 +13110,7 @@
       </c>
       <c r="C218">
         <f t="shared" ca="1" si="4"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D218" t="s">
         <v>184</v>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="C219">
         <f t="shared" ca="1" si="4"/>
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="D219" t="s">
         <v>184</v>
@@ -13208,7 +13208,7 @@
         <v>272</v>
       </c>
       <c r="B220" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C220">
         <f t="shared" ca="1" si="4"/>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="C221">
         <f t="shared" ca="1" si="4"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D221" t="s">
         <v>184</v>
@@ -13310,7 +13310,7 @@
         <v>274</v>
       </c>
       <c r="B222" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C222">
         <f t="shared" ca="1" si="4"/>
@@ -13361,7 +13361,7 @@
         <v>275</v>
       </c>
       <c r="B223" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C223">
         <f t="shared" ca="1" si="4"/>
@@ -13412,7 +13412,7 @@
         <v>276</v>
       </c>
       <c r="B224" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C224">
         <f t="shared" ca="1" si="4"/>
@@ -13463,7 +13463,7 @@
         <v>277</v>
       </c>
       <c r="B225" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C225">
         <f t="shared" ca="1" si="4"/>
@@ -13518,7 +13518,7 @@
       </c>
       <c r="C226">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D226" t="s">
         <v>184</v>
@@ -13569,7 +13569,7 @@
       </c>
       <c r="C227">
         <f t="shared" ca="1" si="4"/>
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="D227" t="s">
         <v>184</v>
@@ -13620,7 +13620,7 @@
       </c>
       <c r="C228">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D228" t="s">
         <v>184</v>
@@ -13667,7 +13667,7 @@
         <v>281</v>
       </c>
       <c r="B229" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C229">
         <f t="shared" ca="1" si="4"/>
@@ -13718,7 +13718,7 @@
         <v>282</v>
       </c>
       <c r="B230" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C230">
         <f t="shared" ca="1" si="4"/>
@@ -13769,11 +13769,11 @@
         <v>283</v>
       </c>
       <c r="B231" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C231">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D231" t="s">
         <v>184</v>
@@ -13820,7 +13820,7 @@
         <v>284</v>
       </c>
       <c r="B232" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C232">
         <f t="shared" ca="1" si="4"/>
@@ -13875,7 +13875,7 @@
       </c>
       <c r="C233">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D233" t="s">
         <v>184</v>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="C234">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D234" t="s">
         <v>184</v>
@@ -13973,7 +13973,7 @@
         <v>287</v>
       </c>
       <c r="B235" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C235">
         <f t="shared" ca="1" si="4"/>
@@ -14024,11 +14024,11 @@
         <v>288</v>
       </c>
       <c r="B236" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C236">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D236" t="s">
         <v>184</v>
@@ -14075,7 +14075,7 @@
         <v>289</v>
       </c>
       <c r="B237" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C237">
         <f t="shared" ca="1" si="4"/>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="C238">
         <f t="shared" ca="1" si="4"/>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="D238" t="s">
         <v>184</v>
@@ -14177,7 +14177,7 @@
         <v>291</v>
       </c>
       <c r="B239" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C239">
         <f t="shared" ca="1" si="4"/>
@@ -14228,7 +14228,7 @@
         <v>292</v>
       </c>
       <c r="B240" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C240">
         <f t="shared" ca="1" si="4"/>
@@ -14283,7 +14283,7 @@
       </c>
       <c r="C241">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D241" t="s">
         <v>184</v>
@@ -14330,7 +14330,7 @@
         <v>294</v>
       </c>
       <c r="B242" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C242">
         <f t="shared" ca="1" si="4"/>
@@ -14381,7 +14381,7 @@
         <v>295</v>
       </c>
       <c r="B243" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C243">
         <f t="shared" ca="1" si="4"/>
@@ -14432,7 +14432,7 @@
         <v>296</v>
       </c>
       <c r="B244" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C244">
         <f t="shared" ca="1" si="4"/>
@@ -14483,7 +14483,7 @@
         <v>297</v>
       </c>
       <c r="B245" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C245">
         <f t="shared" ca="1" si="4"/>
@@ -14534,7 +14534,7 @@
         <v>298</v>
       </c>
       <c r="B246" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C246">
         <f t="shared" ca="1" si="4"/>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="C247">
         <f t="shared" ca="1" si="4"/>
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="D247" t="s">
         <v>184</v>
@@ -14636,7 +14636,7 @@
         <v>300</v>
       </c>
       <c r="B248" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C248">
         <f t="shared" ca="1" si="4"/>
@@ -14687,7 +14687,7 @@
         <v>301</v>
       </c>
       <c r="B249" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C249">
         <f t="shared" ca="1" si="4"/>
@@ -14738,7 +14738,7 @@
         <v>302</v>
       </c>
       <c r="B250" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C250">
         <f t="shared" ca="1" si="4"/>
@@ -14789,7 +14789,7 @@
         <v>303</v>
       </c>
       <c r="B251" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C251">
         <f t="shared" ca="1" si="4"/>
@@ -14840,7 +14840,7 @@
         <v>304</v>
       </c>
       <c r="B252" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C252">
         <f t="shared" ca="1" si="4"/>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="C253">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D253" t="s">
         <v>184</v>
@@ -14946,7 +14946,7 @@
       </c>
       <c r="C254">
         <f t="shared" ca="1" si="4"/>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="D254" t="s">
         <v>184</v>
@@ -14993,11 +14993,11 @@
         <v>307</v>
       </c>
       <c r="B255" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C255">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D255" t="s">
         <v>184</v>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="C256">
         <f t="shared" ref="C256:C319" ca="1" si="5">B256-$R$1</f>
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="D256" t="s">
         <v>184</v>
@@ -15095,7 +15095,7 @@
         <v>309</v>
       </c>
       <c r="B257" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C257">
         <f t="shared" ca="1" si="5"/>
@@ -15146,7 +15146,7 @@
         <v>310</v>
       </c>
       <c r="B258" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C258">
         <f t="shared" ca="1" si="5"/>
@@ -15197,7 +15197,7 @@
         <v>311</v>
       </c>
       <c r="B259" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C259">
         <f t="shared" ca="1" si="5"/>
@@ -15248,7 +15248,7 @@
         <v>312</v>
       </c>
       <c r="B260" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C260">
         <f t="shared" ca="1" si="5"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="C261">
         <f t="shared" ca="1" si="5"/>
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="D261" t="s">
         <v>184</v>
@@ -15350,7 +15350,7 @@
         <v>314</v>
       </c>
       <c r="B262" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C262">
         <f t="shared" ca="1" si="5"/>
@@ -15401,7 +15401,7 @@
         <v>315</v>
       </c>
       <c r="B263" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C263">
         <f t="shared" ca="1" si="5"/>
@@ -15452,7 +15452,7 @@
         <v>316</v>
       </c>
       <c r="B264" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C264">
         <f t="shared" ca="1" si="5"/>
@@ -15507,7 +15507,7 @@
       </c>
       <c r="C265">
         <f t="shared" ca="1" si="5"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D265" t="s">
         <v>184</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="C266">
         <f t="shared" ca="1" si="5"/>
-        <v>-140</v>
+        <v>-141</v>
       </c>
       <c r="D266" t="s">
         <v>184</v>
@@ -15605,7 +15605,7 @@
         <v>319</v>
       </c>
       <c r="B267" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C267">
         <f t="shared" ca="1" si="5"/>
@@ -15660,7 +15660,7 @@
       </c>
       <c r="C268">
         <f t="shared" ca="1" si="5"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="D268" t="s">
         <v>184</v>
@@ -15707,7 +15707,7 @@
         <v>321</v>
       </c>
       <c r="B269" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C269">
         <f t="shared" ca="1" si="5"/>
@@ -15758,7 +15758,7 @@
         <v>322</v>
       </c>
       <c r="B270" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C270">
         <f t="shared" ca="1" si="5"/>
@@ -15809,7 +15809,7 @@
         <v>323</v>
       </c>
       <c r="B271" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C271">
         <f t="shared" ca="1" si="5"/>
@@ -15860,7 +15860,7 @@
         <v>324</v>
       </c>
       <c r="B272" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C272">
         <f t="shared" ca="1" si="5"/>
@@ -15911,11 +15911,11 @@
         <v>325</v>
       </c>
       <c r="B273" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C273">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D273" t="s">
         <v>184</v>
@@ -15962,7 +15962,7 @@
         <v>326</v>
       </c>
       <c r="B274" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C274">
         <f t="shared" ca="1" si="5"/>
@@ -16013,7 +16013,7 @@
         <v>327</v>
       </c>
       <c r="B275" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C275">
         <f t="shared" ca="1" si="5"/>
@@ -16064,7 +16064,7 @@
         <v>328</v>
       </c>
       <c r="B276" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C276">
         <f t="shared" ca="1" si="5"/>
@@ -16115,7 +16115,7 @@
         <v>329</v>
       </c>
       <c r="B277" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C277">
         <f t="shared" ca="1" si="5"/>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="C278">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D278" t="s">
         <v>184</v>
@@ -16217,7 +16217,7 @@
         <v>331</v>
       </c>
       <c r="B279" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C279">
         <f t="shared" ca="1" si="5"/>
@@ -16268,7 +16268,7 @@
         <v>332</v>
       </c>
       <c r="B280" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C280">
         <f t="shared" ca="1" si="5"/>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="C281">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D281" t="s">
         <v>184</v>
@@ -16374,7 +16374,7 @@
       </c>
       <c r="C282">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D282" t="s">
         <v>184</v>
@@ -16421,7 +16421,7 @@
         <v>335</v>
       </c>
       <c r="B283" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C283">
         <f t="shared" ca="1" si="5"/>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="C284">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D284" t="s">
         <v>184</v>
@@ -16523,7 +16523,7 @@
         <v>337</v>
       </c>
       <c r="B285" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C285">
         <f t="shared" ca="1" si="5"/>
@@ -16574,11 +16574,11 @@
         <v>338</v>
       </c>
       <c r="B286" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C286">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D286" t="s">
         <v>184</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C287">
         <f t="shared" ca="1" si="5"/>
-        <v>-226</v>
+        <v>-227</v>
       </c>
       <c r="D287" t="s">
         <v>184</v>
@@ -16676,7 +16676,7 @@
         <v>340</v>
       </c>
       <c r="B288" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C288">
         <f t="shared" ca="1" si="5"/>
@@ -16727,7 +16727,7 @@
         <v>341</v>
       </c>
       <c r="B289" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C289">
         <f t="shared" ca="1" si="5"/>
@@ -16778,7 +16778,7 @@
         <v>342</v>
       </c>
       <c r="B290" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C290">
         <f t="shared" ca="1" si="5"/>
@@ -16829,7 +16829,7 @@
         <v>343</v>
       </c>
       <c r="B291" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C291">
         <f t="shared" ca="1" si="5"/>
@@ -16880,7 +16880,7 @@
         <v>344</v>
       </c>
       <c r="B292" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C292">
         <f t="shared" ca="1" si="5"/>
@@ -16931,7 +16931,7 @@
         <v>345</v>
       </c>
       <c r="B293" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C293">
         <f t="shared" ca="1" si="5"/>
@@ -16982,7 +16982,7 @@
         <v>346</v>
       </c>
       <c r="B294" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C294">
         <f t="shared" ca="1" si="5"/>
@@ -17033,7 +17033,7 @@
         <v>347</v>
       </c>
       <c r="B295" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C295">
         <f t="shared" ca="1" si="5"/>
@@ -17084,11 +17084,11 @@
         <v>348</v>
       </c>
       <c r="B296" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C296">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D296" t="s">
         <v>184</v>
@@ -17135,7 +17135,7 @@
         <v>349</v>
       </c>
       <c r="B297" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C297">
         <f t="shared" ca="1" si="5"/>
@@ -17186,7 +17186,7 @@
         <v>350</v>
       </c>
       <c r="B298" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C298">
         <f t="shared" ca="1" si="5"/>
@@ -17237,7 +17237,7 @@
         <v>351</v>
       </c>
       <c r="B299" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C299">
         <f t="shared" ca="1" si="5"/>
@@ -17288,7 +17288,7 @@
         <v>352</v>
       </c>
       <c r="B300" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C300">
         <f t="shared" ca="1" si="5"/>
@@ -17339,7 +17339,7 @@
         <v>353</v>
       </c>
       <c r="B301" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C301">
         <f t="shared" ca="1" si="5"/>
@@ -17390,7 +17390,7 @@
         <v>354</v>
       </c>
       <c r="B302" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C302">
         <f t="shared" ca="1" si="5"/>
@@ -17441,7 +17441,7 @@
         <v>355</v>
       </c>
       <c r="B303" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C303">
         <f t="shared" ca="1" si="5"/>
@@ -17492,7 +17492,7 @@
         <v>356</v>
       </c>
       <c r="B304" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C304">
         <f t="shared" ca="1" si="5"/>
@@ -17543,7 +17543,7 @@
         <v>357</v>
       </c>
       <c r="B305" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C305">
         <f t="shared" ca="1" si="5"/>
@@ -17594,7 +17594,7 @@
         <v>358</v>
       </c>
       <c r="B306" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C306">
         <f t="shared" ca="1" si="5"/>
@@ -17645,7 +17645,7 @@
         <v>359</v>
       </c>
       <c r="B307" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C307">
         <f t="shared" ca="1" si="5"/>
@@ -17700,7 +17700,7 @@
       </c>
       <c r="C308">
         <f t="shared" ca="1" si="5"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D308" t="s">
         <v>184</v>
@@ -17747,7 +17747,7 @@
         <v>361</v>
       </c>
       <c r="B309" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C309">
         <f t="shared" ca="1" si="5"/>
@@ -17798,7 +17798,7 @@
         <v>362</v>
       </c>
       <c r="B310" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C310">
         <f t="shared" ca="1" si="5"/>
@@ -17849,7 +17849,7 @@
         <v>363</v>
       </c>
       <c r="B311" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C311">
         <f t="shared" ca="1" si="5"/>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="C312">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D312" t="s">
         <v>184</v>
@@ -17951,7 +17951,7 @@
         <v>365</v>
       </c>
       <c r="B313" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C313">
         <f t="shared" ca="1" si="5"/>
@@ -18006,7 +18006,7 @@
       </c>
       <c r="C314">
         <f t="shared" ca="1" si="5"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D314" t="s">
         <v>184</v>
@@ -18057,7 +18057,7 @@
       </c>
       <c r="C315">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D315" t="s">
         <v>184</v>
@@ -18104,7 +18104,7 @@
         <v>368</v>
       </c>
       <c r="B316" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C316">
         <f t="shared" ca="1" si="5"/>
@@ -18159,7 +18159,7 @@
       </c>
       <c r="C317">
         <f t="shared" ca="1" si="5"/>
-        <v>-73</v>
+        <v>-74</v>
       </c>
       <c r="D317" t="s">
         <v>184</v>
@@ -18206,7 +18206,7 @@
         <v>370</v>
       </c>
       <c r="B318" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C318">
         <f t="shared" ca="1" si="5"/>
@@ -18257,11 +18257,11 @@
         <v>371</v>
       </c>
       <c r="B319" s="2">
-        <v>46306</v>
+        <v>46317</v>
       </c>
       <c r="C319">
         <f t="shared" ca="1" si="5"/>
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="D319" t="s">
         <v>184</v>
@@ -18308,7 +18308,7 @@
         <v>372</v>
       </c>
       <c r="B320" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C320">
         <f t="shared" ref="C320:C383" ca="1" si="6">B320-$R$1</f>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="C321">
         <f t="shared" ca="1" si="6"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D321" t="s">
         <v>184</v>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="C322">
         <f t="shared" ca="1" si="6"/>
-        <v>-77</v>
+        <v>-78</v>
       </c>
       <c r="D322" t="s">
         <v>184</v>
@@ -18465,7 +18465,7 @@
       </c>
       <c r="C323">
         <f t="shared" ca="1" si="6"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="D323" t="s">
         <v>184</v>
@@ -18512,7 +18512,7 @@
         <v>376</v>
       </c>
       <c r="B324" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C324">
         <f t="shared" ca="1" si="6"/>
@@ -18563,7 +18563,7 @@
         <v>377</v>
       </c>
       <c r="B325" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C325">
         <f t="shared" ca="1" si="6"/>
@@ -18614,7 +18614,7 @@
         <v>378</v>
       </c>
       <c r="B326" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C326">
         <f t="shared" ca="1" si="6"/>
@@ -18665,7 +18665,7 @@
         <v>379</v>
       </c>
       <c r="B327" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C327">
         <f t="shared" ca="1" si="6"/>
@@ -18720,7 +18720,7 @@
       </c>
       <c r="C328">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D328" t="s">
         <v>184</v>
@@ -18767,7 +18767,7 @@
         <v>381</v>
       </c>
       <c r="B329" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C329">
         <f t="shared" ca="1" si="6"/>
@@ -18818,11 +18818,11 @@
         <v>382</v>
       </c>
       <c r="B330" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C330">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D330" t="s">
         <v>184</v>
@@ -18869,11 +18869,11 @@
         <v>383</v>
       </c>
       <c r="B331" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C331">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D331" t="s">
         <v>184</v>
@@ -18924,7 +18924,7 @@
       </c>
       <c r="C332">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D332" t="s">
         <v>184</v>
@@ -18971,7 +18971,7 @@
         <v>385</v>
       </c>
       <c r="B333" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C333">
         <f t="shared" ca="1" si="6"/>
@@ -19022,11 +19022,11 @@
         <v>386</v>
       </c>
       <c r="B334" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C334">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D334" t="s">
         <v>184</v>
@@ -19073,7 +19073,7 @@
         <v>387</v>
       </c>
       <c r="B335" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C335">
         <f t="shared" ca="1" si="6"/>
@@ -19128,7 +19128,7 @@
       </c>
       <c r="C336">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D336" t="s">
         <v>184</v>
@@ -19175,7 +19175,7 @@
         <v>389</v>
       </c>
       <c r="B337" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C337">
         <f t="shared" ca="1" si="6"/>
@@ -19230,7 +19230,7 @@
       </c>
       <c r="C338">
         <f t="shared" ca="1" si="6"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D338" t="s">
         <v>184</v>
@@ -19277,7 +19277,7 @@
         <v>391</v>
       </c>
       <c r="B339" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C339">
         <f t="shared" ca="1" si="6"/>
@@ -19328,7 +19328,7 @@
         <v>392</v>
       </c>
       <c r="B340" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C340">
         <f t="shared" ca="1" si="6"/>
@@ -19379,7 +19379,7 @@
         <v>393</v>
       </c>
       <c r="B341" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C341">
         <f t="shared" ca="1" si="6"/>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="C342">
         <f t="shared" ca="1" si="6"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D342" t="s">
         <v>184</v>
@@ -19481,7 +19481,7 @@
         <v>395</v>
       </c>
       <c r="B343" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C343">
         <f t="shared" ca="1" si="6"/>
@@ -19532,7 +19532,7 @@
         <v>396</v>
       </c>
       <c r="B344" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C344">
         <f t="shared" ca="1" si="6"/>
@@ -19583,11 +19583,11 @@
         <v>397</v>
       </c>
       <c r="B345" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C345">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D345" t="s">
         <v>184</v>
@@ -19634,7 +19634,7 @@
         <v>398</v>
       </c>
       <c r="B346" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C346">
         <f t="shared" ca="1" si="6"/>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="C347">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D347" t="s">
         <v>184</v>
@@ -19736,7 +19736,7 @@
         <v>400</v>
       </c>
       <c r="B348" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C348">
         <f t="shared" ca="1" si="6"/>
@@ -19787,7 +19787,7 @@
         <v>401</v>
       </c>
       <c r="B349" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C349">
         <f t="shared" ca="1" si="6"/>
@@ -19838,7 +19838,7 @@
         <v>402</v>
       </c>
       <c r="B350" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C350">
         <f t="shared" ca="1" si="6"/>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C351">
         <f t="shared" ca="1" si="6"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D351" t="s">
         <v>184</v>
@@ -19940,7 +19940,7 @@
         <v>404</v>
       </c>
       <c r="B352" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C352">
         <f t="shared" ca="1" si="6"/>
@@ -19991,7 +19991,7 @@
         <v>405</v>
       </c>
       <c r="B353" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C353">
         <f t="shared" ca="1" si="6"/>
@@ -20042,7 +20042,7 @@
         <v>406</v>
       </c>
       <c r="B354" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C354">
         <f t="shared" ca="1" si="6"/>
@@ -20093,7 +20093,7 @@
         <v>407</v>
       </c>
       <c r="B355" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C355">
         <f t="shared" ca="1" si="6"/>
@@ -20148,7 +20148,7 @@
       </c>
       <c r="C356">
         <f t="shared" ca="1" si="6"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="D356" t="s">
         <v>184</v>
@@ -20195,7 +20195,7 @@
         <v>409</v>
       </c>
       <c r="B357" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C357">
         <f t="shared" ca="1" si="6"/>
@@ -20246,7 +20246,7 @@
         <v>410</v>
       </c>
       <c r="B358" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C358">
         <f t="shared" ca="1" si="6"/>
@@ -20297,7 +20297,7 @@
         <v>411</v>
       </c>
       <c r="B359" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C359">
         <f t="shared" ca="1" si="6"/>
@@ -20348,7 +20348,7 @@
         <v>412</v>
       </c>
       <c r="B360" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C360">
         <f t="shared" ca="1" si="6"/>
@@ -20403,7 +20403,7 @@
       </c>
       <c r="C361">
         <f t="shared" ca="1" si="6"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D361" t="s">
         <v>184</v>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="C362">
         <f t="shared" ca="1" si="6"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D362" t="s">
         <v>184</v>
@@ -20501,7 +20501,7 @@
         <v>415</v>
       </c>
       <c r="B363" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C363">
         <f t="shared" ca="1" si="6"/>
@@ -20552,7 +20552,7 @@
         <v>416</v>
       </c>
       <c r="B364" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C364">
         <f t="shared" ca="1" si="6"/>
@@ -20603,7 +20603,7 @@
         <v>417</v>
       </c>
       <c r="B365" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C365">
         <f t="shared" ca="1" si="6"/>
@@ -20654,7 +20654,7 @@
         <v>418</v>
       </c>
       <c r="B366" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C366">
         <f t="shared" ca="1" si="6"/>
@@ -20705,7 +20705,7 @@
         <v>419</v>
       </c>
       <c r="B367" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C367">
         <f t="shared" ca="1" si="6"/>
@@ -20756,7 +20756,7 @@
         <v>420</v>
       </c>
       <c r="B368" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C368">
         <f t="shared" ca="1" si="6"/>
@@ -20807,7 +20807,7 @@
         <v>421</v>
       </c>
       <c r="B369" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C369">
         <f t="shared" ca="1" si="6"/>
@@ -20858,7 +20858,7 @@
         <v>422</v>
       </c>
       <c r="B370" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C370">
         <f t="shared" ca="1" si="6"/>
@@ -20913,7 +20913,7 @@
       </c>
       <c r="C371">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D371" t="s">
         <v>184</v>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C372">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D372" t="s">
         <v>184</v>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C373">
         <f t="shared" ca="1" si="6"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D373" t="s">
         <v>184</v>
@@ -21062,7 +21062,7 @@
         <v>426</v>
       </c>
       <c r="B374" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C374">
         <f t="shared" ca="1" si="6"/>
@@ -21113,7 +21113,7 @@
         <v>427</v>
       </c>
       <c r="B375" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C375">
         <f t="shared" ca="1" si="6"/>
@@ -21164,7 +21164,7 @@
         <v>428</v>
       </c>
       <c r="B376" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C376">
         <f t="shared" ca="1" si="6"/>
@@ -21215,7 +21215,7 @@
         <v>429</v>
       </c>
       <c r="B377" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C377">
         <f t="shared" ca="1" si="6"/>
@@ -21266,7 +21266,7 @@
         <v>430</v>
       </c>
       <c r="B378" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C378">
         <f t="shared" ca="1" si="6"/>
@@ -21317,7 +21317,7 @@
         <v>431</v>
       </c>
       <c r="B379" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C379">
         <f t="shared" ca="1" si="6"/>
@@ -21368,7 +21368,7 @@
         <v>432</v>
       </c>
       <c r="B380" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C380">
         <f t="shared" ca="1" si="6"/>
@@ -21419,7 +21419,7 @@
         <v>433</v>
       </c>
       <c r="B381" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C381">
         <f t="shared" ca="1" si="6"/>
@@ -21474,7 +21474,7 @@
       </c>
       <c r="C382">
         <f t="shared" ca="1" si="6"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D382" t="s">
         <v>184</v>
@@ -21521,11 +21521,11 @@
         <v>435</v>
       </c>
       <c r="B383" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C383">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D383" t="s">
         <v>184</v>
@@ -21576,7 +21576,7 @@
       </c>
       <c r="C384">
         <f t="shared" ref="C384:C391" ca="1" si="7">B384-$R$1</f>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D384" t="s">
         <v>184</v>
@@ -21627,7 +21627,7 @@
       </c>
       <c r="C385">
         <f t="shared" ca="1" si="7"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D385" t="s">
         <v>184</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="C386">
         <f t="shared" ca="1" si="7"/>
-        <v>-46317</v>
+        <v>-46318</v>
       </c>
       <c r="D386" t="s">
         <v>184</v>
@@ -21729,7 +21729,7 @@
       </c>
       <c r="C387">
         <f t="shared" ca="1" si="7"/>
-        <v>-46317</v>
+        <v>-46318</v>
       </c>
       <c r="D387" t="s">
         <v>184</v>
@@ -21780,7 +21780,7 @@
       </c>
       <c r="C388">
         <f t="shared" ca="1" si="7"/>
-        <v>-46317</v>
+        <v>-46318</v>
       </c>
       <c r="D388" t="s">
         <v>184</v>
@@ -21831,7 +21831,7 @@
       </c>
       <c r="C389">
         <f t="shared" ca="1" si="7"/>
-        <v>-46317</v>
+        <v>-46318</v>
       </c>
       <c r="D389" t="s">
         <v>184</v>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="C390">
         <f t="shared" ca="1" si="7"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D390" t="s">
         <v>184</v>
@@ -21929,11 +21929,11 @@
         <v>443</v>
       </c>
       <c r="B391" s="2">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="C391">
         <f t="shared" ca="1" si="7"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D391" t="s">
         <v>184</v>
@@ -21982,6 +21982,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -21991,15 +22000,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22264,20 +22264,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="446" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F743263-5561-4440-98BF-18E2B83EC2C2}"/>
+  <xr:revisionPtr revIDLastSave="454" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89721849-851B-48B3-A4C6-2327B958081E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4795" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4797" uniqueCount="467">
   <si>
     <t>Placa</t>
   </si>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="R1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1875,11 +1875,11 @@
         <v>9</v>
       </c>
       <c r="B2" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C2">
         <f ca="1">B2-$R$1</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D2" t="s">
         <v>184</v>
@@ -1927,7 +1927,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="2">
-        <v>46316</v>
+        <v>46319</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C66" ca="1" si="0">B3-$R$1</f>
@@ -1979,11 +1979,11 @@
         <v>15</v>
       </c>
       <c r="B4" s="2">
-        <v>46315</v>
+        <v>46320</v>
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D4" t="s">
         <v>184</v>
@@ -2031,11 +2031,11 @@
         <v>16</v>
       </c>
       <c r="B5" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D5" t="s">
         <v>184</v>
@@ -2083,7 +2083,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="D7" t="s">
         <v>184</v>
@@ -2187,11 +2187,11 @@
         <v>19</v>
       </c>
       <c r="B8" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D8" t="s">
         <v>184</v>
@@ -2239,7 +2239,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
@@ -2291,7 +2291,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
@@ -2345,11 +2345,11 @@
         <v>26</v>
       </c>
       <c r="B11" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D11" t="s">
         <v>184</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="B12" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
@@ -2453,7 +2453,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
@@ -2507,11 +2507,11 @@
         <v>36</v>
       </c>
       <c r="B14" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D14" t="s">
         <v>184</v>
@@ -2561,7 +2561,7 @@
         <v>37</v>
       </c>
       <c r="B15" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
@@ -2615,11 +2615,11 @@
         <v>38</v>
       </c>
       <c r="B16" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D16" t="s">
         <v>184</v>
@@ -2669,11 +2669,11 @@
         <v>39</v>
       </c>
       <c r="B17" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D17" t="s">
         <v>184</v>
@@ -2723,11 +2723,11 @@
         <v>40</v>
       </c>
       <c r="B18" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D18" t="s">
         <v>184</v>
@@ -2777,11 +2777,11 @@
         <v>41</v>
       </c>
       <c r="B19" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D19" t="s">
         <v>184</v>
@@ -2831,7 +2831,7 @@
         <v>42</v>
       </c>
       <c r="B20" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
@@ -2885,7 +2885,7 @@
         <v>43</v>
       </c>
       <c r="B21" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="0"/>
@@ -2939,7 +2939,7 @@
         <v>44</v>
       </c>
       <c r="B22" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="0"/>
@@ -2993,7 +2993,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="0"/>
@@ -3047,11 +3047,11 @@
         <v>47</v>
       </c>
       <c r="B24" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D24" t="s">
         <v>184</v>
@@ -3101,11 +3101,11 @@
         <v>48</v>
       </c>
       <c r="B25" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D25" t="s">
         <v>184</v>
@@ -3155,11 +3155,11 @@
         <v>49</v>
       </c>
       <c r="B26" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D26" t="s">
         <v>184</v>
@@ -3209,11 +3209,11 @@
         <v>50</v>
       </c>
       <c r="B27" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D27" t="s">
         <v>184</v>
@@ -3263,11 +3263,11 @@
         <v>51</v>
       </c>
       <c r="B28" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D28" t="s">
         <v>184</v>
@@ -3317,11 +3317,11 @@
         <v>52</v>
       </c>
       <c r="B29" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D29" t="s">
         <v>184</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="D30" t="s">
         <v>184</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D31" t="s">
         <v>184</v>
@@ -3479,11 +3479,11 @@
         <v>55</v>
       </c>
       <c r="B32" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D32" t="s">
         <v>184</v>
@@ -3533,7 +3533,7 @@
         <v>56</v>
       </c>
       <c r="B33" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="0"/>
@@ -3587,11 +3587,11 @@
         <v>57</v>
       </c>
       <c r="B34" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D34" t="s">
         <v>184</v>
@@ -3641,11 +3641,11 @@
         <v>58</v>
       </c>
       <c r="B35" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D35" t="s">
         <v>184</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D36" t="s">
         <v>184</v>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="0"/>
-        <v>-52</v>
+        <v>-55</v>
       </c>
       <c r="D37" t="s">
         <v>184</v>
@@ -3803,11 +3803,11 @@
         <v>62</v>
       </c>
       <c r="B38" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D38" t="s">
         <v>184</v>
@@ -3857,7 +3857,7 @@
         <v>63</v>
       </c>
       <c r="B39" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="0"/>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="0"/>
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="D40" t="s">
         <v>184</v>
@@ -3965,11 +3965,11 @@
         <v>65</v>
       </c>
       <c r="B41" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D41" t="s">
         <v>184</v>
@@ -4019,11 +4019,11 @@
         <v>66</v>
       </c>
       <c r="B42" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D42" t="s">
         <v>184</v>
@@ -4073,7 +4073,7 @@
         <v>67</v>
       </c>
       <c r="B43" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="0"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="D44" t="s">
         <v>184</v>
@@ -4181,7 +4181,7 @@
         <v>69</v>
       </c>
       <c r="B45" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="0"/>
@@ -4235,11 +4235,11 @@
         <v>70</v>
       </c>
       <c r="B46" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D46" t="s">
         <v>184</v>
@@ -4289,11 +4289,11 @@
         <v>71</v>
       </c>
       <c r="B47" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D47" t="s">
         <v>184</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="0"/>
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="D48" t="s">
         <v>184</v>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="D49" t="s">
         <v>184</v>
@@ -4451,11 +4451,11 @@
         <v>74</v>
       </c>
       <c r="B50" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D50" t="s">
         <v>184</v>
@@ -4505,11 +4505,11 @@
         <v>75</v>
       </c>
       <c r="B51" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D51" t="s">
         <v>184</v>
@@ -4559,11 +4559,11 @@
         <v>76</v>
       </c>
       <c r="B52" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D52" t="s">
         <v>184</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D53" t="s">
         <v>184</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="0"/>
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="D54" t="s">
         <v>184</v>
@@ -4721,11 +4721,11 @@
         <v>79</v>
       </c>
       <c r="B55" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D55" t="s">
         <v>184</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="0"/>
-        <v>-22</v>
+        <v>-25</v>
       </c>
       <c r="D56" t="s">
         <v>184</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="0"/>
-        <v>-16</v>
+        <v>-19</v>
       </c>
       <c r="D57" t="s">
         <v>184</v>
@@ -4883,11 +4883,11 @@
         <v>82</v>
       </c>
       <c r="B58" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D58" t="s">
         <v>184</v>
@@ -4937,7 +4937,7 @@
         <v>83</v>
       </c>
       <c r="B59" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="0"/>
@@ -4991,11 +4991,11 @@
         <v>84</v>
       </c>
       <c r="B60" s="2">
-        <v>46315</v>
+        <v>46320</v>
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D60" t="s">
         <v>184</v>
@@ -5045,7 +5045,7 @@
         <v>85</v>
       </c>
       <c r="B61" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="0"/>
@@ -5099,7 +5099,7 @@
         <v>86</v>
       </c>
       <c r="B62" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="0"/>
@@ -5153,11 +5153,11 @@
         <v>87</v>
       </c>
       <c r="B63" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D63" t="s">
         <v>184</v>
@@ -5207,7 +5207,7 @@
         <v>90</v>
       </c>
       <c r="B64" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="0"/>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="D65" t="s">
         <v>184</v>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="0"/>
-        <v>-28</v>
+        <v>-31</v>
       </c>
       <c r="D66" t="s">
         <v>184</v>
@@ -5369,11 +5369,11 @@
         <v>94</v>
       </c>
       <c r="B67" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C67">
         <f t="shared" ref="C67:C130" ca="1" si="1">B67-$R$1</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D67" t="s">
         <v>184</v>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="1"/>
-        <v>-63</v>
+        <v>-66</v>
       </c>
       <c r="D68" t="s">
         <v>184</v>
@@ -5477,11 +5477,11 @@
         <v>96</v>
       </c>
       <c r="B69" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D69" t="s">
         <v>184</v>
@@ -5531,11 +5531,11 @@
         <v>97</v>
       </c>
       <c r="B70" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D70" t="s">
         <v>184</v>
@@ -5585,11 +5585,11 @@
         <v>98</v>
       </c>
       <c r="B71" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D71" t="s">
         <v>184</v>
@@ -5639,11 +5639,11 @@
         <v>99</v>
       </c>
       <c r="B72" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D72" t="s">
         <v>184</v>
@@ -5693,7 +5693,7 @@
         <v>100</v>
       </c>
       <c r="B73" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="1"/>
@@ -5747,7 +5747,7 @@
         <v>102</v>
       </c>
       <c r="B74" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="1"/>
@@ -5801,7 +5801,7 @@
         <v>103</v>
       </c>
       <c r="B75" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="1"/>
@@ -5855,7 +5855,7 @@
         <v>104</v>
       </c>
       <c r="B76" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="1"/>
@@ -5909,7 +5909,7 @@
         <v>105</v>
       </c>
       <c r="B77" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="1"/>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="1"/>
-        <v>-30</v>
+        <v>-33</v>
       </c>
       <c r="D78" t="s">
         <v>184</v>
@@ -6071,11 +6071,11 @@
         <v>108</v>
       </c>
       <c r="B80" s="2">
-        <v>46315</v>
+        <v>46320</v>
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D80" t="s">
         <v>184</v>
@@ -6233,11 +6233,11 @@
         <v>111</v>
       </c>
       <c r="B83" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D83" t="s">
         <v>184</v>
@@ -6287,11 +6287,11 @@
         <v>112</v>
       </c>
       <c r="B84" s="2">
-        <v>46314</v>
+        <v>46320</v>
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="1"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D84" t="s">
         <v>184</v>
@@ -6341,7 +6341,7 @@
         <v>113</v>
       </c>
       <c r="B85" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="1"/>
@@ -6395,11 +6395,11 @@
         <v>114</v>
       </c>
       <c r="B86" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D86" t="s">
         <v>184</v>
@@ -6503,7 +6503,7 @@
         <v>116</v>
       </c>
       <c r="B88" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="1"/>
@@ -6557,11 +6557,11 @@
         <v>117</v>
       </c>
       <c r="B89" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D89" t="s">
         <v>184</v>
@@ -6611,11 +6611,11 @@
         <v>121</v>
       </c>
       <c r="B90" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D90" t="s">
         <v>184</v>
@@ -6665,7 +6665,7 @@
         <v>122</v>
       </c>
       <c r="B91" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="1"/>
@@ -6719,11 +6719,11 @@
         <v>123</v>
       </c>
       <c r="B92" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D92" t="s">
         <v>184</v>
@@ -6773,11 +6773,11 @@
         <v>124</v>
       </c>
       <c r="B93" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D93" t="s">
         <v>184</v>
@@ -6827,7 +6827,7 @@
         <v>125</v>
       </c>
       <c r="B94" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="1"/>
@@ -6881,11 +6881,11 @@
         <v>126</v>
       </c>
       <c r="B95" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D95" t="s">
         <v>184</v>
@@ -6935,11 +6935,11 @@
         <v>127</v>
       </c>
       <c r="B96" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D96" t="s">
         <v>184</v>
@@ -6989,7 +6989,7 @@
         <v>128</v>
       </c>
       <c r="B97" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="1"/>
@@ -7043,11 +7043,11 @@
         <v>129</v>
       </c>
       <c r="B98" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D98" t="s">
         <v>184</v>
@@ -7097,11 +7097,11 @@
         <v>130</v>
       </c>
       <c r="B99" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D99" t="s">
         <v>184</v>
@@ -7151,11 +7151,11 @@
         <v>131</v>
       </c>
       <c r="B100" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D100" t="s">
         <v>184</v>
@@ -7205,7 +7205,7 @@
         <v>132</v>
       </c>
       <c r="B101" s="2">
-        <v>46316</v>
+        <v>46319</v>
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="1"/>
@@ -7259,11 +7259,11 @@
         <v>133</v>
       </c>
       <c r="B102" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C102">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D102" t="s">
         <v>184</v>
@@ -7313,7 +7313,7 @@
         <v>134</v>
       </c>
       <c r="B103" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C103">
         <f t="shared" ca="1" si="1"/>
@@ -7367,11 +7367,11 @@
         <v>135</v>
       </c>
       <c r="B104" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C104">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D104" t="s">
         <v>184</v>
@@ -7421,7 +7421,7 @@
         <v>136</v>
       </c>
       <c r="B105" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C105">
         <f t="shared" ca="1" si="1"/>
@@ -7475,11 +7475,11 @@
         <v>137</v>
       </c>
       <c r="B106" s="2">
-        <v>46315</v>
+        <v>46320</v>
       </c>
       <c r="C106">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D106" t="s">
         <v>184</v>
@@ -7529,7 +7529,7 @@
         <v>138</v>
       </c>
       <c r="B107" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C107">
         <f t="shared" ca="1" si="1"/>
@@ -7583,7 +7583,7 @@
         <v>139</v>
       </c>
       <c r="B108" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C108">
         <f t="shared" ca="1" si="1"/>
@@ -7637,7 +7637,7 @@
         <v>140</v>
       </c>
       <c r="B109" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C109">
         <f t="shared" ca="1" si="1"/>
@@ -7691,7 +7691,7 @@
         <v>141</v>
       </c>
       <c r="B110" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C110">
         <f t="shared" ca="1" si="1"/>
@@ -7745,7 +7745,7 @@
         <v>142</v>
       </c>
       <c r="B111" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C111">
         <f t="shared" ca="1" si="1"/>
@@ -7831,11 +7831,11 @@
         <v>143</v>
       </c>
       <c r="B113" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C113">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D113" t="s">
         <v>184</v>
@@ -7885,11 +7885,11 @@
         <v>144</v>
       </c>
       <c r="B114" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C114">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D114" t="s">
         <v>184</v>
@@ -7939,11 +7939,11 @@
         <v>145</v>
       </c>
       <c r="B115" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C115">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D115" t="s">
         <v>184</v>
@@ -7993,11 +7993,11 @@
         <v>147</v>
       </c>
       <c r="B116" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C116">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D116" t="s">
         <v>184</v>
@@ -8047,11 +8047,11 @@
         <v>148</v>
       </c>
       <c r="B117" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C117">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D117" t="s">
         <v>184</v>
@@ -8101,11 +8101,11 @@
         <v>149</v>
       </c>
       <c r="B118" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C118">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D118" t="s">
         <v>184</v>
@@ -8155,11 +8155,11 @@
         <v>150</v>
       </c>
       <c r="B119" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C119">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D119" t="s">
         <v>184</v>
@@ -8209,7 +8209,7 @@
         <v>151</v>
       </c>
       <c r="B120" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C120">
         <f t="shared" ca="1" si="1"/>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C121">
         <f t="shared" ca="1" si="1"/>
-        <v>-46318</v>
+        <v>-46321</v>
       </c>
       <c r="D121" t="s">
         <v>465</v>
@@ -8317,7 +8317,7 @@
         <v>154</v>
       </c>
       <c r="B122" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C122">
         <f t="shared" ca="1" si="1"/>
@@ -8371,7 +8371,7 @@
         <v>155</v>
       </c>
       <c r="B123" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C123">
         <f t="shared" ca="1" si="1"/>
@@ -8425,7 +8425,7 @@
         <v>156</v>
       </c>
       <c r="B124" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C124">
         <f t="shared" ca="1" si="1"/>
@@ -8479,11 +8479,11 @@
         <v>157</v>
       </c>
       <c r="B125" s="2">
-        <v>46314</v>
+        <v>46320</v>
       </c>
       <c r="C125">
         <f t="shared" ca="1" si="1"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D125" t="s">
         <v>184</v>
@@ -8533,7 +8533,7 @@
         <v>158</v>
       </c>
       <c r="B126" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C126">
         <f t="shared" ca="1" si="1"/>
@@ -8587,7 +8587,7 @@
         <v>159</v>
       </c>
       <c r="B127" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C127">
         <f t="shared" ca="1" si="1"/>
@@ -8641,11 +8641,11 @@
         <v>160</v>
       </c>
       <c r="B128" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C128">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D128" t="s">
         <v>184</v>
@@ -8695,7 +8695,7 @@
         <v>161</v>
       </c>
       <c r="B129" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C129">
         <f t="shared" ca="1" si="1"/>
@@ -8749,11 +8749,11 @@
         <v>162</v>
       </c>
       <c r="B130" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C130">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D130" t="s">
         <v>184</v>
@@ -8803,7 +8803,7 @@
         <v>186</v>
       </c>
       <c r="B131" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C131">
         <f t="shared" ref="C131:C193" ca="1" si="2">B131-$R$1</f>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="C132">
         <f t="shared" ca="1" si="2"/>
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="D132" t="s">
         <v>184</v>
@@ -8953,7 +8953,7 @@
         <v>188</v>
       </c>
       <c r="B134" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C134">
         <f t="shared" ca="1" si="2"/>
@@ -9007,7 +9007,7 @@
         <v>189</v>
       </c>
       <c r="B135" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C135">
         <f t="shared" ca="1" si="2"/>
@@ -9061,7 +9061,7 @@
         <v>190</v>
       </c>
       <c r="B136" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C136">
         <f t="shared" ca="1" si="2"/>
@@ -9115,7 +9115,7 @@
         <v>191</v>
       </c>
       <c r="B137" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C137">
         <f t="shared" ca="1" si="2"/>
@@ -9169,7 +9169,7 @@
         <v>192</v>
       </c>
       <c r="B138" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C138">
         <f t="shared" ca="1" si="2"/>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C140">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="D140" t="s">
         <v>184</v>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="C145">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="D145" t="s">
         <v>184</v>
@@ -9706,7 +9706,7 @@
         <v>205</v>
       </c>
       <c r="B151" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C151">
         <f t="shared" ca="1" si="2"/>
@@ -9756,11 +9756,11 @@
         <v>164</v>
       </c>
       <c r="B152" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C152">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D152" t="s">
         <v>184</v>
@@ -9810,7 +9810,7 @@
         <v>165</v>
       </c>
       <c r="B153" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C153">
         <f t="shared" ca="1" si="2"/>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="C154">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="D154" t="s">
         <v>184</v>
@@ -9918,11 +9918,11 @@
         <v>167</v>
       </c>
       <c r="B155" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D155" t="s">
         <v>184</v>
@@ -9972,7 +9972,7 @@
         <v>168</v>
       </c>
       <c r="B156" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
-        <v>-29</v>
+        <v>-32</v>
       </c>
       <c r="D157" t="s">
         <v>184</v>
@@ -10080,7 +10080,7 @@
         <v>170</v>
       </c>
       <c r="B158" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C158">
         <f t="shared" ca="1" si="2"/>
@@ -10134,7 +10134,7 @@
         <v>171</v>
       </c>
       <c r="B159" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C159">
         <f t="shared" ca="1" si="2"/>
@@ -10188,11 +10188,11 @@
         <v>172</v>
       </c>
       <c r="B160" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D160" t="s">
         <v>184</v>
@@ -10242,7 +10242,7 @@
         <v>173</v>
       </c>
       <c r="B161" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
@@ -10296,11 +10296,11 @@
         <v>175</v>
       </c>
       <c r="B162" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D162" t="s">
         <v>184</v>
@@ -10350,7 +10350,7 @@
         <v>176</v>
       </c>
       <c r="B163" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C163">
         <f t="shared" ca="1" si="2"/>
@@ -10404,11 +10404,11 @@
         <v>206</v>
       </c>
       <c r="B164" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C164">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D164" t="s">
         <v>184</v>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
-        <v>-46318</v>
+        <v>-46321</v>
       </c>
       <c r="D165" t="s">
         <v>184</v>
@@ -10500,7 +10500,7 @@
         <v>208</v>
       </c>
       <c r="B166" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C166">
         <f t="shared" ca="1" si="2"/>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="C167">
         <f t="shared" ca="1" si="2"/>
-        <v>-46318</v>
+        <v>-46321</v>
       </c>
       <c r="D167" t="s">
         <v>465</v>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C168">
         <f t="shared" ca="1" si="2"/>
-        <v>-46318</v>
+        <v>-46321</v>
       </c>
       <c r="D168" t="s">
         <v>465</v>
@@ -10638,7 +10638,7 @@
         <v>211</v>
       </c>
       <c r="B169" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C169">
         <f t="shared" ca="1" si="2"/>
@@ -10692,7 +10692,7 @@
         <v>212</v>
       </c>
       <c r="B170" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C170">
         <f t="shared" ca="1" si="2"/>
@@ -10734,8 +10734,12 @@
       <c r="O170" t="s">
         <v>217</v>
       </c>
-      <c r="P170" s="2"/>
-      <c r="Q170" s="2"/>
+      <c r="P170" s="2">
+        <v>46310</v>
+      </c>
+      <c r="Q170" s="2">
+        <v>46310</v>
+      </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
@@ -10746,7 +10750,7 @@
       </c>
       <c r="C171">
         <f t="shared" ca="1" si="2"/>
-        <v>-46318</v>
+        <v>-46321</v>
       </c>
       <c r="D171" t="s">
         <v>465</v>
@@ -10788,7 +10792,7 @@
       </c>
       <c r="C172">
         <f t="shared" ca="1" si="2"/>
-        <v>-46318</v>
+        <v>-46321</v>
       </c>
       <c r="D172" t="s">
         <v>465</v>
@@ -10832,6 +10836,12 @@
         <f t="shared" ca="1" si="2"/>
         <v>#N/A</v>
       </c>
+      <c r="D173" t="s">
+        <v>184</v>
+      </c>
+      <c r="I173" t="s">
+        <v>184</v>
+      </c>
       <c r="J173" t="s">
         <v>22</v>
       </c>
@@ -10866,7 +10876,7 @@
       </c>
       <c r="C174">
         <f t="shared" ca="1" si="2"/>
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="D174" t="s">
         <v>184</v>
@@ -10913,11 +10923,11 @@
         <v>227</v>
       </c>
       <c r="B175" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C175">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D175" t="s">
         <v>184</v>
@@ -10968,7 +10978,7 @@
       </c>
       <c r="C176">
         <f t="shared" ca="1" si="2"/>
-        <v>-19</v>
+        <v>-22</v>
       </c>
       <c r="D176" t="s">
         <v>184</v>
@@ -11015,11 +11025,11 @@
         <v>229</v>
       </c>
       <c r="B177" s="2">
-        <v>46315</v>
+        <v>46320</v>
       </c>
       <c r="C177">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D177" t="s">
         <v>184</v>
@@ -11066,11 +11076,11 @@
         <v>230</v>
       </c>
       <c r="B178" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C178">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D178" t="s">
         <v>184</v>
@@ -11117,7 +11127,7 @@
         <v>231</v>
       </c>
       <c r="B179" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C179">
         <f t="shared" ca="1" si="2"/>
@@ -11168,7 +11178,7 @@
         <v>232</v>
       </c>
       <c r="B180" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C180">
         <f t="shared" ca="1" si="2"/>
@@ -11219,11 +11229,11 @@
         <v>233</v>
       </c>
       <c r="B181" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C181">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D181" t="s">
         <v>184</v>
@@ -11274,7 +11284,7 @@
       </c>
       <c r="C182">
         <f t="shared" ca="1" si="2"/>
-        <v>-16</v>
+        <v>-19</v>
       </c>
       <c r="D182" t="s">
         <v>184</v>
@@ -11321,11 +11331,11 @@
         <v>235</v>
       </c>
       <c r="B183" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C183">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D183" t="s">
         <v>184</v>
@@ -11372,11 +11382,11 @@
         <v>236</v>
       </c>
       <c r="B184" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C184">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D184" t="s">
         <v>184</v>
@@ -11427,7 +11437,7 @@
       </c>
       <c r="C185">
         <f t="shared" ca="1" si="2"/>
-        <v>-52</v>
+        <v>-55</v>
       </c>
       <c r="D185" t="s">
         <v>184</v>
@@ -11478,7 +11488,7 @@
       </c>
       <c r="C186">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="D186" t="s">
         <v>184</v>
@@ -11525,7 +11535,7 @@
         <v>239</v>
       </c>
       <c r="B187" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C187">
         <f t="shared" ca="1" si="2"/>
@@ -11580,7 +11590,7 @@
       </c>
       <c r="C188">
         <f t="shared" ca="1" si="2"/>
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="D188" t="s">
         <v>184</v>
@@ -11627,11 +11637,11 @@
         <v>241</v>
       </c>
       <c r="B189" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C189">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D189" t="s">
         <v>184</v>
@@ -11678,11 +11688,11 @@
         <v>242</v>
       </c>
       <c r="B190" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C190">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D190" t="s">
         <v>184</v>
@@ -11729,11 +11739,11 @@
         <v>243</v>
       </c>
       <c r="B191" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C191">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D191" t="s">
         <v>184</v>
@@ -11780,7 +11790,7 @@
         <v>244</v>
       </c>
       <c r="B192" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C192">
         <f t="shared" ca="1" si="2"/>
@@ -11835,7 +11845,7 @@
       </c>
       <c r="C193">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D193" t="s">
         <v>184</v>
@@ -11886,7 +11896,7 @@
       </c>
       <c r="C194">
         <f t="shared" ref="C194:C255" ca="1" si="4">B194-$R$1</f>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="D194" t="s">
         <v>184</v>
@@ -11937,7 +11947,7 @@
       </c>
       <c r="C195">
         <f t="shared" ca="1" si="4"/>
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="D195" t="s">
         <v>184</v>
@@ -11984,11 +11994,11 @@
         <v>248</v>
       </c>
       <c r="B196" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C196">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D196" t="s">
         <v>184</v>
@@ -12039,7 +12049,7 @@
       </c>
       <c r="C197">
         <f t="shared" ca="1" si="4"/>
-        <v>-151</v>
+        <v>-154</v>
       </c>
       <c r="D197" t="s">
         <v>184</v>
@@ -12090,7 +12100,7 @@
       </c>
       <c r="C198">
         <f t="shared" ca="1" si="4"/>
-        <v>-32</v>
+        <v>-35</v>
       </c>
       <c r="D198" t="s">
         <v>184</v>
@@ -12141,7 +12151,7 @@
       </c>
       <c r="C199">
         <f t="shared" ca="1" si="4"/>
-        <v>-37</v>
+        <v>-40</v>
       </c>
       <c r="D199" t="s">
         <v>184</v>
@@ -12192,7 +12202,7 @@
       </c>
       <c r="C200">
         <f t="shared" ca="1" si="4"/>
-        <v>-19</v>
+        <v>-22</v>
       </c>
       <c r="D200" t="s">
         <v>184</v>
@@ -12243,7 +12253,7 @@
       </c>
       <c r="C201">
         <f t="shared" ca="1" si="4"/>
-        <v>-281</v>
+        <v>-284</v>
       </c>
       <c r="D201" t="s">
         <v>184</v>
@@ -12290,11 +12300,11 @@
         <v>254</v>
       </c>
       <c r="B202" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C202">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D202" t="s">
         <v>184</v>
@@ -12341,7 +12351,7 @@
         <v>255</v>
       </c>
       <c r="B203" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C203">
         <f t="shared" ca="1" si="4"/>
@@ -12392,7 +12402,7 @@
         <v>256</v>
       </c>
       <c r="B204" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C204">
         <f t="shared" ca="1" si="4"/>
@@ -12443,11 +12453,11 @@
         <v>257</v>
       </c>
       <c r="B205" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C205">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D205" t="s">
         <v>184</v>
@@ -12494,11 +12504,11 @@
         <v>258</v>
       </c>
       <c r="B206" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C206">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D206" t="s">
         <v>184</v>
@@ -12545,7 +12555,7 @@
         <v>259</v>
       </c>
       <c r="B207" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C207">
         <f t="shared" ca="1" si="4"/>
@@ -12596,7 +12606,7 @@
         <v>260</v>
       </c>
       <c r="B208" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C208">
         <f t="shared" ca="1" si="4"/>
@@ -12647,11 +12657,11 @@
         <v>261</v>
       </c>
       <c r="B209" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C209">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D209" t="s">
         <v>184</v>
@@ -12698,11 +12708,11 @@
         <v>262</v>
       </c>
       <c r="B210" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C210">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D210" t="s">
         <v>184</v>
@@ -12749,7 +12759,7 @@
         <v>263</v>
       </c>
       <c r="B211" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C211">
         <f t="shared" ca="1" si="4"/>
@@ -12800,7 +12810,7 @@
         <v>264</v>
       </c>
       <c r="B212" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C212">
         <f t="shared" ca="1" si="4"/>
@@ -12851,11 +12861,11 @@
         <v>265</v>
       </c>
       <c r="B213" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C213">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D213" t="s">
         <v>184</v>
@@ -12902,7 +12912,7 @@
         <v>266</v>
       </c>
       <c r="B214" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C214">
         <f t="shared" ca="1" si="4"/>
@@ -12957,7 +12967,7 @@
       </c>
       <c r="C215">
         <f t="shared" ca="1" si="4"/>
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="D215" t="s">
         <v>184</v>
@@ -13008,7 +13018,7 @@
       </c>
       <c r="C216">
         <f t="shared" ca="1" si="4"/>
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
@@ -13055,11 +13065,11 @@
         <v>269</v>
       </c>
       <c r="B217" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C217">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D217" t="s">
         <v>184</v>
@@ -13110,7 +13120,7 @@
       </c>
       <c r="C218">
         <f t="shared" ca="1" si="4"/>
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="D218" t="s">
         <v>184</v>
@@ -13161,7 +13171,7 @@
       </c>
       <c r="C219">
         <f t="shared" ca="1" si="4"/>
-        <v>-33</v>
+        <v>-36</v>
       </c>
       <c r="D219" t="s">
         <v>184</v>
@@ -13208,11 +13218,11 @@
         <v>272</v>
       </c>
       <c r="B220" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C220">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D220" t="s">
         <v>184</v>
@@ -13263,7 +13273,7 @@
       </c>
       <c r="C221">
         <f t="shared" ca="1" si="4"/>
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="D221" t="s">
         <v>184</v>
@@ -13310,11 +13320,11 @@
         <v>274</v>
       </c>
       <c r="B222" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C222">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D222" t="s">
         <v>184</v>
@@ -13361,7 +13371,7 @@
         <v>275</v>
       </c>
       <c r="B223" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C223">
         <f t="shared" ca="1" si="4"/>
@@ -13412,11 +13422,11 @@
         <v>276</v>
       </c>
       <c r="B224" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C224">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D224" t="s">
         <v>184</v>
@@ -13463,7 +13473,7 @@
         <v>277</v>
       </c>
       <c r="B225" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C225">
         <f t="shared" ca="1" si="4"/>
@@ -13514,11 +13524,11 @@
         <v>278</v>
       </c>
       <c r="B226" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C226">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D226" t="s">
         <v>184</v>
@@ -13565,11 +13575,11 @@
         <v>279</v>
       </c>
       <c r="B227" s="2">
-        <v>46292</v>
+        <v>46318</v>
       </c>
       <c r="C227">
         <f t="shared" ca="1" si="4"/>
-        <v>-26</v>
+        <v>-3</v>
       </c>
       <c r="D227" t="s">
         <v>184</v>
@@ -13616,11 +13626,11 @@
         <v>280</v>
       </c>
       <c r="B228" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C228">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D228" t="s">
         <v>184</v>
@@ -13667,11 +13677,11 @@
         <v>281</v>
       </c>
       <c r="B229" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C229">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D229" t="s">
         <v>184</v>
@@ -13718,11 +13728,11 @@
         <v>282</v>
       </c>
       <c r="B230" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C230">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D230" t="s">
         <v>184</v>
@@ -13769,7 +13779,7 @@
         <v>283</v>
       </c>
       <c r="B231" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C231">
         <f t="shared" ca="1" si="4"/>
@@ -13820,7 +13830,7 @@
         <v>284</v>
       </c>
       <c r="B232" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C232">
         <f t="shared" ca="1" si="4"/>
@@ -13875,7 +13885,7 @@
       </c>
       <c r="C233">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="D233" t="s">
         <v>184</v>
@@ -13922,11 +13932,11 @@
         <v>286</v>
       </c>
       <c r="B234" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C234">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D234" t="s">
         <v>184</v>
@@ -13973,11 +13983,11 @@
         <v>287</v>
       </c>
       <c r="B235" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C235">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D235" t="s">
         <v>184</v>
@@ -14024,7 +14034,7 @@
         <v>288</v>
       </c>
       <c r="B236" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C236">
         <f t="shared" ca="1" si="4"/>
@@ -14075,7 +14085,7 @@
         <v>289</v>
       </c>
       <c r="B237" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C237">
         <f t="shared" ca="1" si="4"/>
@@ -14126,11 +14136,11 @@
         <v>290</v>
       </c>
       <c r="B238" s="2">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="C238">
         <f t="shared" ca="1" si="4"/>
-        <v>-17</v>
+        <v>-2</v>
       </c>
       <c r="D238" t="s">
         <v>184</v>
@@ -14177,7 +14187,7 @@
         <v>291</v>
       </c>
       <c r="B239" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C239">
         <f t="shared" ca="1" si="4"/>
@@ -14228,7 +14238,7 @@
         <v>292</v>
       </c>
       <c r="B240" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C240">
         <f t="shared" ca="1" si="4"/>
@@ -14283,7 +14293,7 @@
       </c>
       <c r="C241">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="D241" t="s">
         <v>184</v>
@@ -14330,7 +14340,7 @@
         <v>294</v>
       </c>
       <c r="B242" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C242">
         <f t="shared" ca="1" si="4"/>
@@ -14381,11 +14391,11 @@
         <v>295</v>
       </c>
       <c r="B243" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C243">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D243" t="s">
         <v>184</v>
@@ -14432,7 +14442,7 @@
         <v>296</v>
       </c>
       <c r="B244" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C244">
         <f t="shared" ca="1" si="4"/>
@@ -14483,11 +14493,11 @@
         <v>297</v>
       </c>
       <c r="B245" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C245">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D245" t="s">
         <v>184</v>
@@ -14534,11 +14544,11 @@
         <v>298</v>
       </c>
       <c r="B246" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C246">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D246" t="s">
         <v>184</v>
@@ -14589,7 +14599,7 @@
       </c>
       <c r="C247">
         <f t="shared" ca="1" si="4"/>
-        <v>-36</v>
+        <v>-39</v>
       </c>
       <c r="D247" t="s">
         <v>184</v>
@@ -14636,7 +14646,7 @@
         <v>300</v>
       </c>
       <c r="B248" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C248">
         <f t="shared" ca="1" si="4"/>
@@ -14687,11 +14697,11 @@
         <v>301</v>
       </c>
       <c r="B249" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C249">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D249" t="s">
         <v>184</v>
@@ -14738,7 +14748,7 @@
         <v>302</v>
       </c>
       <c r="B250" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C250">
         <f t="shared" ca="1" si="4"/>
@@ -14789,7 +14799,7 @@
         <v>303</v>
       </c>
       <c r="B251" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C251">
         <f t="shared" ca="1" si="4"/>
@@ -14840,7 +14850,7 @@
         <v>304</v>
       </c>
       <c r="B252" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C252">
         <f t="shared" ca="1" si="4"/>
@@ -14895,7 +14905,7 @@
       </c>
       <c r="C253">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="D253" t="s">
         <v>184</v>
@@ -14946,7 +14956,7 @@
       </c>
       <c r="C254">
         <f t="shared" ca="1" si="4"/>
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="D254" t="s">
         <v>184</v>
@@ -14993,7 +15003,7 @@
         <v>307</v>
       </c>
       <c r="B255" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C255">
         <f t="shared" ca="1" si="4"/>
@@ -15048,7 +15058,7 @@
       </c>
       <c r="C256">
         <f t="shared" ref="C256:C319" ca="1" si="5">B256-$R$1</f>
-        <v>-111</v>
+        <v>-114</v>
       </c>
       <c r="D256" t="s">
         <v>184</v>
@@ -15095,7 +15105,7 @@
         <v>309</v>
       </c>
       <c r="B257" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C257">
         <f t="shared" ca="1" si="5"/>
@@ -15146,7 +15156,7 @@
         <v>310</v>
       </c>
       <c r="B258" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C258">
         <f t="shared" ca="1" si="5"/>
@@ -15197,7 +15207,7 @@
         <v>311</v>
       </c>
       <c r="B259" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C259">
         <f t="shared" ca="1" si="5"/>
@@ -15248,7 +15258,7 @@
         <v>312</v>
       </c>
       <c r="B260" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C260">
         <f t="shared" ca="1" si="5"/>
@@ -15303,7 +15313,7 @@
       </c>
       <c r="C261">
         <f t="shared" ca="1" si="5"/>
-        <v>-21</v>
+        <v>-24</v>
       </c>
       <c r="D261" t="s">
         <v>184</v>
@@ -15350,11 +15360,11 @@
         <v>314</v>
       </c>
       <c r="B262" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C262">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D262" t="s">
         <v>184</v>
@@ -15401,7 +15411,7 @@
         <v>315</v>
       </c>
       <c r="B263" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C263">
         <f t="shared" ca="1" si="5"/>
@@ -15452,7 +15462,7 @@
         <v>316</v>
       </c>
       <c r="B264" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C264">
         <f t="shared" ca="1" si="5"/>
@@ -15507,7 +15517,7 @@
       </c>
       <c r="C265">
         <f t="shared" ca="1" si="5"/>
-        <v>-16</v>
+        <v>-19</v>
       </c>
       <c r="D265" t="s">
         <v>184</v>
@@ -15558,7 +15568,7 @@
       </c>
       <c r="C266">
         <f t="shared" ca="1" si="5"/>
-        <v>-141</v>
+        <v>-144</v>
       </c>
       <c r="D266" t="s">
         <v>184</v>
@@ -15605,11 +15615,11 @@
         <v>319</v>
       </c>
       <c r="B267" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C267">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D267" t="s">
         <v>184</v>
@@ -15660,7 +15670,7 @@
       </c>
       <c r="C268">
         <f t="shared" ca="1" si="5"/>
-        <v>-19</v>
+        <v>-22</v>
       </c>
       <c r="D268" t="s">
         <v>184</v>
@@ -15707,7 +15717,7 @@
         <v>321</v>
       </c>
       <c r="B269" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C269">
         <f t="shared" ca="1" si="5"/>
@@ -15758,11 +15768,11 @@
         <v>322</v>
       </c>
       <c r="B270" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C270">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D270" t="s">
         <v>184</v>
@@ -15809,7 +15819,7 @@
         <v>323</v>
       </c>
       <c r="B271" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C271">
         <f t="shared" ca="1" si="5"/>
@@ -15860,11 +15870,11 @@
         <v>324</v>
       </c>
       <c r="B272" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C272">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D272" t="s">
         <v>184</v>
@@ -15911,11 +15921,11 @@
         <v>325</v>
       </c>
       <c r="B273" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C273">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D273" t="s">
         <v>184</v>
@@ -15962,11 +15972,11 @@
         <v>326</v>
       </c>
       <c r="B274" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C274">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D274" t="s">
         <v>184</v>
@@ -16013,11 +16023,11 @@
         <v>327</v>
       </c>
       <c r="B275" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C275">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D275" t="s">
         <v>184</v>
@@ -16064,11 +16074,11 @@
         <v>328</v>
       </c>
       <c r="B276" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C276">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D276" t="s">
         <v>184</v>
@@ -16115,7 +16125,7 @@
         <v>329</v>
       </c>
       <c r="B277" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C277">
         <f t="shared" ca="1" si="5"/>
@@ -16170,7 +16180,7 @@
       </c>
       <c r="C278">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D278" t="s">
         <v>184</v>
@@ -16217,11 +16227,11 @@
         <v>331</v>
       </c>
       <c r="B279" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C279">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D279" t="s">
         <v>184</v>
@@ -16268,11 +16278,11 @@
         <v>332</v>
       </c>
       <c r="B280" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C280">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D280" t="s">
         <v>184</v>
@@ -16323,7 +16333,7 @@
       </c>
       <c r="C281">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="D281" t="s">
         <v>184</v>
@@ -16370,11 +16380,11 @@
         <v>334</v>
       </c>
       <c r="B282" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C282">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D282" t="s">
         <v>184</v>
@@ -16421,11 +16431,11 @@
         <v>335</v>
       </c>
       <c r="B283" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C283">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D283" t="s">
         <v>184</v>
@@ -16476,7 +16486,7 @@
       </c>
       <c r="C284">
         <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="D284" t="s">
         <v>184</v>
@@ -16523,7 +16533,7 @@
         <v>337</v>
       </c>
       <c r="B285" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C285">
         <f t="shared" ca="1" si="5"/>
@@ -16574,7 +16584,7 @@
         <v>338</v>
       </c>
       <c r="B286" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C286">
         <f t="shared" ca="1" si="5"/>
@@ -16629,7 +16639,7 @@
       </c>
       <c r="C287">
         <f t="shared" ca="1" si="5"/>
-        <v>-227</v>
+        <v>-230</v>
       </c>
       <c r="D287" t="s">
         <v>184</v>
@@ -16676,7 +16686,7 @@
         <v>340</v>
       </c>
       <c r="B288" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C288">
         <f t="shared" ca="1" si="5"/>
@@ -16727,7 +16737,7 @@
         <v>341</v>
       </c>
       <c r="B289" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C289">
         <f t="shared" ca="1" si="5"/>
@@ -16778,11 +16788,11 @@
         <v>342</v>
       </c>
       <c r="B290" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C290">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D290" t="s">
         <v>184</v>
@@ -16829,7 +16839,7 @@
         <v>343</v>
       </c>
       <c r="B291" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C291">
         <f t="shared" ca="1" si="5"/>
@@ -16880,11 +16890,11 @@
         <v>344</v>
       </c>
       <c r="B292" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C292">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D292" t="s">
         <v>184</v>
@@ -16931,7 +16941,7 @@
         <v>345</v>
       </c>
       <c r="B293" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C293">
         <f t="shared" ca="1" si="5"/>
@@ -16982,7 +16992,7 @@
         <v>346</v>
       </c>
       <c r="B294" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C294">
         <f t="shared" ca="1" si="5"/>
@@ -17033,11 +17043,11 @@
         <v>347</v>
       </c>
       <c r="B295" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C295">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D295" t="s">
         <v>184</v>
@@ -17088,7 +17098,7 @@
       </c>
       <c r="C296">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="D296" t="s">
         <v>184</v>
@@ -17135,11 +17145,11 @@
         <v>349</v>
       </c>
       <c r="B297" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C297">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D297" t="s">
         <v>184</v>
@@ -17186,11 +17196,11 @@
         <v>350</v>
       </c>
       <c r="B298" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C298">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D298" t="s">
         <v>184</v>
@@ -17237,11 +17247,11 @@
         <v>351</v>
       </c>
       <c r="B299" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C299">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D299" t="s">
         <v>184</v>
@@ -17288,7 +17298,7 @@
         <v>352</v>
       </c>
       <c r="B300" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C300">
         <f t="shared" ca="1" si="5"/>
@@ -17339,7 +17349,7 @@
         <v>353</v>
       </c>
       <c r="B301" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C301">
         <f t="shared" ca="1" si="5"/>
@@ -17390,11 +17400,11 @@
         <v>354</v>
       </c>
       <c r="B302" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C302">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D302" t="s">
         <v>184</v>
@@ -17441,11 +17451,11 @@
         <v>355</v>
       </c>
       <c r="B303" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C303">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D303" t="s">
         <v>184</v>
@@ -17492,7 +17502,7 @@
         <v>356</v>
       </c>
       <c r="B304" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C304">
         <f t="shared" ca="1" si="5"/>
@@ -17543,7 +17553,7 @@
         <v>357</v>
       </c>
       <c r="B305" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C305">
         <f t="shared" ca="1" si="5"/>
@@ -17594,7 +17604,7 @@
         <v>358</v>
       </c>
       <c r="B306" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C306">
         <f t="shared" ca="1" si="5"/>
@@ -17645,11 +17655,11 @@
         <v>359</v>
       </c>
       <c r="B307" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C307">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D307" t="s">
         <v>184</v>
@@ -17700,7 +17710,7 @@
       </c>
       <c r="C308">
         <f t="shared" ca="1" si="5"/>
-        <v>-16</v>
+        <v>-19</v>
       </c>
       <c r="D308" t="s">
         <v>184</v>
@@ -17751,7 +17761,7 @@
       </c>
       <c r="C309">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="D309" t="s">
         <v>184</v>
@@ -17798,11 +17808,11 @@
         <v>362</v>
       </c>
       <c r="B310" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C310">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D310" t="s">
         <v>184</v>
@@ -17849,11 +17859,11 @@
         <v>363</v>
       </c>
       <c r="B311" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C311">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D311" t="s">
         <v>184</v>
@@ -17900,7 +17910,7 @@
         <v>364</v>
       </c>
       <c r="B312" s="2">
-        <v>46316</v>
+        <v>46319</v>
       </c>
       <c r="C312">
         <f t="shared" ca="1" si="5"/>
@@ -17951,7 +17961,7 @@
         <v>365</v>
       </c>
       <c r="B313" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C313">
         <f t="shared" ca="1" si="5"/>
@@ -18006,7 +18016,7 @@
       </c>
       <c r="C314">
         <f t="shared" ca="1" si="5"/>
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="D314" t="s">
         <v>184</v>
@@ -18053,11 +18063,11 @@
         <v>367</v>
       </c>
       <c r="B315" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C315">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D315" t="s">
         <v>184</v>
@@ -18104,11 +18114,11 @@
         <v>368</v>
       </c>
       <c r="B316" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C316">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D316" t="s">
         <v>184</v>
@@ -18159,7 +18169,7 @@
       </c>
       <c r="C317">
         <f t="shared" ca="1" si="5"/>
-        <v>-74</v>
+        <v>-77</v>
       </c>
       <c r="D317" t="s">
         <v>184</v>
@@ -18206,11 +18216,11 @@
         <v>370</v>
       </c>
       <c r="B318" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C318">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D318" t="s">
         <v>184</v>
@@ -18257,11 +18267,11 @@
         <v>371</v>
       </c>
       <c r="B319" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C319">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D319" t="s">
         <v>184</v>
@@ -18308,7 +18318,7 @@
         <v>372</v>
       </c>
       <c r="B320" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C320">
         <f t="shared" ref="C320:C383" ca="1" si="6">B320-$R$1</f>
@@ -18363,7 +18373,7 @@
       </c>
       <c r="C321">
         <f t="shared" ca="1" si="6"/>
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="D321" t="s">
         <v>184</v>
@@ -18414,7 +18424,7 @@
       </c>
       <c r="C322">
         <f t="shared" ca="1" si="6"/>
-        <v>-78</v>
+        <v>-81</v>
       </c>
       <c r="D322" t="s">
         <v>184</v>
@@ -18465,7 +18475,7 @@
       </c>
       <c r="C323">
         <f t="shared" ca="1" si="6"/>
-        <v>-20</v>
+        <v>-23</v>
       </c>
       <c r="D323" t="s">
         <v>184</v>
@@ -18512,7 +18522,7 @@
         <v>376</v>
       </c>
       <c r="B324" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C324">
         <f t="shared" ca="1" si="6"/>
@@ -18563,11 +18573,11 @@
         <v>377</v>
       </c>
       <c r="B325" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C325">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D325" t="s">
         <v>184</v>
@@ -18614,11 +18624,11 @@
         <v>378</v>
       </c>
       <c r="B326" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C326">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D326" t="s">
         <v>184</v>
@@ -18665,7 +18675,7 @@
         <v>379</v>
       </c>
       <c r="B327" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C327">
         <f t="shared" ca="1" si="6"/>
@@ -18720,7 +18730,7 @@
       </c>
       <c r="C328">
         <f t="shared" ca="1" si="6"/>
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="D328" t="s">
         <v>184</v>
@@ -18767,7 +18777,7 @@
         <v>381</v>
       </c>
       <c r="B329" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C329">
         <f t="shared" ca="1" si="6"/>
@@ -18818,7 +18828,7 @@
         <v>382</v>
       </c>
       <c r="B330" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C330">
         <f t="shared" ca="1" si="6"/>
@@ -18869,7 +18879,7 @@
         <v>383</v>
       </c>
       <c r="B331" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C331">
         <f t="shared" ca="1" si="6"/>
@@ -18924,7 +18934,7 @@
       </c>
       <c r="C332">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="D332" t="s">
         <v>184</v>
@@ -18971,11 +18981,11 @@
         <v>385</v>
       </c>
       <c r="B333" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C333">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D333" t="s">
         <v>184</v>
@@ -19022,7 +19032,7 @@
         <v>386</v>
       </c>
       <c r="B334" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C334">
         <f t="shared" ca="1" si="6"/>
@@ -19073,7 +19083,7 @@
         <v>387</v>
       </c>
       <c r="B335" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C335">
         <f t="shared" ca="1" si="6"/>
@@ -19124,11 +19134,11 @@
         <v>388</v>
       </c>
       <c r="B336" s="2">
-        <v>46315</v>
+        <v>46320</v>
       </c>
       <c r="C336">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D336" t="s">
         <v>184</v>
@@ -19175,11 +19185,11 @@
         <v>389</v>
       </c>
       <c r="B337" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C337">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D337" t="s">
         <v>184</v>
@@ -19230,7 +19240,7 @@
       </c>
       <c r="C338">
         <f t="shared" ca="1" si="6"/>
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="D338" t="s">
         <v>184</v>
@@ -19277,7 +19287,7 @@
         <v>391</v>
       </c>
       <c r="B339" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C339">
         <f t="shared" ca="1" si="6"/>
@@ -19328,11 +19338,11 @@
         <v>392</v>
       </c>
       <c r="B340" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C340">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D340" t="s">
         <v>184</v>
@@ -19379,11 +19389,11 @@
         <v>393</v>
       </c>
       <c r="B341" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C341">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D341" t="s">
         <v>184</v>
@@ -19434,7 +19444,7 @@
       </c>
       <c r="C342">
         <f t="shared" ca="1" si="6"/>
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="D342" t="s">
         <v>184</v>
@@ -19481,11 +19491,11 @@
         <v>395</v>
       </c>
       <c r="B343" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C343">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D343" t="s">
         <v>184</v>
@@ -19532,11 +19542,11 @@
         <v>396</v>
       </c>
       <c r="B344" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C344">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D344" t="s">
         <v>184</v>
@@ -19583,11 +19593,11 @@
         <v>397</v>
       </c>
       <c r="B345" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C345">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D345" t="s">
         <v>184</v>
@@ -19634,7 +19644,7 @@
         <v>398</v>
       </c>
       <c r="B346" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C346">
         <f t="shared" ca="1" si="6"/>
@@ -19689,7 +19699,7 @@
       </c>
       <c r="C347">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D347" t="s">
         <v>184</v>
@@ -19736,7 +19746,7 @@
         <v>400</v>
       </c>
       <c r="B348" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C348">
         <f t="shared" ca="1" si="6"/>
@@ -19787,11 +19797,11 @@
         <v>401</v>
       </c>
       <c r="B349" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C349">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D349" t="s">
         <v>184</v>
@@ -19838,11 +19848,11 @@
         <v>402</v>
       </c>
       <c r="B350" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C350">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D350" t="s">
         <v>184</v>
@@ -19893,7 +19903,7 @@
       </c>
       <c r="C351">
         <f t="shared" ca="1" si="6"/>
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="D351" t="s">
         <v>184</v>
@@ -19940,7 +19950,7 @@
         <v>404</v>
       </c>
       <c r="B352" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C352">
         <f t="shared" ca="1" si="6"/>
@@ -19991,7 +20001,7 @@
         <v>405</v>
       </c>
       <c r="B353" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C353">
         <f t="shared" ca="1" si="6"/>
@@ -20042,7 +20052,7 @@
         <v>406</v>
       </c>
       <c r="B354" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C354">
         <f t="shared" ca="1" si="6"/>
@@ -20093,7 +20103,7 @@
         <v>407</v>
       </c>
       <c r="B355" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C355">
         <f t="shared" ca="1" si="6"/>
@@ -20148,7 +20158,7 @@
       </c>
       <c r="C356">
         <f t="shared" ca="1" si="6"/>
-        <v>-20</v>
+        <v>-23</v>
       </c>
       <c r="D356" t="s">
         <v>184</v>
@@ -20195,7 +20205,7 @@
         <v>409</v>
       </c>
       <c r="B357" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C357">
         <f t="shared" ca="1" si="6"/>
@@ -20246,7 +20256,7 @@
         <v>410</v>
       </c>
       <c r="B358" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C358">
         <f t="shared" ca="1" si="6"/>
@@ -20297,7 +20307,7 @@
         <v>411</v>
       </c>
       <c r="B359" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C359">
         <f t="shared" ca="1" si="6"/>
@@ -20348,7 +20358,7 @@
         <v>412</v>
       </c>
       <c r="B360" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C360">
         <f t="shared" ca="1" si="6"/>
@@ -20399,11 +20409,11 @@
         <v>413</v>
       </c>
       <c r="B361" s="2">
-        <v>46307</v>
+        <v>46320</v>
       </c>
       <c r="C361">
         <f t="shared" ca="1" si="6"/>
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="D361" t="s">
         <v>184</v>
@@ -20454,7 +20464,7 @@
       </c>
       <c r="C362">
         <f t="shared" ca="1" si="6"/>
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="D362" t="s">
         <v>184</v>
@@ -20501,7 +20511,7 @@
         <v>415</v>
       </c>
       <c r="B363" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C363">
         <f t="shared" ca="1" si="6"/>
@@ -20552,11 +20562,11 @@
         <v>416</v>
       </c>
       <c r="B364" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C364">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D364" t="s">
         <v>184</v>
@@ -20603,11 +20613,11 @@
         <v>417</v>
       </c>
       <c r="B365" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C365">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D365" t="s">
         <v>184</v>
@@ -20654,11 +20664,11 @@
         <v>418</v>
       </c>
       <c r="B366" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C366">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D366" t="s">
         <v>184</v>
@@ -20705,11 +20715,11 @@
         <v>419</v>
       </c>
       <c r="B367" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C367">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D367" t="s">
         <v>184</v>
@@ -20756,11 +20766,11 @@
         <v>420</v>
       </c>
       <c r="B368" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C368">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D368" t="s">
         <v>184</v>
@@ -20807,11 +20817,11 @@
         <v>421</v>
       </c>
       <c r="B369" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C369">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D369" t="s">
         <v>184</v>
@@ -20858,7 +20868,7 @@
         <v>422</v>
       </c>
       <c r="B370" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C370">
         <f t="shared" ca="1" si="6"/>
@@ -20913,7 +20923,7 @@
       </c>
       <c r="C371">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D371" t="s">
         <v>184</v>
@@ -20964,7 +20974,7 @@
       </c>
       <c r="C372">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D372" t="s">
         <v>184</v>
@@ -21015,7 +21025,7 @@
       </c>
       <c r="C373">
         <f t="shared" ca="1" si="6"/>
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="D373" t="s">
         <v>184</v>
@@ -21062,7 +21072,7 @@
         <v>426</v>
       </c>
       <c r="B374" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C374">
         <f t="shared" ca="1" si="6"/>
@@ -21113,7 +21123,7 @@
         <v>427</v>
       </c>
       <c r="B375" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C375">
         <f t="shared" ca="1" si="6"/>
@@ -21164,7 +21174,7 @@
         <v>428</v>
       </c>
       <c r="B376" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C376">
         <f t="shared" ca="1" si="6"/>
@@ -21215,11 +21225,11 @@
         <v>429</v>
       </c>
       <c r="B377" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C377">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D377" t="s">
         <v>184</v>
@@ -21266,7 +21276,7 @@
         <v>430</v>
       </c>
       <c r="B378" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C378">
         <f t="shared" ca="1" si="6"/>
@@ -21317,11 +21327,11 @@
         <v>431</v>
       </c>
       <c r="B379" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C379">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D379" t="s">
         <v>184</v>
@@ -21368,7 +21378,7 @@
         <v>432</v>
       </c>
       <c r="B380" s="2">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C380">
         <f t="shared" ca="1" si="6"/>
@@ -21419,11 +21429,11 @@
         <v>433</v>
       </c>
       <c r="B381" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C381">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D381" t="s">
         <v>184</v>
@@ -21474,7 +21484,7 @@
       </c>
       <c r="C382">
         <f t="shared" ca="1" si="6"/>
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="D382" t="s">
         <v>184</v>
@@ -21525,7 +21535,7 @@
       </c>
       <c r="C383">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="D383" t="s">
         <v>184</v>
@@ -21576,7 +21586,7 @@
       </c>
       <c r="C384">
         <f t="shared" ref="C384:C391" ca="1" si="7">B384-$R$1</f>
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="D384" t="s">
         <v>184</v>
@@ -21623,11 +21633,11 @@
         <v>437</v>
       </c>
       <c r="B385" s="2">
-        <v>46314</v>
+        <v>46319</v>
       </c>
       <c r="C385">
         <f t="shared" ca="1" si="7"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D385" t="s">
         <v>184</v>
@@ -21678,7 +21688,7 @@
       </c>
       <c r="C386">
         <f t="shared" ca="1" si="7"/>
-        <v>-46318</v>
+        <v>-46321</v>
       </c>
       <c r="D386" t="s">
         <v>184</v>
@@ -21729,7 +21739,7 @@
       </c>
       <c r="C387">
         <f t="shared" ca="1" si="7"/>
-        <v>-46318</v>
+        <v>-46321</v>
       </c>
       <c r="D387" t="s">
         <v>184</v>
@@ -21780,7 +21790,7 @@
       </c>
       <c r="C388">
         <f t="shared" ca="1" si="7"/>
-        <v>-46318</v>
+        <v>-46321</v>
       </c>
       <c r="D388" t="s">
         <v>184</v>
@@ -21831,7 +21841,7 @@
       </c>
       <c r="C389">
         <f t="shared" ca="1" si="7"/>
-        <v>-46318</v>
+        <v>-46321</v>
       </c>
       <c r="D389" t="s">
         <v>184</v>
@@ -21878,7 +21888,7 @@
         <v>442</v>
       </c>
       <c r="B390" s="2">
-        <v>46316</v>
+        <v>46319</v>
       </c>
       <c r="C390">
         <f t="shared" ca="1" si="7"/>
@@ -21929,11 +21939,11 @@
         <v>443</v>
       </c>
       <c r="B391" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="C391">
         <f t="shared" ca="1" si="7"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D391" t="s">
         <v>184</v>
@@ -21976,21 +21986,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R391" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -22000,6 +22000,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22264,20 +22273,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="454" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89721849-851B-48B3-A4C6-2327B958081E}"/>
+  <xr:revisionPtr revIDLastSave="460" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18961E38-3AF3-43B4-9AE4-6404601485A9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4797" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4798" uniqueCount="467">
   <si>
     <t>Placa</t>
   </si>
@@ -7805,6 +7805,9 @@
         <f t="shared" ca="1" si="1"/>
         <v>#N/A</v>
       </c>
+      <c r="D112" t="s">
+        <v>184</v>
+      </c>
       <c r="J112" t="s">
         <v>28</v>
       </c>
@@ -7823,8 +7826,12 @@
       <c r="O112" t="s">
         <v>217</v>
       </c>
-      <c r="P112" s="2"/>
-      <c r="Q112" s="2"/>
+      <c r="P112" s="2">
+        <v>46321</v>
+      </c>
+      <c r="Q112" s="2">
+        <v>46321</v>
+      </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
@@ -21991,18 +21998,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -22011,7 +22006,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -22272,18 +22267,19 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -22291,7 +22287,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22308,4 +22304,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="460" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18961E38-3AF3-43B4-9AE4-6404601485A9}"/>
+  <xr:revisionPtr revIDLastSave="463" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23962C76-70C0-4B0E-8509-22F9265062AF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="R1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C2">
         <f ca="1">B2-$R$1</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D2" t="s">
         <v>184</v>
@@ -1927,11 +1927,11 @@
         <v>14</v>
       </c>
       <c r="B3" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C66" ca="1" si="0">B3-$R$1</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D3" t="s">
         <v>184</v>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D4" t="s">
         <v>184</v>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D5" t="s">
         <v>184</v>
@@ -2083,7 +2083,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D7" t="s">
         <v>184</v>
@@ -2187,11 +2187,11 @@
         <v>19</v>
       </c>
       <c r="B8" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D8" t="s">
         <v>184</v>
@@ -2239,7 +2239,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
@@ -2291,7 +2291,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
@@ -2345,11 +2345,11 @@
         <v>26</v>
       </c>
       <c r="B11" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D11" t="s">
         <v>184</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="B12" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D13" t="s">
         <v>184</v>
@@ -2507,11 +2507,11 @@
         <v>36</v>
       </c>
       <c r="B14" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D14" t="s">
         <v>184</v>
@@ -2561,7 +2561,7 @@
         <v>37</v>
       </c>
       <c r="B15" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
@@ -2615,11 +2615,11 @@
         <v>38</v>
       </c>
       <c r="B16" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D16" t="s">
         <v>184</v>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D17" t="s">
         <v>184</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D18" t="s">
         <v>184</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D19" t="s">
         <v>184</v>
@@ -2831,7 +2831,7 @@
         <v>42</v>
       </c>
       <c r="B20" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
@@ -2885,7 +2885,7 @@
         <v>43</v>
       </c>
       <c r="B21" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="0"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D22" t="s">
         <v>184</v>
@@ -2993,7 +2993,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="0"/>
@@ -3047,11 +3047,11 @@
         <v>47</v>
       </c>
       <c r="B24" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D24" t="s">
         <v>184</v>
@@ -3101,11 +3101,11 @@
         <v>48</v>
       </c>
       <c r="B25" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D25" t="s">
         <v>184</v>
@@ -3155,11 +3155,11 @@
         <v>49</v>
       </c>
       <c r="B26" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D26" t="s">
         <v>184</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D27" t="s">
         <v>184</v>
@@ -3263,11 +3263,11 @@
         <v>51</v>
       </c>
       <c r="B28" s="2">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D28" t="s">
         <v>184</v>
@@ -3317,11 +3317,11 @@
         <v>52</v>
       </c>
       <c r="B29" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D29" t="s">
         <v>184</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D30" t="s">
         <v>184</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D31" t="s">
         <v>184</v>
@@ -3479,11 +3479,11 @@
         <v>55</v>
       </c>
       <c r="B32" s="2">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D32" t="s">
         <v>184</v>
@@ -3533,7 +3533,7 @@
         <v>56</v>
       </c>
       <c r="B33" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="0"/>
@@ -3587,11 +3587,11 @@
         <v>57</v>
       </c>
       <c r="B34" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D34" t="s">
         <v>184</v>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D35" t="s">
         <v>184</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D36" t="s">
         <v>184</v>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="0"/>
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="D37" t="s">
         <v>184</v>
@@ -3803,11 +3803,11 @@
         <v>62</v>
       </c>
       <c r="B38" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D38" t="s">
         <v>184</v>
@@ -3857,7 +3857,7 @@
         <v>63</v>
       </c>
       <c r="B39" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="0"/>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="0"/>
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="D40" t="s">
         <v>184</v>
@@ -3965,11 +3965,11 @@
         <v>65</v>
       </c>
       <c r="B41" s="2">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D41" t="s">
         <v>184</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D42" t="s">
         <v>184</v>
@@ -4073,7 +4073,7 @@
         <v>67</v>
       </c>
       <c r="B43" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="0"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D44" t="s">
         <v>184</v>
@@ -4181,7 +4181,7 @@
         <v>69</v>
       </c>
       <c r="B45" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="0"/>
@@ -4235,11 +4235,11 @@
         <v>70</v>
       </c>
       <c r="B46" s="2">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D46" t="s">
         <v>184</v>
@@ -4289,11 +4289,11 @@
         <v>71</v>
       </c>
       <c r="B47" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D47" t="s">
         <v>184</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="0"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D48" t="s">
         <v>184</v>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D49" t="s">
         <v>184</v>
@@ -4451,11 +4451,11 @@
         <v>74</v>
       </c>
       <c r="B50" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D50" t="s">
         <v>184</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D51" t="s">
         <v>184</v>
@@ -4559,11 +4559,11 @@
         <v>76</v>
       </c>
       <c r="B52" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D52" t="s">
         <v>184</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D53" t="s">
         <v>184</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="0"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D54" t="s">
         <v>184</v>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D55" t="s">
         <v>184</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="0"/>
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="D56" t="s">
         <v>184</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="0"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="D57" t="s">
         <v>184</v>
@@ -4883,11 +4883,11 @@
         <v>82</v>
       </c>
       <c r="B58" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D58" t="s">
         <v>184</v>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D59" t="s">
         <v>184</v>
@@ -4991,7 +4991,7 @@
         <v>84</v>
       </c>
       <c r="B60" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="0"/>
@@ -5045,7 +5045,7 @@
         <v>85</v>
       </c>
       <c r="B61" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="0"/>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D62" t="s">
         <v>184</v>
@@ -5153,11 +5153,11 @@
         <v>87</v>
       </c>
       <c r="B63" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D63" t="s">
         <v>184</v>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D64" t="s">
         <v>184</v>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D65" t="s">
         <v>184</v>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="0"/>
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="D66" t="s">
         <v>184</v>
@@ -5369,11 +5369,11 @@
         <v>94</v>
       </c>
       <c r="B67" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C67">
         <f t="shared" ref="C67:C130" ca="1" si="1">B67-$R$1</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D67" t="s">
         <v>184</v>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="1"/>
-        <v>-66</v>
+        <v>-67</v>
       </c>
       <c r="D68" t="s">
         <v>184</v>
@@ -5477,11 +5477,11 @@
         <v>96</v>
       </c>
       <c r="B69" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D69" t="s">
         <v>184</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D70" t="s">
         <v>184</v>
@@ -5585,11 +5585,11 @@
         <v>98</v>
       </c>
       <c r="B71" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D71" t="s">
         <v>184</v>
@@ -5639,11 +5639,11 @@
         <v>99</v>
       </c>
       <c r="B72" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D72" t="s">
         <v>184</v>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D73" t="s">
         <v>184</v>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D74" t="s">
         <v>184</v>
@@ -5801,7 +5801,7 @@
         <v>103</v>
       </c>
       <c r="B75" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="1"/>
@@ -5855,7 +5855,7 @@
         <v>104</v>
       </c>
       <c r="B76" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="1"/>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D77" t="s">
         <v>184</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="1"/>
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="D78" t="s">
         <v>184</v>
@@ -6071,7 +6071,7 @@
         <v>108</v>
       </c>
       <c r="B80" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="1"/>
@@ -6233,11 +6233,11 @@
         <v>111</v>
       </c>
       <c r="B83" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D83" t="s">
         <v>184</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D84" t="s">
         <v>184</v>
@@ -6341,7 +6341,7 @@
         <v>113</v>
       </c>
       <c r="B85" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="1"/>
@@ -6395,11 +6395,11 @@
         <v>114</v>
       </c>
       <c r="B86" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D86" t="s">
         <v>184</v>
@@ -6503,7 +6503,7 @@
         <v>116</v>
       </c>
       <c r="B88" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="1"/>
@@ -6557,11 +6557,11 @@
         <v>117</v>
       </c>
       <c r="B89" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D89" t="s">
         <v>184</v>
@@ -6611,11 +6611,11 @@
         <v>121</v>
       </c>
       <c r="B90" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D90" t="s">
         <v>184</v>
@@ -6665,7 +6665,7 @@
         <v>122</v>
       </c>
       <c r="B91" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="1"/>
@@ -6719,11 +6719,11 @@
         <v>123</v>
       </c>
       <c r="B92" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D92" t="s">
         <v>184</v>
@@ -6773,11 +6773,11 @@
         <v>124</v>
       </c>
       <c r="B93" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D93" t="s">
         <v>184</v>
@@ -6827,7 +6827,7 @@
         <v>125</v>
       </c>
       <c r="B94" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="1"/>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D95" t="s">
         <v>184</v>
@@ -6935,11 +6935,11 @@
         <v>127</v>
       </c>
       <c r="B96" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D96" t="s">
         <v>184</v>
@@ -6989,7 +6989,7 @@
         <v>128</v>
       </c>
       <c r="B97" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="1"/>
@@ -7043,11 +7043,11 @@
         <v>129</v>
       </c>
       <c r="B98" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D98" t="s">
         <v>184</v>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D99" t="s">
         <v>184</v>
@@ -7151,11 +7151,11 @@
         <v>131</v>
       </c>
       <c r="B100" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D100" t="s">
         <v>184</v>
@@ -7205,11 +7205,11 @@
         <v>132</v>
       </c>
       <c r="B101" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D101" t="s">
         <v>184</v>
@@ -7259,11 +7259,11 @@
         <v>133</v>
       </c>
       <c r="B102" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C102">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D102" t="s">
         <v>184</v>
@@ -7313,7 +7313,7 @@
         <v>134</v>
       </c>
       <c r="B103" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C103">
         <f t="shared" ca="1" si="1"/>
@@ -7367,11 +7367,11 @@
         <v>135</v>
       </c>
       <c r="B104" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C104">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D104" t="s">
         <v>184</v>
@@ -7421,7 +7421,7 @@
         <v>136</v>
       </c>
       <c r="B105" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C105">
         <f t="shared" ca="1" si="1"/>
@@ -7475,7 +7475,7 @@
         <v>137</v>
       </c>
       <c r="B106" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C106">
         <f t="shared" ca="1" si="1"/>
@@ -7529,7 +7529,7 @@
         <v>138</v>
       </c>
       <c r="B107" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C107">
         <f t="shared" ca="1" si="1"/>
@@ -7583,7 +7583,7 @@
         <v>139</v>
       </c>
       <c r="B108" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C108">
         <f t="shared" ca="1" si="1"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="C109">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D109" t="s">
         <v>184</v>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="C110">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D110" t="s">
         <v>184</v>
@@ -7745,7 +7745,7 @@
         <v>142</v>
       </c>
       <c r="B111" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C111">
         <f t="shared" ca="1" si="1"/>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="C113">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D113" t="s">
         <v>184</v>
@@ -7892,7 +7892,7 @@
         <v>144</v>
       </c>
       <c r="B114" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C114">
         <f t="shared" ca="1" si="1"/>
@@ -7946,11 +7946,11 @@
         <v>145</v>
       </c>
       <c r="B115" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C115">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D115" t="s">
         <v>184</v>
@@ -8000,11 +8000,11 @@
         <v>147</v>
       </c>
       <c r="B116" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C116">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D116" t="s">
         <v>184</v>
@@ -8054,11 +8054,11 @@
         <v>148</v>
       </c>
       <c r="B117" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C117">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D117" t="s">
         <v>184</v>
@@ -8108,11 +8108,11 @@
         <v>149</v>
       </c>
       <c r="B118" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C118">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D118" t="s">
         <v>184</v>
@@ -8162,11 +8162,11 @@
         <v>150</v>
       </c>
       <c r="B119" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C119">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D119" t="s">
         <v>184</v>
@@ -8216,7 +8216,7 @@
         <v>151</v>
       </c>
       <c r="B120" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C120">
         <f t="shared" ca="1" si="1"/>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="C121">
         <f t="shared" ca="1" si="1"/>
-        <v>-46321</v>
+        <v>-46322</v>
       </c>
       <c r="D121" t="s">
         <v>465</v>
@@ -8324,7 +8324,7 @@
         <v>154</v>
       </c>
       <c r="B122" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C122">
         <f t="shared" ca="1" si="1"/>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="C123">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D123" t="s">
         <v>184</v>
@@ -8432,7 +8432,7 @@
         <v>156</v>
       </c>
       <c r="B124" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C124">
         <f t="shared" ca="1" si="1"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="C125">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D125" t="s">
         <v>184</v>
@@ -8540,7 +8540,7 @@
         <v>158</v>
       </c>
       <c r="B126" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C126">
         <f t="shared" ca="1" si="1"/>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="C127">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D127" t="s">
         <v>184</v>
@@ -8648,11 +8648,11 @@
         <v>160</v>
       </c>
       <c r="B128" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C128">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D128" t="s">
         <v>184</v>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="C129">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D129" t="s">
         <v>184</v>
@@ -8756,11 +8756,11 @@
         <v>162</v>
       </c>
       <c r="B130" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C130">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D130" t="s">
         <v>184</v>
@@ -8810,7 +8810,7 @@
         <v>186</v>
       </c>
       <c r="B131" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C131">
         <f t="shared" ref="C131:C193" ca="1" si="2">B131-$R$1</f>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="C132">
         <f t="shared" ca="1" si="2"/>
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="D132" t="s">
         <v>184</v>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="C134">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D134" t="s">
         <v>184</v>
@@ -9014,7 +9014,7 @@
         <v>189</v>
       </c>
       <c r="B135" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C135">
         <f t="shared" ca="1" si="2"/>
@@ -9068,7 +9068,7 @@
         <v>190</v>
       </c>
       <c r="B136" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C136">
         <f t="shared" ca="1" si="2"/>
@@ -9122,7 +9122,7 @@
         <v>191</v>
       </c>
       <c r="B137" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C137">
         <f t="shared" ca="1" si="2"/>
@@ -9176,7 +9176,7 @@
         <v>192</v>
       </c>
       <c r="B138" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C138">
         <f t="shared" ca="1" si="2"/>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C140">
         <f t="shared" ca="1" si="2"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D140" t="s">
         <v>184</v>
@@ -9475,7 +9475,7 @@
       </c>
       <c r="C145">
         <f t="shared" ca="1" si="2"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D145" t="s">
         <v>184</v>
@@ -9713,7 +9713,7 @@
         <v>205</v>
       </c>
       <c r="B151" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C151">
         <f t="shared" ca="1" si="2"/>
@@ -9763,11 +9763,11 @@
         <v>164</v>
       </c>
       <c r="B152" s="2">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="C152">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D152" t="s">
         <v>184</v>
@@ -9817,7 +9817,7 @@
         <v>165</v>
       </c>
       <c r="B153" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C153">
         <f t="shared" ca="1" si="2"/>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="C154">
         <f t="shared" ca="1" si="2"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D154" t="s">
         <v>184</v>
@@ -9925,11 +9925,11 @@
         <v>167</v>
       </c>
       <c r="B155" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D155" t="s">
         <v>184</v>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D156" t="s">
         <v>184</v>
@@ -10037,7 +10037,7 @@
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="D157" t="s">
         <v>184</v>
@@ -10087,7 +10087,7 @@
         <v>170</v>
       </c>
       <c r="B158" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C158">
         <f t="shared" ca="1" si="2"/>
@@ -10141,7 +10141,7 @@
         <v>171</v>
       </c>
       <c r="B159" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C159">
         <f t="shared" ca="1" si="2"/>
@@ -10195,11 +10195,11 @@
         <v>172</v>
       </c>
       <c r="B160" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D160" t="s">
         <v>184</v>
@@ -10249,7 +10249,7 @@
         <v>173</v>
       </c>
       <c r="B161" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
@@ -10303,7 +10303,7 @@
         <v>175</v>
       </c>
       <c r="B162" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
@@ -10357,7 +10357,7 @@
         <v>176</v>
       </c>
       <c r="B163" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C163">
         <f t="shared" ca="1" si="2"/>
@@ -10411,7 +10411,7 @@
         <v>206</v>
       </c>
       <c r="B164" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C164">
         <f t="shared" ca="1" si="2"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
-        <v>-46321</v>
+        <v>-46322</v>
       </c>
       <c r="D165" t="s">
         <v>184</v>
@@ -10507,7 +10507,7 @@
         <v>208</v>
       </c>
       <c r="B166" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C166">
         <f t="shared" ca="1" si="2"/>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="C167">
         <f t="shared" ca="1" si="2"/>
-        <v>-46321</v>
+        <v>-46322</v>
       </c>
       <c r="D167" t="s">
         <v>465</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="C168">
         <f t="shared" ca="1" si="2"/>
-        <v>-46321</v>
+        <v>-46322</v>
       </c>
       <c r="D168" t="s">
         <v>465</v>
@@ -10645,7 +10645,7 @@
         <v>211</v>
       </c>
       <c r="B169" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C169">
         <f t="shared" ca="1" si="2"/>
@@ -10699,7 +10699,7 @@
         <v>212</v>
       </c>
       <c r="B170" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C170">
         <f t="shared" ca="1" si="2"/>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="C171">
         <f t="shared" ca="1" si="2"/>
-        <v>-46321</v>
+        <v>-46322</v>
       </c>
       <c r="D171" t="s">
         <v>465</v>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="C172">
         <f t="shared" ca="1" si="2"/>
-        <v>-46321</v>
+        <v>-46322</v>
       </c>
       <c r="D172" t="s">
         <v>465</v>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="C174">
         <f t="shared" ca="1" si="2"/>
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="D174" t="s">
         <v>184</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C175">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D175" t="s">
         <v>184</v>
@@ -10985,7 +10985,7 @@
       </c>
       <c r="C176">
         <f t="shared" ca="1" si="2"/>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="D176" t="s">
         <v>184</v>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="C177">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D177" t="s">
         <v>184</v>
@@ -11083,11 +11083,11 @@
         <v>230</v>
       </c>
       <c r="B178" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C178">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D178" t="s">
         <v>184</v>
@@ -11134,7 +11134,7 @@
         <v>231</v>
       </c>
       <c r="B179" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C179">
         <f t="shared" ca="1" si="2"/>
@@ -11185,7 +11185,7 @@
         <v>232</v>
       </c>
       <c r="B180" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C180">
         <f t="shared" ca="1" si="2"/>
@@ -11236,11 +11236,11 @@
         <v>233</v>
       </c>
       <c r="B181" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C181">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D181" t="s">
         <v>184</v>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="C182">
         <f t="shared" ca="1" si="2"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="D182" t="s">
         <v>184</v>
@@ -11342,7 +11342,7 @@
       </c>
       <c r="C183">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D183" t="s">
         <v>184</v>
@@ -11389,11 +11389,11 @@
         <v>236</v>
       </c>
       <c r="B184" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C184">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D184" t="s">
         <v>184</v>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="C185">
         <f t="shared" ca="1" si="2"/>
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="D185" t="s">
         <v>184</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C186">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D186" t="s">
         <v>184</v>
@@ -11542,7 +11542,7 @@
         <v>239</v>
       </c>
       <c r="B187" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C187">
         <f t="shared" ca="1" si="2"/>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="C188">
         <f t="shared" ca="1" si="2"/>
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="D188" t="s">
         <v>184</v>
@@ -11648,7 +11648,7 @@
       </c>
       <c r="C189">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D189" t="s">
         <v>184</v>
@@ -11695,11 +11695,11 @@
         <v>242</v>
       </c>
       <c r="B190" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C190">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D190" t="s">
         <v>184</v>
@@ -11746,11 +11746,11 @@
         <v>243</v>
       </c>
       <c r="B191" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C191">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D191" t="s">
         <v>184</v>
@@ -11797,7 +11797,7 @@
         <v>244</v>
       </c>
       <c r="B192" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C192">
         <f t="shared" ca="1" si="2"/>
@@ -11852,7 +11852,7 @@
       </c>
       <c r="C193">
         <f t="shared" ca="1" si="2"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D193" t="s">
         <v>184</v>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="C194">
         <f t="shared" ref="C194:C255" ca="1" si="4">B194-$R$1</f>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D194" t="s">
         <v>184</v>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="C195">
         <f t="shared" ca="1" si="4"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="D195" t="s">
         <v>184</v>
@@ -12001,11 +12001,11 @@
         <v>248</v>
       </c>
       <c r="B196" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C196">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D196" t="s">
         <v>184</v>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="C197">
         <f t="shared" ca="1" si="4"/>
-        <v>-154</v>
+        <v>-155</v>
       </c>
       <c r="D197" t="s">
         <v>184</v>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="C198">
         <f t="shared" ca="1" si="4"/>
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="D198" t="s">
         <v>184</v>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="C199">
         <f t="shared" ca="1" si="4"/>
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="D199" t="s">
         <v>184</v>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="C200">
         <f t="shared" ca="1" si="4"/>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="D200" t="s">
         <v>184</v>
@@ -12260,7 +12260,7 @@
       </c>
       <c r="C201">
         <f t="shared" ca="1" si="4"/>
-        <v>-284</v>
+        <v>-285</v>
       </c>
       <c r="D201" t="s">
         <v>184</v>
@@ -12307,11 +12307,11 @@
         <v>254</v>
       </c>
       <c r="B202" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C202">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D202" t="s">
         <v>184</v>
@@ -12358,7 +12358,7 @@
         <v>255</v>
       </c>
       <c r="B203" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C203">
         <f t="shared" ca="1" si="4"/>
@@ -12409,7 +12409,7 @@
         <v>256</v>
       </c>
       <c r="B204" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C204">
         <f t="shared" ca="1" si="4"/>
@@ -12460,11 +12460,11 @@
         <v>257</v>
       </c>
       <c r="B205" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C205">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D205" t="s">
         <v>184</v>
@@ -12511,11 +12511,11 @@
         <v>258</v>
       </c>
       <c r="B206" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C206">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D206" t="s">
         <v>184</v>
@@ -12562,7 +12562,7 @@
         <v>259</v>
       </c>
       <c r="B207" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C207">
         <f t="shared" ca="1" si="4"/>
@@ -12613,7 +12613,7 @@
         <v>260</v>
       </c>
       <c r="B208" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C208">
         <f t="shared" ca="1" si="4"/>
@@ -12664,11 +12664,11 @@
         <v>261</v>
       </c>
       <c r="B209" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C209">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D209" t="s">
         <v>184</v>
@@ -12715,7 +12715,7 @@
         <v>262</v>
       </c>
       <c r="B210" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C210">
         <f t="shared" ca="1" si="4"/>
@@ -12766,7 +12766,7 @@
         <v>263</v>
       </c>
       <c r="B211" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C211">
         <f t="shared" ca="1" si="4"/>
@@ -12817,7 +12817,7 @@
         <v>264</v>
       </c>
       <c r="B212" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C212">
         <f t="shared" ca="1" si="4"/>
@@ -12868,11 +12868,11 @@
         <v>265</v>
       </c>
       <c r="B213" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C213">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D213" t="s">
         <v>184</v>
@@ -12919,7 +12919,7 @@
         <v>266</v>
       </c>
       <c r="B214" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C214">
         <f t="shared" ca="1" si="4"/>
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C215">
         <f t="shared" ca="1" si="4"/>
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="D215" t="s">
         <v>184</v>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="C216">
         <f t="shared" ca="1" si="4"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
@@ -13076,7 +13076,7 @@
       </c>
       <c r="C217">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D217" t="s">
         <v>184</v>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="C218">
         <f t="shared" ca="1" si="4"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="D218" t="s">
         <v>184</v>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C219">
         <f t="shared" ca="1" si="4"/>
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="D219" t="s">
         <v>184</v>
@@ -13225,11 +13225,11 @@
         <v>272</v>
       </c>
       <c r="B220" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C220">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D220" t="s">
         <v>184</v>
@@ -13280,7 +13280,7 @@
       </c>
       <c r="C221">
         <f t="shared" ca="1" si="4"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D221" t="s">
         <v>184</v>
@@ -13327,11 +13327,11 @@
         <v>274</v>
       </c>
       <c r="B222" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C222">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D222" t="s">
         <v>184</v>
@@ -13378,7 +13378,7 @@
         <v>275</v>
       </c>
       <c r="B223" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C223">
         <f t="shared" ca="1" si="4"/>
@@ -13429,11 +13429,11 @@
         <v>276</v>
       </c>
       <c r="B224" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C224">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D224" t="s">
         <v>184</v>
@@ -13480,7 +13480,7 @@
         <v>277</v>
       </c>
       <c r="B225" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C225">
         <f t="shared" ca="1" si="4"/>
@@ -13531,7 +13531,7 @@
         <v>278</v>
       </c>
       <c r="B226" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C226">
         <f t="shared" ca="1" si="4"/>
@@ -13582,11 +13582,11 @@
         <v>279</v>
       </c>
       <c r="B227" s="2">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="C227">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D227" t="s">
         <v>184</v>
@@ -13633,7 +13633,7 @@
         <v>280</v>
       </c>
       <c r="B228" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C228">
         <f t="shared" ca="1" si="4"/>
@@ -13684,11 +13684,11 @@
         <v>281</v>
       </c>
       <c r="B229" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C229">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D229" t="s">
         <v>184</v>
@@ -13735,11 +13735,11 @@
         <v>282</v>
       </c>
       <c r="B230" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C230">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D230" t="s">
         <v>184</v>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="C231">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D231" t="s">
         <v>184</v>
@@ -13841,7 +13841,7 @@
       </c>
       <c r="C232">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D232" t="s">
         <v>184</v>
@@ -13888,11 +13888,11 @@
         <v>285</v>
       </c>
       <c r="B233" s="2">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="C233">
         <f t="shared" ca="1" si="4"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D233" t="s">
         <v>184</v>
@@ -13943,7 +13943,7 @@
       </c>
       <c r="C234">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D234" t="s">
         <v>184</v>
@@ -13990,11 +13990,11 @@
         <v>287</v>
       </c>
       <c r="B235" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C235">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D235" t="s">
         <v>184</v>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="C236">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D236" t="s">
         <v>184</v>
@@ -14092,7 +14092,7 @@
         <v>289</v>
       </c>
       <c r="B237" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C237">
         <f t="shared" ca="1" si="4"/>
@@ -14147,7 +14147,7 @@
       </c>
       <c r="C238">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D238" t="s">
         <v>184</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C239">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D239" t="s">
         <v>184</v>
@@ -14245,7 +14245,7 @@
         <v>292</v>
       </c>
       <c r="B240" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C240">
         <f t="shared" ca="1" si="4"/>
@@ -14300,7 +14300,7 @@
       </c>
       <c r="C241">
         <f t="shared" ca="1" si="4"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D241" t="s">
         <v>184</v>
@@ -14347,7 +14347,7 @@
         <v>294</v>
       </c>
       <c r="B242" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C242">
         <f t="shared" ca="1" si="4"/>
@@ -14402,7 +14402,7 @@
       </c>
       <c r="C243">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D243" t="s">
         <v>184</v>
@@ -14449,7 +14449,7 @@
         <v>296</v>
       </c>
       <c r="B244" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C244">
         <f t="shared" ca="1" si="4"/>
@@ -14500,11 +14500,11 @@
         <v>297</v>
       </c>
       <c r="B245" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C245">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D245" t="s">
         <v>184</v>
@@ -14555,7 +14555,7 @@
       </c>
       <c r="C246">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D246" t="s">
         <v>184</v>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="C247">
         <f t="shared" ca="1" si="4"/>
-        <v>-39</v>
+        <v>-40</v>
       </c>
       <c r="D247" t="s">
         <v>184</v>
@@ -14653,7 +14653,7 @@
         <v>300</v>
       </c>
       <c r="B248" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C248">
         <f t="shared" ca="1" si="4"/>
@@ -14704,11 +14704,11 @@
         <v>301</v>
       </c>
       <c r="B249" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C249">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D249" t="s">
         <v>184</v>
@@ -14759,7 +14759,7 @@
       </c>
       <c r="C250">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D250" t="s">
         <v>184</v>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="C251">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D251" t="s">
         <v>184</v>
@@ -14861,7 +14861,7 @@
       </c>
       <c r="C252">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D252" t="s">
         <v>184</v>
@@ -14912,7 +14912,7 @@
       </c>
       <c r="C253">
         <f t="shared" ca="1" si="4"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D253" t="s">
         <v>184</v>
@@ -14963,7 +14963,7 @@
       </c>
       <c r="C254">
         <f t="shared" ca="1" si="4"/>
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="D254" t="s">
         <v>184</v>
@@ -15010,7 +15010,7 @@
         <v>307</v>
       </c>
       <c r="B255" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C255">
         <f t="shared" ca="1" si="4"/>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="C256">
         <f t="shared" ref="C256:C319" ca="1" si="5">B256-$R$1</f>
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="D256" t="s">
         <v>184</v>
@@ -15112,7 +15112,7 @@
         <v>309</v>
       </c>
       <c r="B257" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C257">
         <f t="shared" ca="1" si="5"/>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="C258">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D258" t="s">
         <v>184</v>
@@ -15214,7 +15214,7 @@
         <v>311</v>
       </c>
       <c r="B259" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C259">
         <f t="shared" ca="1" si="5"/>
@@ -15265,7 +15265,7 @@
         <v>312</v>
       </c>
       <c r="B260" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C260">
         <f t="shared" ca="1" si="5"/>
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C261">
         <f t="shared" ca="1" si="5"/>
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="D261" t="s">
         <v>184</v>
@@ -15367,11 +15367,11 @@
         <v>314</v>
       </c>
       <c r="B262" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C262">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D262" t="s">
         <v>184</v>
@@ -15418,7 +15418,7 @@
         <v>315</v>
       </c>
       <c r="B263" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C263">
         <f t="shared" ca="1" si="5"/>
@@ -15473,7 +15473,7 @@
       </c>
       <c r="C264">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D264" t="s">
         <v>184</v>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C265">
         <f t="shared" ca="1" si="5"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="D265" t="s">
         <v>184</v>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="C266">
         <f t="shared" ca="1" si="5"/>
-        <v>-144</v>
+        <v>-145</v>
       </c>
       <c r="D266" t="s">
         <v>184</v>
@@ -15622,11 +15622,11 @@
         <v>319</v>
       </c>
       <c r="B267" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C267">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D267" t="s">
         <v>184</v>
@@ -15677,7 +15677,7 @@
       </c>
       <c r="C268">
         <f t="shared" ca="1" si="5"/>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="D268" t="s">
         <v>184</v>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="C269">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D269" t="s">
         <v>184</v>
@@ -15775,11 +15775,11 @@
         <v>322</v>
       </c>
       <c r="B270" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C270">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D270" t="s">
         <v>184</v>
@@ -15826,7 +15826,7 @@
         <v>323</v>
       </c>
       <c r="B271" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C271">
         <f t="shared" ca="1" si="5"/>
@@ -15877,11 +15877,11 @@
         <v>324</v>
       </c>
       <c r="B272" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C272">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D272" t="s">
         <v>184</v>
@@ -15928,11 +15928,11 @@
         <v>325</v>
       </c>
       <c r="B273" s="2">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="C273">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D273" t="s">
         <v>184</v>
@@ -15979,11 +15979,11 @@
         <v>326</v>
       </c>
       <c r="B274" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C274">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D274" t="s">
         <v>184</v>
@@ -16030,11 +16030,11 @@
         <v>327</v>
       </c>
       <c r="B275" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C275">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D275" t="s">
         <v>184</v>
@@ -16081,11 +16081,11 @@
         <v>328</v>
       </c>
       <c r="B276" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C276">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D276" t="s">
         <v>184</v>
@@ -16132,7 +16132,7 @@
         <v>329</v>
       </c>
       <c r="B277" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C277">
         <f t="shared" ca="1" si="5"/>
@@ -16187,7 +16187,7 @@
       </c>
       <c r="C278">
         <f t="shared" ca="1" si="5"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D278" t="s">
         <v>184</v>
@@ -16234,11 +16234,11 @@
         <v>331</v>
       </c>
       <c r="B279" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C279">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D279" t="s">
         <v>184</v>
@@ -16285,11 +16285,11 @@
         <v>332</v>
       </c>
       <c r="B280" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C280">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D280" t="s">
         <v>184</v>
@@ -16340,7 +16340,7 @@
       </c>
       <c r="C281">
         <f t="shared" ca="1" si="5"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D281" t="s">
         <v>184</v>
@@ -16387,7 +16387,7 @@
         <v>334</v>
       </c>
       <c r="B282" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C282">
         <f t="shared" ca="1" si="5"/>
@@ -16438,11 +16438,11 @@
         <v>335</v>
       </c>
       <c r="B283" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C283">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D283" t="s">
         <v>184</v>
@@ -16489,11 +16489,11 @@
         <v>336</v>
       </c>
       <c r="B284" s="2">
-        <v>46313</v>
+        <v>46321</v>
       </c>
       <c r="C284">
         <f t="shared" ca="1" si="5"/>
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="D284" t="s">
         <v>184</v>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="C285">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D285" t="s">
         <v>184</v>
@@ -16591,7 +16591,7 @@
         <v>338</v>
       </c>
       <c r="B286" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C286">
         <f t="shared" ca="1" si="5"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="C287">
         <f t="shared" ca="1" si="5"/>
-        <v>-230</v>
+        <v>-231</v>
       </c>
       <c r="D287" t="s">
         <v>184</v>
@@ -16693,7 +16693,7 @@
         <v>340</v>
       </c>
       <c r="B288" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C288">
         <f t="shared" ca="1" si="5"/>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="C289">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D289" t="s">
         <v>184</v>
@@ -16795,11 +16795,11 @@
         <v>342</v>
       </c>
       <c r="B290" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C290">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D290" t="s">
         <v>184</v>
@@ -16846,7 +16846,7 @@
         <v>343</v>
       </c>
       <c r="B291" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C291">
         <f t="shared" ca="1" si="5"/>
@@ -16897,11 +16897,11 @@
         <v>344</v>
       </c>
       <c r="B292" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C292">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D292" t="s">
         <v>184</v>
@@ -16952,7 +16952,7 @@
       </c>
       <c r="C293">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D293" t="s">
         <v>184</v>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="C294">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D294" t="s">
         <v>184</v>
@@ -17050,11 +17050,11 @@
         <v>347</v>
       </c>
       <c r="B295" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C295">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D295" t="s">
         <v>184</v>
@@ -17105,7 +17105,7 @@
       </c>
       <c r="C296">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D296" t="s">
         <v>184</v>
@@ -17152,11 +17152,11 @@
         <v>349</v>
       </c>
       <c r="B297" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C297">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D297" t="s">
         <v>184</v>
@@ -17203,11 +17203,11 @@
         <v>350</v>
       </c>
       <c r="B298" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C298">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D298" t="s">
         <v>184</v>
@@ -17254,11 +17254,11 @@
         <v>351</v>
       </c>
       <c r="B299" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C299">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D299" t="s">
         <v>184</v>
@@ -17305,7 +17305,7 @@
         <v>352</v>
       </c>
       <c r="B300" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C300">
         <f t="shared" ca="1" si="5"/>
@@ -17356,7 +17356,7 @@
         <v>353</v>
       </c>
       <c r="B301" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C301">
         <f t="shared" ca="1" si="5"/>
@@ -17407,11 +17407,11 @@
         <v>354</v>
       </c>
       <c r="B302" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C302">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D302" t="s">
         <v>184</v>
@@ -17458,11 +17458,11 @@
         <v>355</v>
       </c>
       <c r="B303" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C303">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D303" t="s">
         <v>184</v>
@@ -17509,7 +17509,7 @@
         <v>356</v>
       </c>
       <c r="B304" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C304">
         <f t="shared" ca="1" si="5"/>
@@ -17560,7 +17560,7 @@
         <v>357</v>
       </c>
       <c r="B305" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C305">
         <f t="shared" ca="1" si="5"/>
@@ -17611,7 +17611,7 @@
         <v>358</v>
       </c>
       <c r="B306" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C306">
         <f t="shared" ca="1" si="5"/>
@@ -17662,11 +17662,11 @@
         <v>359</v>
       </c>
       <c r="B307" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C307">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D307" t="s">
         <v>184</v>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="C308">
         <f t="shared" ca="1" si="5"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="D308" t="s">
         <v>184</v>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="C309">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D309" t="s">
         <v>184</v>
@@ -17819,7 +17819,7 @@
       </c>
       <c r="C310">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D310" t="s">
         <v>184</v>
@@ -17866,11 +17866,11 @@
         <v>363</v>
       </c>
       <c r="B311" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C311">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D311" t="s">
         <v>184</v>
@@ -17917,11 +17917,11 @@
         <v>364</v>
       </c>
       <c r="B312" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C312">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D312" t="s">
         <v>184</v>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="C313">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D313" t="s">
         <v>184</v>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="C314">
         <f t="shared" ca="1" si="5"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D314" t="s">
         <v>184</v>
@@ -18074,7 +18074,7 @@
       </c>
       <c r="C315">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D315" t="s">
         <v>184</v>
@@ -18121,11 +18121,11 @@
         <v>368</v>
       </c>
       <c r="B316" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C316">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D316" t="s">
         <v>184</v>
@@ -18176,7 +18176,7 @@
       </c>
       <c r="C317">
         <f t="shared" ca="1" si="5"/>
-        <v>-77</v>
+        <v>-78</v>
       </c>
       <c r="D317" t="s">
         <v>184</v>
@@ -18223,11 +18223,11 @@
         <v>370</v>
       </c>
       <c r="B318" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C318">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D318" t="s">
         <v>184</v>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C319">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D319" t="s">
         <v>184</v>
@@ -18325,7 +18325,7 @@
         <v>372</v>
       </c>
       <c r="B320" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C320">
         <f t="shared" ref="C320:C383" ca="1" si="6">B320-$R$1</f>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="C321">
         <f t="shared" ca="1" si="6"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D321" t="s">
         <v>184</v>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="C322">
         <f t="shared" ca="1" si="6"/>
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="D322" t="s">
         <v>184</v>
@@ -18482,7 +18482,7 @@
       </c>
       <c r="C323">
         <f t="shared" ca="1" si="6"/>
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="D323" t="s">
         <v>184</v>
@@ -18529,7 +18529,7 @@
         <v>376</v>
       </c>
       <c r="B324" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C324">
         <f t="shared" ca="1" si="6"/>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="C325">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D325" t="s">
         <v>184</v>
@@ -18631,11 +18631,11 @@
         <v>378</v>
       </c>
       <c r="B326" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C326">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D326" t="s">
         <v>184</v>
@@ -18682,7 +18682,7 @@
         <v>379</v>
       </c>
       <c r="B327" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C327">
         <f t="shared" ca="1" si="6"/>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="C328">
         <f t="shared" ca="1" si="6"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D328" t="s">
         <v>184</v>
@@ -18788,7 +18788,7 @@
       </c>
       <c r="C329">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D329" t="s">
         <v>184</v>
@@ -18835,7 +18835,7 @@
         <v>382</v>
       </c>
       <c r="B330" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C330">
         <f t="shared" ca="1" si="6"/>
@@ -18890,7 +18890,7 @@
       </c>
       <c r="C331">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D331" t="s">
         <v>184</v>
@@ -18937,11 +18937,11 @@
         <v>384</v>
       </c>
       <c r="B332" s="2">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="C332">
         <f t="shared" ca="1" si="6"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D332" t="s">
         <v>184</v>
@@ -18988,11 +18988,11 @@
         <v>385</v>
       </c>
       <c r="B333" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C333">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D333" t="s">
         <v>184</v>
@@ -19043,7 +19043,7 @@
       </c>
       <c r="C334">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D334" t="s">
         <v>184</v>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="C335">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D335" t="s">
         <v>184</v>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C336">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D336" t="s">
         <v>184</v>
@@ -19192,11 +19192,11 @@
         <v>389</v>
       </c>
       <c r="B337" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C337">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D337" t="s">
         <v>184</v>
@@ -19247,7 +19247,7 @@
       </c>
       <c r="C338">
         <f t="shared" ca="1" si="6"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D338" t="s">
         <v>184</v>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="C339">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D339" t="s">
         <v>184</v>
@@ -19345,11 +19345,11 @@
         <v>392</v>
       </c>
       <c r="B340" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C340">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D340" t="s">
         <v>184</v>
@@ -19396,11 +19396,11 @@
         <v>393</v>
       </c>
       <c r="B341" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C341">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D341" t="s">
         <v>184</v>
@@ -19451,7 +19451,7 @@
       </c>
       <c r="C342">
         <f t="shared" ca="1" si="6"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D342" t="s">
         <v>184</v>
@@ -19498,11 +19498,11 @@
         <v>395</v>
       </c>
       <c r="B343" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C343">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D343" t="s">
         <v>184</v>
@@ -19549,11 +19549,11 @@
         <v>396</v>
       </c>
       <c r="B344" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C344">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D344" t="s">
         <v>184</v>
@@ -19600,11 +19600,11 @@
         <v>397</v>
       </c>
       <c r="B345" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C345">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D345" t="s">
         <v>184</v>
@@ -19651,7 +19651,7 @@
         <v>398</v>
       </c>
       <c r="B346" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C346">
         <f t="shared" ca="1" si="6"/>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C347">
         <f t="shared" ca="1" si="6"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D347" t="s">
         <v>184</v>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C348">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D348" t="s">
         <v>184</v>
@@ -19804,11 +19804,11 @@
         <v>401</v>
       </c>
       <c r="B349" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C349">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D349" t="s">
         <v>184</v>
@@ -19855,11 +19855,11 @@
         <v>402</v>
       </c>
       <c r="B350" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C350">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D350" t="s">
         <v>184</v>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C351">
         <f t="shared" ca="1" si="6"/>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="D351" t="s">
         <v>184</v>
@@ -19957,7 +19957,7 @@
         <v>404</v>
       </c>
       <c r="B352" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C352">
         <f t="shared" ca="1" si="6"/>
@@ -20008,7 +20008,7 @@
         <v>405</v>
       </c>
       <c r="B353" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C353">
         <f t="shared" ca="1" si="6"/>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="C354">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D354" t="s">
         <v>184</v>
@@ -20114,7 +20114,7 @@
       </c>
       <c r="C355">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D355" t="s">
         <v>184</v>
@@ -20161,11 +20161,11 @@
         <v>408</v>
       </c>
       <c r="B356" s="2">
-        <v>46298</v>
+        <v>46321</v>
       </c>
       <c r="C356">
         <f t="shared" ca="1" si="6"/>
-        <v>-23</v>
+        <v>-1</v>
       </c>
       <c r="D356" t="s">
         <v>184</v>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="C357">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D357" t="s">
         <v>184</v>
@@ -20267,7 +20267,7 @@
       </c>
       <c r="C358">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D358" t="s">
         <v>184</v>
@@ -20314,7 +20314,7 @@
         <v>411</v>
       </c>
       <c r="B359" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C359">
         <f t="shared" ca="1" si="6"/>
@@ -20369,7 +20369,7 @@
       </c>
       <c r="C360">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D360" t="s">
         <v>184</v>
@@ -20416,7 +20416,7 @@
         <v>413</v>
       </c>
       <c r="B361" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C361">
         <f t="shared" ca="1" si="6"/>
@@ -20471,7 +20471,7 @@
       </c>
       <c r="C362">
         <f t="shared" ca="1" si="6"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D362" t="s">
         <v>184</v>
@@ -20522,7 +20522,7 @@
       </c>
       <c r="C363">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D363" t="s">
         <v>184</v>
@@ -20569,11 +20569,11 @@
         <v>416</v>
       </c>
       <c r="B364" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C364">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D364" t="s">
         <v>184</v>
@@ -20620,11 +20620,11 @@
         <v>417</v>
       </c>
       <c r="B365" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C365">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D365" t="s">
         <v>184</v>
@@ -20671,11 +20671,11 @@
         <v>418</v>
       </c>
       <c r="B366" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C366">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D366" t="s">
         <v>184</v>
@@ -20722,11 +20722,11 @@
         <v>419</v>
       </c>
       <c r="B367" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C367">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D367" t="s">
         <v>184</v>
@@ -20773,11 +20773,11 @@
         <v>420</v>
       </c>
       <c r="B368" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C368">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D368" t="s">
         <v>184</v>
@@ -20824,11 +20824,11 @@
         <v>421</v>
       </c>
       <c r="B369" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C369">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D369" t="s">
         <v>184</v>
@@ -20875,7 +20875,7 @@
         <v>422</v>
       </c>
       <c r="B370" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C370">
         <f t="shared" ca="1" si="6"/>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="C371">
         <f t="shared" ca="1" si="6"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D371" t="s">
         <v>184</v>
@@ -20981,7 +20981,7 @@
       </c>
       <c r="C372">
         <f t="shared" ca="1" si="6"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D372" t="s">
         <v>184</v>
@@ -21032,7 +21032,7 @@
       </c>
       <c r="C373">
         <f t="shared" ca="1" si="6"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D373" t="s">
         <v>184</v>
@@ -21079,7 +21079,7 @@
         <v>426</v>
       </c>
       <c r="B374" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C374">
         <f t="shared" ca="1" si="6"/>
@@ -21130,7 +21130,7 @@
         <v>427</v>
       </c>
       <c r="B375" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C375">
         <f t="shared" ca="1" si="6"/>
@@ -21185,7 +21185,7 @@
       </c>
       <c r="C376">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D376" t="s">
         <v>184</v>
@@ -21232,11 +21232,11 @@
         <v>429</v>
       </c>
       <c r="B377" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C377">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D377" t="s">
         <v>184</v>
@@ -21283,7 +21283,7 @@
         <v>430</v>
       </c>
       <c r="B378" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C378">
         <f t="shared" ca="1" si="6"/>
@@ -21334,11 +21334,11 @@
         <v>431</v>
       </c>
       <c r="B379" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C379">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D379" t="s">
         <v>184</v>
@@ -21385,7 +21385,7 @@
         <v>432</v>
       </c>
       <c r="B380" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C380">
         <f t="shared" ca="1" si="6"/>
@@ -21436,11 +21436,11 @@
         <v>433</v>
       </c>
       <c r="B381" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C381">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D381" t="s">
         <v>184</v>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="C382">
         <f t="shared" ca="1" si="6"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D382" t="s">
         <v>184</v>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="C383">
         <f t="shared" ca="1" si="6"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D383" t="s">
         <v>184</v>
@@ -21593,7 +21593,7 @@
       </c>
       <c r="C384">
         <f t="shared" ref="C384:C391" ca="1" si="7">B384-$R$1</f>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D384" t="s">
         <v>184</v>
@@ -21640,11 +21640,11 @@
         <v>437</v>
       </c>
       <c r="B385" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C385">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D385" t="s">
         <v>184</v>
@@ -21695,7 +21695,7 @@
       </c>
       <c r="C386">
         <f t="shared" ca="1" si="7"/>
-        <v>-46321</v>
+        <v>-46322</v>
       </c>
       <c r="D386" t="s">
         <v>184</v>
@@ -21746,7 +21746,7 @@
       </c>
       <c r="C387">
         <f t="shared" ca="1" si="7"/>
-        <v>-46321</v>
+        <v>-46322</v>
       </c>
       <c r="D387" t="s">
         <v>184</v>
@@ -21797,7 +21797,7 @@
       </c>
       <c r="C388">
         <f t="shared" ca="1" si="7"/>
-        <v>-46321</v>
+        <v>-46322</v>
       </c>
       <c r="D388" t="s">
         <v>184</v>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="C389">
         <f t="shared" ca="1" si="7"/>
-        <v>-46321</v>
+        <v>-46322</v>
       </c>
       <c r="D389" t="s">
         <v>184</v>
@@ -21895,11 +21895,11 @@
         <v>442</v>
       </c>
       <c r="B390" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C390">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D390" t="s">
         <v>184</v>
@@ -21946,11 +21946,11 @@
         <v>443</v>
       </c>
       <c r="B391" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="C391">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D391" t="s">
         <v>184</v>
@@ -21998,12 +21998,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22268,21 +22271,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -22307,12 +22310,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="463" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23962C76-70C0-4B0E-8509-22F9265062AF}"/>
+  <xr:revisionPtr revIDLastSave="473" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF712D7B-1A5E-49BF-8D5A-59293203E764}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6016,12 +6016,12 @@
       <c r="A79" t="s">
         <v>107</v>
       </c>
-      <c r="B79" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C79" t="e">
+      <c r="B79" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C79">
         <f t="shared" ca="1" si="1"/>
-        <v>#N/A</v>
+        <v>-1</v>
       </c>
       <c r="D79" t="s">
         <v>184</v>
@@ -6124,12 +6124,12 @@
       <c r="A81" t="s">
         <v>109</v>
       </c>
-      <c r="B81" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C81" t="e">
+      <c r="B81" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C81">
         <f t="shared" ca="1" si="1"/>
-        <v>#N/A</v>
+        <v>-1</v>
       </c>
       <c r="D81" t="s">
         <v>184</v>
@@ -6178,12 +6178,12 @@
       <c r="A82" t="s">
         <v>110</v>
       </c>
-      <c r="B82" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C82" t="e">
+      <c r="B82" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C82">
         <f t="shared" ca="1" si="1"/>
-        <v>#N/A</v>
+        <v>-1</v>
       </c>
       <c r="D82" t="s">
         <v>184</v>
@@ -6448,12 +6448,12 @@
       <c r="A87" t="s">
         <v>115</v>
       </c>
-      <c r="B87" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C87" t="e">
+      <c r="B87" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C87">
         <f t="shared" ca="1" si="1"/>
-        <v>#N/A</v>
+        <v>-1</v>
       </c>
       <c r="D87" t="s">
         <v>184</v>
@@ -7798,12 +7798,12 @@
       <c r="A112" t="s">
         <v>185</v>
       </c>
-      <c r="B112" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C112" t="e">
+      <c r="B112" s="2">
+        <v>0</v>
+      </c>
+      <c r="C112">
         <f t="shared" ca="1" si="1"/>
-        <v>#N/A</v>
+        <v>-46322</v>
       </c>
       <c r="D112" t="s">
         <v>184</v>
@@ -8864,11 +8864,11 @@
         <v>187</v>
       </c>
       <c r="B132" s="2">
-        <v>46300</v>
+        <v>46321</v>
       </c>
       <c r="C132">
         <f t="shared" ca="1" si="2"/>
-        <v>-22</v>
+        <v>-1</v>
       </c>
       <c r="D132" t="s">
         <v>184</v>
@@ -8917,12 +8917,12 @@
       <c r="A133" t="s">
         <v>466</v>
       </c>
-      <c r="B133" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C133" t="e">
+      <c r="B133" s="2">
+        <v>0</v>
+      </c>
+      <c r="C133">
         <f t="shared" ref="C133" ca="1" si="3">B133-$R$1</f>
-        <v>#N/A</v>
+        <v>-46322</v>
       </c>
       <c r="D133" t="s">
         <v>184</v>
@@ -9229,12 +9229,12 @@
       <c r="A139" t="s">
         <v>193</v>
       </c>
-      <c r="B139" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C139" t="e">
+      <c r="B139" s="2">
+        <v>0</v>
+      </c>
+      <c r="C139">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46322</v>
       </c>
       <c r="D139" t="s">
         <v>184</v>
@@ -9272,11 +9272,11 @@
         <v>194</v>
       </c>
       <c r="B140" s="2">
-        <v>46314</v>
+        <v>0</v>
       </c>
       <c r="C140">
         <f t="shared" ca="1" si="2"/>
-        <v>-8</v>
+        <v>-46322</v>
       </c>
       <c r="D140" t="s">
         <v>184</v>
@@ -9325,12 +9325,12 @@
       <c r="A141" t="s">
         <v>195</v>
       </c>
-      <c r="B141" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C141" t="e">
+      <c r="B141" s="2">
+        <v>0</v>
+      </c>
+      <c r="C141">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46322</v>
       </c>
       <c r="D141" t="s">
         <v>184</v>
@@ -9367,12 +9367,12 @@
       <c r="A142" t="s">
         <v>196</v>
       </c>
-      <c r="B142" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C142" t="e">
+      <c r="B142" s="2">
+        <v>0</v>
+      </c>
+      <c r="C142">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46322</v>
       </c>
       <c r="D142" t="s">
         <v>184</v>
@@ -9409,12 +9409,12 @@
       <c r="A143" t="s">
         <v>197</v>
       </c>
-      <c r="B143" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C143" t="e">
+      <c r="B143" s="2">
+        <v>0</v>
+      </c>
+      <c r="C143">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46322</v>
       </c>
       <c r="J143" t="s">
         <v>28</v>
@@ -9438,12 +9438,12 @@
       <c r="A144" t="s">
         <v>198</v>
       </c>
-      <c r="B144" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C144" t="e">
+      <c r="B144" s="2">
+        <v>0</v>
+      </c>
+      <c r="C144">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46322</v>
       </c>
       <c r="J144" t="s">
         <v>28</v>
@@ -9471,11 +9471,11 @@
         <v>199</v>
       </c>
       <c r="B145" s="2">
-        <v>46314</v>
+        <v>0</v>
       </c>
       <c r="C145">
         <f t="shared" ca="1" si="2"/>
-        <v>-8</v>
+        <v>-46322</v>
       </c>
       <c r="D145" t="s">
         <v>184</v>
@@ -9520,12 +9520,12 @@
       <c r="A146" t="s">
         <v>200</v>
       </c>
-      <c r="B146" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C146" t="e">
+      <c r="B146" s="2">
+        <v>0</v>
+      </c>
+      <c r="C146">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46322</v>
       </c>
       <c r="J146" t="s">
         <v>28</v>
@@ -9552,12 +9552,12 @@
       <c r="A147" t="s">
         <v>201</v>
       </c>
-      <c r="B147" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C147" t="e">
+      <c r="B147" s="2">
+        <v>0</v>
+      </c>
+      <c r="C147">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46322</v>
       </c>
       <c r="D147" t="s">
         <v>184</v>
@@ -9594,12 +9594,12 @@
       <c r="A148" t="s">
         <v>202</v>
       </c>
-      <c r="B148" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C148" t="e">
+      <c r="B148" s="2">
+        <v>0</v>
+      </c>
+      <c r="C148">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46322</v>
       </c>
       <c r="D148" t="s">
         <v>184</v>
@@ -9636,12 +9636,12 @@
       <c r="A149" t="s">
         <v>203</v>
       </c>
-      <c r="B149" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C149" t="e">
+      <c r="B149" s="2">
+        <v>0</v>
+      </c>
+      <c r="C149">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46322</v>
       </c>
       <c r="D149" t="s">
         <v>184</v>
@@ -9678,12 +9678,12 @@
       <c r="A150" t="s">
         <v>204</v>
       </c>
-      <c r="B150" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C150" t="e">
+      <c r="B150" s="2">
+        <v>0</v>
+      </c>
+      <c r="C150">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46322</v>
       </c>
       <c r="J150" t="s">
         <v>22</v>
@@ -9755,8 +9755,12 @@
       <c r="O151" t="s">
         <v>217</v>
       </c>
-      <c r="P151" s="2"/>
-      <c r="Q151" s="2"/>
+      <c r="P151" s="2">
+        <v>46315</v>
+      </c>
+      <c r="Q151" s="2">
+        <v>46315</v>
+      </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
@@ -10836,12 +10840,12 @@
       <c r="A173" t="s">
         <v>215</v>
       </c>
-      <c r="B173" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C173" t="e">
+      <c r="B173" s="2">
+        <v>0</v>
+      </c>
+      <c r="C173">
         <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
+        <v>-46322</v>
       </c>
       <c r="D173" t="s">
         <v>184</v>
@@ -22010,6 +22014,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -22270,15 +22283,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
@@ -22291,6 +22295,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22307,12 +22319,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="473" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF712D7B-1A5E-49BF-8D5A-59293203E764}"/>
+  <xr:revisionPtr revIDLastSave="476" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FAA0D96-C461-427C-8AE0-57AD3017481D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="R1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C2">
         <f ca="1">B2-$R$1</f>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D2" t="s">
         <v>184</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C66" ca="1" si="0">B3-$R$1</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D3" t="s">
         <v>184</v>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D4" t="s">
         <v>184</v>
@@ -2031,11 +2031,11 @@
         <v>16</v>
       </c>
       <c r="B5" s="2">
-        <v>46319</v>
+        <v>46322</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D5" t="s">
         <v>184</v>
@@ -2083,7 +2083,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D7" t="s">
         <v>184</v>
@@ -2187,7 +2187,7 @@
         <v>19</v>
       </c>
       <c r="B8" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
@@ -2239,7 +2239,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
@@ -2291,7 +2291,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
@@ -2345,7 +2345,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D12" t="s">
         <v>184</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D13" t="s">
         <v>184</v>
@@ -2507,7 +2507,7 @@
         <v>36</v>
       </c>
       <c r="B14" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D15" t="s">
         <v>184</v>
@@ -2615,7 +2615,7 @@
         <v>38</v>
       </c>
       <c r="B16" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D17" t="s">
         <v>184</v>
@@ -2723,11 +2723,11 @@
         <v>40</v>
       </c>
       <c r="B18" s="2">
-        <v>46319</v>
+        <v>46322</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D18" t="s">
         <v>184</v>
@@ -2777,11 +2777,11 @@
         <v>41</v>
       </c>
       <c r="B19" s="2">
-        <v>46319</v>
+        <v>46322</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D19" t="s">
         <v>184</v>
@@ -2831,7 +2831,7 @@
         <v>42</v>
       </c>
       <c r="B20" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
@@ -2885,7 +2885,7 @@
         <v>43</v>
       </c>
       <c r="B21" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="0"/>
@@ -2939,11 +2939,11 @@
         <v>44</v>
       </c>
       <c r="B22" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D22" t="s">
         <v>184</v>
@@ -2993,7 +2993,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="0"/>
@@ -3047,11 +3047,11 @@
         <v>47</v>
       </c>
       <c r="B24" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="s">
         <v>184</v>
@@ -3101,7 +3101,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="0"/>
@@ -3155,7 +3155,7 @@
         <v>49</v>
       </c>
       <c r="B26" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="0"/>
@@ -3209,11 +3209,11 @@
         <v>50</v>
       </c>
       <c r="B27" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D27" t="s">
         <v>184</v>
@@ -3263,7 +3263,7 @@
         <v>51</v>
       </c>
       <c r="B28" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="0"/>
@@ -3317,7 +3317,7 @@
         <v>52</v>
       </c>
       <c r="B29" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="0"/>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="0"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D30" t="s">
         <v>184</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D31" t="s">
         <v>184</v>
@@ -3479,7 +3479,7 @@
         <v>55</v>
       </c>
       <c r="B32" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="0"/>
@@ -3533,7 +3533,7 @@
         <v>56</v>
       </c>
       <c r="B33" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="0"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D34" t="s">
         <v>184</v>
@@ -3641,11 +3641,11 @@
         <v>58</v>
       </c>
       <c r="B35" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D35" t="s">
         <v>184</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D36" t="s">
         <v>184</v>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="0"/>
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="D37" t="s">
         <v>184</v>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D38" t="s">
         <v>184</v>
@@ -3857,7 +3857,7 @@
         <v>63</v>
       </c>
       <c r="B39" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="0"/>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="0"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="D40" t="s">
         <v>184</v>
@@ -3965,7 +3965,7 @@
         <v>65</v>
       </c>
       <c r="B41" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="0"/>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D42" t="s">
         <v>184</v>
@@ -4073,7 +4073,7 @@
         <v>67</v>
       </c>
       <c r="B43" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="0"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="0"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D44" t="s">
         <v>184</v>
@@ -4181,7 +4181,7 @@
         <v>69</v>
       </c>
       <c r="B45" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="0"/>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D46" t="s">
         <v>184</v>
@@ -4289,7 +4289,7 @@
         <v>71</v>
       </c>
       <c r="B47" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="0"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="0"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D48" t="s">
         <v>184</v>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D49" t="s">
         <v>184</v>
@@ -4451,7 +4451,7 @@
         <v>74</v>
       </c>
       <c r="B50" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="0"/>
@@ -4505,11 +4505,11 @@
         <v>75</v>
       </c>
       <c r="B51" s="2">
-        <v>46319</v>
+        <v>46322</v>
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D51" t="s">
         <v>184</v>
@@ -4559,7 +4559,7 @@
         <v>76</v>
       </c>
       <c r="B52" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="0"/>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D53" t="s">
         <v>184</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="0"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D54" t="s">
         <v>184</v>
@@ -4721,11 +4721,11 @@
         <v>79</v>
       </c>
       <c r="B55" s="2">
-        <v>46319</v>
+        <v>46322</v>
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D55" t="s">
         <v>184</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="0"/>
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="D56" t="s">
         <v>184</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="0"/>
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="D57" t="s">
         <v>184</v>
@@ -4883,7 +4883,7 @@
         <v>82</v>
       </c>
       <c r="B58" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="0"/>
@@ -4937,11 +4937,11 @@
         <v>83</v>
       </c>
       <c r="B59" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D59" t="s">
         <v>184</v>
@@ -4991,7 +4991,7 @@
         <v>84</v>
       </c>
       <c r="B60" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="0"/>
@@ -5045,7 +5045,7 @@
         <v>85</v>
       </c>
       <c r="B61" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="0"/>
@@ -5099,11 +5099,11 @@
         <v>86</v>
       </c>
       <c r="B62" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D62" t="s">
         <v>184</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D63" t="s">
         <v>184</v>
@@ -5207,11 +5207,11 @@
         <v>90</v>
       </c>
       <c r="B64" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D64" t="s">
         <v>184</v>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D65" t="s">
         <v>184</v>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="0"/>
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="D66" t="s">
         <v>184</v>
@@ -5369,7 +5369,7 @@
         <v>94</v>
       </c>
       <c r="B67" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C67">
         <f t="shared" ref="C67:C130" ca="1" si="1">B67-$R$1</f>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="1"/>
-        <v>-67</v>
+        <v>-68</v>
       </c>
       <c r="D68" t="s">
         <v>184</v>
@@ -5477,7 +5477,7 @@
         <v>96</v>
       </c>
       <c r="B69" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="1"/>
@@ -5531,11 +5531,11 @@
         <v>97</v>
       </c>
       <c r="B70" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D70" t="s">
         <v>184</v>
@@ -5585,7 +5585,7 @@
         <v>98</v>
       </c>
       <c r="B71" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="1"/>
@@ -5639,7 +5639,7 @@
         <v>99</v>
       </c>
       <c r="B72" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="1"/>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D73" t="s">
         <v>184</v>
@@ -5747,11 +5747,11 @@
         <v>102</v>
       </c>
       <c r="B74" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D74" t="s">
         <v>184</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D75" t="s">
         <v>184</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D76" t="s">
         <v>184</v>
@@ -5909,11 +5909,11 @@
         <v>105</v>
       </c>
       <c r="B77" s="2">
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D77" t="s">
         <v>184</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="1"/>
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="D78" t="s">
         <v>184</v>
@@ -6017,7 +6017,7 @@
         <v>107</v>
       </c>
       <c r="B79" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C79">
         <f t="shared" ca="1" si="1"/>
@@ -6071,7 +6071,7 @@
         <v>108</v>
       </c>
       <c r="B80" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="1"/>
@@ -6125,7 +6125,7 @@
         <v>109</v>
       </c>
       <c r="B81" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C81">
         <f t="shared" ca="1" si="1"/>
@@ -6179,7 +6179,7 @@
         <v>110</v>
       </c>
       <c r="B82" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C82">
         <f t="shared" ca="1" si="1"/>
@@ -6233,7 +6233,7 @@
         <v>111</v>
       </c>
       <c r="B83" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="1"/>
@@ -6287,11 +6287,11 @@
         <v>112</v>
       </c>
       <c r="B84" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D84" t="s">
         <v>184</v>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D85" t="s">
         <v>184</v>
@@ -6395,7 +6395,7 @@
         <v>114</v>
       </c>
       <c r="B86" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="1"/>
@@ -6449,7 +6449,7 @@
         <v>115</v>
       </c>
       <c r="B87" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C87">
         <f t="shared" ca="1" si="1"/>
@@ -6503,7 +6503,7 @@
         <v>116</v>
       </c>
       <c r="B88" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="1"/>
@@ -6557,7 +6557,7 @@
         <v>117</v>
       </c>
       <c r="B89" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="1"/>
@@ -6611,7 +6611,7 @@
         <v>121</v>
       </c>
       <c r="B90" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="1"/>
@@ -6665,7 +6665,7 @@
         <v>122</v>
       </c>
       <c r="B91" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="1"/>
@@ -6719,7 +6719,7 @@
         <v>123</v>
       </c>
       <c r="B92" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="1"/>
@@ -6773,7 +6773,7 @@
         <v>124</v>
       </c>
       <c r="B93" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="1"/>
@@ -6827,7 +6827,7 @@
         <v>125</v>
       </c>
       <c r="B94" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="1"/>
@@ -6881,11 +6881,11 @@
         <v>126</v>
       </c>
       <c r="B95" s="2">
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D95" t="s">
         <v>184</v>
@@ -6935,7 +6935,7 @@
         <v>127</v>
       </c>
       <c r="B96" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="1"/>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D97" t="s">
         <v>184</v>
@@ -7043,11 +7043,11 @@
         <v>129</v>
       </c>
       <c r="B98" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="s">
         <v>184</v>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D99" t="s">
         <v>184</v>
@@ -7151,7 +7151,7 @@
         <v>131</v>
       </c>
       <c r="B100" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="1"/>
@@ -7205,7 +7205,7 @@
         <v>132</v>
       </c>
       <c r="B101" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="1"/>
@@ -7263,7 +7263,7 @@
       </c>
       <c r="C102">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D102" t="s">
         <v>184</v>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="C103">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D103" t="s">
         <v>184</v>
@@ -7367,7 +7367,7 @@
         <v>135</v>
       </c>
       <c r="B104" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C104">
         <f t="shared" ca="1" si="1"/>
@@ -7421,7 +7421,7 @@
         <v>136</v>
       </c>
       <c r="B105" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C105">
         <f t="shared" ca="1" si="1"/>
@@ -7475,7 +7475,7 @@
         <v>137</v>
       </c>
       <c r="B106" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C106">
         <f t="shared" ca="1" si="1"/>
@@ -7529,7 +7529,7 @@
         <v>138</v>
       </c>
       <c r="B107" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C107">
         <f t="shared" ca="1" si="1"/>
@@ -7583,7 +7583,7 @@
         <v>139</v>
       </c>
       <c r="B108" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C108">
         <f t="shared" ca="1" si="1"/>
@@ -7637,11 +7637,11 @@
         <v>140</v>
       </c>
       <c r="B109" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C109">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D109" t="s">
         <v>184</v>
@@ -7691,11 +7691,11 @@
         <v>141</v>
       </c>
       <c r="B110" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C110">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D110" t="s">
         <v>184</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="C111">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D111" t="s">
         <v>184</v>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="C112">
         <f t="shared" ca="1" si="1"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D112" t="s">
         <v>184</v>
@@ -7838,11 +7838,11 @@
         <v>143</v>
       </c>
       <c r="B113" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C113">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D113" t="s">
         <v>184</v>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="C114">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D114" t="s">
         <v>184</v>
@@ -7946,7 +7946,7 @@
         <v>145</v>
       </c>
       <c r="B115" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C115">
         <f t="shared" ca="1" si="1"/>
@@ -8000,7 +8000,7 @@
         <v>147</v>
       </c>
       <c r="B116" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C116">
         <f t="shared" ca="1" si="1"/>
@@ -8054,7 +8054,7 @@
         <v>148</v>
       </c>
       <c r="B117" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C117">
         <f t="shared" ca="1" si="1"/>
@@ -8108,7 +8108,7 @@
         <v>149</v>
       </c>
       <c r="B118" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C118">
         <f t="shared" ca="1" si="1"/>
@@ -8162,7 +8162,7 @@
         <v>150</v>
       </c>
       <c r="B119" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C119">
         <f t="shared" ca="1" si="1"/>
@@ -8216,7 +8216,7 @@
         <v>151</v>
       </c>
       <c r="B120" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C120">
         <f t="shared" ca="1" si="1"/>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="C121">
         <f t="shared" ca="1" si="1"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D121" t="s">
         <v>465</v>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="C122">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D122" t="s">
         <v>184</v>
@@ -8378,11 +8378,11 @@
         <v>155</v>
       </c>
       <c r="B123" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C123">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D123" t="s">
         <v>184</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C124">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D124" t="s">
         <v>184</v>
@@ -8486,11 +8486,11 @@
         <v>157</v>
       </c>
       <c r="B125" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C125">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D125" t="s">
         <v>184</v>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="C126">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D126" t="s">
         <v>184</v>
@@ -8594,11 +8594,11 @@
         <v>159</v>
       </c>
       <c r="B127" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C127">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D127" t="s">
         <v>184</v>
@@ -8648,7 +8648,7 @@
         <v>160</v>
       </c>
       <c r="B128" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C128">
         <f t="shared" ca="1" si="1"/>
@@ -8702,11 +8702,11 @@
         <v>161</v>
       </c>
       <c r="B129" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C129">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D129" t="s">
         <v>184</v>
@@ -8756,7 +8756,7 @@
         <v>162</v>
       </c>
       <c r="B130" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C130">
         <f t="shared" ca="1" si="1"/>
@@ -8810,7 +8810,7 @@
         <v>186</v>
       </c>
       <c r="B131" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C131">
         <f t="shared" ref="C131:C193" ca="1" si="2">B131-$R$1</f>
@@ -8864,7 +8864,7 @@
         <v>187</v>
       </c>
       <c r="B132" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C132">
         <f t="shared" ca="1" si="2"/>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="C133">
         <f t="shared" ref="C133" ca="1" si="3">B133-$R$1</f>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D133" t="s">
         <v>184</v>
@@ -8960,11 +8960,11 @@
         <v>188</v>
       </c>
       <c r="B134" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C134">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D134" t="s">
         <v>184</v>
@@ -9014,7 +9014,7 @@
         <v>189</v>
       </c>
       <c r="B135" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C135">
         <f t="shared" ca="1" si="2"/>
@@ -9068,7 +9068,7 @@
         <v>190</v>
       </c>
       <c r="B136" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C136">
         <f t="shared" ca="1" si="2"/>
@@ -9122,7 +9122,7 @@
         <v>191</v>
       </c>
       <c r="B137" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C137">
         <f t="shared" ca="1" si="2"/>
@@ -9176,7 +9176,7 @@
         <v>192</v>
       </c>
       <c r="B138" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C138">
         <f t="shared" ca="1" si="2"/>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="C139">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D139" t="s">
         <v>184</v>
@@ -9272,11 +9272,11 @@
         <v>194</v>
       </c>
       <c r="B140" s="2">
-        <v>0</v>
+        <v>46322</v>
       </c>
       <c r="C140">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-1</v>
       </c>
       <c r="D140" t="s">
         <v>184</v>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="C141">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D141" t="s">
         <v>184</v>
@@ -9368,11 +9368,11 @@
         <v>196</v>
       </c>
       <c r="B142" s="2">
-        <v>0</v>
+        <v>46322</v>
       </c>
       <c r="C142">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-1</v>
       </c>
       <c r="D142" t="s">
         <v>184</v>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="C143">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="J143" t="s">
         <v>28</v>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="C144">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="J144" t="s">
         <v>28</v>
@@ -9471,11 +9471,11 @@
         <v>199</v>
       </c>
       <c r="B145" s="2">
-        <v>0</v>
+        <v>46322</v>
       </c>
       <c r="C145">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-1</v>
       </c>
       <c r="D145" t="s">
         <v>184</v>
@@ -9525,7 +9525,7 @@
       </c>
       <c r="C146">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="J146" t="s">
         <v>28</v>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="C147">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D147" t="s">
         <v>184</v>
@@ -9595,11 +9595,11 @@
         <v>202</v>
       </c>
       <c r="B148" s="2">
-        <v>0</v>
+        <v>46322</v>
       </c>
       <c r="C148">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-1</v>
       </c>
       <c r="D148" t="s">
         <v>184</v>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="C149">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D149" t="s">
         <v>184</v>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="C150">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="J150" t="s">
         <v>22</v>
@@ -9713,7 +9713,7 @@
         <v>205</v>
       </c>
       <c r="B151" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C151">
         <f t="shared" ca="1" si="2"/>
@@ -9767,7 +9767,7 @@
         <v>164</v>
       </c>
       <c r="B152" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C152">
         <f t="shared" ca="1" si="2"/>
@@ -9821,7 +9821,7 @@
         <v>165</v>
       </c>
       <c r="B153" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C153">
         <f t="shared" ca="1" si="2"/>
@@ -9875,11 +9875,11 @@
         <v>166</v>
       </c>
       <c r="B154" s="2">
-        <v>46316</v>
+        <v>46322</v>
       </c>
       <c r="C154">
         <f t="shared" ca="1" si="2"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="D154" t="s">
         <v>184</v>
@@ -9929,7 +9929,7 @@
         <v>167</v>
       </c>
       <c r="B155" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
@@ -9983,11 +9983,11 @@
         <v>168</v>
       </c>
       <c r="B156" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D156" t="s">
         <v>184</v>
@@ -10041,7 +10041,7 @@
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="D157" t="s">
         <v>184</v>
@@ -10091,7 +10091,7 @@
         <v>170</v>
       </c>
       <c r="B158" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C158">
         <f t="shared" ca="1" si="2"/>
@@ -10145,7 +10145,7 @@
         <v>171</v>
       </c>
       <c r="B159" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C159">
         <f t="shared" ca="1" si="2"/>
@@ -10199,7 +10199,7 @@
         <v>172</v>
       </c>
       <c r="B160" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
@@ -10257,7 +10257,7 @@
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D161" t="s">
         <v>184</v>
@@ -10307,7 +10307,7 @@
         <v>175</v>
       </c>
       <c r="B162" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
@@ -10361,7 +10361,7 @@
         <v>176</v>
       </c>
       <c r="B163" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C163">
         <f t="shared" ca="1" si="2"/>
@@ -10415,7 +10415,7 @@
         <v>206</v>
       </c>
       <c r="B164" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C164">
         <f t="shared" ca="1" si="2"/>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D165" t="s">
         <v>184</v>
@@ -10511,7 +10511,7 @@
         <v>208</v>
       </c>
       <c r="B166" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C166">
         <f t="shared" ca="1" si="2"/>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="C167">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D167" t="s">
         <v>465</v>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="C168">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D168" t="s">
         <v>465</v>
@@ -10649,7 +10649,7 @@
         <v>211</v>
       </c>
       <c r="B169" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C169">
         <f t="shared" ca="1" si="2"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="C170">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D170" t="s">
         <v>184</v>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="C171">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D171" t="s">
         <v>465</v>
@@ -10803,7 +10803,7 @@
       </c>
       <c r="C172">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D172" t="s">
         <v>465</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="C173">
         <f t="shared" ca="1" si="2"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D173" t="s">
         <v>184</v>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="C174">
         <f t="shared" ca="1" si="2"/>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="D174" t="s">
         <v>184</v>
@@ -10938,7 +10938,7 @@
       </c>
       <c r="C175">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D175" t="s">
         <v>184</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="C176">
         <f t="shared" ca="1" si="2"/>
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="D176" t="s">
         <v>184</v>
@@ -11040,7 +11040,7 @@
       </c>
       <c r="C177">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D177" t="s">
         <v>184</v>
@@ -11087,7 +11087,7 @@
         <v>230</v>
       </c>
       <c r="B178" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C178">
         <f t="shared" ca="1" si="2"/>
@@ -11138,7 +11138,7 @@
         <v>231</v>
       </c>
       <c r="B179" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C179">
         <f t="shared" ca="1" si="2"/>
@@ -11189,7 +11189,7 @@
         <v>232</v>
       </c>
       <c r="B180" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C180">
         <f t="shared" ca="1" si="2"/>
@@ -11240,7 +11240,7 @@
         <v>233</v>
       </c>
       <c r="B181" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C181">
         <f t="shared" ca="1" si="2"/>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="C182">
         <f t="shared" ca="1" si="2"/>
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="D182" t="s">
         <v>184</v>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="C183">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D183" t="s">
         <v>184</v>
@@ -11393,7 +11393,7 @@
         <v>236</v>
       </c>
       <c r="B184" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C184">
         <f t="shared" ca="1" si="2"/>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="C185">
         <f t="shared" ca="1" si="2"/>
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="D185" t="s">
         <v>184</v>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="C186">
         <f t="shared" ca="1" si="2"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D186" t="s">
         <v>184</v>
@@ -11546,7 +11546,7 @@
         <v>239</v>
       </c>
       <c r="B187" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C187">
         <f t="shared" ca="1" si="2"/>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="C188">
         <f t="shared" ca="1" si="2"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="D188" t="s">
         <v>184</v>
@@ -11648,11 +11648,11 @@
         <v>241</v>
       </c>
       <c r="B189" s="2">
-        <v>46319</v>
+        <v>46322</v>
       </c>
       <c r="C189">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D189" t="s">
         <v>184</v>
@@ -11699,7 +11699,7 @@
         <v>242</v>
       </c>
       <c r="B190" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C190">
         <f t="shared" ca="1" si="2"/>
@@ -11750,7 +11750,7 @@
         <v>243</v>
       </c>
       <c r="B191" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C191">
         <f t="shared" ca="1" si="2"/>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="C192">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D192" t="s">
         <v>184</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C193">
         <f t="shared" ca="1" si="2"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D193" t="s">
         <v>184</v>
@@ -11907,7 +11907,7 @@
       </c>
       <c r="C194">
         <f t="shared" ref="C194:C255" ca="1" si="4">B194-$R$1</f>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D194" t="s">
         <v>184</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="C195">
         <f t="shared" ca="1" si="4"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="D195" t="s">
         <v>184</v>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="C196">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D196" t="s">
         <v>184</v>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="C197">
         <f t="shared" ca="1" si="4"/>
-        <v>-155</v>
+        <v>-156</v>
       </c>
       <c r="D197" t="s">
         <v>184</v>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="C198">
         <f t="shared" ca="1" si="4"/>
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="D198" t="s">
         <v>184</v>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="C199">
         <f t="shared" ca="1" si="4"/>
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="D199" t="s">
         <v>184</v>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="C200">
         <f t="shared" ca="1" si="4"/>
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="D200" t="s">
         <v>184</v>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="C201">
         <f t="shared" ca="1" si="4"/>
-        <v>-285</v>
+        <v>-286</v>
       </c>
       <c r="D201" t="s">
         <v>184</v>
@@ -12311,7 +12311,7 @@
         <v>254</v>
       </c>
       <c r="B202" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C202">
         <f t="shared" ca="1" si="4"/>
@@ -12362,7 +12362,7 @@
         <v>255</v>
       </c>
       <c r="B203" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C203">
         <f t="shared" ca="1" si="4"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="C204">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D204" t="s">
         <v>184</v>
@@ -12464,7 +12464,7 @@
         <v>257</v>
       </c>
       <c r="B205" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C205">
         <f t="shared" ca="1" si="4"/>
@@ -12515,7 +12515,7 @@
         <v>258</v>
       </c>
       <c r="B206" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C206">
         <f t="shared" ca="1" si="4"/>
@@ -12566,7 +12566,7 @@
         <v>259</v>
       </c>
       <c r="B207" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C207">
         <f t="shared" ca="1" si="4"/>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="C208">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D208" t="s">
         <v>184</v>
@@ -12668,7 +12668,7 @@
         <v>261</v>
       </c>
       <c r="B209" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C209">
         <f t="shared" ca="1" si="4"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="C210">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D210" t="s">
         <v>184</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="C211">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D211" t="s">
         <v>184</v>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="C212">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D212" t="s">
         <v>184</v>
@@ -12872,7 +12872,7 @@
         <v>265</v>
       </c>
       <c r="B213" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C213">
         <f t="shared" ca="1" si="4"/>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="C214">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D214" t="s">
         <v>184</v>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="C215">
         <f t="shared" ca="1" si="4"/>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="D215" t="s">
         <v>184</v>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="C216">
         <f t="shared" ca="1" si="4"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="C217">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D217" t="s">
         <v>184</v>
@@ -13131,7 +13131,7 @@
       </c>
       <c r="C218">
         <f t="shared" ca="1" si="4"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="D218" t="s">
         <v>184</v>
@@ -13178,11 +13178,11 @@
         <v>271</v>
       </c>
       <c r="B219" s="2">
-        <v>46285</v>
+        <v>46322</v>
       </c>
       <c r="C219">
         <f t="shared" ca="1" si="4"/>
-        <v>-37</v>
+        <v>-1</v>
       </c>
       <c r="D219" t="s">
         <v>184</v>
@@ -13233,7 +13233,7 @@
       </c>
       <c r="C220">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D220" t="s">
         <v>184</v>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="C221">
         <f t="shared" ca="1" si="4"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D221" t="s">
         <v>184</v>
@@ -13331,7 +13331,7 @@
         <v>274</v>
       </c>
       <c r="B222" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C222">
         <f t="shared" ca="1" si="4"/>
@@ -13382,7 +13382,7 @@
         <v>275</v>
       </c>
       <c r="B223" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C223">
         <f t="shared" ca="1" si="4"/>
@@ -13437,7 +13437,7 @@
       </c>
       <c r="C224">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D224" t="s">
         <v>184</v>
@@ -13488,7 +13488,7 @@
       </c>
       <c r="C225">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D225" t="s">
         <v>184</v>
@@ -13539,7 +13539,7 @@
       </c>
       <c r="C226">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D226" t="s">
         <v>184</v>
@@ -13586,7 +13586,7 @@
         <v>279</v>
       </c>
       <c r="B227" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C227">
         <f t="shared" ca="1" si="4"/>
@@ -13637,7 +13637,7 @@
         <v>280</v>
       </c>
       <c r="B228" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C228">
         <f t="shared" ca="1" si="4"/>
@@ -13688,7 +13688,7 @@
         <v>281</v>
       </c>
       <c r="B229" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C229">
         <f t="shared" ca="1" si="4"/>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="C230">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D230" t="s">
         <v>184</v>
@@ -13790,11 +13790,11 @@
         <v>283</v>
       </c>
       <c r="B231" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C231">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D231" t="s">
         <v>184</v>
@@ -13841,11 +13841,11 @@
         <v>284</v>
       </c>
       <c r="B232" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C232">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D232" t="s">
         <v>184</v>
@@ -13892,7 +13892,7 @@
         <v>285</v>
       </c>
       <c r="B233" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C233">
         <f t="shared" ca="1" si="4"/>
@@ -13943,11 +13943,11 @@
         <v>286</v>
       </c>
       <c r="B234" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C234">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D234" t="s">
         <v>184</v>
@@ -13994,7 +13994,7 @@
         <v>287</v>
       </c>
       <c r="B235" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C235">
         <f t="shared" ca="1" si="4"/>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C236">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D236" t="s">
         <v>184</v>
@@ -14100,7 +14100,7 @@
       </c>
       <c r="C237">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D237" t="s">
         <v>184</v>
@@ -14151,7 +14151,7 @@
       </c>
       <c r="C238">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D238" t="s">
         <v>184</v>
@@ -14198,11 +14198,11 @@
         <v>291</v>
       </c>
       <c r="B239" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C239">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D239" t="s">
         <v>184</v>
@@ -14249,7 +14249,7 @@
         <v>292</v>
       </c>
       <c r="B240" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C240">
         <f t="shared" ca="1" si="4"/>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="C241">
         <f t="shared" ca="1" si="4"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D241" t="s">
         <v>184</v>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="C242">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D242" t="s">
         <v>184</v>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="C243">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D243" t="s">
         <v>184</v>
@@ -14453,7 +14453,7 @@
         <v>296</v>
       </c>
       <c r="B244" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C244">
         <f t="shared" ca="1" si="4"/>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="C245">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D245" t="s">
         <v>184</v>
@@ -14555,11 +14555,11 @@
         <v>298</v>
       </c>
       <c r="B246" s="2">
-        <v>46319</v>
+        <v>46322</v>
       </c>
       <c r="C246">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D246" t="s">
         <v>184</v>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="C247">
         <f t="shared" ca="1" si="4"/>
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="D247" t="s">
         <v>184</v>
@@ -14661,7 +14661,7 @@
       </c>
       <c r="C248">
         <f t="shared" ca="1" si="4"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D248" t="s">
         <v>184</v>
@@ -14708,7 +14708,7 @@
         <v>301</v>
       </c>
       <c r="B249" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C249">
         <f t="shared" ca="1" si="4"/>
@@ -14759,11 +14759,11 @@
         <v>302</v>
       </c>
       <c r="B250" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C250">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D250" t="s">
         <v>184</v>
@@ -14810,11 +14810,11 @@
         <v>303</v>
       </c>
       <c r="B251" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C251">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D251" t="s">
         <v>184</v>
@@ -14861,11 +14861,11 @@
         <v>304</v>
       </c>
       <c r="B252" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C252">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D252" t="s">
         <v>184</v>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="C253">
         <f t="shared" ca="1" si="4"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D253" t="s">
         <v>184</v>
@@ -14967,7 +14967,7 @@
       </c>
       <c r="C254">
         <f t="shared" ca="1" si="4"/>
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="D254" t="s">
         <v>184</v>
@@ -15014,7 +15014,7 @@
         <v>307</v>
       </c>
       <c r="B255" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C255">
         <f t="shared" ca="1" si="4"/>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="C256">
         <f t="shared" ref="C256:C319" ca="1" si="5">B256-$R$1</f>
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="D256" t="s">
         <v>184</v>
@@ -15116,7 +15116,7 @@
         <v>309</v>
       </c>
       <c r="B257" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C257">
         <f t="shared" ca="1" si="5"/>
@@ -15167,11 +15167,11 @@
         <v>310</v>
       </c>
       <c r="B258" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C258">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D258" t="s">
         <v>184</v>
@@ -15218,7 +15218,7 @@
         <v>311</v>
       </c>
       <c r="B259" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C259">
         <f t="shared" ca="1" si="5"/>
@@ -15273,7 +15273,7 @@
       </c>
       <c r="C260">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D260" t="s">
         <v>184</v>
@@ -15324,7 +15324,7 @@
       </c>
       <c r="C261">
         <f t="shared" ca="1" si="5"/>
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="D261" t="s">
         <v>184</v>
@@ -15371,7 +15371,7 @@
         <v>314</v>
       </c>
       <c r="B262" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C262">
         <f t="shared" ca="1" si="5"/>
@@ -15422,7 +15422,7 @@
         <v>315</v>
       </c>
       <c r="B263" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C263">
         <f t="shared" ca="1" si="5"/>
@@ -15473,11 +15473,11 @@
         <v>316</v>
       </c>
       <c r="B264" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C264">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D264" t="s">
         <v>184</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C265">
         <f t="shared" ca="1" si="5"/>
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="D265" t="s">
         <v>184</v>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="C266">
         <f t="shared" ca="1" si="5"/>
-        <v>-145</v>
+        <v>-146</v>
       </c>
       <c r="D266" t="s">
         <v>184</v>
@@ -15626,7 +15626,7 @@
         <v>319</v>
       </c>
       <c r="B267" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C267">
         <f t="shared" ca="1" si="5"/>
@@ -15681,7 +15681,7 @@
       </c>
       <c r="C268">
         <f t="shared" ca="1" si="5"/>
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="D268" t="s">
         <v>184</v>
@@ -15728,11 +15728,11 @@
         <v>321</v>
       </c>
       <c r="B269" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C269">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D269" t="s">
         <v>184</v>
@@ -15779,7 +15779,7 @@
         <v>322</v>
       </c>
       <c r="B270" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C270">
         <f t="shared" ca="1" si="5"/>
@@ -15830,7 +15830,7 @@
         <v>323</v>
       </c>
       <c r="B271" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C271">
         <f t="shared" ca="1" si="5"/>
@@ -15881,7 +15881,7 @@
         <v>324</v>
       </c>
       <c r="B272" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C272">
         <f t="shared" ca="1" si="5"/>
@@ -15932,7 +15932,7 @@
         <v>325</v>
       </c>
       <c r="B273" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C273">
         <f t="shared" ca="1" si="5"/>
@@ -15983,7 +15983,7 @@
         <v>326</v>
       </c>
       <c r="B274" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C274">
         <f t="shared" ca="1" si="5"/>
@@ -16034,7 +16034,7 @@
         <v>327</v>
       </c>
       <c r="B275" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C275">
         <f t="shared" ca="1" si="5"/>
@@ -16085,7 +16085,7 @@
         <v>328</v>
       </c>
       <c r="B276" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C276">
         <f t="shared" ca="1" si="5"/>
@@ -16136,7 +16136,7 @@
         <v>329</v>
       </c>
       <c r="B277" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C277">
         <f t="shared" ca="1" si="5"/>
@@ -16187,11 +16187,11 @@
         <v>330</v>
       </c>
       <c r="B278" s="2">
-        <v>46315</v>
+        <v>46322</v>
       </c>
       <c r="C278">
         <f t="shared" ca="1" si="5"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="D278" t="s">
         <v>184</v>
@@ -16238,7 +16238,7 @@
         <v>331</v>
       </c>
       <c r="B279" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C279">
         <f t="shared" ca="1" si="5"/>
@@ -16289,7 +16289,7 @@
         <v>332</v>
       </c>
       <c r="B280" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C280">
         <f t="shared" ca="1" si="5"/>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="C281">
         <f t="shared" ca="1" si="5"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D281" t="s">
         <v>184</v>
@@ -16391,7 +16391,7 @@
         <v>334</v>
       </c>
       <c r="B282" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C282">
         <f t="shared" ca="1" si="5"/>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="C283">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D283" t="s">
         <v>184</v>
@@ -16493,7 +16493,7 @@
         <v>336</v>
       </c>
       <c r="B284" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C284">
         <f t="shared" ca="1" si="5"/>
@@ -16544,11 +16544,11 @@
         <v>337</v>
       </c>
       <c r="B285" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C285">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D285" t="s">
         <v>184</v>
@@ -16595,7 +16595,7 @@
         <v>338</v>
       </c>
       <c r="B286" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C286">
         <f t="shared" ca="1" si="5"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="C287">
         <f t="shared" ca="1" si="5"/>
-        <v>-231</v>
+        <v>-232</v>
       </c>
       <c r="D287" t="s">
         <v>184</v>
@@ -16701,7 +16701,7 @@
       </c>
       <c r="C288">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D288" t="s">
         <v>184</v>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="C289">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D289" t="s">
         <v>184</v>
@@ -16799,7 +16799,7 @@
         <v>342</v>
       </c>
       <c r="B290" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C290">
         <f t="shared" ca="1" si="5"/>
@@ -16850,7 +16850,7 @@
         <v>343</v>
       </c>
       <c r="B291" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C291">
         <f t="shared" ca="1" si="5"/>
@@ -16901,7 +16901,7 @@
         <v>344</v>
       </c>
       <c r="B292" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C292">
         <f t="shared" ca="1" si="5"/>
@@ -16952,11 +16952,11 @@
         <v>345</v>
       </c>
       <c r="B293" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C293">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D293" t="s">
         <v>184</v>
@@ -17003,11 +17003,11 @@
         <v>346</v>
       </c>
       <c r="B294" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C294">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D294" t="s">
         <v>184</v>
@@ -17054,7 +17054,7 @@
         <v>347</v>
       </c>
       <c r="B295" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C295">
         <f t="shared" ca="1" si="5"/>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="C296">
         <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D296" t="s">
         <v>184</v>
@@ -17156,7 +17156,7 @@
         <v>349</v>
       </c>
       <c r="B297" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C297">
         <f t="shared" ca="1" si="5"/>
@@ -17207,7 +17207,7 @@
         <v>350</v>
       </c>
       <c r="B298" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C298">
         <f t="shared" ca="1" si="5"/>
@@ -17258,7 +17258,7 @@
         <v>351</v>
       </c>
       <c r="B299" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C299">
         <f t="shared" ca="1" si="5"/>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="C300">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D300" t="s">
         <v>184</v>
@@ -17360,7 +17360,7 @@
         <v>353</v>
       </c>
       <c r="B301" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C301">
         <f t="shared" ca="1" si="5"/>
@@ -17411,7 +17411,7 @@
         <v>354</v>
       </c>
       <c r="B302" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C302">
         <f t="shared" ca="1" si="5"/>
@@ -17462,7 +17462,7 @@
         <v>355</v>
       </c>
       <c r="B303" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C303">
         <f t="shared" ca="1" si="5"/>
@@ -17517,7 +17517,7 @@
       </c>
       <c r="C304">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D304" t="s">
         <v>184</v>
@@ -17568,7 +17568,7 @@
       </c>
       <c r="C305">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D305" t="s">
         <v>184</v>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="C306">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D306" t="s">
         <v>184</v>
@@ -17666,7 +17666,7 @@
         <v>359</v>
       </c>
       <c r="B307" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C307">
         <f t="shared" ca="1" si="5"/>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="C308">
         <f t="shared" ca="1" si="5"/>
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="D308" t="s">
         <v>184</v>
@@ -17772,7 +17772,7 @@
       </c>
       <c r="C309">
         <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D309" t="s">
         <v>184</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="C310">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D310" t="s">
         <v>184</v>
@@ -17870,7 +17870,7 @@
         <v>363</v>
       </c>
       <c r="B311" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C311">
         <f t="shared" ca="1" si="5"/>
@@ -17921,7 +17921,7 @@
         <v>364</v>
       </c>
       <c r="B312" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C312">
         <f t="shared" ca="1" si="5"/>
@@ -17972,11 +17972,11 @@
         <v>365</v>
       </c>
       <c r="B313" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C313">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D313" t="s">
         <v>184</v>
@@ -18023,11 +18023,11 @@
         <v>366</v>
       </c>
       <c r="B314" s="2">
-        <v>46309</v>
+        <v>46322</v>
       </c>
       <c r="C314">
         <f t="shared" ca="1" si="5"/>
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="D314" t="s">
         <v>184</v>
@@ -18074,11 +18074,11 @@
         <v>367</v>
       </c>
       <c r="B315" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C315">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D315" t="s">
         <v>184</v>
@@ -18125,7 +18125,7 @@
         <v>368</v>
       </c>
       <c r="B316" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C316">
         <f t="shared" ca="1" si="5"/>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="C317">
         <f t="shared" ca="1" si="5"/>
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="D317" t="s">
         <v>184</v>
@@ -18227,7 +18227,7 @@
         <v>370</v>
       </c>
       <c r="B318" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C318">
         <f t="shared" ca="1" si="5"/>
@@ -18282,7 +18282,7 @@
       </c>
       <c r="C319">
         <f t="shared" ca="1" si="5"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D319" t="s">
         <v>184</v>
@@ -18329,7 +18329,7 @@
         <v>372</v>
       </c>
       <c r="B320" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C320">
         <f t="shared" ref="C320:C383" ca="1" si="6">B320-$R$1</f>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="C321">
         <f t="shared" ca="1" si="6"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D321" t="s">
         <v>184</v>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C322">
         <f t="shared" ca="1" si="6"/>
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="D322" t="s">
         <v>184</v>
@@ -18482,11 +18482,11 @@
         <v>375</v>
       </c>
       <c r="B323" s="2">
-        <v>46298</v>
+        <v>46322</v>
       </c>
       <c r="C323">
         <f t="shared" ca="1" si="6"/>
-        <v>-24</v>
+        <v>-1</v>
       </c>
       <c r="D323" t="s">
         <v>184</v>
@@ -18533,7 +18533,7 @@
         <v>376</v>
       </c>
       <c r="B324" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C324">
         <f t="shared" ca="1" si="6"/>
@@ -18584,11 +18584,11 @@
         <v>377</v>
       </c>
       <c r="B325" s="2">
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C325">
         <f t="shared" ca="1" si="6"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D325" t="s">
         <v>184</v>
@@ -18635,7 +18635,7 @@
         <v>378</v>
       </c>
       <c r="B326" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C326">
         <f t="shared" ca="1" si="6"/>
@@ -18690,7 +18690,7 @@
       </c>
       <c r="C327">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D327" t="s">
         <v>184</v>
@@ -18741,7 +18741,7 @@
       </c>
       <c r="C328">
         <f t="shared" ca="1" si="6"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D328" t="s">
         <v>184</v>
@@ -18788,11 +18788,11 @@
         <v>381</v>
       </c>
       <c r="B329" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C329">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D329" t="s">
         <v>184</v>
@@ -18839,7 +18839,7 @@
         <v>382</v>
       </c>
       <c r="B330" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C330">
         <f t="shared" ca="1" si="6"/>
@@ -18890,11 +18890,11 @@
         <v>383</v>
       </c>
       <c r="B331" s="2">
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="C331">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D331" t="s">
         <v>184</v>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="C332">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D332" t="s">
         <v>184</v>
@@ -18992,7 +18992,7 @@
         <v>385</v>
       </c>
       <c r="B333" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C333">
         <f t="shared" ca="1" si="6"/>
@@ -19043,11 +19043,11 @@
         <v>386</v>
       </c>
       <c r="B334" s="2">
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="C334">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D334" t="s">
         <v>184</v>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="C335">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D335" t="s">
         <v>184</v>
@@ -19145,11 +19145,11 @@
         <v>388</v>
       </c>
       <c r="B336" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C336">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D336" t="s">
         <v>184</v>
@@ -19196,7 +19196,7 @@
         <v>389</v>
       </c>
       <c r="B337" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C337">
         <f t="shared" ca="1" si="6"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="C338">
         <f t="shared" ca="1" si="6"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D338" t="s">
         <v>184</v>
@@ -19302,7 +19302,7 @@
       </c>
       <c r="C339">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D339" t="s">
         <v>184</v>
@@ -19349,7 +19349,7 @@
         <v>392</v>
       </c>
       <c r="B340" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C340">
         <f t="shared" ca="1" si="6"/>
@@ -19400,7 +19400,7 @@
         <v>393</v>
       </c>
       <c r="B341" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C341">
         <f t="shared" ca="1" si="6"/>
@@ -19455,7 +19455,7 @@
       </c>
       <c r="C342">
         <f t="shared" ca="1" si="6"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D342" t="s">
         <v>184</v>
@@ -19502,7 +19502,7 @@
         <v>395</v>
       </c>
       <c r="B343" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C343">
         <f t="shared" ca="1" si="6"/>
@@ -19553,7 +19553,7 @@
         <v>396</v>
       </c>
       <c r="B344" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C344">
         <f t="shared" ca="1" si="6"/>
@@ -19604,7 +19604,7 @@
         <v>397</v>
       </c>
       <c r="B345" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C345">
         <f t="shared" ca="1" si="6"/>
@@ -19655,7 +19655,7 @@
         <v>398</v>
       </c>
       <c r="B346" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C346">
         <f t="shared" ca="1" si="6"/>
@@ -19710,7 +19710,7 @@
       </c>
       <c r="C347">
         <f t="shared" ca="1" si="6"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D347" t="s">
         <v>184</v>
@@ -19757,11 +19757,11 @@
         <v>400</v>
       </c>
       <c r="B348" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C348">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D348" t="s">
         <v>184</v>
@@ -19808,11 +19808,11 @@
         <v>401</v>
       </c>
       <c r="B349" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C349">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D349" t="s">
         <v>184</v>
@@ -19859,11 +19859,11 @@
         <v>402</v>
       </c>
       <c r="B350" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C350">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D350" t="s">
         <v>184</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="C351">
         <f t="shared" ca="1" si="6"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D351" t="s">
         <v>184</v>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C352">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D352" t="s">
         <v>184</v>
@@ -20016,7 +20016,7 @@
       </c>
       <c r="C353">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D353" t="s">
         <v>184</v>
@@ -20067,7 +20067,7 @@
       </c>
       <c r="C354">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D354" t="s">
         <v>184</v>
@@ -20114,11 +20114,11 @@
         <v>407</v>
       </c>
       <c r="B355" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C355">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D355" t="s">
         <v>184</v>
@@ -20165,7 +20165,7 @@
         <v>408</v>
       </c>
       <c r="B356" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C356">
         <f t="shared" ca="1" si="6"/>
@@ -20216,11 +20216,11 @@
         <v>409</v>
       </c>
       <c r="B357" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C357">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D357" t="s">
         <v>184</v>
@@ -20271,7 +20271,7 @@
       </c>
       <c r="C358">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D358" t="s">
         <v>184</v>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C359">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D359" t="s">
         <v>184</v>
@@ -20369,11 +20369,11 @@
         <v>412</v>
       </c>
       <c r="B360" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C360">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D360" t="s">
         <v>184</v>
@@ -20424,7 +20424,7 @@
       </c>
       <c r="C361">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D361" t="s">
         <v>184</v>
@@ -20475,7 +20475,7 @@
       </c>
       <c r="C362">
         <f t="shared" ca="1" si="6"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D362" t="s">
         <v>184</v>
@@ -20522,11 +20522,11 @@
         <v>415</v>
       </c>
       <c r="B363" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C363">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D363" t="s">
         <v>184</v>
@@ -20573,7 +20573,7 @@
         <v>416</v>
       </c>
       <c r="B364" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C364">
         <f t="shared" ca="1" si="6"/>
@@ -20624,7 +20624,7 @@
         <v>417</v>
       </c>
       <c r="B365" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C365">
         <f t="shared" ca="1" si="6"/>
@@ -20675,7 +20675,7 @@
         <v>418</v>
       </c>
       <c r="B366" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C366">
         <f t="shared" ca="1" si="6"/>
@@ -20726,7 +20726,7 @@
         <v>419</v>
       </c>
       <c r="B367" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C367">
         <f t="shared" ca="1" si="6"/>
@@ -20777,7 +20777,7 @@
         <v>420</v>
       </c>
       <c r="B368" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C368">
         <f t="shared" ca="1" si="6"/>
@@ -20828,7 +20828,7 @@
         <v>421</v>
       </c>
       <c r="B369" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C369">
         <f t="shared" ca="1" si="6"/>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="C370">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D370" t="s">
         <v>184</v>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="C371">
         <f t="shared" ca="1" si="6"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D371" t="s">
         <v>184</v>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C372">
         <f t="shared" ca="1" si="6"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="D372" t="s">
         <v>184</v>
@@ -21032,11 +21032,11 @@
         <v>425</v>
       </c>
       <c r="B373" s="2">
-        <v>46309</v>
+        <v>46322</v>
       </c>
       <c r="C373">
         <f t="shared" ca="1" si="6"/>
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="D373" t="s">
         <v>184</v>
@@ -21087,7 +21087,7 @@
       </c>
       <c r="C374">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D374" t="s">
         <v>184</v>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="C375">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D375" t="s">
         <v>184</v>
@@ -21185,11 +21185,11 @@
         <v>428</v>
       </c>
       <c r="B376" s="2">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="C376">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D376" t="s">
         <v>184</v>
@@ -21236,7 +21236,7 @@
         <v>429</v>
       </c>
       <c r="B377" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C377">
         <f t="shared" ca="1" si="6"/>
@@ -21287,7 +21287,7 @@
         <v>430</v>
       </c>
       <c r="B378" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C378">
         <f t="shared" ca="1" si="6"/>
@@ -21338,7 +21338,7 @@
         <v>431</v>
       </c>
       <c r="B379" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C379">
         <f t="shared" ca="1" si="6"/>
@@ -21389,7 +21389,7 @@
         <v>432</v>
       </c>
       <c r="B380" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C380">
         <f t="shared" ca="1" si="6"/>
@@ -21440,7 +21440,7 @@
         <v>433</v>
       </c>
       <c r="B381" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C381">
         <f t="shared" ca="1" si="6"/>
@@ -21495,7 +21495,7 @@
       </c>
       <c r="C382">
         <f t="shared" ca="1" si="6"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D382" t="s">
         <v>184</v>
@@ -21546,7 +21546,7 @@
       </c>
       <c r="C383">
         <f t="shared" ca="1" si="6"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D383" t="s">
         <v>184</v>
@@ -21597,7 +21597,7 @@
       </c>
       <c r="C384">
         <f t="shared" ref="C384:C391" ca="1" si="7">B384-$R$1</f>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="D384" t="s">
         <v>184</v>
@@ -21644,7 +21644,7 @@
         <v>437</v>
       </c>
       <c r="B385" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C385">
         <f t="shared" ca="1" si="7"/>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="C386">
         <f t="shared" ca="1" si="7"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D386" t="s">
         <v>184</v>
@@ -21750,7 +21750,7 @@
       </c>
       <c r="C387">
         <f t="shared" ca="1" si="7"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D387" t="s">
         <v>184</v>
@@ -21801,7 +21801,7 @@
       </c>
       <c r="C388">
         <f t="shared" ca="1" si="7"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D388" t="s">
         <v>184</v>
@@ -21852,7 +21852,7 @@
       </c>
       <c r="C389">
         <f t="shared" ca="1" si="7"/>
-        <v>-46322</v>
+        <v>-46323</v>
       </c>
       <c r="D389" t="s">
         <v>184</v>
@@ -21899,7 +21899,7 @@
         <v>442</v>
       </c>
       <c r="B390" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C390">
         <f t="shared" ca="1" si="7"/>
@@ -21954,7 +21954,7 @@
       </c>
       <c r="C391">
         <f t="shared" ca="1" si="7"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D391" t="s">
         <v>184</v>
@@ -22002,6 +22002,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
@@ -22011,15 +22020,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22284,20 +22284,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
     <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delunatransportes-my.sharepoint.com/personal/alexsander_miranda_delunatransportes_com_br/Documents/Área de Trabalho/BID FROTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="476" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FAA0D96-C461-427C-8AE0-57AD3017481D}"/>
+  <xr:revisionPtr revIDLastSave="482" documentId="11_1BA57A0BCA357D1375850D421C43AE8381E2225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{688FA8F0-D6FE-475A-8CFB-738601EE274B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4798" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4799" uniqueCount="467">
   <si>
     <t>Placa</t>
   </si>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="R1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C2">
         <f ca="1">B2-$R$1</f>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D2" t="s">
         <v>184</v>
@@ -1927,11 +1927,11 @@
         <v>14</v>
       </c>
       <c r="B3" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C66" ca="1" si="0">B3-$R$1</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D3" t="s">
         <v>184</v>
@@ -1979,11 +1979,11 @@
         <v>15</v>
       </c>
       <c r="B4" s="2">
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D4" t="s">
         <v>184</v>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D5" t="s">
         <v>184</v>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D6" t="s">
         <v>184</v>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D7" t="s">
         <v>184</v>
@@ -2187,7 +2187,7 @@
         <v>19</v>
       </c>
       <c r="B8" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
@@ -2239,7 +2239,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D10" t="s">
         <v>184</v>
@@ -2345,7 +2345,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D12" t="s">
         <v>184</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D13" t="s">
         <v>184</v>
@@ -2507,7 +2507,7 @@
         <v>36</v>
       </c>
       <c r="B14" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
@@ -2561,11 +2561,11 @@
         <v>37</v>
       </c>
       <c r="B15" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D15" t="s">
         <v>184</v>
@@ -2615,7 +2615,7 @@
         <v>38</v>
       </c>
       <c r="B16" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D17" t="s">
         <v>184</v>
@@ -2723,7 +2723,7 @@
         <v>40</v>
       </c>
       <c r="B18" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
@@ -2777,7 +2777,7 @@
         <v>41</v>
       </c>
       <c r="B19" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
@@ -2831,7 +2831,7 @@
         <v>42</v>
       </c>
       <c r="B20" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D21" t="s">
         <v>184</v>
@@ -2939,7 +2939,7 @@
         <v>44</v>
       </c>
       <c r="B22" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="0"/>
@@ -2993,7 +2993,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="0"/>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D24" t="s">
         <v>184</v>
@@ -3101,7 +3101,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="0"/>
@@ -3155,7 +3155,7 @@
         <v>49</v>
       </c>
       <c r="B26" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="0"/>
@@ -3209,7 +3209,7 @@
         <v>50</v>
       </c>
       <c r="B27" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="0"/>
@@ -3263,7 +3263,7 @@
         <v>51</v>
       </c>
       <c r="B28" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="0"/>
@@ -3317,7 +3317,7 @@
         <v>52</v>
       </c>
       <c r="B29" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="0"/>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="0"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D30" t="s">
         <v>184</v>
@@ -3425,11 +3425,11 @@
         <v>54</v>
       </c>
       <c r="B31" s="2">
-        <v>46315</v>
+        <v>46323</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="0"/>
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="D31" t="s">
         <v>184</v>
@@ -3479,7 +3479,7 @@
         <v>55</v>
       </c>
       <c r="B32" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="0"/>
@@ -3533,7 +3533,7 @@
         <v>56</v>
       </c>
       <c r="B33" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="0"/>
@@ -3587,11 +3587,11 @@
         <v>57</v>
       </c>
       <c r="B34" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D34" t="s">
         <v>184</v>
@@ -3641,7 +3641,7 @@
         <v>58</v>
       </c>
       <c r="B35" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="0"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="0"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D36" t="s">
         <v>184</v>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="0"/>
-        <v>-57</v>
+        <v>-58</v>
       </c>
       <c r="D37" t="s">
         <v>184</v>
@@ -3803,11 +3803,11 @@
         <v>62</v>
       </c>
       <c r="B38" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D38" t="s">
         <v>184</v>
@@ -3857,7 +3857,7 @@
         <v>63</v>
       </c>
       <c r="B39" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="0"/>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="0"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="D40" t="s">
         <v>184</v>
@@ -3965,7 +3965,7 @@
         <v>65</v>
       </c>
       <c r="B41" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="0"/>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D42" t="s">
         <v>184</v>
@@ -4073,7 +4073,7 @@
         <v>67</v>
       </c>
       <c r="B43" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="0"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="0"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D44" t="s">
         <v>184</v>
@@ -4181,7 +4181,7 @@
         <v>69</v>
       </c>
       <c r="B45" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="0"/>
@@ -4235,11 +4235,11 @@
         <v>70</v>
       </c>
       <c r="B46" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D46" t="s">
         <v>184</v>
@@ -4289,7 +4289,7 @@
         <v>71</v>
       </c>
       <c r="B47" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="0"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="0"/>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="D48" t="s">
         <v>184</v>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="0"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D49" t="s">
         <v>184</v>
@@ -4451,7 +4451,7 @@
         <v>74</v>
       </c>
       <c r="B50" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="0"/>
@@ -4505,7 +4505,7 @@
         <v>75</v>
       </c>
       <c r="B51" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="0"/>
@@ -4559,7 +4559,7 @@
         <v>76</v>
       </c>
       <c r="B52" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="0"/>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="0"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D53" t="s">
         <v>184</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="0"/>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="D54" t="s">
         <v>184</v>
@@ -4721,7 +4721,7 @@
         <v>79</v>
       </c>
       <c r="B55" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="0"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="0"/>
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="D56" t="s">
         <v>184</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="0"/>
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="D57" t="s">
         <v>184</v>
@@ -4883,7 +4883,7 @@
         <v>82</v>
       </c>
       <c r="B58" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="0"/>
@@ -4937,7 +4937,7 @@
         <v>83</v>
       </c>
       <c r="B59" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="0"/>
@@ -4991,7 +4991,7 @@
         <v>84</v>
       </c>
       <c r="B60" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="0"/>
@@ -5045,7 +5045,7 @@
         <v>85</v>
       </c>
       <c r="B61" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="0"/>
@@ -5099,7 +5099,7 @@
         <v>86</v>
       </c>
       <c r="B62" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="0"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D63" t="s">
         <v>184</v>
@@ -5207,7 +5207,7 @@
         <v>90</v>
       </c>
       <c r="B64" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="0"/>
@@ -5261,11 +5261,11 @@
         <v>92</v>
       </c>
       <c r="B65" s="2">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="0"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="D65" t="s">
         <v>184</v>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="0"/>
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="D66" t="s">
         <v>184</v>
@@ -5369,7 +5369,7 @@
         <v>94</v>
       </c>
       <c r="B67" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C67">
         <f t="shared" ref="C67:C130" ca="1" si="1">B67-$R$1</f>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="1"/>
-        <v>-68</v>
+        <v>-69</v>
       </c>
       <c r="D68" t="s">
         <v>184</v>
@@ -5477,7 +5477,7 @@
         <v>96</v>
       </c>
       <c r="B69" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="1"/>
@@ -5531,7 +5531,7 @@
         <v>97</v>
       </c>
       <c r="B70" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="1"/>
@@ -5585,7 +5585,7 @@
         <v>98</v>
       </c>
       <c r="B71" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="1"/>
@@ -5639,7 +5639,7 @@
         <v>99</v>
       </c>
       <c r="B72" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="1"/>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="1"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D73" t="s">
         <v>184</v>
@@ -5747,7 +5747,7 @@
         <v>102</v>
       </c>
       <c r="B74" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="1"/>
@@ -5801,11 +5801,11 @@
         <v>103</v>
       </c>
       <c r="B75" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D75" t="s">
         <v>184</v>
@@ -5855,11 +5855,11 @@
         <v>104</v>
       </c>
       <c r="B76" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D76" t="s">
         <v>184</v>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D77" t="s">
         <v>184</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="1"/>
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="D78" t="s">
         <v>184</v>
@@ -6017,7 +6017,7 @@
         <v>107</v>
       </c>
       <c r="B79" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C79">
         <f t="shared" ca="1" si="1"/>
@@ -6071,7 +6071,7 @@
         <v>108</v>
       </c>
       <c r="B80" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="1"/>
@@ -6125,7 +6125,7 @@
         <v>109</v>
       </c>
       <c r="B81" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C81">
         <f t="shared" ca="1" si="1"/>
@@ -6179,7 +6179,7 @@
         <v>110</v>
       </c>
       <c r="B82" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C82">
         <f t="shared" ca="1" si="1"/>
@@ -6233,7 +6233,7 @@
         <v>111</v>
       </c>
       <c r="B83" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="1"/>
@@ -6287,7 +6287,7 @@
         <v>112</v>
       </c>
       <c r="B84" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="1"/>
@@ -6341,11 +6341,11 @@
         <v>113</v>
       </c>
       <c r="B85" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D85" t="s">
         <v>184</v>
@@ -6395,7 +6395,7 @@
         <v>114</v>
       </c>
       <c r="B86" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="1"/>
@@ -6449,7 +6449,7 @@
         <v>115</v>
       </c>
       <c r="B87" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C87">
         <f t="shared" ca="1" si="1"/>
@@ -6503,7 +6503,7 @@
         <v>116</v>
       </c>
       <c r="B88" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="1"/>
@@ -6557,7 +6557,7 @@
         <v>117</v>
       </c>
       <c r="B89" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="1"/>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D90" t="s">
         <v>184</v>
@@ -6665,7 +6665,7 @@
         <v>122</v>
       </c>
       <c r="B91" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="1"/>
@@ -6719,7 +6719,7 @@
         <v>123</v>
       </c>
       <c r="B92" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="1"/>
@@ -6773,7 +6773,7 @@
         <v>124</v>
       </c>
       <c r="B93" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="1"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D94" t="s">
         <v>184</v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D95" t="s">
         <v>184</v>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D96" t="s">
         <v>184</v>
@@ -6989,11 +6989,11 @@
         <v>128</v>
       </c>
       <c r="B97" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D97" t="s">
         <v>184</v>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D98" t="s">
         <v>184</v>
@@ -7097,11 +7097,11 @@
         <v>130</v>
       </c>
       <c r="B99" s="2">
-        <v>46319</v>
+        <v>46323</v>
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="1"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D99" t="s">
         <v>184</v>
@@ -7151,7 +7151,7 @@
         <v>131</v>
       </c>
       <c r="B100" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="1"/>
@@ -7205,7 +7205,7 @@
         <v>132</v>
       </c>
       <c r="B101" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="1"/>
@@ -7263,7 +7263,7 @@
       </c>
       <c r="C102">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D102" t="s">
         <v>184</v>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="C103">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D103" t="s">
         <v>184</v>
@@ -7367,7 +7367,7 @@
         <v>135</v>
       </c>
       <c r="B104" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C104">
         <f t="shared" ca="1" si="1"/>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="C105">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D105" t="s">
         <v>184</v>
@@ -7475,7 +7475,7 @@
         <v>137</v>
       </c>
       <c r="B106" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C106">
         <f t="shared" ca="1" si="1"/>
@@ -7529,7 +7529,7 @@
         <v>138</v>
       </c>
       <c r="B107" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C107">
         <f t="shared" ca="1" si="1"/>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="C108">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D108" t="s">
         <v>184</v>
@@ -7637,7 +7637,7 @@
         <v>140</v>
       </c>
       <c r="B109" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C109">
         <f t="shared" ca="1" si="1"/>
@@ -7691,7 +7691,7 @@
         <v>141</v>
       </c>
       <c r="B110" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C110">
         <f t="shared" ca="1" si="1"/>
@@ -7745,11 +7745,11 @@
         <v>142</v>
       </c>
       <c r="B111" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C111">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D111" t="s">
         <v>184</v>
@@ -7803,9 +7803,12 @@
       </c>
       <c r="C112">
         <f t="shared" ca="1" si="1"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D112" t="s">
+        <v>184</v>
+      </c>
+      <c r="I112" t="s">
         <v>184</v>
       </c>
       <c r="J112" t="s">
@@ -7838,7 +7841,7 @@
         <v>143</v>
       </c>
       <c r="B113" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C113">
         <f t="shared" ca="1" si="1"/>
@@ -7896,7 +7899,7 @@
       </c>
       <c r="C114">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D114" t="s">
         <v>184</v>
@@ -7946,7 +7949,7 @@
         <v>145</v>
       </c>
       <c r="B115" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C115">
         <f t="shared" ca="1" si="1"/>
@@ -8000,7 +8003,7 @@
         <v>147</v>
       </c>
       <c r="B116" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C116">
         <f t="shared" ca="1" si="1"/>
@@ -8054,7 +8057,7 @@
         <v>148</v>
       </c>
       <c r="B117" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C117">
         <f t="shared" ca="1" si="1"/>
@@ -8108,7 +8111,7 @@
         <v>149</v>
       </c>
       <c r="B118" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C118">
         <f t="shared" ca="1" si="1"/>
@@ -8162,7 +8165,7 @@
         <v>150</v>
       </c>
       <c r="B119" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C119">
         <f t="shared" ca="1" si="1"/>
@@ -8216,7 +8219,7 @@
         <v>151</v>
       </c>
       <c r="B120" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C120">
         <f t="shared" ca="1" si="1"/>
@@ -8274,7 +8277,7 @@
       </c>
       <c r="C121">
         <f t="shared" ca="1" si="1"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D121" t="s">
         <v>465</v>
@@ -8324,11 +8327,11 @@
         <v>154</v>
       </c>
       <c r="B122" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C122">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D122" t="s">
         <v>184</v>
@@ -8378,7 +8381,7 @@
         <v>155</v>
       </c>
       <c r="B123" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C123">
         <f t="shared" ca="1" si="1"/>
@@ -8432,11 +8435,11 @@
         <v>156</v>
       </c>
       <c r="B124" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C124">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D124" t="s">
         <v>184</v>
@@ -8490,7 +8493,7 @@
       </c>
       <c r="C125">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D125" t="s">
         <v>184</v>
@@ -8540,11 +8543,11 @@
         <v>158</v>
       </c>
       <c r="B126" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C126">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D126" t="s">
         <v>184</v>
@@ -8594,7 +8597,7 @@
         <v>159</v>
       </c>
       <c r="B127" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C127">
         <f t="shared" ca="1" si="1"/>
@@ -8648,7 +8651,7 @@
         <v>160</v>
       </c>
       <c r="B128" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C128">
         <f t="shared" ca="1" si="1"/>
@@ -8702,7 +8705,7 @@
         <v>161</v>
       </c>
       <c r="B129" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C129">
         <f t="shared" ca="1" si="1"/>
@@ -8756,7 +8759,7 @@
         <v>162</v>
       </c>
       <c r="B130" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C130">
         <f t="shared" ca="1" si="1"/>
@@ -8810,7 +8813,7 @@
         <v>186</v>
       </c>
       <c r="B131" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C131">
         <f t="shared" ref="C131:C193" ca="1" si="2">B131-$R$1</f>
@@ -8864,7 +8867,7 @@
         <v>187</v>
       </c>
       <c r="B132" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C132">
         <f t="shared" ca="1" si="2"/>
@@ -8922,7 +8925,7 @@
       </c>
       <c r="C133">
         <f t="shared" ref="C133" ca="1" si="3">B133-$R$1</f>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D133" t="s">
         <v>184</v>
@@ -8960,7 +8963,7 @@
         <v>188</v>
       </c>
       <c r="B134" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C134">
         <f t="shared" ca="1" si="2"/>
@@ -9014,7 +9017,7 @@
         <v>189</v>
       </c>
       <c r="B135" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C135">
         <f t="shared" ca="1" si="2"/>
@@ -9068,7 +9071,7 @@
         <v>190</v>
       </c>
       <c r="B136" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C136">
         <f t="shared" ca="1" si="2"/>
@@ -9122,7 +9125,7 @@
         <v>191</v>
       </c>
       <c r="B137" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C137">
         <f t="shared" ca="1" si="2"/>
@@ -9176,7 +9179,7 @@
         <v>192</v>
       </c>
       <c r="B138" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C138">
         <f t="shared" ca="1" si="2"/>
@@ -9234,7 +9237,7 @@
       </c>
       <c r="C139">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D139" t="s">
         <v>184</v>
@@ -9272,7 +9275,7 @@
         <v>194</v>
       </c>
       <c r="B140" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C140">
         <f t="shared" ca="1" si="2"/>
@@ -9330,7 +9333,7 @@
       </c>
       <c r="C141">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D141" t="s">
         <v>184</v>
@@ -9368,7 +9371,7 @@
         <v>196</v>
       </c>
       <c r="B142" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C142">
         <f t="shared" ca="1" si="2"/>
@@ -9414,7 +9417,7 @@
       </c>
       <c r="C143">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="J143" t="s">
         <v>28</v>
@@ -9443,7 +9446,7 @@
       </c>
       <c r="C144">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="J144" t="s">
         <v>28</v>
@@ -9471,7 +9474,7 @@
         <v>199</v>
       </c>
       <c r="B145" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C145">
         <f t="shared" ca="1" si="2"/>
@@ -9525,7 +9528,7 @@
       </c>
       <c r="C146">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="J146" t="s">
         <v>28</v>
@@ -9557,7 +9560,7 @@
       </c>
       <c r="C147">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D147" t="s">
         <v>184</v>
@@ -9595,7 +9598,7 @@
         <v>202</v>
       </c>
       <c r="B148" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C148">
         <f t="shared" ca="1" si="2"/>
@@ -9641,7 +9644,7 @@
       </c>
       <c r="C149">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D149" t="s">
         <v>184</v>
@@ -9683,7 +9686,7 @@
       </c>
       <c r="C150">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="J150" t="s">
         <v>22</v>
@@ -9713,7 +9716,7 @@
         <v>205</v>
       </c>
       <c r="B151" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C151">
         <f t="shared" ca="1" si="2"/>
@@ -9767,7 +9770,7 @@
         <v>164</v>
       </c>
       <c r="B152" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C152">
         <f t="shared" ca="1" si="2"/>
@@ -9821,7 +9824,7 @@
         <v>165</v>
       </c>
       <c r="B153" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C153">
         <f t="shared" ca="1" si="2"/>
@@ -9875,7 +9878,7 @@
         <v>166</v>
       </c>
       <c r="B154" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C154">
         <f t="shared" ca="1" si="2"/>
@@ -9929,7 +9932,7 @@
         <v>167</v>
       </c>
       <c r="B155" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
@@ -9983,7 +9986,7 @@
         <v>168</v>
       </c>
       <c r="B156" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
@@ -10041,7 +10044,7 @@
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="D157" t="s">
         <v>184</v>
@@ -10091,7 +10094,7 @@
         <v>170</v>
       </c>
       <c r="B158" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C158">
         <f t="shared" ca="1" si="2"/>
@@ -10145,7 +10148,7 @@
         <v>171</v>
       </c>
       <c r="B159" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C159">
         <f t="shared" ca="1" si="2"/>
@@ -10199,7 +10202,7 @@
         <v>172</v>
       </c>
       <c r="B160" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
@@ -10253,11 +10256,11 @@
         <v>173</v>
       </c>
       <c r="B161" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D161" t="s">
         <v>184</v>
@@ -10307,7 +10310,7 @@
         <v>175</v>
       </c>
       <c r="B162" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
@@ -10365,7 +10368,7 @@
       </c>
       <c r="C163">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D163" t="s">
         <v>184</v>
@@ -10415,7 +10418,7 @@
         <v>206</v>
       </c>
       <c r="B164" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C164">
         <f t="shared" ca="1" si="2"/>
@@ -10473,7 +10476,7 @@
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D165" t="s">
         <v>184</v>
@@ -10515,7 +10518,7 @@
       </c>
       <c r="C166">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D166" t="s">
         <v>465</v>
@@ -10569,7 +10572,7 @@
       </c>
       <c r="C167">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D167" t="s">
         <v>465</v>
@@ -10611,7 +10614,7 @@
       </c>
       <c r="C168">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D168" t="s">
         <v>465</v>
@@ -10649,7 +10652,7 @@
         <v>211</v>
       </c>
       <c r="B169" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C169">
         <f t="shared" ca="1" si="2"/>
@@ -10703,11 +10706,11 @@
         <v>212</v>
       </c>
       <c r="B170" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C170">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D170" t="s">
         <v>184</v>
@@ -10757,11 +10760,11 @@
         <v>213</v>
       </c>
       <c r="B171" s="2">
-        <v>0</v>
+        <v>46323</v>
       </c>
       <c r="C171">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-1</v>
       </c>
       <c r="D171" t="s">
         <v>465</v>
@@ -10803,7 +10806,7 @@
       </c>
       <c r="C172">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D172" t="s">
         <v>465</v>
@@ -10845,7 +10848,7 @@
       </c>
       <c r="C173">
         <f t="shared" ca="1" si="2"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D173" t="s">
         <v>184</v>
@@ -10887,7 +10890,7 @@
       </c>
       <c r="C174">
         <f t="shared" ca="1" si="2"/>
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="D174" t="s">
         <v>184</v>
@@ -10938,7 +10941,7 @@
       </c>
       <c r="C175">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D175" t="s">
         <v>184</v>
@@ -10989,7 +10992,7 @@
       </c>
       <c r="C176">
         <f t="shared" ca="1" si="2"/>
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="D176" t="s">
         <v>184</v>
@@ -11036,11 +11039,11 @@
         <v>229</v>
       </c>
       <c r="B177" s="2">
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="C177">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D177" t="s">
         <v>184</v>
@@ -11087,7 +11090,7 @@
         <v>230</v>
       </c>
       <c r="B178" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C178">
         <f t="shared" ca="1" si="2"/>
@@ -11138,7 +11141,7 @@
         <v>231</v>
       </c>
       <c r="B179" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C179">
         <f t="shared" ca="1" si="2"/>
@@ -11189,7 +11192,7 @@
         <v>232</v>
       </c>
       <c r="B180" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C180">
         <f t="shared" ca="1" si="2"/>
@@ -11240,7 +11243,7 @@
         <v>233</v>
       </c>
       <c r="B181" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C181">
         <f t="shared" ca="1" si="2"/>
@@ -11295,7 +11298,7 @@
       </c>
       <c r="C182">
         <f t="shared" ca="1" si="2"/>
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="D182" t="s">
         <v>184</v>
@@ -11342,11 +11345,11 @@
         <v>235</v>
       </c>
       <c r="B183" s="2">
-        <v>46319</v>
+        <v>46323</v>
       </c>
       <c r="C183">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D183" t="s">
         <v>184</v>
@@ -11397,7 +11400,7 @@
       </c>
       <c r="C184">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D184" t="s">
         <v>184</v>
@@ -11448,7 +11451,7 @@
       </c>
       <c r="C185">
         <f t="shared" ca="1" si="2"/>
-        <v>-57</v>
+        <v>-58</v>
       </c>
       <c r="D185" t="s">
         <v>184</v>
@@ -11499,7 +11502,7 @@
       </c>
       <c r="C186">
         <f t="shared" ca="1" si="2"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D186" t="s">
         <v>184</v>
@@ -11546,7 +11549,7 @@
         <v>239</v>
       </c>
       <c r="B187" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C187">
         <f t="shared" ca="1" si="2"/>
@@ -11601,7 +11604,7 @@
       </c>
       <c r="C188">
         <f t="shared" ca="1" si="2"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="D188" t="s">
         <v>184</v>
@@ -11648,7 +11651,7 @@
         <v>241</v>
       </c>
       <c r="B189" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C189">
         <f t="shared" ca="1" si="2"/>
@@ -11699,7 +11702,7 @@
         <v>242</v>
       </c>
       <c r="B190" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C190">
         <f t="shared" ca="1" si="2"/>
@@ -11750,7 +11753,7 @@
         <v>243</v>
       </c>
       <c r="B191" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C191">
         <f t="shared" ca="1" si="2"/>
@@ -11805,7 +11808,7 @@
       </c>
       <c r="C192">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D192" t="s">
         <v>184</v>
@@ -11856,7 +11859,7 @@
       </c>
       <c r="C193">
         <f t="shared" ca="1" si="2"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D193" t="s">
         <v>184</v>
@@ -11907,7 +11910,7 @@
       </c>
       <c r="C194">
         <f t="shared" ref="C194:C255" ca="1" si="4">B194-$R$1</f>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D194" t="s">
         <v>184</v>
@@ -11958,7 +11961,7 @@
       </c>
       <c r="C195">
         <f t="shared" ca="1" si="4"/>
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="D195" t="s">
         <v>184</v>
@@ -12005,11 +12008,11 @@
         <v>248</v>
       </c>
       <c r="B196" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C196">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D196" t="s">
         <v>184</v>
@@ -12060,7 +12063,7 @@
       </c>
       <c r="C197">
         <f t="shared" ca="1" si="4"/>
-        <v>-156</v>
+        <v>-157</v>
       </c>
       <c r="D197" t="s">
         <v>184</v>
@@ -12111,7 +12114,7 @@
       </c>
       <c r="C198">
         <f t="shared" ca="1" si="4"/>
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="D198" t="s">
         <v>184</v>
@@ -12162,7 +12165,7 @@
       </c>
       <c r="C199">
         <f t="shared" ca="1" si="4"/>
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="D199" t="s">
         <v>184</v>
@@ -12213,7 +12216,7 @@
       </c>
       <c r="C200">
         <f t="shared" ca="1" si="4"/>
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="D200" t="s">
         <v>184</v>
@@ -12264,7 +12267,7 @@
       </c>
       <c r="C201">
         <f t="shared" ca="1" si="4"/>
-        <v>-286</v>
+        <v>-287</v>
       </c>
       <c r="D201" t="s">
         <v>184</v>
@@ -12311,7 +12314,7 @@
         <v>254</v>
       </c>
       <c r="B202" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C202">
         <f t="shared" ca="1" si="4"/>
@@ -12362,7 +12365,7 @@
         <v>255</v>
       </c>
       <c r="B203" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C203">
         <f t="shared" ca="1" si="4"/>
@@ -12413,11 +12416,11 @@
         <v>256</v>
       </c>
       <c r="B204" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C204">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D204" t="s">
         <v>184</v>
@@ -12464,7 +12467,7 @@
         <v>257</v>
       </c>
       <c r="B205" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C205">
         <f t="shared" ca="1" si="4"/>
@@ -12515,7 +12518,7 @@
         <v>258</v>
       </c>
       <c r="B206" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C206">
         <f t="shared" ca="1" si="4"/>
@@ -12566,7 +12569,7 @@
         <v>259</v>
       </c>
       <c r="B207" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C207">
         <f t="shared" ca="1" si="4"/>
@@ -12617,11 +12620,11 @@
         <v>260</v>
       </c>
       <c r="B208" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C208">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D208" t="s">
         <v>184</v>
@@ -12668,7 +12671,7 @@
         <v>261</v>
       </c>
       <c r="B209" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C209">
         <f t="shared" ca="1" si="4"/>
@@ -12719,11 +12722,11 @@
         <v>262</v>
       </c>
       <c r="B210" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C210">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D210" t="s">
         <v>184</v>
@@ -12770,11 +12773,11 @@
         <v>263</v>
       </c>
       <c r="B211" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C211">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D211" t="s">
         <v>184</v>
@@ -12821,11 +12824,11 @@
         <v>264</v>
       </c>
       <c r="B212" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C212">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D212" t="s">
         <v>184</v>
@@ -12872,7 +12875,7 @@
         <v>265</v>
       </c>
       <c r="B213" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C213">
         <f t="shared" ca="1" si="4"/>
@@ -12923,11 +12926,11 @@
         <v>266</v>
       </c>
       <c r="B214" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C214">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D214" t="s">
         <v>184</v>
@@ -12978,7 +12981,7 @@
       </c>
       <c r="C215">
         <f t="shared" ca="1" si="4"/>
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="D215" t="s">
         <v>184</v>
@@ -13029,7 +13032,7 @@
       </c>
       <c r="C216">
         <f t="shared" ca="1" si="4"/>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
@@ -13076,11 +13079,11 @@
         <v>269</v>
       </c>
       <c r="B217" s="2">
-        <v>46319</v>
+        <v>46323</v>
       </c>
       <c r="C217">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D217" t="s">
         <v>184</v>
@@ -13131,7 +13134,7 @@
       </c>
       <c r="C218">
         <f t="shared" ca="1" si="4"/>
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="D218" t="s">
         <v>184</v>
@@ -13178,7 +13181,7 @@
         <v>271</v>
       </c>
       <c r="B219" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C219">
         <f t="shared" ca="1" si="4"/>
@@ -13229,11 +13232,11 @@
         <v>272</v>
       </c>
       <c r="B220" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C220">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D220" t="s">
         <v>184</v>
@@ -13284,7 +13287,7 @@
       </c>
       <c r="C221">
         <f t="shared" ca="1" si="4"/>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="D221" t="s">
         <v>184</v>
@@ -13331,7 +13334,7 @@
         <v>274</v>
       </c>
       <c r="B222" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C222">
         <f t="shared" ca="1" si="4"/>
@@ -13382,7 +13385,7 @@
         <v>275</v>
       </c>
       <c r="B223" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C223">
         <f t="shared" ca="1" si="4"/>
@@ -13437,7 +13440,7 @@
       </c>
       <c r="C224">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D224" t="s">
         <v>184</v>
@@ -13484,11 +13487,11 @@
         <v>277</v>
       </c>
       <c r="B225" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C225">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D225" t="s">
         <v>184</v>
@@ -13535,11 +13538,11 @@
         <v>278</v>
       </c>
       <c r="B226" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C226">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D226" t="s">
         <v>184</v>
@@ -13586,7 +13589,7 @@
         <v>279</v>
       </c>
       <c r="B227" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C227">
         <f t="shared" ca="1" si="4"/>
@@ -13637,7 +13640,7 @@
         <v>280</v>
       </c>
       <c r="B228" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C228">
         <f t="shared" ca="1" si="4"/>
@@ -13688,7 +13691,7 @@
         <v>281</v>
       </c>
       <c r="B229" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C229">
         <f t="shared" ca="1" si="4"/>
@@ -13739,11 +13742,11 @@
         <v>282</v>
       </c>
       <c r="B230" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C230">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D230" t="s">
         <v>184</v>
@@ -13790,7 +13793,7 @@
         <v>283</v>
       </c>
       <c r="B231" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C231">
         <f t="shared" ca="1" si="4"/>
@@ -13841,7 +13844,7 @@
         <v>284</v>
       </c>
       <c r="B232" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C232">
         <f t="shared" ca="1" si="4"/>
@@ -13892,7 +13895,7 @@
         <v>285</v>
       </c>
       <c r="B233" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C233">
         <f t="shared" ca="1" si="4"/>
@@ -13943,7 +13946,7 @@
         <v>286</v>
       </c>
       <c r="B234" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C234">
         <f t="shared" ca="1" si="4"/>
@@ -13994,7 +13997,7 @@
         <v>287</v>
       </c>
       <c r="B235" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C235">
         <f t="shared" ca="1" si="4"/>
@@ -14045,11 +14048,11 @@
         <v>288</v>
       </c>
       <c r="B236" s="2">
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="C236">
         <f t="shared" ca="1" si="4"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D236" t="s">
         <v>184</v>
@@ -14096,11 +14099,11 @@
         <v>289</v>
       </c>
       <c r="B237" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C237">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D237" t="s">
         <v>184</v>
@@ -14151,7 +14154,7 @@
       </c>
       <c r="C238">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D238" t="s">
         <v>184</v>
@@ -14198,7 +14201,7 @@
         <v>291</v>
       </c>
       <c r="B239" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C239">
         <f t="shared" ca="1" si="4"/>
@@ -14249,7 +14252,7 @@
         <v>292</v>
       </c>
       <c r="B240" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C240">
         <f t="shared" ca="1" si="4"/>
@@ -14300,11 +14303,11 @@
         <v>293</v>
       </c>
       <c r="B241" s="2">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="C241">
         <f t="shared" ca="1" si="4"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="D241" t="s">
         <v>184</v>
@@ -14351,11 +14354,11 @@
         <v>294</v>
       </c>
       <c r="B242" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C242">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D242" t="s">
         <v>184</v>
@@ -14406,7 +14409,7 @@
       </c>
       <c r="C243">
         <f t="shared" ca="1" si="4"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D243" t="s">
         <v>184</v>
@@ -14453,7 +14456,7 @@
         <v>296</v>
       </c>
       <c r="B244" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C244">
         <f t="shared" ca="1" si="4"/>
@@ -14508,7 +14511,7 @@
       </c>
       <c r="C245">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D245" t="s">
         <v>184</v>
@@ -14555,7 +14558,7 @@
         <v>298</v>
       </c>
       <c r="B246" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C246">
         <f t="shared" ca="1" si="4"/>
@@ -14610,7 +14613,7 @@
       </c>
       <c r="C247">
         <f t="shared" ca="1" si="4"/>
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="D247" t="s">
         <v>184</v>
@@ -14657,11 +14660,11 @@
         <v>300</v>
       </c>
       <c r="B248" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C248">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D248" t="s">
         <v>184</v>
@@ -14708,7 +14711,7 @@
         <v>301</v>
       </c>
       <c r="B249" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C249">
         <f t="shared" ca="1" si="4"/>
@@ -14759,7 +14762,7 @@
         <v>302</v>
       </c>
       <c r="B250" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C250">
         <f t="shared" ca="1" si="4"/>
@@ -14810,7 +14813,7 @@
         <v>303</v>
       </c>
       <c r="B251" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C251">
         <f t="shared" ca="1" si="4"/>
@@ -14861,7 +14864,7 @@
         <v>304</v>
       </c>
       <c r="B252" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C252">
         <f t="shared" ca="1" si="4"/>
@@ -14916,7 +14919,7 @@
       </c>
       <c r="C253">
         <f t="shared" ca="1" si="4"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D253" t="s">
         <v>184</v>
@@ -14967,7 +14970,7 @@
       </c>
       <c r="C254">
         <f t="shared" ca="1" si="4"/>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="D254" t="s">
         <v>184</v>
@@ -15014,7 +15017,7 @@
         <v>307</v>
       </c>
       <c r="B255" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C255">
         <f t="shared" ca="1" si="4"/>
@@ -15065,11 +15068,11 @@
         <v>308</v>
       </c>
       <c r="B256" s="2">
-        <v>46207</v>
+        <v>46323</v>
       </c>
       <c r="C256">
         <f t="shared" ref="C256:C319" ca="1" si="5">B256-$R$1</f>
-        <v>-116</v>
+        <v>-1</v>
       </c>
       <c r="D256" t="s">
         <v>184</v>
@@ -15116,7 +15119,7 @@
         <v>309</v>
       </c>
       <c r="B257" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C257">
         <f t="shared" ca="1" si="5"/>
@@ -15167,7 +15170,7 @@
         <v>310</v>
       </c>
       <c r="B258" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C258">
         <f t="shared" ca="1" si="5"/>
@@ -15222,7 +15225,7 @@
       </c>
       <c r="C259">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D259" t="s">
         <v>184</v>
@@ -15269,11 +15272,11 @@
         <v>312</v>
       </c>
       <c r="B260" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C260">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D260" t="s">
         <v>184</v>
@@ -15324,7 +15327,7 @@
       </c>
       <c r="C261">
         <f t="shared" ca="1" si="5"/>
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="D261" t="s">
         <v>184</v>
@@ -15371,7 +15374,7 @@
         <v>314</v>
       </c>
       <c r="B262" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C262">
         <f t="shared" ca="1" si="5"/>
@@ -15422,7 +15425,7 @@
         <v>315</v>
       </c>
       <c r="B263" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C263">
         <f t="shared" ca="1" si="5"/>
@@ -15473,7 +15476,7 @@
         <v>316</v>
       </c>
       <c r="B264" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C264">
         <f t="shared" ca="1" si="5"/>
@@ -15528,7 +15531,7 @@
       </c>
       <c r="C265">
         <f t="shared" ca="1" si="5"/>
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="D265" t="s">
         <v>184</v>
@@ -15579,7 +15582,7 @@
       </c>
       <c r="C266">
         <f t="shared" ca="1" si="5"/>
-        <v>-146</v>
+        <v>-147</v>
       </c>
       <c r="D266" t="s">
         <v>184</v>
@@ -15626,7 +15629,7 @@
         <v>319</v>
       </c>
       <c r="B267" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C267">
         <f t="shared" ca="1" si="5"/>
@@ -15681,7 +15684,7 @@
       </c>
       <c r="C268">
         <f t="shared" ca="1" si="5"/>
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="D268" t="s">
         <v>184</v>
@@ -15728,7 +15731,7 @@
         <v>321</v>
       </c>
       <c r="B269" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C269">
         <f t="shared" ca="1" si="5"/>
@@ -15779,7 +15782,7 @@
         <v>322</v>
       </c>
       <c r="B270" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C270">
         <f t="shared" ca="1" si="5"/>
@@ -15834,7 +15837,7 @@
       </c>
       <c r="C271">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D271" t="s">
         <v>184</v>
@@ -15881,7 +15884,7 @@
         <v>324</v>
       </c>
       <c r="B272" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C272">
         <f t="shared" ca="1" si="5"/>
@@ -15932,7 +15935,7 @@
         <v>325</v>
       </c>
       <c r="B273" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C273">
         <f t="shared" ca="1" si="5"/>
@@ -15983,7 +15986,7 @@
         <v>326</v>
       </c>
       <c r="B274" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C274">
         <f t="shared" ca="1" si="5"/>
@@ -16034,7 +16037,7 @@
         <v>327</v>
       </c>
       <c r="B275" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C275">
         <f t="shared" ca="1" si="5"/>
@@ -16085,7 +16088,7 @@
         <v>328</v>
       </c>
       <c r="B276" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C276">
         <f t="shared" ca="1" si="5"/>
@@ -16136,7 +16139,7 @@
         <v>329</v>
       </c>
       <c r="B277" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C277">
         <f t="shared" ca="1" si="5"/>
@@ -16187,7 +16190,7 @@
         <v>330</v>
       </c>
       <c r="B278" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C278">
         <f t="shared" ca="1" si="5"/>
@@ -16238,7 +16241,7 @@
         <v>331</v>
       </c>
       <c r="B279" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C279">
         <f t="shared" ca="1" si="5"/>
@@ -16289,7 +16292,7 @@
         <v>332</v>
       </c>
       <c r="B280" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C280">
         <f t="shared" ca="1" si="5"/>
@@ -16340,11 +16343,11 @@
         <v>333</v>
       </c>
       <c r="B281" s="2">
-        <v>46314</v>
+        <v>46323</v>
       </c>
       <c r="C281">
         <f t="shared" ca="1" si="5"/>
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="D281" t="s">
         <v>184</v>
@@ -16391,7 +16394,7 @@
         <v>334</v>
       </c>
       <c r="B282" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C282">
         <f t="shared" ca="1" si="5"/>
@@ -16446,7 +16449,7 @@
       </c>
       <c r="C283">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D283" t="s">
         <v>184</v>
@@ -16493,7 +16496,7 @@
         <v>336</v>
       </c>
       <c r="B284" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C284">
         <f t="shared" ca="1" si="5"/>
@@ -16544,7 +16547,7 @@
         <v>337</v>
       </c>
       <c r="B285" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C285">
         <f t="shared" ca="1" si="5"/>
@@ -16595,7 +16598,7 @@
         <v>338</v>
       </c>
       <c r="B286" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C286">
         <f t="shared" ca="1" si="5"/>
@@ -16650,7 +16653,7 @@
       </c>
       <c r="C287">
         <f t="shared" ca="1" si="5"/>
-        <v>-232</v>
+        <v>-233</v>
       </c>
       <c r="D287" t="s">
         <v>184</v>
@@ -16697,11 +16700,11 @@
         <v>340</v>
       </c>
       <c r="B288" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C288">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D288" t="s">
         <v>184</v>
@@ -16748,11 +16751,11 @@
         <v>341</v>
       </c>
       <c r="B289" s="2">
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="C289">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D289" t="s">
         <v>184</v>
@@ -16799,7 +16802,7 @@
         <v>342</v>
       </c>
       <c r="B290" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C290">
         <f t="shared" ca="1" si="5"/>
@@ -16850,7 +16853,7 @@
         <v>343</v>
       </c>
       <c r="B291" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C291">
         <f t="shared" ca="1" si="5"/>
@@ -16901,7 +16904,7 @@
         <v>344</v>
       </c>
       <c r="B292" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C292">
         <f t="shared" ca="1" si="5"/>
@@ -16952,7 +16955,7 @@
         <v>345</v>
       </c>
       <c r="B293" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C293">
         <f t="shared" ca="1" si="5"/>
@@ -17003,7 +17006,7 @@
         <v>346</v>
       </c>
       <c r="B294" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C294">
         <f t="shared" ca="1" si="5"/>
@@ -17054,7 +17057,7 @@
         <v>347</v>
       </c>
       <c r="B295" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C295">
         <f t="shared" ca="1" si="5"/>
@@ -17109,7 +17112,7 @@
       </c>
       <c r="C296">
         <f t="shared" ca="1" si="5"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D296" t="s">
         <v>184</v>
@@ -17156,7 +17159,7 @@
         <v>349</v>
       </c>
       <c r="B297" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C297">
         <f t="shared" ca="1" si="5"/>
@@ -17207,7 +17210,7 @@
         <v>350</v>
       </c>
       <c r="B298" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C298">
         <f t="shared" ca="1" si="5"/>
@@ -17258,7 +17261,7 @@
         <v>351</v>
       </c>
       <c r="B299" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C299">
         <f t="shared" ca="1" si="5"/>
@@ -17309,11 +17312,11 @@
         <v>352</v>
       </c>
       <c r="B300" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C300">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D300" t="s">
         <v>184</v>
@@ -17360,7 +17363,7 @@
         <v>353</v>
       </c>
       <c r="B301" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C301">
         <f t="shared" ca="1" si="5"/>
@@ -17411,7 +17414,7 @@
         <v>354</v>
       </c>
       <c r="B302" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C302">
         <f t="shared" ca="1" si="5"/>
@@ -17462,7 +17465,7 @@
         <v>355</v>
       </c>
       <c r="B303" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C303">
         <f t="shared" ca="1" si="5"/>
@@ -17513,11 +17516,11 @@
         <v>356</v>
       </c>
       <c r="B304" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C304">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D304" t="s">
         <v>184</v>
@@ -17564,11 +17567,11 @@
         <v>357</v>
       </c>
       <c r="B305" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C305">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D305" t="s">
         <v>184</v>
@@ -17615,11 +17618,11 @@
         <v>358</v>
       </c>
       <c r="B306" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C306">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D306" t="s">
         <v>184</v>
@@ -17670,7 +17673,7 @@
       </c>
       <c r="C307">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D307" t="s">
         <v>184</v>
@@ -17721,7 +17724,7 @@
       </c>
       <c r="C308">
         <f t="shared" ca="1" si="5"/>
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="D308" t="s">
         <v>184</v>
@@ -17772,7 +17775,7 @@
       </c>
       <c r="C309">
         <f t="shared" ca="1" si="5"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D309" t="s">
         <v>184</v>
@@ -17823,7 +17826,7 @@
       </c>
       <c r="C310">
         <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D310" t="s">
         <v>184</v>
@@ -17870,7 +17873,7 @@
         <v>363</v>
       </c>
       <c r="B311" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C311">
         <f t="shared" ca="1" si="5"/>
@@ -17925,7 +17928,7 @@
       </c>
       <c r="C312">
         <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D312" t="s">
         <v>184</v>
@@ -17972,7 +17975,7 @@
         <v>365</v>
       </c>
       <c r="B313" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C313">
         <f t="shared" ca="1" si="5"/>
@@ -18023,7 +18026,7 @@
         <v>366</v>
       </c>
       <c r="B314" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C314">
         <f t="shared" ca="1" si="5"/>
@@ -18074,7 +18077,7 @@
         <v>367</v>
       </c>
       <c r="B315" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C315">
         <f t="shared" ca="1" si="5"/>
@@ -18125,7 +18128,7 @@
         <v>368</v>
       </c>
       <c r="B316" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C316">
         <f t="shared" ca="1" si="5"/>
@@ -18180,7 +18183,7 @@
       </c>
       <c r="C317">
         <f t="shared" ca="1" si="5"/>
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="D317" t="s">
         <v>184</v>
@@ -18227,7 +18230,7 @@
         <v>370</v>
       </c>
       <c r="B318" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C318">
         <f t="shared" ca="1" si="5"/>
@@ -18282,7 +18285,7 @@
       </c>
       <c r="C319">
         <f t="shared" ca="1" si="5"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D319" t="s">
         <v>184</v>
@@ -18329,7 +18332,7 @@
         <v>372</v>
       </c>
       <c r="B320" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C320">
         <f t="shared" ref="C320:C383" ca="1" si="6">B320-$R$1</f>
@@ -18384,7 +18387,7 @@
       </c>
       <c r="C321">
         <f t="shared" ca="1" si="6"/>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="D321" t="s">
         <v>184</v>
@@ -18435,7 +18438,7 @@
       </c>
       <c r="C322">
         <f t="shared" ca="1" si="6"/>
-        <v>-83</v>
+        <v>-84</v>
       </c>
       <c r="D322" t="s">
         <v>184</v>
@@ -18482,7 +18485,7 @@
         <v>375</v>
       </c>
       <c r="B323" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C323">
         <f t="shared" ca="1" si="6"/>
@@ -18533,7 +18536,7 @@
         <v>376</v>
       </c>
       <c r="B324" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C324">
         <f t="shared" ca="1" si="6"/>
@@ -18584,7 +18587,7 @@
         <v>377</v>
       </c>
       <c r="B325" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C325">
         <f t="shared" ca="1" si="6"/>
@@ -18635,7 +18638,7 @@
         <v>378</v>
       </c>
       <c r="B326" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C326">
         <f t="shared" ca="1" si="6"/>
@@ -18690,7 +18693,7 @@
       </c>
       <c r="C327">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D327" t="s">
         <v>184</v>
@@ -18741,7 +18744,7 @@
       </c>
       <c r="C328">
         <f t="shared" ca="1" si="6"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D328" t="s">
         <v>184</v>
@@ -18788,7 +18791,7 @@
         <v>381</v>
       </c>
       <c r="B329" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C329">
         <f t="shared" ca="1" si="6"/>
@@ -18839,7 +18842,7 @@
         <v>382</v>
       </c>
       <c r="B330" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C330">
         <f t="shared" ca="1" si="6"/>
@@ -18894,7 +18897,7 @@
       </c>
       <c r="C331">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D331" t="s">
         <v>184</v>
@@ -18941,11 +18944,11 @@
         <v>384</v>
       </c>
       <c r="B332" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C332">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D332" t="s">
         <v>184</v>
@@ -18992,7 +18995,7 @@
         <v>385</v>
       </c>
       <c r="B333" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C333">
         <f t="shared" ca="1" si="6"/>
@@ -19047,7 +19050,7 @@
       </c>
       <c r="C334">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D334" t="s">
         <v>184</v>
@@ -19094,11 +19097,11 @@
         <v>387</v>
       </c>
       <c r="B335" s="2">
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="C335">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D335" t="s">
         <v>184</v>
@@ -19145,7 +19148,7 @@
         <v>388</v>
       </c>
       <c r="B336" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C336">
         <f t="shared" ca="1" si="6"/>
@@ -19196,7 +19199,7 @@
         <v>389</v>
       </c>
       <c r="B337" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C337">
         <f t="shared" ca="1" si="6"/>
@@ -19251,7 +19254,7 @@
       </c>
       <c r="C338">
         <f t="shared" ca="1" si="6"/>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="D338" t="s">
         <v>184</v>
@@ -19298,11 +19301,11 @@
         <v>391</v>
       </c>
       <c r="B339" s="2">
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="C339">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D339" t="s">
         <v>184</v>
@@ -19349,7 +19352,7 @@
         <v>392</v>
       </c>
       <c r="B340" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C340">
         <f t="shared" ca="1" si="6"/>
@@ -19400,7 +19403,7 @@
         <v>393</v>
       </c>
       <c r="B341" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C341">
         <f t="shared" ca="1" si="6"/>
@@ -19455,7 +19458,7 @@
       </c>
       <c r="C342">
         <f t="shared" ca="1" si="6"/>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="D342" t="s">
         <v>184</v>
@@ -19502,7 +19505,7 @@
         <v>395</v>
       </c>
       <c r="B343" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C343">
         <f t="shared" ca="1" si="6"/>
@@ -19553,7 +19556,7 @@
         <v>396</v>
       </c>
       <c r="B344" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C344">
         <f t="shared" ca="1" si="6"/>
@@ -19604,7 +19607,7 @@
         <v>397</v>
       </c>
       <c r="B345" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C345">
         <f t="shared" ca="1" si="6"/>
@@ -19655,7 +19658,7 @@
         <v>398</v>
       </c>
       <c r="B346" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C346">
         <f t="shared" ca="1" si="6"/>
@@ -19710,7 +19713,7 @@
       </c>
       <c r="C347">
         <f t="shared" ca="1" si="6"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D347" t="s">
         <v>184</v>
@@ -19757,7 +19760,7 @@
         <v>400</v>
       </c>
       <c r="B348" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C348">
         <f t="shared" ca="1" si="6"/>
@@ -19812,7 +19815,7 @@
       </c>
       <c r="C349">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D349" t="s">
         <v>184</v>
@@ -19863,7 +19866,7 @@
       </c>
       <c r="C350">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D350" t="s">
         <v>184</v>
@@ -19914,7 +19917,7 @@
       </c>
       <c r="C351">
         <f t="shared" ca="1" si="6"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="D351" t="s">
         <v>184</v>
@@ -19961,11 +19964,11 @@
         <v>404</v>
       </c>
       <c r="B352" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C352">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D352" t="s">
         <v>184</v>
@@ -20012,11 +20015,11 @@
         <v>405</v>
       </c>
       <c r="B353" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C353">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D353" t="s">
         <v>184</v>
@@ -20063,11 +20066,11 @@
         <v>406</v>
       </c>
       <c r="B354" s="2">
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="C354">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D354" t="s">
         <v>184</v>
@@ -20114,7 +20117,7 @@
         <v>407</v>
       </c>
       <c r="B355" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C355">
         <f t="shared" ca="1" si="6"/>
@@ -20169,7 +20172,7 @@
       </c>
       <c r="C356">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D356" t="s">
         <v>184</v>
@@ -20216,7 +20219,7 @@
         <v>409</v>
       </c>
       <c r="B357" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C357">
         <f t="shared" ca="1" si="6"/>
@@ -20271,7 +20274,7 @@
       </c>
       <c r="C358">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D358" t="s">
         <v>184</v>
@@ -20318,11 +20321,11 @@
         <v>411</v>
       </c>
       <c r="B359" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C359">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D359" t="s">
         <v>184</v>
@@ -20373,7 +20376,7 @@
       </c>
       <c r="C360">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D360" t="s">
         <v>184</v>
@@ -20420,11 +20423,11 @@
         <v>413</v>
       </c>
       <c r="B361" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C361">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D361" t="s">
         <v>184</v>
@@ -20475,7 +20478,7 @@
       </c>
       <c r="C362">
         <f t="shared" ca="1" si="6"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="D362" t="s">
         <v>184</v>
@@ -20522,7 +20525,7 @@
         <v>415</v>
       </c>
       <c r="B363" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C363">
         <f t="shared" ca="1" si="6"/>
@@ -20573,7 +20576,7 @@
         <v>416</v>
       </c>
       <c r="B364" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C364">
         <f t="shared" ca="1" si="6"/>
@@ -20624,7 +20627,7 @@
         <v>417</v>
       </c>
       <c r="B365" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C365">
         <f t="shared" ca="1" si="6"/>
@@ -20675,7 +20678,7 @@
         <v>418</v>
       </c>
       <c r="B366" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C366">
         <f t="shared" ca="1" si="6"/>
@@ -20726,7 +20729,7 @@
         <v>419</v>
       </c>
       <c r="B367" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C367">
         <f t="shared" ca="1" si="6"/>
@@ -20777,7 +20780,7 @@
         <v>420</v>
       </c>
       <c r="B368" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C368">
         <f t="shared" ca="1" si="6"/>
@@ -20828,7 +20831,7 @@
         <v>421</v>
       </c>
       <c r="B369" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C369">
         <f t="shared" ca="1" si="6"/>
@@ -20879,11 +20882,11 @@
         <v>422</v>
       </c>
       <c r="B370" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C370">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D370" t="s">
         <v>184</v>
@@ -20934,7 +20937,7 @@
       </c>
       <c r="C371">
         <f t="shared" ca="1" si="6"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D371" t="s">
         <v>184</v>
@@ -20985,7 +20988,7 @@
       </c>
       <c r="C372">
         <f t="shared" ca="1" si="6"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="D372" t="s">
         <v>184</v>
@@ -21032,7 +21035,7 @@
         <v>425</v>
       </c>
       <c r="B373" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C373">
         <f t="shared" ca="1" si="6"/>
@@ -21083,11 +21086,11 @@
         <v>426</v>
       </c>
       <c r="B374" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C374">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D374" t="s">
         <v>184</v>
@@ -21134,11 +21137,11 @@
         <v>427</v>
       </c>
       <c r="B375" s="2">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="C375">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D375" t="s">
         <v>184</v>
@@ -21185,7 +21188,7 @@
         <v>428</v>
       </c>
       <c r="B376" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C376">
         <f t="shared" ca="1" si="6"/>
@@ -21236,7 +21239,7 @@
         <v>429</v>
       </c>
       <c r="B377" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C377">
         <f t="shared" ca="1" si="6"/>
@@ -21291,7 +21294,7 @@
       </c>
       <c r="C378">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D378" t="s">
         <v>184</v>
@@ -21342,7 +21345,7 @@
       </c>
       <c r="C379">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D379" t="s">
         <v>184</v>
@@ -21389,7 +21392,7 @@
         <v>432</v>
       </c>
       <c r="B380" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C380">
         <f t="shared" ca="1" si="6"/>
@@ -21440,7 +21443,7 @@
         <v>433</v>
       </c>
       <c r="B381" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C381">
         <f t="shared" ca="1" si="6"/>
@@ -21495,7 +21498,7 @@
       </c>
       <c r="C382">
         <f t="shared" ca="1" si="6"/>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="D382" t="s">
         <v>184</v>
@@ -21546,7 +21549,7 @@
       </c>
       <c r="C383">
         <f t="shared" ca="1" si="6"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D383" t="s">
         <v>184</v>
@@ -21597,7 +21600,7 @@
       </c>
       <c r="C384">
         <f t="shared" ref="C384:C391" ca="1" si="7">B384-$R$1</f>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="D384" t="s">
         <v>184</v>
@@ -21648,7 +21651,7 @@
       </c>
       <c r="C385">
         <f t="shared" ca="1" si="7"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D385" t="s">
         <v>184</v>
@@ -21699,7 +21702,7 @@
       </c>
       <c r="C386">
         <f t="shared" ca="1" si="7"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D386" t="s">
         <v>184</v>
@@ -21750,7 +21753,7 @@
       </c>
       <c r="C387">
         <f t="shared" ca="1" si="7"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D387" t="s">
         <v>184</v>
@@ -21801,7 +21804,7 @@
       </c>
       <c r="C388">
         <f t="shared" ca="1" si="7"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D388" t="s">
         <v>184</v>
@@ -21852,7 +21855,7 @@
       </c>
       <c r="C389">
         <f t="shared" ca="1" si="7"/>
-        <v>-46323</v>
+        <v>-46324</v>
       </c>
       <c r="D389" t="s">
         <v>184</v>
@@ -21899,7 +21902,7 @@
         <v>442</v>
       </c>
       <c r="B390" s="2">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C390">
         <f t="shared" ca="1" si="7"/>
@@ -21954,7 +21957,7 @@
       </c>
       <c r="C391">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D391" t="s">
         <v>184</v>
@@ -22002,27 +22005,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006F4802EAABF65E4BAAC603EC7F0DCC44" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c310cddf71992cf9237b6768f3dad3b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xmlns:ns3="a6b958bc-5708-46f2-92f1-bce61d011186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a175c140041af67bda373d2162dd419d" ns2:_="" ns3:_="">
     <xsd:import namespace="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
@@ -22283,26 +22265,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
-    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="a6b958bc-5708-46f2-92f1-bce61d011186" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3de46e4f-e4f7-4f2d-9405-5f3152497b0a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33441B8A-5AA1-47A1-A1DA-726E9F61DB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22319,4 +22303,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282D203E-C74B-4DE1-8719-2ECAB83F6933}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8024B45-775F-4EC1-A55D-56BA361D2067}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3de46e4f-e4f7-4f2d-9405-5f3152497b0a"/>
+    <ds:schemaRef ds:uri="a6b958bc-5708-46f2-92f1-bce61d011186"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>